--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NEFTy Ranking" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NEFTy Ranking'!$A$1:$K$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NEFTy Ranking'!$A$1:$L$96</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,12 +61,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
+        <fgColor rgb="00E2F0D9"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E2F0D9"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
     <fill>
@@ -176,10 +176,10 @@
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -569,7 +569,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K96"/>
+  <dimension ref="A1:L96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -583,6 +583,7 @@
     <col width="12" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="12" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -613,32 +614,37 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>18m</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>12m</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>12-1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>6m</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>3m</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>1m</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>1d</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>18m</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>12m</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>12-1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>6m</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>1m</t>
         </is>
       </c>
     </row>
@@ -667,22 +673,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
+        <v>1.204180602006689</v>
+      </c>
+      <c r="G2" s="3" t="n">
+        <v>1.215294117647059</v>
+      </c>
+      <c r="H2" s="4" t="n">
+        <v>2.156638655462185</v>
+      </c>
+      <c r="I2" s="3" t="n">
+        <v>0.4170070952483338</v>
+      </c>
+      <c r="J2" s="5" t="n">
+        <v>-0.01398862956313585</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>-0.2982110531359812</v>
+      </c>
+      <c r="L2" s="5" t="n">
         <v>-0.04871535796766746</v>
-      </c>
-      <c r="G2" s="4" t="n">
-        <v>1.204180602006689</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>1.215294117647059</v>
-      </c>
-      <c r="I2" s="5" t="n">
-        <v>2.156638655462185</v>
-      </c>
-      <c r="J2" s="4" t="n">
-        <v>0.4170070952483338</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>-0.2982110531359812</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -710,22 +719,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
+        <v>1.498922046976058</v>
+      </c>
+      <c r="G3" s="3" t="n">
+        <v>1.277220556302347</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1.94643780374315</v>
+      </c>
+      <c r="I3" s="3" t="n">
+        <v>0.4483098776798631</v>
+      </c>
+      <c r="J3" s="3" t="n">
+        <v>0.03142562757587108</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>-0.2271275662396912</v>
+      </c>
+      <c r="L3" s="5" t="n">
         <v>-0.03475631136044888</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>1.498922046976058</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>1.277220556302347</v>
-      </c>
-      <c r="I3" s="6" t="n">
-        <v>1.94643780374315</v>
-      </c>
-      <c r="J3" s="4" t="n">
-        <v>0.4483098776798631</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>-0.2271275662396912</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -753,22 +765,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
+        <v>1.773824130879345</v>
+      </c>
+      <c r="G4" s="3" t="n">
+        <v>1.285810583080552</v>
+      </c>
+      <c r="H4" s="8" t="n">
+        <v>1.875294910684193</v>
+      </c>
+      <c r="I4" s="3" t="n">
+        <v>0.5923925804179382</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.1341137123745819</v>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>-0.2050169968350722</v>
+      </c>
+      <c r="L4" s="5" t="n">
         <v>-0.03058890794739855</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>1.773824130879345</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>1.285810583080552</v>
-      </c>
-      <c r="I4" s="8" t="n">
-        <v>1.875294910684193</v>
-      </c>
-      <c r="J4" s="4" t="n">
-        <v>0.5923925804179382</v>
-      </c>
-      <c r="K4" s="3" t="n">
-        <v>-0.2050169968350722</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -792,22 +807,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
+        <v>2.338891977024272</v>
+      </c>
+      <c r="G5" s="3" t="n">
+        <v>1.474934761708556</v>
+      </c>
+      <c r="H5" s="10" t="n">
+        <v>1.772970745776679</v>
+      </c>
+      <c r="I5" s="3" t="n">
+        <v>0.4721019524548646</v>
+      </c>
+      <c r="J5" s="3" t="n">
+        <v>0.1209256033839263</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>-0.1074789499752353</v>
+      </c>
+      <c r="L5" s="5" t="n">
         <v>-0.01065114746897988</v>
-      </c>
-      <c r="G5" s="4" t="n">
-        <v>2.338891977024272</v>
-      </c>
-      <c r="H5" s="4" t="n">
-        <v>1.474934761708556</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>1.772970745776679</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0.4721019524548646</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>-0.1074789499752353</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -831,22 +849,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
+        <v>1.331728785586577</v>
+      </c>
+      <c r="G6" s="3" t="n">
+        <v>1.118985126859143</v>
+      </c>
+      <c r="H6" s="3" t="n">
+        <v>1.669499645877599</v>
+      </c>
+      <c r="I6" s="3" t="n">
+        <v>0.468726537684089</v>
+      </c>
+      <c r="J6" s="3" t="n">
+        <v>0.102245145631068</v>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>-0.2062238591672388</v>
+      </c>
+      <c r="L6" s="5" t="n">
         <v>-0.03199284395637847</v>
-      </c>
-      <c r="G6" s="4" t="n">
-        <v>1.331728785586577</v>
-      </c>
-      <c r="H6" s="4" t="n">
-        <v>1.118985126859143</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>1.669499645877599</v>
-      </c>
-      <c r="J6" s="4" t="n">
-        <v>0.468726537684089</v>
-      </c>
-      <c r="K6" s="3" t="n">
-        <v>-0.2062238591672388</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -874,22 +895,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
+        <v>1.285569620253165</v>
+      </c>
+      <c r="G7" s="3" t="n">
+        <v>1.042996152975786</v>
+      </c>
+      <c r="H7" s="3" t="n">
+        <v>1.536773025571396</v>
+      </c>
+      <c r="I7" s="3" t="n">
+        <v>0.4327884462783687</v>
+      </c>
+      <c r="J7" s="3" t="n">
+        <v>0.09231699939503923</v>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>-0.1946476360392506</v>
+      </c>
+      <c r="L7" s="5" t="n">
         <v>-0.03505771697306548</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1.285569620253165</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>1.042996152975786</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>1.536773025571396</v>
-      </c>
-      <c r="J7" s="4" t="n">
-        <v>0.4327884462783687</v>
-      </c>
-      <c r="K7" s="3" t="n">
-        <v>-0.1946476360392506</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -917,22 +941,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
+        <v>1.270380100155981</v>
+      </c>
+      <c r="G8" s="3" t="n">
+        <v>0.9153334718470811</v>
+      </c>
+      <c r="H8" s="3" t="n">
+        <v>1.271244546021193</v>
+      </c>
+      <c r="I8" s="3" t="n">
+        <v>0.3709165716551828</v>
+      </c>
+      <c r="J8" s="3" t="n">
+        <v>0.09154957372908101</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>-0.1567031057037003</v>
+      </c>
+      <c r="L8" s="5" t="n">
         <v>-0.03471204188481669</v>
-      </c>
-      <c r="G8" s="4" t="n">
-        <v>1.270380100155981</v>
-      </c>
-      <c r="H8" s="4" t="n">
-        <v>0.9153334718470811</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>1.271244546021193</v>
-      </c>
-      <c r="J8" s="4" t="n">
-        <v>0.3709165716551828</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>-0.1567031057037003</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -960,22 +987,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
+        <v>0.8787354902445046</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>0.8562713518789653</v>
+      </c>
+      <c r="H9" s="3" t="n">
+        <v>0.9102000976085898</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>0.08749106504646154</v>
+      </c>
+      <c r="J9" s="5" t="n">
+        <v>-0.1379193109700816</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>-0.02823198773633118</v>
+      </c>
+      <c r="L9" s="5" t="n">
         <v>-0.01374303124594844</v>
-      </c>
-      <c r="G9" s="4" t="n">
-        <v>0.8787354902445046</v>
-      </c>
-      <c r="H9" s="4" t="n">
-        <v>0.8562713518789653</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>0.9102000976085898</v>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>0.08749106504646154</v>
-      </c>
-      <c r="K9" s="3" t="n">
-        <v>-0.02823198773633118</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1003,22 +1033,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
+        <v>1.097181729834791</v>
+      </c>
+      <c r="G10" s="3" t="n">
+        <v>0.8488690884167238</v>
+      </c>
+      <c r="H10" s="3" t="n">
+        <v>0.8610349554489376</v>
+      </c>
+      <c r="I10" s="3" t="n">
+        <v>0.5853658536585367</v>
+      </c>
+      <c r="J10" s="3" t="n">
+        <v>0.200489541611037</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>-0.006537151275204822</v>
+      </c>
+      <c r="L10" s="5" t="n">
         <v>-0.006720058915584914</v>
-      </c>
-      <c r="G10" s="4" t="n">
-        <v>1.097181729834791</v>
-      </c>
-      <c r="H10" s="4" t="n">
-        <v>0.8488690884167238</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>0.8610349554489376</v>
-      </c>
-      <c r="J10" s="4" t="n">
-        <v>0.5853658536585367</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>-0.006537151275204822</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1042,22 +1075,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
+        <v>0.7522391280889176</v>
+      </c>
+      <c r="G11" s="3" t="n">
+        <v>0.8956339014709316</v>
+      </c>
+      <c r="H11" s="3" t="n">
+        <v>0.8474200326873687</v>
+      </c>
+      <c r="I11" s="3" t="n">
+        <v>0.3016432865731462</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.2364273204903675</v>
+      </c>
+      <c r="K11" s="3" t="n">
+        <v>0.02609794628751971</v>
+      </c>
+      <c r="L11" s="5" t="n">
         <v>-0.03477382155382513</v>
-      </c>
-      <c r="G11" s="4" t="n">
-        <v>0.7522391280889176</v>
-      </c>
-      <c r="H11" s="4" t="n">
-        <v>0.8956339014709316</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>0.8474200326873687</v>
-      </c>
-      <c r="J11" s="4" t="n">
-        <v>0.3016432865731462</v>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0.02609794628751971</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1085,22 +1121,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
+        <v>1.473022524882137</v>
+      </c>
+      <c r="G12" s="3" t="n">
+        <v>1.193263646922184</v>
+      </c>
+      <c r="H12" s="3" t="n">
+        <v>0.7879210220673636</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0.1133121094210587</v>
+      </c>
+      <c r="J12" s="3" t="n">
+        <v>0.1860319055395052</v>
+      </c>
+      <c r="K12" s="3" t="n">
+        <v>0.2267117058594257</v>
+      </c>
+      <c r="L12" s="5" t="n">
         <v>-0.02104717470191808</v>
-      </c>
-      <c r="G12" s="4" t="n">
-        <v>1.473022524882137</v>
-      </c>
-      <c r="H12" s="4" t="n">
-        <v>1.193263646922184</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>0.7879210220673636</v>
-      </c>
-      <c r="J12" s="4" t="n">
-        <v>0.1133121094210587</v>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0.2267117058594257</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1128,22 +1167,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
+        <v>0.4580972263644496</v>
+      </c>
+      <c r="G13" s="3" t="n">
+        <v>0.3853782941343158</v>
+      </c>
+      <c r="H13" s="3" t="n">
+        <v>0.7376027203173705</v>
+      </c>
+      <c r="I13" s="5" t="n">
+        <v>-0.007511165245635332</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>-0.1664109121909633</v>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>-0.2027071102413568</v>
+      </c>
+      <c r="L13" s="5" t="n">
         <v>-0.03283877349159237</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>0.4580972263644496</v>
-      </c>
-      <c r="H13" s="4" t="n">
-        <v>0.3853782941343158</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>0.7376027203173705</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>-0.007511165245635332</v>
-      </c>
-      <c r="K13" s="3" t="n">
-        <v>-0.2027071102413568</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1171,22 +1213,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
+        <v>1.291459781529295</v>
+      </c>
+      <c r="G14" s="3" t="n">
+        <v>0.8972250770811923</v>
+      </c>
+      <c r="H14" s="3" t="n">
+        <v>0.7163412127440905</v>
+      </c>
+      <c r="I14" s="3" t="n">
+        <v>0.0658198614318708</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.1629078997102178</v>
+      </c>
+      <c r="K14" s="3" t="n">
+        <v>0.1053892215568861</v>
+      </c>
+      <c r="L14" s="5" t="n">
         <v>-0.02265988987717071</v>
-      </c>
-      <c r="G14" s="4" t="n">
-        <v>1.291459781529295</v>
-      </c>
-      <c r="H14" s="4" t="n">
-        <v>0.8972250770811923</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>0.7163412127440905</v>
-      </c>
-      <c r="J14" s="4" t="n">
-        <v>0.0658198614318708</v>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0.1053892215568861</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1210,22 +1255,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
+        <v>1.866146285053484</v>
+      </c>
+      <c r="G15" s="3" t="n">
+        <v>1.094212082805238</v>
+      </c>
+      <c r="H15" s="3" t="n">
+        <v>0.6362484157160961</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0.05132555673382821</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.1192142695868141</v>
+      </c>
+      <c r="K15" s="3" t="n">
+        <v>0.2798863929770206</v>
+      </c>
+      <c r="L15" s="5" t="n">
         <v>-0.03878223773511735</v>
-      </c>
-      <c r="G15" s="4" t="n">
-        <v>1.866146285053484</v>
-      </c>
-      <c r="H15" s="4" t="n">
-        <v>1.094212082805238</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>0.6362484157160961</v>
-      </c>
-      <c r="J15" s="4" t="n">
-        <v>0.05132555673382821</v>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0.2798863929770206</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1253,22 +1301,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
+        <v>0.4918032786885245</v>
+      </c>
+      <c r="G16" s="3" t="n">
+        <v>0.4402332361516033</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>0.606413994169096</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0.07591785936527695</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>-0.07737459978655281</v>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>-0.1034482758620691</v>
+      </c>
+      <c r="L16" s="5" t="n">
         <v>-0.006607296753806446</v>
-      </c>
-      <c r="G16" s="4" t="n">
-        <v>0.4918032786885245</v>
-      </c>
-      <c r="H16" s="4" t="n">
-        <v>0.4402332361516033</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>0.606413994169096</v>
-      </c>
-      <c r="J16" s="4" t="n">
-        <v>0.07591785936527695</v>
-      </c>
-      <c r="K16" s="3" t="n">
-        <v>-0.1034482758620691</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1292,22 +1343,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
+        <v>1.105226236408278</v>
+      </c>
+      <c r="G17" s="3" t="n">
+        <v>0.8013205282112845</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>0.6047418967587035</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>-0.2044008483563096</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>-0.09960996099609953</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.1224985973443053</v>
+      </c>
+      <c r="L17" s="5" t="n">
         <v>-0.04381073761350962</v>
-      </c>
-      <c r="G17" s="4" t="n">
-        <v>1.105226236408278</v>
-      </c>
-      <c r="H17" s="4" t="n">
-        <v>0.8013205282112845</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>0.6047418967587035</v>
-      </c>
-      <c r="J17" s="3" t="n">
-        <v>-0.2044008483563096</v>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0.1224985973443053</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1334,23 +1388,26 @@
           <t>Dry Bulk Freight</t>
         </is>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="3" t="n">
+        <v>1.689774696707106</v>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v>1.097297297297297</v>
+      </c>
+      <c r="H18" s="3" t="n">
+        <v>0.6040540540540538</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.3460537727666957</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.3242320819112627</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.3074978938500421</v>
+      </c>
+      <c r="L18" s="3" t="n">
         <v>0.04723346828609976</v>
-      </c>
-      <c r="G18" s="4" t="n">
-        <v>1.689774696707106</v>
-      </c>
-      <c r="H18" s="4" t="n">
-        <v>1.097297297297297</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>0.6040540540540538</v>
-      </c>
-      <c r="J18" s="4" t="n">
-        <v>0.3460537727666957</v>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0.3074978938500421</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1378,22 +1435,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
+        <v>0.5888324873096447</v>
+      </c>
+      <c r="G19" s="3" t="n">
+        <v>0.475106154635808</v>
+      </c>
+      <c r="H19" s="3" t="n">
+        <v>0.5617096729037376</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.3422069375451109</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0.1856505269474553</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>-0.05545430099495052</v>
+      </c>
+      <c r="L19" s="5" t="n">
         <v>-0.01749751367478869</v>
-      </c>
-      <c r="G19" s="4" t="n">
-        <v>0.5888324873096447</v>
-      </c>
-      <c r="H19" s="4" t="n">
-        <v>0.475106154635808</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>0.5617096729037376</v>
-      </c>
-      <c r="J19" s="4" t="n">
-        <v>0.3422069375451109</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>-0.05545430099495052</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1417,22 +1477,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
+        <v>0.3800579856296484</v>
+      </c>
+      <c r="G20" s="3" t="n">
+        <v>0.2557926129846295</v>
+      </c>
+      <c r="H20" s="3" t="n">
+        <v>0.5284468914888736</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>-0.006533575317604345</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>-0.1372054535424383</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>-0.1783864915572232</v>
+      </c>
+      <c r="L20" s="5" t="n">
         <v>-0.02926050718212447</v>
-      </c>
-      <c r="G20" s="4" t="n">
-        <v>0.3800579856296484</v>
-      </c>
-      <c r="H20" s="4" t="n">
-        <v>0.2557926129846295</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>0.5284468914888736</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>-0.006533575317604345</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>-0.1783864915572232</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1459,23 +1522,26 @@
           <t>Oil Services</t>
         </is>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="3" t="n">
+        <v>0.5103625072212594</v>
+      </c>
+      <c r="G21" s="3" t="n">
+        <v>0.7163548334153946</v>
+      </c>
+      <c r="H21" s="3" t="n">
+        <v>0.5264647956671589</v>
+      </c>
+      <c r="I21" s="3" t="n">
+        <v>0.2006946238410976</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>-0.06677226485811172</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.1243985700077952</v>
+      </c>
+      <c r="L21" s="3" t="n">
         <v>0.008097361127846758</v>
-      </c>
-      <c r="G21" s="4" t="n">
-        <v>0.5103625072212594</v>
-      </c>
-      <c r="H21" s="4" t="n">
-        <v>0.7163548334153946</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>0.5264647956671589</v>
-      </c>
-      <c r="J21" s="4" t="n">
-        <v>0.2006946238410976</v>
-      </c>
-      <c r="K21" s="4" t="n">
-        <v>0.1243985700077952</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1503,22 +1569,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
+        <v>0.8639455782312926</v>
+      </c>
+      <c r="G22" s="3" t="n">
+        <v>0.7133923918707661</v>
+      </c>
+      <c r="H22" s="3" t="n">
+        <v>0.5151120375195413</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0.1277653918710342</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.06753246753246755</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.1308684436801377</v>
+      </c>
+      <c r="L22" s="5" t="n">
         <v>-0.01350135013501341</v>
-      </c>
-      <c r="G22" s="4" t="n">
-        <v>0.8639455782312926</v>
-      </c>
-      <c r="H22" s="4" t="n">
-        <v>0.7133923918707661</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>0.5151120375195413</v>
-      </c>
-      <c r="J22" s="4" t="n">
-        <v>0.1277653918710342</v>
-      </c>
-      <c r="K22" s="4" t="n">
-        <v>0.1308684436801377</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1546,22 +1615,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
+        <v>1.002360876897133</v>
+      </c>
+      <c r="G23" s="3" t="n">
+        <v>0.6194762684124386</v>
+      </c>
+      <c r="H23" s="3" t="n">
+        <v>0.458401527550464</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0.0001684636118597371</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>8.422471153024524e-05</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0.1104460862246328</v>
+      </c>
+      <c r="L23" s="5" t="n">
         <v>-0.03463414634146345</v>
-      </c>
-      <c r="G23" s="4" t="n">
-        <v>1.002360876897133</v>
-      </c>
-      <c r="H23" s="4" t="n">
-        <v>0.6194762684124386</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>0.458401527550464</v>
-      </c>
-      <c r="J23" s="4" t="n">
-        <v>0.0001684636118597371</v>
-      </c>
-      <c r="K23" s="4" t="n">
-        <v>0.1104460862246328</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1588,23 +1660,26 @@
           <t>Japan Hedged Equity</t>
         </is>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="3" t="n">
+        <v>0.6314883594528489</v>
+      </c>
+      <c r="G24" s="3" t="n">
+        <v>0.5088806970509383</v>
+      </c>
+      <c r="H24" s="3" t="n">
+        <v>0.4537533512064345</v>
+      </c>
+      <c r="I24" s="3" t="n">
+        <v>0.1792051332416684</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0.1112482260751528</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.03792070078377119</v>
+      </c>
+      <c r="L24" s="3" t="n">
         <v>0.005246706854208583</v>
-      </c>
-      <c r="G24" s="4" t="n">
-        <v>0.6314883594528489</v>
-      </c>
-      <c r="H24" s="4" t="n">
-        <v>0.5088806970509383</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>0.4537533512064345</v>
-      </c>
-      <c r="J24" s="4" t="n">
-        <v>0.1792051332416684</v>
-      </c>
-      <c r="K24" s="4" t="n">
-        <v>0.03792070078377119</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1628,22 +1703,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
+        <v>0.6089593622736331</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.4134886199284462</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.4502550049478573</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0.2905893800389214</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.1642006269592475</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>-0.02535166911610331</v>
+      </c>
+      <c r="L25" s="5" t="n">
         <v>-0.01548168177721232</v>
-      </c>
-      <c r="G25" s="4" t="n">
-        <v>0.6089593622736331</v>
-      </c>
-      <c r="H25" s="4" t="n">
-        <v>0.4134886199284462</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>0.4502550049478573</v>
-      </c>
-      <c r="J25" s="4" t="n">
-        <v>0.2905893800389214</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>-0.02535166911610331</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1671,22 +1749,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
+        <v>0.5069234097793163</v>
+      </c>
+      <c r="G26" s="3" t="n">
+        <v>0.5738927387767401</v>
+      </c>
+      <c r="H26" s="3" t="n">
+        <v>0.4325851159987948</v>
+      </c>
+      <c r="I26" s="3" t="n">
+        <v>0.2117960911674301</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0.2386626356037702</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.0986382039013618</v>
+      </c>
+      <c r="L26" s="5" t="n">
         <v>-0.02723463687150851</v>
-      </c>
-      <c r="G26" s="4" t="n">
-        <v>0.5069234097793163</v>
-      </c>
-      <c r="H26" s="4" t="n">
-        <v>0.5738927387767401</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>0.4325851159987948</v>
-      </c>
-      <c r="J26" s="4" t="n">
-        <v>0.2117960911674301</v>
-      </c>
-      <c r="K26" s="4" t="n">
-        <v>0.0986382039013618</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1714,22 +1795,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
+        <v>0.3678517639541781</v>
+      </c>
+      <c r="G27" s="3" t="n">
+        <v>0.2421152969455842</v>
+      </c>
+      <c r="H27" s="3" t="n">
+        <v>0.4208214182104522</v>
+      </c>
+      <c r="I27" s="3" t="n">
+        <v>0.1712454570323185</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.05539122473413616</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>-0.125776623982732</v>
+      </c>
+      <c r="L27" s="5" t="n">
         <v>-0.01485718042270667</v>
-      </c>
-      <c r="G27" s="4" t="n">
-        <v>0.3678517639541781</v>
-      </c>
-      <c r="H27" s="4" t="n">
-        <v>0.2421152969455842</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>0.4208214182104522</v>
-      </c>
-      <c r="J27" s="4" t="n">
-        <v>0.1712454570323185</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>-0.125776623982732</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1753,22 +1837,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
+        <v>0.2819168850617746</v>
+      </c>
+      <c r="G28" s="3" t="n">
+        <v>0.3297087378640777</v>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v>0.4031067961165049</v>
+      </c>
+      <c r="I28" s="3" t="n">
+        <v>0.1398135818908124</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0.05613818630475009</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>-0.0523110988098533</v>
+      </c>
+      <c r="L28" s="5" t="n">
         <v>-0.01524302559677881</v>
-      </c>
-      <c r="G28" s="4" t="n">
-        <v>0.2819168850617746</v>
-      </c>
-      <c r="H28" s="4" t="n">
-        <v>0.3297087378640777</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>0.4031067961165049</v>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>0.1398135818908124</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>-0.0523110988098533</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1792,22 +1879,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
+        <v>0.4672131147540983</v>
+      </c>
+      <c r="G29" s="3" t="n">
+        <v>0.2687354136053246</v>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v>0.3963177456997147</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0.224493200967715</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0.09709245833021907</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>-0.09137055837563446</v>
+      </c>
+      <c r="L29" s="5" t="n">
         <v>-0.01224764468371464</v>
-      </c>
-      <c r="G29" s="4" t="n">
-        <v>0.4672131147540983</v>
-      </c>
-      <c r="H29" s="4" t="n">
-        <v>0.2687354136053246</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>0.3963177456997147</v>
-      </c>
-      <c r="J29" s="4" t="n">
-        <v>0.224493200967715</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>-0.09137055837563446</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1835,22 +1925,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
+        <v>0.5732448174359617</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0.3854723953449892</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0.3911532733991505</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>0.2663205121742198</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.1517124386777313</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>-0.004083574515323374</v>
+      </c>
+      <c r="L30" s="5" t="n">
         <v>-0.01028328277057644</v>
-      </c>
-      <c r="G30" s="4" t="n">
-        <v>0.5732448174359617</v>
-      </c>
-      <c r="H30" s="4" t="n">
-        <v>0.3854723953449892</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>0.3911532733991505</v>
-      </c>
-      <c r="J30" s="4" t="n">
-        <v>0.2663205121742198</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>-0.004083574515323374</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1878,22 +1971,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
+        <v>0.5621933936552928</v>
+      </c>
+      <c r="G31" s="3" t="n">
+        <v>0.3930203169048314</v>
+      </c>
+      <c r="H31" s="3" t="n">
+        <v>0.3880626032857002</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0.285432364549695</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.1635743575169504</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.003571678688983893</v>
+      </c>
+      <c r="L31" s="5" t="n">
         <v>-0.01528946916337393</v>
-      </c>
-      <c r="G31" s="4" t="n">
-        <v>0.5621933936552928</v>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>0.3930203169048314</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>0.3880626032857002</v>
-      </c>
-      <c r="J31" s="4" t="n">
-        <v>0.285432364549695</v>
-      </c>
-      <c r="K31" s="4" t="n">
-        <v>0.003571678688983893</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -1917,22 +2013,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
+        <v>0.5577322262584328</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.3911481867686246</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.3847758081334722</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.2843084821906086</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.1636945144407829</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.004601740294511325</v>
+      </c>
+      <c r="L32" s="5" t="n">
         <v>-0.01509310146829634</v>
-      </c>
-      <c r="G32" s="4" t="n">
-        <v>0.5577322262584328</v>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>0.3911481867686246</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>0.3847758081334722</v>
-      </c>
-      <c r="J32" s="4" t="n">
-        <v>0.2843084821906086</v>
-      </c>
-      <c r="K32" s="4" t="n">
-        <v>0.004601740294511325</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -1960,22 +2059,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
+        <v>0.3640054127198917</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>0.2937590245467672</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>0.3742980908069951</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0.1141199226305609</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>-0.01236987140232704</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>-0.05860378239551711</v>
+      </c>
+      <c r="L33" s="5" t="n">
         <v>-0.01885874193940862</v>
-      </c>
-      <c r="G33" s="4" t="n">
-        <v>0.3640054127198917</v>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>0.2937590245467672</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>0.3742980908069951</v>
-      </c>
-      <c r="J33" s="4" t="n">
-        <v>0.1141199226305609</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>-0.05860378239551711</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2003,22 +2105,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
+        <v>0.4917073170731707</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>0.2601215617595549</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>0.3621098176573607</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-0.01291155584247905</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>-0.05023681962885318</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>-0.0748752079866889</v>
+      </c>
+      <c r="L34" s="5" t="n">
         <v>-0.01481958762886604</v>
-      </c>
-      <c r="G34" s="4" t="n">
-        <v>0.4917073170731707</v>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>0.2601215617595549</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>0.3621098176573607</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>-0.01291155584247905</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>-0.0748752079866889</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2046,22 +2151,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
+        <v>0.2761779663871207</v>
+      </c>
+      <c r="G35" s="3" t="n">
+        <v>0.3059107358262969</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>0.3577804583835946</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.1266018493741268</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0.05287873735689685</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>-0.03820184790334036</v>
+      </c>
+      <c r="L35" s="5" t="n">
         <v>-0.02065133109330564</v>
-      </c>
-      <c r="G35" s="4" t="n">
-        <v>0.2761779663871207</v>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>0.3059107358262969</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>0.3577804583835946</v>
-      </c>
-      <c r="J35" s="4" t="n">
-        <v>0.1266018493741268</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>-0.03820184790334036</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2089,22 +2197,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
+        <v>0.4920209734412402</v>
+      </c>
+      <c r="G36" s="3" t="n">
+        <v>0.2089683199408887</v>
+      </c>
+      <c r="H36" s="3" t="n">
+        <v>0.3105661771497183</v>
+      </c>
+      <c r="I36" s="5" t="n">
+        <v>-0.04092174677608429</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.01022613259242111</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>-0.07752211142041654</v>
+      </c>
+      <c r="L36" s="5" t="n">
         <v>-0.01601202781432054</v>
-      </c>
-      <c r="G36" s="4" t="n">
-        <v>0.4920209734412402</v>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>0.2089683199408887</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>0.3105661771497183</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>-0.04092174677608429</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>-0.07752211142041654</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2132,22 +2243,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
+        <v>0.172548419199265</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.1744364361294279</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.3045545161785002</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>0.09188765326489867</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>-0.0416692736032036</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>-0.09974138944398736</v>
+      </c>
+      <c r="L37" s="5" t="n">
         <v>-0.02408410321758525</v>
-      </c>
-      <c r="G37" s="4" t="n">
-        <v>0.172548419199265</v>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>0.1744364361294279</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>0.3045545161785002</v>
-      </c>
-      <c r="J37" s="4" t="n">
-        <v>0.09188765326489867</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>-0.09974138944398736</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2171,22 +2285,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
+        <v>0.3717092036990943</v>
+      </c>
+      <c r="G38" s="3" t="n">
+        <v>0.2679952567211199</v>
+      </c>
+      <c r="H38" s="3" t="n">
+        <v>0.303339763897984</v>
+      </c>
+      <c r="I38" s="3" t="n">
+        <v>0.1520575039799315</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0.07291760265971781</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>-0.02711841390548619</v>
+      </c>
+      <c r="L38" s="5" t="n">
         <v>-0.006489994591671211</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>0.3717092036990943</v>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>0.2679952567211199</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>0.303339763897984</v>
-      </c>
-      <c r="J38" s="4" t="n">
-        <v>0.1520575039799315</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>-0.02711841390548619</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2210,22 +2327,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
+        <v>0.3721568445043955</v>
+      </c>
+      <c r="G39" s="3" t="n">
+        <v>0.2684353097992003</v>
+      </c>
+      <c r="H39" s="3" t="n">
+        <v>0.3027045620673348</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0.1521187268111697</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0.07311749727173522</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>-0.02630623494075335</v>
+      </c>
+      <c r="L39" s="5" t="n">
         <v>-0.00646638825272805</v>
-      </c>
-      <c r="G39" s="4" t="n">
-        <v>0.3721568445043955</v>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>0.2684353097992003</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>0.3027045620673348</v>
-      </c>
-      <c r="J39" s="4" t="n">
-        <v>0.1521187268111697</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>-0.02630623494075335</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2249,22 +2369,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
+        <v>0.2057160481134983</v>
+      </c>
+      <c r="G40" s="3" t="n">
+        <v>0.2459364708382024</v>
+      </c>
+      <c r="H40" s="3" t="n">
+        <v>0.2950175289493253</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>0.1246643651706942</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.0503940769047051</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>-0.03789991796554559</v>
+      </c>
+      <c r="L40" s="5" t="n">
         <v>-0.01983507911745042</v>
-      </c>
-      <c r="G40" s="4" t="n">
-        <v>0.2057160481134983</v>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>0.2459364708382024</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>0.2950175289493253</v>
-      </c>
-      <c r="J40" s="4" t="n">
-        <v>0.1246643651706942</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>-0.03789991796554559</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2288,22 +2411,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
+        <v>0.3078742019389928</v>
+      </c>
+      <c r="G41" s="3" t="n">
+        <v>0.2105493543444956</v>
+      </c>
+      <c r="H41" s="3" t="n">
+        <v>0.2895600787918582</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0.08985221674876853</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>-0.02606092621940481</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>-0.06126951799049563</v>
+      </c>
+      <c r="L41" s="5" t="n">
         <v>-0.01337852301105957</v>
-      </c>
-      <c r="G41" s="4" t="n">
-        <v>0.3078742019389928</v>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>0.2105493543444956</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>0.2895600787918582</v>
-      </c>
-      <c r="J41" s="4" t="n">
-        <v>0.08985221674876853</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>-0.06126951799049563</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2327,22 +2453,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
+        <v>0.4629555466559874</v>
+      </c>
+      <c r="G42" s="3" t="n">
+        <v>0.2995375311277126</v>
+      </c>
+      <c r="H42" s="3" t="n">
+        <v>0.2673425827107792</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>0.1036253776435045</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0.06191860465116283</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0.02540350877192976</v>
+      </c>
+      <c r="L42" s="5" t="n">
         <v>-0.004903296104603605</v>
-      </c>
-      <c r="G42" s="4" t="n">
-        <v>0.4629555466559874</v>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>0.2995375311277126</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>0.2673425827107792</v>
-      </c>
-      <c r="J42" s="4" t="n">
-        <v>0.1036253776435045</v>
-      </c>
-      <c r="K42" s="4" t="n">
-        <v>0.02540350877192976</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2369,23 +2498,26 @@
           <t>Shipping</t>
         </is>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="3" t="n">
+        <v>0.7707881417208964</v>
+      </c>
+      <c r="G43" s="3" t="n">
+        <v>0.6294078509647372</v>
+      </c>
+      <c r="H43" s="3" t="n">
+        <v>0.2611443779108449</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>0.3677743647025968</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.1813796430294259</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.2920073859140069</v>
+      </c>
+      <c r="L43" s="3" t="n">
         <v>0.0004084967320261423</v>
-      </c>
-      <c r="G43" s="4" t="n">
-        <v>0.7707881417208964</v>
-      </c>
-      <c r="H43" s="4" t="n">
-        <v>0.6294078509647372</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>0.2611443779108449</v>
-      </c>
-      <c r="J43" s="4" t="n">
-        <v>0.3677743647025968</v>
-      </c>
-      <c r="K43" s="4" t="n">
-        <v>0.2920073859140069</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2412,23 +2544,26 @@
           <t>Small Cap Value</t>
         </is>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="3" t="n">
+        <v>0.3112672863296306</v>
+      </c>
+      <c r="G44" s="3" t="n">
+        <v>0.4388059701492537</v>
+      </c>
+      <c r="H44" s="3" t="n">
+        <v>0.258955223880597</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0.2745702952842661</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.2052510939779122</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.142857142857143</v>
+      </c>
+      <c r="L44" s="3" t="n">
         <v>0.002426343154246169</v>
-      </c>
-      <c r="G44" s="4" t="n">
-        <v>0.3112672863296306</v>
-      </c>
-      <c r="H44" s="4" t="n">
-        <v>0.4388059701492537</v>
-      </c>
-      <c r="I44" s="4" t="n">
-        <v>0.258955223880597</v>
-      </c>
-      <c r="J44" s="4" t="n">
-        <v>0.2745702952842661</v>
-      </c>
-      <c r="K44" s="4" t="n">
-        <v>0.142857142857143</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2451,23 +2586,26 @@
           <t>Fundamental Equity</t>
         </is>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="3" t="n">
+        <v>0.3199350385708486</v>
+      </c>
+      <c r="G45" s="3" t="n">
+        <v>0.3156616754350463</v>
+      </c>
+      <c r="H45" s="3" t="n">
+        <v>0.2585997571833265</v>
+      </c>
+      <c r="I45" s="3" t="n">
+        <v>0.1455250176180409</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0.08042539049518105</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0.0453376205787781</v>
+      </c>
+      <c r="L45" s="3" t="n">
         <v>0.001540357362908029</v>
-      </c>
-      <c r="G45" s="4" t="n">
-        <v>0.3199350385708486</v>
-      </c>
-      <c r="H45" s="4" t="n">
-        <v>0.3156616754350463</v>
-      </c>
-      <c r="I45" s="4" t="n">
-        <v>0.2585997571833265</v>
-      </c>
-      <c r="J45" s="4" t="n">
-        <v>0.1455250176180409</v>
-      </c>
-      <c r="K45" s="4" t="n">
-        <v>0.0453376205787781</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2491,22 +2629,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
+        <v>0.3481020857624044</v>
+      </c>
+      <c r="G46" s="3" t="n">
+        <v>0.2508714989782426</v>
+      </c>
+      <c r="H46" s="3" t="n">
+        <v>0.2407741315061906</v>
+      </c>
+      <c r="I46" s="3" t="n">
+        <v>0.1270442976280732</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0.06032198899531283</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.008137957760123937</v>
+      </c>
+      <c r="L46" s="5" t="n">
         <v>-0.004401071565250603</v>
-      </c>
-      <c r="G46" s="4" t="n">
-        <v>0.3481020857624044</v>
-      </c>
-      <c r="H46" s="4" t="n">
-        <v>0.2508714989782426</v>
-      </c>
-      <c r="I46" s="4" t="n">
-        <v>0.2407741315061906</v>
-      </c>
-      <c r="J46" s="4" t="n">
-        <v>0.1270442976280732</v>
-      </c>
-      <c r="K46" s="4" t="n">
-        <v>0.008137957760123937</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2530,22 +2671,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
+        <v>0.2989010989010989</v>
+      </c>
+      <c r="G47" s="3" t="n">
+        <v>0.2494714587737843</v>
+      </c>
+      <c r="H47" s="3" t="n">
+        <v>0.2402219873150104</v>
+      </c>
+      <c r="I47" s="3" t="n">
+        <v>0.1044148563419762</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0.07259528130671522</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0.007457916045173762</v>
+      </c>
+      <c r="L47" s="5" t="n">
         <v>-0.000422832980972454</v>
-      </c>
-      <c r="G47" s="4" t="n">
-        <v>0.2989010989010989</v>
-      </c>
-      <c r="H47" s="4" t="n">
-        <v>0.2494714587737843</v>
-      </c>
-      <c r="I47" s="4" t="n">
-        <v>0.2402219873150104</v>
-      </c>
-      <c r="J47" s="4" t="n">
-        <v>0.1044148563419762</v>
-      </c>
-      <c r="K47" s="4" t="n">
-        <v>0.007457916045173762</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2573,22 +2717,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
+        <v>0.1853602688628726</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.329136988570482</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.2382391916514826</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>0.1172375382901698</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.1780077809586729</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.07340891608976285</v>
+      </c>
+      <c r="L48" s="5" t="n">
         <v>-0.006100393274084293</v>
-      </c>
-      <c r="G48" s="4" t="n">
-        <v>0.1853602688628726</v>
-      </c>
-      <c r="H48" s="4" t="n">
-        <v>0.329136988570482</v>
-      </c>
-      <c r="I48" s="4" t="n">
-        <v>0.2382391916514826</v>
-      </c>
-      <c r="J48" s="4" t="n">
-        <v>0.1172375382901698</v>
-      </c>
-      <c r="K48" s="4" t="n">
-        <v>0.07340891608976285</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2612,22 +2759,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
+        <v>0.4869076510410013</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.184231943031536</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.2330620549338758</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0.001893450382993267</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0.06524524158125922</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>-0.03960069301212765</v>
+      </c>
+      <c r="L49" s="5" t="n">
         <v>-0.006147016135917394</v>
-      </c>
-      <c r="G49" s="4" t="n">
-        <v>0.4869076510410013</v>
-      </c>
-      <c r="H49" s="4" t="n">
-        <v>0.184231943031536</v>
-      </c>
-      <c r="I49" s="4" t="n">
-        <v>0.2330620549338758</v>
-      </c>
-      <c r="J49" s="4" t="n">
-        <v>0.001893450382993267</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>-0.03960069301212765</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2654,23 +2804,26 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="F50" s="4" t="n">
+      <c r="F50" s="3" t="n">
+        <v>0.4281323303405322</v>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0.4418946508779094</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>0.2260514495712536</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0.2279018012379166</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0.0411605142115814</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0.1760474255645108</v>
+      </c>
+      <c r="L50" s="3" t="n">
         <v>0.004665983839763355</v>
-      </c>
-      <c r="G50" s="4" t="n">
-        <v>0.4281323303405322</v>
-      </c>
-      <c r="H50" s="4" t="n">
-        <v>0.4418946508779094</v>
-      </c>
-      <c r="I50" s="4" t="n">
-        <v>0.2260514495712536</v>
-      </c>
-      <c r="J50" s="4" t="n">
-        <v>0.2279018012379166</v>
-      </c>
-      <c r="K50" s="4" t="n">
-        <v>0.1760474255645108</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2694,22 +2847,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
+        <v>0.2803758583303215</v>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0.1653180711795277</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0.2185382540622327</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0.07072050290135379</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0.01466376446328321</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>-0.04367543054580791</v>
+      </c>
+      <c r="L51" s="5" t="n">
         <v>-0.009284116331096381</v>
-      </c>
-      <c r="G51" s="4" t="n">
-        <v>0.2803758583303215</v>
-      </c>
-      <c r="H51" s="4" t="n">
-        <v>0.1653180711795277</v>
-      </c>
-      <c r="I51" s="4" t="n">
-        <v>0.2185382540622327</v>
-      </c>
-      <c r="J51" s="4" t="n">
-        <v>0.07072050290135379</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>-0.04367543054580791</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2732,23 +2888,26 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="F52" s="4" t="n">
+      <c r="F52" s="3" t="n">
+        <v>0.4303970789593792</v>
+      </c>
+      <c r="G52" s="3" t="n">
+        <v>0.4372850263700987</v>
+      </c>
+      <c r="H52" s="3" t="n">
+        <v>0.2178399449667507</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0.2278158667972576</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0.05079631181894384</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0.1801920542270758</v>
+      </c>
+      <c r="L52" s="3" t="n">
         <v>0.006261037084604348</v>
-      </c>
-      <c r="G52" s="4" t="n">
-        <v>0.4303970789593792</v>
-      </c>
-      <c r="H52" s="4" t="n">
-        <v>0.4372850263700987</v>
-      </c>
-      <c r="I52" s="4" t="n">
-        <v>0.2178399449667507</v>
-      </c>
-      <c r="J52" s="4" t="n">
-        <v>0.2278158667972576</v>
-      </c>
-      <c r="K52" s="4" t="n">
-        <v>0.1801920542270758</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2772,22 +2931,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
+        <v>0.5853981463968223</v>
+      </c>
+      <c r="G53" s="3" t="n">
+        <v>0.3517174649250121</v>
+      </c>
+      <c r="H53" s="3" t="n">
+        <v>0.2177068214804065</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>-0.080921052631579</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-0.03488773747841112</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0.1100516487882397</v>
+      </c>
+      <c r="L53" s="5" t="n">
         <v>-0.03232509812976236</v>
-      </c>
-      <c r="G53" s="4" t="n">
-        <v>0.5853981463968223</v>
-      </c>
-      <c r="H53" s="4" t="n">
-        <v>0.3517174649250121</v>
-      </c>
-      <c r="I53" s="4" t="n">
-        <v>0.2177068214804065</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>-0.080921052631579</v>
-      </c>
-      <c r="K53" s="4" t="n">
-        <v>0.1100516487882397</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2811,22 +2973,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
+        <v>0.5814124381188117</v>
+      </c>
+      <c r="G54" s="3" t="n">
+        <v>0.349650118827568</v>
+      </c>
+      <c r="H54" s="3" t="n">
+        <v>0.2159360971745445</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>-0.08104281379930334</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>-0.03486286172874486</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0.1099679678592758</v>
+      </c>
+      <c r="L54" s="5" t="n">
         <v>-0.03244202555608144</v>
-      </c>
-      <c r="G54" s="4" t="n">
-        <v>0.5814124381188117</v>
-      </c>
-      <c r="H54" s="4" t="n">
-        <v>0.349650118827568</v>
-      </c>
-      <c r="I54" s="4" t="n">
-        <v>0.2159360971745445</v>
-      </c>
-      <c r="J54" s="3" t="n">
-        <v>-0.08104281379930334</v>
-      </c>
-      <c r="K54" s="4" t="n">
-        <v>0.1099679678592758</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -2853,23 +3018,26 @@
           <t>Banks</t>
         </is>
       </c>
-      <c r="F55" s="4" t="n">
+      <c r="F55" s="3" t="n">
+        <v>0.1629013079667063</v>
+      </c>
+      <c r="G55" s="3" t="n">
+        <v>0.2177161152614726</v>
+      </c>
+      <c r="H55" s="3" t="n">
+        <v>0.2134471718249733</v>
+      </c>
+      <c r="I55" s="3" t="n">
+        <v>0.07692307692307687</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.06652126499454747</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0.003518029903254005</v>
+      </c>
+      <c r="L55" s="3" t="n">
         <v>0.0005846243788365513</v>
-      </c>
-      <c r="G55" s="4" t="n">
-        <v>0.1629013079667063</v>
-      </c>
-      <c r="H55" s="4" t="n">
-        <v>0.2177161152614726</v>
-      </c>
-      <c r="I55" s="4" t="n">
-        <v>0.2134471718249733</v>
-      </c>
-      <c r="J55" s="4" t="n">
-        <v>0.07692307692307687</v>
-      </c>
-      <c r="K55" s="4" t="n">
-        <v>0.003518029903254005</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -2897,22 +3065,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
+        <v>0.4098183929015671</v>
+      </c>
+      <c r="G56" s="3" t="n">
+        <v>0.1644520547945205</v>
+      </c>
+      <c r="H56" s="3" t="n">
+        <v>0.2099315068493151</v>
+      </c>
+      <c r="I56" s="5" t="n">
+        <v>-0.02617711078015816</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0.01528814571513881</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>-0.03758845174073033</v>
+      </c>
+      <c r="L56" s="5" t="n">
         <v>-0.009785077756421456</v>
-      </c>
-      <c r="G56" s="4" t="n">
-        <v>0.4098183929015671</v>
-      </c>
-      <c r="H56" s="4" t="n">
-        <v>0.1644520547945205</v>
-      </c>
-      <c r="I56" s="4" t="n">
-        <v>0.2099315068493151</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>-0.02617711078015816</v>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>-0.03758845174073033</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -2939,23 +3110,26 @@
           <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
-      <c r="F57" s="4" t="n">
+      <c r="F57" s="3" t="n">
+        <v>0.3859570661896243</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0.4509559110417478</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0.2037456106125632</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0.3258699372504277</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0.04337579260423086</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0.2053675612602102</v>
+      </c>
+      <c r="L57" s="3" t="n">
         <v>0.002534102550277639</v>
-      </c>
-      <c r="G57" s="4" t="n">
-        <v>0.3859570661896243</v>
-      </c>
-      <c r="H57" s="4" t="n">
-        <v>0.4509559110417478</v>
-      </c>
-      <c r="I57" s="4" t="n">
-        <v>0.2037456106125632</v>
-      </c>
-      <c r="J57" s="4" t="n">
-        <v>0.3258699372504277</v>
-      </c>
-      <c r="K57" s="4" t="n">
-        <v>0.2053675612602102</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -2979,22 +3153,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
+        <v>0.3691441441441441</v>
+      </c>
+      <c r="G58" s="3" t="n">
+        <v>0.2206827309236947</v>
+      </c>
+      <c r="H58" s="3" t="n">
+        <v>0.1985943775100403</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0.07650079688330091</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>0.0315628712031224</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>0.01842854749539291</v>
+      </c>
+      <c r="L58" s="5" t="n">
         <v>-0.00360596623504339</v>
-      </c>
-      <c r="G58" s="4" t="n">
-        <v>0.3691441441441441</v>
-      </c>
-      <c r="H58" s="4" t="n">
-        <v>0.2206827309236947</v>
-      </c>
-      <c r="I58" s="4" t="n">
-        <v>0.1985943775100403</v>
-      </c>
-      <c r="J58" s="4" t="n">
-        <v>0.07650079688330091</v>
-      </c>
-      <c r="K58" s="4" t="n">
-        <v>0.01842854749539291</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3017,23 +3194,26 @@
           <t>Dividend</t>
         </is>
       </c>
-      <c r="F59" s="4" t="n">
+      <c r="F59" s="3" t="n">
+        <v>0.2540424002874595</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0.3169811320754716</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0.1966037735849058</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>0.1703554661301139</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0.08824446523230423</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0.1005991800693786</v>
+      </c>
+      <c r="L59" s="3" t="n">
         <v>0.002009761699684143</v>
-      </c>
-      <c r="G59" s="4" t="n">
-        <v>0.2540424002874595</v>
-      </c>
-      <c r="H59" s="4" t="n">
-        <v>0.3169811320754716</v>
-      </c>
-      <c r="I59" s="4" t="n">
-        <v>0.1966037735849058</v>
-      </c>
-      <c r="J59" s="4" t="n">
-        <v>0.1703554661301139</v>
-      </c>
-      <c r="K59" s="4" t="n">
-        <v>0.1005991800693786</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3057,22 +3237,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
+        <v>0.4014565316340464</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0.3714922048997773</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0.1875278396436526</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0.2603356528857961</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>-0.009967845659164087</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>0.154913728432108</v>
+      </c>
+      <c r="L60" s="5" t="n">
         <v>-0.002268308489954629</v>
-      </c>
-      <c r="G60" s="4" t="n">
-        <v>0.4014565316340464</v>
-      </c>
-      <c r="H60" s="4" t="n">
-        <v>0.3714922048997773</v>
-      </c>
-      <c r="I60" s="4" t="n">
-        <v>0.1875278396436526</v>
-      </c>
-      <c r="J60" s="4" t="n">
-        <v>0.2603356528857961</v>
-      </c>
-      <c r="K60" s="4" t="n">
-        <v>0.154913728432108</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3096,22 +3279,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
+        <v>0.2781522780257712</v>
+      </c>
+      <c r="G61" s="3" t="n">
+        <v>0.21723864927197</v>
+      </c>
+      <c r="H61" s="3" t="n">
+        <v>0.1820763484905854</v>
+      </c>
+      <c r="I61" s="3" t="n">
+        <v>0.1116280531891485</v>
+      </c>
+      <c r="J61" s="3" t="n">
+        <v>0.07063489660601285</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>0.0297462180224517</v>
+      </c>
+      <c r="L61" s="5" t="n">
         <v>-0.002130511463844798</v>
-      </c>
-      <c r="G61" s="4" t="n">
-        <v>0.2781522780257712</v>
-      </c>
-      <c r="H61" s="4" t="n">
-        <v>0.21723864927197</v>
-      </c>
-      <c r="I61" s="4" t="n">
-        <v>0.1820763484905854</v>
-      </c>
-      <c r="J61" s="4" t="n">
-        <v>0.1116280531891485</v>
-      </c>
-      <c r="K61" s="4" t="n">
-        <v>0.0297462180224517</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3135,22 +3321,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
+        <v>0.278372270778638</v>
+      </c>
+      <c r="G62" s="3" t="n">
+        <v>0.2171718769775977</v>
+      </c>
+      <c r="H62" s="3" t="n">
+        <v>0.1814485508163524</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0.1118256571816698</v>
+      </c>
+      <c r="J62" s="3" t="n">
+        <v>0.07053404948097852</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>0.03023688685940784</v>
+      </c>
+      <c r="L62" s="5" t="n">
         <v>-0.002269485151082828</v>
-      </c>
-      <c r="G62" s="4" t="n">
-        <v>0.278372270778638</v>
-      </c>
-      <c r="H62" s="4" t="n">
-        <v>0.2171718769775977</v>
-      </c>
-      <c r="I62" s="4" t="n">
-        <v>0.1814485508163524</v>
-      </c>
-      <c r="J62" s="4" t="n">
-        <v>0.1118256571816698</v>
-      </c>
-      <c r="K62" s="4" t="n">
-        <v>0.03023688685940784</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3174,22 +3363,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
+        <v>0.2784889682775957</v>
+      </c>
+      <c r="G63" s="3" t="n">
+        <v>0.2175145692234999</v>
+      </c>
+      <c r="H63" s="3" t="n">
+        <v>0.1795400850527642</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0.1121822079622463</v>
+      </c>
+      <c r="J63" s="3" t="n">
+        <v>0.07053332779370414</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0.03219431425175934</v>
+      </c>
+      <c r="L63" s="5" t="n">
         <v>-0.002258793159083616</v>
-      </c>
-      <c r="G63" s="4" t="n">
-        <v>0.2784889682775957</v>
-      </c>
-      <c r="H63" s="4" t="n">
-        <v>0.2175145692234999</v>
-      </c>
-      <c r="I63" s="4" t="n">
-        <v>0.1795400850527642</v>
-      </c>
-      <c r="J63" s="4" t="n">
-        <v>0.1121822079622463</v>
-      </c>
-      <c r="K63" s="4" t="n">
-        <v>0.03219431425175934</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3216,23 +3408,26 @@
           <t>S&amp;P 100</t>
         </is>
       </c>
-      <c r="F64" s="4" t="n">
+      <c r="F64" s="3" t="n">
+        <v>0.2931491037479632</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0.2148301706266944</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0.166863339180354</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>0.1087146349982537</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0.0735907553551296</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0.04110749719845863</v>
+      </c>
+      <c r="L64" s="3" t="n">
         <v>5.250859828298537e-05</v>
-      </c>
-      <c r="G64" s="4" t="n">
-        <v>0.2931491037479632</v>
-      </c>
-      <c r="H64" s="4" t="n">
-        <v>0.2148301706266944</v>
-      </c>
-      <c r="I64" s="4" t="n">
-        <v>0.166863339180354</v>
-      </c>
-      <c r="J64" s="4" t="n">
-        <v>0.1087146349982537</v>
-      </c>
-      <c r="K64" s="4" t="n">
-        <v>0.04110749719845863</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3256,22 +3451,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
+        <v>0.2176671816376075</v>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0.2018188749115069</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0.1586886674290695</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0.1141457996768982</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>0.08479158474243009</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>0.03722329275743763</v>
+      </c>
+      <c r="L65" s="5" t="n">
         <v>-0.003431925942650627</v>
-      </c>
-      <c r="G65" s="4" t="n">
-        <v>0.2176671816376075</v>
-      </c>
-      <c r="H65" s="4" t="n">
-        <v>0.2018188749115069</v>
-      </c>
-      <c r="I65" s="4" t="n">
-        <v>0.1586886674290695</v>
-      </c>
-      <c r="J65" s="4" t="n">
-        <v>0.1141457996768982</v>
-      </c>
-      <c r="K65" s="4" t="n">
-        <v>0.03722329275743763</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3295,22 +3493,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
+        <v>0.2940838598506605</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0.1840756799369334</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0.1550387596899225</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0.1102624122212641</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0.07285714285714295</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>0.02513934705949272</v>
+      </c>
+      <c r="L66" s="5" t="n">
         <v>-0.003978779840848823</v>
-      </c>
-      <c r="G66" s="4" t="n">
-        <v>0.2940838598506605</v>
-      </c>
-      <c r="H66" s="4" t="n">
-        <v>0.1840756799369334</v>
-      </c>
-      <c r="I66" s="4" t="n">
-        <v>0.1550387596899225</v>
-      </c>
-      <c r="J66" s="4" t="n">
-        <v>0.1102624122212641</v>
-      </c>
-      <c r="K66" s="4" t="n">
-        <v>0.02513934705949272</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3334,22 +3535,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
+        <v>0.2697547683923707</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.1671500131821777</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.1355127867123649</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0.1031647146772987</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0.06456655043886017</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>0.02786162061759923</v>
+      </c>
+      <c r="L67" s="5" t="n">
         <v>-0.004049493813273353</v>
-      </c>
-      <c r="G67" s="4" t="n">
-        <v>0.2697547683923707</v>
-      </c>
-      <c r="H67" s="4" t="n">
-        <v>0.1671500131821777</v>
-      </c>
-      <c r="I67" s="4" t="n">
-        <v>0.1355127867123649</v>
-      </c>
-      <c r="J67" s="4" t="n">
-        <v>0.1031647146772987</v>
-      </c>
-      <c r="K67" s="4" t="n">
-        <v>0.02786162061759923</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3373,22 +3577,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
+        <v>0.07745629897528628</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0.06812070510905288</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0.1335524350164325</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>-0.04206859592711687</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>-0.070221066319896</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>-0.05772272008434365</v>
+      </c>
+      <c r="L68" s="5" t="n">
         <v>-0.01079136690647486</v>
-      </c>
-      <c r="G68" s="4" t="n">
-        <v>0.07745629897528628</v>
-      </c>
-      <c r="H68" s="4" t="n">
-        <v>0.06812070510905288</v>
-      </c>
-      <c r="I68" s="4" t="n">
-        <v>0.1335524350164325</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>-0.04206859592711687</v>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>-0.05772272008434365</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3412,22 +3619,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
+        <v>0.1995504739568064</v>
+      </c>
+      <c r="G69" s="3" t="n">
+        <v>0.1148955495004542</v>
+      </c>
+      <c r="H69" s="3" t="n">
+        <v>0.1277929155313353</v>
+      </c>
+      <c r="I69" s="3" t="n">
+        <v>0.05373851832775345</v>
+      </c>
+      <c r="J69" s="3" t="n">
+        <v>0.02917749643665646</v>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>-0.01143593460578241</v>
+      </c>
+      <c r="L69" s="5" t="n">
         <v>-0.009201711195415241</v>
-      </c>
-      <c r="G69" s="4" t="n">
-        <v>0.1995504739568064</v>
-      </c>
-      <c r="H69" s="4" t="n">
-        <v>0.1148955495004542</v>
-      </c>
-      <c r="I69" s="4" t="n">
-        <v>0.1277929155313353</v>
-      </c>
-      <c r="J69" s="4" t="n">
-        <v>0.05373851832775345</v>
-      </c>
-      <c r="K69" s="3" t="n">
-        <v>-0.01143593460578241</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3451,22 +3661,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
+        <v>0.2212821959014852</v>
+      </c>
+      <c r="G70" s="3" t="n">
+        <v>0.09952606635071093</v>
+      </c>
+      <c r="H70" s="3" t="n">
+        <v>0.1272850372376437</v>
+      </c>
+      <c r="I70" s="3" t="n">
+        <v>0.008539046731873778</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>-0.05209397344228817</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>-0.02462462462462467</v>
+      </c>
+      <c r="L70" s="5" t="n">
         <v>-0.009756097560975618</v>
-      </c>
-      <c r="G70" s="4" t="n">
-        <v>0.2212821959014852</v>
-      </c>
-      <c r="H70" s="4" t="n">
-        <v>0.09952606635071093</v>
-      </c>
-      <c r="I70" s="4" t="n">
-        <v>0.1272850372376437</v>
-      </c>
-      <c r="J70" s="4" t="n">
-        <v>0.008539046731873778</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>-0.02462462462462467</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3490,22 +3703,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
+        <v>0.2000759661950431</v>
+      </c>
+      <c r="G71" s="3" t="n">
+        <v>0.1143638127149282</v>
+      </c>
+      <c r="H71" s="3" t="n">
+        <v>0.1269729300767128</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>0.05290344080646503</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0.02948843271423907</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>-0.01118848290431118</v>
+      </c>
+      <c r="L71" s="5" t="n">
         <v>-0.009716345400407556</v>
-      </c>
-      <c r="G71" s="4" t="n">
-        <v>0.2000759661950431</v>
-      </c>
-      <c r="H71" s="4" t="n">
-        <v>0.1143638127149282</v>
-      </c>
-      <c r="I71" s="4" t="n">
-        <v>0.1269729300767128</v>
-      </c>
-      <c r="J71" s="4" t="n">
-        <v>0.05290344080646503</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>-0.01118848290431118</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3533,22 +3749,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
+        <v>0.1706349206349207</v>
+      </c>
+      <c r="G72" s="3" t="n">
+        <v>0.164402423352304</v>
+      </c>
+      <c r="H72" s="3" t="n">
+        <v>0.1225445199192217</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>0.1005552663543292</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>0.08363232530326314</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0.0372884127892712</v>
+      </c>
+      <c r="L72" s="5" t="n">
         <v>-0.004238951252060641</v>
-      </c>
-      <c r="G72" s="4" t="n">
-        <v>0.1706349206349207</v>
-      </c>
-      <c r="H72" s="4" t="n">
-        <v>0.164402423352304</v>
-      </c>
-      <c r="I72" s="4" t="n">
-        <v>0.1225445199192217</v>
-      </c>
-      <c r="J72" s="4" t="n">
-        <v>0.1005552663543292</v>
-      </c>
-      <c r="K72" s="4" t="n">
-        <v>0.0372884127892712</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3572,22 +3791,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
+        <v>0.2576449912126539</v>
+      </c>
+      <c r="G73" s="3" t="n">
+        <v>0.1839841164791529</v>
+      </c>
+      <c r="H73" s="3" t="n">
+        <v>0.1197882197220386</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0.118125</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.08720753570343365</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0.05732860520094563</v>
+      </c>
+      <c r="L73" s="5" t="n">
         <v>-0.002230897936419396</v>
-      </c>
-      <c r="G73" s="4" t="n">
-        <v>0.2576449912126539</v>
-      </c>
-      <c r="H73" s="4" t="n">
-        <v>0.1839841164791529</v>
-      </c>
-      <c r="I73" s="4" t="n">
-        <v>0.1197882197220386</v>
-      </c>
-      <c r="J73" s="4" t="n">
-        <v>0.118125</v>
-      </c>
-      <c r="K73" s="4" t="n">
-        <v>0.05732860520094563</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3614,23 +3836,26 @@
           <t>Retail</t>
         </is>
       </c>
-      <c r="F74" s="4" t="n">
+      <c r="F74" s="3" t="n">
+        <v>0.08274143302180681</v>
+      </c>
+      <c r="G74" s="3" t="n">
+        <v>0.1074432832016314</v>
+      </c>
+      <c r="H74" s="3" t="n">
+        <v>0.1182768289574305</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>0.006486736939650184</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0.0129400792725578</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>-0.009687713699566891</v>
+      </c>
+      <c r="L74" s="3" t="n">
         <v>0.003464603302921754</v>
-      </c>
-      <c r="G74" s="4" t="n">
-        <v>0.08274143302180681</v>
-      </c>
-      <c r="H74" s="4" t="n">
-        <v>0.1074432832016314</v>
-      </c>
-      <c r="I74" s="4" t="n">
-        <v>0.1182768289574305</v>
-      </c>
-      <c r="J74" s="4" t="n">
-        <v>0.006486736939650184</v>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>-0.009687713699566891</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3653,23 +3878,26 @@
           <t>Cash Flow Factor</t>
         </is>
       </c>
-      <c r="F75" s="4" t="n">
+      <c r="F75" s="3" t="n">
+        <v>0.2472006890611544</v>
+      </c>
+      <c r="G75" s="3" t="n">
+        <v>0.3009883198562444</v>
+      </c>
+      <c r="H75" s="3" t="n">
+        <v>0.1176999101527405</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>0.1626786574594508</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>0.139977956227366</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>0.1639871382636657</v>
+      </c>
+      <c r="L75" s="3" t="n">
         <v>0.004718290313627582</v>
-      </c>
-      <c r="G75" s="4" t="n">
-        <v>0.2472006890611544</v>
-      </c>
-      <c r="H75" s="4" t="n">
-        <v>0.3009883198562444</v>
-      </c>
-      <c r="I75" s="4" t="n">
-        <v>0.1176999101527405</v>
-      </c>
-      <c r="J75" s="4" t="n">
-        <v>0.1626786574594508</v>
-      </c>
-      <c r="K75" s="4" t="n">
-        <v>0.1639871382636657</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3697,22 +3925,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
+        <v>0.003912032142102007</v>
+      </c>
+      <c r="G76" s="3" t="n">
+        <v>0.2460629921259843</v>
+      </c>
+      <c r="H76" s="3" t="n">
+        <v>0.1053805774278216</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0.09680027723229778</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>0.1819992530810408</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0.1272705686809925</v>
+      </c>
+      <c r="L76" s="5" t="n">
         <v>-0.001472289410032634</v>
-      </c>
-      <c r="G76" s="4" t="n">
-        <v>0.003912032142102007</v>
-      </c>
-      <c r="H76" s="4" t="n">
-        <v>0.2460629921259843</v>
-      </c>
-      <c r="I76" s="4" t="n">
-        <v>0.1053805774278216</v>
-      </c>
-      <c r="J76" s="4" t="n">
-        <v>0.09680027723229778</v>
-      </c>
-      <c r="K76" s="4" t="n">
-        <v>0.1272705686809925</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3740,22 +3971,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
+        <v>0.08464384828862159</v>
+      </c>
+      <c r="G77" s="3" t="n">
+        <v>0.1340829403941484</v>
+      </c>
+      <c r="H77" s="3" t="n">
+        <v>0.1038568492322574</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>-0.04480651731160901</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0.02952475030183299</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0.02738225629791891</v>
+      </c>
+      <c r="L77" s="5" t="n">
         <v>-0.003717472118959231</v>
-      </c>
-      <c r="G77" s="4" t="n">
-        <v>0.08464384828862159</v>
-      </c>
-      <c r="H77" s="4" t="n">
-        <v>0.1340829403941484</v>
-      </c>
-      <c r="I77" s="4" t="n">
-        <v>0.1038568492322574</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>-0.04480651731160901</v>
-      </c>
-      <c r="K77" s="4" t="n">
-        <v>0.02738225629791891</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -3782,23 +4016,26 @@
           <t>Insurance</t>
         </is>
       </c>
-      <c r="F78" s="4" t="n">
+      <c r="F78" s="3" t="n">
+        <v>0.1257856754869249</v>
+      </c>
+      <c r="G78" s="3" t="n">
+        <v>0.1381501529771711</v>
+      </c>
+      <c r="H78" s="3" t="n">
+        <v>0.1026908292147173</v>
+      </c>
+      <c r="I78" s="3" t="n">
+        <v>0.09082706766917292</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0.09643288996372457</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0.03215708594194666</v>
+      </c>
+      <c r="L78" s="3" t="n">
         <v>0.003180749550546258</v>
-      </c>
-      <c r="G78" s="4" t="n">
-        <v>0.1257856754869249</v>
-      </c>
-      <c r="H78" s="4" t="n">
-        <v>0.1381501529771711</v>
-      </c>
-      <c r="I78" s="4" t="n">
-        <v>0.1026908292147173</v>
-      </c>
-      <c r="J78" s="4" t="n">
-        <v>0.09082706766917292</v>
-      </c>
-      <c r="K78" s="4" t="n">
-        <v>0.03215708594194666</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -3825,23 +4062,26 @@
           <t>Consumer Discretionary</t>
         </is>
       </c>
-      <c r="F79" s="4" t="n">
+      <c r="F79" s="3" t="n">
+        <v>0.008502138339010035</v>
+      </c>
+      <c r="G79" s="3" t="n">
+        <v>0.06561857343868382</v>
+      </c>
+      <c r="H79" s="3" t="n">
+        <v>0.073195150990367</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-0.01347729151531851</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.0005843792875654952</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>-0.007059832076851347</v>
+      </c>
+      <c r="L79" s="3" t="n">
         <v>0.01015775298191612</v>
-      </c>
-      <c r="G79" s="4" t="n">
-        <v>0.008502138339010035</v>
-      </c>
-      <c r="H79" s="4" t="n">
-        <v>0.06561857343868382</v>
-      </c>
-      <c r="I79" s="4" t="n">
-        <v>0.073195150990367</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>-0.01347729151531851</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>-0.007059832076851347</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -3869,22 +4109,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
+        <v>0.1130065975494816</v>
+      </c>
+      <c r="G80" s="3" t="n">
+        <v>0.1353715988847226</v>
+      </c>
+      <c r="H80" s="3" t="n">
+        <v>0.06095567733871743</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>-0.03157290470723306</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.07462007462007469</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.07014046216583614</v>
+      </c>
+      <c r="L80" s="5" t="n">
         <v>-0.003375812304835746</v>
-      </c>
-      <c r="G80" s="4" t="n">
-        <v>0.1130065975494816</v>
-      </c>
-      <c r="H80" s="4" t="n">
-        <v>0.1353715988847226</v>
-      </c>
-      <c r="I80" s="4" t="n">
-        <v>0.06095567733871743</v>
-      </c>
-      <c r="J80" s="3" t="n">
-        <v>-0.03157290470723306</v>
-      </c>
-      <c r="K80" s="4" t="n">
-        <v>0.07014046216583614</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -3908,22 +4151,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
+        <v>0.09732922444786851</v>
+      </c>
+      <c r="G81" s="5" t="n">
+        <v>-0.002567693744164434</v>
+      </c>
+      <c r="H81" s="3" t="n">
+        <v>0.05835667600373484</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>-0.01202312138728334</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>-0.08794023479188906</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>-0.05756506396118233</v>
+      </c>
+      <c r="L81" s="5" t="n">
         <v>-0.01042149143121818</v>
-      </c>
-      <c r="G81" s="4" t="n">
-        <v>0.09732922444786851</v>
-      </c>
-      <c r="H81" s="3" t="n">
-        <v>-0.002567693744164434</v>
-      </c>
-      <c r="I81" s="4" t="n">
-        <v>0.05835667600373484</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>-0.01202312138728334</v>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>-0.05756506396118233</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -3951,22 +4197,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
+        <v>0.1205353841603196</v>
+      </c>
+      <c r="G82" s="3" t="n">
+        <v>0.0407995054605399</v>
+      </c>
+      <c r="H82" s="3" t="n">
+        <v>0.05192664331341446</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0.09403992635644931</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0.06505007907221927</v>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>-0.01057786483839374</v>
+      </c>
+      <c r="L82" s="5" t="n">
         <v>-0.01286603042246182</v>
-      </c>
-      <c r="G82" s="4" t="n">
-        <v>0.1205353841603196</v>
-      </c>
-      <c r="H82" s="4" t="n">
-        <v>0.0407995054605399</v>
-      </c>
-      <c r="I82" s="4" t="n">
-        <v>0.05192664331341446</v>
-      </c>
-      <c r="J82" s="4" t="n">
-        <v>0.09403992635644931</v>
-      </c>
-      <c r="K82" s="3" t="n">
-        <v>-0.01057786483839374</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -3993,23 +4242,26 @@
           <t>Inverse Euro</t>
         </is>
       </c>
-      <c r="F83" s="4" t="n">
+      <c r="F83" s="5" t="n">
+        <v>-0.1397079874033782</v>
+      </c>
+      <c r="G83" s="3" t="n">
+        <v>0.02245661789724407</v>
+      </c>
+      <c r="H83" s="3" t="n">
+        <v>0.04185096971759106</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0.07359771346909616</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.04412786657400969</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>-0.01861528412802094</v>
+      </c>
+      <c r="L83" s="3" t="n">
         <v>0.01212529471202428</v>
-      </c>
-      <c r="G83" s="3" t="n">
-        <v>-0.1397079874033782</v>
-      </c>
-      <c r="H83" s="4" t="n">
-        <v>0.02245661789724407</v>
-      </c>
-      <c r="I83" s="4" t="n">
-        <v>0.04185096971759106</v>
-      </c>
-      <c r="J83" s="4" t="n">
-        <v>0.07359771346909616</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>-0.01861528412802094</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4032,23 +4284,26 @@
           <t>Consumer Staples</t>
         </is>
       </c>
-      <c r="F84" s="4" t="n">
+      <c r="F84" s="3" t="n">
+        <v>0.08191947328437577</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0.07107044372023075</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0.04123840561544245</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0.02323075080828629</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0.01352152769540971</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0.0286505356927893</v>
+      </c>
+      <c r="L84" s="3" t="n">
         <v>0.004348848142924355</v>
-      </c>
-      <c r="G84" s="4" t="n">
-        <v>0.08191947328437577</v>
-      </c>
-      <c r="H84" s="4" t="n">
-        <v>0.07107044372023075</v>
-      </c>
-      <c r="I84" s="4" t="n">
-        <v>0.04123840561544245</v>
-      </c>
-      <c r="J84" s="4" t="n">
-        <v>0.02323075080828629</v>
-      </c>
-      <c r="K84" s="4" t="n">
-        <v>0.0286505356927893</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4072,22 +4327,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
+        <v>0.04633548674537757</v>
+      </c>
+      <c r="G85" s="5" t="n">
+        <v>-0.003606279168434368</v>
+      </c>
+      <c r="H85" s="3" t="n">
+        <v>0.03528496676566273</v>
+      </c>
+      <c r="I85" s="3" t="n">
+        <v>0.03877626244010313</v>
+      </c>
+      <c r="J85" s="3" t="n">
+        <v>0.03374660699875287</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>-0.03756574004507884</v>
+      </c>
+      <c r="L85" s="5" t="n">
         <v>-0.01695269987442449</v>
-      </c>
-      <c r="G85" s="4" t="n">
-        <v>0.04633548674537757</v>
-      </c>
-      <c r="H85" s="3" t="n">
-        <v>-0.003606279168434368</v>
-      </c>
-      <c r="I85" s="4" t="n">
-        <v>0.03528496676566273</v>
-      </c>
-      <c r="J85" s="4" t="n">
-        <v>0.03877626244010313</v>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>-0.03756574004507884</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4110,23 +4368,26 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="F86" s="4" t="n">
+      <c r="F86" s="3" t="n">
+        <v>0.1280584683825867</v>
+      </c>
+      <c r="G86" s="3" t="n">
+        <v>0.1112850211300673</v>
+      </c>
+      <c r="H86" s="3" t="n">
+        <v>0.02989513225856943</v>
+      </c>
+      <c r="I86" s="3" t="n">
+        <v>0.0848804339521736</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.1076443057722309</v>
+      </c>
+      <c r="K86" s="3" t="n">
+        <v>0.07902735562310026</v>
+      </c>
+      <c r="L86" s="3" t="n">
         <v>0.003108222661768911</v>
-      </c>
-      <c r="G86" s="4" t="n">
-        <v>0.1280584683825867</v>
-      </c>
-      <c r="H86" s="4" t="n">
-        <v>0.1112850211300673</v>
-      </c>
-      <c r="I86" s="4" t="n">
-        <v>0.02989513225856943</v>
-      </c>
-      <c r="J86" s="4" t="n">
-        <v>0.0848804339521736</v>
-      </c>
-      <c r="K86" s="4" t="n">
-        <v>0.07902735562310026</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4149,23 +4410,26 @@
           <t>Financials</t>
         </is>
       </c>
-      <c r="F87" s="4" t="n">
+      <c r="F87" s="3" t="n">
+        <v>0.1288129007188654</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.1094137865189995</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.02367767805995813</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0.08720059880239539</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.1145213888356034</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0.08375303115090471</v>
+      </c>
+      <c r="L87" s="3" t="n">
         <v>0.003800967519004717</v>
-      </c>
-      <c r="G87" s="4" t="n">
-        <v>0.1288129007188654</v>
-      </c>
-      <c r="H87" s="4" t="n">
-        <v>0.1094137865189995</v>
-      </c>
-      <c r="I87" s="4" t="n">
-        <v>0.02367767805995813</v>
-      </c>
-      <c r="J87" s="4" t="n">
-        <v>0.08720059880239539</v>
-      </c>
-      <c r="K87" s="4" t="n">
-        <v>0.08375303115090471</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4192,23 +4456,26 @@
           <t>US Dollar Basket</t>
         </is>
       </c>
-      <c r="F88" s="4" t="n">
+      <c r="F88" s="5" t="n">
+        <v>-0.04506946797695699</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.01003584229390686</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0.01827956989247315</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0.04953445065176898</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.02997076023391809</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>-0.008095740936290063</v>
+      </c>
+      <c r="L88" s="3" t="n">
         <v>0.005710206995003464</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>-0.04506946797695699</v>
-      </c>
-      <c r="H88" s="4" t="n">
-        <v>0.01003584229390686</v>
-      </c>
-      <c r="I88" s="4" t="n">
-        <v>0.01827956989247315</v>
-      </c>
-      <c r="J88" s="4" t="n">
-        <v>0.04953445065176898</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>-0.008095740936290063</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4235,23 +4502,26 @@
           <t>US Dollar Basket</t>
         </is>
       </c>
-      <c r="F89" s="4" t="n">
+      <c r="F89" s="5" t="n">
+        <v>-0.04730949801372342</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.009015777610818954</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.00488354620586029</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0.0336990595611284</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.01774691358024683</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-0.01383177570093463</v>
+      </c>
+      <c r="L89" s="3" t="n">
         <v>0.003041825095057016</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>-0.04730949801372342</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>-0.009015777610818954</v>
-      </c>
-      <c r="I89" s="4" t="n">
-        <v>0.00488354620586029</v>
-      </c>
-      <c r="J89" s="4" t="n">
-        <v>0.0336990595611284</v>
-      </c>
-      <c r="K89" s="3" t="n">
-        <v>-0.01383177570093463</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4278,23 +4548,26 @@
           <t>TIPS</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
+      <c r="F90" s="5" t="n">
+        <v>-0.009906490139801938</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>-0.02489286039937999</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>-0.002188383331813593</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>-0.03204199855177414</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>-0.04141269272140558</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.02275427213743952</v>
+      </c>
+      <c r="L90" s="5" t="n">
         <v>-0.004653760238272575</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>-0.009906490139801938</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>-0.02489286039937999</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>-0.002188383331813593</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>-0.03204199855177414</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>-0.02275427213743952</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4317,23 +4590,26 @@
           <t>Intermediate Treasury</t>
         </is>
       </c>
-      <c r="F91" s="3" t="n">
+      <c r="F91" s="5" t="n">
+        <v>-0.001827563964738821</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.0216016859852477</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>-0.003477344573235119</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>-0.03220762976860536</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>-0.02242577384712585</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>-0.01818758591519509</v>
+      </c>
+      <c r="L91" s="5" t="n">
         <v>-0.004075941220637258</v>
-      </c>
-      <c r="G91" s="3" t="n">
-        <v>-0.001827563964738821</v>
-      </c>
-      <c r="H91" s="3" t="n">
-        <v>-0.0216016859852477</v>
-      </c>
-      <c r="I91" s="3" t="n">
-        <v>-0.003477344573235119</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>-0.03220762976860536</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>-0.01818758591519509</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4356,23 +4632,26 @@
           <t>Short Treasury</t>
         </is>
       </c>
-      <c r="F92" s="3" t="n">
+      <c r="F92" s="5" t="n">
+        <v>-0.004860857941426766</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.007634512845370756</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>-0.004968492486669862</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>-0.01325460898903474</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>-0.00715324927255101</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>-0.002679332602606221</v>
+      </c>
+      <c r="L92" s="5" t="n">
         <v>-0.001828376401755261</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>-0.004860857941426766</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>-0.007634512845370756</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>-0.004968492486669862</v>
-      </c>
-      <c r="J92" s="3" t="n">
-        <v>-0.01325460898903474</v>
-      </c>
-      <c r="K92" s="3" t="n">
-        <v>-0.002679332602606221</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4396,22 +4675,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
+        <v>0.0002508780732564109</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-0.007962179646678336</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>-0.005100771336153276</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>-0.0170118343195268</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>-0.007962179646678336</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>-0.0028760785294486</v>
+      </c>
+      <c r="L93" s="5" t="n">
         <v>-0.001627644923000049</v>
-      </c>
-      <c r="G93" s="4" t="n">
-        <v>0.0002508780732564109</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>-0.007962179646678336</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>-0.005100771336153276</v>
-      </c>
-      <c r="J93" s="3" t="n">
-        <v>-0.0170118343195268</v>
-      </c>
-      <c r="K93" s="3" t="n">
-        <v>-0.0028760785294486</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4434,23 +4716,26 @@
           <t>Long Treasury</t>
         </is>
       </c>
-      <c r="F94" s="3" t="n">
+      <c r="F94" s="5" t="n">
+        <v>-0.05560619872379224</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.0464795213989877</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-0.005752416014726203</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>-0.04877768851141973</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>-0.0320018687222613</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>-0.04096274010645695</v>
+      </c>
+      <c r="L94" s="5" t="n">
         <v>-0.003007337904486929</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>-0.05560619872379224</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>-0.0464795213989877</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>-0.005752416014726203</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>-0.04877768851141973</v>
-      </c>
-      <c r="K94" s="3" t="n">
-        <v>-0.04096274010645695</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4477,23 +4762,26 @@
           <t>India Equity</t>
         </is>
       </c>
-      <c r="F95" s="4" t="n">
+      <c r="F95" s="5" t="n">
+        <v>-0.0280447146499313</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.05851063829787229</v>
+      </c>
+      <c r="H95" s="5" t="n">
+        <v>-0.06174012158054709</v>
+      </c>
+      <c r="I95" s="5" t="n">
+        <v>-0.04213374565133354</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0.002832861189801639</v>
+      </c>
+      <c r="K95" s="3" t="n">
+        <v>0.003441992306134845</v>
+      </c>
+      <c r="L95" s="3" t="n">
         <v>0.0006056935190794643</v>
-      </c>
-      <c r="G95" s="3" t="n">
-        <v>-0.0280447146499313</v>
-      </c>
-      <c r="H95" s="3" t="n">
-        <v>-0.05851063829787229</v>
-      </c>
-      <c r="I95" s="3" t="n">
-        <v>-0.06174012158054709</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>-0.04213374565133354</v>
-      </c>
-      <c r="K95" s="4" t="n">
-        <v>0.003441992306134845</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4520,27 +4808,30 @@
           <t>Digital Payments</t>
         </is>
       </c>
-      <c r="F96" s="3" t="n">
+      <c r="F96" s="5" t="n">
+        <v>-0.1536198725281909</v>
+      </c>
+      <c r="G96" s="5" t="n">
+        <v>-0.111663807890223</v>
+      </c>
+      <c r="H96" s="5" t="n">
+        <v>-0.20926243567753</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.06563786008230443</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>0.09910865874363339</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>0.1234273318872017</v>
+      </c>
+      <c r="L96" s="5" t="n">
         <v>-0.01220675185962239</v>
       </c>
-      <c r="G96" s="3" t="n">
-        <v>-0.1536198725281909</v>
-      </c>
-      <c r="H96" s="3" t="n">
-        <v>-0.111663807890223</v>
-      </c>
-      <c r="I96" s="3" t="n">
-        <v>-0.20926243567753</v>
-      </c>
-      <c r="J96" s="4" t="n">
-        <v>0.06563786008230443</v>
-      </c>
-      <c r="K96" s="4" t="n">
-        <v>0.1234273318872017</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K96"/>
+  <autoFilter ref="A1:L96"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -203,6 +203,9 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -673,25 +676,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.204180602006689</v>
+        <v>1.212541806020067</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.215294117647059</v>
+        <v>1.223697478991597</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>2.156638655462185</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.4170070952483338</v>
+        <v>0.4223822833799185</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.01398862956313585</v>
+        <v>-0.01024835427887494</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.2982110531359812</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>-0.04871535796766746</v>
+        <v>-0.2955489298264296</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.003793338896897147</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -719,25 +722,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.498922046976058</v>
+        <v>1.513105639396346</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.277220556302347</v>
+        <v>1.290145796711819</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>1.94643780374315</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4483098776798631</v>
+        <v>0.4565303169801394</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03142562757587108</v>
+        <v>0.03727988010490813</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.2271275662396912</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>-0.03475631136044888</v>
+        <v>-0.222740831724864</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.005675884302774437</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -765,25 +768,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.773824130879345</v>
+        <v>1.784867075664622</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.285810583080552</v>
+        <v>1.294910684192787</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>1.875294910684193</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.5923925804179382</v>
+        <v>0.598732096736323</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.1341137123745819</v>
+        <v>0.1386287625418061</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.2050169968350722</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>-0.03058890794739855</v>
+        <v>-0.2018520689250967</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.003981126511353628</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -807,25 +810,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.338891977024272</v>
+        <v>2.366314619232907</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.474934761708556</v>
+        <v>1.495261639884631</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>1.772970745776679</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.4721019524548646</v>
+        <v>0.4841924679356262</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.1209256033839263</v>
+        <v>0.1301318736003982</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.1074789499752353</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>-0.01065114746897988</v>
+        <v>-0.100148588410104</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.008213096559378519</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -849,25 +852,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.331728785586577</v>
+        <v>1.346765690184752</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.118985126859143</v>
+        <v>1.132650085405991</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>1.669499645877599</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.468726537684089</v>
+        <v>0.4781980941380306</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.102245145631068</v>
+        <v>0.1093533287101247</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.2062238591672388</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>-0.03199284395637847</v>
+        <v>-0.20110493788626</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.006448822303487756</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -895,25 +898,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.285569620253165</v>
+        <v>1.298987341772152</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.042996152975786</v>
+        <v>1.054989816700611</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.536773025571396</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4327884462783687</v>
+        <v>0.441199809554039</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.09231699939503923</v>
+        <v>0.09872958257713238</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.1946476360392506</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>-0.03505771697306548</v>
+        <v>-0.1899197145405886</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.00587062472308375</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -941,25 +944,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.270380100155981</v>
+        <v>1.284213118791561</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9153334718470811</v>
+        <v>0.9270032550730662</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1.271244546021193</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3709165716551828</v>
+        <v>0.3792693203787241</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.09154957372908101</v>
+        <v>0.09820018945374165</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.1567031057037003</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>-0.03471204188481669</v>
+        <v>-0.1515650490173657</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.006092820596264703</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -987,25 +990,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8787354902445046</v>
+        <v>0.8878735490244503</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8562713518789653</v>
+        <v>0.8653001464128844</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.9102000976085898</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.08749106504646154</v>
+        <v>0.09278055754110071</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.1379193109700816</v>
+        <v>-0.1337262012692656</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.02823198773633118</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>-0.01374303124594844</v>
+        <v>-0.02350536535513548</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.00486394110687538</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1033,25 +1036,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.097181729834791</v>
+        <v>1.11137026239067</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8488690884167238</v>
+        <v>0.8613776559287183</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.8610349554489376</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.5853658536585367</v>
+        <v>0.5960916838084043</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.200489541611037</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>-0.006537151275204822</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>-0.006720058915584914</v>
+        <v>0.2086114819759679</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.0001841451063437916</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.00676552363299332</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1075,25 +1078,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.7522391280889176</v>
+        <v>0.7303334412431206</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8956339014709316</v>
+        <v>0.8719355591874853</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.8474200326873687</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.3016432865731462</v>
+        <v>0.2853707414829658</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2364273204903675</v>
+        <v>0.2209700753826238</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.02609794628751971</v>
+        <v>0.0132701421800947</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.03477382155382513</v>
+        <v>-0.01250153959847278</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1121,25 +1124,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.473022524882137</v>
+        <v>1.427710843373494</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.193263646922184</v>
+        <v>1.153077816492451</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.7879210220673636</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.1133121094210587</v>
+        <v>0.09291357151279334</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.1860319055395052</v>
+        <v>0.1643009672151738</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.2267117058594257</v>
+        <v>0.2042354163959985</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.02104717470191808</v>
+        <v>-0.01832238932429575</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1167,25 +1170,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.4580972263644496</v>
+        <v>0.4592901878914404</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.3853782941343158</v>
+        <v>0.3865117597052989</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.7376027203173705</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.007511165245635332</v>
+        <v>-0.006699147381242332</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.1664109121909633</v>
+        <v>-0.1657289002557545</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.2027071102413568</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>-0.03283877349159237</v>
+        <v>-0.202054794520548</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.0008181632235630953</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1213,25 +1216,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.291459781529295</v>
+        <v>1.274081429990069</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.8972250770811923</v>
+        <v>0.882836587872559</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.7163412127440905</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.0658198614318708</v>
+        <v>0.05773672055427248</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.1629078997102178</v>
+        <v>0.1540884465163159</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.1053892215568861</v>
+        <v>0.09700598802395199</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-0.02265988987717071</v>
+        <v>-0.007583965330444253</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1255,25 +1258,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.866146285053484</v>
+        <v>1.784041630529054</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.094212082805238</v>
+        <v>1.034220532319392</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.6362484157160961</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.05132555673382821</v>
+        <v>0.02120890774125139</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.1192142695868141</v>
+        <v>0.08715285617520885</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.2798863929770206</v>
+        <v>0.2432223082881488</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>-0.03878223773511735</v>
+        <v>-0.02864635868468834</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1301,25 +1304,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4918032786885245</v>
+        <v>0.4913718723037102</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4402332361516033</v>
+        <v>0.4398167430237401</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.606413994169096</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.07591785936527695</v>
+        <v>0.07560672059738649</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.07737459978655281</v>
+        <v>-0.07764140875133396</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.1034482758620691</v>
+        <v>-0.1037075447238787</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.006607296753806446</v>
+        <v>-0.0002891844997107151</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1343,25 +1346,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.105226236408278</v>
+        <v>1.104524728165556</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.8013205282112845</v>
+        <v>0.800720288115246</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.6047418967587035</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.2044008483563096</v>
+        <v>-0.2046659597030752</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.09960996099609953</v>
+        <v>-0.09990999099909992</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1224985973443053</v>
+        <v>0.1221245558256967</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.04381073761350962</v>
+        <v>-0.0003332222592469236</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1389,25 +1392,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.689774696707106</v>
+        <v>1.662045060658579</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.097297297297297</v>
+        <v>1.075675675675675</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.6040540540540538</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3460537727666957</v>
+        <v>0.3321769297484822</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.3242320819112627</v>
+        <v>0.310580204778157</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.3074978938500421</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.04723346828609976</v>
+        <v>0.2940185341196293</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>-0.01030927835051543</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1435,25 +1438,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.5888324873096447</v>
+        <v>0.5868723928230386</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.475106154635808</v>
+        <v>0.4732863608791005</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.5617096729037376</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3422069375451109</v>
+        <v>0.3405510975247314</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.1856505269474553</v>
+        <v>0.1841878258260512</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.05545430099495052</v>
+        <v>-0.05661955839732291</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-0.01749751367478869</v>
+        <v>-0.001233669692847883</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1477,25 +1480,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.3800579856296484</v>
+        <v>0.3684608596999874</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.2557926129846295</v>
+        <v>0.2452397338839183</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.5284468914888736</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.006533575317604345</v>
+        <v>-0.01488203266787658</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.1372054535424383</v>
+        <v>-0.1444558278824178</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.1783864915572232</v>
+        <v>-0.1852908067542214</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>-0.02926050718212447</v>
+        <v>-0.008403361344537785</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1523,25 +1526,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.5103625072212594</v>
+        <v>0.564810803004044</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.7163548334153946</v>
+        <v>0.778229115378303</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.5264647956671589</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.2006946238410976</v>
+        <v>0.2439794483194122</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.06677226485811172</v>
+        <v>-0.03312957344279854</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.1243985700077952</v>
+        <v>0.164932935515953</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.008097361127846758</v>
+        <v>0.03604981951184527</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1569,25 +1572,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.8639455782312926</v>
+        <v>0.8545918367346941</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.7133923918707661</v>
+        <v>0.7047941636268891</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0.5151120375195413</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1277653918710342</v>
+        <v>0.1221059852512434</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.06753246753246755</v>
+        <v>0.06217532467532472</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.1308684436801377</v>
+        <v>0.1251934651762685</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.01350135013501341</v>
+        <v>-0.005018248175182483</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1615,25 +1618,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.002360876897133</v>
+        <v>1.000505902192243</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.6194762684124386</v>
+        <v>0.6179759956355702</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.458401527550464</v>
       </c>
-      <c r="I23" s="3" t="n">
-        <v>0.0001684636118597371</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>8.422471153024524e-05</v>
+      <c r="I23" s="5" t="n">
+        <v>-0.0007580862533692612</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>-0.0008422471153036737</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.1104460862246328</v>
+        <v>0.1094173758533619</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>-0.03463414634146345</v>
+        <v>-0.0009263938015833251</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1661,25 +1664,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6314883594528489</v>
+        <v>0.635836579400308</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.5088806970509383</v>
+        <v>0.512902144772118</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.4537533512064345</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1792051332416684</v>
+        <v>0.1823479342630787</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.1112482260751528</v>
+        <v>0.1142099092984514</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.03792070078377119</v>
+        <v>0.04068695251267873</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.005246706854208583</v>
+        <v>0.002665186007773546</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1703,25 +1706,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.6089593622736331</v>
+        <v>0.6118187332120268</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4134886199284462</v>
+        <v>0.4160006089670396</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.4502550049478573</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2905893800389214</v>
+        <v>0.2928829580205727</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1642006269592475</v>
+        <v>0.1662695924764892</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>-0.02535166911610331</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>-0.01548168177721232</v>
+        <v>-0.02361956749947514</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.00177715547417745</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1749,25 +1752,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.5069234097793163</v>
+        <v>0.4898312418866293</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.5738927387767401</v>
+        <v>0.5560409761976501</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.4325851159987948</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.2117960911674301</v>
+        <v>0.1980513831699819</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.2386626356037702</v>
+        <v>0.2246131958029522</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.0986382039013618</v>
+        <v>0.08617698091382309</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>-0.02723463687150851</v>
+        <v>-0.01134242641780314</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1795,25 +1798,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.3678517639541781</v>
+        <v>0.3708183104376797</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.2421152969455842</v>
+        <v>0.2448091508143728</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.4208214182104522</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.1712454570323185</v>
+        <v>0.1737856110047287</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.05539122473413616</v>
+        <v>0.05768011831819142</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>-0.125776623982732</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>-0.01485718042270667</v>
+        <v>-0.1238806405507101</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.00216876313769987</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1837,25 +1840,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.2819168850617746</v>
+        <v>0.2759266192437289</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3297087378640777</v>
+        <v>0.323495145631068</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.4031067961165049</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.1398135818908124</v>
+        <v>0.1344873501997337</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.05613818630475009</v>
+        <v>0.0512029611351017</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.0523110988098533</v>
+        <v>-0.05673955161915323</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.01524302559677881</v>
+        <v>-0.004672897196261738</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1879,25 +1882,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.4672131147540983</v>
+        <v>0.4658136745301877</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.2687354136053246</v>
+        <v>0.2675252830841039</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.3963177456997147</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.224493200967715</v>
+        <v>0.2233252690414613</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.09709245833021907</v>
+        <v>0.09604604230510505</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.09137055837563446</v>
+        <v>-0.09223721678841157</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.01224764468371464</v>
+        <v>-0.000953808420765867</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1925,25 +1928,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5732448174359617</v>
+        <v>0.5709275380472225</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3854723953449892</v>
+        <v>0.3834316915779605</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3911532733991505</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.2663205121742198</v>
+        <v>0.2644553107828804</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.1517124386777313</v>
+        <v>0.1500160469487872</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.004083574515323374</v>
+        <v>-0.005550489632478173</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.01028328277057644</v>
+        <v>-0.001472929936305656</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1971,25 +1974,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5621933936552928</v>
+        <v>0.5626839638068244</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3930203169048314</v>
+        <v>0.3934577622241664</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3880626032857002</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.285432364549695</v>
+        <v>0.2858360243989952</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1635743575169504</v>
+        <v>0.1639397507206366</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.003571678688983893</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>-0.01528946916337393</v>
+        <v>0.003886826808600086</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.0003140265177947743</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2013,25 +2016,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5577322262584328</v>
+        <v>0.5587701089776855</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.3911481867686246</v>
+        <v>0.392075078206465</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3847758081334722</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.2843084821906086</v>
+        <v>0.2851641886832819</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.1636945144407829</v>
+        <v>0.1644698584997093</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.004601740294511325</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>-0.01509310146829634</v>
+        <v>0.005271084337349574</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.0006662780044974781</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2059,25 +2062,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.3640054127198917</v>
+        <v>0.3658660351826795</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2937590245467672</v>
+        <v>0.2955238248034655</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.3742980908069951</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1141199226305609</v>
+        <v>0.1156396794694667</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.01236987140232704</v>
+        <v>-0.01102265768524191</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.05860378239551711</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>-0.01885874193940862</v>
+        <v>-0.05731963576932053</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.001364087301587213</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2105,25 +2108,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.4917073170731707</v>
+        <v>0.4915853658536586</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2601215617595549</v>
+        <v>0.2600185433192543</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3621098176573607</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.01291155584247905</v>
+        <v>-0.01299225306649454</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.05023681962885318</v>
+        <v>-0.05031446540880491</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.0748752079866889</v>
+        <v>-0.07495083950990766</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-0.01481958762886604</v>
+        <v>-8.175277959443505e-05</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2151,25 +2154,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.2761779663871207</v>
+        <v>0.2657707722878986</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.3059107358262969</v>
+        <v>0.2952610718593831</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.3577804583835946</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.1266018493741268</v>
+        <v>0.1174144441471174</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.05287873735689685</v>
+        <v>0.04429254195843058</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.03820184790334036</v>
+        <v>-0.04604528378515582</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.02065133109330564</v>
+        <v>-0.008154970837402131</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2197,25 +2200,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.4920209734412402</v>
+        <v>0.4653482275162431</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2089683199408887</v>
+        <v>0.1873556848619193</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.3105661771497183</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>-0.04092174677608429</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0.01022613259242111</v>
+        <v>-0.05806711606096115</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-0.007833603457590432</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.07752211142041654</v>
+        <v>-0.09401317875894144</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.01601202781432054</v>
+        <v>-0.01787692425226328</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2243,25 +2246,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.172548419199265</v>
+        <v>0.1688739187016766</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.1744364361294279</v>
+        <v>0.1707560190154884</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.3045545161785002</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.09188765326489867</v>
+        <v>0.0884659252922726</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.0416692736032036</v>
+        <v>-0.04467246449352447</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.09974138944398736</v>
+        <v>-0.1025625955095802</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.02408410321758525</v>
+        <v>-0.003133772932036205</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2285,25 +2288,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.3717092036990943</v>
+        <v>0.3703306592123152</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2679952567211199</v>
+        <v>0.2667209429921595</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.303339763897984</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1520575039799315</v>
+        <v>0.1508997057262773</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.07291760265971781</v>
+        <v>0.07183933866474979</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.02711841390548619</v>
+        <v>-0.02809614340032585</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.006489994591671211</v>
+        <v>-0.001004983040911012</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2327,25 +2330,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3721568445043955</v>
+        <v>0.3707614307642215</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2684353097992003</v>
+        <v>0.2671453755858451</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.3027045620673348</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1521187268111697</v>
+        <v>0.1509470806483109</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.07311749727173522</v>
+        <v>0.07202619134230637</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.02630623494075335</v>
+        <v>-0.02729643198996612</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.00646638825272805</v>
+        <v>-0.001016949152542357</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2369,25 +2372,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.2057160481134983</v>
+        <v>0.1948185463143828</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2459364708382024</v>
+        <v>0.234675448847339</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.2950175289493253</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1246643651706942</v>
+        <v>0.1144994246260072</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.0503940769047051</v>
+        <v>0.04090040601862932</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.03789991796554559</v>
+        <v>-0.04659557013945848</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.01983507911745042</v>
+        <v>-0.009038199181445994</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2411,25 +2414,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.3078742019389928</v>
+        <v>0.2993615511941359</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2105493543444956</v>
+        <v>0.20267016852703</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.2895600787918582</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.08985221674876853</v>
+        <v>0.08275862068965534</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.02606092621940481</v>
+        <v>-0.03240007043493565</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.06126951799049563</v>
+        <v>-0.06737949762389683</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.01337852301105957</v>
+        <v>-0.006508768757909955</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2453,25 +2456,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4629555466559874</v>
+        <v>0.4639567480977174</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2995375311277126</v>
+        <v>0.3004268943436499</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2673425827107792</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1036253776435045</v>
+        <v>0.104380664652568</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.06191860465116283</v>
+        <v>0.0626453488372094</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.02540350877192976</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>-0.004903296104603605</v>
+        <v>0.02610526315789463</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0.0006843690117710466</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2499,25 +2502,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.7707881417208964</v>
+        <v>0.7718727404193781</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.6294078509647372</v>
+        <v>0.6304058549567531</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.2611443779108449</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.3677743647025968</v>
+        <v>0.3686121195196872</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.1813796430294259</v>
+        <v>0.1821032320308731</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.2920073859140069</v>
+        <v>0.2927987338433131</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.0004084967320261423</v>
+        <v>0.0006124948958758925</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2545,25 +2548,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.3112672863296306</v>
+        <v>0.3042394014962595</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.4388059701492537</v>
+        <v>0.4310945273631841</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.258955223880597</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.2745702952842661</v>
+        <v>0.2677390921110621</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.2052510939779122</v>
+        <v>0.1987914148780996</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.142857142857143</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>0.002426343154246169</v>
+        <v>0.1367318711717052</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>-0.005359612724758045</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2587,25 +2590,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3199350385708486</v>
+        <v>0.3162809581810802</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.3156616754350463</v>
+        <v>0.3120194253338731</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0.2585997571833265</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1455250176180409</v>
+        <v>0.1423537702607471</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.08042539049518105</v>
+        <v>0.07743436357593891</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.0453376205787781</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>0.001540357362908029</v>
+        <v>0.04244372990353695</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>-0.002768378960319784</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2629,25 +2632,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.3481020857624044</v>
+        <v>0.3431791682860474</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2508714989782426</v>
+        <v>0.2463036422646954</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.2407741315061906</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1270442976280732</v>
+        <v>0.1229286255821511</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.06032198899531283</v>
+        <v>0.05644996943142466</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.008137957760123937</v>
+        <v>0.004456500678163167</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.004401071565250603</v>
+        <v>-0.003651739381126284</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2671,25 +2674,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.2989010989010989</v>
+        <v>0.3008241758241759</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2494714587737843</v>
+        <v>0.2513213530655389</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.2402219873150104</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1044148563419762</v>
+        <v>0.1060499883204857</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.07259528130671522</v>
+        <v>0.07418330308529963</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.007457916045173762</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>-0.000422832980972454</v>
+        <v>0.008949499254208515</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0.001480541455160855</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2717,25 +2720,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.1853602688628726</v>
+        <v>0.1725080326476347</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.329136988570482</v>
+        <v>0.314725857213848</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2382391916514826</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1172375382901698</v>
+        <v>0.1051239209133947</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.1780077809586729</v>
+        <v>0.1652352638919476</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.07340891608976285</v>
+        <v>0.0617705093475136</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.006100393274084293</v>
+        <v>-0.01084247258225313</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2759,25 +2762,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4869076510410013</v>
+        <v>0.4600843019542724</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.184231943031536</v>
+        <v>0.1628687690742625</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2330620549338758</v>
       </c>
-      <c r="I49" s="3" t="n">
-        <v>0.001893450382993267</v>
+      <c r="I49" s="5" t="n">
+        <v>-0.01618039418194328</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.06524524158125922</v>
+        <v>0.04602855051244514</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.03960069301212765</v>
+        <v>-0.05692599620493355</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.006147016135917394</v>
+        <v>-0.01803968731208649</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2805,25 +2808,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4281323303405322</v>
+        <v>0.4614575750222438</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.4418946508779094</v>
+        <v>0.4755410371580238</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2260514495712536</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.2279018012379166</v>
+        <v>0.2565546978232145</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.0411605142115814</v>
+        <v>0.06545583205566685</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.1760474255645108</v>
+        <v>0.2034903083993873</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.004665983839763355</v>
+        <v>0.02333484367920247</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2847,25 +2850,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.2803758583303215</v>
+        <v>0.2680881821467294</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1653180711795277</v>
+        <v>0.1541345964081311</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>0.2185382540622327</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.07072050290135379</v>
+        <v>0.0604448742746615</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.01466376446328321</v>
+        <v>0.004926108374384119</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.04367543054580791</v>
+        <v>-0.05285320952329531</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>-0.009284116331096381</v>
+        <v>-0.009596928982725461</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2889,25 +2892,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4303970789593792</v>
+        <v>0.4646280237334552</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.4372850263700987</v>
+        <v>0.4716808071543226</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0.2178399449667507</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.2278158667972576</v>
+        <v>0.2571988246816848</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.05079631181894384</v>
+        <v>0.07594300083822314</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>0.1801920542270758</v>
+        <v>0.2084353229147056</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.006261037084604348</v>
+        <v>0.0239310784939375</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2931,25 +2934,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.5853981463968223</v>
+        <v>0.5719689805182524</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.3517174649250121</v>
+        <v>0.3402676987582649</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2177068214804065</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>-0.080921052631579</v>
+        <v>-0.08870614035087721</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.03488773747841112</v>
+        <v>-0.04306275187104192</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.1100516487882397</v>
+        <v>0.1006489206727585</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.03232509812976236</v>
+        <v>-0.008470532092579308</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2973,25 +2976,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.5814124381188117</v>
+        <v>0.5683013613861385</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.349650118827568</v>
+        <v>0.3384605228412993</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.2159360971745445</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.08104281379930334</v>
+        <v>-0.0886616473761096</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.03486286172874486</v>
+        <v>-0.04286456120473969</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.1099679678592758</v>
+        <v>0.1007655138715458</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.03244202555608144</v>
+        <v>-0.008290738340384962</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3019,25 +3022,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1629013079667063</v>
+        <v>0.1549176150840836</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2177161152614726</v>
+        <v>0.2093561010316614</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.2134471718249733</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.07692307692307687</v>
+        <v>0.06952965235173814</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.06652126499454747</v>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>0.003518029903254005</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>0.0005846243788365513</v>
+        <v>0.05919925221997202</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>-0.003371445323951949</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>-0.00686532281624308</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3065,25 +3068,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.4098183929015671</v>
+        <v>0.3899162451281202</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1644520547945205</v>
+        <v>0.148013698630137</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.2099315068493151</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>-0.02617711078015816</v>
+        <v>-0.03992438996448622</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.01528814571513881</v>
+        <v>0.0009555091071962174</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.03758845174073033</v>
+        <v>-0.05117463911689779</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.009785077756421456</v>
+        <v>-0.01411681665784348</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3111,25 +3114,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.3859570661896243</v>
+        <v>0.4149522957662495</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.4509559110417478</v>
+        <v>0.4813109637143973</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0.2037456106125632</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.3258699372504277</v>
+        <v>0.3536081003993155</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.04337579260423086</v>
+        <v>0.0652039728410303</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.2053675612602102</v>
+        <v>0.2305847270841439</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.002534102550277639</v>
+        <v>0.02092072711627413</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3153,25 +3156,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3691441441441441</v>
+        <v>0.3680180180180181</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2206827309236947</v>
+        <v>0.2196787148594379</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.1985943775100403</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.07650079688330091</v>
+        <v>0.07561537099344795</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.0315628712031224</v>
+        <v>0.03071440692346861</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.01842854749539291</v>
+        <v>0.01759088624560246</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.00360596623504339</v>
+        <v>-0.0008225037012665748</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3195,25 +3198,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2540424002874595</v>
+        <v>0.2529644268774704</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.3169811320754716</v>
+        <v>0.3158490566037735</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>0.1966037735849058</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1703554661301139</v>
+        <v>0.16934942991281</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.08824446523230423</v>
+        <v>0.08730901153726212</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.1005991800693786</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>0.002009761699684143</v>
+        <v>0.09965310627562274</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>-0.0008595988538682153</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3237,25 +3240,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.4014565316340464</v>
+        <v>0.4228493400091036</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.3714922048997773</v>
+        <v>0.3924276169265035</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.1875278396436526</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.2603356528857961</v>
-      </c>
-      <c r="J60" s="5" t="n">
-        <v>-0.009967845659164087</v>
+        <v>0.2795742939009416</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>0.005144694533762095</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.154913728432108</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>-0.002268308489954629</v>
+        <v>0.172543135783946</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0.0152646963299774</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3279,25 +3282,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.2781522780257712</v>
+        <v>0.2730558617822998</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.21723864927197</v>
+        <v>0.2123851158307803</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>0.1820763484905854</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1116280531891485</v>
+        <v>0.1071956241551664</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.07063489660601285</v>
+        <v>0.0663659208574281</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.0297462180224517</v>
+        <v>0.02564027897089449</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.002130511463844798</v>
+        <v>-0.003987331033312613</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3321,25 +3324,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.278372270778638</v>
+        <v>0.2732544614668837</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2171718769775977</v>
+        <v>0.2122990760663206</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.1814485508163524</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1118256571816698</v>
+        <v>0.1073745971646169</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.07053404948097852</v>
+        <v>0.06624829543873312</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.03023688685940784</v>
+        <v>0.02611245765095016</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.002269485151082828</v>
+        <v>-0.004003379476181235</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3363,25 +3366,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.2784889682775957</v>
+        <v>0.2734279382091231</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2175145692234999</v>
+        <v>0.2126949125846591</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1795400850527642</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1121822079622463</v>
+        <v>0.1077795203084759</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.07053332779370414</v>
+        <v>0.06629551151550395</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.03219431425175934</v>
+        <v>0.02810826690168122</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.002258793159083616</v>
+        <v>-0.003958602846054315</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3409,25 +3412,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.2931491037479632</v>
+        <v>0.2878870179250408</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2148301706266944</v>
+        <v>0.2098867804177962</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.166863339180354</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1087146349982537</v>
+        <v>0.1042030504133193</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.0735907553551296</v>
+        <v>0.06922209695603154</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.04110749719845863</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>5.250859828298537e-05</v>
+        <v>0.03687101976111729</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>-0.004069202698800289</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3451,25 +3454,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2176671816376075</v>
+        <v>0.2100529684396379</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.2018188749115069</v>
+        <v>0.1943037630016882</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1586886674290695</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1141457996768982</v>
+        <v>0.1071789176090467</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.08479158474243009</v>
+        <v>0.0780082579630359</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.03722329275743763</v>
+        <v>0.03073741598909607</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.003431925942650627</v>
+        <v>-0.006253115229507444</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3493,25 +3496,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2940838598506605</v>
+        <v>0.2887708213670304</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1840756799369334</v>
+        <v>0.1792142950991986</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.1550387596899225</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1102624122212641</v>
+        <v>0.1057040778612788</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.07285714285714295</v>
+        <v>0.06845238095238093</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.02513934705949272</v>
+        <v>0.02093049709930606</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>-0.003978779840848823</v>
+        <v>-0.004105636928539824</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3535,25 +3538,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.2697547683923707</v>
+        <v>0.2637315359242793</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1671500131821777</v>
+        <v>0.1616134985499604</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.1355127867123649</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1031647146772987</v>
+        <v>0.0979317219038125</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.06456655043886017</v>
+        <v>0.05951665263917283</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.02786162061759923</v>
+        <v>0.02298583700951951</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.004049493813273353</v>
+        <v>-0.00474361870341089</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3577,25 +3580,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.07745629897528628</v>
+        <v>0.08137432188065108</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.06812070510905288</v>
+        <v>0.07200478040035874</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1335524350164325</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>-0.04206859592711687</v>
+        <v>-0.03858520900321538</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>-0.070221066319896</v>
+        <v>-0.06684005201560472</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.05772272008434365</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>-0.01079136690647486</v>
+        <v>-0.05429625724828668</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0.00363636363636366</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3619,25 +3622,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.1995504739568064</v>
+        <v>0.1954461057363432</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1148955495004542</v>
+        <v>0.1110808356039965</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1277929155313353</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.05373851832775345</v>
+        <v>0.05013305863164219</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.02917749643665646</v>
+        <v>0.02565607445292195</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.01143593460578241</v>
+        <v>-0.0148183941370702</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.009201711195415241</v>
+        <v>-0.00342158859470465</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3661,25 +3664,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2212821959014852</v>
+        <v>0.2205301748448958</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.09952606635071093</v>
+        <v>0.09884901828029791</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1272850372376437</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.008539046731873778</v>
+        <v>0.007918025151374186</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>-0.05209397344228817</v>
+        <v>-0.05267765941923241</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.02462462462462467</v>
+        <v>-0.02522522522522508</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.009756097560975618</v>
+        <v>-0.0006157635467979317</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3703,25 +3706,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.2000759661950431</v>
+        <v>0.196277656442883</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1143638127149282</v>
+        <v>0.110836786879464</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1269729300767128</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.05290344080646503</v>
+        <v>0.0495709405981839</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.02948843271423907</v>
+        <v>0.02623004235907467</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.01118848290431118</v>
+        <v>-0.01431812847195058</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.009716345400407556</v>
+        <v>-0.003165057762304135</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3749,25 +3752,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.1706349206349207</v>
+        <v>0.1578995939461056</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.164402423352304</v>
+        <v>0.1517348999449237</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0.1225445199192217</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1005552663543292</v>
+        <v>0.08858233558910289</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.08363232530326314</v>
+        <v>0.07184349906031096</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0.0372884127892712</v>
+        <v>0.02600376155041295</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.004238951252060641</v>
+        <v>-0.01087899093417422</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3791,25 +3794,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2576449912126539</v>
+        <v>0.2513181019332162</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1839841164791529</v>
+        <v>0.1780277961614825</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1197882197220386</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.118125</v>
+        <v>0.1125</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.08720753570343365</v>
+        <v>0.08173807353388041</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.05732860520094563</v>
+        <v>0.05200945626477527</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.002230897936419396</v>
+        <v>-0.005030743432084983</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3837,25 +3840,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.08274143302180681</v>
+        <v>0.07613707165109029</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1074432832016314</v>
+        <v>0.100688248789192</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.1182768289574305</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.006486736939650184</v>
+        <v>0.000347503764624113</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.0129400792725578</v>
+        <v>0.006761482863138157</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.009687713699566891</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>0.003464603302921754</v>
+        <v>-0.01572828812400273</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>-0.006099666244677171</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3879,25 +3882,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.2472006890611544</v>
+        <v>0.2409991386735575</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.3009883198562444</v>
+        <v>0.2945193171608267</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0.1176999101527405</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1626786574594508</v>
+        <v>0.1568973823671109</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.139977956227366</v>
+        <v>0.1343095575499922</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.1639871382636657</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>0.004718290313627582</v>
+        <v>0.1581993569131834</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-0.004972375690607711</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3924,26 +3927,26 @@
           <t>Health Equipment</t>
         </is>
       </c>
-      <c r="F76" s="3" t="n">
-        <v>0.003912032142102007</v>
+      <c r="F76" s="5" t="n">
+        <v>-0.008458447874814978</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.2460629921259843</v>
+        <v>0.2307086614173228</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0.1053805774278216</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.09680027723229778</v>
+        <v>0.08328520272611772</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.1819992530810408</v>
+        <v>0.1674343333748289</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.1272705686809925</v>
+        <v>0.1133800308678619</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.001472289410032634</v>
+        <v>-0.0123222748815166</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3971,25 +3974,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.08464384828862159</v>
+        <v>0.08869102682701202</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1340829403941484</v>
+        <v>0.138314593156813</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0.1038568492322574</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>-0.04480651731160901</v>
+        <v>-0.04124236252545821</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.02952475030183299</v>
+        <v>0.03336626056415337</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.02738225629791891</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>-0.003717472118959231</v>
+        <v>0.03121577217962779</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0.003731343283582156</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4017,25 +4020,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1257856754869249</v>
+        <v>0.1215954062233258</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1381501529771711</v>
+        <v>0.1339138620851965</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0.1026908292147173</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.09082706766917292</v>
+        <v>0.08676691729323305</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.09643288996372457</v>
+        <v>0.09235187424425639</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.03215708594194666</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>0.003180749550546258</v>
+        <v>0.02831531018781996</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>-0.003722084367245748</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4063,25 +4066,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.008502138339010035</v>
+        <v>0.003073062050244602</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.06561857343868382</v>
+        <v>0.05988202186383806</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.073195150990367</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.01347729151531851</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>0.0005843792875654952</v>
+        <v>-0.0187880457927303</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>-0.004802073276081065</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.007059832076851347</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>0.01015775298191612</v>
+        <v>-0.01240513350646733</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>-0.005383306670729504</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4109,25 +4112,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1130065975494816</v>
+        <v>0.1100848256361924</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1353715988847226</v>
+        <v>0.1323911162388232</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>0.06095567733871743</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.03157290470723306</v>
+        <v>-0.0341151385927505</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.07462007462007469</v>
+        <v>0.07179907179907175</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.07014046216583614</v>
+        <v>0.06733121884911641</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.003375812304835746</v>
+        <v>-0.002625116436616115</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4151,25 +4154,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.09732922444786851</v>
+        <v>0.07909604519774027</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.002567693744164434</v>
+        <v>-0.01914098972922507</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0.05835667600373484</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>-0.01202312138728334</v>
+        <v>-0.02843930635838143</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-0.08794023479188906</v>
+        <v>-0.1030949839914621</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.05756506396118233</v>
+        <v>-0.0732245258050287</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.01042149143121818</v>
+        <v>-0.01661596068336046</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4197,25 +4200,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1205353841603196</v>
+        <v>0.1118095097241736</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.0407995054605399</v>
+        <v>0.03269455319733483</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0.05192664331341446</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.09403992635644931</v>
+        <v>0.08552037832569215</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.06505007907221927</v>
+        <v>0.05675628184853276</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.01057786483839374</v>
+        <v>-0.01828272935031028</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-0.01286603042246182</v>
+        <v>-0.007787236850788637</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4243,25 +4246,25 @@
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>-0.1397079874033782</v>
+        <v>-0.1425708559977097</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.02245661789724407</v>
+        <v>0.01905410003402519</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.04185096971759106</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.07359771346909616</v>
+        <v>0.07002500893176133</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.04412786657400969</v>
+        <v>0.04065323141070176</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.01861528412802094</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>0.01212529471202428</v>
+        <v>-0.02188112344872639</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>-0.003327787021630613</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4285,25 +4288,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.08191947328437577</v>
+        <v>0.07672828564193468</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.07107044372023075</v>
+        <v>0.0659313111055404</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0.04123840561544245</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.02323075080828629</v>
+        <v>0.01832115914261756</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.01352152769540971</v>
+        <v>0.008658522120744916</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>0.0286505356927893</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>0.004348848142924355</v>
+        <v>0.02371493920789702</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>-0.00479812755997655</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4327,25 +4330,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.04633548674537757</v>
+        <v>0.03898418355981281</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.003606279168434368</v>
+        <v>-0.01060670343657188</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0.03528496676566273</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.03877626244010313</v>
+        <v>0.03147806855879076</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.03374660699875287</v>
+        <v>0.02648375027510808</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.03756574004507884</v>
+        <v>-0.04432757325319314</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.01695269987442449</v>
+        <v>-0.007025761124121899</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4369,25 +4372,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.1280584683825867</v>
+        <v>0.1197966317127424</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.1112850211300673</v>
+        <v>0.1031460322429176</v>
       </c>
       <c r="H86" s="3" t="n">
         <v>0.02989513225856943</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.0848804339521736</v>
+        <v>0.07693483077393237</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.1076443057722309</v>
+        <v>0.09953198127925122</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0.07902735562310026</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>0.003108222661768911</v>
+        <v>0.07112462006079046</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>-0.007323943661971755</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4411,25 +4414,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.1288129007188654</v>
+        <v>0.121624247134253</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.1094137865189995</v>
+        <v>0.1023486729043346</v>
       </c>
       <c r="H87" s="3" t="n">
         <v>0.02367767805995813</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.08720059880239539</v>
+        <v>0.08027694610778435</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.1145213888356034</v>
+        <v>0.1074237483215039</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0.08375303115090471</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>0.003800967519004717</v>
+        <v>0.07685133370639807</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-0.006368330464716077</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4457,25 +4460,25 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.04506946797695699</v>
+        <v>-0.04608607251779073</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.01003584229390686</v>
+        <v>0.008960573476702427</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0.01827956989247315</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.04953445065176898</v>
+        <v>0.04841713221601474</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.02997076023391809</v>
+        <v>0.02887426900584789</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.008095740936290063</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>0.005710206995003464</v>
+        <v>-0.009151707145371391</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>-0.001064584811923397</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4520,8 +4523,8 @@
       <c r="K89" s="5" t="n">
         <v>-0.01383177570093463</v>
       </c>
-      <c r="L89" s="3" t="n">
-        <v>0.003041825095057016</v>
+      <c r="L89" s="21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4549,25 +4552,25 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-0.009906490139801938</v>
+        <v>-0.01120266641977608</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.02489286039937999</v>
+        <v>-0.02616941734293798</v>
       </c>
       <c r="H90" s="5" t="n">
         <v>-0.002188383331813593</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-0.03204199855177414</v>
+        <v>-0.0333091962346127</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>-0.04141269272140558</v>
+        <v>-0.04266762280387237</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>-0.02275427213743952</v>
+        <v>-0.02403362880380155</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.004653760238272575</v>
+        <v>-0.001309145315129934</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4580,7 +4583,7 @@
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" s="21" t="inlineStr">
+      <c r="D91" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4591,25 +4594,25 @@
         </is>
       </c>
       <c r="F91" s="5" t="n">
-        <v>-0.001827563964738821</v>
+        <v>-0.00365512792947742</v>
       </c>
       <c r="G91" s="5" t="n">
-        <v>-0.0216016859852477</v>
+        <v>-0.02339304531085351</v>
       </c>
       <c r="H91" s="5" t="n">
         <v>-0.003477344573235119</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.03220762976860536</v>
+        <v>-0.03397957056493628</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.02242577384712585</v>
+        <v>-0.02421562434196667</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.01818758591519509</v>
+        <v>-0.01998519615099914</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>-0.004075941220637258</v>
+        <v>-0.001830910070005243</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4622,7 +4625,7 @@
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr"/>
-      <c r="D92" s="21" t="inlineStr">
+      <c r="D92" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4633,25 +4636,25 @@
         </is>
       </c>
       <c r="F92" s="5" t="n">
-        <v>-0.004860857941426766</v>
+        <v>-0.004617815044355433</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-0.007634512845370756</v>
+        <v>-0.007392147358216139</v>
       </c>
       <c r="H92" s="5" t="n">
         <v>-0.004968492486669862</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.01325460898903474</v>
+        <v>-0.01301361609832508</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.00715324927255101</v>
+        <v>-0.006910766246362887</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.002679332602606221</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>-0.001828376401755261</v>
+        <v>-0.002435756911460252</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>0.0002442300647209628</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4674,26 +4677,26 @@
           <t>High Yield Credit</t>
         </is>
       </c>
-      <c r="F93" s="3" t="n">
-        <v>0.0002508780732564109</v>
+      <c r="F93" s="5" t="n">
+        <v>-0.0007526342197692326</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.007962179646678336</v>
+        <v>-0.008957452102513086</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>-0.005100771336153276</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-0.0170118343195268</v>
+        <v>-0.01799802761341229</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.007962179646678336</v>
+        <v>-0.008957452102513086</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.0028760785294486</v>
+        <v>-0.003876453670126345</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.001627644923000049</v>
+        <v>-0.001003260596940003</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4706,7 +4709,7 @@
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr"/>
-      <c r="D94" s="21" t="inlineStr">
+      <c r="D94" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4717,25 +4720,25 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.05560619872379224</v>
+        <v>-0.06244302643573385</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.0464795213989877</v>
+        <v>-0.05338242061665899</v>
       </c>
       <c r="H94" s="5" t="n">
         <v>-0.005752416014726203</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.04877768851141973</v>
+        <v>-0.05566395041891425</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.0320018687222613</v>
+        <v>-0.03900957720158849</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.04096274010645695</v>
+        <v>-0.04790557741263601</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.003007337904486929</v>
+        <v>-0.007239382239382142</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4763,25 +4766,25 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>-0.0280447146499313</v>
+        <v>-0.02333790939399893</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05851063829787229</v>
+        <v>-0.05395136778115506</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>-0.06174012158054709</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.04213374565133354</v>
+        <v>-0.03749516814843457</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.002832861189801639</v>
+        <v>0.007689194658033083</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>0.003441992306134845</v>
+        <v>0.00830127556185456</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.0006056935190794643</v>
+        <v>0.004842615012106366</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4809,25 +4812,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.1536198725281909</v>
+        <v>-0.1663670534401046</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.111663807890223</v>
+        <v>-0.1250428816466552</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>-0.20926243567753</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.06563786008230443</v>
+        <v>0.04958847736625516</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.09910865874363339</v>
+        <v>0.08255517826825121</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.1234273318872017</v>
+        <v>0.1065075921908893</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.01220675185962239</v>
+        <v>-0.01506082255261632</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -203,9 +203,6 @@
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -676,25 +673,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.212541806020067</v>
+        <v>1.195150501672241</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.223697478991597</v>
+        <v>1.206218487394958</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>2.156638655462185</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.4223822833799185</v>
+        <v>0.4112018920662226</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.01024835427887494</v>
+        <v>-0.01802812687013766</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.2955489298264296</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.003793338896897147</v>
+        <v>-0.3010861463102971</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>-0.004096806008648701</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -722,25 +719,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.513105639396346</v>
+        <v>1.504028140247362</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.290145796711819</v>
+        <v>1.281873642849757</v>
       </c>
       <c r="H3" s="6" t="n">
         <v>1.94643780374315</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4565303169801394</v>
+        <v>0.4512692358279626</v>
       </c>
       <c r="J3" s="3" t="n">
-        <v>0.03727988010490813</v>
+        <v>0.03353315848632454</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.222740831724864</v>
+        <v>-0.2255483418143533</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.005675884302774437</v>
+        <v>0.002043318348998957</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -768,25 +765,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.784867075664622</v>
+        <v>1.758691206543967</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.294910684192787</v>
+        <v>1.273340074148972</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>1.875294910684193</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.598732096736323</v>
+        <v>0.5837050950927447</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.1386287625418061</v>
+        <v>0.1279264214046825</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.2018520689250967</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.003981126511353628</v>
+        <v>-0.2093541202672605</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>-0.005455617811854774</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -810,25 +807,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.366314619232907</v>
+        <v>2.321845469705392</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.495261639884631</v>
+        <v>1.46229913473424</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>1.772970745776679</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.4841924679356262</v>
+        <v>0.4645862266154726</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>0.1301318736003982</v>
+        <v>0.1152027867628764</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.100148588410104</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.008213096559378519</v>
+        <v>-0.112035661218425</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>-0.005105438401775686</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -852,25 +849,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.346765690184752</v>
+        <v>1.333012423783982</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.132650085405991</v>
+        <v>1.120151647710703</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>1.669499645877599</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4781980941380306</v>
+        <v>0.4695350851862545</v>
       </c>
       <c r="J6" s="3" t="n">
-        <v>0.1093533287101247</v>
+        <v>0.1028519417475728</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.20110493788626</v>
+        <v>-0.2057868780822774</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.006448822303487756</v>
+        <v>0.0005505092210293938</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -898,25 +895,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.298987341772152</v>
+        <v>1.288607594936709</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.054989816700611</v>
+        <v>1.04571169947952</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.536773025571396</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.441199809554039</v>
+        <v>0.4346929058879545</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.09872958257713238</v>
+        <v>0.09376890502117363</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.1899197145405886</v>
+        <v>-0.1935771632471007</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.00587062472308375</v>
+        <v>0.001329198050509683</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -944,25 +941,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.284213118791561</v>
+        <v>1.275428946720302</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9270032550730662</v>
+        <v>0.9195927695823813</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1.271244546021193</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3792693203787241</v>
+        <v>0.3739652010112529</v>
       </c>
       <c r="J8" s="3" t="n">
-        <v>0.09820018945374165</v>
+        <v>0.09397694979475846</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.1515650490173657</v>
+        <v>-0.1548277912454832</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.006092820596264703</v>
+        <v>0.002223789119705</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -990,25 +987,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8878735490244503</v>
+        <v>0.8812052358607063</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8653001464128844</v>
+        <v>0.8587115666178626</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.9102000976085898</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.09278055754110071</v>
+        <v>0.0889206576125805</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>-0.1337262012692656</v>
+        <v>-0.1367860380779691</v>
       </c>
       <c r="K9" s="5" t="n">
-        <v>-0.02350536535513548</v>
+        <v>-0.02695452222789985</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.00486394110687538</v>
+        <v>0.001314578677533929</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1036,25 +1033,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.11137026239067</v>
+        <v>1.095432458697765</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8613776559287183</v>
+        <v>0.8473269362577107</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.8610349554489376</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.5960916838084043</v>
+        <v>0.58404349103732</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.2086114819759679</v>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v>0.0001841451063437916</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0.00676552363299332</v>
+        <v>0.1994882064975523</v>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>-0.007365804253751884</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>-0.0008341056533828217</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1078,25 +1075,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.7303334412431206</v>
+        <v>0.7382108557246143</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8719355591874853</v>
+        <v>0.8804576231613357</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.8474200326873687</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.2853707414829658</v>
+        <v>0.2912224448897796</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2209700753826238</v>
+        <v>0.2265285920962461</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.0132701421800947</v>
+        <v>0.01788309636650887</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.01250153959847278</v>
+        <v>-0.008005912058135167</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1124,25 +1121,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.427710843373494</v>
+        <v>1.4248297537978</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.153077816492451</v>
+        <v>1.150522648083624</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.7879210220673636</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.09291357151279334</v>
+        <v>0.09161655465157414</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.1643009672151738</v>
+        <v>0.1629192312523553</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.2042354163959985</v>
+        <v>0.2028062881642199</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.01832238932429575</v>
+        <v>-0.01948739673797928</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1170,25 +1167,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.4592901878914404</v>
+        <v>0.4509394572025052</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.3865117597052989</v>
+        <v>0.378577500708416</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.7376027203173705</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.006699147381242332</v>
+        <v>-0.01238327243199344</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.1657289002557545</v>
+        <v>-0.1705029838022165</v>
       </c>
       <c r="K13" s="5" t="n">
-        <v>-0.202054794520548</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0.0008181632235630953</v>
+        <v>-0.20662100456621</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>-0.004908979341378683</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1216,25 +1213,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.274081429990069</v>
+        <v>1.273088381330685</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.882836587872559</v>
+        <v>0.8820143884892087</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.7163412127440905</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.05773672055427248</v>
+        <v>0.05727482678983842</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.1540884465163159</v>
+        <v>0.1535844777623787</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.09700598802395199</v>
+        <v>0.09652694610778445</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-0.007583965330444253</v>
+        <v>-0.008017334777898122</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1258,25 +1255,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.784041630529054</v>
+        <v>1.816420930904886</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.034220532319392</v>
+        <v>1.057879171947613</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.6362484157160961</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.02120890774125139</v>
+        <v>0.03308589607635204</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.08715285617520885</v>
+        <v>0.09979679385865881</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.2432223082881488</v>
+        <v>0.2576813839400982</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>-0.02864635868468834</v>
+        <v>-0.01734920314706478</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1304,25 +1301,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4913718723037102</v>
+        <v>0.4866264020707507</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4398167430237401</v>
+        <v>0.4352353186172429</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.606413994169096</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.07560672059738649</v>
+        <v>0.07218419415059119</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.07764140875133396</v>
+        <v>-0.08057630736392729</v>
       </c>
       <c r="K16" s="5" t="n">
-        <v>-0.1037075447238787</v>
+        <v>-0.1065595022037853</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.0002891844997107151</v>
+        <v>-0.003470213996529692</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1346,25 +1343,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.104524728165556</v>
+        <v>1.098211153981059</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.800720288115246</v>
+        <v>0.7953181272509005</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.6047418967587035</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.2046659597030752</v>
+        <v>-0.207051961823966</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.09990999099909992</v>
+        <v>-0.1026102610261026</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1221245558256967</v>
+        <v>0.1187581821582195</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.0003332222592469236</v>
+        <v>-0.003332222592469236</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1392,25 +1389,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.662045060658579</v>
+        <v>1.668977469670711</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.075675675675675</v>
+        <v>1.081081081081081</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.6040540540540538</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3321769297484822</v>
+        <v>0.3356461405030358</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.310580204778157</v>
+        <v>0.3139931740614335</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.2940185341196293</v>
+        <v>0.2973883740522327</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.01030927835051543</v>
+        <v>-0.00773195876288657</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1438,25 +1435,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.5868723928230386</v>
+        <v>0.5865205809921095</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4732863608791005</v>
+        <v>0.4729597312304605</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.5617096729037376</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3405510975247314</v>
+        <v>0.3402538954697916</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.1841878258260512</v>
+        <v>0.1839252897273376</v>
       </c>
       <c r="K19" s="5" t="n">
-        <v>-0.05661955839732291</v>
+        <v>-0.05682870716185118</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-0.001233669692847883</v>
+        <v>-0.001455097586435916</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1480,25 +1477,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.3684608596999874</v>
+        <v>0.3614017395688895</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.2452397338839183</v>
+        <v>0.2388162422573983</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.5284468914888736</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.01488203266787658</v>
+        <v>-0.01996370235934664</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.1444558278824178</v>
+        <v>-0.1488690992197966</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.1852908067542214</v>
+        <v>-0.1894934333958724</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>-0.008403361344537785</v>
+        <v>-0.01351845085860437</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1526,25 +1523,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.564810803004044</v>
+        <v>0.5455300404390526</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.778229115378303</v>
+        <v>0.7563187264073528</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.5264647956671589</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.2439794483194122</v>
+        <v>0.2286517982720515</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.03312957344279854</v>
+        <v>-0.04504283419596644</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.164932935515953</v>
+        <v>0.1505792543612074</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.03604981951184527</v>
+        <v>0.0232841672443882</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1572,25 +1569,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.8545918367346941</v>
+        <v>0.8441043083900226</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.7047941636268891</v>
+        <v>0.6951537258989056</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0.5151120375195413</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1221059852512434</v>
+        <v>0.1157605899502658</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.06217532467532472</v>
+        <v>0.05616883116883109</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.1251934651762685</v>
+        <v>0.1188306104901118</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.005018248175182483</v>
+        <v>-0.01064476885644772</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1618,25 +1615,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>1.000505902192243</v>
+        <v>0.9876897133220912</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.6179759956355702</v>
+        <v>0.6076104746317514</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.458401527550464</v>
       </c>
       <c r="I23" s="5" t="n">
-        <v>-0.0007580862533692612</v>
+        <v>-0.007159703504043047</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.0008422471153036737</v>
+        <v>-0.007243325191611194</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.1094173758533619</v>
+        <v>0.1023099223791264</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>-0.0009263938015833251</v>
+        <v>-0.00732693279434049</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1664,25 +1661,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.635836579400308</v>
+        <v>0.6256907328562371</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.512902144772118</v>
+        <v>0.5035187667560324</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.4537533512064345</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1823479342630787</v>
+        <v>0.1750147318797879</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.1142099092984514</v>
+        <v>0.1072993151107546</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.04068695251267873</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>0.002665186007773546</v>
+        <v>0.03423236514522809</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>-0.003553581343697876</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1706,25 +1703,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.6118187332120268</v>
+        <v>0.6112988475868644</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4160006089670396</v>
+        <v>0.4155438836872953</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.4502550049478573</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2928829580205727</v>
+        <v>0.2924659438420907</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1662695924764892</v>
+        <v>0.1658934169278998</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>-0.02361956749947514</v>
+        <v>-0.02393449506613476</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.00177715547417745</v>
+        <v>0.001454036297054317</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1752,25 +1749,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.4898312418866293</v>
+        <v>0.5004327131112074</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.5560409761976501</v>
+        <v>0.5671135884302503</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.4325851159987948</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.1980513831699819</v>
+        <v>0.2065765818013108</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.2246131958029522</v>
+        <v>0.2333274052996621</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.08617698091382309</v>
+        <v>0.09390609390609406</v>
       </c>
       <c r="L26" s="5" t="n">
-        <v>-0.01134242641780314</v>
+        <v>-0.004307250538406193</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1798,25 +1795,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.3708183104376797</v>
+        <v>0.3657523618273926</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.2448091508143728</v>
+        <v>0.2402088772845954</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.4208214182104522</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.1737856110047287</v>
+        <v>0.1694478096056899</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.05768011831819142</v>
+        <v>0.05377139235157391</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>-0.1238806405507101</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>0.00216876313769987</v>
+        <v>-0.1271183968730858</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>-0.00153481698975666</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1840,25 +1837,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.2759266192437289</v>
+        <v>0.2714339198801947</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.323495145631068</v>
+        <v>0.3188349514563107</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.4031067961165049</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.1344873501997337</v>
+        <v>0.1304926764314249</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.0512029611351017</v>
+        <v>0.04750154225786551</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.05673955161915323</v>
+        <v>-0.0600608912261279</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.004672897196261738</v>
+        <v>-0.008177570093457986</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1882,25 +1879,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.4658136745301877</v>
+        <v>0.4626149540183926</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.2675252830841039</v>
+        <v>0.2647592704641715</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.3963177456997147</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.2233252690414613</v>
+        <v>0.2206557103528821</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.09604604230510505</v>
+        <v>0.09365423424770158</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.09223721678841157</v>
+        <v>-0.09421815030333047</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.000953808420765867</v>
+        <v>-0.003133941953944785</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1928,25 +1925,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5709275380472225</v>
+        <v>0.5704265046658734</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3834316915779605</v>
+        <v>0.3829904583310353</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3911532733991505</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.2644553107828804</v>
+        <v>0.2640520239955637</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.1500160469487872</v>
+        <v>0.1496492595479344</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.005550489632478173</v>
+        <v>-0.005867660468619862</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.001472929936305656</v>
+        <v>-0.001791401273885329</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1974,25 +1971,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5626839638068244</v>
+        <v>0.5628474871906683</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3934577622241664</v>
+        <v>0.3936035773306115</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3880626032857002</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.2858360243989952</v>
+        <v>0.2859705776820956</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1639397507206366</v>
+        <v>0.1640615484551988</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.003886826808600086</v>
+        <v>0.003991876181805631</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.0003140265177947743</v>
+        <v>0.0004187020237265138</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2016,25 +2013,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5587701089776855</v>
+        <v>0.5588998443175921</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.392075078206465</v>
+        <v>0.3921909396361951</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3847758081334722</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.2851641886832819</v>
+        <v>0.2852711519948659</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.1644698584997093</v>
+        <v>0.1645667765070749</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.005271084337349574</v>
+        <v>0.005354752342704217</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.0006662780044974781</v>
+        <v>0.0007495627550595518</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2062,25 +2059,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.3658660351826795</v>
+        <v>0.3596075778078485</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2955238248034655</v>
+        <v>0.2895876784854805</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.3742980908069951</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1156396794694667</v>
+        <v>0.1105277701022382</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.01102265768524191</v>
+        <v>-0.01555419473361919</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.05731963576932053</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0.001364087301587213</v>
+        <v>-0.06163903805743642</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>-0.003224206349206393</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2108,25 +2105,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.4915853658536586</v>
+        <v>0.4910975609756096</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2600185433192543</v>
+        <v>0.2596064695580509</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3621098176573607</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.01299225306649454</v>
+        <v>-0.01331504196255651</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.05031446540880491</v>
+        <v>-0.05062504852861249</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.07495083950990766</v>
+        <v>-0.07525336560278328</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-8.175277959443505e-05</v>
+        <v>-0.0004087638979725083</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2154,25 +2151,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.2657707722878986</v>
+        <v>0.2654339698898656</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2952610718593831</v>
+        <v>0.2949164225400658</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.3577804583835946</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.1174144441471174</v>
+        <v>0.1171171171171173</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.04429254195843058</v>
+        <v>0.04401467155718586</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.04604528378515582</v>
+        <v>-0.04629911666158992</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.008154970837402131</v>
+        <v>-0.00841888575123384</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2200,25 +2197,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.4653482275162431</v>
+        <v>0.4615866864242562</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.1873556848619193</v>
+        <v>0.1843077491456544</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.3105661771497183</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>-0.05806711606096115</v>
+        <v>-0.06048505275498239</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.007833603457590432</v>
+        <v>-0.01038048931079727</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.09401317875894144</v>
+        <v>-0.09633884210155408</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.01787692425226328</v>
+        <v>-0.0203980289545056</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2246,25 +2243,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.1688739187016766</v>
+        <v>0.1638980326111918</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.1707560190154884</v>
+        <v>0.165772120840362</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.3045545161785002</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.0884659252922726</v>
+        <v>0.08383233532934131</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.04467246449352447</v>
+        <v>-0.04873928549083417</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.1025625955095802</v>
+        <v>-0.1063829787234042</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.003133772932036205</v>
+        <v>-0.007377423777502057</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2288,25 +2285,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.3703306592123152</v>
+        <v>0.3685883321526355</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2667209429921595</v>
+        <v>0.2651103520291676</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.303339763897984</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1508997057262773</v>
+        <v>0.1494363773779084</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.07183933866474979</v>
+        <v>0.07047653278222055</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.02809614340032585</v>
+        <v>-0.02933188484519289</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.001004983040911012</v>
+        <v>-0.00227516993984056</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2330,25 +2327,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3707614307642215</v>
+        <v>0.3688543653193173</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2671453755858451</v>
+        <v>0.2653824654942598</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.3027045620673348</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1509470806483109</v>
+        <v>0.1493458308924038</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.07202619134230637</v>
+        <v>0.07053473990542036</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.02729643198996612</v>
+        <v>-0.02864970129055688</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.001016949152542357</v>
+        <v>-0.002406779661016878</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2372,25 +2369,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.1948185463143828</v>
+        <v>0.1967376032349817</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.234675448847339</v>
+        <v>0.2366585219023338</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.2950175289493253</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1144994246260072</v>
+        <v>0.1162894770489709</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.04090040601862932</v>
+        <v>0.04257224743252941</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.04659557013945848</v>
+        <v>-0.04506426032266875</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.009038199181445994</v>
+        <v>-0.007446566621191253</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2414,25 +2411,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.2993615511941359</v>
+        <v>0.2936864506975645</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.20267016852703</v>
+        <v>0.1974173779820529</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.2895600787918582</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.08275862068965534</v>
+        <v>0.07802955665024625</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.03240007043493565</v>
+        <v>-0.03662616657862294</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.06737949762389683</v>
+        <v>-0.0714528173794976</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.006508768757909955</v>
+        <v>-0.01084794792985</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2456,25 +2453,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4639567480977174</v>
+        <v>0.456948338005607</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.3004268943436499</v>
+        <v>0.2942013518320883</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2673425827107792</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.104380664652568</v>
+        <v>0.09909365558912397</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.0626453488372094</v>
+        <v>0.05755813953488387</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.02610526315789463</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>0.0006843690117710466</v>
+        <v>0.02119298245614032</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>-0.004106214070626835</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2502,25 +2499,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.7718727404193781</v>
+        <v>0.7617498192335501</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.6304058549567531</v>
+        <v>0.6210911510312707</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.2611443779108449</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.3686121195196872</v>
+        <v>0.3607930745601786</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.1821032320308731</v>
+        <v>0.1753497346840327</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.2927987338433131</v>
-      </c>
-      <c r="L43" s="3" t="n">
-        <v>0.0006124948958758925</v>
+        <v>0.2854128198364547</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>-0.005104124132298882</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2548,25 +2545,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.3042394014962595</v>
+        <v>0.3062797551575607</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.4310945273631841</v>
+        <v>0.4333333333333331</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.258955223880597</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.2677390921110621</v>
+        <v>0.2697223446452179</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.1987914148780996</v>
+        <v>0.2006668055844967</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.1367318711717052</v>
+        <v>0.1385101758545741</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-0.005359612724758045</v>
+        <v>-0.003803596127247677</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2590,25 +2587,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3162809581810802</v>
+        <v>0.3146569224522942</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.3120194253338731</v>
+        <v>0.3104006475111292</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0.2585997571833265</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1423537702607471</v>
+        <v>0.1409443269908388</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.07743436357593891</v>
+        <v>0.07610501827849792</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.04244372990353695</v>
+        <v>0.04115755627009654</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-0.002768378960319784</v>
+        <v>-0.003998769609350861</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2632,25 +2629,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.3431791682860474</v>
+        <v>0.3427905169063352</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2463036422646954</v>
+        <v>0.2459430219978365</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.2407741315061906</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1229286255821511</v>
+        <v>0.1226037041048413</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.05644996943142466</v>
+        <v>0.0561442836763808</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.004456500678163167</v>
+        <v>0.004165859329587462</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.003651739381126284</v>
+        <v>-0.00394003459542569</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2674,25 +2671,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3008241758241759</v>
+        <v>0.2956043956043957</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2513213530655389</v>
+        <v>0.2463002114164903</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.2402219873150104</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1060499883204857</v>
+        <v>0.101611772950245</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.07418330308529963</v>
+        <v>0.06987295825771311</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.008949499254208515</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>0.001480541455160855</v>
+        <v>0.004900916258256949</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>-0.002538071065989911</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2720,25 +2717,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.1725080326476347</v>
+        <v>0.1811131218377222</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.314725857213848</v>
+        <v>0.3243746894152726</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2382391916514826</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1051239209133947</v>
+        <v>0.1132344750765804</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.1652352638919476</v>
+        <v>0.1737869779050136</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.0617705093475136</v>
+        <v>0.06956289087321488</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.01084247258225313</v>
+        <v>-0.003583000997008923</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2762,25 +2759,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4600843019542724</v>
+        <v>0.4607229531230042</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.1628687690742625</v>
+        <v>0.1633774160732453</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2330620549338758</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>-0.01618039418194328</v>
+        <v>-0.01575006454944483</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.04602855051244514</v>
+        <v>0.04648609077598831</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.05692599620493355</v>
+        <v>-0.05651348898605724</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.01803968731208649</v>
+        <v>-0.01761017094751305</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2808,25 +2805,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4614575750222438</v>
+        <v>0.4519129661085497</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.4755410371580238</v>
+        <v>0.4659044507962433</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2260514495712536</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.2565546978232145</v>
+        <v>0.2483482856944155</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.06545583205566685</v>
+        <v>0.05849746432362291</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.2034903083993873</v>
+        <v>0.195630453606874</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.02333484367920247</v>
+        <v>0.01665156320797467</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2850,25 +2847,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.2680881821467294</v>
+        <v>0.2664980122876763</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1541345964081311</v>
+        <v>0.1526873232024211</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>0.2185382540622327</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.0604448742746615</v>
+        <v>0.05911508704061896</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.004926108374384119</v>
+        <v>0.003665941115820859</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.05285320952329531</v>
+        <v>-0.05404092209685252</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>-0.009596928982725461</v>
+        <v>-0.01083888449813697</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2892,25 +2889,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4646280237334552</v>
+        <v>0.4545869465997261</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.4716808071543226</v>
+        <v>0.4615913781242835</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0.2178399449667507</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.2571988246816848</v>
+        <v>0.2485798237022527</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.07594300083822314</v>
+        <v>0.06856663872590119</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>0.2084353229147056</v>
+        <v>0.2001506307663341</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.0239310784939375</v>
+        <v>0.01691129546904913</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2934,25 +2931,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.5719689805182524</v>
+        <v>0.5766975600529602</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.3402676987582649</v>
+        <v>0.3442993065634576</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2177068214804065</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>-0.08870614035087721</v>
+        <v>-0.0859649122807018</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.04306275187104192</v>
+        <v>-0.04018422567645363</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.1006489206727585</v>
+        <v>0.1039597404317307</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.008470532092579308</v>
+        <v>-0.005487950369840067</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2976,25 +2973,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.5683013613861385</v>
+        <v>0.5727103960396038</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.3384605228412993</v>
+        <v>0.342223395827832</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.2159360971745445</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.0886616473761096</v>
+        <v>-0.08609956174851108</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.04286456120473969</v>
+        <v>-0.04017372421281229</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.1007655138715458</v>
+        <v>0.103860144416092</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.008290738340384962</v>
+        <v>-0.005502702438308638</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3022,25 +3019,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1549176150840836</v>
+        <v>0.1515202989638187</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2093561010316614</v>
+        <v>0.2057986481679119</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.2134471718249733</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.06952965235173814</v>
+        <v>0.06638351423627498</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.05919925221997202</v>
+        <v>0.0560835021031314</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.003371445323951949</v>
+        <v>-0.006303136909996954</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>-0.00686532281624308</v>
+        <v>-0.009786736780601601</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3068,25 +3065,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3899162451281202</v>
+        <v>0.389418691433784</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.148013698630137</v>
+        <v>0.1476027397260276</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.2099315068493151</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>-0.03992438996448622</v>
+        <v>-0.04026807194409443</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.0009555091071962174</v>
+        <v>0.0005971931919976914</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.05117463911689779</v>
+        <v>-0.05151429380130201</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.01411681665784348</v>
+        <v>-0.01446973707428967</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3114,25 +3111,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4149522957662495</v>
+        <v>0.4007901013714967</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.4813109637143973</v>
+        <v>0.4664845883730004</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0.2037456106125632</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.3536081003993155</v>
+        <v>0.340059897318882</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.0652039728410303</v>
+        <v>0.05454239380506154</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.2305847270841439</v>
+        <v>0.218267859458058</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.02092072711627413</v>
+        <v>0.01070237711089606</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3156,25 +3153,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3680180180180181</v>
+        <v>0.3628378378378379</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2196787148594379</v>
+        <v>0.2150602409638553</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.1985943775100403</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.07561537099344795</v>
+        <v>0.071542411900124</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.03071440692346861</v>
+        <v>0.02681147123706085</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.01759088624560246</v>
+        <v>0.01373764449656556</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.0008225037012665748</v>
+        <v>-0.004606020727093263</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3198,25 +3195,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2529644268774704</v>
+        <v>0.2536830758174633</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.3158490566037735</v>
+        <v>0.3166037735849057</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>0.1966037735849058</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.16934942991281</v>
+        <v>0.1700201207243461</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.08730901153726212</v>
+        <v>0.087932647333957</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.09965310627562274</v>
+        <v>0.1002838221381268</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.0008595988538682153</v>
+        <v>-0.0002865329512893311</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3240,25 +3237,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.4228493400091036</v>
+        <v>0.4214838416021849</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.3924276169265035</v>
+        <v>0.3910913140311805</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.1875278396436526</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.2795742939009416</v>
+        <v>0.2783462955382727</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.005144694533762095</v>
+        <v>0.004180064308681564</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.172543135783946</v>
+        <v>0.171417854463616</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.0152646963299774</v>
+        <v>0.01429035401104262</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3282,25 +3279,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.2730558617822998</v>
+        <v>0.2725317622395316</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.2123851158307803</v>
+        <v>0.2118859935974666</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>0.1820763484905854</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1071956241551664</v>
+        <v>0.1067398069850052</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.0663659208574281</v>
+        <v>0.06592691271307016</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.02564027897089449</v>
+        <v>0.0252180370116919</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.003987331033312613</v>
+        <v>-0.004397375714043306</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3324,25 +3321,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.2732544614668837</v>
+        <v>0.2728390548669035</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2122990760663206</v>
+        <v>0.2119035565118339</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.1814485508163524</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1073745971646169</v>
+        <v>0.1070133098255703</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.06624829543873312</v>
+        <v>0.06590042579244715</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.02611245765095016</v>
+        <v>0.02577768255286106</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.004003379476181235</v>
+        <v>-0.004328329108988171</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3366,25 +3363,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.2734279382091231</v>
+        <v>0.273295623697529</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2126949125846591</v>
+        <v>0.2125689084895259</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1795400850527642</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1077795203084759</v>
+        <v>0.1076644173632793</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.06629551151550395</v>
+        <v>0.06618471893306732</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.02810826690168122</v>
+        <v>0.02800144213435884</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.003958602846054315</v>
+        <v>-0.004062095730918536</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3412,25 +3409,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.2878870179250408</v>
+        <v>0.2883623030961433</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2098867804177962</v>
+        <v>0.2103332801785998</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.166863339180354</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1042030504133193</v>
+        <v>0.1046105483758295</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.06922209695603154</v>
+        <v>0.06961668545659516</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.03687101976111729</v>
+        <v>0.03725366933610297</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>-0.004069202698800289</v>
+        <v>-0.003701661809876411</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3454,25 +3451,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2100529684396379</v>
+        <v>0.2104943721032884</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1943037630016882</v>
+        <v>0.1947394216631269</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1586886674290695</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1071789176090467</v>
+        <v>0.1075827948303714</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.0780082579630359</v>
+        <v>0.07840149429807308</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.03073741598909607</v>
+        <v>0.03111340884523184</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.006253115229507444</v>
+        <v>-0.005890615795912879</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3496,25 +3493,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2887708213670304</v>
+        <v>0.2886272257323377</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1792142950991986</v>
+        <v>0.1790829063198003</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.1550387596899225</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1057040778612788</v>
+        <v>0.1055808796353332</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.06845238095238093</v>
+        <v>0.06833333333333336</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.02093049709930606</v>
+        <v>0.02081674439767944</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>-0.004105636928539824</v>
+        <v>-0.004216600088770672</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3538,25 +3535,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.2637315359242793</v>
+        <v>0.263157894736842</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1616134985499604</v>
+        <v>0.1610862114421303</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.1355127867123649</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.0979317219038125</v>
+        <v>0.09743334163967088</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.05951665263917283</v>
+        <v>0.05903570999158347</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.02298583700951951</v>
+        <v>0.02252147666589277</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.00474361870341089</v>
+        <v>-0.005195391913259684</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3580,25 +3577,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.08137432188065108</v>
+        <v>0.07866184448462921</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.07200478040035874</v>
+        <v>0.0693158051986853</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1335524350164325</v>
       </c>
       <c r="I68" s="5" t="n">
-        <v>-0.03858520900321538</v>
+        <v>-0.04099678456591638</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>-0.06684005201560472</v>
+        <v>-0.06918075422626802</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.05429625724828668</v>
+        <v>-0.05666842382709536</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.00363636363636366</v>
+        <v>0.001118881118881143</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3622,25 +3619,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.1954461057363432</v>
+        <v>0.1961301671064204</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1110808356039965</v>
+        <v>0.1117166212534062</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1277929155313353</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.05013305863164219</v>
+        <v>0.05073396858099422</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.02565607445292195</v>
+        <v>0.02624297811687781</v>
       </c>
       <c r="K69" s="5" t="n">
-        <v>-0.0148183941370702</v>
+        <v>-0.01425465088185551</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.00342158859470465</v>
+        <v>-0.002851323828920505</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3664,25 +3661,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2205301748448958</v>
+        <v>0.2233502538071066</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.09884901828029791</v>
+        <v>0.1013879485443465</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1272850372376437</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.007918025151374186</v>
+        <v>0.01024685607824871</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>-0.05267765941923241</v>
+        <v>-0.05048883700569107</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.02522522522522508</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>-0.0006157635467979317</v>
+        <v>-0.02297297297297296</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0.001693349753694617</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3706,25 +3703,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.196277656442883</v>
+        <v>0.1964675719304909</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.110836786879464</v>
+        <v>0.1110131381712371</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1269729300767128</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.0495709405981839</v>
+        <v>0.04973756560859788</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.02623004235907467</v>
+        <v>0.02639296187683282</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.01431812847195058</v>
+        <v>-0.01416164619356863</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.003165057762304135</v>
+        <v>-0.003006804874188918</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3752,25 +3749,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.1578995939461056</v>
+        <v>0.1579918789221115</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1517348999449237</v>
+        <v>0.1518266935928034</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0.1225445199192217</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.08858233558910289</v>
+        <v>0.08866909595696693</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.07184349906031096</v>
+        <v>0.07192892533743378</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0.02600376155041295</v>
+        <v>0.02608553438547712</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.01087899093417422</v>
+        <v>-0.01080015766653519</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3794,25 +3791,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2513181019332162</v>
+        <v>0.2523725834797892</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1780277961614825</v>
+        <v>0.1790205162144276</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1197882197220386</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1125</v>
+        <v>0.1134375000000001</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.08173807353388041</v>
+        <v>0.08264965056213947</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.05200945626477527</v>
+        <v>0.05289598108747051</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.005030743432084983</v>
+        <v>-0.00419228619340406</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3840,25 +3837,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.07613707165109029</v>
+        <v>0.07289719626168223</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.100688248789192</v>
+        <v>0.0973744583227123</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.1182768289574305</v>
       </c>
-      <c r="I74" s="3" t="n">
-        <v>0.000347503764624113</v>
+      <c r="I74" s="5" t="n">
+        <v>-0.002664195528784941</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.006761482863138157</v>
+        <v>0.003730473303800386</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01572828812400273</v>
+        <v>-0.01869158878504673</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.006099666244677171</v>
+        <v>-0.00909195534583962</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3882,25 +3879,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.2409991386735575</v>
+        <v>0.2440999138673559</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.2945193171608267</v>
+        <v>0.2977538185085356</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0.1176999101527405</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1568973823671109</v>
+        <v>0.1597880199132808</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.1343095575499922</v>
+        <v>0.1371437568886789</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.1581993569131834</v>
+        <v>0.1610932475884244</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.004972375690607711</v>
+        <v>-0.002486187845303967</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3927,26 +3924,26 @@
           <t>Health Equipment</t>
         </is>
       </c>
-      <c r="F76" s="5" t="n">
-        <v>-0.008458447874814978</v>
+      <c r="F76" s="3" t="n">
+        <v>0.002854726157750065</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.2307086614173228</v>
+        <v>0.2447506561679789</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0.1053805774278216</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.08328520272611772</v>
+        <v>0.09564514265911983</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.1674343333748289</v>
+        <v>0.1807543881488858</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.1133800308678619</v>
+        <v>0.1260833432268786</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.0123222748815166</v>
+        <v>-0.001053185887309183</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3974,25 +3971,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.08869102682701202</v>
+        <v>0.09586031452358923</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.138314593156813</v>
+        <v>0.1458106637649619</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0.1038568492322574</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>-0.04124236252545821</v>
+        <v>-0.03492871690427701</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.03336626056415337</v>
+        <v>0.04017122160026343</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.03121577217962779</v>
+        <v>0.03800657174151145</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.003731343283582156</v>
+        <v>0.01034115138592751</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4020,25 +4017,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1215954062233258</v>
+        <v>0.1188018933809265</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1339138620851965</v>
+        <v>0.1310896681572136</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0.1026908292147173</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.08676691729323305</v>
+        <v>0.08406015037593995</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.09235187424425639</v>
+        <v>0.08963119709794443</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.02831531018781996</v>
+        <v>0.02575412635173602</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.003722084367245748</v>
+        <v>-0.006203473945409432</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4066,25 +4063,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.003073062050244602</v>
+        <v>0.0008194832133985308</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.05988202186383806</v>
+        <v>0.05750081177616617</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.073195150990367</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.0187880457927303</v>
+        <v>-0.02099250983241063</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.004802073276081065</v>
+        <v>-0.007037959245896563</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.01240513350646733</v>
+        <v>-0.01462393787347771</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-0.005383306670729504</v>
+        <v>-0.007617886798202189</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4112,25 +4109,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1100848256361924</v>
+        <v>0.1074458058435439</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1323911162388232</v>
+        <v>0.1296990673973655</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>0.06095567733871743</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.0341151385927505</v>
+        <v>-0.03641134984418559</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.07179907179907175</v>
+        <v>0.06925106925106927</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.06733121884911641</v>
+        <v>0.06479383778885373</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.002625116436616115</v>
+        <v>-0.004996189347108215</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4154,25 +4151,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.07909604519774027</v>
+        <v>0.08474576271186463</v>
       </c>
       <c r="G81" s="5" t="n">
-        <v>-0.01914098972922507</v>
+        <v>-0.01400560224089642</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0.05835667600373484</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>-0.02843930635838143</v>
+        <v>-0.0233526011560693</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-0.1030949839914621</v>
+        <v>-0.09839914621131274</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.0732245258050287</v>
+        <v>-0.06837229819144242</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.01661596068336046</v>
+        <v>-0.01146735314767133</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4200,25 +4197,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1118095097241736</v>
+        <v>0.1153590179693857</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.03269455319733483</v>
+        <v>0.03599148293151999</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0.05192664331341446</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.08552037832569215</v>
+        <v>0.08898595718566127</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.05675628184853276</v>
+        <v>0.06013002987172733</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.01828272935031028</v>
+        <v>-0.01514854717597125</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-0.007787236850788637</v>
+        <v>-0.004619547284366088</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4246,25 +4243,25 @@
         </is>
       </c>
       <c r="F83" s="5" t="n">
-        <v>-0.1425708559977097</v>
+        <v>-0.1437160034354423</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.01905410003402519</v>
+        <v>0.01769309288873755</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.04185096971759106</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.07002500893176133</v>
+        <v>0.06859592711682749</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.04065323141070176</v>
+        <v>0.03926337734537877</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.02188112344872639</v>
+        <v>-0.02318745917700848</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.003327787021630613</v>
+        <v>-0.004658901830282836</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4288,25 +4285,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.07672828564193468</v>
+        <v>0.07609521397822228</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.0659313111055404</v>
+        <v>0.06530458761594371</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0.04123840561544245</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.01832115914261756</v>
+        <v>0.01772242845168237</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.008658522120744916</v>
+        <v>0.008065472660419681</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>0.02371493920789702</v>
+        <v>0.02311303719754432</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.00479812755997655</v>
+        <v>-0.005383265067290921</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4330,25 +4327,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.03898418355981281</v>
+        <v>0.04143461795500114</v>
       </c>
       <c r="G85" s="5" t="n">
-        <v>-0.01060670343657188</v>
+        <v>-0.008273228680526046</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0.03528496676566273</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.03147806855879076</v>
+        <v>0.03391079985256162</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.02648375027510808</v>
+        <v>0.02890470251632316</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.04432757325319314</v>
+        <v>-0.04207362885048838</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.007025761124121899</v>
+        <v>-0.004683840749414525</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4372,25 +4369,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.1197966317127424</v>
+        <v>0.120749920559263</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.1031460322429176</v>
+        <v>0.104085146345281</v>
       </c>
       <c r="H86" s="3" t="n">
         <v>0.02989513225856943</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.07693483077393237</v>
+        <v>0.07785163114065274</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.09953198127925122</v>
+        <v>0.100468018720749</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0.07112462006079046</v>
+        <v>0.07203647416413395</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.007323943661971755</v>
+        <v>-0.006478873239436522</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4414,25 +4411,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.121624247134253</v>
+        <v>0.1222071109384106</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.1023486729043346</v>
+        <v>0.1029215199541722</v>
       </c>
       <c r="H87" s="3" t="n">
         <v>0.02367767805995813</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.08027694610778435</v>
+        <v>0.08083832335329344</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.1074237483215039</v>
+        <v>0.1079992326875119</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0.07685133370639807</v>
+        <v>0.07741093079649319</v>
       </c>
       <c r="L87" s="5" t="n">
-        <v>-0.006368330464716077</v>
+        <v>-0.005851979345955272</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4460,25 +4457,25 @@
         </is>
       </c>
       <c r="F88" s="5" t="n">
-        <v>-0.04608607251779073</v>
+        <v>-0.04710267705862425</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.008960573476702427</v>
+        <v>0.007885304659498216</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0.01827956989247315</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.04841713221601474</v>
+        <v>0.04729981378026071</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.02887426900584789</v>
+        <v>0.0277777777777779</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.009151707145371391</v>
+        <v>-0.01020767335445261</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-0.001064584811923397</v>
+        <v>-0.002129169623846683</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4506,25 +4503,25 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-0.04730949801372342</v>
+        <v>-0.04911520404478165</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.009015777610818954</v>
+        <v>-0.01089406461307296</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.00488354620586029</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.0336990595611284</v>
+        <v>0.03173981191222564</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.01774691358024683</v>
+        <v>0.01581790123456783</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.01383177570093463</v>
-      </c>
-      <c r="L89" s="21" t="n">
-        <v>0</v>
+        <v>-0.01570093457943933</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>-0.001895375284306278</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4552,25 +4549,25 @@
         </is>
       </c>
       <c r="F90" s="5" t="n">
-        <v>-0.01120266641977608</v>
+        <v>-0.01148041847977044</v>
       </c>
       <c r="G90" s="5" t="n">
-        <v>-0.02616941734293798</v>
+        <v>-0.0264429652594147</v>
       </c>
       <c r="H90" s="5" t="n">
         <v>-0.002188383331813593</v>
       </c>
       <c r="I90" s="5" t="n">
-        <v>-0.0333091962346127</v>
+        <v>-0.03358073859522093</v>
       </c>
       <c r="J90" s="5" t="n">
-        <v>-0.04266762280387237</v>
+        <v>-0.04293653639297246</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>-0.02403362880380155</v>
+        <v>-0.02430777666087924</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.001309145315129934</v>
+        <v>-0.001589676454086475</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4583,7 +4580,7 @@
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
-      <c r="D91" s="22" t="inlineStr">
+      <c r="D91" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4625,7 +4622,7 @@
         </is>
       </c>
       <c r="C92" s="15" t="inlineStr"/>
-      <c r="D92" s="22" t="inlineStr">
+      <c r="D92" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4677,26 +4674,26 @@
           <t>High Yield Credit</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>-0.0007526342197692326</v>
+      <c r="F93" s="3" t="n">
+        <v>0.0006271951831409162</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.008957452102513086</v>
+        <v>-0.007588952475740207</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>-0.005100771336153276</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-0.01799802761341229</v>
+        <v>-0.01664201183431968</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.008957452102513086</v>
+        <v>-0.007588952475740207</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.003876453670126345</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>-0.001003260596940003</v>
+        <v>-0.002500937851694474</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0.0003762227238526261</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4709,7 +4706,7 @@
         </is>
       </c>
       <c r="C94" s="15" t="inlineStr"/>
-      <c r="D94" s="22" t="inlineStr">
+      <c r="D94" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4720,25 +4717,25 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.06244302643573385</v>
+        <v>-0.06153144940747501</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.05338242061665899</v>
+        <v>-0.05246203405430283</v>
       </c>
       <c r="H94" s="5" t="n">
         <v>-0.005752416014726203</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.05566395041891425</v>
+        <v>-0.05474578216458159</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.03900957720158849</v>
+        <v>-0.0380752160710115</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.04790557741263601</v>
+        <v>-0.04697986577181212</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.007239382239382142</v>
+        <v>-0.006274131274131234</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4766,25 +4763,25 @@
         </is>
       </c>
       <c r="F95" s="5" t="n">
-        <v>-0.02333790939399893</v>
+        <v>-0.02627966267895676</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05395136778115506</v>
+        <v>-0.05680091185410341</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>-0.06174012158054709</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.03749516814843457</v>
+        <v>-0.04039427908774651</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.007689194658033083</v>
+        <v>0.004653986240388486</v>
       </c>
       <c r="K95" s="3" t="n">
-        <v>0.00830127556185456</v>
+        <v>0.00526422352702971</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.004842615012106366</v>
+        <v>0.001815980629539915</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4812,25 +4809,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.1663670534401046</v>
+        <v>-0.1606471645693741</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1250428816466552</v>
+        <v>-0.1190394511149228</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>-0.20926243567753</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.04958847736625516</v>
+        <v>0.05679012345679002</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.08255517826825121</v>
+        <v>0.08998302207130737</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.1065075921908893</v>
+        <v>0.1140997830802604</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.01506082255261632</v>
+        <v>-0.008302761150801308</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -76,7 +76,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00ECFCCB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="0070AD47"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D18E"/>
       </patternFill>
     </fill>
     <fill>
@@ -86,17 +96,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00A9D18E"/>
+        <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECFCCB"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00C6E0B4"/>
+        <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -106,7 +111,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00EDE9FE"/>
+        <fgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,27 +131,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FEF3C7"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEDD5"/>
+        <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FAE8FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -182,10 +182,10 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -197,9 +197,12 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -654,7 +657,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PSI</t>
+          <t>FTXL</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -673,25 +676,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.195150501672241</v>
+        <v>1.567648110621052</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.206218487394958</v>
+        <v>1.187024063356686</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>2.156638655462185</v>
+        <v>1.198598842522084</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.4112018920662226</v>
+        <v>0.3803268183274591</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.01802812687013766</v>
+        <v>-0.169782231643862</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.3010861463102971</v>
+        <v>-0.005264616237184772</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-0.004096806008648701</v>
+        <v>-0.02933621738542647</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -700,44 +703,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FTXL</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>EWY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>South Korea Equity</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.504028140247362</v>
+        <v>2.269251874885677</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.281873642849757</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>1.94643780374315</v>
+        <v>1.474114064230343</v>
+      </c>
+      <c r="H3" s="7" t="n">
+        <v>1.174695459579181</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4512692358279626</v>
-      </c>
-      <c r="J3" s="3" t="n">
-        <v>0.03353315848632454</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>-0.2255483418143533</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.002043318348998957</v>
+        <v>0.1807491576930698</v>
+      </c>
+      <c r="J3" s="5" t="n">
+        <v>-0.1316620512073071</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.1376830044557606</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>-0.01177706513325238</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -746,7 +745,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>AIS</t>
+          <t>PSI</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -754,36 +753,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.758691206543967</v>
+        <v>1.336700955180015</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.273340074148972</v>
+        <v>1.024025457438345</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1.875294910684193</v>
+        <v>1.170883054892601</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.5837050950927447</v>
-      </c>
-      <c r="J4" s="3" t="n">
-        <v>0.1279264214046825</v>
+        <v>0.2849494949494948</v>
+      </c>
+      <c r="J4" s="5" t="n">
+        <v>-0.1811920700308961</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.2093541202672605</v>
+        <v>-0.06764878334799185</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-0.005455617811854774</v>
+        <v>-0.03497193142163557</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -792,40 +791,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>EWY</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
+          <t>AIS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D5" s="9" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>South Korea Equity</t>
+          <t>Marine Shipping</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.321845469705392</v>
+        <v>1.758392043099876</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.46229913473424</v>
+        <v>1.186596583442838</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>1.772970745776679</v>
+        <v>1.093298291721419</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.4645862266154726</v>
-      </c>
-      <c r="J5" s="3" t="n">
-        <v>0.1152027867628764</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>-0.112035661218425</v>
+        <v>0.4606100504718016</v>
+      </c>
+      <c r="J5" s="5" t="n">
+        <v>-0.1316373124592303</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.04456999372253612</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.005105438401775686</v>
+        <v>-0.02218304686352268</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -849,25 +852,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.333012423783982</v>
+        <v>1.383848072127374</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.120151647710703</v>
+        <v>1.026251426707973</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.669499645877599</v>
+        <v>1.058087396054133</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4695350851862545</v>
-      </c>
-      <c r="J6" s="3" t="n">
-        <v>0.1028519417475728</v>
+        <v>0.4109966221011097</v>
+      </c>
+      <c r="J6" s="5" t="n">
+        <v>-0.1265199971884446</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.2057868780822774</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.0005505092210293938</v>
+        <v>-0.01546871595793142</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>-0.027316844082655</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -895,25 +898,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.288607594936709</v>
+        <v>1.351703940362087</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.04571169947952</v>
+        <v>0.9778325123152711</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.536773025571396</v>
+        <v>0.9939543215405284</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4346929058879545</v>
-      </c>
-      <c r="J7" s="3" t="n">
-        <v>0.09376890502117363</v>
+        <v>0.3853513174404015</v>
+      </c>
+      <c r="J7" s="5" t="n">
+        <v>-0.1257052360684945</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.1935771632471007</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.001329198050509683</v>
+        <v>-0.008085345311622638</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>-0.02677390921110634</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -941,25 +944,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.275428946720302</v>
+        <v>1.335567298191347</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9195927695823813</v>
+        <v>0.8727823900237692</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.271244546021193</v>
+        <v>0.8620345172069308</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3739652010112529</v>
-      </c>
-      <c r="J8" s="3" t="n">
-        <v>0.09397694979475846</v>
-      </c>
-      <c r="K8" s="5" t="n">
-        <v>-0.1548277912454832</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.002223789119705</v>
+        <v>0.3378202131062824</v>
+      </c>
+      <c r="J8" s="5" t="n">
+        <v>-0.09229793131083763</v>
+      </c>
+      <c r="K8" s="3" t="n">
+        <v>0.005772112556194919</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>-0.02331890124499225</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -968,7 +971,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>EWT</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -976,36 +979,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D9" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Taiwan Equity</t>
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.8812052358607063</v>
+        <v>1.176343239519779</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.8587115666178626</v>
+        <v>0.879972798367902</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.9102000976085898</v>
+        <v>0.6414484869092145</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.0889206576125805</v>
-      </c>
-      <c r="J9" s="5" t="n">
-        <v>-0.1367860380779691</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>-0.02695452222789985</v>
+        <v>0.461345315184353</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>0.07589025102159952</v>
+      </c>
+      <c r="K9" s="3" t="n">
+        <v>0.1453133091662351</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.001314578677533929</v>
+        <v>0.02360455429047481</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1014,44 +1017,40 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>EWT</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Taiwan Equity</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.095432458697765</v>
+        <v>0.8243715477398266</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8473269362577107</v>
+        <v>0.801224262659989</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.8610349554489376</v>
+        <v>0.6361713967723985</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.58404349103732</v>
+        <v>0.270628876501531</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.1994882064975523</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>-0.007365804253751884</v>
+        <v>0.1839929768088375</v>
+      </c>
+      <c r="K10" s="3" t="n">
+        <v>0.1008774913271206</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-0.0008341056533828217</v>
+        <v>-0.00406153846153845</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1060,40 +1059,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>BDRY</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Dry Bulk Freight</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.7382108557246143</v>
+        <v>1.4296875</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8804576231613357</v>
+        <v>0.8578255675029871</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.8474200326873687</v>
+        <v>0.6033452807646358</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.2912224448897796</v>
+        <v>0.2883181441590721</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2265285920962461</v>
+        <v>0.2017001545595054</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.01788309636650887</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>-0.008005912058135167</v>
+        <v>0.1587183308494784</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.005171299288946329</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1102,7 +1105,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>EPU</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1110,36 +1113,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D12" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Peru Equity</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.4248297537978</v>
+        <v>1.229604298974109</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>1.150522648083624</v>
+        <v>0.696654275092937</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.7879210220673636</v>
-      </c>
-      <c r="I12" s="3" t="n">
-        <v>0.09161655465157414</v>
+        <v>0.5981412639405206</v>
+      </c>
+      <c r="I12" s="5" t="n">
+        <v>-0.02728047740835471</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.1629192312523553</v>
+        <v>0.06424157630873273</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.2028062881642199</v>
+        <v>0.06164224238194915</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.01948739673797928</v>
+        <v>-0.003058103975535187</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1148,7 +1151,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>QCLN</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1156,36 +1159,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.4509394572025052</v>
+        <v>1.404761904761905</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.378577500708416</v>
+        <v>0.845211804858462</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.7376027203173705</v>
+        <v>0.5832162216422405</v>
       </c>
       <c r="I13" s="5" t="n">
-        <v>-0.01238327243199344</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>-0.1705029838022165</v>
-      </c>
-      <c r="K13" s="5" t="n">
-        <v>-0.20662100456621</v>
+        <v>-0.03960292580982239</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.04277286135693203</v>
+      </c>
+      <c r="K13" s="3" t="n">
+        <v>0.1654831346690337</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.004908979341378683</v>
+        <v>-0.01023045444755544</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1194,7 +1197,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>EPU</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1202,36 +1205,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D14" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Peru Equity</t>
+          <t>Oil Services</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>1.273088381330685</v>
+        <v>0.6160747803889182</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.8820143884892087</v>
+        <v>0.6760365972357405</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.7163412127440905</v>
+        <v>0.4981896048277203</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.05727482678983842</v>
+        <v>0.08443963019875556</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.1535844777623787</v>
+        <v>0.02926479378362234</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.09652694610778445</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>-0.008017334777898122</v>
+        <v>0.1187079337855046</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.003052332354722909</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1240,40 +1243,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" s="11" t="inlineStr">
+          <t>LIT</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.816420930904886</v>
+        <v>0.847815414825724</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>1.057879171947613</v>
+        <v>0.5861778339654447</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.6362484157160961</v>
-      </c>
-      <c r="I15" s="3" t="n">
-        <v>0.03308589607635204</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0.09979679385865881</v>
+        <v>0.4584913611462285</v>
+      </c>
+      <c r="I15" s="5" t="n">
+        <v>-0.001591511936339551</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>-0.136201950659782</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.2576813839400982</v>
+        <v>0.08754695174804983</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>-0.01734920314706478</v>
+        <v>-0.01427262013879804</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1282,44 +1289,40 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DRIV</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Autonomous/EV</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.4866264020707507</v>
+        <v>1.07311903920876</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.4352353186172429</v>
+        <v>0.6217187068250898</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.606413994169096</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.07218419415059119</v>
+        <v>0.446808510638298</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>-0.309448170372985</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.08057630736392729</v>
-      </c>
-      <c r="K16" s="5" t="n">
-        <v>-0.1065595022037853</v>
+        <v>-0.1410800526854968</v>
+      </c>
+      <c r="K16" s="3" t="n">
+        <v>0.1208938120702827</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.003470213996529692</v>
+        <v>-0.02394811242308337</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1328,40 +1331,44 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" s="11" t="inlineStr">
+          <t>PICK</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.098211153981059</v>
+        <v>0.8207282913165264</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7953181272509005</v>
+        <v>0.5853658536585367</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.6047418967587035</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>-0.207051961823966</v>
+        <v>0.4426829268292682</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>0.01025800435188051</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.1026102610261026</v>
+        <v>-0.01649266152216677</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1187581821582195</v>
+        <v>0.09890109890109899</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.003332222592469236</v>
+        <v>-0.00306748466257678</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1370,7 +1377,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1378,36 +1385,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.668977469670711</v>
+        <v>0.6245995483430491</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>1.081081081081081</v>
+        <v>0.4532556609978386</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.6040540540540538</v>
+        <v>0.4024241285351873</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3356461405030358</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.3139931740614335</v>
+        <v>0.3750889046941677</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>-0.03125391456845805</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.2973883740522327</v>
+        <v>0.03624547768993702</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.00773195876288657</v>
+        <v>-0.02265331269154214</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1416,7 +1423,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>QTEC</t>
+          <t>BOAT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1424,36 +1431,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.5865205809921095</v>
+        <v>0.8193620178041541</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4729597312304605</v>
+        <v>0.5536902122267975</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.5617096729037376</v>
+        <v>0.3956287614824201</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3402538954697916</v>
+        <v>0.1703650680028632</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.1839252897273376</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>-0.05682870716185118</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>-0.001455097586435916</v>
+        <v>0.2225822532402792</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.113254652746255</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.008014796547472169</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1462,40 +1469,44 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>U.S. Industrials</t>
+          <t>Japan Hedged Equity</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.3614017395688895</v>
+        <v>0.6665131700128937</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.2388162422573983</v>
+        <v>0.4542312947038494</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.5284468914888736</v>
-      </c>
-      <c r="I20" s="5" t="n">
-        <v>-0.01996370235934664</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>-0.1488690992197966</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>-0.1894934333958724</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>-0.01351845085860437</v>
+        <v>0.3954030378526079</v>
+      </c>
+      <c r="I20" s="3" t="n">
+        <v>0.06704800094350727</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.05497901119402981</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.04215861314288993</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0.007460609097488913</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1504,7 +1515,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1514,34 +1525,34 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>Natural Resources</t>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Oil Services</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.5455300404390526</v>
+        <v>0.5284974093264247</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.7563187264073528</v>
+        <v>0.5153378671682824</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.5264647956671589</v>
+        <v>0.3486470843582694</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.2286517982720515</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>-0.04504283419596644</v>
+        <v>0.1943319838056679</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0.2164595191079102</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.1505792543612074</v>
+        <v>0.1235985193927365</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.0232841672443882</v>
+        <v>0.001913417842621223</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1550,44 +1561,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>PICK</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.8441043083900226</v>
+        <v>0.6289793384765452</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.6951537258989056</v>
+        <v>0.3998323554065382</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.5151120375195413</v>
+        <v>0.3362036119789682</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.1157605899502658</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>0.05616883116883109</v>
+        <v>0.3238685500144134</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>-0.03832059470212557</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.1188306104901118</v>
+        <v>0.04761904761904767</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.01064476885644772</v>
+        <v>-0.01501340482573732</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1596,7 +1603,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1604,36 +1611,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D23" s="11" t="inlineStr">
+      <c r="D23" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.9876897133220912</v>
+        <v>0.4533649071881445</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.6076104746317514</v>
+        <v>0.4304187655063529</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.458401527550464</v>
-      </c>
-      <c r="I23" s="5" t="n">
-        <v>-0.007159703504043047</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>-0.007243325191611194</v>
+        <v>0.3337343056913016</v>
+      </c>
+      <c r="I23" s="3" t="n">
+        <v>0.2377049180327868</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0.1601926946765047</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.1023099223791264</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>-0.00732693279434049</v>
+        <v>0.0724915445321308</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0.006879762912785692</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1642,44 +1649,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DXJ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>DBC</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" s="13" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Broad Commodities</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6256907328562371</v>
+        <v>0.4322727272727274</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.5035187667560324</v>
+        <v>0.4187303016659163</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.4537533512064345</v>
+        <v>0.3259792886087347</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.1750147318797879</v>
+        <v>0.2553784860557768</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.1072993151107546</v>
+        <v>0.06886024423337855</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.03423236514522809</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>-0.003553581343697876</v>
+        <v>0.06994906621392194</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.006709265175718793</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1688,86 +1691,86 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>XLK</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>VDE</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.6112988475868644</v>
+        <v>0.432306477093207</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4155438836872953</v>
+        <v>0.4290330207266138</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.4502550049478573</v>
+        <v>0.323744975963433</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2924659438420907</v>
+        <v>0.1506440764007868</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.1658934169278998</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>-0.02393449506613476</v>
+        <v>0.1397234443746074</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.07953801274037042</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.001454036297054317</v>
+        <v>0.006438363767552913</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
-      <c r="A26" t="n">
+      <c r="A26" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>IBB</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="inlineStr"/>
       <c r="D26" s="12" t="inlineStr">
         <is>
-          <t>Defensive Equity</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Biotechnology</t>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E26" s="14" t="inlineStr">
+        <is>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.5004327131112074</v>
+        <v>0.4138461538461538</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.5671135884302503</v>
+        <v>0.4232300884955751</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.4325851159987948</v>
+        <v>0.3174778761061945</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.2065765818013108</v>
+        <v>0.1503934191702432</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.2333274052996621</v>
+        <v>0.1428317640788772</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.09390609390609406</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>-0.004307250538406193</v>
+        <v>0.08026868178001689</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.005784865540963136</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1776,7 +1779,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>MTUM</t>
+          <t>IYW</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1784,36 +1787,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D27" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.3657523618273926</v>
+        <v>0.6043579464632096</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.2402088772845954</v>
+        <v>0.3649265636173606</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.4208214182104522</v>
+        <v>0.3094229605588867</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.1694478096056899</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0.05377139235157391</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>-0.1271183968730858</v>
+        <v>0.3088405949994724</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>-0.01893879487585004</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.0423878339774828</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>-0.00153481698975666</v>
+        <v>-0.01253581661891123</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1822,40 +1825,44 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SCHA</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>FTEC</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.2714339198801947</v>
+        <v>0.5964143202382959</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3188349514563107</v>
+        <v>0.3697738342093841</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.4031067961165049</v>
+        <v>0.3025027728215268</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.1304926764314249</v>
-      </c>
-      <c r="J28" s="3" t="n">
-        <v>0.04750154225786551</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>-0.0600608912261279</v>
+        <v>0.3117063033941352</v>
+      </c>
+      <c r="J28" s="5" t="n">
+        <v>-0.01797752808988762</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.05164753794890786</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.008177570093457986</v>
+        <v>-0.01220614828209765</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1864,40 +1871,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SPMO</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>QCLN</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.4626149540183926</v>
+        <v>0.575378538512179</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.2647592704641715</v>
+        <v>0.2624637298865735</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3963177456997147</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>0.2206557103528821</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>0.09365423424770158</v>
+        <v>0.2993932999208653</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>-0.01136128898987809</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>-0.2782385763836526</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.09421815030333047</v>
+        <v>-0.02842062525375555</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.003133941953944785</v>
+        <v>-0.0214680024534859</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1906,14 +1917,10 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>IYW</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VGT</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
       <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -1925,25 +1932,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5704265046658734</v>
+        <v>0.5906964309584279</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3829904583310353</v>
+        <v>0.3657752783197521</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3911532733991505</v>
+        <v>0.2986342247216804</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.2640520239955637</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>0.1496492595479344</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>-0.005867660468619862</v>
+        <v>0.3099955966534567</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>-0.01701635552618541</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0.05170128148475461</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.001791401273885329</v>
+        <v>-0.01236617146651176</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1952,7 +1959,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>FTEC</t>
+          <t>DRIV</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1967,29 +1974,29 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Autonomous/EV</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5628474871906683</v>
+        <v>0.4997796386073159</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.3936035773306115</v>
+        <v>0.308846153846154</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3880626032857002</v>
+        <v>0.2849999999999999</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.2859705776820956</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0.1640615484551988</v>
+        <v>0.04194733619105961</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>-0.1819711538461538</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.003991876181805631</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>0.0004187020237265138</v>
+        <v>0.01855731816821327</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>-0.01390901188061422</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -1998,40 +2005,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VGT</t>
+          <t>AIRR</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D32" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>U.S. Industrials</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5588998443175921</v>
+        <v>0.4665567916494986</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.3921909396361951</v>
+        <v>0.166484596897531</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3847758081334722</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>0.2852711519948659</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0.1645667765070749</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0.005354752342704217</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>0.0007495627550595518</v>
+        <v>0.2786759886388464</v>
+      </c>
+      <c r="I32" s="5" t="n">
+        <v>-0.09653947034436072</v>
+      </c>
+      <c r="J32" s="5" t="n">
+        <v>-0.173401455333643</v>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>-0.08774028193079875</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>-0.01330622805396409</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2040,44 +2047,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ROBO</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SIL</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.3596075778078485</v>
+        <v>1.784624244169306</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2895876784854805</v>
+        <v>0.6645438898450946</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3742980908069951</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0.1105277701022382</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>-0.01555419473361919</v>
-      </c>
-      <c r="K33" s="5" t="n">
-        <v>-0.06163903805743642</v>
+        <v>0.2693631669535284</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>-0.1806320427010083</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0.03179344926917738</v>
+      </c>
+      <c r="K33" s="3" t="n">
+        <v>0.3113220338983049</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>-0.003224206349206393</v>
+        <v>-0.0126595201633487</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2086,7 +2089,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ARKQ</t>
+          <t>CALF</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2094,36 +2097,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D34" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Small Cap Value</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.4910975609756096</v>
+        <v>0.4561803444782171</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2596064695580509</v>
+        <v>0.3274070653428769</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3621098176573607</v>
-      </c>
-      <c r="I34" s="5" t="n">
-        <v>-0.01331504196255651</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>-0.05062504852861249</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>-0.07525336560278328</v>
+        <v>0.2519048718540753</v>
+      </c>
+      <c r="I34" s="3" t="n">
+        <v>0.2465307892454467</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.148880895283773</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.06030984876429368</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-0.0004087638979725083</v>
+        <v>-0.001563042723167651</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2132,7 +2135,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>IWO</t>
+          <t>ROBO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2140,36 +2143,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.2654339698898656</v>
+        <v>0.406332920573147</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2949164225400658</v>
+        <v>0.2470588235294118</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.3577804583835946</v>
+        <v>0.2431372549019608</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.1171171171171173</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>0.04401467155718586</v>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>-0.04629911666158992</v>
+        <v>0.01390128810100766</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>-0.1031137184115524</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.003154574132492094</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.00841888575123384</v>
+        <v>-0.01168572849328686</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2178,44 +2181,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XAR</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D36" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>SPMO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.4615866864242562</v>
+        <v>0.4581162324649299</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.1843077491456544</v>
+        <v>0.2493131868131868</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3105661771497183</v>
-      </c>
-      <c r="I36" s="5" t="n">
-        <v>-0.06048505275498239</v>
+        <v>0.2348042582417582</v>
+      </c>
+      <c r="I36" s="3" t="n">
+        <v>0.2180463714740104</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.01038048931079727</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>-0.09633884210155408</v>
+        <v>-0.03366757420811473</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.0117499826183689</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.0203980289545056</v>
+        <v>-0.01067373716772035</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2224,86 +2223,86 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
+          <t>FNDX</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Fundamental Equity</t>
+        </is>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>0.3146569224522942</v>
+      </c>
+      <c r="G37" s="3" t="n">
+        <v>0.2569875776397517</v>
+      </c>
+      <c r="H37" s="3" t="n">
+        <v>0.232142857142857</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>0.1153978642783329</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.04485317844465975</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.02016383112791442</v>
+      </c>
+      <c r="L37" s="18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" ht="21" customHeight="1">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D37" s="14" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Mid Cap Momentum</t>
-        </is>
-      </c>
-      <c r="F37" s="3" t="n">
-        <v>0.1638980326111918</v>
-      </c>
-      <c r="G37" s="3" t="n">
-        <v>0.165772120840362</v>
-      </c>
-      <c r="H37" s="3" t="n">
-        <v>0.3045545161785002</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>0.08383233532934131</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>-0.04873928549083417</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>-0.1063829787234042</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>-0.007377423777502057</v>
-      </c>
-    </row>
-    <row r="38" ht="21" customHeight="1">
-      <c r="A38" s="15" t="n">
-        <v>37</v>
-      </c>
-      <c r="B38" s="16" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C38" s="15" t="inlineStr"/>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E38" s="15" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.3685883321526355</v>
+        <v>0.3553408726706653</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2651103520291676</v>
+        <v>0.2145406802609444</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.303339763897984</v>
+        <v>0.2291880359414105</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1494363773779084</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>0.07047653278222055</v>
+        <v>0.170224541429475</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>-0.06266426015642323</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.02933188484519289</v>
+        <v>-0.01191628559030677</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.00227516993984056</v>
+        <v>-0.01444932747369831</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2312,40 +2311,40 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>QQQM</t>
+          <t>SCHA</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3688543653193173</v>
+        <v>0.3391373169766523</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2653824654942598</v>
+        <v>0.2391065543756867</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.3027045620673348</v>
+        <v>0.2288538996704506</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1493458308924038</v>
-      </c>
-      <c r="J39" s="3" t="n">
-        <v>0.07053473990542036</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>-0.02864970129055688</v>
+        <v>0.1087811271297512</v>
+      </c>
+      <c r="J39" s="5" t="n">
+        <v>-0.00616740088105705</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0.008343265792610355</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.002406779661016878</v>
+        <v>-0.009367681498828828</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2354,40 +2353,44 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>VBK</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XME</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D40" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.1967376032349817</v>
+        <v>1.011531841652324</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2366585219023338</v>
+        <v>0.4195311551074943</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2950175289493253</v>
-      </c>
-      <c r="I40" s="3" t="n">
-        <v>0.1162894770489709</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>0.04257224743252941</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>-0.04506426032266875</v>
+        <v>0.2225191303291632</v>
+      </c>
+      <c r="I40" s="5" t="n">
+        <v>-0.02077922077922068</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>-0.06660809839469684</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.1611525086934922</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.007446566621191253</v>
+        <v>-0.01066621518665867</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2396,40 +2399,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PAVE</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" s="13" t="inlineStr">
+          <t>XAR</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D41" s="16" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.2936864506975645</v>
+        <v>0.5272464814146518</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1974173779820529</v>
+        <v>0.1677704194260485</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2895600787918582</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>0.07802955665024625</v>
+        <v>0.2180831493745401</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>-0.1025659150349898</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.03662616657862294</v>
+        <v>-0.1183333333333334</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.0714528173794976</v>
+        <v>-0.04130484029298509</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.01084794792985</v>
+        <v>-0.01013566193669102</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2438,40 +2445,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Developed Markets</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.456948338005607</v>
+        <v>0.3469286247202188</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2942013518320883</v>
+        <v>0.164480756826489</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2673425827107792</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>0.09909365558912397</v>
-      </c>
-      <c r="J42" s="3" t="n">
-        <v>0.05755813953488387</v>
-      </c>
-      <c r="K42" s="3" t="n">
-        <v>0.02119298245614032</v>
+        <v>0.2117824123844334</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>-0.01688146669086965</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>-0.0381814952939088</v>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>-0.03903477643718956</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.004106214070626835</v>
+        <v>-0.009872029250457159</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2480,44 +2487,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>BOAT</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.7617498192335501</v>
+        <v>0.4677304735448027</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.6210911510312707</v>
+        <v>0.1449954641669187</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2611443779108449</v>
-      </c>
-      <c r="I43" s="3" t="n">
-        <v>0.3607930745601786</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>0.1753497346840327</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0.2854128198364547</v>
+        <v>0.207841951416188</v>
+      </c>
+      <c r="I43" s="5" t="n">
+        <v>-0.06782373215164939</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>-0.03504077471967382</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>-0.05203204539764661</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>-0.005104124132298882</v>
+        <v>-0.005079921173636981</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2526,86 +2529,82 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CALF</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D44" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>QQQM</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Small Cap Value</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.3062797551575607</v>
+        <v>0.3939118799579471</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.4333333333333331</v>
+        <v>0.242238405519356</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.258955223880597</v>
+        <v>0.206464801328734</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.2697223446452179</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0.2006668055844967</v>
+        <v>0.1664800447892505</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>-0.04036715357283849</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.1385101758545741</v>
+        <v>0.02965159377316517</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-0.003803596127247677</v>
+        <v>-0.01182329426112882</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
-      <c r="A45" t="n">
+      <c r="A45" s="14" t="n">
         <v>44</v>
       </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>FNDX</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>Fundamental Equity</t>
+      <c r="B45" s="15" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C45" s="14" t="inlineStr"/>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E45" s="14" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3146569224522942</v>
+        <v>0.3940807210185566</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.3104006475111292</v>
+        <v>0.2419880785413744</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2585997571833265</v>
+        <v>0.2061535764375877</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1409443269908388</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0.07610501827849792</v>
+        <v>0.1665431671853645</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>-0.04047080494643174</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.04115755627009654</v>
+        <v>0.02970973415311251</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-0.003998769609350861</v>
+        <v>-0.01162174228472579</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2614,40 +2613,44 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ONEQ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" s="14" t="inlineStr">
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D46" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.3427905169063352</v>
+        <v>0.3463511560693642</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2459430219978365</v>
+        <v>0.2111472213194672</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2407741315061906</v>
+        <v>0.2046473838154048</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1226037041048413</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>0.0561442836763808</v>
+        <v>0.1116181953765847</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>-0.02127268429760742</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.004165859329587462</v>
+        <v>0.005395634931340654</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.00394003459542569</v>
+        <v>-0.01145918989893624</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2656,40 +2659,40 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="9" t="inlineStr">
+      <c r="D47" s="6" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Developed ex-US Hedged</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.2956043956043957</v>
+        <v>0.422557274329352</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2463002114164903</v>
+        <v>0.2374382558337593</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2402219873150104</v>
+        <v>0.2028615227388861</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.101611772950245</v>
+        <v>0.03431093394077456</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.06987295825771311</v>
+        <v>0.01226139055315612</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.004900916258256949</v>
+        <v>0.02874539790427644</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.002538071065989911</v>
+        <v>-0.003702687877125577</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2698,44 +2701,40 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D48" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>SCHD</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.1811131218377222</v>
+        <v>0.2242466713384723</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.3243746894152726</v>
+        <v>0.2514326647564469</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2382391916514826</v>
+        <v>0.1987822349570199</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1132344750765804</v>
+        <v>0.09977966635190416</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.1737869779050136</v>
+        <v>0.07507692307692304</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.06956289087321488</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>-0.003583000997008923</v>
+        <v>0.0439199282939946</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.001433075379764892</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2744,40 +2743,40 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Developed ex-US Hedged</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4607229531230042</v>
+        <v>0.2689098250336475</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.1633774160732453</v>
+        <v>0.2165161290322581</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2330620549338758</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>-0.01575006454944483</v>
+        <v>0.1987096774193549</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0.04685765045525203</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.04648609077598831</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>-0.05651348898605724</v>
+        <v>0.03536130024159889</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.01485468245425192</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.01761017094751305</v>
+        <v>-0.001905568494600773</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2786,7 +2785,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VDE</t>
+          <t>VHT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2796,34 +2795,34 @@
       </c>
       <c r="D50" s="11" t="inlineStr">
         <is>
-          <t>Natural Resources</t>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4519129661085497</v>
+        <v>0.1852492183189256</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.4659044507962433</v>
+        <v>0.2631723380900108</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2260514495712536</v>
+        <v>0.1949584444095969</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.2483482856944155</v>
+        <v>0.09035227234272947</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.05849746432362291</v>
+        <v>0.1523550659847643</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.195630453606874</v>
+        <v>0.05708474131426122</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.01665156320797467</v>
+        <v>0.007032129016127042</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2832,82 +2831,86 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>ARGT</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.2664980122876763</v>
+        <v>0.1546267214302972</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1526873232024211</v>
+        <v>0.1925140361821585</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2185382540622327</v>
+        <v>0.1871490954460386</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.05911508704061896</v>
-      </c>
-      <c r="J51" s="3" t="n">
-        <v>0.003665941115820859</v>
-      </c>
-      <c r="K51" s="5" t="n">
-        <v>-0.05404092209685252</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>-0.01083888449813697</v>
+        <v>0.06483957219251324</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>-0.02169907881269195</v>
+      </c>
+      <c r="K51" s="3" t="n">
+        <v>0.004519180241723486</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.01089370703331571</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
-      <c r="A52" s="15" t="n">
+      <c r="A52" t="n">
         <v>51</v>
       </c>
-      <c r="B52" s="16" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C52" s="15" t="inlineStr"/>
-      <c r="D52" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E52" s="15" t="inlineStr">
-        <is>
-          <t>Energy</t>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4545869465997261</v>
+        <v>0.3870185833557769</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.4615913781242835</v>
+        <v>0.2192234848484849</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2178399449667507</v>
+        <v>0.1840672348484849</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.2485798237022527</v>
-      </c>
-      <c r="J52" s="3" t="n">
-        <v>0.06856663872590119</v>
+        <v>0.1544496749607711</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>-0.03049698795180722</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>0.2001506307663341</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>0.01691129546904913</v>
+        <v>0.02969109267219827</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>-0.008566753296756158</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2916,82 +2919,86 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>IAU</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D53" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.5766975600529602</v>
+        <v>0.273380767255923</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.3442993065634576</v>
+        <v>0.142030129596737</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2177068214804065</v>
+        <v>0.1830800605223342</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>-0.0859649122807018</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>-0.04018422567645363</v>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>0.1039597404317307</v>
+        <v>-0.01998419329344014</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0.002714723040489808</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>-0.03469750889679724</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.005487950369840067</v>
+        <v>-0.008736367270028023</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
-      <c r="A54" s="15" t="n">
+      <c r="A54" t="n">
         <v>53</v>
       </c>
-      <c r="B54" s="16" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C54" s="15" t="inlineStr"/>
-      <c r="D54" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E54" s="15" t="inlineStr">
-        <is>
-          <t>Gold</t>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.5727103960396038</v>
+        <v>0.4255847827949619</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.342223395827832</v>
+        <v>0.124417111576671</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2159360971745445</v>
+        <v>0.1788876123538554</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.08609956174851108</v>
+        <v>-0.08112884519798969</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.04017372421281229</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>0.103860144416092</v>
+        <v>-0.06312292358803995</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>-0.04620499885347396</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.005502702438308638</v>
+        <v>-0.006033813250492792</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3000,7 +3007,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>XMMO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3010,34 +3017,34 @@
       </c>
       <c r="D55" s="17" t="inlineStr">
         <is>
-          <t>Financials &amp; Credit</t>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1515202989638187</v>
+        <v>0.2350630217711573</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2057986481679119</v>
+        <v>0.1494515539305301</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2134471718249733</v>
+        <v>0.1752742230347348</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.06638351423627498</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>0.0560835021031314</v>
+        <v>0.005664778407197479</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>-0.1062544420753376</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.006303136909996954</v>
+        <v>-0.02197161189966934</v>
       </c>
       <c r="L55" s="5" t="n">
-        <v>-0.009786736780601601</v>
+        <v>-0.009452540370224471</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3046,7 +3053,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>PPA</t>
+          <t>ARKQ</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3054,36 +3061,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D56" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.389418691433784</v>
+        <v>0.6572879494921768</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1476027397260276</v>
+        <v>0.2326459779501839</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2099315068493151</v>
+        <v>0.1746631278072683</v>
       </c>
       <c r="I56" s="5" t="n">
-        <v>-0.04026807194409443</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>0.0005971931919976914</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>-0.05151429380130201</v>
+        <v>-0.01380267886311659</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>-0.1548260656540912</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>0.0493612583644738</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.01446973707428967</v>
+        <v>-0.01428571428571423</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3092,86 +3099,82 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>XOP</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D57" s="11" t="inlineStr">
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
+      <c r="D57" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4007901013714967</v>
+        <v>0.5232968256914796</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.4664845883730004</v>
+        <v>0.2605222734254993</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2037456106125632</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>0.340059897318882</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>0.05454239380506154</v>
+        <v>0.1700460829493089</v>
+      </c>
+      <c r="I57" s="5" t="n">
+        <v>-0.1716967800545068</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-0.04012165165516424</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.218267859458058</v>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>0.01070237711089606</v>
+        <v>0.07732703163975319</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-0.01971090670170816</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
-      <c r="A58" t="n">
+      <c r="A58" s="14" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>VWO</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>Emerging Markets</t>
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr"/>
+      <c r="D58" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3628378378378379</v>
+        <v>0.5206442055684279</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2150602409638553</v>
+        <v>0.258653755462634</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.1985943775100403</v>
-      </c>
-      <c r="I58" s="3" t="n">
-        <v>0.071542411900124</v>
-      </c>
-      <c r="J58" s="3" t="n">
-        <v>0.02681147123706085</v>
+        <v>0.168107649259597</v>
+      </c>
+      <c r="I58" s="5" t="n">
+        <v>-0.1724237726098192</v>
+      </c>
+      <c r="J58" s="5" t="n">
+        <v>-0.04022823168392797</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.01373764449656556</v>
+        <v>0.07751520697636849</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.004606020727093263</v>
+        <v>-0.01978355614318605</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3180,82 +3183,82 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>VBK</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" s="14" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2536830758174633</v>
+        <v>0.2656158572264482</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.3166037735849057</v>
+        <v>0.1809247568674286</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.1966037735849058</v>
+        <v>0.1617812659955637</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1700201207243461</v>
-      </c>
-      <c r="J59" s="3" t="n">
-        <v>0.087932647333957</v>
+        <v>0.08048955633956711</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-0.0267450362787558</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.1002838221381268</v>
+        <v>0.01647770663220349</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.0002865329512893311</v>
+        <v>-0.01190612151667436</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
-      <c r="A60" t="n">
+      <c r="A60" s="14" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>DBC</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
-      <c r="D60" s="18" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>Broad Commodities</t>
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr"/>
+      <c r="D60" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.4214838416021849</v>
+        <v>0.2839375273486149</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.3910913140311805</v>
+        <v>0.1826835129059763</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.1875278396436526</v>
+        <v>0.1580962716068521</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.2783462955382727</v>
+        <v>0.1121007594862899</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.004180064308681564</v>
+        <v>0.008473456006768076</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.171417854463616</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>0.01429035401104262</v>
+        <v>0.02123074039864536</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>-0.005423375268887254</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3268,7 +3271,7 @@
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" s="14" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3279,67 +3282,67 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.2725317622395316</v>
+        <v>0.283784525836033</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.2118859935974666</v>
+        <v>0.1825891953867942</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1820763484905854</v>
+        <v>0.1577696094961893</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1067398069850052</v>
+        <v>0.1114509381338744</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.06592691271307016</v>
+        <v>0.008454470948539905</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.0252180370116919</v>
+        <v>0.02143741352945461</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.004397375714043306</v>
+        <v>-0.004993686958248755</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
-      <c r="A62" s="15" t="n">
+      <c r="A62" t="n">
         <v>61</v>
       </c>
-      <c r="B62" s="16" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="C62" s="15" t="inlineStr"/>
-      <c r="D62" s="14" t="inlineStr">
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>IVV</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E62" s="15" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>US Large Blend</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.2728390548669035</v>
+        <v>0.2838525963149079</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2119035565118339</v>
+        <v>0.1822248272458045</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1814485508163524</v>
+        <v>0.157329713721619</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1070133098255703</v>
+        <v>0.1118106124343614</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.06590042579244715</v>
+        <v>0.008433655680547547</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.02577768255286106</v>
+        <v>0.02151082204925903</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.004328329108988171</v>
+        <v>-0.005553104808365905</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3348,40 +3351,44 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>IVV</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" s="14" t="inlineStr">
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D63" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>US Large Blend</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.273295623697529</v>
+        <v>0.3033967204078822</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2125689084895259</v>
+        <v>0.1834902561856799</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1795400850527642</v>
+        <v>0.1543370139822953</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1076644173632793</v>
+        <v>0.1298076923076923</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.06618471893306732</v>
+        <v>0.002703204091909051</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.02800144213435884</v>
+        <v>0.02525539929003084</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.004062095730918536</v>
+        <v>-0.00428969945786617</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3390,44 +3397,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D64" s="14" t="inlineStr">
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Cash Flow Factor</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.2883623030961433</v>
+        <v>0.2595179881243452</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2103332801785998</v>
+        <v>0.241094475993805</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.166863339180354</v>
+        <v>0.1514369299604199</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1046105483758295</v>
+        <v>0.1105635971666155</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.06961668545659516</v>
+        <v>0.1100507926735417</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.03725366933610297</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>-0.003701661809876411</v>
+        <v>0.07786578986698567</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.0002773925104022634</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3436,40 +3439,44 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RSP</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D65" s="19" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Equal Weight</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2104943721032884</v>
+        <v>0.184196755625327</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1947394216631269</v>
+        <v>0.1118571896495251</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1586886674290695</v>
+        <v>0.1406812970848346</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1075827948303714</v>
+        <v>0.1120393120393122</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.07840149429807308</v>
-      </c>
-      <c r="K65" s="3" t="n">
-        <v>0.03111340884523184</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-0.005890615795912879</v>
+        <v>0.06930225232320053</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>-0.02526920315865044</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.001179766996018294</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3478,40 +3485,40 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MGK</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D66" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2886272257323377</v>
+        <v>0.3650793650793651</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1790829063198003</v>
+        <v>0.1849408111779547</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1550387596899225</v>
+        <v>0.1401125557927421</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1055808796353332</v>
+        <v>0.05094664371772817</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.06833333333333336</v>
+        <v>0.0197060788243153</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.02081674439767944</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-0.004216600088770672</v>
+        <v>0.03931914893617017</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.008922670191672255</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3520,40 +3527,40 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>VUG</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
-      <c r="D67" s="14" t="inlineStr">
+      <c r="D67" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.263157894736842</v>
+        <v>0.2120657120657119</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1610862114421303</v>
+        <v>0.1578305587954616</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1355127867123649</v>
+        <v>0.1399109320326581</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.09743334163967088</v>
+        <v>0.06547299604820211</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.05903570999158347</v>
+        <v>0.04577886319015456</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.02252147666589277</v>
+        <v>0.0157201990605087</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.005195391913259684</v>
+        <v>-0.004558092893933163</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3562,40 +3569,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>MGK</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D68" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.07866184448462921</v>
+        <v>0.3170803782505909</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.0693158051986853</v>
+        <v>0.1608282328428179</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1335524350164325</v>
-      </c>
-      <c r="I68" s="5" t="n">
-        <v>-0.04099678456591638</v>
+        <v>0.1242349264227112</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0.1518284016022742</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>-0.06918075422626802</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>-0.05666842382709536</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>0.001118881118881143</v>
+        <v>-0.02333735071765086</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>0.03254951928645888</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>-0.008453837597330427</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3604,11 +3611,11 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>IWF</t>
+          <t>SCHG</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" s="14" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3619,25 +3626,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.1961301671064204</v>
+        <v>0.2972873900293256</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1117166212534062</v>
+        <v>0.1595674967234602</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1277929155313353</v>
+        <v>0.1195937090432504</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.05073396858099422</v>
+        <v>0.1512687052700066</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.02624297811687781</v>
-      </c>
-      <c r="K69" s="5" t="n">
-        <v>-0.01425465088185551</v>
+        <v>0.007687927107061565</v>
+      </c>
+      <c r="K69" s="3" t="n">
+        <v>0.03570383377231479</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.002851323828920505</v>
+        <v>-0.007571508693213547</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3646,40 +3653,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>IGF</t>
+          <t>VUG</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D70" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2233502538071066</v>
+        <v>0.2939958592132503</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1013879485443465</v>
+        <v>0.1446886446886446</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1272850372376437</v>
+        <v>0.1145996860282574</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.01024685607824871</v>
+        <v>0.1391745866423642</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>-0.05048883700569107</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>-0.02297297297297296</v>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>0.001693349753694617</v>
+        <v>-0.02343749999999989</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0.02699530516431925</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>-0.008386219401631867</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3688,40 +3695,44 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>VONG</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" s="14" t="inlineStr">
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1964675719304909</v>
+        <v>0.1816287878787879</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1110131381712371</v>
+        <v>0.1058135412974122</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1269729300767128</v>
+        <v>0.1108649415101026</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.04973756560859788</v>
+        <v>0.08156366473086596</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.02639296187683282</v>
+        <v>0.03862160812385551</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.01416164619356863</v>
+        <v>-0.004547267650578335</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.003006804874188918</v>
+        <v>-0.004785452225235187</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3730,7 +3741,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPGP</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3738,36 +3749,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D72" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.1579918789221115</v>
+        <v>0.0595413113790062</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1518266935928034</v>
+        <v>0.08539156626505995</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1225445199192217</v>
+        <v>0.1081325301204819</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.08866909595696693</v>
+        <v>0.05542945009885036</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.07192892533743378</v>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>0.02608553438547712</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>-0.01080015766653519</v>
+        <v>0.1228480174495596</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>-0.02052188094590923</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.001389467833819547</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3776,40 +3787,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SCHG</t>
+          <t>IGF</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2523725834797892</v>
+        <v>0.2143257901627083</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1790205162144276</v>
+        <v>0.07589063794531903</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1197882197220386</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>0.1134375000000001</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>0.08264965056213947</v>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>0.05289598108747051</v>
+        <v>0.1070422535211268</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>-0.06400461294507709</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-0.02507507507507489</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>-0.02813950007483901</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.00419228619340406</v>
+        <v>-0.003223825606386121</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3818,7 +3829,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>XHE</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3826,36 +3837,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D74" s="19" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+      <c r="D74" s="11" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.07289719626168223</v>
+        <v>0.07238848108413332</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.0973744583227123</v>
+        <v>0.156215755509558</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1182768289574305</v>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>-0.002664195528784941</v>
+        <v>0.09022281748447591</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>0.07420814479638005</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.003730473303800386</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>-0.01869158878504673</v>
+        <v>0.194615674927664</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>0.06053160598615137</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.00909195534583962</v>
+        <v>-0.0004210526315789886</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3864,40 +3875,44 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>COWZ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>EUO</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D75" s="20" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cash Flow Factor</t>
-        </is>
-      </c>
-      <c r="F75" s="3" t="n">
-        <v>0.2440999138673559</v>
+          <t>Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F75" s="5" t="n">
+        <v>-0.1416309012875537</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.2977538185085356</v>
+        <v>0.06913756236635793</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1176999101527405</v>
+        <v>0.07519600855310071</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1597880199132808</v>
+        <v>0.06082036775106081</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.1371437568886789</v>
-      </c>
-      <c r="K75" s="3" t="n">
-        <v>0.1610932475884244</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>-0.002486187845303967</v>
+        <v>0.02494021182097717</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>-0.005634736493205228</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.004352192835620938</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3906,7 +3921,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>XHE</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -3914,36 +3929,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D76" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D76" s="21" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.002854726157750065</v>
+        <v>0.1574049096304289</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.2447506561679789</v>
+        <v>0.01924219028388174</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1053805774278216</v>
-      </c>
-      <c r="I76" s="3" t="n">
-        <v>0.09564514265911983</v>
+        <v>0.06639743437462875</v>
+      </c>
+      <c r="I76" s="5" t="n">
+        <v>-0.01345136813060477</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.1807543881488858</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>0.1260833432268786</v>
+        <v>0.02166924633884992</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>-0.04421920249498779</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.001053185887309183</v>
+        <v>-0.003368176538908196</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3952,44 +3967,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>ARGT</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>VONG</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr"/>
+      <c r="D77" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.09586031452358923</v>
+        <v>0.231868348443043</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1458106637649619</v>
+        <v>0.09017179733147285</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1038568492322574</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>-0.03492871690427701</v>
-      </c>
-      <c r="J77" s="3" t="n">
-        <v>0.04017122160026343</v>
+        <v>0.06313769948547998</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0.07888150513506509</v>
+      </c>
+      <c r="J77" s="5" t="n">
+        <v>-0.05014816503305231</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.03800657174151145</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>0.01034115138592751</v>
+        <v>0.02542859486506455</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>-0.01091858533111789</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -3998,44 +4009,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>IWF</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
       <c r="D78" s="17" t="inlineStr">
         <is>
-          <t>Financials &amp; Credit</t>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1188018933809265</v>
+        <v>0.2309173846933603</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1310896681572136</v>
+        <v>0.09003590664272898</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1026908292147173</v>
+        <v>0.06211849192100538</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.08406015037593995</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>0.08963119709794443</v>
+        <v>0.07889826743669492</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>-0.05021509581540862</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.02575412635173602</v>
+        <v>0.02628465179175121</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.006203473945409432</v>
+        <v>-0.01043109771004802</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4044,44 +4051,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VCR</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VFH</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr"/>
       <c r="D79" s="19" t="inlineStr">
         <is>
-          <t>Consumer</t>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.0008194832133985308</v>
+        <v>0.1171199746253271</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.05750081177616617</v>
+        <v>0.06751534439645379</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.073195150990367</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>-0.02099250983241063</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>-0.007037959245896563</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>-0.01462393787347771</v>
+        <v>0.0550125028415549</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0.1220133800573431</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.1122690667929891</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.01185089420383534</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-0.007617886798202189</v>
+        <v>-0.0005675368898979682</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4090,44 +4093,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D80" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XLF</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr"/>
+      <c r="D80" s="19" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1074458058435439</v>
+        <v>0.1061709467228824</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1296990673973655</v>
+        <v>0.06908686793850705</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.06095567733871743</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>-0.03641134984418559</v>
+        <v>0.05463974810150019</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.1223021582733812</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.06925106925106927</v>
+        <v>0.1190383869716944</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.06479383778885373</v>
-      </c>
-      <c r="L80" s="5" t="n">
-        <v>-0.004996189347108215</v>
+        <v>0.01369863013698636</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.0001732801940736994</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4136,40 +4135,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" s="12" t="inlineStr">
+      <c r="D81" s="11" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.08474576271186463</v>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>-0.01400560224089642</v>
+        <v>0.03177660086663447</v>
+      </c>
+      <c r="G81" s="3" t="n">
+        <v>0.06115375092844766</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.05835667600373484</v>
+        <v>0.05285961871750433</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>-0.0233526011560693</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>-0.09839914621131274</v>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>-0.06837229819144242</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>-0.01146735314767133</v>
+        <v>-0.04766137095878242</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0.03389217223495367</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>0.007877718988830162</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>0.008707931277947667</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4178,44 +4177,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D82" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" s="11" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1153590179693857</v>
+        <v>0.06690229739964648</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.03599148293151999</v>
+        <v>0.002371916508538963</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.05192664331341446</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>0.08898595718566127</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0.06013002987172733</v>
+        <v>0.05194497153700195</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>-0.1146029750680914</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>-0.04862674470959039</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.01514854717597125</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>-0.004619547284366088</v>
+        <v>-0.04712514092446451</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>0.0007103954534690704</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4224,44 +4219,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D83" s="20" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>BOTZ</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F83" s="5" t="n">
-        <v>-0.1437160034354423</v>
+          <t>Robotics &amp; AI</t>
+        </is>
+      </c>
+      <c r="F83" s="3" t="n">
+        <v>0.1041471780480199</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.01769309288873755</v>
+        <v>0.05543964232488818</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.04185096971759106</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>0.06859592711682749</v>
-      </c>
-      <c r="J83" s="3" t="n">
-        <v>0.03926337734537877</v>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>-0.02318745917700848</v>
+        <v>0.04977645305514167</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>-0.09251665812403909</v>
+      </c>
+      <c r="J83" s="5" t="n">
+        <v>-0.1180572851805729</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0.005394662123793248</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.004658901830282836</v>
+        <v>-0.01337419894120939</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4270,82 +4261,90 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>XLP</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D84" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.07609521397822228</v>
+        <v>0.05459796047288146</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.06530458761594371</v>
+        <v>0.06526891522333633</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.04123840561544245</v>
+        <v>0.03299908842297161</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.01772242845168237</v>
+        <v>0.07993715922742828</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.008065472660419681</v>
+        <v>0.04014241210502889</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>0.02311303719754432</v>
+        <v>0.03123896929050485</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.005383265067290921</v>
+        <v>-0.004005795619193675</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
-      <c r="A85" t="n">
+      <c r="A85" s="14" t="n">
         <v>84</v>
       </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr"/>
-      <c r="D85" s="14" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>0.04143461795500114</v>
-      </c>
-      <c r="G85" s="5" t="n">
-        <v>-0.008273228680526046</v>
+      <c r="B85" s="15" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C85" s="14" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E85" s="14" t="inlineStr">
+        <is>
+          <t>US Dollar Basket</t>
+        </is>
+      </c>
+      <c r="F85" s="5" t="n">
+        <v>-0.04219122150391297</v>
+      </c>
+      <c r="G85" s="3" t="n">
+        <v>0.02849835586408478</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.03528496676566273</v>
+        <v>0.0292290829375228</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.03391079985256162</v>
+        <v>0.03951255539143284</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.02890470251632316</v>
+        <v>0.01771511207519882</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.04207362885048838</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>-0.004683840749414525</v>
+        <v>-0.0007099751508697905</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0.001066856330014243</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4354,40 +4353,44 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VFH</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr"/>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D86" s="17" t="inlineStr">
         <is>
-          <t>Financials &amp; Credit</t>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Mid Growth</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.120749920559263</v>
+        <v>0.145098642464331</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.104085146345281</v>
+        <v>0.02981254755481766</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.02989513225856943</v>
+        <v>0.02206543542920381</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.07785163114065274</v>
-      </c>
-      <c r="J86" s="3" t="n">
-        <v>0.100468018720749</v>
+        <v>0.06927137573167652</v>
+      </c>
+      <c r="J86" s="5" t="n">
+        <v>-0.003280444533708349</v>
       </c>
       <c r="K86" s="3" t="n">
-        <v>0.07203647416413395</v>
+        <v>0.007579859231185759</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.006478873239436522</v>
+        <v>-0.01413766844353204</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4396,392 +4399,392 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>XLF</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr"/>
-      <c r="D87" s="17" t="inlineStr">
+          <t>VCR</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D87" s="21" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.0768437195036944</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.0009070647385061026</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.01409837764992483</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0.005022379514937114</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>-0.03856111526014439</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>-0.01300792231024794</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>-0.01323488080942281</v>
+      </c>
+    </row>
+    <row r="88" ht="21" customHeight="1">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>USDU</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D88" s="20" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>US Dollar Basket</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.04665461121157322</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.004573170731707377</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0.009527439024390238</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0.03738685556867383</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.007645259938837912</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>-0.004907512268780612</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>0.00113938473224473</v>
+      </c>
+    </row>
+    <row r="89" ht="21" customHeight="1">
+      <c r="A89" s="14" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="15" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="C89" s="14" t="inlineStr"/>
+      <c r="D89" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E89" s="14" t="inlineStr">
+        <is>
+          <t>Short Treasury</t>
+        </is>
+      </c>
+      <c r="F89" s="5" t="n">
+        <v>-0.01174049866860327</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.01602795854422745</v>
+      </c>
+      <c r="H89" s="5" t="n">
+        <v>-0.01181007471679929</v>
+      </c>
+      <c r="I89" s="5" t="n">
+        <v>-0.01839384467420058</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.007897934386391192</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-0.004268292682926722</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>-0.002930760776651553</v>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" s="14" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="15" t="inlineStr">
+        <is>
+          <t>HYG</t>
+        </is>
+      </c>
+      <c r="C90" s="14" t="inlineStr"/>
+      <c r="D90" s="19" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>Financials</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>0.1222071109384106</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0.1029215199541722</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>0.02367767805995813</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>0.08083832335329344</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>0.1079992326875119</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>0.07741093079649319</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>-0.005851979345955272</v>
-      </c>
-    </row>
-    <row r="88" ht="21" customHeight="1">
-      <c r="A88" s="15" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="16" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C88" s="15" t="inlineStr">
+      <c r="E90" s="14" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="n">
+        <v>-0.01073255959066521</v>
+      </c>
+      <c r="G90" s="5" t="n">
+        <v>-0.01966361612663869</v>
+      </c>
+      <c r="H90" s="5" t="n">
+        <v>-0.01706653475142217</v>
+      </c>
+      <c r="I90" s="5" t="n">
+        <v>-0.01796333002973249</v>
+      </c>
+      <c r="J90" s="5" t="n">
+        <v>-0.0129498194496328</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.002642174131857189</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>-0.006766069414860354</v>
+      </c>
+    </row>
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" s="14" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="15" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="C91" s="14" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D88" s="20" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E88" s="15" t="inlineStr">
-        <is>
-          <t>US Dollar Basket</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>-0.04710267705862425</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>0.007885304659498216</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>0.01827956989247315</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>0.04729981378026071</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>0.0277777777777779</v>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>-0.01020767335445261</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>-0.002129169623846683</v>
-      </c>
-    </row>
-    <row r="89" ht="21" customHeight="1">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>USDU</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
+      <c r="D91" s="13" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
+        </is>
+      </c>
+      <c r="E91" s="14" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="n">
+        <v>-0.0318107667210441</v>
+      </c>
+      <c r="G91" s="5" t="n">
+        <v>-0.03903930916614196</v>
+      </c>
+      <c r="H91" s="5" t="n">
+        <v>-0.03184312314473337</v>
+      </c>
+      <c r="I91" s="5" t="n">
+        <v>-0.04513764747944227</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>-0.03938494739681675</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>-0.00743287187587105</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>9.361542782260202e-05</v>
+      </c>
+    </row>
+    <row r="92" ht="21" customHeight="1">
+      <c r="A92" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Intermediate Treasury</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="n">
+        <v>-0.03157784305497258</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.03993759750390014</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>-0.03328133125325017</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>-0.05796509847943665</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>-0.02472266244057053</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>-0.006885422270037633</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>-0.004636618503342627</v>
+      </c>
+    </row>
+    <row r="93" ht="21" customHeight="1">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Mid Growth</t>
+        </is>
+      </c>
+      <c r="F93" s="3" t="n">
+        <v>0.09042218021424064</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-0.03127842698201666</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>-0.04107480232314042</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>0.01235831809872034</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>-0.03121063680895741</v>
+      </c>
+      <c r="K93" s="3" t="n">
+        <v>0.01021599532983064</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>-0.01438131852484703</v>
+      </c>
+    </row>
+    <row r="94" ht="21" customHeight="1">
+      <c r="A94" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>INDA</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="20" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>US Dollar Basket</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>-0.04911520404478165</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>-0.01089406461307296</v>
-      </c>
-      <c r="H89" s="3" t="n">
-        <v>0.00488354620586029</v>
-      </c>
-      <c r="I89" s="3" t="n">
-        <v>0.03173981191222564</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>0.01581790123456783</v>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>-0.01570093457943933</v>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v>-0.001895375284306278</v>
-      </c>
-    </row>
-    <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="16" t="inlineStr">
-        <is>
-          <t>TIP</t>
-        </is>
-      </c>
-      <c r="C90" s="15" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D90" s="18" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
-        </is>
-      </c>
-      <c r="E90" s="15" t="inlineStr">
-        <is>
-          <t>TIPS</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>-0.01148041847977044</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>-0.0264429652594147</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>-0.002188383331813593</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>-0.03358073859522093</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>-0.04293653639297246</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>-0.02430777666087924</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>-0.001589676454086475</v>
-      </c>
-    </row>
-    <row r="91" ht="21" customHeight="1">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>IEF</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr"/>
-      <c r="D91" s="21" t="inlineStr">
+      <c r="D94" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>India Equity</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.03575883575883565</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.04155444401692954</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-0.04193920738745671</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>-0.04687201071360247</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0.02594728171334437</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>0.0004016064257028606</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0.002414486921529013</v>
+      </c>
+    </row>
+    <row r="95" ht="21" customHeight="1">
+      <c r="A95" s="14" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" s="15" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C95" s="14" t="inlineStr"/>
+      <c r="D95" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Intermediate Treasury</t>
-        </is>
-      </c>
-      <c r="F91" s="5" t="n">
-        <v>-0.00365512792947742</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.02339304531085351</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>-0.003477344573235119</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>-0.03397957056493628</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>-0.02421562434196667</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>-0.01998519615099914</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>-0.001830910070005243</v>
-      </c>
-    </row>
-    <row r="92" ht="21" customHeight="1">
-      <c r="A92" s="15" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="16" t="inlineStr">
-        <is>
-          <t>SHY</t>
-        </is>
-      </c>
-      <c r="C92" s="15" t="inlineStr"/>
-      <c r="D92" s="21" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E92" s="15" t="inlineStr">
-        <is>
-          <t>Short Treasury</t>
-        </is>
-      </c>
-      <c r="F92" s="5" t="n">
-        <v>-0.004617815044355433</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>-0.007392147358216139</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>-0.004968492486669862</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>-0.01301361609832508</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>-0.006910766246362887</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>-0.002435756911460252</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>0.0002442300647209628</v>
-      </c>
-    </row>
-    <row r="93" ht="21" customHeight="1">
-      <c r="A93" s="15" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="16" t="inlineStr">
-        <is>
-          <t>HYG</t>
-        </is>
-      </c>
-      <c r="C93" s="15" t="inlineStr"/>
-      <c r="D93" s="17" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E93" s="15" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>0.0006271951831409162</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>-0.007588952475740207</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>-0.005100771336153276</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>-0.01664201183431968</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>-0.007588952475740207</v>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>-0.002500937851694474</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>0.0003762227238526261</v>
-      </c>
-    </row>
-    <row r="94" ht="21" customHeight="1">
-      <c r="A94" s="15" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="16" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="C94" s="15" t="inlineStr"/>
-      <c r="D94" s="21" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E94" s="15" t="inlineStr">
+      <c r="E95" s="14" t="inlineStr">
         <is>
           <t>Long Treasury</t>
         </is>
       </c>
-      <c r="F94" s="5" t="n">
-        <v>-0.06153144940747501</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.05246203405430283</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>-0.005752416014726203</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>-0.05474578216458159</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>-0.0380752160710115</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>-0.04697986577181212</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>-0.006274131274131234</v>
-      </c>
-    </row>
-    <row r="95" ht="21" customHeight="1">
-      <c r="A95" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>INDA</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D95" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>India Equity</t>
-        </is>
-      </c>
       <c r="F95" s="5" t="n">
-        <v>-0.02627966267895676</v>
+        <v>-0.1112193010927188</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05680091185410341</v>
+        <v>-0.05138568129330245</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>-0.06174012158054709</v>
+        <v>-0.05023094688221708</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.04039427908774651</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>0.004653986240388486</v>
-      </c>
-      <c r="K95" s="3" t="n">
-        <v>0.00526422352702971</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>0.001815980629539915</v>
+        <v>-0.09546355428319742</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>-0.04209421641791045</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>-0.001215805471124543</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>-0.004483761512360518</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4809,25 +4812,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.1606471645693741</v>
+        <v>-0.1240497581202488</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1190394511149228</v>
+        <v>-0.1603179860881087</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>-0.20926243567753</v>
+        <v>-0.1722424643921829</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.05679012345679002</v>
+        <v>0.1219296304492146</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.08998302207130737</v>
+        <v>0.09385113268608425</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.1140997830802604</v>
+        <v>0.01440576230492208</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.008302761150801308</v>
+        <v>-0.0115032170013647</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00ECFCCB"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECFCCB"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,12 +136,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
+        <fgColor rgb="00FAE8FF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAE8FF"/>
+        <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,9 +200,6 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -657,44 +654,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>FTXL</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>EWY</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Growth &amp; Technology</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>South Korea Equity</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.567648110621052</v>
+        <v>2.353901949752638</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.187024063356686</v>
+        <v>1.538175919849462</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.198598842522084</v>
+        <v>1.267982542779668</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3803268183274591</v>
+        <v>0.355070273537857</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.169782231643862</v>
-      </c>
-      <c r="K2" s="5" t="n">
-        <v>-0.005264616237184772</v>
+        <v>-0.1640796159045355</v>
+      </c>
+      <c r="K2" s="3" t="n">
+        <v>0.1191337993010484</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-0.02933621738542647</v>
+        <v>-0.008459581997124821</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -703,40 +696,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EWY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>FTXL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>South Korea Equity</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.269251874885677</v>
+        <v>1.600386125449507</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.474114064230343</v>
+        <v>1.210803632971448</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.174695459579181</v>
+        <v>1.223416453329785</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.1807491576930698</v>
+        <v>0.4603144780820749</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.1316620512073071</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.1376830044557606</v>
+        <v>-0.2047601717309496</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>-0.005672720618509541</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-0.01177706513325238</v>
+        <v>-0.0205488711639854</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -753,7 +750,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -764,25 +761,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.336700955180015</v>
+        <v>1.354437026254124</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.024025457438345</v>
+        <v>1.037664746536866</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1.170883054892601</v>
+        <v>1.214050101158964</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.2849494949494948</v>
+        <v>0.3421633902242009</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.1811920700308961</v>
+        <v>-0.2079476948570449</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.06764878334799185</v>
+        <v>-0.07966637906241025</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-0.03497193142163557</v>
+        <v>-0.02897891063571534</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -810,25 +807,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.758392043099876</v>
+        <v>1.776212184003315</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.186596583442838</v>
+        <v>1.200722733245729</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>1.093298291721419</v>
+        <v>1.14388961892247</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.4606100504718016</v>
+        <v>0.5550139275766015</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1316373124592303</v>
+        <v>-0.182849475481825</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.04456999372253612</v>
+        <v>0.02650934722647857</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.02218304686352268</v>
+        <v>-0.01586602027324813</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -841,7 +838,7 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="D6" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -852,25 +849,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.383848072127374</v>
+        <v>1.417356187478763</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.026251426707973</v>
+        <v>1.047624058656807</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.058087396054133</v>
+        <v>1.079117146540706</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4109966221011097</v>
+        <v>0.4951180244500555</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1265199971884446</v>
+        <v>-0.1732051320391348</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.01546871595793142</v>
+        <v>-0.01514733690513714</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-0.027316844082655</v>
+        <v>-0.02162257357545405</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -887,7 +884,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="D7" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -898,25 +895,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.351703940362087</v>
+        <v>1.38584928963071</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9778325123152711</v>
+        <v>0.9990883426083936</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.9939543215405284</v>
+        <v>1.023829534967409</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.3853513174404015</v>
+        <v>0.4554654566827183</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1257052360684945</v>
+        <v>-0.176855821518156</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.008085345311622638</v>
+        <v>-0.01222493887530574</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-0.02677390921110634</v>
+        <v>-0.02071397091229632</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -933,7 +930,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="D8" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -944,25 +941,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.335567298191347</v>
+        <v>1.352186219792882</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8727823900237692</v>
+        <v>0.8861081994192328</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.8620345172069308</v>
+        <v>0.8848642014862311</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3378202131062824</v>
+        <v>0.3957448984810517</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.09229793131083763</v>
+        <v>-0.1366476329067873</v>
       </c>
       <c r="K8" s="3" t="n">
-        <v>0.005772112556194919</v>
+        <v>0.0006599934000659502</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-0.02331890124499225</v>
+        <v>-0.01942044086736239</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -979,7 +976,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -990,25 +987,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.176343239519779</v>
+        <v>1.280652818412138</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.879972798367902</v>
+        <v>0.9700777592898071</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.6414484869092145</v>
+        <v>0.7422891854428675</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.461345315184353</v>
+        <v>0.5540749053163136</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.07589025102159952</v>
+        <v>0.03435720287554855</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.1453133091662351</v>
+        <v>0.1307409675443969</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.02360455429047481</v>
+        <v>0.02554845876145517</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1017,40 +1014,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>BDRY</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Dry Bulk Freight</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.8243715477398266</v>
+        <v>1.396875</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.801224262659989</v>
+        <v>0.83273596176822</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.6361713967723985</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.270628876501531</v>
+        <v>0.2272000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.1839929768088375</v>
+        <v>0.1854714064914993</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1008774913271206</v>
+        <v>0.09964157706093202</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-0.00406153846153845</v>
+        <v>-0.008403361344537896</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1059,44 +1060,40 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>BDRY</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D11" s="9" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" s="11" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.4296875</v>
+        <v>0.8432890662035253</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8578255675029871</v>
+        <v>0.819642671327657</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.6033452807646358</v>
+        <v>0.6470142053043144</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.2883181441590721</v>
+        <v>0.3191074158348906</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2017001545595054</v>
+        <v>0.2751233570514127</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.1587183308494784</v>
+        <v>0.1048129794311317</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.005171299288946329</v>
+        <v>0.001538461538461489</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1113,7 +1110,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D12" s="6" t="inlineStr">
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1124,25 +1121,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.229604298974109</v>
+        <v>1.334673450738295</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.696654275092937</v>
+        <v>0.7321448463437814</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.5981412639405206</v>
-      </c>
-      <c r="I12" s="5" t="n">
-        <v>-0.02728047740835471</v>
+        <v>0.6429763821836962</v>
+      </c>
+      <c r="I12" s="3" t="n">
+        <v>0.06004814931051561</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.06424157630873273</v>
+        <v>0.07689971654717676</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.06164224238194915</v>
+        <v>0.05427251732101612</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.003058103975535187</v>
+        <v>-0.002839667977282745</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1170,25 +1167,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.404761904761905</v>
+        <v>1.465837040025303</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.845211804858462</v>
+        <v>0.8817001714624197</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.5832162216422405</v>
-      </c>
-      <c r="I13" s="5" t="n">
-        <v>-0.03960292580982239</v>
-      </c>
-      <c r="J13" s="3" t="n">
-        <v>0.04277286135693203</v>
+        <v>0.6361534524735142</v>
+      </c>
+      <c r="I13" s="3" t="n">
+        <v>0.05240358609946738</v>
+      </c>
+      <c r="J13" s="5" t="n">
+        <v>-0.02220632227220631</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.1654831346690337</v>
+        <v>0.1500756048387097</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.01023045444755544</v>
+        <v>-0.01712255007538233</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1216,25 +1213,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6160747803889182</v>
+        <v>0.6380524833407857</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6760365972357405</v>
+        <v>0.6988296966831267</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.4981896048277203</v>
+        <v>0.513578437849203</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.08443963019875556</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.02926479378362234</v>
+        <v>0.1153006032868733</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>-0.003600882797072824</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.1187079337855046</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.003052332354722909</v>
+        <v>0.1223929029387905</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>-0.0006524069155133816</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1243,7 +1240,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>BOAT</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1251,36 +1248,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D15" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.847815414825724</v>
+        <v>1.05330936158365</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.5861778339654447</v>
+        <v>0.6820713441787007</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.4584913611462285</v>
-      </c>
-      <c r="I15" s="5" t="n">
-        <v>-0.001591511936339551</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>-0.136201950659782</v>
+        <v>0.5134185825451323</v>
+      </c>
+      <c r="I15" s="3" t="n">
+        <v>0.1915756420332992</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.2325271902955466</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.08754695174804983</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>-0.01427262013879804</v>
+        <v>0.1114382785956964</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.008425811755035095</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1289,10 +1286,14 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
+          <t>PICK</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
@@ -1300,29 +1301,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.07311903920876</v>
+        <v>0.8942136794962612</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6217187068250898</v>
+        <v>0.6185147609978248</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.446808510638298</v>
-      </c>
-      <c r="I16" s="5" t="n">
-        <v>-0.309448170372985</v>
+        <v>0.4838467375063418</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>0.07902264354903443</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.1410800526854968</v>
+        <v>-0.05231343702771662</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.1208938120702827</v>
+        <v>0.09075601953190771</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.02394811242308337</v>
+        <v>-0.006441717791411117</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1331,7 +1332,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>PICK</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1346,29 +1347,29 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.8207282913165264</v>
+        <v>0.8701286399901516</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.5853658536585367</v>
+        <v>0.5996559470103948</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.4426829268292682</v>
+        <v>0.4727698538531835</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.01025800435188051</v>
+        <v>0.07624842420499101</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.01649266152216677</v>
+        <v>-0.123679701774614</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.09890109890109899</v>
+        <v>0.08615473274744279</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.00306748466257678</v>
+        <v>-0.01283226397800186</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1377,44 +1378,40 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QTEC</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.6245995483430491</v>
+        <v>1.068173790180148</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4532556609978386</v>
+        <v>0.6178502348715116</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4024241285351873</v>
-      </c>
-      <c r="I18" s="3" t="n">
-        <v>0.3750889046941677</v>
+        <v>0.4495717048908539</v>
+      </c>
+      <c r="I18" s="5" t="n">
+        <v>-0.2159882163899305</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.03125391456845805</v>
+        <v>-0.1388439476393587</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.03624547768993702</v>
+        <v>0.1160884483415936</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.02265331269154214</v>
+        <v>-0.02627640113088314</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1423,7 +1420,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BOAT</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1431,36 +1428,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.8193620178041541</v>
+        <v>0.6309321481562282</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.5536902122267975</v>
+        <v>0.4588567852206087</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.3956287614824201</v>
+        <v>0.4269075867037</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.1703650680028632</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0.2225822532402792</v>
+        <v>0.4092042753952034</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>-0.06733068520483232</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.113254652746255</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>0.008014796547472169</v>
+        <v>0.02239051695752381</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>-0.01898834160058127</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1477,7 +1474,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1488,25 +1485,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.6665131700128937</v>
+        <v>0.7079859756954376</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4542312947038494</v>
+        <v>0.4727363503727076</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.3954030378526079</v>
+        <v>0.386085692206307</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.06704800094350727</v>
+        <v>0.1352829281877919</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.05497901119402981</v>
+        <v>0.06638354571743932</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.04215861314288993</v>
+        <v>0.06251464729318013</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.007460609097488913</v>
+        <v>0.009687656589276727</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1515,44 +1512,40 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IBB</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D21" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.5284974093264247</v>
+        <v>0.6492043098746298</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.5153378671682824</v>
+        <v>0.4123872842826606</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.3486470843582694</v>
+        <v>0.3638216297520602</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1943319838056679</v>
-      </c>
-      <c r="J21" s="3" t="n">
-        <v>0.2164595191079102</v>
+        <v>0.3442136515549445</v>
+      </c>
+      <c r="J21" s="5" t="n">
+        <v>-0.0686653308614521</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.1235985193927365</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0.001913417842621223</v>
+        <v>0.03560997528645249</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>-0.01136729222520105</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1561,40 +1554,44 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>XLK</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>IBB</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6289793384765452</v>
+        <v>0.536899827050993</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.3998323554065382</v>
+        <v>0.5223132902024836</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.3362036119789682</v>
+        <v>0.348452752913778</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.3238685500144134</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>-0.03832059470212557</v>
+        <v>0.2349373304657532</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.2778323506124987</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.04761904761904767</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>-0.01501340482573732</v>
+        <v>0.1289333548491205</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0.003970342023439377</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1603,7 +1600,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>VDE</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1618,29 +1615,29 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.4533649071881445</v>
+        <v>0.4960337236401688</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4304187655063529</v>
+        <v>0.4701617845844455</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3337343056913016</v>
+        <v>0.3452625101176254</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.2377049180327868</v>
+        <v>0.1515699812865627</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.1601926946765047</v>
+        <v>0.1146318705944338</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.0724915445321308</v>
+        <v>0.09284379333212756</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.006879762912785692</v>
+        <v>0.006105344951989888</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1664,25 +1661,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.4322727272727274</v>
+        <v>0.4809471719837373</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.4187303016659163</v>
+        <v>0.4669445359905338</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3259792886087347</v>
+        <v>0.3440786230776209</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2553784860557768</v>
+        <v>0.2165187186414512</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.06886024423337855</v>
+        <v>0.04648074369189903</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.06994906621392194</v>
+        <v>0.09141274238227148</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.006709265175718793</v>
+        <v>0.007028753993610248</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1691,7 +1688,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>VDE</t>
+          <t>IYW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,36 +1696,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.432306477093207</v>
+        <v>0.6138774039728738</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4290330207266138</v>
+        <v>0.3716007846874529</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.323744975963433</v>
+        <v>0.3421341975369978</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1506440764007868</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>0.1397234443746074</v>
+        <v>0.319120912864115</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>-0.04168939169404973</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.07953801274037042</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>0.006438363767552913</v>
+        <v>0.02195502298095864</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>-0.008954154727793706</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1752,25 +1749,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.4138461538461538</v>
+        <v>0.4809934972297745</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.4232300884955751</v>
+        <v>0.4673491164348103</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3174778761061945</v>
+        <v>0.3411917685821284</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.1503934191702432</v>
+        <v>0.1537002733844928</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.1428317640788772</v>
+        <v>0.1177339652557663</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.08026868178001689</v>
+        <v>0.09406361626126891</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.005784865540963136</v>
+        <v>0.005628517823639712</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1779,7 +1776,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IYW</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1787,36 +1784,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.6043579464632096</v>
+        <v>0.5061033903646983</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3649265636173606</v>
+        <v>0.4655004920057189</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3094229605588867</v>
+        <v>0.3407213949960981</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.3088405949994724</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>-0.01893879487585004</v>
+        <v>0.2089004230216991</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.1337500552851598</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.0423878339774828</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>-0.01253581661891123</v>
+        <v>0.09306862520082615</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.00814987298899239</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1825,7 +1822,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>FTEC</t>
+          <t>QCLN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1833,36 +1830,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="D28" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.5964143202382959</v>
+        <v>0.5897626881980509</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3697738342093841</v>
+        <v>0.272466968509441</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3025027728215268</v>
+        <v>0.3332493989886043</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.3117063033941352</v>
+        <v>0.01704269987552021</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.01797752808988762</v>
-      </c>
-      <c r="K28" s="3" t="n">
-        <v>0.05164753794890786</v>
+        <v>-0.2967723090404557</v>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>-0.04558969276511404</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.01220614828209765</v>
+        <v>-0.01553874463299931</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1871,7 +1868,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>QCLN</t>
+          <t>FTEC</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1879,36 +1876,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="D29" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.575378538512179</v>
+        <v>0.6129405591430226</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.2624637298865735</v>
+        <v>0.3803287146180174</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.2993932999208653</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>-0.01136128898987809</v>
+        <v>0.3305417626294094</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0.3237479163198442</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>-0.2782385763836526</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>-0.02842062525375555</v>
+        <v>-0.05059632654380386</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.03741855640082981</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.0214680024534859</v>
+        <v>-0.008867714563917106</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1921,7 +1918,7 @@
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="D30" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -1932,25 +1929,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5906964309584279</v>
+        <v>0.6065719765764286</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3657752783197521</v>
+        <v>0.3761731944174955</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.2986342247216804</v>
+        <v>0.3272958753998194</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3099955966534567</v>
+        <v>0.3226437229339656</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>-0.01701635552618541</v>
+        <v>-0.04967718572015567</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.05170128148475461</v>
+        <v>0.03682473510508943</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.01236617146651176</v>
+        <v>-0.00921238277035441</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1959,44 +1956,40 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>DRIV</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SIL</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Autonomous/EV</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.4997796386073159</v>
+        <v>1.817885685569196</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.308846153846154</v>
+        <v>0.6816484428486422</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.2849999999999999</v>
-      </c>
-      <c r="I31" s="3" t="n">
-        <v>0.04194733619105961</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>-0.1819711538461538</v>
+        <v>0.3203370504868808</v>
+      </c>
+      <c r="I31" s="5" t="n">
+        <v>-0.09287604506689651</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.05000135474177791</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.01855731816821327</v>
+        <v>0.2736508774244621</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.01390901188061422</v>
+        <v>-0.01449719244512504</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2020,25 +2013,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.4665567916494986</v>
+        <v>0.4737151367080119</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.166484596897531</v>
+        <v>0.1699595243783207</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.2786759886388464</v>
+        <v>0.3149605832927664</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>-0.09653947034436072</v>
+        <v>-0.08595303073298388</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-0.173401455333643</v>
+        <v>-0.1692678002950539</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.08774028193079875</v>
+        <v>-0.1102702702702704</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>-0.01330622805396409</v>
+        <v>-0.01136573646276107</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2047,40 +2040,44 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>DRIV</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Autonomous/EV</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1.784624244169306</v>
+        <v>0.5291849540601947</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.6645438898450946</v>
+        <v>0.3248013588784369</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.2693631669535284</v>
-      </c>
-      <c r="I33" s="5" t="n">
-        <v>-0.1806320427010083</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0.03179344926917738</v>
+        <v>0.312409180134178</v>
+      </c>
+      <c r="I33" s="3" t="n">
+        <v>0.1025558639761692</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>-0.1940168890248114</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.3113220338983049</v>
+        <v>0.009442313366774924</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>-0.0126595201633487</v>
+        <v>-0.008693132425383832</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2108,25 +2105,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.4561803444782171</v>
+        <v>0.4869403234132987</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.3274070653428769</v>
+        <v>0.3503766485528657</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.2519048718540753</v>
+        <v>0.2888256851959499</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.2465307892454467</v>
+        <v>0.2656715470221513</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.148880895283773</v>
+        <v>0.1372933727881549</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.06030984876429368</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>-0.001563042723167651</v>
+        <v>0.0477573996731433</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.002084056964223757</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2143,7 +2140,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -2154,22 +2151,22 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.406332920573147</v>
+        <v>0.412234878753597</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2470588235294118</v>
+        <v>0.2522923769962342</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.2431372549019608</v>
+        <v>0.2789134350732609</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.01390128810100766</v>
+        <v>0.06297633373445644</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1031137184115524</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0.003154574132492094</v>
+        <v>-0.1199911445649768</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>-0.02081537135115163</v>
       </c>
       <c r="L35" s="5" t="n">
         <v>-0.01168572849328686</v>
@@ -2181,7 +2178,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SPMO</t>
+          <t>SCHA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -2192,29 +2189,29 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.4581162324649299</v>
+        <v>0.3670788037805752</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2493131868131868</v>
+        <v>0.2579557699259007</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.2348042582417582</v>
+        <v>0.2664780034187713</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2180463714740104</v>
+        <v>0.1296223373511027</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.03366757420811473</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0.0117499826183689</v>
+        <v>-0.006486799426306478</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>-0.006729081334113429</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.01067373716772035</v>
+        <v>-0.00614754098360637</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2223,40 +2220,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>FNDX</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XAR</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D37" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Fundamental Equity</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.3146569224522942</v>
+        <v>0.5344883763204815</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2569875776397517</v>
+        <v>0.1711729921781782</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.232142857142857</v>
-      </c>
-      <c r="I37" s="3" t="n">
-        <v>0.1153978642783329</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>0.04485317844465975</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>0.02016383112791442</v>
-      </c>
-      <c r="L37" s="18" t="n">
-        <v>0</v>
+        <v>0.2627292874018476</v>
+      </c>
+      <c r="I37" s="5" t="n">
+        <v>-0.106860699894029</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>-0.09107216557028208</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>-0.0725066695903227</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>-0.01064244503352563</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2265,14 +2266,10 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MTUM</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>FNDX</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -2280,29 +2277,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Fundamental Equity</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.3553408726706653</v>
+        <v>0.3509333344939944</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2145406802609444</v>
+        <v>0.2802593888320826</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.2291880359414105</v>
+        <v>0.2624999336849052</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.170224541429475</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>-0.06266426015642323</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>-0.01191628559030677</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>-0.01444932747369831</v>
+        <v>0.1392134514308661</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0.04741184110988006</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.01406689590497034</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0.001852995676343339</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2311,7 +2308,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SCHA</t>
+          <t>SPMO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -2322,29 +2319,29 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.3391373169766523</v>
+        <v>0.4818687268393889</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2391065543756867</v>
+        <v>0.2647510259325232</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2288538996704506</v>
+        <v>0.2583445931911303</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1087811271297512</v>
+        <v>0.2307341708503152</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.00616740088105705</v>
+        <v>-0.05187802218640447</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.008343265792610355</v>
+        <v>0.005091159270725898</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.009367681498828828</v>
+        <v>-0.006798558705554458</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2353,44 +2350,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>XME</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D40" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>HEFA</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Developed ex-US Hedged</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>1.011531841652324</v>
+        <v>0.346373646620844</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.4195311551074943</v>
+        <v>0.2689784205774226</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2225191303291632</v>
-      </c>
-      <c r="I40" s="5" t="n">
-        <v>-0.02077922077922068</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>-0.06660809839469684</v>
+        <v>0.2571188091701571</v>
+      </c>
+      <c r="I40" s="3" t="n">
+        <v>0.1023690436208191</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.04339958587866222</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.1611525086934922</v>
+        <v>0.00943396226415083</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.01066621518665867</v>
+        <v>-0.003175947491001474</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2399,7 +2392,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2407,36 +2400,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D41" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.5272464814146518</v>
+        <v>1.022535988850903</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1677704194260485</v>
+        <v>0.4236230399707883</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2180831493745401</v>
+        <v>0.25697697937479</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>-0.1025659150349898</v>
+        <v>-0.002964675411736506</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.1183333333333334</v>
-      </c>
-      <c r="K41" s="5" t="n">
-        <v>-0.04130484029298509</v>
+        <v>-0.120229710251354</v>
+      </c>
+      <c r="K41" s="3" t="n">
+        <v>0.1325768596644361</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.01013566193669102</v>
+        <v>-0.01142808769999148</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2460,25 +2453,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.3469286247202188</v>
+        <v>0.3636039406120863</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.164480756826489</v>
+        <v>0.1759066855188769</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2117824123844334</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>-0.01688146669086965</v>
+        <v>0.2476797102112518</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>0.001199706983114002</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.0381814952939088</v>
+        <v>-0.04508531200550159</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.03903477643718956</v>
+        <v>-0.05752519986096627</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.009872029250457159</v>
+        <v>-0.008592321755027554</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2487,40 +2480,44 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D43" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4677304735448027</v>
+        <v>0.3770501210087085</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.1449954641669187</v>
+        <v>0.2282948088532823</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.207841951416188</v>
-      </c>
-      <c r="I43" s="5" t="n">
-        <v>-0.06782373215164939</v>
+        <v>0.2469716995752658</v>
+      </c>
+      <c r="I43" s="3" t="n">
+        <v>0.2058425027031696</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.03504077471967382</v>
+        <v>-0.08723609943008914</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.05203204539764661</v>
+        <v>-0.01497779839618263</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>-0.005079921173636981</v>
+        <v>-0.01032094819549878</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2529,82 +2526,82 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>QQQM</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D44" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.3939118799579471</v>
+        <v>0.4744220670326458</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.242238405519356</v>
+        <v>0.1472230723318302</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.206464801328734</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0.1664800447892505</v>
+        <v>0.2465058885527058</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-0.07426699019595595</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.04036715357283849</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0.02965159377316517</v>
+        <v>-0.007406012020344854</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>-0.07964889466840064</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-0.01182329426112882</v>
+        <v>-0.008189183271294032</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
-      <c r="A45" s="14" t="n">
+      <c r="A45" t="n">
         <v>44</v>
       </c>
-      <c r="B45" s="15" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C45" s="14" t="inlineStr"/>
-      <c r="D45" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E45" s="14" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SCHD</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3940807210185566</v>
+        <v>0.2924940073855462</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2419880785413744</v>
+        <v>0.2966474612075383</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2061535764375877</v>
+        <v>0.2461480182739115</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1665431671853645</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>-0.04047080494643174</v>
+        <v>0.1236417065842315</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0.08736823187717757</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.02970973415311251</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>-0.01162174228472579</v>
+        <v>0.04052443384982118</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.0008598452278589797</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2613,44 +2610,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>IWO</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D46" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>VEA</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.3463511560693642</v>
+        <v>0.4799099759185059</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2111472213194672</v>
+        <v>0.2712917951327229</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2046473838154048</v>
+        <v>0.2450037100389941</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1116181953765847</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>-0.02127268429760742</v>
+        <v>0.09662101090697583</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0.008321745387405155</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.005395634931340654</v>
+        <v>0.02111486486486491</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.01145918989893624</v>
+        <v>-0.005211190345584149</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2659,40 +2652,44 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>VEA</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D47" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Developed Markets</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.422557274329352</v>
+        <v>0.3605392882078162</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2374382558337593</v>
+        <v>0.2207178833146417</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2028615227388861</v>
+        <v>0.2352179699994568</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.03431093394077456</v>
-      </c>
-      <c r="J47" s="3" t="n">
-        <v>0.01226139055315612</v>
-      </c>
-      <c r="K47" s="3" t="n">
-        <v>0.02874539790427644</v>
+        <v>0.1293178597449449</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>-0.02132721665428805</v>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>-0.01173888903577192</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.003702687877125577</v>
+        <v>-0.008488288814026856</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2701,82 +2698,82 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>QQQM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.2242466713384723</v>
+        <v>0.4100975931095658</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2514326647564469</v>
+        <v>0.2528163307573226</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.1987822349570199</v>
+        <v>0.2338550176542991</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.09977966635190416</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>0.07507692307692304</v>
+        <v>0.1845647142652613</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-0.04619103250996581</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.0439199282939946</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>0.001433075379764892</v>
+        <v>0.01536753737815255</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>-0.008401653228538586</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
-      <c r="A49" t="n">
+      <c r="A49" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>HEFA</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr"/>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Developed ex-US Hedged</t>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.2689098250336475</v>
+        <v>0.4092173979644307</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2165161290322581</v>
+        <v>0.2521976141941051</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.1987096774193549</v>
+        <v>0.2332428059717051</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.04685765045525203</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>0.03536130024159889</v>
+        <v>0.1843952519040273</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>-0.04630217903671596</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.01485468245425192</v>
+        <v>0.01536989158227042</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.001905568494600773</v>
+        <v>-0.008273341146269209</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2785,44 +2782,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D50" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.1852492183189256</v>
+        <v>0.2979905308787409</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2631723380900108</v>
+        <v>0.1570147655599017</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.1949584444095969</v>
-      </c>
-      <c r="I50" s="3" t="n">
-        <v>0.09035227234272947</v>
-      </c>
-      <c r="J50" s="3" t="n">
-        <v>0.1523550659847643</v>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>0.05708474131426122</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>0.007032129016127042</v>
+        <v>0.2204493461181274</v>
+      </c>
+      <c r="I50" s="5" t="n">
+        <v>-0.00503693200145372</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>-0.0007049536965453296</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>-0.05197641406420617</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-0.008507965511334481</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2831,7 +2824,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ARGT</t>
+          <t>PPA</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2839,36 +2832,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D51" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.1546267214302972</v>
+        <v>0.4289625946653275</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1925140361821585</v>
+        <v>0.1253230399768213</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.1871490954460386</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>0.06483957219251324</v>
+        <v>0.2155714506840796</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>-0.08853697380084125</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.02169907881269195</v>
-      </c>
-      <c r="K51" s="3" t="n">
-        <v>0.004519180241723486</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0.01089370703331571</v>
+        <v>-0.04047664682178675</v>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>-0.07424360835101029</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>-0.009259812414122659</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2892,25 +2885,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3870185833557769</v>
+        <v>0.4031942032963434</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2192234848484849</v>
+        <v>0.2299422550038301</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.1840672348484849</v>
+        <v>0.2152972504185957</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1544496749607711</v>
+        <v>0.1682431344983688</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.03049698795180722</v>
+        <v>-0.0305127188784593</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>0.02969109267219827</v>
+        <v>0.01205055354168705</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-0.008566753296756158</v>
+        <v>-0.005679083646164207</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2919,40 +2912,44 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D53" s="11" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.273380767255923</v>
+        <v>0.2133421671313263</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.142030129596737</v>
+        <v>0.2835954461277141</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.1830800605223342</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>-0.01998419329344014</v>
+        <v>0.2144803021743404</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>0.1199478476303635</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.002714723040489808</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>-0.03469750889679724</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>-0.008736367270028023</v>
+        <v>0.1830972879432742</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0.05690923420464999</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0.005906988373546751</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2961,7 +2958,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PPA</t>
+          <t>ARKQ</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2969,36 +2966,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4255847827949619</v>
+        <v>0.6612680781587468</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.124417111576671</v>
+        <v>0.235606319993418</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.1788876123538554</v>
+        <v>0.21401161001921</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.08112884519798969</v>
+        <v>-0.0009102946044355908</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.06312292358803995</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>-0.04620499885347396</v>
+        <v>-0.1488896721889319</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0.01778789411566351</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.006033813250492792</v>
+        <v>-0.01444897959183666</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3007,7 +3004,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>XMMO</t>
+          <t>ARGT</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3015,36 +3012,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2350630217711573</v>
+        <v>0.1761995538024865</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1494515539305301</v>
+        <v>0.2138008064055681</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.1752742230347348</v>
+        <v>0.2006786355255077</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.005664778407197479</v>
+        <v>0.1190068832659232</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-0.1062544420753376</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>-0.02197161189966934</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>-0.009452540370224471</v>
+        <v>-0.01280252878975752</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0.01092896174863389</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0.01745108408249618</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3053,7 +3050,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ARKQ</t>
+          <t>XMMO</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -3061,36 +3058,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D56" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D56" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.6572879494921768</v>
+        <v>0.2534705356656861</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2326459779501839</v>
+        <v>0.1606046414647759</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.1746631278072683</v>
-      </c>
-      <c r="I56" s="5" t="n">
-        <v>-0.01380267886311659</v>
+        <v>0.1992505676869119</v>
+      </c>
+      <c r="I56" s="3" t="n">
+        <v>0.02132934302830924</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.1548260656540912</v>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>0.0493612583644738</v>
+        <v>-0.1080874254424551</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>-0.0322250639386189</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.01428571428571423</v>
+        <v>-0.006432978863069372</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3099,82 +3096,82 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>IAU</t>
+          <t>VBK</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D57" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.5232968256914796</v>
+        <v>0.2798028818161704</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2605222734254993</v>
+        <v>0.1905044405989609</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.1700460829493089</v>
-      </c>
-      <c r="I57" s="5" t="n">
-        <v>-0.1716967800545068</v>
+        <v>0.1885841615312283</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0.09844652254175346</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.04012165165516424</v>
+        <v>-0.02950162986196181</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.07732703163975319</v>
+        <v>0.001615602100282665</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.01971090670170816</v>
+        <v>-0.008736866148926437</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
-      <c r="A58" s="14" t="n">
+      <c r="A58" t="n">
         <v>57</v>
       </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr"/>
-      <c r="D58" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>Gold</t>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>IVV</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>US Large Blend</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.5206442055684279</v>
+        <v>0.3097304869732127</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.258653755462634</v>
+        <v>0.1985744764304729</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.168107649259597</v>
-      </c>
-      <c r="I58" s="5" t="n">
-        <v>-0.1724237726098192</v>
-      </c>
-      <c r="J58" s="5" t="n">
-        <v>-0.04022823168392797</v>
+        <v>0.1883350528676975</v>
+      </c>
+      <c r="I58" s="3" t="n">
+        <v>0.1296839708824455</v>
+      </c>
+      <c r="J58" s="3" t="n">
+        <v>0.009019529696495221</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.07751520697636849</v>
+        <v>0.008616613250669758</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.01978355614318605</v>
+        <v>-0.003710719568207232</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3183,7 +3180,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VBK</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -3194,29 +3191,29 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2656158572264482</v>
+        <v>0.3093011824318097</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1809247568674286</v>
+        <v>0.1982280323615775</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.1617812659955637</v>
+        <v>0.1880771719749448</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.08048955633956711</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>-0.0267450362787558</v>
+        <v>0.12928916328079</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0.008786526758499891</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.01647770663220349</v>
+        <v>0.00854394026421601</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.01190612151667436</v>
+        <v>-0.003603399111918093</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3240,25 +3237,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.2839375273486149</v>
+        <v>0.3080751778852353</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1826835129059763</v>
+        <v>0.1977630007876094</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.1580962716068521</v>
+        <v>0.1876059580013714</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1121007594862899</v>
+        <v>0.1291738760983436</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.008473456006768076</v>
+        <v>0.008621469302541707</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.02123074039864536</v>
+        <v>0.008552536064513561</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>-0.005423375268887254</v>
+        <v>-0.003780718336483857</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3267,10 +3264,14 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>VOO</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3278,29 +3279,29 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.283784525836033</v>
+        <v>0.3237342228853832</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1825891953867942</v>
+        <v>0.1968200077425082</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1577696094961893</v>
+        <v>0.1836518298209084</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1114509381338744</v>
+        <v>0.1425069857027834</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.008454470948539905</v>
+        <v>0.005139563836355832</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.02143741352945461</v>
+        <v>0.01112504335298681</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.004993686958248755</v>
+        <v>-0.002579083109637392</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3309,40 +3310,44 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IVV</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr"/>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>US Large Blend</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.2838525963149079</v>
+        <v>0.2247139140055816</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1822248272458045</v>
+        <v>0.1339401663715465</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.157329713721619</v>
+        <v>0.1827460513610628</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1118106124343614</v>
+        <v>0.111529685238982</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.008433655680547547</v>
-      </c>
-      <c r="K62" s="3" t="n">
-        <v>0.02151082204925903</v>
+        <v>0.07010530438880958</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>-0.04126488939307993</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.005553104808365905</v>
+        <v>-0.002949417490045736</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3351,14 +3356,10 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
       <c r="D63" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3366,29 +3367,29 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Cash Flow Factor</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3033967204078822</v>
+        <v>0.2975400033228202</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1834902561856799</v>
+        <v>0.2694188531781825</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1543370139822953</v>
+        <v>0.1819575099459281</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1298076923076923</v>
+        <v>0.1281540838541464</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.002703204091909051</v>
+        <v>0.1120407345720607</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.02525539929003084</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>-0.00428969945786617</v>
+        <v>0.07399702823179788</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>0.002496532593620149</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3397,40 +3398,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>COWZ</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cash Flow Factor</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.2595179881243452</v>
+        <v>0.4058207427542615</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.241094475993805</v>
+        <v>0.2155463166887452</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1514369299604199</v>
+        <v>0.176116734332197</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1105635971666155</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>0.1100507926735417</v>
+        <v>0.1065099825819016</v>
+      </c>
+      <c r="J64" s="5" t="n">
+        <v>-0.001265770189730175</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.07786578986698567</v>
+        <v>0.03352522858110385</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.0002773925104022634</v>
+        <v>0.008592200925313875</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3439,44 +3440,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.184196755625327</v>
+        <v>0.5234824577687023</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1118571896495251</v>
+        <v>0.2606758832565284</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1406812970848346</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>0.1120393120393122</v>
-      </c>
-      <c r="J65" s="3" t="n">
-        <v>0.06930225232320053</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>-0.02526920315865044</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0.001179766996018294</v>
+        <v>0.1703533026113673</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>-0.1443911592994163</v>
+      </c>
+      <c r="J65" s="5" t="n">
+        <v>-0.02783700544894585</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>0.07717548234676452</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>-0.01959144666109192</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3485,82 +3482,82 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="6" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D66" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3650793650793651</v>
+        <v>0.2446191433228566</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1849408111779547</v>
+        <v>0.1784350410106414</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1401125557927421</v>
+        <v>0.1701350640467429</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.05094664371772817</v>
+        <v>0.09083775311018116</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.0197060788243153</v>
+        <v>0.04502373651806613</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.03931914893617017</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>0.008922670191672255</v>
+        <v>0.007093178573073455</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>-0.003372988741510485</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
-      <c r="A67" t="n">
+      <c r="A67" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>RSP</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Equal Weight</t>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr"/>
+      <c r="D67" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.2120657120657119</v>
+        <v>0.5209480761195733</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1578305587954616</v>
+        <v>0.2589052724243093</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1399109320326581</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>0.06547299604820211</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>0.04577886319015456</v>
+        <v>0.1686421228031565</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>-0.1446575810654932</v>
+      </c>
+      <c r="J67" s="5" t="n">
+        <v>-0.02798883359631021</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.0157201990605087</v>
+        <v>0.07723763148691187</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.004558092893933163</v>
+        <v>-0.01958767934968908</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3584,25 +3581,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3170803782505909</v>
+        <v>0.3279950879387308</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1608282328428179</v>
+        <v>0.167971337763887</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1242349264227112</v>
+        <v>0.1534631888726838</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1518284016022742</v>
+        <v>0.160892315358294</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>-0.02333735071765086</v>
+        <v>-0.02539683075159926</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.03254951928645888</v>
+        <v>0.0125779036827196</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.008453837597330427</v>
+        <v>-0.006006674082313701</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3626,25 +3623,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.2972873900293256</v>
+        <v>0.3067974276727434</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1595674967234602</v>
+        <v>0.1657311032387989</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1195937090432504</v>
+        <v>0.1469767501807657</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1512687052700066</v>
+        <v>0.1589445990163998</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.007687927107061565</v>
+        <v>0.0104421032965667</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.03570383377231479</v>
+        <v>0.01635111876075723</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.007571508693213547</v>
+        <v>-0.0064498037016264</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3668,25 +3665,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2939958592132503</v>
+        <v>0.3050089130062659</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1446886446886446</v>
+        <v>0.151592419918815</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1145996860282574</v>
+        <v>0.1441034560927599</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1391745866423642</v>
+        <v>0.1473908628432798</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>-0.02343749999999989</v>
+        <v>-0.02546424596414776</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0.02699530516431925</v>
+        <v>0.006545705098759846</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.008386219401631867</v>
+        <v>-0.006686310063463208</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3695,7 +3692,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SPGP</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3703,36 +3700,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1816287878787879</v>
+        <v>0.09618769627687707</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1058135412974122</v>
+        <v>0.11366104586611</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1108649415101026</v>
+        <v>0.1387236407720365</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.08156366473086596</v>
+        <v>0.07439276114201543</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.03862160812385551</v>
+        <v>0.118345873049853</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.004547267650578335</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>-0.004785452225235187</v>
+        <v>-0.02200937436315475</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0.0002084201750729431</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3741,7 +3738,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>SPGP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3749,36 +3746,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D72" s="19" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.0595413113790062</v>
+        <v>0.2052538189677442</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.08539156626505995</v>
+        <v>0.1189183592893026</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1081325301204819</v>
+        <v>0.1369798511045845</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.05542945009885036</v>
+        <v>0.1050670295172078</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.1228480174495596</v>
+        <v>0.03569397581964528</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.02052188094590923</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>0.001389467833819547</v>
+        <v>-0.01588549858446053</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>-0.001914180890094097</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3787,40 +3784,44 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IGF</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D73" s="11" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2143257901627083</v>
+        <v>0.07332758513106441</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.07589063794531903</v>
+        <v>0.1569364667986335</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1070422535211268</v>
-      </c>
-      <c r="I73" s="5" t="n">
-        <v>-0.06400461294507709</v>
-      </c>
-      <c r="J73" s="5" t="n">
-        <v>-0.02507507507507489</v>
-      </c>
-      <c r="K73" s="5" t="n">
-        <v>-0.02813950007483901</v>
+        <v>0.1351281656658454</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0.1020076592781709</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.2174358974358974</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0.01921219276591168</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.003223825606386121</v>
+        <v>-0.0004210526315789886</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3829,44 +3830,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D74" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>IGF</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.07238848108413332</v>
+        <v>0.2703272679860584</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.156215755509558</v>
+        <v>0.1068883258916933</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.09022281748447591</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>0.07420814479638005</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>0.194615674927664</v>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>0.06053160598615137</v>
+        <v>0.1343812324743165</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>-0.03006874738320242</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>-0.0142134576254529</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>-0.02423603793466822</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.0004210526315789886</v>
+        <v>-0.004912496162112534</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3875,7 +3872,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>EUO</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3883,36 +3880,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D75" s="20" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F75" s="5" t="n">
-        <v>-0.1416309012875537</v>
+          <t>Retail</t>
+        </is>
+      </c>
+      <c r="F75" s="3" t="n">
+        <v>0.1825979653310801</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.06913756236635793</v>
+        <v>0.03593248165283658</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.07519600855310071</v>
+        <v>0.09508073014295459</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.06082036775106081</v>
+        <v>0.01507334234025204</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.02494021182097717</v>
+        <v>0.03592209909388822</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.005634736493205228</v>
+        <v>-0.05401268314017049</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.004352192835620938</v>
+        <v>0.004878048780487809</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3921,44 +3918,40 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>XRT</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D76" s="21" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+          <t>VONG</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr"/>
+      <c r="D76" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1574049096304289</v>
+        <v>0.2441708526274009</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.01924219028388174</v>
+        <v>0.09810264723418549</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.06639743437462875</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>-0.01345136813060477</v>
-      </c>
-      <c r="J76" s="3" t="n">
-        <v>0.02166924633884992</v>
-      </c>
-      <c r="K76" s="5" t="n">
-        <v>-0.04421920249498779</v>
+        <v>0.09065402182401017</v>
+      </c>
+      <c r="I76" s="3" t="n">
+        <v>0.08788274192944212</v>
+      </c>
+      <c r="J76" s="5" t="n">
+        <v>-0.04990798990871492</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0.006829503454925279</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.003368176538908196</v>
+        <v>-0.008544979824353205</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3967,7 +3960,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>IWF</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -3982,25 +3975,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.231868348443043</v>
+        <v>0.2411643503836511</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.09017179733147285</v>
+        <v>0.09686821610525076</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.06313769948547998</v>
+        <v>0.08902958173682984</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.07888150513506509</v>
+        <v>0.08722860495252083</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.05014816503305231</v>
+        <v>-0.05022047382540462</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.02542859486506455</v>
+        <v>0.007197815835194854</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.01091858533111789</v>
+        <v>-0.007904816233395784</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4009,40 +4002,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>IWF</t>
+          <t>VFH</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D78" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2309173846933603</v>
+        <v>0.1452077816755308</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.09003590664272898</v>
+        <v>0.08563592050123026</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.06211849192100538</v>
+        <v>0.08386175351447944</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.07889826743669492</v>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>-0.05021509581540862</v>
+        <v>0.1329571243530894</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0.121444058445584</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.02628465179175121</v>
+        <v>0.001636894171233472</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.01043109771004802</v>
+        <v>-0.001560726447219052</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4051,40 +4044,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VFH</t>
+          <t>XLU</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="19" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D79" s="11" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1171199746253271</v>
+        <v>0.115001136494693</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.06751534439645379</v>
+        <v>0.03300663335308673</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.0550125028415549</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>0.1220133800573431</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>0.1122690667929891</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>0.01185089420383534</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>-0.0005675368898979682</v>
+        <v>0.08152405606662572</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-0.08776995297781587</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>-0.02868897061449949</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>-0.0448602344454464</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.00331517878285581</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4093,40 +4086,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="19" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D80" s="11" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1061709467228824</v>
+        <v>0.07432393670833282</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.06908686793850705</v>
+        <v>0.09160231642795336</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.05463974810150019</v>
-      </c>
-      <c r="I80" s="3" t="n">
-        <v>0.1223021582733812</v>
+        <v>0.07964303697058406</v>
+      </c>
+      <c r="I80" s="5" t="n">
+        <v>-0.009783115456913571</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.1190383869716944</v>
+        <v>0.05579044383313803</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.01369863013698636</v>
+        <v>0.01107706811218478</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.0001732801940736994</v>
+        <v>0.009649329253942129</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4135,40 +4128,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D81" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.03177660086663447</v>
+        <v>0.1297134193958533</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.06115375092844766</v>
+        <v>0.08417294394131658</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.05285961871750433</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>-0.04766137095878242</v>
+        <v>0.07928250387496072</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0.135310300393682</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.03389217223495367</v>
+        <v>0.1240169407043166</v>
       </c>
       <c r="K81" s="3" t="n">
-        <v>0.007877718988830162</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>0.008707931277947667</v>
+        <v>0.00453119553851522</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>-0.001212961358516673</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4177,40 +4170,44 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLU</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>EUO</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D82" s="20" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="F82" s="3" t="n">
-        <v>0.06690229739964648</v>
+          <t>Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F82" s="5" t="n">
+        <v>-0.1430615164520744</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.002371916508538963</v>
+        <v>0.06735566642908064</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.05194497153700195</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>-0.1146029750680914</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>-0.04862674470959039</v>
+        <v>0.07875980042765507</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0.02323197813460887</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0.01628775025449603</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.04712514092446451</v>
+        <v>-0.01057152296002639</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.0007103954534690704</v>
+        <v>0.002678272514228253</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4223,7 +4220,7 @@
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="D83" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -4234,117 +4231,117 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1041471780480199</v>
+        <v>0.1112489881408318</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.05543964232488818</v>
+        <v>0.05962845804102446</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.04977645305514167</v>
+        <v>0.07610091852498591</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>-0.09251665812403909</v>
+        <v>-0.04071292279390826</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-0.1180572851805729</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>0.005394662123793248</v>
+        <v>-0.128993775129591</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>-0.0153075424436403</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.01337419894120939</v>
+        <v>-0.01421008637503474</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
-      <c r="A84" t="n">
+      <c r="A84" s="14" t="n">
         <v>83</v>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="15" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C84" s="14" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E84" s="14" t="inlineStr">
+        <is>
+          <t>US Dollar Basket</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>-0.009127828623342715</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0.06400194443331664</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0.06437978603290229</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0.02549162418062645</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0.01440922190201732</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>-0.0003549875754349507</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>0.001422475106685583</v>
+      </c>
+    </row>
+    <row r="85" ht="21" customHeight="1">
+      <c r="A85" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" t="inlineStr">
         <is>
           <t>EDEN</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
+      <c r="C85" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D84" s="6" t="inlineStr">
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
+      <c r="E85" t="inlineStr">
         <is>
           <t>Denmark Equity</t>
         </is>
       </c>
-      <c r="F84" s="3" t="n">
-        <v>0.05459796047288146</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>0.06526891522333633</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>0.03299908842297161</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>0.07993715922742828</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>0.04014241210502889</v>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>0.03123896929050485</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>-0.004005795619193675</v>
-      </c>
-    </row>
-    <row r="85" ht="21" customHeight="1">
-      <c r="A85" s="14" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D85" s="20" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E85" s="14" t="inlineStr">
-        <is>
-          <t>US Dollar Basket</t>
-        </is>
-      </c>
-      <c r="F85" s="5" t="n">
-        <v>-0.04219122150391297</v>
+      <c r="F85" s="3" t="n">
+        <v>0.09090726964345541</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.02849835586408478</v>
+        <v>0.1017442501356522</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.0292290829375228</v>
+        <v>0.05789559726861548</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.03951255539143284</v>
+        <v>0.1517123323152914</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.01771511207519882</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>-0.0007099751508697905</v>
+        <v>0.08802512106477978</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>0.04144894163493062</v>
       </c>
       <c r="L85" s="3" t="n">
-        <v>0.001066856330014243</v>
+        <v>0.002215972044660397</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4372,25 +4369,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.145098642464331</v>
+        <v>0.159715704106179</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.02981254755481766</v>
+        <v>0.03950786301076548</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.02206543542920381</v>
+        <v>0.04970730724966965</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.06927137573167652</v>
+        <v>0.08968063029431672</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.003280444533708349</v>
-      </c>
-      <c r="K86" s="3" t="n">
-        <v>0.007579859231185759</v>
+        <v>-0.01798308912966862</v>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>-0.009716464931188828</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.01413766844353204</v>
+        <v>-0.01129026917855835</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4399,7 +4396,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>VCR</t>
+          <t>USDU</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4407,36 +4404,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="21" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>0.0768437195036944</v>
+          <t>US Dollar Basket</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>-0.009217790489280842</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.0009070647385061026</v>
+        <v>0.04402163446054064</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.01409837764992483</v>
+        <v>0.04877078518591094</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.005022379514937114</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>-0.03856111526014439</v>
+        <v>0.01617873651771951</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.005718642775447869</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.01300792231024794</v>
-      </c>
-      <c r="L87" s="5" t="n">
-        <v>-0.01323488080942281</v>
+        <v>-0.004528301886792541</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>0.001898974553740995</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4445,7 +4442,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>USDU</t>
+          <t>VCR</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -4453,36 +4450,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D88" s="20" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D88" s="19" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>US Dollar Basket</t>
-        </is>
-      </c>
-      <c r="F88" s="5" t="n">
-        <v>-0.04665461121157322</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.09387368174368205</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.004573170731707377</v>
+        <v>0.01242404581255085</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.009527439024390238</v>
+        <v>0.0434944144559628</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.03738685556867383</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>0.007645259938837912</v>
+        <v>0.03286725651430311</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>-0.01193919261392085</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.004907512268780612</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>0.00113938473224473</v>
+        <v>-0.0297753090126609</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>-0.00927463655177696</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4491,40 +4488,40 @@
       </c>
       <c r="B89" s="15" t="inlineStr">
         <is>
-          <t>SHY</t>
+          <t>HYG</t>
         </is>
       </c>
       <c r="C89" s="14" t="inlineStr"/>
-      <c r="D89" s="22" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+      <c r="D89" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>Short Treasury</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>-0.01174049866860327</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>-0.01602795854422745</v>
-      </c>
-      <c r="H89" s="5" t="n">
-        <v>-0.01181007471679929</v>
-      </c>
-      <c r="I89" s="5" t="n">
-        <v>-0.01839384467420058</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-0.007897934386391192</v>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.07932232099056247</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.0388679157243681</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.03978564356511405</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0.01368688797374196</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.001174139140428299</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.004268292682926722</v>
+        <v>-0.0008826125330980705</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.002930760776651553</v>
+        <v>-0.007141962160130411</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4533,40 +4530,40 @@
       </c>
       <c r="B90" s="15" t="inlineStr">
         <is>
-          <t>HYG</t>
+          <t>SHY</t>
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr"/>
-      <c r="D90" s="19" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D90" s="21" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="F90" s="5" t="n">
-        <v>-0.01073255959066521</v>
-      </c>
-      <c r="G90" s="5" t="n">
-        <v>-0.01966361612663869</v>
-      </c>
-      <c r="H90" s="5" t="n">
-        <v>-0.01706653475142217</v>
-      </c>
-      <c r="I90" s="5" t="n">
-        <v>-0.01796333002973249</v>
-      </c>
-      <c r="J90" s="5" t="n">
-        <v>-0.0129498194496328</v>
+          <t>Short Treasury</t>
+        </is>
+      </c>
+      <c r="F90" s="3" t="n">
+        <v>0.04439782948976956</v>
+      </c>
+      <c r="G90" s="3" t="n">
+        <v>0.01994609068948727</v>
+      </c>
+      <c r="H90" s="3" t="n">
+        <v>0.02157020866829207</v>
+      </c>
+      <c r="I90" s="3" t="n">
+        <v>0.0007634727524090668</v>
+      </c>
+      <c r="J90" s="3" t="n">
+        <v>0.001447636577220024</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>-0.002642174131857189</v>
+        <v>-0.001589825119236776</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.006766069414860354</v>
+        <v>-0.003052875809012034</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4593,26 +4590,26 @@
           <t>TIPS</t>
         </is>
       </c>
-      <c r="F91" s="5" t="n">
-        <v>-0.0318107667210441</v>
-      </c>
-      <c r="G91" s="5" t="n">
-        <v>-0.03903930916614196</v>
-      </c>
-      <c r="H91" s="5" t="n">
-        <v>-0.03184312314473337</v>
+      <c r="F91" s="3" t="n">
+        <v>0.03615943608408512</v>
+      </c>
+      <c r="G91" s="3" t="n">
+        <v>0.008436781053551279</v>
+      </c>
+      <c r="H91" s="3" t="n">
+        <v>0.008908851450074806</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.04513764747944227</v>
+        <v>-0.009303598430488003</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.03938494739681675</v>
+        <v>-0.01205650669899572</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.00743287187587105</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>9.361542782260202e-05</v>
+        <v>-0.0004679019277559204</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>-9.361542782237997e-05</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4625,7 +4622,7 @@
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" s="22" t="inlineStr">
+      <c r="D92" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4635,68 +4632,68 @@
           <t>Intermediate Treasury</t>
         </is>
       </c>
-      <c r="F92" s="5" t="n">
-        <v>-0.03157784305497258</v>
+      <c r="F92" s="3" t="n">
+        <v>0.0253626833916778</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-0.03993759750390014</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>-0.03328133125325017</v>
+        <v>-0.002678627698448399</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.003266172938441558</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.05796509847943665</v>
+        <v>-0.03285013429893591</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.02472266244057053</v>
+        <v>-0.01430140290715232</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.006885422270037633</v>
+        <v>-0.005925447101917669</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>-0.004636618503342627</v>
+        <v>-0.00506793185249077</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
-      <c r="A93" t="n">
+      <c r="A93" s="14" t="n">
         <v>92</v>
       </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F93" s="3" t="n">
-        <v>0.09042218021424064</v>
+      <c r="B93" s="15" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C93" s="14" t="inlineStr"/>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E93" s="14" t="inlineStr">
+        <is>
+          <t>Long Treasury</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="n">
+        <v>-0.05017692267545248</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.03127842698201666</v>
+        <v>-0.007953497019903888</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>-0.04107480232314042</v>
-      </c>
-      <c r="I93" s="3" t="n">
-        <v>0.01235831809872034</v>
+        <v>-0.007470455509019036</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>-0.06349799056677685</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.03121063680895741</v>
-      </c>
-      <c r="K93" s="3" t="n">
-        <v>0.01021599532983064</v>
+        <v>-0.03344367985700669</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>-0.0004866772113394369</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.01438131852484703</v>
+        <v>-0.004483761512360518</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4705,86 +4702,86 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Mid Growth</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.09919778407246649</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.02525552011489984</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-0.01753115639561731</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0.02602980623746309</v>
+      </c>
+      <c r="J94" s="5" t="n">
+        <v>-0.03170362757142986</v>
+      </c>
+      <c r="K94" s="5" t="n">
+        <v>-0.007862197126724313</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>-0.01174711661683048</v>
+      </c>
+    </row>
+    <row r="95" ht="21" customHeight="1">
+      <c r="A95" t="n">
+        <v>94</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
           <t>INDA</t>
         </is>
       </c>
-      <c r="C94" t="inlineStr">
+      <c r="C95" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D94" s="6" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="E94" t="inlineStr">
+      <c r="E95" t="inlineStr">
         <is>
           <t>India Equity</t>
         </is>
       </c>
-      <c r="F94" s="3" t="n">
-        <v>0.03575883575883565</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.04155444401692954</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>-0.04193920738745671</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>-0.04687201071360247</v>
-      </c>
-      <c r="J94" s="3" t="n">
-        <v>0.02594728171334437</v>
-      </c>
-      <c r="K94" s="3" t="n">
-        <v>0.0004016064257028606</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>0.002414486921529013</v>
-      </c>
-    </row>
-    <row r="95" ht="21" customHeight="1">
-      <c r="A95" s="14" t="n">
-        <v>94</v>
-      </c>
-      <c r="B95" s="15" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="C95" s="14" t="inlineStr"/>
-      <c r="D95" s="22" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E95" s="14" t="inlineStr">
-        <is>
-          <t>Long Treasury</t>
-        </is>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>-0.1112193010927188</v>
+      <c r="F95" s="3" t="n">
+        <v>0.03555093555093558</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05138568129330245</v>
+        <v>-0.04174682570219301</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>-0.05023094688221708</v>
+        <v>-0.03501346671796846</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.09546355428319742</v>
-      </c>
-      <c r="J95" s="5" t="n">
-        <v>-0.04209421641791045</v>
+        <v>-0.008164078056551061</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0.03706017072662915</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.001215805471124543</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>-0.004483761512360518</v>
+        <v>-0.006977671451355527</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0.002213279678068503</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4801,7 +4798,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D96" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -4812,25 +4809,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.1240497581202488</v>
+        <v>-0.1076586848779814</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1603179860881087</v>
+        <v>-0.1446055878629385</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>-0.1722424643921829</v>
+        <v>-0.1527839929741026</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.1219296304492146</v>
+        <v>0.1286060339132351</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.09385113268608425</v>
+        <v>0.1296010579678202</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.01440576230492208</v>
+        <v>0.00965327029156815</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.0115032170013647</v>
+        <v>-0.0007798791187365595</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -669,25 +669,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.353901949752638</v>
+        <v>2.300787124919663</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.538175919849462</v>
+        <v>1.497979524308435</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.267982542779668</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.355070273537857</v>
+        <v>0.3336103974610851</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1640796159045355</v>
+        <v>-0.1773178576422878</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.1191337993010484</v>
+        <v>0.1014103844233649</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-0.008459581997124821</v>
+        <v>-0.02416233550812785</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -715,25 +715,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.600386125449507</v>
+        <v>1.597395113112897</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.210803632971448</v>
+        <v>1.208260725641138</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>1.223416453329785</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4603144780820749</v>
+        <v>0.4586347972929306</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.2047601717309496</v>
+        <v>-0.2056748713263822</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.005672720618509541</v>
+        <v>-0.006816414291596185</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-0.0205488711639854</v>
+        <v>-0.02167545401288817</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -761,25 +761,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.354437026254124</v>
+        <v>1.356092655109795</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.037664746536866</v>
+        <v>1.039097479561775</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>1.214050101158964</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3421633902242009</v>
+        <v>0.3431070988579523</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2079476948570449</v>
+        <v>-0.2073907830799913</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.07966637906241025</v>
+        <v>-0.07901926948518845</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-0.02897891063571534</v>
+        <v>-0.028296161432256</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -807,25 +807,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.776212184003315</v>
+        <v>1.756319933692499</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.200722733245729</v>
+        <v>1.184954007884363</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>1.14388961892247</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5550139275766015</v>
+        <v>0.5438718662952648</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.182849475481825</v>
+        <v>-0.1887045620883142</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.02650934722647857</v>
+        <v>0.01915415262028808</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.01586602027324813</v>
+        <v>-0.02291758483913597</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -849,25 +849,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.417356187478763</v>
+        <v>1.420643679068192</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.047624058656807</v>
+        <v>1.050408754943486</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.079117146540706</v>
+        <v>1.079117016617151</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4951180244500555</v>
+        <v>0.4971514256313312</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1732051320391348</v>
+        <v>-0.1720806685294378</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.01514733690513714</v>
+        <v>-0.0138079104947999</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-0.02162257357545405</v>
+        <v>-0.02029195366311831</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -895,25 +895,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.38584928963071</v>
+        <v>1.386923273605417</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.9990883426083936</v>
+        <v>0.99998802233054</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.023829534967409</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4554654566827183</v>
+        <v>0.4561204816407216</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.176855821518156</v>
+        <v>-0.1764853695926466</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.01222493887530574</v>
+        <v>-0.01178039564347633</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-0.02071397091229632</v>
+        <v>-0.02027324812692821</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -941,25 +941,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.352186219792882</v>
+        <v>1.350117681839892</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8861081994192328</v>
+        <v>0.884449535508564</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.8848642014862311</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3957448984810517</v>
+        <v>0.3945174653505856</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1366476329067873</v>
-      </c>
-      <c r="K8" s="3" t="n">
-        <v>0.0006599934000659502</v>
+        <v>-0.1374068742980972</v>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>-0.0002199978000220204</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-0.01942044086736239</v>
+        <v>-0.02028277311679205</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -987,25 +987,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.280652818412138</v>
+        <v>1.261920134372468</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9700777592898071</v>
+        <v>0.9538960573225379</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7422891854428675</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5540749053163136</v>
+        <v>0.5413101416748489</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.03435720287554855</v>
+        <v>0.02586126412099699</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.1307409675443969</v>
+        <v>0.1214533578281281</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.02554845876145517</v>
+        <v>0.01712487272054064</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1033,25 +1033,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.396875</v>
+        <v>1.4609375</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.83273596176822</v>
+        <v>0.881720430107527</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.6666666666666667</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.2272000000000001</v>
+        <v>0.26</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.1854714064914993</v>
+        <v>0.2171561051004638</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.09964157706093202</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>-0.008403361344537896</v>
+        <v>0.1290322580645162</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.01809954751131215</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1075,25 +1075,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8432890662035253</v>
+        <v>0.8471397101718916</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.819642671327657</v>
+        <v>0.8234440753722125</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.6470142053043144</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.3191074158348906</v>
+        <v>0.3218631548295685</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2751233570514127</v>
+        <v>0.2777872092258979</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.1048129794311317</v>
+        <v>0.1071210372683458</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.001538461538461489</v>
+        <v>0.003630769230769326</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1121,25 +1121,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.334673450738295</v>
+        <v>1.324444870450285</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7321448463437814</v>
+        <v>0.7245560408833487</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.6429763821836962</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.06004814931051561</v>
+        <v>0.05540390769250703</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.07689971654717676</v>
+        <v>0.07218164549987249</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.05427251732101612</v>
+        <v>0.04965357967667461</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.002839667977282745</v>
+        <v>-0.007208387942332806</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1167,25 +1167,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.465837040025303</v>
+        <v>1.432336021841548</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.8817001714624197</v>
+        <v>0.8561352737675212</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6361534524735142</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.05240358609946738</v>
+        <v>0.03810556433148959</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.02220632227220631</v>
+        <v>-0.03549068910010666</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.1500756048387097</v>
+        <v>0.1344506048387097</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.01712255007538233</v>
+        <v>-0.03047598535429674</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1213,25 +1213,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6380524833407857</v>
+        <v>0.6387781302790807</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6988296966831267</v>
+        <v>0.6995822675443293</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.513578437849203</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1153006032868733</v>
+        <v>0.1157946744331182</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.003600882797072824</v>
+        <v>-0.003159484260657486</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.1223929029387905</v>
+        <v>0.122890115929134</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-0.0006524069155133816</v>
+        <v>-0.0002097022228436662</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1259,25 +1259,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.05330936158365</v>
+        <v>1.043266682823102</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.6820713441787007</v>
+        <v>0.6738444896359364</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5134185825451323</v>
+        <v>0.5134186814955273</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.1915756420332992</v>
+        <v>0.185747678836071</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.2325271902955466</v>
+        <v>0.2264989342191062</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.1114382785956964</v>
+        <v>0.1060022650056625</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.008425811755035095</v>
+        <v>0.003493629264282871</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1305,25 +1305,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8942136794962612</v>
+        <v>0.8825173924972103</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6185147609978248</v>
+        <v>0.6085208445977146</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.4838467375063418</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.07902264354903443</v>
+        <v>0.07235995356108105</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.05231343702771662</v>
+        <v>-0.05816516017049089</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.09075601953190771</v>
+        <v>0.08402087893584764</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.006441717791411117</v>
+        <v>-0.01257668711656457</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1351,25 +1351,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.8701286399901516</v>
+        <v>0.8559891874792827</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.5996559470103948</v>
+        <v>0.5875614531810283</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.4727698538531835</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.07624842420499101</v>
+        <v>0.06811124948955327</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.123679701774614</v>
+        <v>-0.130305283018658</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.08615473274744279</v>
+        <v>0.07794265955914126</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.01283226397800186</v>
+        <v>-0.02029592772030919</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1393,25 +1393,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.068173790180148</v>
+        <v>1.052278346873896</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.6178502348715116</v>
+        <v>0.6054158607350097</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.4495717048908539</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.2159882163899305</v>
+        <v>-0.2220139260846278</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.1388439476393587</v>
+        <v>-0.1454625680247095</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.1160884483415936</v>
+        <v>0.1075104841784216</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.02627640113088314</v>
+        <v>-0.03376018626309663</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1439,25 +1439,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.6309321481562282</v>
+        <v>0.6180632793543515</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4588567852206087</v>
+        <v>0.4473456769314283</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.4269075867037</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.4092042753952034</v>
+        <v>0.3980849501948225</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.06733068520483232</v>
+        <v>-0.07468991168228212</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.02239051695752381</v>
+        <v>0.01432334540665137</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-0.01898834160058127</v>
+        <v>-0.02672901330131738</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1485,25 +1485,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.7079859756954376</v>
+        <v>0.697155074829434</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4727363503727076</v>
+        <v>0.4633972447596466</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.386085692206307</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.1352829281877919</v>
+        <v>0.1280837257206511</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.06638354571743932</v>
+        <v>0.05962125689706399</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.06251464729318013</v>
+        <v>0.05577689243027883</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.009687656589276727</v>
+        <v>0.00328489505038676</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1527,25 +1527,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.6492043098746298</v>
+        <v>0.6432115437877206</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4123872842826606</v>
+        <v>0.4072552806936363</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.3638216297520602</v>
+        <v>0.3638219485857872</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.3442136515549445</v>
+        <v>0.3393290483087044</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.0686653308614521</v>
+        <v>-0.07204961455991621</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.03560997528645249</v>
+        <v>0.03184677600539221</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.01136729222520105</v>
+        <v>-0.0149597855227882</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1573,25 +1573,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.536899827050993</v>
+        <v>0.5407076596699492</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.5223132902024836</v>
+        <v>0.526085152027403</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.348452752913778</v>
+        <v>0.3484529021550118</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.2349373304657532</v>
+        <v>0.2379970189155445</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.2778323506124987</v>
+        <v>0.2809983160323506</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.1289333548491205</v>
+        <v>0.131730407186273</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.003970342023439377</v>
+        <v>0.006457785218847212</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1619,25 +1619,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.4960337236401688</v>
+        <v>0.5065976512964794</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4701617845844455</v>
+        <v>0.4805430229816876</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.3452625101176254</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.1515699812865627</v>
+        <v>0.1597015506364099</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.1146318705944338</v>
+        <v>0.1225026092404364</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.09284379333212756</v>
+        <v>0.100560680050642</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.006105344951989888</v>
+        <v>0.01320974635066885</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1661,25 +1661,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.4809471719837373</v>
+        <v>0.5016202924048301</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.4669445359905338</v>
+        <v>0.4874221881426859</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.3440786230776209</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2165187186414512</v>
+        <v>0.2335005789270552</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.04648074369189903</v>
+        <v>0.06108897742363872</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.09141274238227148</v>
+        <v>0.1066481994459834</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.007028753993610248</v>
+        <v>0.02108626198083074</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1707,25 +1707,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.6138774039728738</v>
+        <v>0.6069429446927488</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.3716007846874529</v>
+        <v>0.3657074672573621</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.3421341975369978</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.319120912864115</v>
+        <v>0.3134530841817691</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>-0.04168939169404973</v>
+        <v>-0.04580693717406159</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.02195502298095864</v>
+        <v>0.01756401838476696</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.008954154727793706</v>
+        <v>-0.01321235275389998</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1749,25 +1749,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.4809934972297745</v>
+        <v>0.4904336479345273</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.4673491164348103</v>
+        <v>0.4767026830468319</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3411917685821284</v>
+        <v>0.341191885313197</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.1537002733844928</v>
+        <v>0.1610543951520249</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.1177339652557663</v>
+        <v>0.1248588241760846</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.09406361626126891</v>
+        <v>0.1010375914271135</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.005628517823639712</v>
+        <v>0.01203877423389632</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1795,25 +1795,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5061033903646983</v>
+        <v>0.520176259145132</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4655004920057189</v>
+        <v>0.4791937087951668</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3407213949960981</v>
+        <v>0.3407212376160893</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.2089004230216991</v>
+        <v>0.2201960673513983</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.1337500552851598</v>
+        <v>0.1443436253555408</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.09306862520082615</v>
+        <v>0.1032820748221253</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.00814987298899239</v>
+        <v>0.01756985605419126</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1841,25 +1841,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.5897626881980509</v>
+        <v>0.5910833633284334</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.272466968509441</v>
+        <v>0.2735240542569046</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.3332493989886043</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.01704269987552021</v>
+        <v>0.01788759516098271</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.2967723090404557</v>
+        <v>-0.2961881115817147</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.04558969276511404</v>
+        <v>-0.04479682854311207</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.01553874463299931</v>
+        <v>-0.01472091596810465</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1887,25 +1887,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.6129405591430226</v>
+        <v>0.6064324308562452</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3803287146180174</v>
+        <v>0.3747592641902024</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3305417626294094</v>
+        <v>0.3305418609560147</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3237479163198442</v>
+        <v>0.3184066647715906</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>-0.05059632654380386</v>
+        <v>-0.0544271192334449</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.03741855640082981</v>
+        <v>0.0332326283987916</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.008867714563917106</v>
+        <v>-0.01286687995548752</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1929,25 +1929,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.6065719765764286</v>
+        <v>0.6006506189814074</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3761731944174955</v>
+        <v>0.3711010198024536</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3272958753998194</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3226437229339656</v>
+        <v>0.3177688424004514</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>-0.04967718572015567</v>
+        <v>-0.05317979954393792</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.03682473510508943</v>
+        <v>0.03300330033003296</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.00921238277035441</v>
+        <v>-0.01286413810274711</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1971,25 +1971,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.817885685569196</v>
+        <v>1.779060574600513</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6816484428486422</v>
+        <v>0.6584785223162826</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3203370504868808</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>-0.09287604506689651</v>
+        <v>-0.1053744896961416</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.05000135474177791</v>
+        <v>0.03553433099986814</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.2736508774244621</v>
+        <v>0.2561023881778599</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.01449719244512504</v>
+        <v>-0.02807554874936191</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2013,25 +2013,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.4737151367080119</v>
+        <v>0.4618690627368605</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.1699595243783207</v>
+        <v>0.1605553292969812</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3149605832927664</v>
+        <v>0.314960692998794</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>-0.08595303073298388</v>
+        <v>-0.09330026312451234</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-0.1692678002950539</v>
+        <v>-0.1759453373709139</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.1102702702702704</v>
+        <v>-0.1174220374220375</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>-0.01136573646276107</v>
+        <v>-0.01931251155054525</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2059,25 +2059,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.5291849540601947</v>
+        <v>0.519350967217364</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.3248013588784369</v>
+        <v>0.3162817359917589</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.312409180134178</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1025558639761692</v>
+        <v>0.09546547256796223</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.1940168890248114</v>
+        <v>-0.1992000601564846</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.009442313366774924</v>
+        <v>0.002950722927117289</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>-0.008693132425383832</v>
+        <v>-0.01506809620399874</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2105,25 +2105,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.4869403234132987</v>
+        <v>0.4750860331399867</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.3503766485528657</v>
+        <v>0.3396112004137897</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.2888256851959499</v>
+        <v>0.2888258002583401</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.2656715470221513</v>
+        <v>0.25558127125733</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.1372933727881549</v>
+        <v>0.1282265625371575</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.0477573996731433</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>0.002084056964223757</v>
+        <v>0.03940439440711829</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>-0.005904828065300349</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2151,25 +2151,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.412234878753597</v>
+        <v>0.4005106646658314</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2522923769962342</v>
+        <v>0.2418959874513598</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.2789134350732609</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.06297633373445644</v>
+        <v>0.05415162454873634</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1199911445649768</v>
+        <v>-0.1272968784591543</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.02081537135115163</v>
+        <v>-0.02894445128710421</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.01168572849328686</v>
+        <v>-0.01989060169070112</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2193,25 +2193,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.3670788037805752</v>
+        <v>0.3582198677456889</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2579557699259007</v>
+        <v>0.2498040683240244</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.2664780034187713</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.1296223373511027</v>
+        <v>0.1223022515125975</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.006486799426306478</v>
+        <v>-0.01292488202207143</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.006729081334113429</v>
+        <v>-0.01316559391457006</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.00614754098360637</v>
+        <v>-0.01258782201405151</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2239,25 +2239,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.5344883763204815</v>
+        <v>0.5269305116670255</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.1711729921781782</v>
+        <v>0.1654045764004772</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.2627292874018476</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>-0.106860699894029</v>
+        <v>-0.1112597074401596</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.09107216557028208</v>
+        <v>-0.09554893688923527</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.0725066695903227</v>
+        <v>-0.07707488214011626</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.01064244503352563</v>
+        <v>-0.01551535942616555</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2281,25 +2281,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.3509333344939944</v>
+        <v>0.3463524877987312</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2802593888320826</v>
+        <v>0.2759181886849948</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.2624999336849052</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1392134514308661</v>
+        <v>0.135350520491982</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.04741184110988006</v>
+        <v>0.04386019799884155</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.01406689590497034</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>0.001852995676343339</v>
+        <v>0.01062832135042191</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>-0.001544163063619597</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2323,25 +2323,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.4818687268393889</v>
+        <v>0.4758839281890643</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2647510259325232</v>
+        <v>0.2596432776222755</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2583445931911303</v>
+        <v>0.2583446763051391</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2307341708503152</v>
+        <v>0.2257637200268388</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.05187802218640447</v>
+        <v>-0.055707113615729</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.005091159270725898</v>
+        <v>0.001031991744065985</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.006798558705554458</v>
+        <v>-0.01080970834183159</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2365,25 +2365,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.346373646620844</v>
+        <v>0.3420840109582883</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2689784205774226</v>
+        <v>0.2649353712340365</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.2571188091701571</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1023690436208191</v>
+        <v>0.09885682279365016</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.04339958587866222</v>
+        <v>0.04007524565177611</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.00943396226415083</v>
+        <v>0.006217838765008477</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.003175947491001474</v>
+        <v>-0.006351894982002948</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2411,25 +2411,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1.022535988850903</v>
+        <v>1.016993845363729</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.4236230399707883</v>
+        <v>0.4197219028502881</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.25697697937479</v>
+        <v>0.2569768624668831</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>-0.002964675411736506</v>
+        <v>-0.005696746861199253</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.120229710251354</v>
+        <v>-0.1226404526106584</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.1325768596644361</v>
+        <v>0.129473377945883</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.01142808769999148</v>
+        <v>-0.01413696774739692</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2453,25 +2453,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.3636039406120863</v>
+        <v>0.3545519330037821</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.1759066855188769</v>
+        <v>0.1681005559450839</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2476797102112518</v>
       </c>
-      <c r="I42" s="3" t="n">
-        <v>0.001199706983114002</v>
+      <c r="I42" s="5" t="n">
+        <v>-0.005446649176095275</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.04508531200550159</v>
+        <v>-0.05142441006336662</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.05752519986096627</v>
+        <v>-0.06378171706638858</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.008592321755027554</v>
+        <v>-0.01517367458866559</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2499,25 +2499,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3770501210087085</v>
+        <v>0.3715837981169965</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2282948088532823</v>
+        <v>0.2234189062625505</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2469716995752658</v>
+        <v>0.2469716209535007</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2058425027031696</v>
+        <v>0.2010558036747441</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.08723609943008914</v>
+        <v>-0.09085939688912337</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.01497779839618263</v>
+        <v>-0.01888793160580549</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>-0.01032094819549878</v>
+        <v>-0.01424956718604353</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2541,25 +2541,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4744220670326458</v>
+        <v>0.4663496086551335</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1472230723318302</v>
+        <v>0.1409419145709179</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2465058885527058</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.07426699019595595</v>
+        <v>-0.07933546834924532</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.007406012020344854</v>
+        <v>-0.01284056052394233</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.07964889466840064</v>
+        <v>-0.08468790637191159</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-0.008189183271294032</v>
+        <v>-0.01361944383621627</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2583,25 +2583,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2924940073855462</v>
+        <v>0.287682408115262</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2966474612075383</v>
+        <v>0.2918202170828688</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2461480182739115</v>
+        <v>0.2461479300172775</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1236417065842315</v>
+        <v>0.1194586189022169</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.08736823187717757</v>
+        <v>0.08332018290398069</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.04052443384982118</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>0.0008598452278589797</v>
+        <v>0.03665077473182343</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>-0.002866150759530006</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2625,25 +2625,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4799099759185059</v>
+        <v>0.4719534706716324</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2712917951327229</v>
+        <v>0.2644568930083535</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.2450037100389941</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.09662101090697583</v>
+        <v>0.09072519902037923</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.008321745387405155</v>
+        <v>0.002900660734784788</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.02111486486486491</v>
+        <v>0.015625</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.005211190345584149</v>
+        <v>-0.01055951727921001</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2671,25 +2671,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3605392882078162</v>
+        <v>0.3526044166267333</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2207178833146417</v>
+        <v>0.2135983504319205</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2352179699994568</v>
+        <v>0.2352178468928858</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1293178597449449</v>
+        <v>0.1227315066208805</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-0.02132721665428805</v>
+        <v>-0.02703498483346256</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.01173888903577192</v>
+        <v>-0.01750257779657882</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.008488288814026856</v>
+        <v>-0.01427093556858272</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2713,25 +2713,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4100975931095658</v>
+        <v>0.4032084931500621</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2528163307573226</v>
+        <v>0.2466956360084911</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2338550176542991</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1845647142652613</v>
+        <v>0.1787774660882906</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.04619103250996581</v>
+        <v>-0.05085091233063799</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.01536753737815255</v>
+        <v>0.01040691018836504</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.008401653228538586</v>
+        <v>-0.01324615488854264</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2755,25 +2755,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4092173979644307</v>
+        <v>0.4025958624225974</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2521976141941051</v>
+        <v>0.2463138726083414</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2332428059717051</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1843952519040273</v>
+        <v>0.178829975595092</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.04630217903671596</v>
+        <v>-0.0507833499524305</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.01536989158227042</v>
+        <v>0.01059894010598939</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.008273341146269209</v>
+        <v>-0.01293319939728776</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2797,25 +2797,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.2979905308787409</v>
+        <v>0.2892445684211959</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.1570147655599017</v>
+        <v>0.1492187089156662</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2204493461181274</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-0.00503693200145372</v>
+        <v>-0.01174115794729691</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.0007049536965453296</v>
+        <v>-0.007438282446689537</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.05197641406420617</v>
+        <v>-0.05836427167503822</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>-0.008507965511334481</v>
+        <v>-0.01518871695312052</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2843,25 +2843,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4289625946653275</v>
+        <v>0.4225001160457833</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1253230399768213</v>
+        <v>0.1202338438843067</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>0.2155714506840796</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>-0.08853697380084125</v>
+        <v>-0.09265892658974084</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.04047664682178675</v>
+        <v>-0.04481602522798356</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.07424360835101029</v>
+        <v>-0.07843027799486424</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>-0.009259812414122659</v>
+        <v>-0.01374036680805291</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2885,25 +2885,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4031942032963434</v>
+        <v>0.3973529310194592</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2299422550038301</v>
+        <v>0.2248224566528947</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0.2152972504185957</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1682431344983688</v>
+        <v>0.1633801669491501</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.0305127188784593</v>
+        <v>-0.03454833873211138</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>0.01205055354168705</v>
+        <v>0.00783775840109735</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-0.005679083646164207</v>
+        <v>-0.009818076812012633</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2931,25 +2931,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.2133421671313263</v>
+        <v>0.2108917324299577</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2835954461277141</v>
+        <v>0.2810031297070739</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2144803021743404</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1199478476303635</v>
+        <v>0.1176860296997755</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.1830972879432742</v>
+        <v>0.1807079350237055</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.05690923420464999</v>
+        <v>0.05477472743990552</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.005906988373546751</v>
+        <v>0.00387548443555441</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2977,25 +2977,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.6612680781587468</v>
+        <v>0.6554887971778249</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.235606319993418</v>
+        <v>0.231307846917983</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.21401161001921</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.0009102946044355908</v>
+        <v>-0.004385964912280715</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.1488896721889319</v>
+        <v>-0.15185054635178</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.01778789411566351</v>
+        <v>0.01424717585567348</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.01444897959183666</v>
+        <v>-0.01787755102040811</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3023,25 +3023,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1761995538024865</v>
+        <v>0.1650733418070576</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2138008064055681</v>
+        <v>0.2023189068855153</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.2006786355255077</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1190068832659232</v>
+        <v>0.1084216830188134</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-0.01280252878975752</v>
+        <v>-0.02214088324715158</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.01092896174863389</v>
+        <v>0.001366120218579292</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.01745108408249618</v>
+        <v>0.007826546800634659</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3069,25 +3069,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2534705356656861</v>
+        <v>0.2513173753903617</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1606046414647759</v>
+        <v>0.1586111379734456</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.1992505676869119</v>
+        <v>0.1992507080016339</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.02132934302830924</v>
+        <v>0.01957494537247295</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.1080874254424551</v>
+        <v>-0.1096195162814151</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.0322250639386189</v>
+        <v>-0.03388746803069065</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.006432978863069372</v>
+        <v>-0.008139687541026674</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3111,25 +3111,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.2798028818161704</v>
+        <v>0.2723567382379459</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1905044405989609</v>
+        <v>0.1835778435338309</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.1885841615312283</v>
+        <v>0.1885842859128997</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.09844652254175346</v>
+        <v>0.09205542289449764</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.02950162986196181</v>
-      </c>
-      <c r="K57" s="3" t="n">
-        <v>0.001615602100282665</v>
+        <v>-0.03514828781368373</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>-0.004212105475737027</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.008736866148926437</v>
+        <v>-0.01450433988122424</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3153,25 +3153,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3097304869732127</v>
+        <v>0.3045622475937049</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.1985744764304729</v>
+        <v>0.1938452140565832</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.1883350528676975</v>
+        <v>0.1883352792907864</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1296839708824455</v>
+        <v>0.1252264191205568</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.009019529696495221</v>
+        <v>0.005038010220821398</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.008616613250669758</v>
+        <v>0.004636683654704932</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.003710719568207232</v>
+        <v>-0.007642006383475564</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3195,25 +3195,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3093011824318097</v>
+        <v>0.3046968261167993</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1982280323615775</v>
+        <v>0.1940142701107708</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.1880771719749448</v>
+        <v>0.1880772956866044</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.12928916328079</v>
+        <v>0.1253177185120797</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.008786526758499891</v>
+        <v>0.005238861461862143</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.00854394026421601</v>
+        <v>0.004997128087306235</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.003603399111918093</v>
+        <v>-0.007107491949098432</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3237,25 +3237,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3080751778852353</v>
+        <v>0.3031966720792949</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1977630007876094</v>
+        <v>0.193295782895514</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.1876059580013714</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1291738760983436</v>
+        <v>0.1249624705537775</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.008621469302541707</v>
+        <v>0.004859680141366063</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.008552536064513561</v>
+        <v>0.004791003999102594</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>-0.003780718336483857</v>
+        <v>-0.007496251874062998</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3283,25 +3283,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3237342228853832</v>
+        <v>0.3191938503311289</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1968200077425082</v>
+        <v>0.1927147054395155</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1836518298209084</v>
+        <v>0.1836517157529616</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1425069857027834</v>
+        <v>0.1385880963059136</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.005139563836355832</v>
+        <v>0.001691855569898593</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.01112504335298681</v>
+        <v>0.007656804418002761</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.002579083109637392</v>
+        <v>-0.006000315806095169</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3329,25 +3329,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.2247139140055816</v>
+        <v>0.2129395604468827</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1339401663715465</v>
+        <v>0.1230385082123762</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.1827460513610628</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.111529685238982</v>
+        <v>0.1008434806034941</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.07010530438880958</v>
+        <v>0.05981735219456707</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.04126488939307993</v>
+        <v>-0.05048213272830404</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.002949417490045736</v>
+        <v>-0.01253502433269438</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3371,25 +3371,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.2975400033228202</v>
+        <v>0.2883846989274874</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2694188531781825</v>
+        <v>0.2604619686303009</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1819575099459281</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1281540838541464</v>
+        <v>0.1201939485087449</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.1120407345720607</v>
+        <v>0.1041942933070943</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.07399702823179788</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>0.002496532593620149</v>
+        <v>0.0664190193164933</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>-0.004576976421636569</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3413,25 +3413,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.4058207427542615</v>
+        <v>0.3975295326069559</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2155463166887452</v>
+        <v>0.2083773017148274</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.176116734332197</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1065099825819016</v>
+        <v>0.09998403904111708</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>-0.001265770189730175</v>
+        <v>-0.007156076918624299</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.03352522858110385</v>
+        <v>0.02742973247544866</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.008592200925313875</v>
+        <v>0.002643754130865705</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3455,25 +3455,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.5234824577687023</v>
+        <v>0.5127157972897716</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.2606758832565284</v>
+        <v>0.2517665130568356</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1703533026113673</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>-0.1443911592994163</v>
+        <v>-0.1504378648874063</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>-0.02783700544894585</v>
+        <v>-0.03470741530443033</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.07717548234676452</v>
+        <v>0.06956293476834219</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.01959144666109192</v>
+        <v>-0.02652012901684386</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3497,25 +3497,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2446191433228566</v>
+        <v>0.2378453185775824</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1784350410106414</v>
+        <v>0.1720214224476291</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.1701350640467429</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.09083775311018116</v>
+        <v>0.08490088173491883</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.04502373651806613</v>
+        <v>0.03933620737808674</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.007093178573073455</v>
+        <v>0.001612086039334937</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>-0.003372988741510485</v>
+        <v>-0.008797119285290922</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3539,25 +3539,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.5209480761195733</v>
+        <v>0.5102746230105977</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.2589052724243093</v>
+        <v>0.2500707391454713</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.1686421228031565</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>-0.1446575810654932</v>
+        <v>-0.1506600589567223</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-0.02798883359631021</v>
+        <v>-0.03481004976332069</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.07723763148691187</v>
+        <v>0.06967797476527404</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.01958767934968908</v>
+        <v>-0.02646785172126731</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3581,25 +3581,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3279950879387308</v>
+        <v>0.3229421365770231</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.167971337763887</v>
+        <v>0.1635272842426088</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1534631888726838</v>
+        <v>0.1534630738531815</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.160892315358294</v>
+        <v>0.1564753123678975</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>-0.02539683075159926</v>
+        <v>-0.02910503439466616</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.0125779036827196</v>
+        <v>0.008725212464589127</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.006006674082313701</v>
+        <v>-0.009788654060066793</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3623,25 +3623,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3067974276727434</v>
+        <v>0.3008957252751554</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1657311032387989</v>
+        <v>0.1604667234330355</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1469767501807657</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1589445990163998</v>
+        <v>0.1537107947224814</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.0104421032965667</v>
+        <v>0.005879000374538812</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.01635111876075723</v>
+        <v>0.01176133103843968</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.0064498037016264</v>
+        <v>-0.0109366236679751</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3665,25 +3665,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.3050089130062659</v>
+        <v>0.3011378084154885</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.151592419918815</v>
+        <v>0.1481764013314915</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1441034560927599</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1473908628432798</v>
+        <v>0.1439873075171045</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>-0.02546424596414776</v>
+        <v>-0.02835505367720337</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0.006545705098759846</v>
+        <v>0.003559944878272825</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.006686310063463208</v>
+        <v>-0.009632819582955476</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3711,25 +3711,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.09618769627687707</v>
+        <v>0.09253297588920684</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.11366104586611</v>
+        <v>0.1099480688430101</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1387236407720365</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.07439276114201543</v>
+        <v>0.07081070567665337</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.118345873049853</v>
+        <v>0.1146172766821103</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.02200937436315475</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>0.0002084201750729431</v>
+        <v>-0.02527002241695531</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>-0.003126302626094146</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3757,25 +3757,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2052538189677442</v>
+        <v>0.1962967624579151</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1189183592893026</v>
+        <v>0.1106029199882075</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0.1369798511045845</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1050670295172078</v>
+        <v>0.09685452881838241</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.03569397581964528</v>
+        <v>0.02799703321526414</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.01588549858446053</v>
+        <v>-0.02319911921988049</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.001914180890094097</v>
+        <v>-0.00933163183920882</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3803,25 +3803,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.07332758513106441</v>
+        <v>0.07016276074356775</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1569364667986335</v>
+        <v>0.1535251124314936</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1351281656658454</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1020076592781709</v>
+        <v>0.09875826853893477</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.2174358974358974</v>
+        <v>0.213846153846154</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.01921219276591168</v>
+        <v>0.01620693356230563</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.0004210526315789886</v>
+        <v>-0.003368421052631465</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3845,25 +3845,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.2703272679860584</v>
+        <v>0.2679755359256091</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1068883258916933</v>
+        <v>0.1048391651526159</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.1343812324743165</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>-0.03006874738320242</v>
+        <v>-0.03186436216743582</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-0.0142134576254529</v>
+        <v>-0.01603842499794506</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.02423603793466822</v>
+        <v>-0.02604245069998501</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.004912496162112534</v>
+        <v>-0.006754682222904429</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3891,25 +3891,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1825979653310801</v>
+        <v>0.1731665832115519</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.03593248165283658</v>
+        <v>0.02767088419166641</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0.09508073014295459</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.01507334234025204</v>
+        <v>0.00697809723837084</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.03592209909388822</v>
+        <v>0.02766058443398545</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.05401268314017049</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>0.004878048780487809</v>
+        <v>-0.06155696479335226</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-0.003135888501742068</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3933,25 +3933,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2441708526274009</v>
+        <v>0.2392064808588772</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.09810264723418549</v>
+        <v>0.09372110287525892</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0.09065402182401017</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.08788274192944212</v>
+        <v>0.08354197606107783</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>-0.04990798990871492</v>
+        <v>-0.05369895635229993</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.006829503454925279</v>
+        <v>0.002812148481439847</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.008544979824353205</v>
+        <v>-0.01250098900229446</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3975,25 +3975,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2411643503836511</v>
+        <v>0.2356589392681003</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.09686821610525076</v>
+        <v>0.09200285684209297</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0.08902958173682984</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.08722860495252083</v>
+        <v>0.08240600394484598</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.05022047382540462</v>
+        <v>-0.05443339434564676</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.007197815835194854</v>
+        <v>0.002730206006453129</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.007904816233395784</v>
+        <v>-0.01230543557982222</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4017,25 +4017,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1452077816755308</v>
+        <v>0.136989436319978</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.08563592050123026</v>
+        <v>0.07784501329854265</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0.08386175351447944</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1329571243530894</v>
+        <v>0.1248266234606876</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.121444058445584</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>0.001636894171233472</v>
+        <v>0.1133961793846914</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>-0.005551206319834856</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.001560726447219052</v>
+        <v>-0.008725879682179416</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4059,25 +4059,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.115001136494693</v>
+        <v>0.118422080338382</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.03300663335308673</v>
+        <v>0.03617611322884562</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.08152405606662572</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.08776995297781587</v>
+        <v>-0.08497104086752816</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.02868897061449949</v>
+        <v>-0.02570878572377222</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.0448602344454464</v>
+        <v>-0.04192966636609552</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.00331517878285581</v>
+        <v>0.006393559081221856</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4101,25 +4101,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.07432393670833282</v>
+        <v>0.06706150513027365</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.09160231642795336</v>
+        <v>0.08422297606757478</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.07964303697058406</v>
+        <v>0.07964282737731065</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.009783115456913571</v>
+        <v>-0.0164768892685101</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.05579044383313803</v>
+        <v>0.04865339887482545</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.01107706811218478</v>
+        <v>0.004242281404666537</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.009649329253942129</v>
+        <v>0.002824193927982943</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4143,25 +4143,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.1297134193958533</v>
+        <v>0.1222655370955372</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.08417294394131658</v>
+        <v>0.07702537769048878</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0.07928250387496072</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.135310300393682</v>
+        <v>0.1278256037568049</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.1240169407043166</v>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>0.00453119553851522</v>
+        <v>0.1166066971674038</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>-0.002091321017776315</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.001212961358516673</v>
+        <v>-0.007797608733321804</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4189,25 +4189,25 @@
         </is>
       </c>
       <c r="F82" s="5" t="n">
-        <v>-0.1430615164520744</v>
+        <v>-0.1410586552217454</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.06735566642908064</v>
+        <v>0.06985032074126885</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0.07875980042765507</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.02323197813460887</v>
+        <v>0.02562350529552448</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.01628775025449603</v>
+        <v>0.01866304716661005</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.01057152296002639</v>
+        <v>-0.008259002312520636</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.002678272514228253</v>
+        <v>0.005021760964178057</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4231,25 +4231,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1112489881408318</v>
+        <v>0.1049671962350045</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.05962845804102446</v>
+        <v>0.0536384724104928</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.07610091852498591</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>-0.04071292279390826</v>
+        <v>-0.04613568750394836</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-0.128993775129591</v>
+        <v>-0.1339174960163656</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.0153075424436403</v>
+        <v>-0.02087392151405509</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.01421008637503474</v>
+        <v>-0.0197826692672054</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4277,25 +4277,25 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.009127828623342715</v>
+        <v>-0.00807221196349539</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.06400194443331664</v>
+        <v>0.06513546923207381</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0.06437978603290229</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.02549162418062645</v>
+        <v>0.02658412235979601</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.01440922190201732</v>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>-0.0003549875754349507</v>
+        <v>0.01548991354466867</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0.0007099751508696794</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>0.001422475106685583</v>
+        <v>0.002489331436699826</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4323,25 +4323,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.09090726964345541</v>
+        <v>0.08747470148486958</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.1017442501356522</v>
+        <v>0.09827758313548052</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0.05789559726861548</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1517123323152914</v>
+        <v>0.1480884394421162</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.08802512106477978</v>
+        <v>0.08460162166182061</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0.04144894163493062</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>0.002215972044660397</v>
+        <v>0.03817199539456206</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>-0.0009375266342793731</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4369,25 +4369,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.159715704106179</v>
+        <v>0.1521425797363825</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.03950786301076548</v>
+        <v>0.03271994669026879</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.04970730724966965</v>
+        <v>0.04970741876310547</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.08968063029431672</v>
+        <v>0.08256497417927444</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.01798308912966862</v>
+        <v>-0.02439569704674427</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.009716464931188828</v>
+        <v>-0.01618305421986399</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.01129026917855835</v>
+        <v>-0.01774658146541719</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4415,25 +4415,25 @@
         </is>
       </c>
       <c r="F87" s="5" t="n">
-        <v>-0.009217790489280842</v>
+        <v>-0.008466628844466029</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.04402163446054064</v>
+        <v>0.04481315958143561</v>
       </c>
       <c r="H87" s="3" t="n">
         <v>0.04877078518591094</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.01617873651771951</v>
+        <v>0.01694915254237284</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.005718642775447869</v>
+        <v>0.006481128478840859</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.004528301886792541</v>
+        <v>-0.003773584905660377</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>0.001898974553740995</v>
+        <v>0.002658564375237482</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4461,25 +4461,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.09387368174368205</v>
+        <v>0.08371796317715163</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.01242404581255085</v>
+        <v>0.003024686480125993</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.0434944144559628</v>
+        <v>0.04349449760164292</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.03286725651430311</v>
+        <v>0.02327802058627682</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>-0.01193919261392085</v>
+        <v>-0.02111244128987988</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.0297753090126609</v>
+        <v>-0.0387829655206926</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-0.00927463655177696</v>
+        <v>-0.01847262321469623</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4503,25 +4503,25 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.07932232099056247</v>
+        <v>0.07741539109481943</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.0388679157243681</v>
+        <v>0.03703246004287619</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.03978564356511405</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01368688797374196</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>0.001174139140428299</v>
+        <v>0.01189592174057275</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.0005947197626466894</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.0008826125330980705</v>
+        <v>-0.00264783759929399</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.007141962160130411</v>
+        <v>-0.00889612830472386</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4545,25 +4545,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04439782948976956</v>
+        <v>0.04401404782778173</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.01994609068948727</v>
+        <v>0.01957139141396413</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.02157020866829207</v>
+        <v>0.02157030603994414</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.0007634727524090668</v>
+        <v>0.0003956317134283793</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.001447636577220024</v>
+        <v>0.001079637690677648</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>-0.001589825119236776</v>
+        <v>-0.001956707839060767</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.003052875809012034</v>
+        <v>-0.00341922090609359</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4591,25 +4591,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.03615943608408512</v>
+        <v>0.03635345526507638</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.008436781053551279</v>
+        <v>0.008625609212160823</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0.008908851450074806</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.009303598430488003</v>
+        <v>-0.009118092129286048</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.01205650669899572</v>
+        <v>-0.01187151587542101</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.0004679019277559204</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>-9.361542782237997e-05</v>
+        <v>-0.0002807411566535523</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>9.361542782260202e-05</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4633,25 +4633,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.0253626833916778</v>
+        <v>0.02347353571446331</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-0.002678627698448399</v>
+        <v>-0.004516111531669087</v>
       </c>
       <c r="H92" s="3" t="n">
         <v>0.003266172938441558</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.03285013429893591</v>
+        <v>-0.03463195237569527</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.01430140290715232</v>
+        <v>-0.01611747271863795</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.005925447101917669</v>
+        <v>-0.007756948933419494</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>-0.00506793185249077</v>
+        <v>-0.006901013586370519</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4675,25 +4675,25 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>-0.05017692267545248</v>
+        <v>-0.05376116070309234</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.007953497019903888</v>
+        <v>-0.01169715978442831</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>-0.007470455509019036</v>
+        <v>-0.007470546953594392</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-0.06349799056677685</v>
+        <v>-0.06703187926939391</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.03344367985700669</v>
+        <v>-0.03709106219716896</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.0004866772113394369</v>
+        <v>-0.004258425599221294</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.004483761512360518</v>
+        <v>-0.008240426563257297</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4717,25 +4717,25 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.09919778407246649</v>
+        <v>0.09270449814720139</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.02525552011489984</v>
+        <v>-0.03101368216018319</v>
       </c>
       <c r="H94" s="5" t="n">
         <v>-0.01753115639561731</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.02602980623746309</v>
+        <v>0.01996868354374715</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.03170362757142986</v>
+        <v>-0.03742369835445281</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.007862197126724313</v>
+        <v>-0.0137231077121005</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.01174711661683048</v>
+        <v>-0.01758507760216432</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4763,25 +4763,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.03555093555093558</v>
+        <v>0.03097713097713095</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.04174682570219301</v>
+        <v>-0.04597922277799138</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>-0.03501346671796846</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.008164078056551061</v>
+        <v>-0.01254480286738346</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.03706017072662915</v>
+        <v>0.03247970018738289</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.006977671451355527</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>0.002213279678068503</v>
+        <v>-0.01136363636363624</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>-0.002213279678068392</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4809,25 +4809,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.1076586848779814</v>
+        <v>-0.1236772997055375</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1446055878629385</v>
+        <v>-0.159960960724716</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>-0.1527839929741026</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.1286060339132351</v>
+        <v>0.1083461792556706</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1296010579678202</v>
-      </c>
-      <c r="K96" s="3" t="n">
-        <v>0.00965327029156815</v>
+        <v>0.1093233414150321</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>-0.00847123719464149</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.0007798791187365595</v>
+        <v>-0.01871709884967832</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,6 +204,9 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -669,25 +672,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.300787124919663</v>
+        <v>2.2949893799555</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.497979524308435</v>
+        <v>1.493591889583886</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.267982542779668</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3336103974610851</v>
+        <v>0.3312679461991839</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1773178576422878</v>
+        <v>-0.1787628769869015</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.1014103844233649</v>
+        <v>0.09947578632051912</v>
       </c>
       <c r="L2" s="5" t="n">
-        <v>-0.02416233550812785</v>
+        <v>-0.02587636846179364</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -715,25 +718,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.597395113112897</v>
+        <v>1.596079304650891</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.208260725641138</v>
+        <v>1.207141675130683</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.223416453329785</v>
+        <v>1.223416280781676</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4586347972929306</v>
+        <v>0.4578957377457071</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.2056748713263822</v>
+        <v>-0.2060773391483725</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.006816414291596185</v>
+        <v>-0.007319639507754272</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-0.02167545401288817</v>
+        <v>-0.02217115046640528</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -761,25 +764,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.356092655109795</v>
+        <v>1.347631231725107</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.039097479561775</v>
+        <v>1.031774745262783</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1.214050101158964</v>
+        <v>1.214050235611909</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3431070988579523</v>
+        <v>0.3382836991743339</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2073907830799913</v>
+        <v>-0.2102372210515988</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.07901926948518845</v>
+        <v>-0.08232671843543293</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-0.028296161432256</v>
+        <v>-0.03178576847215897</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -807,25 +810,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.756319933692499</v>
+        <v>1.754247824285122</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.184954007884363</v>
+        <v>1.183311432325887</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>1.14388961892247</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5438718662952648</v>
+        <v>0.542711234911792</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1887045620883142</v>
+        <v>-0.189314466943157</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.01915415262028808</v>
+        <v>0.01838798651547635</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.02291758483913597</v>
+        <v>-0.02365212281474949</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -849,25 +852,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.420643679068192</v>
+        <v>1.411892675295021</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.050408754943486</v>
+        <v>1.042996335729784</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.079117016617151</v>
+        <v>1.079117146540706</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4971514256313312</v>
+        <v>0.491738990134112</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1720806685294378</v>
+        <v>-0.1750737258126018</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.0138079104947999</v>
+        <v>-0.01737314843996218</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-0.02029195366311831</v>
+        <v>-0.02383375078271766</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -895,25 +898,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.386923273605417</v>
+        <v>1.378869738932092</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.99998802233054</v>
+        <v>0.993240424414445</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.023829534967409</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4561204816407216</v>
+        <v>0.4512077944556989</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1764853695926466</v>
+        <v>-0.1792637590339669</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.01178039564347633</v>
+        <v>-0.015114469882196</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-0.02027324812692821</v>
+        <v>-0.02357866901718819</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -941,25 +944,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.350117681839892</v>
+        <v>1.343524217114739</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.884449535508564</v>
+        <v>0.8791625442933069</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.8848642014862311</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3945174653505856</v>
+        <v>0.3906050222472253</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1374068742980972</v>
+        <v>-0.1398269562328974</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.0002199978000220204</v>
+        <v>-0.003024969750302642</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-0.02028277311679205</v>
+        <v>-0.02303145716184907</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -987,25 +990,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.261920134372468</v>
+        <v>1.259244036652515</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9538960573225379</v>
+        <v>0.9515843856129282</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7422891854428675</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5413101416748489</v>
+        <v>0.5394866040117827</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.02586126412099699</v>
+        <v>0.02464755858463263</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.1214533578281281</v>
+        <v>0.1201265564400897</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.01712487272054064</v>
+        <v>0.01592150328612418</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1033,25 +1036,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.4609375</v>
+        <v>1.4640625</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.881720430107527</v>
+        <v>0.8841099163679811</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.6666666666666667</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.26</v>
+        <v>0.2616000000000001</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.2171561051004638</v>
+        <v>0.2187017001545595</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1290322580645162</v>
+        <v>0.1304659498207885</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.01809954751131215</v>
+        <v>0.01939237233354874</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1075,25 +1078,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8471397101718916</v>
+        <v>0.8479325226049779</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8234440753722125</v>
+        <v>0.8242267173813858</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.6470142053043144</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.3218631548295685</v>
+        <v>0.3224305128578846</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2777872092258979</v>
+        <v>0.2783356493794684</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.1071210372683458</v>
+        <v>0.1075962256465957</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.003630769230769326</v>
+        <v>0.004061538461538339</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1121,25 +1124,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.324444870450285</v>
+        <v>1.316517720727077</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7245560408833487</v>
+        <v>0.7186748410362902</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6429763821836962</v>
+        <v>0.6429765010899957</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.05540390769250703</v>
+        <v>0.05180462043855005</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.07218164549987249</v>
+        <v>0.0685251404382119</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.04965357967667461</v>
+        <v>0.04607390300230962</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.007208387942332806</v>
+        <v>-0.01059414591524677</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1167,25 +1170,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.432336021841548</v>
+        <v>1.416396021254116</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.8561352737675212</v>
+        <v>0.8439714755323826</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6361534524735142</v>
+        <v>0.6361535811521677</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.03810556433148959</v>
+        <v>0.03130247332898395</v>
       </c>
       <c r="J13" s="5" t="n">
-        <v>-0.03549068910010666</v>
+        <v>-0.04181147654241413</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.1344506048387097</v>
+        <v>0.127016129032258</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.03047598535429674</v>
+        <v>-0.03682963601119971</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1213,25 +1216,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6387781302790807</v>
+        <v>0.6320181561697005</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6995822675443293</v>
+        <v>0.6925714758373367</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.513578437849203</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1157946744331182</v>
+        <v>0.1111920116496776</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.003159484260657486</v>
+        <v>-0.007271460099895433</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.122890115929134</v>
+        <v>0.1182581843875121</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-0.0002097022228436662</v>
+        <v>-0.004333845938766956</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1259,25 +1262,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.043266682823102</v>
+        <v>1.042848237874746</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.6738444896359364</v>
+        <v>0.6735016994476022</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.5134186814955273</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.185747678836071</v>
+        <v>0.1855048470361864</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.2264989342191062</v>
+        <v>0.2262477568825878</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.1060022650056625</v>
+        <v>0.1057757644394111</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.003493629264282871</v>
+        <v>0.003288121660501409</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1305,25 +1308,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8825173924972103</v>
+        <v>0.8769614479163266</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6085208445977146</v>
+        <v>0.6037735814529424</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.4838467375063418</v>
+        <v>0.4838465960817924</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.07235995356108105</v>
+        <v>0.06919517581680323</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.05816516017049089</v>
+        <v>-0.06094472866330858</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.08402087893584764</v>
+        <v>0.0808216871527192</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.01257668711656457</v>
+        <v>-0.01549079754601235</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1351,25 +1354,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.8559891874792827</v>
+        <v>0.8542527634867201</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.5875614531810283</v>
+        <v>0.5860761644651413</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.4727698538531835</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.06811124948955327</v>
+        <v>0.06711194733151715</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.130305283018658</v>
+        <v>-0.1311189508907334</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.07794265955914126</v>
+        <v>0.07693415934303416</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.02029592772030919</v>
+        <v>-0.02121251800445212</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1393,25 +1396,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.052278346873896</v>
+        <v>1.045213705404451</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.6054158607350097</v>
+        <v>0.5998894722298977</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.4495717048908539</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>-0.2220139260846278</v>
+        <v>-0.2246920192822711</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.1454625680247095</v>
+        <v>-0.1484041770848654</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.1075104841784216</v>
+        <v>0.1036980556614564</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.03376018626309663</v>
+        <v>-0.03708631298852494</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1439,25 +1442,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.6180632793543515</v>
+        <v>0.6176955973885836</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4473456769314283</v>
+        <v>0.4470167881231661</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.4269075867037</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.3980849501948225</v>
+        <v>0.3977672551890974</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.07468991168228212</v>
+        <v>-0.07490017529592352</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.01432334540665137</v>
+        <v>0.01409285479091227</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-0.02672901330131738</v>
+        <v>-0.02695017534990984</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1485,25 +1488,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.697155074829434</v>
+        <v>0.6967782259208435</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4633972447596466</v>
+        <v>0.4630724063035403</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.386085692206307</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.1280837257206511</v>
+        <v>0.1278333186783158</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.05962125689706399</v>
+        <v>0.05938604685113802</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.05577689243027883</v>
+        <v>0.05554253573939527</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.00328489505038676</v>
+        <v>0.003062190301208023</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1527,25 +1530,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.6432115437877206</v>
+        <v>0.6404386073923805</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4072552806936363</v>
+        <v>0.4048804545808653</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.3638219485857872</v>
+        <v>0.3638217891689055</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.3393290483087044</v>
+        <v>0.3370690080007424</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.07204961455991621</v>
+        <v>-0.07361547716666828</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.03184677600539221</v>
+        <v>0.03010559424848358</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.0149597855227882</v>
+        <v>-0.0166219839142091</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1573,25 +1576,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.5407076596699492</v>
+        <v>0.5415131627239591</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.526085152027403</v>
+        <v>0.5268828412451154</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.3484529021550118</v>
+        <v>0.348452752913778</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.2379970189155445</v>
+        <v>0.2386442607030002</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.2809983160323506</v>
+        <v>0.2816680394865498</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.131730407186273</v>
+        <v>0.1323220913345167</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.006457785218847212</v>
+        <v>0.006983975125568032</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1619,25 +1622,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5065976512964794</v>
+        <v>0.5067625229167432</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4805430229816876</v>
+        <v>0.4807052298316443</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.3452625101176254</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.1597015506364099</v>
+        <v>0.1598284939785313</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.1225026092404364</v>
+        <v>0.12262558953178</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.100560680050642</v>
+        <v>0.1006812564056188</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.01320974635066885</v>
+        <v>0.01332075262252319</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1661,25 +1664,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.5016202924048301</v>
+        <v>0.5002107614670284</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.4874221881426859</v>
+        <v>0.4860259845868573</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.3440786230776209</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2335005789270552</v>
+        <v>0.2323427248166732</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.06108897742363872</v>
+        <v>0.06009296148738374</v>
       </c>
       <c r="K24" s="3" t="n">
-        <v>0.1066481994459834</v>
+        <v>0.1056094182825484</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.02108626198083074</v>
+        <v>0.0201277955271566</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1707,25 +1710,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.6069429446927488</v>
+        <v>0.605582166141748</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.3657074672573621</v>
+        <v>0.3645509495440686</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.3421341975369978</v>
+        <v>0.342134310332588</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.3134530841817691</v>
+        <v>0.3123407065899066</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>-0.04580693717406159</v>
+        <v>-0.04661505357668083</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.01756401838476696</v>
+        <v>0.01670223243598157</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.01321235275389998</v>
+        <v>-0.01404807386182749</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1749,25 +1752,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.4904336479345273</v>
+        <v>0.4906641637228792</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.4767026830468319</v>
+        <v>0.4769305586126709</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.341191885313197</v>
+        <v>0.3411916518510802</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.1610543951520249</v>
+        <v>0.1612338434316269</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.1248588241760846</v>
+        <v>0.1250326012229215</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.1010375914271135</v>
+        <v>0.1012076883823778</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.01203877423389632</v>
+        <v>0.01219512195121952</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1795,25 +1798,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.520176259145132</v>
+        <v>0.521915499449892</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4791937087951668</v>
+        <v>0.4808863239427867</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3407212376160893</v>
+        <v>0.3407213949960981</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.2201960673513983</v>
+        <v>0.2215922909799322</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.1443436253555408</v>
+        <v>0.1456529430046889</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.1032820748221253</v>
+        <v>0.1045444112921734</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.01756985605419126</v>
+        <v>0.01873412362404747</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1841,25 +1844,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.5910833633284334</v>
+        <v>0.5887721818502638</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.2735240542569046</v>
+        <v>0.2716740259994095</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3332493989886043</v>
+        <v>0.3332492645816754</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.01788759516098271</v>
+        <v>0.01640902841142333</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.2961881115817147</v>
+        <v>-0.2972104571345114</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.04479682854311207</v>
+        <v>-0.04618434093161561</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.01472091596810465</v>
+        <v>-0.01615211613167045</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1887,25 +1890,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.6064324308562452</v>
+        <v>0.6048478430994644</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3747592641902024</v>
+        <v>0.3734030977557887</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3305418609560147</v>
+        <v>0.3305417626294094</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.3184066647715906</v>
+        <v>0.3171061861337547</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>-0.0544271192334449</v>
+        <v>-0.05535983397527067</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.0332326283987916</v>
+        <v>0.03221344592872999</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.01286687995548752</v>
+        <v>-0.01384058978995695</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1929,25 +1932,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.6006506189814074</v>
+        <v>0.5976899401838969</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.3711010198024536</v>
+        <v>0.368564812127385</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3272958753998194</v>
+        <v>0.3272957586619534</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3177688424004514</v>
+        <v>0.3153315133162373</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>-0.05317979954393792</v>
+        <v>-0.0549311064558291</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.03300330033003296</v>
+        <v>0.03109258294250483</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.01286413810274711</v>
+        <v>-0.01469001576894347</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1971,25 +1974,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.779060574600513</v>
+        <v>1.756874796904122</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6584785223162826</v>
+        <v>0.6452385677263626</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3203370504868808</v>
       </c>
       <c r="I31" s="5" t="n">
-        <v>-0.1053744896961416</v>
+        <v>-0.1125164580557103</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.03553433099986814</v>
+        <v>0.02726746029020521</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.2561023881778599</v>
+        <v>0.246074680036944</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.02807554874936191</v>
+        <v>-0.03583460949464012</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2013,25 +2016,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.4618690627368605</v>
+        <v>0.4607671167741831</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.1605553292969812</v>
+        <v>0.159680317870067</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.314960692998794</v>
+        <v>0.3149604735867568</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>-0.09330026312451234</v>
+        <v>-0.09398372660279408</v>
       </c>
       <c r="J32" s="5" t="n">
-        <v>-0.1759453373709139</v>
+        <v>-0.1765665036105287</v>
       </c>
       <c r="K32" s="5" t="n">
-        <v>-0.1174220374220375</v>
+        <v>-0.1180873180873181</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>-0.01931251155054525</v>
+        <v>-0.02005174644243213</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2059,25 +2062,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.519350967217364</v>
+        <v>0.5211389648251512</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.3162817359917589</v>
+        <v>0.3178307583347912</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.312409180134178</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.09546547256796223</v>
+        <v>0.0967546346421817</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.1992000601564846</v>
+        <v>-0.1982576654052713</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.002950722927117289</v>
+        <v>0.004131012097964071</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>-0.01506809620399874</v>
+        <v>-0.01390901188061422</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2105,25 +2108,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.4750860331399867</v>
+        <v>0.4753437351024499</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.3396112004137897</v>
+        <v>0.3398451148986406</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.2888258002583401</v>
+        <v>0.2888256851959499</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.25558127125733</v>
+        <v>0.2558006250783045</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.1282265625371575</v>
+        <v>0.1284236671078314</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.03940439440711829</v>
+        <v>0.03958598147811876</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-0.005904828065300349</v>
+        <v>-0.005731156651615166</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2151,25 +2154,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.4005106646658314</v>
+        <v>0.3990895478067082</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2418959874513598</v>
+        <v>0.240635819021678</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.2789134350732609</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.05415162454873634</v>
+        <v>0.05308196282925515</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1272968784591543</v>
+        <v>-0.1281824219614789</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.02894445128710421</v>
+        <v>-0.02992979430964393</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.01989060169070112</v>
+        <v>-0.0208851317752361</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2193,25 +2196,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.3582198677456889</v>
+        <v>0.3566091711933668</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2498040683240244</v>
+        <v>0.2483219407600468</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.2664780034187713</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.1223022515125975</v>
+        <v>0.1209713268146877</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.01292488202207143</v>
+        <v>-0.01409544249402861</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.01316559391457006</v>
+        <v>-0.01433586892919847</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.01258782201405151</v>
+        <v>-0.01375878220140514</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2239,25 +2242,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.5269305116670255</v>
+        <v>0.524935376087668</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.1654045764004772</v>
+        <v>0.1638817146351643</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.2627292874018476</v>
       </c>
       <c r="I37" s="5" t="n">
-        <v>-0.1112597074401596</v>
+        <v>-0.112421045432338</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.09554893688923527</v>
+        <v>-0.09673080451743887</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.07707488214011626</v>
+        <v>-0.07828089025326168</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.01551535942616555</v>
+        <v>-0.0168018088258225</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2281,25 +2284,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.3463524877987312</v>
+        <v>0.3467689284073916</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2759181886849948</v>
+        <v>0.2763128432438211</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.2624999336849052</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.135350520491982</v>
+        <v>0.1357016960318809</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.04386019799884155</v>
+        <v>0.0441830746452998</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.01062832135042191</v>
+        <v>0.01094091903719918</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.001544163063619597</v>
+        <v>-0.001235330450895633</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2323,25 +2326,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.4758839281890643</v>
+        <v>0.4741596418068887</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2596432776222755</v>
+        <v>0.258171446360282</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2583446763051391</v>
+        <v>0.2583445931911303</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2257637200268388</v>
+        <v>0.2243315562302439</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.055707113615729</v>
-      </c>
-      <c r="K39" s="3" t="n">
-        <v>0.001031991744065985</v>
+        <v>-0.05681041114621221</v>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>-0.000137598899208724</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.01080970834183159</v>
+        <v>-0.01196546332177573</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2365,25 +2368,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.3420840109582883</v>
+        <v>0.3409401081149401</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2649353712340365</v>
+        <v>0.2638570947590639</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2571188091701571</v>
+        <v>0.2571186798797769</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.09885682279365016</v>
+        <v>0.09792023057307175</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.04007524565177611</v>
+        <v>0.03918875492460661</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.006217838765008477</v>
+        <v>0.005360205831903997</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.006351894982002948</v>
+        <v>-0.007198814312936563</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2411,25 +2414,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1.016993845363729</v>
+        <v>1.006948577699148</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.4197219028502881</v>
+        <v>0.4126513318074136</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.2569768624668831</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>-0.005696746861199253</v>
+        <v>-0.01064862636335018</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.1226404526106584</v>
+        <v>-0.1270099231368976</v>
       </c>
       <c r="K41" s="3" t="n">
-        <v>0.129473377945883</v>
+        <v>0.1238483173310057</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.01413696774739692</v>
+        <v>-0.01904681283331922</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2453,25 +2456,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.3545519330037821</v>
+        <v>0.3543004847147524</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.1681005559450839</v>
+        <v>0.1678837190124787</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2476797102112518</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-0.005446649176095275</v>
+        <v>-0.005631270180517789</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.05142441006336662</v>
+        <v>-0.05160049612052953</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.06378171706638858</v>
+        <v>-0.0639555092109837</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.01517367458866559</v>
+        <v>-0.01535648994515548</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2502,10 +2505,10 @@
         <v>0.3715837981169965</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2234189062625505</v>
+        <v>0.2234189833993132</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2469716209535007</v>
+        <v>0.2469716995752658</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>0.2010558036747441</v>
@@ -2541,25 +2544,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4663496086551335</v>
+        <v>0.4670657268266485</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1409419145709179</v>
+        <v>0.1414991140497084</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2465058885527058</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.07933546834924532</v>
+        <v>-0.07888584528726006</v>
       </c>
       <c r="J44" s="5" t="n">
-        <v>-0.01284056052394233</v>
+        <v>-0.01235846347926839</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.08468790637191159</v>
+        <v>-0.08424089726918083</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>-0.01361944383621627</v>
+        <v>-0.01313772717319905</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2583,13 +2586,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.287682408115262</v>
+        <v>0.2876823172091394</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2918202170828688</v>
+        <v>0.2918203085741768</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2461479300172775</v>
+        <v>0.2461480182739115</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>0.1194586189022169</v>
@@ -2625,25 +2628,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4719534706716324</v>
+        <v>0.4703214814586738</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2644568930083535</v>
+        <v>0.2630547773630163</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2450037100389941</v>
+        <v>0.2450036268054487</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.09072519902037923</v>
+        <v>0.08951567604871391</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.002900660734784788</v>
+        <v>0.001788643370144616</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.015625</v>
+        <v>0.01449887387387361</v>
       </c>
       <c r="L46" s="5" t="n">
-        <v>-0.01055951727921001</v>
+        <v>-0.01165660998354368</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2671,25 +2674,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3526044166267333</v>
+        <v>0.3508207403973176</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2135983504319205</v>
+        <v>0.2119982365920166</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2352178468928858</v>
+        <v>0.2352179699994568</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1227315066208805</v>
+        <v>0.1212510877994166</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-0.02703498483346256</v>
+        <v>-0.02831792355263485</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.01750257779657882</v>
+        <v>-0.01879808582079689</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.01427093556858272</v>
+        <v>-0.01557070479323064</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2713,25 +2716,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4032084931500621</v>
+        <v>0.4025821082317258</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2466956360084911</v>
+        <v>0.2461392092131427</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2338550176542991</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1787774660882906</v>
+        <v>0.1782513526176568</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.05085091233063799</v>
+        <v>-0.05127453776888091</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.01040691018836504</v>
+        <v>0.009955944080202617</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.01324615488854264</v>
+        <v>-0.01368656413036118</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2755,25 +2758,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4025958624225974</v>
+        <v>0.4017830391974024</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2463138726083414</v>
+        <v>0.2455916169046999</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2332428059717051</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.178829975595092</v>
+        <v>0.1781468277202189</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.0507833499524305</v>
+        <v>-0.05133343380735356</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.01059894010598939</v>
+        <v>0.01001328438584714</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.01293319939728776</v>
+        <v>-0.01350521792510739</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2797,25 +2800,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.2892445684211959</v>
+        <v>0.2901412958989593</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.1492187089156662</v>
+        <v>0.1500183044689212</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2204493461181274</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-0.01174115794729691</v>
+        <v>-0.0110535539521307</v>
       </c>
       <c r="J50" s="5" t="n">
-        <v>-0.007438282446689537</v>
+        <v>-0.006747684626161821</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.05836427167503822</v>
+        <v>-0.05770910679187591</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>-0.01518871695312052</v>
+        <v>-0.01450351167703989</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2843,25 +2846,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4225001160457833</v>
+        <v>0.4226723527792104</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1202338438843067</v>
+        <v>0.1203695557801072</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>0.2155714506840796</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>-0.09265892658974084</v>
+        <v>-0.09254908191182398</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.04481602522798356</v>
+        <v>-0.0447003084704849</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.07843027799486424</v>
+        <v>-0.07831863347102808</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>-0.01374036680805291</v>
+        <v>-0.01362088535754813</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2885,25 +2888,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3973529310194592</v>
+        <v>0.397624894260995</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2248224566528947</v>
+        <v>0.225060698092582</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2152972504185957</v>
+        <v>0.2152973608155295</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1633801669491501</v>
+        <v>0.1636063514863231</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.03454833873211138</v>
+        <v>-0.03436063548310431</v>
       </c>
       <c r="K52" s="3" t="n">
-        <v>0.00783775840109735</v>
+        <v>0.008033702361124773</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-0.009818076812012633</v>
+        <v>-0.009625565501973243</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2931,25 +2934,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.2108917324299577</v>
+        <v>0.2114573567370326</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2810031297070739</v>
+        <v>0.2816012785818076</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2144803021743404</v>
+        <v>0.2144802282674094</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1176860296997755</v>
+        <v>0.118207868938331</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.1807079350237055</v>
+        <v>0.1812593241589906</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.05477472743990552</v>
+        <v>0.05526730592407736</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.00387548443555441</v>
+        <v>0.004344293036629754</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2977,25 +2980,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.6554887971778249</v>
+        <v>0.6542503798247703</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.231307846917983</v>
+        <v>0.2303867455446755</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.21401161001921</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.004385964912280715</v>
+        <v>-0.005130751406818956</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.15185054635178</v>
+        <v>-0.152485019386676</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.01424717585567348</v>
+        <v>0.01348845051424719</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.01787755102040811</v>
+        <v>-0.01861224489795921</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3023,25 +3026,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1650733418070576</v>
+        <v>0.1649510757411736</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2023189068855153</v>
+        <v>0.2021927321655148</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.2006786355255077</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1084216830188134</v>
+        <v>0.1083053621369769</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-0.02214088324715158</v>
+        <v>-0.02224350252690321</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.001366120218579292</v>
+        <v>0.001261034047919329</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.007826546800634659</v>
+        <v>0.007720782654680125</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3069,25 +3072,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2513173753903617</v>
+        <v>0.2494125777449336</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1586111379734456</v>
+        <v>0.1568475339910902</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.1992507080016339</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.01957494537247295</v>
+        <v>0.01802297821538734</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.1096195162814151</v>
+        <v>-0.1109748274081872</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.03388746803069065</v>
+        <v>-0.03535805626598465</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.008139687541026674</v>
+        <v>-0.009649468294604113</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3111,25 +3114,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.2723567382379459</v>
+        <v>0.2701079639661315</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1835778435338309</v>
+        <v>0.1814859871201451</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.1885842859128997</v>
+        <v>0.1885841615312283</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.09205542289449764</v>
+        <v>0.09012543735745493</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.03514828781368373</v>
+        <v>-0.03685346670009493</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.004212105475737027</v>
+        <v>-0.005971957763545088</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.01450433988122424</v>
+        <v>-0.01624600274097765</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3153,25 +3156,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3045622475937049</v>
+        <v>0.3041187800061069</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.1938452140565832</v>
+        <v>0.193439155771703</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.1883352792907864</v>
+        <v>0.1883350528676975</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1252264191205568</v>
+        <v>0.1248439142255169</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.005038010220821398</v>
+        <v>0.00469636168495513</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.004636683654704932</v>
+        <v>0.004295171544160148</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.007642006383475564</v>
+        <v>-0.007979344526039878</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3195,25 +3198,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3046968261167993</v>
+        <v>0.3036340996460296</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1940142701107708</v>
+        <v>0.1930418346447433</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>0.1880772956866044</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1253177185120797</v>
+        <v>0.124401231257762</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.005238861461862143</v>
+        <v>0.004420169470330304</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.004997128087306235</v>
+        <v>0.004178632969557672</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.007107491949098432</v>
+        <v>-0.007916128757678553</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3237,25 +3240,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3031966720792949</v>
+        <v>0.3024262240319064</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.193295782895514</v>
+        <v>0.1925903186078104</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.1876059580013714</v>
+        <v>0.1876058443840174</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1249624705537775</v>
+        <v>0.1242975117835829</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.004859680141366063</v>
+        <v>0.004265713431707008</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.004791003999102594</v>
+        <v>0.004197077883511424</v>
       </c>
       <c r="L60" s="5" t="n">
-        <v>-0.007496251874062998</v>
+        <v>-0.008082915064206886</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3283,25 +3286,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3191938503311289</v>
+        <v>0.3184951692328024</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1927147054395155</v>
+        <v>0.1920832530944507</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1836517157529616</v>
+        <v>0.1836518298209084</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1385880963059136</v>
+        <v>0.1379851902448568</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.001691855569898593</v>
+        <v>0.001161438913520607</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.007656804418002761</v>
+        <v>0.00712322919723607</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.006000315806095169</v>
+        <v>-0.006526659297857784</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3329,25 +3332,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.2129395604468827</v>
+        <v>0.2114903255245717</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1230385082123762</v>
+        <v>0.121696765669709</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.1827460513610628</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1008434806034941</v>
+        <v>0.09952825541758781</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.05981735219456707</v>
+        <v>0.05855114269373729</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.05048213272830404</v>
+        <v>-0.05161656267725467</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.01253502433269438</v>
+        <v>-0.01371479132871267</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3371,25 +3374,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.2883846989274874</v>
+        <v>0.288564214699945</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2604619686303009</v>
+        <v>0.2606375093602329</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1819575099459281</v>
+        <v>0.1819574307598728</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1201939485087449</v>
+        <v>0.1203500295939488</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.1041942933070943</v>
+        <v>0.1043481450966035</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.0664190193164933</v>
+        <v>0.06656760772659731</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.004576976421636569</v>
+        <v>-0.004438280166435438</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3413,25 +3416,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3975295326069559</v>
+        <v>0.3966084097366138</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2083773017148274</v>
+        <v>0.2075807444955033</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.176116734332197</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.09998403904111708</v>
+        <v>0.09925893420325216</v>
       </c>
       <c r="J64" s="5" t="n">
-        <v>-0.007156076918624299</v>
+        <v>-0.007810555444056955</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.02742973247544866</v>
+        <v>0.02675245513037594</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.002643754130865705</v>
+        <v>0.00198281559814939</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3455,25 +3458,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.5127157972897716</v>
+        <v>0.5104882123630965</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.2517665130568356</v>
+        <v>0.2499231950844856</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1703533026113673</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>-0.1504378648874063</v>
+        <v>-0.1516889074228523</v>
       </c>
       <c r="J65" s="5" t="n">
-        <v>-0.03470741530443033</v>
+        <v>-0.03612887941246146</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.06956293476834219</v>
+        <v>0.06798792492453076</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.02652012901684386</v>
+        <v>-0.02795364950424073</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3497,25 +3500,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2378453185775824</v>
+        <v>0.2376176269895058</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1720214224476291</v>
+        <v>0.1718058386303849</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.1701350640467429</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.08490088173491883</v>
+        <v>0.08470132303322919</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.03933620737808674</v>
+        <v>0.03914502992800339</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.001612086039334937</v>
+        <v>0.001427847634839274</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>-0.008797119285290922</v>
+        <v>-0.008979443001048359</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3539,25 +3542,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.5102746230105977</v>
+        <v>0.5078436586014361</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.2500707391454713</v>
+        <v>0.2480586034520704</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.1686421228031565</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>-0.1506600589567223</v>
+        <v>-0.1520271713589951</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-0.03481004976332069</v>
+        <v>-0.03636363636363626</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.06967797476527404</v>
+        <v>0.06795620241586198</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.02646785172126731</v>
+        <v>-0.02803486606924244</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3581,25 +3584,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3229421365770231</v>
+        <v>0.3221990776371348</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1635272842426088</v>
+        <v>0.1628737640874511</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1534630738531815</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1564753123678975</v>
+        <v>0.1558257531046039</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>-0.02910503439466616</v>
+        <v>-0.02965035845982311</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.008725212464589127</v>
+        <v>0.008158640226628933</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.009788654060066793</v>
+        <v>-0.01034482758620692</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3623,25 +3626,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3008957252751554</v>
+        <v>0.2997892992291971</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1604667234330355</v>
+        <v>0.1594795794548101</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1469767501807657</v>
+        <v>0.1469766782007569</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1537107947224814</v>
+        <v>0.1527295418949459</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.005879000374538812</v>
+        <v>0.005023418576658445</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.01176133103843968</v>
+        <v>0.01090074584050504</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.0109366236679751</v>
+        <v>-0.01177790241166554</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3665,25 +3668,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.3011378084154885</v>
+        <v>0.2995001810068219</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1481764013314915</v>
+        <v>0.1467311626983931</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1441034560927599</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1439873075171045</v>
+        <v>0.1425473418021843</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>-0.02835505367720337</v>
+        <v>-0.02957808770964998</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0.003559944878272825</v>
+        <v>0.00229673863114388</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.009632819582955476</v>
+        <v>-0.0108794197642792</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3711,25 +3714,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.09253297588920684</v>
+        <v>0.09321836297248343</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1099480688430101</v>
+        <v>0.1106441209428966</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1387236407720365</v>
+        <v>0.1387235063658157</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.07081070567665337</v>
+        <v>0.07148234107640872</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.1146172766821103</v>
+        <v>0.1153163885010622</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.02527002241695531</v>
+        <v>-0.0246586509068677</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.003126302626094146</v>
+        <v>-0.002501042100875317</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3757,25 +3760,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.1962967624579151</v>
+        <v>0.1963929869818803</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1106029199882075</v>
+        <v>0.1106924090820809</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1369798511045845</v>
+        <v>0.1369799286658946</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.09685452881838241</v>
+        <v>0.09694283527750969</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.02799703321526414</v>
+        <v>0.02807979603896715</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.02319911921988049</v>
+        <v>-0.02312047813777918</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.00933163183920882</v>
+        <v>-0.009251874302121488</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3803,25 +3806,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.07016276074356775</v>
+        <v>0.06179858200518318</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1535251124314936</v>
+        <v>0.1445093901754804</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1351281656658454</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.09875826853893477</v>
+        <v>0.09017059301380992</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.213846153846154</v>
+        <v>0.2043589743589744</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.01620693356230563</v>
+        <v>0.008264462809917328</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.003368421052631465</v>
+        <v>-0.01115789473684214</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3845,25 +3848,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.2679755359256091</v>
+        <v>0.2681715135973131</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1048391651526159</v>
+        <v>0.105009928547539</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.1343812324743165</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>-0.03186436216743582</v>
+        <v>-0.03171472760208316</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-0.01603842499794506</v>
+        <v>-0.01588634438357084</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.02604245069998501</v>
+        <v>-0.02589191630287535</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.006754682222904429</v>
+        <v>-0.006601166717838614</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3891,25 +3894,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1731665832115519</v>
+        <v>0.1730298983014724</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.02767088419166641</v>
+        <v>0.02755115089512761</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0.09508073014295459</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.00697809723837084</v>
+        <v>0.006860864969585823</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.02766058443398545</v>
+        <v>0.02754085233746495</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.06155696479335226</v>
+        <v>-0.0616663022086158</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.003135888501742068</v>
+        <v>-0.003252032520325243</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3933,25 +3936,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2392064808588772</v>
+        <v>0.2377170755708811</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.09372110287525892</v>
+        <v>0.09240663956758088</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0.09065402182401017</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.08354197606107783</v>
+        <v>0.08223974630056841</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>-0.05369895635229993</v>
+        <v>-0.05483624628537553</v>
       </c>
       <c r="K76" s="3" t="n">
-        <v>0.002812148481439847</v>
+        <v>0.001606941989394262</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.01250098900229446</v>
+        <v>-0.01368779175567691</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3975,25 +3978,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2356589392681003</v>
+        <v>0.2348432267564229</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.09200285684209297</v>
+        <v>0.09128206287718088</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0.08902958173682984</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.08240600394484598</v>
+        <v>0.08169154453630156</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.05443339434564676</v>
+        <v>-0.05505753071901587</v>
       </c>
       <c r="K77" s="3" t="n">
-        <v>0.002730206006453129</v>
+        <v>0.002068337883676774</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.01230543557982222</v>
+        <v>-0.01295737918670026</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4017,25 +4020,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.136989436319978</v>
+        <v>0.1353620271217815</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.07784501329854265</v>
+        <v>0.0763022593970204</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0.08386175351447944</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1248266234606876</v>
+        <v>0.1232166232839744</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.1133961793846914</v>
+        <v>0.1118025399666929</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.005551206319834856</v>
+        <v>-0.006974592555689885</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.008725879682179416</v>
+        <v>-0.01014472190692395</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4059,25 +4062,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.118422080338382</v>
+        <v>0.118685463077576</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.03617611322884562</v>
+        <v>0.03641991937313471</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.08152405606662572</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.08497104086752816</v>
+        <v>-0.0847556647662292</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.02570878572377222</v>
+        <v>-0.02547954073217784</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.04192966636609552</v>
+        <v>-0.04170423805229939</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.006393559081221856</v>
+        <v>0.00663035756571162</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4101,25 +4104,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.06706150513027365</v>
+        <v>0.06693629256219924</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.08422297606757478</v>
+        <v>0.08409585494392169</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.07964282737731065</v>
+        <v>0.07964293217393736</v>
       </c>
       <c r="I80" s="5" t="n">
-        <v>-0.0164768892685101</v>
+        <v>-0.0165922991618136</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.04865339887482545</v>
+        <v>0.04853034637554421</v>
       </c>
       <c r="K80" s="3" t="n">
-        <v>0.004242281404666537</v>
+        <v>0.004124440254536843</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.002824193927982943</v>
+        <v>0.002706519180983635</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4143,25 +4146,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.1222655370955372</v>
+        <v>0.1206975796563539</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.07702537769048878</v>
+        <v>0.07552062690084105</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0.07928250387496072</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.1278256037568049</v>
+        <v>0.1262498781490413</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.1166066971674038</v>
+        <v>0.115046645896475</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.002091321017776315</v>
+        <v>-0.003485535029627118</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.007797608733321804</v>
+        <v>-0.009183850285912287</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4231,25 +4234,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1049671962350045</v>
+        <v>0.1040248613093895</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.0536384724104928</v>
+        <v>0.05273997456591295</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.07610091852498591</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>-0.04613568750394836</v>
+        <v>-0.04694910221045445</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-0.1339174960163656</v>
+        <v>-0.1346560541493818</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.02087392151405509</v>
+        <v>-0.02170887837461732</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.0197826692672054</v>
+        <v>-0.02061855670103097</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4277,25 +4280,25 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.00807221196349539</v>
+        <v>-0.007720339743546356</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.06513546923207381</v>
+        <v>0.06551331083165923</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0.06437978603290229</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.02658412235979601</v>
+        <v>0.02694828841951935</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.01548991354466867</v>
+        <v>0.01585014409221897</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>0.0007099751508696794</v>
+        <v>0.001064962726304408</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>0.002489331436699826</v>
+        <v>0.002844950213371167</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4323,25 +4326,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.08747470148486958</v>
+        <v>0.08413490543867841</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.09827758313548052</v>
+        <v>0.09490460983801619</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0.05789559726861548</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1480884394421162</v>
+        <v>0.1445624896195674</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.08460162166182061</v>
+        <v>0.08127064926975214</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0.03817199539456206</v>
+        <v>0.03498361526879812</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.0009375266342793731</v>
+        <v>-0.004005795619193675</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4369,25 +4372,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.1521425797363825</v>
+        <v>0.1511328481466314</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.03271994669026879</v>
+        <v>0.0318149860695629</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.04970741876310547</v>
+        <v>0.04970753027656505</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.08256497417927444</v>
+        <v>0.08161622003060232</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.02439569704674427</v>
+        <v>-0.02525071143568769</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.01618305421986399</v>
+        <v>-0.01704526612502066</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.01774658146541719</v>
+        <v>-0.01860742310366503</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4461,25 +4464,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.08371796317715163</v>
+        <v>0.08346397929155103</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.003024686480125993</v>
+        <v>0.002789620577745122</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.04349449760164292</v>
+        <v>0.0434944144559628</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.02327802058627682</v>
+        <v>0.02303828968807609</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>-0.02111244128987988</v>
+        <v>-0.02134177250677893</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.0387829655206926</v>
+        <v>-0.03900815693339343</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-0.01847262321469623</v>
+        <v>-0.01870257288126931</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4503,25 +4506,25 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.07741539109481943</v>
+        <v>0.07714286060220621</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.03703246004287619</v>
+        <v>0.03677035579070598</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.03978564356511405</v>
+        <v>0.03978574756905551</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01189592174057275</v>
+        <v>0.0116400694215486</v>
       </c>
       <c r="J89" s="5" t="n">
-        <v>-0.0005947197626466894</v>
+        <v>-0.0008475102051197503</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.00264783759929399</v>
+        <v>-0.002900012608750502</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.00889612830472386</v>
+        <v>-0.009146723468237083</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4545,25 +4548,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04401404782778173</v>
+        <v>0.04388622249116625</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.01957139141396413</v>
+        <v>0.01944616774224706</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.02157030603994414</v>
+        <v>0.02157001392504343</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.0003956317134283793</v>
+        <v>0.000273142780457869</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.001079637690677648</v>
+        <v>0.0009569713951633751</v>
       </c>
       <c r="K90" s="5" t="n">
-        <v>-0.001956707839060767</v>
+        <v>-0.002079002079002135</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.00341922090609359</v>
+        <v>-0.003541335938454071</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4591,25 +4594,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.03635345526507638</v>
+        <v>0.03625644567458064</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.008625609212160823</v>
+        <v>0.008531340426373379</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.008908851450074806</v>
+        <v>0.008908996797999169</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.009118092129286048</v>
+        <v>-0.00921077516664992</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.01187151587542101</v>
+        <v>-0.01196401128720848</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.0002807411566535523</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>9.361542782260202e-05</v>
+        <v>-0.0003743215422048474</v>
+      </c>
+      <c r="L91" s="22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4633,7 +4636,7 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.02347353571446331</v>
+        <v>0.02347344894165726</v>
       </c>
       <c r="G92" s="5" t="n">
         <v>-0.004516111531669087</v>
@@ -4642,7 +4645,7 @@
         <v>0.003266172938441558</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.03463195237569527</v>
+        <v>-0.03463202957550671</v>
       </c>
       <c r="J92" s="5" t="n">
         <v>-0.01611747271863795</v>
@@ -4675,19 +4678,19 @@
         </is>
       </c>
       <c r="F93" s="5" t="n">
-        <v>-0.05376116070309234</v>
+        <v>-0.0537609937647624</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.01169715978442831</v>
+        <v>-0.01169706872926279</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>-0.007470546953594392</v>
+        <v>-0.007470455509019036</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-0.06703187926939391</v>
+        <v>-0.06703196041369475</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.03709106219716896</v>
+        <v>-0.03709097576111753</v>
       </c>
       <c r="K93" s="5" t="n">
         <v>-0.004258425599221294</v>
@@ -4717,25 +4720,25 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.09270449814720139</v>
+        <v>0.09199174716225866</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.03101368216018319</v>
+        <v>-0.03164567555539721</v>
       </c>
       <c r="H94" s="5" t="n">
         <v>-0.01753115639561731</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.01996868354374715</v>
+        <v>0.01930343837004656</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.03742369835445281</v>
+        <v>-0.03805151100136994</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.0137231077121005</v>
+        <v>-0.01436637838610533</v>
       </c>
       <c r="L94" s="5" t="n">
-        <v>-0.01758507760216432</v>
+        <v>-0.01822582941762785</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4763,25 +4766,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.03097713097713095</v>
+        <v>0.0303534303534303</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.04597922277799138</v>
+        <v>-0.04655636783378214</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>-0.03501346671796846</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.01254480286738346</v>
+        <v>-0.01314217443249699</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.03247970018738289</v>
+        <v>0.03185509056839475</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.01136363636363624</v>
+        <v>-0.01196172248803817</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.002213279678068392</v>
+        <v>-0.0028169014084507</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4809,25 +4812,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.1236772997055375</v>
+        <v>-0.1259407996268226</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.159960960724716</v>
+        <v>-0.1621307416725758</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>-0.1527839929741026</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.1083461792556706</v>
+        <v>0.1054833737062322</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1093233414150321</v>
+        <v>0.1064580119021381</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.00847123719464149</v>
+        <v>-0.01103230890464924</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.01871709884967832</v>
+        <v>-0.02125170598557213</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -101,17 +101,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DCFCE7"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFEDD5"/>
+        <fgColor rgb="00E0F2FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,12 +121,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0F2FE"/>
+        <fgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E7EB"/>
+        <fgColor rgb="00FFEDD5"/>
       </patternFill>
     </fill>
     <fill>
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -204,9 +204,6 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -672,25 +669,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.2949893799555</v>
+        <v>2.335419460987433</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.493591889583886</v>
+        <v>1.519187642256516</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.267982542779668</v>
+        <v>1.433034836883635</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3312679461991839</v>
+        <v>0.3187467440648952</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1787628769869015</v>
+        <v>-0.1679188580015027</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.09947578632051912</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>-0.02587636846179364</v>
+        <v>0.0354096061703868</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.00796359499431154</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -718,25 +715,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.596079304650891</v>
+        <v>1.678215924420186</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.207141675130683</v>
+        <v>1.219888635508382</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.223416280781676</v>
+        <v>1.41714350708147</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4578957377457071</v>
+        <v>0.4180406824665301</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.2060773391483725</v>
+        <v>-0.2272939098098348</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.007319639507754272</v>
+        <v>-0.08160660341233039</v>
       </c>
       <c r="L3" s="5" t="n">
-        <v>-0.02217115046640528</v>
+        <v>-0.007540576578233593</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -764,25 +761,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.347631231725107</v>
+        <v>1.443153892162519</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.031774745262783</v>
+        <v>1.052330360266249</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1.214050235611909</v>
+        <v>1.37796613036288</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3382836991743339</v>
+        <v>0.3105288964394104</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2102372210515988</v>
+        <v>-0.2253883142295557</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.08232671843543293</v>
+        <v>-0.1369387755102041</v>
       </c>
       <c r="L4" s="5" t="n">
-        <v>-0.03178576847215897</v>
+        <v>-0.008285781286641147</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -810,25 +807,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.754247824285122</v>
+        <v>1.844597503228584</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.183311432325887</v>
+        <v>1.201932689103632</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>1.14388961892247</v>
+        <v>1.327224258580473</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.542711234911792</v>
+        <v>0.4903022101939556</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.189314466943157</v>
-      </c>
-      <c r="K5" s="3" t="n">
-        <v>0.01838798651547635</v>
+        <v>-0.1997093375317912</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>-0.05383734249713634</v>
       </c>
       <c r="L5" s="5" t="n">
-        <v>-0.02365212281474949</v>
+        <v>-0.005717724947336689</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -852,25 +849,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.411892675295021</v>
+        <v>1.4819694841986</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.042996335729784</v>
+        <v>1.048844288150543</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.079117146540706</v>
+        <v>1.243298522804681</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.491738990134112</v>
+        <v>0.451514961602187</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1750737258126018</v>
+        <v>-0.1952878668760081</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.01737314843996218</v>
+        <v>-0.08668228177274495</v>
       </c>
       <c r="L6" s="5" t="n">
-        <v>-0.02383375078271766</v>
+        <v>-0.01019367991845066</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -898,25 +895,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.378869738932092</v>
+        <v>1.465397637807288</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.993240424414445</v>
+        <v>1.005801090864574</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.023829534967409</v>
+        <v>1.180001049549638</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4512077944556989</v>
+        <v>0.4185923031552927</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1792637590339669</v>
+        <v>-0.1945586392832013</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.015114469882196</v>
+        <v>-0.07990819945754224</v>
       </c>
       <c r="L7" s="5" t="n">
-        <v>-0.02357866901718819</v>
+        <v>-0.007874015748031482</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -944,25 +941,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.343524217114739</v>
+        <v>1.447707363972409</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.8791625442933069</v>
+        <v>0.9054147944864905</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.8848642014862311</v>
+        <v>1.015852309634522</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3906050222472253</v>
+        <v>0.3634928589325981</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1398269562328974</v>
+        <v>-0.1469352563097664</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.003024969750302642</v>
+        <v>-0.05478452693196245</v>
       </c>
       <c r="L8" s="5" t="n">
-        <v>-0.02303145716184907</v>
+        <v>-0.00192582810608577</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -990,25 +987,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.259244036652515</v>
+        <v>1.264647673162021</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9515843856129282</v>
+        <v>0.9603538670008971</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7422891854428675</v>
+        <v>0.841615521563986</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5394866040117827</v>
+        <v>0.519128734990226</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.02464755858463263</v>
+        <v>0.01777362020579965</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.1201265564400897</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.01592150328612418</v>
+        <v>0.0644751002837296</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>-0.008565700747220628</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1036,25 +1033,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.4640625</v>
+        <v>1.676422764227642</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8841099163679811</v>
+        <v>1.052369077306734</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.6666666666666667</v>
+        <v>0.7344139650872819</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.2616000000000001</v>
+        <v>0.382031905961377</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.2187017001545595</v>
+        <v>0.3042789223454836</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1304659498207885</v>
+        <v>0.1833213515456507</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.01939237233354874</v>
+        <v>0.04177215189873418</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1063,40 +1060,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
+          <t>COPX</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>Defensive Equity</t>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.8479325226049779</v>
+        <v>1.491340492627738</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8242267173813858</v>
+        <v>0.8650522496875344</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.6470142053043144</v>
+        <v>0.7198697678003514</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.3224305128578846</v>
+        <v>0.03663241737497058</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2783356493794684</v>
+        <v>0.01262621292311561</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.1075962256465957</v>
+        <v>0.08441481128705797</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.004061538461538339</v>
+        <v>0.02061855670103108</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1124,25 +1125,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.316517720727077</v>
+        <v>1.354840243044582</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7186748410362902</v>
+        <v>0.7231536663553493</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6429765010899957</v>
+        <v>0.6447102092677597</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.05180462043855005</v>
+        <v>0.06270809296757651</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.0685251404382119</v>
+        <v>0.1223240340189802</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.04607390300230962</v>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v>-0.01059414591524677</v>
+        <v>0.04769439421338162</v>
+      </c>
+      <c r="L12" s="3" t="n">
+        <v>0.02002640845070425</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1151,44 +1152,40 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>COPX</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Natural Resources</t>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.416396021254116</v>
+        <v>0.9379590766115058</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.8439714755323826</v>
+        <v>0.7858064524679051</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6361535811521677</v>
+        <v>0.6427126400631422</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.03130247332898395</v>
-      </c>
-      <c r="J13" s="5" t="n">
-        <v>-0.04181147654241413</v>
+        <v>0.3073254164674946</v>
+      </c>
+      <c r="J13" s="3" t="n">
+        <v>0.2729883388097329</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.127016129032258</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>-0.03682963601119971</v>
+        <v>0.08710824335001321</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.01046511627906987</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1205,7 +1202,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D14" s="12" t="inlineStr">
+      <c r="D14" s="11" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1216,25 +1213,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6320181561697005</v>
+        <v>0.6991696339400699</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6925714758373367</v>
+        <v>0.6832939005095919</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.513578437849203</v>
+        <v>0.566193805217065</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1111920116496776</v>
+        <v>0.099783419878402</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.007271460099895433</v>
+        <v>-0.02261026854042025</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.1182581843875121</v>
+        <v>0.07476730842789769</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-0.004333845938766956</v>
+        <v>-0.01267335082458765</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1243,7 +1240,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BOAT</t>
+          <t>PICK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1251,36 +1248,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D15" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>1.042848237874746</v>
+        <v>0.9153229220467776</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.6735016994476022</v>
+        <v>0.6363414502372797</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5134186814955273</v>
+        <v>0.5517507049189849</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.1855048470361864</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0.2262477568825878</v>
+        <v>0.07361549199235418</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>-0.01942912540769204</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.1057757644394111</v>
+        <v>0.05451310255580721</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.003288121660501409</v>
+        <v>0.01668746101060492</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1289,7 +1286,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PICK</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1297,36 +1294,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8769614479163266</v>
+        <v>0.8480729076004281</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6037735814529424</v>
+        <v>0.5960529595432538</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.4838465960817924</v>
+        <v>0.5422703419551942</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.06919517581680323</v>
+        <v>0.04735615072502086</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.06094472866330858</v>
+        <v>-0.1219783737753833</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.0808216871527192</v>
+        <v>0.03487236713628117</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.01549079754601235</v>
+        <v>-0.006960246285637739</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1335,7 +1332,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1343,36 +1340,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.8542527634867201</v>
+        <v>0.6348244366103697</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.5860761644651413</v>
+        <v>0.4459339472036188</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.4727698538531835</v>
+        <v>0.5180241978289608</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.06711194733151715</v>
+        <v>0.3520662397524912</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.1311189508907334</v>
-      </c>
-      <c r="K17" s="3" t="n">
-        <v>0.07693415934303416</v>
+        <v>-0.08550182185092314</v>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>-0.04748952666791717</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.02121251800445212</v>
+        <v>-0.01087591714823699</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1381,40 +1378,44 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>BOAT</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.045213705404451</v>
+        <v>1.071898707730655</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.5998894722298977</v>
+        <v>0.6823362521049703</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4495717048908539</v>
-      </c>
-      <c r="I18" s="5" t="n">
-        <v>-0.2246920192822711</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>-0.1484041770848654</v>
+        <v>0.5092959518884592</v>
+      </c>
+      <c r="I18" s="3" t="n">
+        <v>0.2034003722104905</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.241098858849623</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.1036980556614564</v>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v>-0.03708631298852494</v>
+        <v>0.1146496815286624</v>
+      </c>
+      <c r="L18" s="3" t="n">
+        <v>0.007194244604316502</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1423,44 +1424,40 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>QTEC</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.6176955973885836</v>
+        <v>1.056</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4470167881231661</v>
+        <v>0.5911170928667564</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4269075867037</v>
-      </c>
-      <c r="I19" s="3" t="n">
-        <v>0.3977672551890974</v>
+        <v>0.4492597577388966</v>
+      </c>
+      <c r="I19" s="5" t="n">
+        <v>-0.2154234138571808</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.07490017529592352</v>
+        <v>-0.1072345567134874</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.01409285479091227</v>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v>-0.02695017534990984</v>
+        <v>0.0978826151560177</v>
+      </c>
+      <c r="L19" s="3" t="n">
+        <v>0.02054558011049723</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1469,44 +1466,40 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DXJ</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.6967782259208435</v>
+        <v>0.6854416689013056</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4630724063035403</v>
+        <v>0.4138475412780702</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.386085692206307</v>
+        <v>0.446349783606302</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.1278333186783158</v>
-      </c>
-      <c r="J20" s="3" t="n">
-        <v>0.05938604685113802</v>
-      </c>
-      <c r="K20" s="3" t="n">
-        <v>0.05554253573939527</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0.003062190301208023</v>
+        <v>0.3096773850571988</v>
+      </c>
+      <c r="J20" s="5" t="n">
+        <v>-0.06783952874160826</v>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>-0.02247191011235961</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>-0.005118710520583769</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1515,10 +1508,14 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>XLK</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>IYW</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -1530,25 +1527,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.6404386073923805</v>
+        <v>0.6539152318062351</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4048804545808653</v>
+        <v>0.3763125793627176</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.3638217891689055</v>
+        <v>0.4106967477762746</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.3370690080007424</v>
+        <v>0.2930109364212197</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.07361547716666828</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0.03010559424848358</v>
+        <v>-0.03928106344144033</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>-0.02437389075133112</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.0166219839142091</v>
+        <v>-0.002298943292732059</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1557,7 +1554,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>QCLN</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1565,36 +1562,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D22" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.5415131627239591</v>
+        <v>0.6488822377928691</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.5268828412451154</v>
+        <v>0.2878657953209027</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.348452752913778</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>0.2386442607030002</v>
-      </c>
-      <c r="J22" s="3" t="n">
-        <v>0.2816680394865498</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0.1323220913345167</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0.006983975125568032</v>
+        <v>0.4082497372925555</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>-0.007328228484660637</v>
+      </c>
+      <c r="J22" s="5" t="n">
+        <v>-0.2987241531016278</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>-0.08548479632816985</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>-0.007677941481635142</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1603,7 +1600,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>VDE</t>
+          <t>FTEC</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1611,36 +1608,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D23" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.5067625229167432</v>
+        <v>0.6539267529013344</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4807052298316443</v>
+        <v>0.3847523777698021</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3452625101176254</v>
+        <v>0.4037450577010362</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.1598284939785313</v>
-      </c>
-      <c r="J23" s="3" t="n">
-        <v>0.12262558953178</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.1006812564056188</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>0.01332075262252319</v>
+        <v>0.2969494292529689</v>
+      </c>
+      <c r="J23" s="5" t="n">
+        <v>-0.04336494281051606</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>-0.01353000662551873</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>-0.002784827975183424</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1649,40 +1646,40 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>DBC</t>
+          <t>VGT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" s="13" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Broad Commodities</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.5002107614670284</v>
+        <v>0.6500926479867792</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.4860259845868573</v>
+        <v>0.3802861415344834</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3440786230776209</v>
+        <v>0.3995053156571156</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2323427248166732</v>
-      </c>
-      <c r="J24" s="3" t="n">
-        <v>0.06009296148738374</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0.1056094182825484</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>0.0201277955271566</v>
+        <v>0.2959885533531585</v>
+      </c>
+      <c r="J24" s="5" t="n">
+        <v>-0.04252232215081309</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>-0.01373283395755309</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>-0.003112644064944936</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1691,7 +1688,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IYW</t>
+          <t>DXJ</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1699,78 +1696,82 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D25" s="6" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Japan Hedged Equity</t>
+        </is>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>0.6760371147118991</v>
+      </c>
+      <c r="G25" s="3" t="n">
+        <v>0.4362951716595533</v>
+      </c>
+      <c r="H25" s="3" t="n">
+        <v>0.39846199533543</v>
+      </c>
+      <c r="I25" s="3" t="n">
+        <v>0.1086274813793711</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.04370518864288409</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.02705341757610569</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>-0.006997278836008203</v>
+      </c>
+    </row>
+    <row r="26" ht="21" customHeight="1">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>DRIV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="F25" s="3" t="n">
-        <v>0.605582166141748</v>
-      </c>
-      <c r="G25" s="3" t="n">
-        <v>0.3645509495440686</v>
-      </c>
-      <c r="H25" s="3" t="n">
-        <v>0.342134310332588</v>
-      </c>
-      <c r="I25" s="3" t="n">
-        <v>0.3123407065899066</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>-0.04661505357668083</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0.01670223243598157</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>-0.01404807386182749</v>
-      </c>
-    </row>
-    <row r="26" ht="21" customHeight="1">
-      <c r="A26" s="14" t="n">
-        <v>25</v>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="inlineStr"/>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E26" s="14" t="inlineStr">
-        <is>
-          <t>Energy</t>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Autonomous/EV</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.4906641637228792</v>
+        <v>0.5467528411243796</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.4769305586126709</v>
+        <v>0.3318501434564265</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3411916518510802</v>
+        <v>0.3787268565801516</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.1612338434316269</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>0.1250326012229215</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>0.1012076883823778</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>0.01219512195121952</v>
+        <v>0.07925011285434724</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>-0.1951137828405894</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>-0.03399999999999992</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>-0.006464883925947684</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1779,7 +1780,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1789,34 +1790,34 @@
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>Natural Resources</t>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.521915499449892</v>
+        <v>0.593509634387051</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4808863239427867</v>
+        <v>0.5221318533158781</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3407213949960981</v>
+        <v>0.3576947739375842</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.2215922909799322</v>
+        <v>0.233541771188718</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.1456529430046889</v>
+        <v>0.272895339966692</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.1045444112921734</v>
+        <v>0.1211149092821457</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.01873412362404747</v>
+        <v>0.01119438383455096</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1825,7 +1826,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>QCLN</t>
+          <t>ROBO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1840,29 +1841,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.5887721818502638</v>
+        <v>0.4224457966700454</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.2716740259994095</v>
+        <v>0.2598221447848854</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3332492645816754</v>
+        <v>0.3542365497216067</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.01640902841142333</v>
+        <v>0.04238076258801637</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.2972104571345114</v>
+        <v>-0.1247211066488175</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.04618434093161561</v>
+        <v>-0.06971780886886425</v>
       </c>
       <c r="L28" s="5" t="n">
-        <v>-0.01615211613167045</v>
+        <v>-0.005198427792570182</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1871,44 +1872,40 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FTEC</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D29" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>U.S. Industrials</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.6048478430994644</v>
+        <v>0.4923155200376177</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3734030977557887</v>
+        <v>0.1604974622842956</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3305417626294094</v>
-      </c>
-      <c r="I29" s="3" t="n">
-        <v>0.3171061861337547</v>
+        <v>0.3519481311025898</v>
+      </c>
+      <c r="I29" s="5" t="n">
+        <v>-0.1068821865254341</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>-0.05535983397527067</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>0.03221344592872999</v>
+        <v>-0.1868242199567499</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>-0.1416109571172346</v>
       </c>
       <c r="L29" s="5" t="n">
-        <v>-0.01384058978995695</v>
+        <v>-0.007072802715956228</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1917,82 +1914,86 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VGT</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>VDE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5976899401838969</v>
+        <v>0.5571369387095066</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.368564812127385</v>
+        <v>0.4691906654988622</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3272957586619534</v>
+        <v>0.3372831587644558</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.3153315133162373</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>-0.0549311064558291</v>
+        <v>0.1571967832430097</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.1038800028248377</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.03109258294250483</v>
+        <v>0.09863842662632383</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.01469001576894347</v>
+        <v>-0.006131274976733825</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
-      <c r="A31" t="n">
+      <c r="A31" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" s="12" t="inlineStr">
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C31" s="14" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Silver Miners</t>
+      <c r="E31" s="14" t="inlineStr">
+        <is>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>1.756874796904122</v>
+        <v>0.5386769266495128</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.6452385677263626</v>
+        <v>0.4692768907322107</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3203370504868808</v>
-      </c>
-      <c r="I31" s="5" t="n">
-        <v>-0.1125164580557103</v>
+        <v>0.3332622677259882</v>
+      </c>
+      <c r="I31" s="3" t="n">
+        <v>0.1635430486960077</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.02726746029020521</v>
+        <v>0.1063717891203011</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.246074680036944</v>
+        <v>0.1020164046479834</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.03583460949464012</v>
+        <v>-0.004322989038134994</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2001,40 +2002,40 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>AIRR</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>U.S. Industrials</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.4607671167741831</v>
+        <v>1.883533456042781</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.159680317870067</v>
+        <v>0.6625556243375015</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3149604735867568</v>
+        <v>0.3304169281812877</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>-0.09398372660279408</v>
-      </c>
-      <c r="J32" s="5" t="n">
-        <v>-0.1765665036105287</v>
-      </c>
-      <c r="K32" s="5" t="n">
-        <v>-0.1180873180873181</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>-0.02005174644243213</v>
+        <v>-0.08490328747342157</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.1240763643823657</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.2496500827077235</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.04157386785449124</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2043,7 +2044,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>DRIV</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2051,36 +2052,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D33" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Autonomous/EV</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.5211389648251512</v>
+        <v>1.133863293655958</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.3178307583347912</v>
+        <v>0.4672031375354084</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.312409180134178</v>
+        <v>0.3276218994510833</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.0967546346421817</v>
+        <v>0.01449609397562712</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.1982576654052713</v>
+        <v>-0.07195555709908608</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.004131012097964071</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>-0.01390901188061422</v>
+        <v>0.1051362877804563</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.02962771011488297</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2089,44 +2090,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CALF</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D34" s="17" t="inlineStr">
+          <t>SPMO</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Small Cap Value</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.4753437351024499</v>
+        <v>0.5067735066529344</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.3398451148986406</v>
+        <v>0.2684498581282948</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.2888256851959499</v>
+        <v>0.3191494568881006</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.2558006250783045</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0.1284236671078314</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0.03958598147811876</v>
+        <v>0.2139942620993247</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>-0.06129951109981679</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>-0.03843355163061435</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-0.005731156651615166</v>
+        <v>-0.001236773395629887</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2135,7 +2132,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ROBO</t>
+          <t>CALF</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2143,36 +2140,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D35" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Small Cap Value</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.3990895478067082</v>
+        <v>0.5422710015956773</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.240635819021678</v>
+        <v>0.3457197173110236</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.2789134350732609</v>
+        <v>0.3079631197695643</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.05308196282925515</v>
-      </c>
-      <c r="J35" s="5" t="n">
-        <v>-0.1281824219614789</v>
-      </c>
-      <c r="K35" s="5" t="n">
-        <v>-0.02992979430964393</v>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v>-0.0208851317752361</v>
+        <v>0.2604809199765588</v>
+      </c>
+      <c r="J35" s="3" t="n">
+        <v>0.1510016524149791</v>
+      </c>
+      <c r="K35" s="3" t="n">
+        <v>0.02886671418389164</v>
+      </c>
+      <c r="L35" s="3" t="n">
+        <v>0.00785477395706069</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2181,40 +2178,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SCHA</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XOP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.3566091711933668</v>
+        <v>0.5965486491281249</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2483219407600468</v>
+        <v>0.4611339917628601</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.2664780034187713</v>
+        <v>0.3074624785783919</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.1209713268146877</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>-0.01409544249402861</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>-0.01433586892919847</v>
+        <v>0.2059334776937514</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.1283926642301956</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.1175341669089853</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.01375878220140514</v>
+        <v>-0.002905770029057675</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2223,44 +2224,40 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>XAR</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>SCHA</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.524935376087668</v>
+        <v>0.4018852880506596</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.1638817146351643</v>
+        <v>0.2602494444435173</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.2627292874018476</v>
-      </c>
-      <c r="I37" s="5" t="n">
-        <v>-0.112421045432338</v>
+        <v>0.3049259387812489</v>
+      </c>
+      <c r="I37" s="3" t="n">
+        <v>0.1177764975242372</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.09673080451743887</v>
+        <v>-0.003598142148407479</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.07828089025326168</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>-0.0168018088258225</v>
+        <v>-0.03423680456490719</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.003557663800771049</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2269,40 +2266,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>FNDX</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" s="17" t="inlineStr">
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Fundamental Equity</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.3467689284073916</v>
+        <v>0.3882992372863519</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2763128432438211</v>
+        <v>0.2214101878258636</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.2624999336849052</v>
+        <v>0.301400531657773</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1357016960318809</v>
-      </c>
-      <c r="J38" s="3" t="n">
-        <v>0.0441830746452998</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0.01094091903719918</v>
+        <v>0.1753772026645555</v>
+      </c>
+      <c r="J38" s="5" t="n">
+        <v>-0.106479820708881</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>-0.06146481570129259</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.001235330450895633</v>
+        <v>-0.008195062727640701</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2311,40 +2312,44 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SPMO</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XAR</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D39" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.4741596418068887</v>
+        <v>0.5453121453961143</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.258171446360282</v>
+        <v>0.1522523427812272</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2583445931911303</v>
-      </c>
-      <c r="I39" s="3" t="n">
-        <v>0.2243315562302439</v>
+        <v>0.3001554535006254</v>
+      </c>
+      <c r="I39" s="5" t="n">
+        <v>-0.1288991344421934</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.05681041114621221</v>
+        <v>-0.08559011374412528</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.000137598899208724</v>
+        <v>-0.1137580204899145</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.01196546332177573</v>
+        <v>-0.008093953340739479</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2353,40 +2358,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>DBC</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Developed ex-US Hedged</t>
+          <t>Broad Commodities</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.3409401081149401</v>
+        <v>0.5008344859216418</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2638570947590639</v>
+        <v>0.453621662594011</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2571186798797769</v>
+        <v>0.2965352636432406</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.09792023057307175</v>
+        <v>0.214231063504208</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.03918875492460661</v>
+        <v>0.04787058435127101</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.005360205831903997</v>
+        <v>0.1211586012009891</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.007198814312936563</v>
+        <v>-0.00595051675540248</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2395,44 +2400,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>XME</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D41" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>QQQM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>1.006948577699148</v>
+        <v>0.4310642030995158</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.4126513318074136</v>
+        <v>0.2545135127512785</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2569768624668831</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>-0.01064862636335018</v>
+        <v>0.2863673222269516</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0.1591883525169222</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.1270099231368976</v>
-      </c>
-      <c r="K41" s="3" t="n">
-        <v>0.1238483173310057</v>
+        <v>-0.05095612743574551</v>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>-0.02476260779116191</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.01904681283331922</v>
+        <v>-0.002573781743308134</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2441,86 +2442,86 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>PAVE</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>ARKQ</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.3543004847147524</v>
+        <v>0.7053086207098791</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.1678837190124787</v>
+        <v>0.2288176771474049</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2476797102112518</v>
+        <v>0.2861013719989147</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-0.005631270180517789</v>
+        <v>-0.02795436022819886</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.05160049612052953</v>
+        <v>-0.1408917380969532</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.0639555092109837</v>
+        <v>-0.04454057518224785</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.01535648994515548</v>
+        <v>-0.007324178110695079</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
-      <c r="A43" t="n">
+      <c r="A43" s="14" t="n">
         <v>42</v>
       </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>MTUM</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Momentum Factor</t>
+      <c r="B43" s="15" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="inlineStr"/>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E43" s="14" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3715837981169965</v>
+        <v>0.4309344316293171</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2234189833993132</v>
+        <v>0.2541814008874828</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2469716995752658</v>
+        <v>0.2859094421059849</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2010558036747441</v>
+        <v>0.1586688511899681</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.09085939688912337</v>
+        <v>-0.05031395536529237</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.01888793160580549</v>
+        <v>-0.02467362022518482</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>-0.01424956718604353</v>
+        <v>-0.002331694081736391</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2529,40 +2530,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>FNDX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
       <c r="D44" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Fundamental Equity</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4670657268266485</v>
+        <v>0.3695598883203353</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1414991140497084</v>
+        <v>0.2870441649126694</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2465058885527058</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>-0.07888584528726006</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>-0.01235846347926839</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>-0.08424089726918083</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>-0.01313772717319905</v>
+        <v>0.2838721521833716</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0.1347756685434189</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.04940774140611204</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.002470660901791266</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.003400309119010902</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2571,40 +2572,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D45" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.2876823172091394</v>
+        <v>0.391001450077654</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2918203085741768</v>
+        <v>0.1768848517237445</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2461480182739115</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>0.1194586189022169</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0.08332018290398069</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0.03665077473182343</v>
+        <v>0.2809720292452051</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>-0.006735809548506499</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>-0.05892164019710389</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>-0.08125640150221913</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-0.002866150759530006</v>
+        <v>-0.001854599406528212</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2628,25 +2629,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4703214814586738</v>
+        <v>0.4673597628419217</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2630547773630163</v>
+        <v>0.2812377962033576</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2450036268054487</v>
+        <v>0.276994115950959</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.08951567604871391</v>
+        <v>0.08289355028941636</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.001788643370144616</v>
+        <v>0.0163443636014966</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.01449887387387361</v>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v>-0.01165660998354368</v>
+        <v>0.003323179174743673</v>
+      </c>
+      <c r="L46" s="3" t="n">
+        <v>0.004853695742615294</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2663,7 +2664,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2674,25 +2675,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3508207403973176</v>
+        <v>0.4054692115784004</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2119982365920166</v>
+        <v>0.2262912195102045</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2352179699994568</v>
+        <v>0.2757304985180495</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1212510877994166</v>
+        <v>0.1162532474476856</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-0.02831792355263485</v>
+        <v>-0.00861001476495471</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.01879808582079689</v>
-      </c>
-      <c r="L47" s="5" t="n">
-        <v>-0.01557070479323064</v>
+        <v>-0.03875370155787305</v>
+      </c>
+      <c r="L47" s="3" t="n">
+        <v>0.005088715974260305</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2701,82 +2702,82 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>QQQM</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Developed ex-US Hedged</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4025821082317258</v>
+        <v>0.3396964144457804</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2461392092131427</v>
+        <v>0.2663975533575162</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2338550176542991</v>
+        <v>0.2717910693428549</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1782513526176568</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>-0.05127453776888091</v>
-      </c>
-      <c r="K48" s="3" t="n">
-        <v>0.009955944080202617</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>-0.01368656413036118</v>
+        <v>0.08925721152505939</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.04530471319483786</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>-0.004240882103477395</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.001065870816457037</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
-      <c r="A49" s="14" t="n">
+      <c r="A49" t="n">
         <v>48</v>
       </c>
-      <c r="B49" s="15" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C49" s="14" t="inlineStr"/>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E49" s="14" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4017830391974024</v>
+        <v>0.472222136041198</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2455916169046999</v>
+        <v>0.1321780527805594</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2332428059717051</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>0.1781468277202189</v>
+        <v>0.2691432420816064</v>
+      </c>
+      <c r="I49" s="5" t="n">
+        <v>-0.09340327044917529</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.05133343380735356</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>0.01001328438584714</v>
+        <v>-0.00503817068072232</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>-0.1079194095352085</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.01350521792510739</v>
+        <v>-0.008249800408054675</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2785,40 +2786,40 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>SCHD</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
       <c r="D50" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.2901412958989593</v>
+        <v>0.297749646060073</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.1500183044689212</v>
+        <v>0.299256184647273</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2204493461181274</v>
-      </c>
-      <c r="I50" s="5" t="n">
-        <v>-0.0110535539521307</v>
-      </c>
-      <c r="J50" s="5" t="n">
-        <v>-0.006747684626161821</v>
-      </c>
-      <c r="K50" s="5" t="n">
-        <v>-0.05770910679187591</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>-0.01450351167703989</v>
+        <v>0.260527998002585</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>0.1244561628946537</v>
+      </c>
+      <c r="J50" s="3" t="n">
+        <v>0.0864340667295167</v>
+      </c>
+      <c r="K50" s="3" t="n">
+        <v>0.03072378138847864</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.002298190175237025</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2827,44 +2828,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr"/>
       <c r="D51" s="16" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4226723527792104</v>
+        <v>0.4378614081250456</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1203695557801072</v>
+        <v>0.2351867588879453</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2155714506840796</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>-0.09254908191182398</v>
+        <v>0.2573872398356056</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0.149793314569838</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.0447003084704849</v>
+        <v>-0.02567566486240636</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.07831863347102808</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>-0.01362088535754813</v>
+        <v>-0.01765604122924214</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.0007778317938746948</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2873,40 +2870,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ONEQ</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D52" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.397624894260995</v>
+        <v>0.3034570636473846</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.225060698092582</v>
+        <v>0.1563845827198231</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2152973608155295</v>
-      </c>
-      <c r="I52" s="3" t="n">
-        <v>0.1636063514863231</v>
+        <v>0.2540001525334519</v>
+      </c>
+      <c r="I52" s="5" t="n">
+        <v>-0.01803093872764194</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.03436063548310431</v>
-      </c>
-      <c r="K52" s="3" t="n">
-        <v>0.008033702361124773</v>
+        <v>-0.009980428297433397</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>-0.07784334763948508</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-0.009625565501973243</v>
+        <v>-0.004863081109245715</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2915,7 +2912,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VHT</t>
+          <t>PPA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2923,36 +2920,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D53" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D53" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.2114573567370326</v>
+        <v>0.4230873344825417</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2816012785818076</v>
+        <v>0.1099233707084495</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2144802282674094</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>0.118207868938331</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>0.1812593241589906</v>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>0.05526730592407736</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>0.004344293036629754</v>
+        <v>0.2462702524154461</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>-0.1091011399245219</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-0.03749760480569375</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>-0.1094039446442192</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>-0.01005329457364335</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2961,7 +2958,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ARKQ</t>
+          <t>XMMO</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2969,36 +2966,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D54" s="16" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.6542503798247703</v>
+        <v>0.2804473765205426</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2303867455446755</v>
+        <v>0.1527476680657531</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.21401161001921</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>-0.005130751406818956</v>
+        <v>0.2278719265107476</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0.01422806216606598</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.152485019386676</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>0.01348845051424719</v>
+        <v>-0.1184765118849228</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>-0.06118248721466879</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.01861224489795921</v>
+        <v>-0.002518057120137751</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3007,44 +3004,40 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ARGT</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>VBK</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" s="16" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.1649510757411736</v>
+        <v>0.3062093855662442</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2021927321655148</v>
+        <v>0.187191711913302</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2006786355255077</v>
+        <v>0.2265889806389327</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1083053621369769</v>
+        <v>0.08284028370561924</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-0.02224350252690321</v>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>0.001261034047919329</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>0.007720782654680125</v>
+        <v>-0.02683496106553351</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>-0.03211937278705113</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>-0.0005803325305400175</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3053,44 +3046,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D56" s="17" t="inlineStr">
+          <t>IVV</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>US Large Blend</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2494125777449336</v>
+        <v>0.3306144322014664</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1568475339910902</v>
+        <v>0.2058936422840127</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.1992507080016339</v>
+        <v>0.218570207380995</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.01802297821538734</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>-0.1109748274081872</v>
+        <v>0.1199453863761764</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0.01523849824827961</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.03535805626598465</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>-0.009649468294604113</v>
+        <v>-0.01040281882832761</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0.001803096622460254</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3099,82 +3088,82 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>VBK</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D57" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.2701079639661315</v>
+        <v>0.3309580626824351</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1814859871201451</v>
+        <v>0.2059537473599964</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.1885841615312283</v>
+        <v>0.2185173768342532</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.09012543735745493</v>
-      </c>
-      <c r="J57" s="5" t="n">
-        <v>-0.03685346670009493</v>
+        <v>0.1202111325157036</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0.01493207944041552</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.005971957763545088</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>-0.01624600274097765</v>
+        <v>-0.01031058704053722</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.001984920317587235</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
-      <c r="A58" t="n">
+      <c r="A58" s="14" t="n">
         <v>57</v>
       </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>IVV</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr"/>
-      <c r="D58" s="17" t="inlineStr">
+      <c r="B58" s="15" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C58" s="14" t="inlineStr"/>
+      <c r="D58" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>US Large Blend</t>
+      <c r="E58" s="14" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3041187800061069</v>
+        <v>0.329902956186837</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.193439155771703</v>
+        <v>0.2053468668709282</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.1883350528676975</v>
+        <v>0.218043206151729</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1248439142255169</v>
+        <v>0.1200010397009772</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.00469636168495513</v>
-      </c>
-      <c r="K58" s="3" t="n">
-        <v>0.004295171544160148</v>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v>-0.007979344526039878</v>
+        <v>0.01460598534739521</v>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>-0.01042355412080442</v>
+      </c>
+      <c r="L58" s="3" t="n">
+        <v>0.001982199585182087</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3183,82 +3172,90 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VOO</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" s="17" t="inlineStr">
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D59" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>Health Care</t>
+        </is>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>0.2305331451857311</v>
+      </c>
+      <c r="G59" s="3" t="n">
+        <v>0.2986403650153284</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>0.2136427912548644</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>0.1324765153869347</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0.1896589944165297</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0.07003508311747941</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0.01480145526913157</v>
+      </c>
+    </row>
+    <row r="60" ht="21" customHeight="1">
+      <c r="A60" t="n">
+        <v>59</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D60" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
-      <c r="F59" s="3" t="n">
-        <v>0.3036340996460296</v>
-      </c>
-      <c r="G59" s="3" t="n">
-        <v>0.1930418346447433</v>
-      </c>
-      <c r="H59" s="3" t="n">
-        <v>0.1880772956866044</v>
-      </c>
-      <c r="I59" s="3" t="n">
-        <v>0.124401231257762</v>
-      </c>
-      <c r="J59" s="3" t="n">
-        <v>0.004420169470330304</v>
-      </c>
-      <c r="K59" s="3" t="n">
-        <v>0.004178632969557672</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>-0.007916128757678553</v>
-      </c>
-    </row>
-    <row r="60" ht="21" customHeight="1">
-      <c r="A60" s="14" t="n">
-        <v>59</v>
-      </c>
-      <c r="B60" s="15" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="C60" s="14" t="inlineStr"/>
-      <c r="D60" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E60" s="14" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3024262240319064</v>
+        <v>0.3523625492389717</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1925903186078104</v>
+        <v>0.2048393740893546</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.1876058443840174</v>
+        <v>0.2126543423440079</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1242975117835829</v>
+        <v>0.134712232244437</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.004265713431707008</v>
-      </c>
-      <c r="K60" s="3" t="n">
-        <v>0.004197077883511424</v>
-      </c>
-      <c r="L60" s="5" t="n">
-        <v>-0.008082915064206886</v>
+        <v>0.01466459281406696</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>-0.006444514303678206</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0.003891050583657574</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3267,7 +3264,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>OEF</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3275,36 +3272,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3184951692328024</v>
+        <v>0.2445476442114105</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1920832530944507</v>
+        <v>0.1476580932643332</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1836518298209084</v>
+        <v>0.2053030203232722</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1379851902448568</v>
+        <v>0.1103564677217599</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.001161438913520607</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>0.00712322919723607</v>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v>-0.006526659297857784</v>
+        <v>0.09963895845012827</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>-0.04782608695652169</v>
+      </c>
+      <c r="L61" s="3" t="n">
+        <v>0.0140403286034354</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3313,7 +3310,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>KBE</t>
+          <t>ARGT</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3321,36 +3318,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.2114903255245717</v>
+        <v>0.1931104313008116</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.121696765669709</v>
+        <v>0.2341280431721937</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1827460513610628</v>
+        <v>0.2019645981679137</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.09952825541758781</v>
+        <v>0.1005158926864174</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.05855114269373729</v>
-      </c>
-      <c r="K62" s="5" t="n">
-        <v>-0.05161656267725467</v>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v>-0.01371479132871267</v>
+        <v>0.02014044569721807</v>
+      </c>
+      <c r="K62" s="3" t="n">
+        <v>0.02675906183368881</v>
+      </c>
+      <c r="L62" s="3" t="n">
+        <v>0.00890425309029963</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3363,7 +3360,7 @@
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
-      <c r="D63" s="17" t="inlineStr">
+      <c r="D63" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3374,25 +3371,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.288564214699945</v>
+        <v>0.3242921586687793</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2606375093602329</v>
+        <v>0.2723952948648507</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1819574307598728</v>
+        <v>0.2005423840960121</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1203500295939488</v>
+        <v>0.1275107971594809</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.1043481450966035</v>
+        <v>0.1153477948774517</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.06656760772659731</v>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v>-0.004438280166435438</v>
+        <v>0.05985037406483795</v>
+      </c>
+      <c r="L63" s="3" t="n">
+        <v>0.005567153792623625</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3416,25 +3413,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3966084097366138</v>
+        <v>0.4115600107267119</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2075807444955033</v>
+        <v>0.2104198425636161</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.176116734332197</v>
+        <v>0.1974581803285855</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.09925893420325216</v>
-      </c>
-      <c r="J64" s="5" t="n">
-        <v>-0.007810555444056955</v>
+        <v>0.09341746298461184</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0.007328725120322455</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.02675245513037594</v>
+        <v>0.0108243130724397</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.00198281559814939</v>
+        <v>0.0003295978905735186</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3443,40 +3440,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>IAU</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D65" s="16" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.5104882123630965</v>
+        <v>0.2552628529695071</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.2499231950844856</v>
+        <v>0.1852104962974932</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1703533026113673</v>
-      </c>
-      <c r="I65" s="5" t="n">
-        <v>-0.1516889074228523</v>
-      </c>
-      <c r="J65" s="5" t="n">
-        <v>-0.03612887941246146</v>
-      </c>
-      <c r="K65" s="3" t="n">
-        <v>0.06798792492453076</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-0.02795364950424073</v>
+        <v>0.1964014649108354</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0.08409762807685572</v>
+      </c>
+      <c r="J65" s="3" t="n">
+        <v>0.04666629576771109</v>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>-0.00935385733097216</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.002665563674801197</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3485,82 +3482,82 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RSP</t>
+          <t>MGK</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="17" t="inlineStr">
+      <c r="D66" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Equal Weight</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2376176269895058</v>
+        <v>0.3547634802913204</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1718058386303849</v>
+        <v>0.1746047117420475</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1701350640467429</v>
+        <v>0.1925416352539404</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.08470132303322919</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>0.03914502992800339</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>0.001427847634839274</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-0.008979443001048359</v>
+        <v>0.1443818795682543</v>
+      </c>
+      <c r="J66" s="5" t="n">
+        <v>-0.01753605964434324</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>-0.01504092015040914</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.0002246181491463162</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
-      <c r="A67" s="14" t="n">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr"/>
-      <c r="D67" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E67" s="14" t="inlineStr">
-        <is>
-          <t>Gold</t>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>VUG</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" s="16" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.5078436586014361</v>
+        <v>0.3336315119817748</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.2480586034520704</v>
+        <v>0.1575451394693657</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1686421228031565</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>-0.1520271713589951</v>
+        <v>0.1799278772920569</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0.1325792718283929</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-0.03636363636363626</v>
-      </c>
-      <c r="K67" s="3" t="n">
-        <v>0.06795620241586198</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>-0.02803486606924244</v>
+        <v>-0.01611466012902874</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>-0.01896958132225834</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.0003433672885428951</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3569,40 +3566,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>MGK</t>
+          <t>SCHG</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" s="17" t="inlineStr">
+      <c r="D68" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3221990776371348</v>
+        <v>0.3357888476438622</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1628737640874511</v>
+        <v>0.1710462189238553</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1534630738531815</v>
+        <v>0.1783445239709731</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1558257531046039</v>
-      </c>
-      <c r="J68" s="5" t="n">
-        <v>-0.02965035845982311</v>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>0.008158640226628933</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>-0.01034482758620692</v>
+        <v>0.1427573697324755</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0.01922076956315188</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>-0.006193693693693825</v>
+      </c>
+      <c r="L68" s="3" t="n">
+        <v>0.0008505812305072968</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3611,40 +3608,44 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SCHG</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D69" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.2997892992291971</v>
+        <v>0.08644211192315909</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1594795794548101</v>
+        <v>0.1646478807575276</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1469766782007569</v>
+        <v>0.1598525611471451</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1527295418949459</v>
+        <v>0.1015234329573207</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.005023418576658445</v>
+        <v>0.2134255700743017</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.01090074584050504</v>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v>-0.01177790241166554</v>
+        <v>0.004134421711014635</v>
+      </c>
+      <c r="L69" s="3" t="n">
+        <v>0.007981270618282466</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3653,40 +3654,44 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VUG</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
-      <c r="D70" s="17" t="inlineStr">
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D70" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2995001810068219</v>
+        <v>0.2397483228173023</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1467311626983931</v>
+        <v>0.1278031197466372</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1441034560927599</v>
+        <v>0.1565501589155687</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1425473418021843</v>
-      </c>
-      <c r="J70" s="5" t="n">
-        <v>-0.02957808770964998</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>0.00229673863114388</v>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v>-0.0108794197642792</v>
+        <v>0.09782883278221499</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0.04162419932796335</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>-0.02485585164407045</v>
+      </c>
+      <c r="L70" s="3" t="n">
+        <v>0.00691930163327692</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3695,90 +3700,82 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D71" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr"/>
+      <c r="D71" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.09321836297248343</v>
+        <v>0.5105369250503942</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1106441209428966</v>
+        <v>0.2367591897974493</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1387235063658157</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>0.07148234107640872</v>
-      </c>
-      <c r="J71" s="3" t="n">
-        <v>0.1153163885010622</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>-0.0246586509068677</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>-0.002501042100875317</v>
+        <v>0.1506376594148535</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>-0.1471288153129849</v>
+      </c>
+      <c r="J71" s="5" t="n">
+        <v>-0.01387725804522066</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.07484678576085546</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0.01327596803933639</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
-      <c r="A72" t="n">
+      <c r="A72" s="14" t="n">
         <v>71</v>
       </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>SPGP</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D72" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>GARP Factor</t>
+      <c r="B72" s="15" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C72" s="14" t="inlineStr"/>
+      <c r="D72" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E72" s="14" t="inlineStr">
+        <is>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.1963929869818803</v>
+        <v>0.507647896828372</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1106924090820809</v>
+        <v>0.2351423569519948</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1369799286658946</v>
-      </c>
-      <c r="I72" s="3" t="n">
-        <v>0.09694283527750969</v>
-      </c>
-      <c r="J72" s="3" t="n">
-        <v>0.02807979603896715</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>-0.02312047813777918</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>-0.009251874302121488</v>
+        <v>0.149175343223072</v>
+      </c>
+      <c r="I72" s="5" t="n">
+        <v>-0.147626112759644</v>
+      </c>
+      <c r="J72" s="5" t="n">
+        <v>-0.01402407629882074</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0.07480756895445784</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.01361058601134202</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3787,44 +3784,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D73" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>IGF</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.06179858200518318</v>
+        <v>0.2654653205051096</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1445093901754804</v>
+        <v>0.1085172005431787</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1351281656658454</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>0.09017059301380992</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>0.2043589743589744</v>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>0.008264462809917328</v>
+        <v>0.1481871797130763</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>-0.0436609508499769</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-0.01697586178557564</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>-0.03455009764158024</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.01115789473684214</v>
+        <v>-0.008025929927458098</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3833,40 +3826,44 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IGF</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr"/>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>IAK</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D74" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.2681715135973131</v>
+        <v>0.09092591174013953</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.105009928547539</v>
+        <v>0.1206932713711621</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1343812324743165</v>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>-0.03171472760208316</v>
-      </c>
-      <c r="J74" s="5" t="n">
-        <v>-0.01588634438357084</v>
+        <v>0.144848487075399</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>0.07947031450855313</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0.1308163682630588</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.02589191630287535</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>-0.006601166717838614</v>
+        <v>-0.02109905020352787</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>0.003267973856209139</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3875,44 +3872,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>XRT</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D75" s="19" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+          <t>VONG</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" s="16" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1730298983014724</v>
+        <v>0.2690915058581829</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.02755115089512761</v>
+        <v>0.1033967283063204</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.09508073014295459</v>
+        <v>0.1305265373396409</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.006860864969585823</v>
-      </c>
-      <c r="J75" s="3" t="n">
-        <v>0.02754085233746495</v>
+        <v>0.07384019052346646</v>
+      </c>
+      <c r="J75" s="5" t="n">
+        <v>-0.04068006368136257</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.0616663022086158</v>
-      </c>
-      <c r="L75" s="5" t="n">
-        <v>-0.003252032520325243</v>
+        <v>-0.02399749863206446</v>
+      </c>
+      <c r="L75" s="3" t="n">
+        <v>0.0004006089255668144</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3921,11 +3914,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>IWF</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" s="17" t="inlineStr">
+      <c r="D76" s="16" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3936,25 +3929,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2377170755708811</v>
+        <v>0.2682238815168374</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.09240663956758088</v>
+        <v>0.1028763521667317</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.09065402182401017</v>
+        <v>0.1298733254291993</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.08223974630056841</v>
+        <v>0.07304418170882099</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>-0.05483624628537553</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>0.001606941989394262</v>
-      </c>
-      <c r="L76" s="5" t="n">
-        <v>-0.01368779175567691</v>
+        <v>-0.04101042160552082</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>-0.02389380530973451</v>
+      </c>
+      <c r="L76" s="3" t="n">
+        <v>0.0009900173253032385</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3963,40 +3956,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IWF</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D77" s="6" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2348432267564229</v>
+        <v>0.1277215986326417</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.09128206287718088</v>
+        <v>0.05672087389618063</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.08902958173682984</v>
-      </c>
-      <c r="I77" s="3" t="n">
-        <v>0.08169154453630156</v>
+        <v>0.1191826731241958</v>
+      </c>
+      <c r="I77" s="5" t="n">
+        <v>-0.05635570632389342</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.05505753071901587</v>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>0.002068337883676774</v>
+        <v>-0.1299350746521507</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>-0.05581019142626042</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.01295737918670026</v>
+        <v>-0.003698435277382561</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4005,40 +3998,44 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VFH</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr"/>
-      <c r="D78" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>XRT</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.1353620271217815</v>
+        <v>0.218648859081473</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.0763022593970204</v>
+        <v>0.03456826352379427</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.08386175351447944</v>
+        <v>0.1037705537941589</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1232166232839744</v>
+        <v>0.01211572988408771</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.1118025399666929</v>
+        <v>0.04050338233284911</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.006974592555689885</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>-0.01014472190692395</v>
+        <v>-0.06269626421223595</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0.007448789571694592</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4047,40 +4044,40 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>VFH</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D79" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.118685463077576</v>
+        <v>0.158777719777873</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.03641991937313471</v>
+        <v>0.09617930816011722</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.08152405606662572</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>-0.0847556647662292</v>
-      </c>
-      <c r="J79" s="5" t="n">
-        <v>-0.02547954073217784</v>
+        <v>0.1018533554901666</v>
+      </c>
+      <c r="I79" s="3" t="n">
+        <v>0.1297070276484318</v>
+      </c>
+      <c r="J79" s="3" t="n">
+        <v>0.1395429727621096</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.04170423805229939</v>
+        <v>-0.005149548532731307</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.00663035756571162</v>
+        <v>0.01053310404127261</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4089,40 +4086,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>XLP</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="11" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.06693629256219924</v>
+        <v>0.1420876743518373</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.08409585494392169</v>
+        <v>0.09491829672076713</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.07964293217393736</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>-0.0165922991618136</v>
+        <v>0.09681327473516799</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.1316592999298891</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.04853034637554421</v>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>0.004124440254536843</v>
+        <v>0.1398152494026546</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>-0.001727712508638568</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.002706519180983635</v>
+        <v>0.01013986013986012</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4131,40 +4128,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D81" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.1206975796563539</v>
+        <v>0.06280986282613599</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.07552062690084105</v>
+        <v>0.08737247052464592</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.07928250387496072</v>
-      </c>
-      <c r="I81" s="3" t="n">
-        <v>0.1262498781490413</v>
+        <v>0.08788219628136673</v>
+      </c>
+      <c r="I81" s="5" t="n">
+        <v>-0.008654199156339804</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.115046645896475</v>
+        <v>0.04578956232590259</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.003485535029627118</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>-0.009183850285912287</v>
+        <v>-0.0004685486704931741</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>0.0009384164222874247</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4173,44 +4170,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D82" s="20" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F82" s="5" t="n">
-        <v>-0.1410586552217454</v>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F82" s="3" t="n">
+        <v>0.1062203031109124</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.06985032074126885</v>
+        <v>0.02984352463759543</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.07875980042765507</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>0.02562350529552448</v>
-      </c>
-      <c r="J82" s="3" t="n">
-        <v>0.01866304716661005</v>
+        <v>0.07901182593264466</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>-0.09741809265038093</v>
+      </c>
+      <c r="J82" s="5" t="n">
+        <v>-0.03068336263727234</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.008259002312520636</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>0.005021760964178057</v>
+        <v>-0.04556789843572884</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>-0.01080827067669177</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4219,132 +4212,136 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BOTZ</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D83" s="16" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Mid Growth</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1040248613093895</v>
+        <v>0.1721535674414156</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.05273997456591295</v>
+        <v>0.03577383951086577</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.07610091852498591</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>-0.04694910221045445</v>
+        <v>0.07657110362803721</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0.07038780282207635</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-0.1346560541493818</v>
+        <v>-0.02006744862674148</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.02170887837461732</v>
+        <v>-0.03789555931761956</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.02061855670103097</v>
+        <v>-0.003842782983887405</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
-      <c r="A84" s="14" t="n">
+      <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="15" t="inlineStr">
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>EUO</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F84" s="5" t="n">
+        <v>-0.1213805206200643</v>
+      </c>
+      <c r="G84" s="3" t="n">
+        <v>0.05737416402675111</v>
+      </c>
+      <c r="H84" s="3" t="n">
+        <v>0.06335797254487852</v>
+      </c>
+      <c r="I84" s="3" t="n">
+        <v>0.03088538091969806</v>
+      </c>
+      <c r="J84" s="3" t="n">
+        <v>0.01417960837272103</v>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>-0.005627275736511117</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>0.001667222407469193</v>
+      </c>
+    </row>
+    <row r="85" ht="21" customHeight="1">
+      <c r="A85" s="14" t="n">
+        <v>84</v>
+      </c>
+      <c r="B85" s="15" t="inlineStr">
         <is>
           <t>UUP</t>
         </is>
       </c>
-      <c r="C84" s="14" t="inlineStr">
+      <c r="C85" s="14" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D84" s="20" t="inlineStr">
+      <c r="D85" s="20" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E84" s="14" t="inlineStr">
+      <c r="E85" s="14" t="inlineStr">
         <is>
           <t>US Dollar Basket</t>
         </is>
       </c>
-      <c r="F84" s="5" t="n">
-        <v>-0.007720339743546356</v>
-      </c>
-      <c r="G84" s="3" t="n">
-        <v>0.06551331083165923</v>
-      </c>
-      <c r="H84" s="3" t="n">
-        <v>0.06437978603290229</v>
-      </c>
-      <c r="I84" s="3" t="n">
-        <v>0.02694828841951935</v>
-      </c>
-      <c r="J84" s="3" t="n">
-        <v>0.01585014409221897</v>
-      </c>
-      <c r="K84" s="3" t="n">
-        <v>0.001064962726304408</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>0.002844950213371167</v>
-      </c>
-    </row>
-    <row r="85" ht="21" customHeight="1">
-      <c r="A85" t="n">
-        <v>84</v>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>Denmark Equity</t>
-        </is>
-      </c>
-      <c r="F85" s="3" t="n">
-        <v>0.08413490543867841</v>
+      <c r="F85" s="5" t="n">
+        <v>-0.000662708324130179</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.09490460983801619</v>
+        <v>0.0559241217753339</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.05789559726861548</v>
+        <v>0.05705024063965181</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1445624896195674</v>
+        <v>0.02626778547975195</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.08127064926975214</v>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>0.03498361526879812</v>
+        <v>0.009691313711414296</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>-0.001065340909090939</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.004005795619193675</v>
+        <v>-0.002835873803615829</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4353,7 +4350,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VOT</t>
+          <t>VCR</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4361,36 +4358,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D86" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D86" s="19" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
+          <t>Consumer Discretionary</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.1511328481466314</v>
+        <v>0.1158204837995478</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.0318149860695629</v>
+        <v>0.01525729915819407</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.04970753027656505</v>
+        <v>0.05622885704625968</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.08161622003060232</v>
+        <v>0.01030523414199824</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.02525071143568769</v>
+        <v>-0.009787732086473544</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.01704526612502066</v>
-      </c>
-      <c r="L86" s="5" t="n">
-        <v>-0.01860742310366503</v>
+        <v>-0.03879041707177222</v>
+      </c>
+      <c r="L86" s="3" t="n">
+        <v>0.00280891570652031</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4399,132 +4396,132 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Denmark Equity</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.1182661886893694</v>
+      </c>
+      <c r="G87" s="3" t="n">
+        <v>0.1059186102379364</v>
+      </c>
+      <c r="H87" s="3" t="n">
+        <v>0.04419292036419109</v>
+      </c>
+      <c r="I87" s="3" t="n">
+        <v>0.1212582744476014</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.1055951014415892</v>
+      </c>
+      <c r="K87" s="3" t="n">
+        <v>0.05911330049261077</v>
+      </c>
+      <c r="L87" s="3" t="n">
+        <v>0.01241438356164393</v>
+      </c>
+    </row>
+    <row r="88" ht="21" customHeight="1">
+      <c r="A88" s="14" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="15" t="inlineStr">
+        <is>
+          <t>HYG</t>
+        </is>
+      </c>
+      <c r="C88" s="14" t="inlineStr"/>
+      <c r="D88" s="18" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E88" s="14" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="F88" s="3" t="n">
+        <v>0.08681470151860204</v>
+      </c>
+      <c r="G88" s="3" t="n">
+        <v>0.04503172583351378</v>
+      </c>
+      <c r="H88" s="3" t="n">
+        <v>0.04406074666604187</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0.01505170385670751</v>
+      </c>
+      <c r="J88" s="3" t="n">
+        <v>0.008803343036953182</v>
+      </c>
+      <c r="K88" s="3" t="n">
+        <v>0.0009300025602652084</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>0.001137800252844601</v>
+      </c>
+    </row>
+    <row r="89" ht="21" customHeight="1">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
           <t>USDU</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="20" t="inlineStr">
+      <c r="D89" s="20" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>US Dollar Basket</t>
         </is>
       </c>
-      <c r="F87" s="5" t="n">
-        <v>-0.008466628844466029</v>
-      </c>
-      <c r="G87" s="3" t="n">
-        <v>0.04481315958143561</v>
-      </c>
-      <c r="H87" s="3" t="n">
-        <v>0.04877078518591094</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>0.01694915254237284</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>0.006481128478840859</v>
-      </c>
-      <c r="K87" s="5" t="n">
-        <v>-0.003773584905660377</v>
-      </c>
-      <c r="L87" s="3" t="n">
-        <v>0.002658564375237482</v>
-      </c>
-    </row>
-    <row r="88" ht="21" customHeight="1">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>VCR</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D88" s="19" t="inlineStr">
-        <is>
-          <t>Consumer</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>Consumer Discretionary</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>0.08346397929155103</v>
-      </c>
-      <c r="G88" s="3" t="n">
-        <v>0.002789620577745122</v>
-      </c>
-      <c r="H88" s="3" t="n">
-        <v>0.0434944144559628</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>0.02303828968807609</v>
-      </c>
-      <c r="J88" s="5" t="n">
-        <v>-0.02134177250677893</v>
-      </c>
-      <c r="K88" s="5" t="n">
-        <v>-0.03900815693339343</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>-0.01870257288126931</v>
-      </c>
-    </row>
-    <row r="89" ht="21" customHeight="1">
-      <c r="A89" s="14" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="15" t="inlineStr">
-        <is>
-          <t>HYG</t>
-        </is>
-      </c>
-      <c r="C89" s="14" t="inlineStr"/>
-      <c r="D89" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E89" s="14" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
-        </is>
-      </c>
-      <c r="F89" s="3" t="n">
-        <v>0.07714286060220621</v>
+      <c r="F89" s="5" t="n">
+        <v>-0.004568774105219942</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.03677035579070598</v>
+        <v>0.03769364660046404</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.03978574756905551</v>
+        <v>0.04163026893202892</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.0116400694215486</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-0.0008475102051197503</v>
+        <v>0.01658310836868493</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.002662609357169998</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.002900012608750502</v>
+        <v>-0.003779289493575311</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.009146723468237083</v>
+        <v>-0.001893222264293892</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4548,25 +4545,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04388622249116625</v>
+        <v>0.04671709536350144</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.01944616774224706</v>
+        <v>0.02338853524157236</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.02157001392504343</v>
+        <v>0.02333911154842916</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.000273142780457869</v>
+        <v>0.004237776505672697</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.0009569713951633751</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>-0.002079002079002135</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>-0.003541335938454071</v>
+        <v>0.004807520746793692</v>
+      </c>
+      <c r="K90" s="3" t="n">
+        <v>4.829649583948381e-05</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0.0004902561588429055</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4583,7 +4580,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D91" s="13" t="inlineStr">
+      <c r="D91" s="17" t="inlineStr">
         <is>
           <t>Inflation &amp; Real Assets</t>
         </is>
@@ -4594,25 +4591,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.03625644567458064</v>
+        <v>0.03441415623188337</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.008531340426373379</v>
+        <v>0.01132893193926487</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.008908996797999169</v>
+        <v>0.01255856868778804</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.00921077516664992</v>
+        <v>-0.006054699332682545</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.01196401128720848</v>
+        <v>-0.009237209243750377</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.0003743215422048474</v>
-      </c>
-      <c r="L91" s="22" t="n">
-        <v>0</v>
+        <v>-0.001214385801027507</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0.001029866117404632</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4621,124 +4618,124 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr"/>
+      <c r="D92" s="16" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Mid Growth</t>
+        </is>
+      </c>
+      <c r="F92" s="3" t="n">
+        <v>0.1102429640734004</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.02950093201030202</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.0122363994361534</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0.008621526896963605</v>
+      </c>
+      <c r="J92" s="5" t="n">
+        <v>-0.0328965578076944</v>
+      </c>
+      <c r="K92" s="5" t="n">
+        <v>-0.04123279055140128</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>-0.005292923433874663</v>
+      </c>
+    </row>
+    <row r="93" ht="21" customHeight="1">
+      <c r="A93" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
           <t>IEF</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" s="21" t="inlineStr">
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E92" t="inlineStr">
+      <c r="E93" t="inlineStr">
         <is>
           <t>Intermediate Treasury</t>
         </is>
       </c>
-      <c r="F92" s="3" t="n">
-        <v>0.02347344894165726</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>-0.004516111531669087</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>0.003266172938441558</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>-0.03463202957550671</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>-0.01611747271863795</v>
-      </c>
-      <c r="K92" s="5" t="n">
-        <v>-0.007756948933419494</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>-0.006901013586370519</v>
-      </c>
-    </row>
-    <row r="93" ht="21" customHeight="1">
-      <c r="A93" s="14" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="15" t="inlineStr">
+      <c r="F93" s="3" t="n">
+        <v>0.02432450501836292</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0.002920998099465333</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0.01093061201269308</v>
+      </c>
+      <c r="I93" s="5" t="n">
+        <v>-0.02831885405572254</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>-0.009201585150591329</v>
+      </c>
+      <c r="K93" s="5" t="n">
+        <v>-0.007923010558836707</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0.0008686210640609371</v>
+      </c>
+    </row>
+    <row r="94" ht="21" customHeight="1">
+      <c r="A94" s="14" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="15" t="inlineStr">
         <is>
           <t>TLT</t>
         </is>
       </c>
-      <c r="C93" s="14" t="inlineStr"/>
-      <c r="D93" s="21" t="inlineStr">
+      <c r="C94" s="14" t="inlineStr"/>
+      <c r="D94" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E93" s="14" t="inlineStr">
+      <c r="E94" s="14" t="inlineStr">
         <is>
           <t>Long Treasury</t>
         </is>
       </c>
-      <c r="F93" s="5" t="n">
-        <v>-0.0537609937647624</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>-0.01169706872926279</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>-0.007470455509019036</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>-0.06703196041369475</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>-0.03709097576111753</v>
-      </c>
-      <c r="K93" s="5" t="n">
-        <v>-0.004258425599221294</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>-0.008240426563257297</v>
-      </c>
-    </row>
-    <row r="94" ht="21" customHeight="1">
-      <c r="A94" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr"/>
-      <c r="D94" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
-      <c r="F94" s="3" t="n">
-        <v>0.09199174716225866</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.03164567555539721</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>-0.01753115639561731</v>
-      </c>
-      <c r="I94" s="3" t="n">
-        <v>0.01930343837004656</v>
+      <c r="F94" s="5" t="n">
+        <v>-0.05235241106441324</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.001848566966137222</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0.007635828913300058</v>
+      </c>
+      <c r="I94" s="5" t="n">
+        <v>-0.05833429798664913</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.03805151100136994</v>
+        <v>-0.02729585455396011</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.01436637838610533</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>-0.01822582941762785</v>
+        <v>-0.005743406279433594</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0.00195431782093558</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4766,25 +4763,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.0303534303534303</v>
+        <v>0.0451882845188285</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.04655636783378214</v>
+        <v>-0.04565425023877745</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>-0.03501346671796846</v>
+        <v>-0.03476599808978031</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.01314217443249699</v>
+        <v>-0.006166699820966848</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.03185509056839475</v>
+        <v>0.05489864864864868</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.01196172248803817</v>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v>-0.0028169014084507</v>
+        <v>-0.0112804274688304</v>
+      </c>
+      <c r="L95" s="3" t="n">
+        <v>0.007664380798709125</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4812,25 +4809,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.1259407996268226</v>
+        <v>-0.1063351594680185</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1621307416725758</v>
+        <v>-0.1399531018094254</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>-0.1527839929741026</v>
+        <v>-0.1214227377250664</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.1054833737062322</v>
+        <v>0.09906582663480346</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1064580119021381</v>
+        <v>0.1635234590616377</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.01103230890464924</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>-0.02125170598557213</v>
+        <v>-0.02109133126934981</v>
+      </c>
+      <c r="L96" s="3" t="n">
+        <v>0.008170585890793225</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,6 +200,9 @@
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -669,25 +672,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.335419460987433</v>
+        <v>2.368547780690243</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.519187642256516</v>
+        <v>1.544208919064482</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.433034836883635</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3187467440648952</v>
+        <v>0.3318449058569621</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1679188580015027</v>
+        <v>-0.1596543951915853</v>
       </c>
       <c r="K2" s="3" t="n">
-        <v>0.0354096061703868</v>
+        <v>0.0456935842000703</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.00796359499431154</v>
+        <v>0.01797497155858929</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -715,25 +718,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.678215924420186</v>
+        <v>1.717052483889353</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.219888635508382</v>
+        <v>1.25207882049398</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>1.41714350708147</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4180406824665301</v>
+        <v>0.4386034220362325</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.2272939098098348</v>
+        <v>-0.2160890450320019</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.08160660341233039</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>-0.007540576578233593</v>
+        <v>-0.06828915457601159</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.006850889696077944</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -761,25 +764,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.443153892162519</v>
+        <v>1.485519609532721</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.052330360266249</v>
+        <v>1.087919097863352</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1.37796613036288</v>
+        <v>1.37796627710477</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3105288964394104</v>
+        <v>0.3332542339673263</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2253883142295557</v>
+        <v>-0.2119560945661604</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.1369387755102041</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>-0.008285781286641147</v>
+        <v>-0.1219727891156464</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.008911123270538557</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -807,25 +810,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.844597503228584</v>
+        <v>1.878174773999139</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.201932689103632</v>
+        <v>1.227924025324892</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>1.327224258580473</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.4903022101939556</v>
+        <v>0.5078935498421289</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1997093375317912</v>
+        <v>-0.1902628073150054</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.05383734249713634</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>-0.005717724947336689</v>
+        <v>-0.0426689576174113</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.006018657839302</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -849,25 +852,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.4819694841986</v>
+        <v>1.511589937204509</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.048844288150543</v>
+        <v>1.073295742938953</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.243298522804681</v>
+        <v>1.243298381184007</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.451514961602187</v>
+        <v>0.468837821445625</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1952878668760081</v>
+        <v>-0.1856841660081686</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.08668228177274495</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>-0.01019367991845066</v>
+        <v>-0.07578244591578909</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.001618996222342073</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -895,25 +898,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.465397637807288</v>
+        <v>1.493349991977438</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.005801090864574</v>
+        <v>1.028542775811386</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.180001049549638</v>
+        <v>1.180001238669052</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4185923031552927</v>
+        <v>0.4346761161162371</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1945586392832013</v>
+        <v>-0.1854266510664576</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.07990819945754224</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>-0.007874015748031482</v>
+        <v>-0.06947631963279777</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.003374578177727683</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -941,25 +944,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.447707363972409</v>
+        <v>1.474515780256429</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9054147944864905</v>
+        <v>0.9262837732525739</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>1.015852309634522</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3634928589325981</v>
+        <v>0.3784264595339513</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1469352563097664</v>
+        <v>-0.1375920990750901</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.05478452693196245</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>-0.00192582810608577</v>
+        <v>-0.04443209254659475</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.009005539048457356</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -987,25 +990,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.264647673162021</v>
+        <v>1.276512095714432</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9603538670008971</v>
+        <v>0.9706241032526481</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.841615521563986</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.519128734990226</v>
+        <v>0.5270874057525829</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.01777362020579965</v>
+        <v>0.02310570626753972</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.0644751002837296</v>
+        <v>0.07005185402602487</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-0.008565700747220628</v>
+        <v>-0.003371605613267659</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1033,25 +1036,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.676422764227642</v>
+        <v>1.682926829268292</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.052369077306734</v>
+        <v>1.057356608478803</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.7344139650872819</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.382031905961377</v>
+        <v>0.385390428211587</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.3042789223454836</v>
+        <v>0.307448494453249</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1833213515456507</v>
+        <v>0.1861969805895038</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.04177215189873418</v>
+        <v>0.04430379746835444</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1079,25 +1082,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.491340492627738</v>
+        <v>1.458790040429374</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8650522496875344</v>
+        <v>0.8406845270576686</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.7198697678003514</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.03663241737497058</v>
-      </c>
-      <c r="J11" s="3" t="n">
-        <v>0.01262621292311561</v>
+        <v>0.02308836185590812</v>
+      </c>
+      <c r="J11" s="5" t="n">
+        <v>-0.0006041910445887533</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.08441481128705797</v>
+        <v>0.07024645791165618</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.02061855670103108</v>
+        <v>0.007283729269385919</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1125,25 +1128,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.354840243044582</v>
+        <v>1.346457316613031</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7231536663553493</v>
+        <v>0.7170194623650876</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.6447102092677597</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.06270809296757651</v>
+        <v>0.05892498972400273</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.1223240340189802</v>
+        <v>0.1183287057425373</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.04769439421338162</v>
+        <v>0.04396473779385168</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0.02002640845070425</v>
+        <v>0.01639524647887325</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1167,25 +1170,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9379590766115058</v>
+        <v>0.9438279414815054</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.7858064524679051</v>
+        <v>0.7912143818860746</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6427126400631422</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.3073254164674946</v>
+        <v>0.3112843693366956</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.2729883388097329</v>
+        <v>0.2768433092500748</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.08710824335001321</v>
+        <v>0.09040031603897836</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.01046511627906987</v>
+        <v>0.01352509179926575</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1213,25 +1216,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.6991696339400699</v>
+        <v>0.7623034191857612</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6832939005095919</v>
+        <v>0.7458378122517804</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.566193805217065</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.099783419878402</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>-0.02261026854042025</v>
+        <v>0.1406466090859275</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.01370530123834701</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.07476730842789769</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>-0.01267335082458765</v>
+        <v>0.1147010072676273</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.02401143178410803</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1259,25 +1262,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.9153229220467776</v>
+        <v>0.9050397034133006</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.6363414502372797</v>
+        <v>0.627556061257635</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.5517507049189849</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.07361549199235418</v>
+        <v>0.06785133457254577</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.01942912540769204</v>
+        <v>-0.02469373357009885</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.05451310255580721</v>
+        <v>0.04885150436751862</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.01668746101060492</v>
+        <v>0.01122894572676225</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1305,25 +1308,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8480729076004281</v>
+        <v>0.8483221832366232</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.5960529595432538</v>
+        <v>0.5962682210125698</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5422703419551942</v>
+        <v>0.5422704685227915</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.04735615072502086</v>
+        <v>0.04749732287096031</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.1219783737753833</v>
+        <v>-0.1218600260700018</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.03487236713628117</v>
+        <v>0.03501185660482631</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.006960246285637739</v>
+        <v>-0.006826395395529206</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1351,25 +1354,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.6348244366103697</v>
+        <v>0.6401903224429437</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.4459339472036188</v>
+        <v>0.4506798491539374</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.5180241978289608</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.3520662397524912</v>
+        <v>0.3565040453774377</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.08550182185092314</v>
+        <v>-0.08250021953317255</v>
       </c>
       <c r="K17" s="5" t="n">
-        <v>-0.04748952666791717</v>
+        <v>-0.04436315888201092</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.01087591714823699</v>
+        <v>-0.007629374715927395</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1397,25 +1400,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.071898707730655</v>
+        <v>1.075281232127661</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.6823362521049703</v>
+        <v>0.6850829235369784</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.5092959518884592</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.2034003722104905</v>
+        <v>0.2053651075120586</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.241098858849623</v>
+        <v>0.2431251427008061</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.1146496815286624</v>
+        <v>0.116469517743403</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.007194244604316502</v>
+        <v>0.008838643371017474</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1439,25 +1442,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.056</v>
+        <v>1.051478260869565</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.5911170928667564</v>
+        <v>0.5876177658142665</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.4492597577388966</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.2154234138571808</v>
+        <v>-0.217148924873905</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.1072345567134874</v>
+        <v>-0.1091980063434526</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.0978826151560177</v>
+        <v>0.09546805349182752</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.02054558011049723</v>
+        <v>0.01830110497237558</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1481,25 +1484,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.6854416689013056</v>
+        <v>0.6936519661417311</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4138475412780702</v>
+        <v>0.4207349212000051</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.446349783606302</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.3096773850571988</v>
+        <v>0.3160573132055344</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.06783952874160826</v>
+        <v>-0.06329862661013597</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.02247191011235961</v>
+        <v>-0.01771000535045475</v>
       </c>
       <c r="L20" s="5" t="n">
-        <v>-0.005118710520583769</v>
+        <v>-0.0002722718362011545</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1527,25 +1530,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.6539152318062351</v>
+        <v>0.6604008188942445</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.3763125793627176</v>
+        <v>0.3817094472205089</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.4106967477762746</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.2930109364212197</v>
+        <v>0.2980812611137345</v>
       </c>
       <c r="J21" s="5" t="n">
-        <v>-0.03928106344144033</v>
+        <v>-0.03551384280651371</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.02437389075133112</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>-0.002298943292732059</v>
+        <v>-0.02054821534214157</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.001613293538759386</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1573,25 +1576,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6488822377928691</v>
+        <v>0.6702603585472395</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.2878657953209027</v>
+        <v>0.304563344319208</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0.4082497372925555</v>
       </c>
-      <c r="I22" s="5" t="n">
-        <v>-0.007328228484660637</v>
+      <c r="I22" s="3" t="n">
+        <v>0.00554204542457204</v>
       </c>
       <c r="J22" s="5" t="n">
-        <v>-0.2987241531016278</v>
+        <v>-0.2896319108373662</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.08548479632816985</v>
-      </c>
-      <c r="L22" s="5" t="n">
-        <v>-0.007677941481635142</v>
+        <v>-0.07362784471218209</v>
+      </c>
+      <c r="L22" s="3" t="n">
+        <v>0.005187798298402102</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1619,25 +1622,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6539267529013344</v>
+        <v>0.6609424487068054</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3847523777698021</v>
+        <v>0.3906265063595988</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4037450577010362</v>
+        <v>0.4037451625496926</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.2969494292529689</v>
+        <v>0.3024509998814944</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.04336494281051606</v>
+        <v>-0.03930696243430143</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.01353000662551873</v>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v>-0.002784827975183424</v>
+        <v>-0.009345468493915043</v>
+      </c>
+      <c r="L23" s="3" t="n">
+        <v>0.00144529046813302</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1661,25 +1664,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6500926479867792</v>
+        <v>0.658726044119706</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3802861415344834</v>
+        <v>0.3875080151199981</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3995053156571156</v>
+        <v>0.3995054400324696</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.2959885533531585</v>
+        <v>0.3027692529572004</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-0.04252232215081309</v>
+        <v>-0.03751273430046287</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.01373283395755309</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>-0.003112644064944936</v>
+        <v>-0.008572617561381612</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.002103137881719563</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1707,25 +1710,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.6760371147118991</v>
+        <v>0.6888785153447232</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4362951716595533</v>
+        <v>0.4472997261317506</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.39846199533543</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1086274813793711</v>
+        <v>0.1171215233764056</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.04370518864288409</v>
+        <v>0.05170181136219942</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.02705341757610569</v>
-      </c>
-      <c r="L25" s="5" t="n">
-        <v>-0.006997278836008203</v>
+        <v>0.03492245835726604</v>
+      </c>
+      <c r="L25" s="3" t="n">
+        <v>0.0006108735491754391</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1753,25 +1756,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.5467528411243796</v>
+        <v>0.5600197361720183</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3318501434564265</v>
+        <v>0.3432738802680906</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.3787268565801516</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.07925011285434724</v>
+        <v>0.08850721231390812</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-0.1951137828405894</v>
+        <v>-0.1882099968903905</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>-0.03399999999999992</v>
-      </c>
-      <c r="L26" s="5" t="n">
-        <v>-0.006464883925947684</v>
+        <v>-0.02571428571428569</v>
+      </c>
+      <c r="L26" s="3" t="n">
+        <v>0.0020570085218925</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1799,25 +1802,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.593509634387051</v>
+        <v>0.599265345140771</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.5221318533158781</v>
+        <v>0.5276297495868847</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3576947739375842</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.233541771188718</v>
+        <v>0.2379972884221135</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.272895339966692</v>
+        <v>0.2774930011533621</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.1211149092821457</v>
+        <v>0.1251643439389953</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.01119438383455096</v>
+        <v>0.01484678872972212</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1845,25 +1848,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.4224457966700454</v>
+        <v>0.4304228059809661</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.2598221447848854</v>
+        <v>0.2668871682835519</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.3542365497216067</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.04238076258801637</v>
+        <v>0.04822638501394994</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.1247211066488175</v>
+        <v>-0.1198125836680053</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.06971780886886425</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>-0.005198427792570182</v>
+        <v>-0.06450082997391504</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.0003803727653099997</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1887,25 +1890,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.4923155200376177</v>
+        <v>0.5064890661684365</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.1604974622842956</v>
+        <v>0.1715193775875941</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.3519481311025898</v>
       </c>
       <c r="I29" s="5" t="n">
-        <v>-0.1068821865254341</v>
+        <v>-0.09839973032375726</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>-0.1868242199567499</v>
+        <v>-0.1791010194624651</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.1416109571172346</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>-0.007072802715956228</v>
+        <v>-0.1334583401271807</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.00235760090531878</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1933,25 +1936,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5571369387095066</v>
+        <v>0.57763563626492</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4691906654988622</v>
+        <v>0.4885317967329457</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3372831587644558</v>
+        <v>0.3372832413293425</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1571967832430097</v>
+        <v>0.1724307188753615</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.1038800028248377</v>
+        <v>0.1184119400694059</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.09863842662632383</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>-0.006131274976733825</v>
+        <v>0.1131013615733736</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0.006952427875403844</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1975,25 +1978,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5386769266495128</v>
+        <v>0.5553784769376733</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.4692768907322107</v>
+        <v>0.4852250039825217</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3332622677259882</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.1635430486960077</v>
+        <v>0.1761726057449642</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1063717891203011</v>
+        <v>0.1183807866762665</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1020164046479834</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>-0.004322989038134994</v>
+        <v>0.1139781271360218</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.006484483557202436</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2017,25 +2020,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1.883533456042781</v>
+        <v>1.891754506523302</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.6625556243375015</v>
+        <v>0.6672956261175087</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3304169281812877</v>
       </c>
       <c r="I32" s="5" t="n">
-        <v>-0.08490328747342157</v>
+        <v>-0.08229431609059457</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.1240763643823657</v>
+        <v>0.1272811437533774</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.2496500827077235</v>
+        <v>0.2532128769563557</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.04157386785449124</v>
+        <v>0.04454342984409787</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2063,25 +2066,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1.133863293655958</v>
+        <v>1.138159516690923</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.4672031375354084</v>
+        <v>0.4701569616923915</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3276218994510833</v>
+        <v>0.3276216501016522</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.01449609397562712</v>
+        <v>0.01653870356081288</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.07195555709908608</v>
+        <v>-0.07008701124089634</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.1051362877804563</v>
+        <v>0.1073613944001484</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.02962771011488297</v>
+        <v>0.03170078604128879</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2105,25 +2108,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5067735066529344</v>
+        <v>0.5164137058906009</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2684498581282948</v>
+        <v>0.2765652844358022</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3191494568881006</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.2139942620993247</v>
+        <v>0.2217612086303504</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.06129951109981679</v>
+        <v>-0.05529379113093158</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.03843355163061435</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>-0.001236773395629887</v>
+        <v>-0.03228153734206518</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.005153222481791842</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2151,25 +2154,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5422710015956773</v>
+        <v>0.547346018746754</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.3457197173110236</v>
+        <v>0.3501479602325526</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.3079631197695643</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.2604809199765588</v>
+        <v>0.2646287803086949</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0.1510016524149791</v>
+        <v>0.1547891535226833</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0.02886671418389164</v>
+        <v>0.0322523164647186</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.00785477395706069</v>
+        <v>0.01117123407226384</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2197,25 +2200,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5965486491281249</v>
+        <v>0.6113377635258623</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.4611339917628601</v>
+        <v>0.474668642602462</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.3074624785783919</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2059334776937514</v>
+        <v>0.2171040605115115</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.1283926642301956</v>
+        <v>0.1388450941965242</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.1175341669089853</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>-0.002905770029057675</v>
+        <v>0.1278860133759814</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.006330427563304264</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2239,25 +2242,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.4018852880506596</v>
+        <v>0.4105823607387138</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2602494444435173</v>
+        <v>0.2680680110471252</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3049259387812489</v>
+        <v>0.3049261241104444</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.1177764975242372</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>-0.003598142148407479</v>
+        <v>0.1247110045989814</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.002583376024379413</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.03423680456490719</v>
+        <v>-0.02824536376604836</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.003557663800771049</v>
+        <v>0.00978357545211983</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2285,25 +2288,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.3882992372863519</v>
+        <v>0.4012338488343969</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2214101878258636</v>
+        <v>0.2327899148299879</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.301400531657773</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1753772026645555</v>
+        <v>0.1863279737166403</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.106479820708881</v>
+        <v>-0.09815500418585166</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.06146481570129259</v>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v>-0.008195062727640701</v>
+        <v>-0.05272059996808698</v>
+      </c>
+      <c r="L38" s="3" t="n">
+        <v>0.001045460677188803</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2331,25 +2334,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5453121453961143</v>
+        <v>0.5475373948854847</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.1522523427812272</v>
+        <v>0.153911667307016</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.3001554535006254</v>
+        <v>0.3001555449378339</v>
       </c>
       <c r="I39" s="5" t="n">
-        <v>-0.1288991344421934</v>
+        <v>-0.1276447491957901</v>
       </c>
       <c r="J39" s="5" t="n">
-        <v>-0.08559011374412528</v>
+        <v>-0.08427336350791681</v>
       </c>
       <c r="K39" s="5" t="n">
-        <v>-0.1137580204899145</v>
+        <v>-0.11248183203942</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.008093953340739479</v>
+        <v>-0.006665608633550146</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2373,25 +2376,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5008344859216418</v>
+        <v>0.5098186873181481</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.453621662594011</v>
+        <v>0.462323241544637</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.2965352636432406</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.214231063504208</v>
+        <v>0.2214996174445294</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.04787058435127101</v>
+        <v>0.05414328161109272</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.1211586012009891</v>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v>-0.00595051675540248</v>
+        <v>0.1278700105969623</v>
+      </c>
+      <c r="L40" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2415,25 +2418,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4310642030995158</v>
+        <v>0.4371693358946382</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2545135127512785</v>
+        <v>0.2598657263160833</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2863673222269516</v>
+        <v>0.2863674069477622</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1591883525169222</v>
+        <v>0.1641337974063803</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.05095612743574551</v>
+        <v>-0.04690722187242302</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.02476260779116191</v>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v>-0.002573781743308134</v>
+        <v>-0.02060195282354116</v>
+      </c>
+      <c r="L41" s="3" t="n">
+        <v>0.001681537405628042</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2461,25 +2464,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.7053086207098791</v>
+        <v>0.7181767162799211</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2288176771474049</v>
+        <v>0.2380902176809228</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2861013719989147</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-0.02795436022819886</v>
+        <v>-0.02061939690301551</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.1408917380969532</v>
+        <v>-0.1344089894115106</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.04454057518224785</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>-0.007324178110695079</v>
+        <v>-0.03733076984699191</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0.0001664585934249008</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2503,25 +2506,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4309344316293171</v>
+        <v>0.4368529167152122</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2541814008874828</v>
+        <v>0.2593688767642219</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2859094421059849</v>
+        <v>0.2859095815347252</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1586688511899681</v>
+        <v>0.1634611471792522</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.05031395536529237</v>
+        <v>-0.04638601977083168</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.02467362022518482</v>
-      </c>
-      <c r="L43" s="5" t="n">
-        <v>-0.002331694081736391</v>
+        <v>-0.02063963528355328</v>
+      </c>
+      <c r="L43" s="3" t="n">
+        <v>0.001794697868972905</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2545,25 +2548,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.3695598883203353</v>
+        <v>0.375466911653618</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2870441649126694</v>
+        <v>0.292595187188941</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2838721521833716</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.1347756685434189</v>
+        <v>0.1396699567010307</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.04940774140611204</v>
+        <v>0.05393383764138182</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.002470660901791266</v>
+        <v>0.006794317479925871</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.003400309119010902</v>
+        <v>0.007727975270479082</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2587,25 +2590,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.391001450077654</v>
+        <v>0.4052164407417695</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.1768848517237445</v>
+        <v>0.1889117314793753</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0.2809720292452051</v>
       </c>
-      <c r="I45" s="5" t="n">
-        <v>-0.006735809548506499</v>
+      <c r="I45" s="3" t="n">
+        <v>0.003414604883829497</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>-0.05892164019710389</v>
+        <v>-0.04930452578068634</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.08125640150221913</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>-0.001854599406528212</v>
+        <v>-0.07186753158074433</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.008345697329376733</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2629,25 +2632,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4673597628419217</v>
+        <v>0.4697897234318233</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2812377962033576</v>
+        <v>0.2833595497650527</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.276994115950959</v>
+        <v>0.2769940298158184</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.08289355028941636</v>
+        <v>0.08468691526367422</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.0163443636014966</v>
+        <v>0.01802751739161801</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.003323179174743673</v>
+        <v>0.004984768762115843</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.004853695742615294</v>
+        <v>0.006517819997226448</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2675,25 +2678,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4054692115784004</v>
+        <v>0.4134133316867059</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2262912195102045</v>
+        <v>0.2332225735770852</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.2757304985180495</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1162532474476856</v>
+        <v>0.1225626349433049</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-0.00861001476495471</v>
+        <v>-0.003006390685538762</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.03875370155787305</v>
+        <v>-0.0333204583494271</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.005088715974260305</v>
+        <v>0.01076976925769357</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2717,25 +2720,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.3396964144457804</v>
+        <v>0.3425492603027773</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2663975533575162</v>
+        <v>0.2690943113501858</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2717910693428549</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.08925721152505939</v>
+        <v>0.09157675413903954</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.04530471319483786</v>
+        <v>0.04753066019908592</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.004240882103477395</v>
+        <v>-0.002120441051738586</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.001065870816457037</v>
+        <v>0.003197612449371334</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2759,25 +2762,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.472222136041198</v>
+        <v>0.4721562942640944</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.1321780527805594</v>
+        <v>0.1321275061693294</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2691432420816064</v>
+        <v>0.2691433401374945</v>
       </c>
       <c r="I49" s="5" t="n">
-        <v>-0.09340327044917529</v>
+        <v>-0.09344381592008533</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.00503817068072232</v>
+        <v>-0.005082668079171238</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.1079194095352085</v>
+        <v>-0.1079593058049072</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.008249800408054675</v>
+        <v>-0.008294154173689394</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2801,25 +2804,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.297749646060073</v>
+        <v>0.3037009198740486</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.299256184647273</v>
+        <v>0.3052144599135536</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.260527998002585</v>
+        <v>0.2605280875342024</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1244561628946537</v>
+        <v>0.1296126708725589</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.0864340667295167</v>
+        <v>0.09141628085037423</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.03072378138847864</v>
+        <v>0.03545051698670587</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.002298190175237025</v>
+        <v>0.006894570525710852</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2843,25 +2846,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4378614081250456</v>
+        <v>0.442331434630503</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2351867588879453</v>
+        <v>0.2390268420788917</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>0.2573872398356056</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.149793314569838</v>
+        <v>0.153367917315999</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.02567566486240636</v>
+        <v>-0.02264657919987823</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.01765604122924214</v>
+        <v>-0.01460202328688687</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.0007778317938746948</v>
+        <v>0.00388915896937303</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2885,25 +2888,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3034570636473846</v>
+        <v>0.3122535980209629</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.1563845827198231</v>
+        <v>0.1641885658374895</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2540001525334519</v>
+        <v>0.2540002812603759</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>-0.01803093872764194</v>
+        <v>-0.01140411860386537</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.009980428297433397</v>
+        <v>-0.003299279288328738</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.07784334763948508</v>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v>-0.004863081109245715</v>
+        <v>-0.07162017167381973</v>
+      </c>
+      <c r="L52" s="3" t="n">
+        <v>0.001852602327331754</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2931,25 +2934,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4230873344825417</v>
+        <v>0.4251766865363329</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1099233707084495</v>
+        <v>0.1115530147129156</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2462702524154461</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>-0.1091011399245219</v>
+        <v>-0.1077931526632692</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.03749760480569375</v>
+        <v>-0.0360844115177541</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.1094039446442192</v>
+        <v>-0.1080963277759617</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.01005329457364335</v>
+        <v>-0.008599806201550431</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2977,25 +2980,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.2804473765205426</v>
+        <v>0.2875927188099208</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.1527476680657531</v>
+        <v>0.1591801908302251</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2278719265107476</v>
+        <v>0.2278717830330863</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.01422806216606598</v>
+        <v>0.01988774177956154</v>
       </c>
       <c r="J54" s="5" t="n">
-        <v>-0.1184765118849228</v>
+        <v>-0.113557361350035</v>
       </c>
       <c r="K54" s="5" t="n">
-        <v>-0.06118248721466879</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>-0.002518057120137751</v>
+        <v>-0.05594361980790818</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0.003048174408587956</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3019,25 +3022,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3062093855662442</v>
+        <v>0.3123152689757225</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.187191711913302</v>
+        <v>0.1927413593967722</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2265889806389327</v>
+        <v>0.2265892386860922</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.08284028370561924</v>
+        <v>0.08790190103502149</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-0.02683496106553351</v>
+        <v>-0.02228600855650553</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.03211937278705113</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>-0.0005803325305400175</v>
+        <v>-0.02759512167706402</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0.004091344340307002</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3061,25 +3064,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3306144322014664</v>
+        <v>0.3344498974423498</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2058936422840127</v>
+        <v>0.2093694746493144</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.218570207380995</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1199453863761764</v>
+        <v>0.1231734840166645</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.01523849824827961</v>
+        <v>0.01816479183419473</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.01040281882832761</v>
+        <v>-0.007550433020560243</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.001803096622460254</v>
+        <v>0.004690664401907574</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3103,25 +3106,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.3309580626824351</v>
+        <v>0.334523973648378</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2059537473599964</v>
+        <v>0.2091848859935945</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0.2185173768342532</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1202111325157036</v>
+        <v>0.1232125390588499</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.01493207944041552</v>
+        <v>0.01765140948067367</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.01031058704053722</v>
+        <v>-0.007658890236678095</v>
       </c>
       <c r="L57" s="3" t="n">
-        <v>0.001984920317587235</v>
+        <v>0.004669560747129653</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3145,25 +3148,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.329902956186837</v>
+        <v>0.3335442837733791</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2053468668709282</v>
+        <v>0.2086472834252657</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.218043206151729</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1200010397009772</v>
+        <v>0.1230677668596916</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.01460598534739521</v>
+        <v>0.01738412538509526</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.01042355412080442</v>
+        <v>-0.007713948634177403</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.001982199585182087</v>
+        <v>0.004725773845467129</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3191,25 +3194,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2305331451857311</v>
+        <v>0.2232181940545519</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2986403650153284</v>
+        <v>0.2909204695393164</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2136427912548644</v>
+        <v>0.2136427175635649</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1324765153869347</v>
+        <v>0.1257443464086216</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.1896589944165297</v>
+        <v>0.1825870212307843</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.07003508311747941</v>
+        <v>0.06367421882684687</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.01480145526913157</v>
+        <v>0.008768929382132695</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3237,25 +3240,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3523625492389717</v>
+        <v>0.3555717626923154</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2048393740893546</v>
+        <v>0.2076985088166667</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.2126543423440079</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.134712232244437</v>
+        <v>0.1374049523019703</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.01466459281406696</v>
+        <v>0.01707243475240117</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.006444514303678206</v>
+        <v>-0.004086765168186068</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.003891050583657574</v>
+        <v>0.006273326451203154</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3272,7 +3275,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D61" s="18" t="inlineStr">
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -3283,25 +3286,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.2445476442114105</v>
+        <v>0.2529801963946936</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1476580932643332</v>
+        <v>0.155434316292115</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2053030203232722</v>
+        <v>0.2053030980486876</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1103564677217599</v>
+        <v>0.1178798031198742</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.09963895845012827</v>
+        <v>0.1070897453242929</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.04782608695652169</v>
+        <v>-0.04137447405329597</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.0140403286034354</v>
+        <v>0.02091112770724401</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3329,25 +3332,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.1931104313008116</v>
+        <v>0.2115690085119029</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2341280431721937</v>
+        <v>0.2532210842305114</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.2019645981679137</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1005158926864174</v>
+        <v>0.1175418368262029</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.02014044569721807</v>
+        <v>0.03592291131957137</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.02675906183368881</v>
+        <v>0.04264392324093813</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.00890425309029963</v>
+        <v>0.02451288497800119</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3371,25 +3374,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3242921586687793</v>
+        <v>0.3255753025803778</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2723952948648507</v>
+        <v>0.2736281509559286</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.2005423840960121</v>
+        <v>0.2005424647492489</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1275107971594809</v>
+        <v>0.128603195163649</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.1153477948774517</v>
+        <v>0.1164284086579557</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.05985037406483795</v>
+        <v>0.06087721871791096</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.005567153792623625</v>
+        <v>0.006541405706332659</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3413,25 +3416,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.4115600107267119</v>
+        <v>0.412955292450659</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2104198425636161</v>
+        <v>0.2116163036930034</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.1974581803285855</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.09341746298461184</v>
+        <v>0.09449827102051089</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.007328725120322455</v>
+        <v>0.008324437204461077</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.0108243130724397</v>
+        <v>0.01182348043297243</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.0003295978905735186</v>
+        <v>0.001318391562294075</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3455,25 +3458,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2552628529695071</v>
+        <v>0.2590602287909303</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1852104962974932</v>
+        <v>0.1887959522609914</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1964014649108354</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.08409762807685572</v>
+        <v>0.0873772010453242</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.04666629576771109</v>
+        <v>0.04983263282233219</v>
       </c>
       <c r="K65" s="5" t="n">
-        <v>-0.00935385733097216</v>
+        <v>-0.0063569904191072</v>
       </c>
       <c r="L65" s="3" t="n">
-        <v>0.002665563674801197</v>
+        <v>0.005698791304747486</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3497,25 +3500,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3547634802913204</v>
+        <v>0.3584144714821011</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1746047117420475</v>
+        <v>0.1777698141690642</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1925416352539404</v>
+        <v>0.1925413952650257</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1443818795682543</v>
+        <v>0.1474657741460264</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>-0.01753605964434324</v>
+        <v>-0.01488850355086291</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.01504092015040914</v>
+        <v>-0.01238664012386648</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.0002246181491463162</v>
+        <v>0.002920035938903665</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3539,25 +3542,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3336315119817748</v>
+        <v>0.3369884791744062</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1575451394693657</v>
+        <v>0.1604589859175878</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1799278772920569</v>
+        <v>0.1799279965236009</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1325792718283929</v>
+        <v>0.1354302701301024</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-0.01611466012902874</v>
+        <v>-0.01363806087534891</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.01896958132225834</v>
+        <v>-0.01650016836906498</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.0003433672885428951</v>
+        <v>0.002861394071191459</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3581,25 +3584,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3357888476438622</v>
+        <v>0.3373024893975665</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1710462189238553</v>
+        <v>0.172373183477877</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1783445239709731</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1427573697324755</v>
+        <v>0.1440522789333059</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.01922076956315188</v>
+        <v>0.02037569394792604</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.006193693693693825</v>
+        <v>-0.005067567567567544</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.0008505812305072968</v>
+        <v>0.001984689537850803</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3627,25 +3630,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.08644211192315909</v>
+        <v>0.08609801074750778</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1646478807575276</v>
+        <v>0.1642790100182674</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1598525611471451</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1015234329573207</v>
+        <v>0.101174555180835</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.2134255700743017</v>
+        <v>0.2130412503202663</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.004134421711014635</v>
+        <v>0.0038163892717058</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.007981270618282466</v>
+        <v>0.007662019793551078</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3673,25 +3676,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2397483228173023</v>
+        <v>0.2398474775145598</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1278031197466372</v>
+        <v>0.1278932358568845</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1565501589155687</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.09782883278221499</v>
+        <v>0.09791655382358777</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.04162419932796335</v>
+        <v>0.04170742938783767</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.02485585164407045</v>
+        <v>-0.02477793361383829</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.00691930163327692</v>
+        <v>0.006999758629012698</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3715,25 +3718,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.5105369250503942</v>
+        <v>0.5110866776617187</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.2367591897974493</v>
+        <v>0.2372093023255812</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1506376594148535</v>
       </c>
       <c r="I71" s="5" t="n">
-        <v>-0.1471288153129849</v>
+        <v>-0.146818416968443</v>
       </c>
       <c r="J71" s="5" t="n">
-        <v>-0.01387725804522066</v>
+        <v>-0.01351836344060309</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.07484678576085546</v>
+        <v>0.07523797105228835</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.01327596803933639</v>
+        <v>0.01364474492931778</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3757,25 +3760,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.507647896828372</v>
+        <v>0.5083227112544049</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2351423569519948</v>
+        <v>0.2356951994840137</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0.149175343223072</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>-0.147626112759644</v>
+        <v>-0.1472445951674439</v>
       </c>
       <c r="J72" s="5" t="n">
-        <v>-0.01402407629882074</v>
+        <v>-0.01358275921249419</v>
       </c>
       <c r="K72" s="3" t="n">
-        <v>0.07480756895445784</v>
+        <v>0.07528864656831291</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.01361058601134202</v>
+        <v>0.01406427221172013</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3799,25 +3802,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2654653205051096</v>
+        <v>0.2747195402131757</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1085172005431787</v>
+        <v>0.1166236745474623</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1481871797130763</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>-0.0436609508499769</v>
+        <v>-0.03666734025248963</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>-0.01697586178557564</v>
+        <v>-0.00978710583473108</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.03455009764158024</v>
+        <v>-0.02748986029743128</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.008025929927458098</v>
+        <v>-0.0007717240314865093</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3834,7 +3837,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D74" s="18" t="inlineStr">
+      <c r="D74" s="19" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -3845,25 +3848,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.09092591174013953</v>
+        <v>0.09410113148967203</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1206932713711621</v>
+        <v>0.1239553905337922</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.144848487075399</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.07947031450855313</v>
+        <v>0.08261244169750315</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.1308163682630588</v>
+        <v>0.1341079537829872</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.02109905020352787</v>
+        <v>-0.01824966078697421</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.003267973856209139</v>
+        <v>0.006188290919204587</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3887,25 +3890,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.2690915058581829</v>
+        <v>0.2746817695793264</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1033967283063204</v>
+        <v>0.1082571922671844</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1305265373396409</v>
+        <v>0.1305266135614458</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.07384019052346646</v>
+        <v>0.07857038517978476</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>-0.04068006368136257</v>
+        <v>-0.03645432313214547</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.02399749863206446</v>
+        <v>-0.01969827249276956</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.0004006089255668144</v>
+        <v>0.004807307106802217</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3929,25 +3932,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2682238815168374</v>
+        <v>0.2732411687757847</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1028763521667317</v>
+        <v>0.1072394225749558</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1298733254291993</v>
+        <v>0.1298732470738608</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.07304418170882099</v>
+        <v>0.07728930828279479</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>-0.04101042160552082</v>
+        <v>-0.03721651245173074</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.02389380530973451</v>
+        <v>-0.0200321802091713</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.0009900173253032385</v>
+        <v>0.00495008662651597</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3971,25 +3974,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.1277215986326417</v>
+        <v>0.1322298393073846</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.05672087389618063</v>
+        <v>0.06094534340918623</v>
       </c>
       <c r="H77" s="3" t="n">
         <v>0.1191826731241958</v>
       </c>
       <c r="I77" s="5" t="n">
-        <v>-0.05635570632389342</v>
+        <v>-0.05258328481862073</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.1299350746521507</v>
+        <v>-0.1264568025348265</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.05581019142626042</v>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v>-0.003698435277382561</v>
+        <v>-0.05203558910757633</v>
+      </c>
+      <c r="L77" s="3" t="n">
+        <v>0.0002844950213369835</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4006,7 +4009,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D78" s="19" t="inlineStr">
+      <c r="D78" s="20" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -4017,25 +4020,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.218648859081473</v>
+        <v>0.2182263684126184</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.03456826352379427</v>
+        <v>0.03420960812804097</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1037705537941589</v>
+        <v>0.1037704531448582</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.01211572988408771</v>
+        <v>0.0117649504028432</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.04050338233284911</v>
+        <v>0.04014276424747498</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.06269626421223595</v>
+        <v>-0.06302111532214394</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0.007448789571694592</v>
+        <v>0.007099627560521515</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4048,7 +4051,7 @@
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="18" t="inlineStr">
+      <c r="D79" s="19" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4059,25 +4062,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.158777719777873</v>
+        <v>0.1586133891078343</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.09617930816011722</v>
+        <v>0.09602385480860898</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.1018533554901666</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.1297070276484318</v>
+        <v>0.1295468196036684</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.1395429727621096</v>
+        <v>0.139381369844608</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.005149548532731307</v>
+        <v>-0.005290632054176125</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.01053310404127261</v>
+        <v>0.01038979650329597</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4090,7 +4093,7 @@
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="18" t="inlineStr">
+      <c r="D80" s="19" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4101,25 +4104,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.1420876743518373</v>
+        <v>0.140704044424447</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.09491829672076713</v>
+        <v>0.09359173305748358</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.09681327473516799</v>
+        <v>0.09681319544909295</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.1316592999298891</v>
+        <v>0.1302883038932829</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.1398152494026546</v>
+        <v>0.1384343724996053</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.001727712508638568</v>
+        <v>-0.002937111264685544</v>
       </c>
       <c r="L80" s="3" t="n">
-        <v>0.01013986013986012</v>
+        <v>0.008916083916083783</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4143,25 +4146,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.06280986282613599</v>
+        <v>0.06617299365111395</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.08737247052464592</v>
+        <v>0.09081311938251124</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0.08788219628136673</v>
       </c>
       <c r="I81" s="5" t="n">
-        <v>-0.008654199156339804</v>
+        <v>-0.005517396552006226</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.04578956232590259</v>
-      </c>
-      <c r="K81" s="5" t="n">
-        <v>-0.0004685486704931741</v>
+        <v>0.04909863512360557</v>
+      </c>
+      <c r="K81" s="3" t="n">
+        <v>0.002694154855335418</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>0.0009384164222874247</v>
+        <v>0.004105571847507372</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4185,25 +4188,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1062203031109124</v>
+        <v>0.1201465919624274</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.02984352463759543</v>
+        <v>0.04280830060096674</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0.07901182593264466</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>-0.09741809265038093</v>
+        <v>-0.08605542255785603</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.03068336263727234</v>
+        <v>-0.01848056411465371</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.04556789843572884</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>-0.01080827067669177</v>
+        <v>-0.03355248243028786</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>0.00164473684210531</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4231,25 +4234,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1721535674414156</v>
+        <v>0.1761597130135908</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.03577383951086577</v>
+        <v>0.03931369713782717</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.07657110362803721</v>
+        <v>0.07657098847622512</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.07038780282207635</v>
+        <v>0.07404607190995627</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-0.02006744862674148</v>
+        <v>-0.01671832884842872</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.03789555931761956</v>
+        <v>-0.03460737075140008</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.003842782983887405</v>
+        <v>-0.0004382120946540002</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4266,7 +4269,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D84" s="20" t="inlineStr">
+      <c r="D84" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -4277,25 +4280,25 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.1213805206200643</v>
+        <v>-0.1205030710734132</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05737416402675111</v>
+        <v>0.05843013023583254</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0.06335797254487852</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.03088538091969806</v>
+        <v>0.03191489361702127</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.01417960837272103</v>
+        <v>0.01519243754220123</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.005627275736511117</v>
+        <v>-0.004634227077126796</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>0.001667222407469193</v>
+        <v>0.002667555851950665</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4312,7 +4315,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D85" s="20" t="inlineStr">
+      <c r="D85" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -4322,26 +4325,26 @@
           <t>US Dollar Basket</t>
         </is>
       </c>
-      <c r="F85" s="5" t="n">
-        <v>-0.000662708324130179</v>
+      <c r="F85" s="3" t="n">
+        <v>0.000758318752550835</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.0559241217753339</v>
+        <v>0.05742561359442444</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0.05705024063965181</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.02626778547975195</v>
+        <v>0.02772710689529378</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.009691313711414296</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>-0.001065340909090939</v>
+        <v>0.01112706389088314</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>0.0003551136363637575</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.002835873803615829</v>
+        <v>-0.001417936901807804</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4358,7 +4361,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D86" s="19" t="inlineStr">
+      <c r="D86" s="20" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -4369,25 +4372,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.1158204837995478</v>
+        <v>0.1161968945179135</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.01525729915819407</v>
+        <v>0.01559968812884494</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.05622885704625968</v>
+        <v>0.05622894192150274</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.01030523414199824</v>
+        <v>0.01064587184835109</v>
       </c>
       <c r="J86" s="5" t="n">
-        <v>-0.009787732086473544</v>
+        <v>-0.009453868988128944</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.03879041707177222</v>
+        <v>-0.03846633261037569</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.00280891570652031</v>
+        <v>0.003147025930453351</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4415,25 +4418,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.1182661886893694</v>
+        <v>0.1105116155415868</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.1059186102379364</v>
+        <v>0.09824958252660787</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.04419292036419109</v>
+        <v>0.04419284585792171</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.1212582744476014</v>
+        <v>0.1134829527981551</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.1055951014415892</v>
+        <v>0.09792839545273435</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0.05911330049261077</v>
+        <v>0.05176892073443806</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>0.01241438356164393</v>
+        <v>0.005393835616438469</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4446,7 +4449,7 @@
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr"/>
-      <c r="D88" s="18" t="inlineStr">
+      <c r="D88" s="19" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4457,25 +4460,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.08681470151860204</v>
+        <v>0.0862655084118984</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.04503172583351378</v>
+        <v>0.04450386538354123</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0.04406074666604187</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.01505170385670751</v>
+        <v>0.01453898674401333</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.008803343036953182</v>
+        <v>0.008293782060548871</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.0009300025602652084</v>
+        <v>0.0004244185205835027</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.001137800252844601</v>
+        <v>0.0006321112515803584</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4492,7 +4495,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="20" t="inlineStr">
+      <c r="D89" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -4503,25 +4506,25 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-0.004568774105219942</v>
+        <v>-0.003435885760119661</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.03769364660046404</v>
+        <v>0.03887463329993346</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.04163026893202892</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01658310836868493</v>
+        <v>0.01774006941766304</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.002662609357169998</v>
+        <v>0.003803727653099997</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.003779289493575311</v>
+        <v>-0.002645502645502673</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.001893222264293892</v>
+        <v>-0.0007572889057174681</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4534,7 +4537,7 @@
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr"/>
-      <c r="D90" s="21" t="inlineStr">
+      <c r="D90" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4545,25 +4548,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04671709536350144</v>
+        <v>0.04684532237506156</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.02338853524157236</v>
+        <v>0.02351380651347768</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.02333911154842916</v>
+        <v>0.02333901366698798</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.004237776505672697</v>
+        <v>0.00436070536305766</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.004807520746793692</v>
+        <v>0.004930708044105225</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>4.829649583948381e-05</v>
+        <v>0.0001708063937320148</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.0004902561588429055</v>
+        <v>0.0006128201985537984</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4591,25 +4594,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.03441415623188337</v>
+        <v>0.03364010750443769</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.01132893193926487</v>
+        <v>0.01057215947428825</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.01255856868778804</v>
+        <v>0.01255849561702127</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.006054699332682545</v>
+        <v>-0.006798392038007917</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.009237209243750377</v>
+        <v>-0.009978520722056627</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.001214385801027507</v>
+        <v>-0.001961700140121425</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.001029866117404632</v>
+        <v>0.0002808725774741117</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4633,25 +4636,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.1102429640734004</v>
+        <v>0.1128325720789105</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-0.02950093201030202</v>
+        <v>-0.02723710733610807</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.0122363994361534</v>
+        <v>0.01223650869955861</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.008621526896963605</v>
+        <v>0.01097405499207937</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.0328965578076944</v>
+        <v>-0.03064075854024395</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.04123279055140128</v>
+        <v>-0.03899643580963041</v>
       </c>
       <c r="L92" s="5" t="n">
-        <v>-0.005292923433874663</v>
+        <v>-0.002972737819025517</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4664,7 +4667,7 @@
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" s="21" t="inlineStr">
+      <c r="D93" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4675,25 +4678,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02432450501836292</v>
+        <v>0.02399122521055363</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.002920998099465333</v>
+        <v>0.002594680477317368</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.01093061201269308</v>
+        <v>0.01093069592805329</v>
       </c>
       <c r="I93" s="5" t="n">
-        <v>-0.02831885405572254</v>
+        <v>-0.02863508788495162</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.009201585150591329</v>
+        <v>-0.009524121922589779</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.007923010558836707</v>
+        <v>-0.008245882219535705</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>0.0008686210640609371</v>
+        <v>0.0005428881650382245</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4706,7 +4709,7 @@
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr"/>
-      <c r="D94" s="21" t="inlineStr">
+      <c r="D94" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4717,25 +4720,25 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.05235241106441324</v>
+        <v>-0.05385439653051349</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.001848566966137222</v>
+        <v>0.0002607581255067437</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.007635828913300058</v>
+        <v>0.007635735022504697</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.05833429798664913</v>
+        <v>-0.05982671900073333</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.02729585455396011</v>
+        <v>-0.02883747037798634</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.005743406279433594</v>
+        <v>-0.007319090263142813</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>0.00195431782093558</v>
+        <v>0.0003664345914253797</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4763,25 +4766,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.0451882845188285</v>
+        <v>0.04581589958159005</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.04565425023877745</v>
+        <v>-0.04508118433619868</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>-0.03476599808978031</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.006166699820966848</v>
+        <v>-0.005569922418937723</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.05489864864864868</v>
+        <v>0.05553209459459474</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.0112804274688304</v>
+        <v>-0.01068672075994459</v>
       </c>
       <c r="L95" s="3" t="n">
-        <v>0.007664380798709125</v>
+        <v>0.008269463493344231</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4809,25 +4812,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.1063351594680185</v>
+        <v>-0.08902360493705708</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1399531018094254</v>
+        <v>-0.1232927744675246</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>-0.1214227377250664</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.09906582663480346</v>
+        <v>0.1203562893764936</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1635234590616377</v>
+        <v>0.1860625574977002</v>
       </c>
       <c r="K96" s="5" t="n">
-        <v>-0.02109133126934981</v>
+        <v>-0.002128482972136192</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0.008170585890793225</v>
+        <v>0.02770027899561578</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -56,7 +56,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECFCCB"/>
+        <fgColor rgb="00DBEAFE"/>
       </patternFill>
     </fill>
     <fill>
@@ -76,7 +76,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00DBEAFE"/>
+        <fgColor rgb="00ECFCCB"/>
       </patternFill>
     </fill>
     <fill>
@@ -121,12 +121,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E5E7EB"/>
+        <fgColor rgb="00FFEDD5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEDD5"/>
+        <fgColor rgb="00E5E7EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -199,10 +199,10 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -657,40 +657,44 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>EWY</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>FTXL</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>South Korea Equity</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>2.368547780690243</v>
+        <v>1.686654966662124</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.544208919064482</v>
+        <v>1.22597821074228</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.433034836883635</v>
+        <v>1.383619836185349</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.3318449058569621</v>
+        <v>0.4372027525969295</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1596543951915853</v>
-      </c>
-      <c r="K2" s="3" t="n">
-        <v>0.0456935842000703</v>
-      </c>
-      <c r="L2" s="3" t="n">
-        <v>0.01797497155858929</v>
+        <v>-0.2104255355214136</v>
+      </c>
+      <c r="K2" s="5" t="n">
+        <v>-0.06613538914634665</v>
+      </c>
+      <c r="L2" s="5" t="n">
+        <v>-0.0170047868702986</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -699,44 +703,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FTXL</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>EWY</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>Growth &amp; Technology</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>South Korea Equity</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.717052483889353</v>
+        <v>2.342435491790483</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.25207882049398</v>
+        <v>1.501669362791878</v>
       </c>
       <c r="H3" s="7" t="n">
-        <v>1.41714350708147</v>
+        <v>1.371951096040239</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4386034220362325</v>
+        <v>0.4187211706696357</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.2160890450320019</v>
-      </c>
-      <c r="K3" s="5" t="n">
-        <v>-0.06828915457601159</v>
-      </c>
-      <c r="L3" s="3" t="n">
-        <v>0.006850889696077944</v>
+        <v>-0.1254105995979802</v>
+      </c>
+      <c r="K3" s="3" t="n">
+        <v>0.05468842379094241</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>-0.002627753550262901</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -753,7 +753,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D4" s="6" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -764,25 +764,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.485519609532721</v>
+        <v>1.409287615528959</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.087919097863352</v>
+        <v>1.051954947178543</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1.37796627710477</v>
+        <v>1.322415522367409</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3332542339673263</v>
+        <v>0.3384103426207239</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2119560945661604</v>
+        <v>-0.2187398611239915</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.1219727891156464</v>
-      </c>
-      <c r="L4" s="3" t="n">
-        <v>0.008911123270538557</v>
+        <v>-0.1164565826330533</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>-0.02352759074375055</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -810,25 +810,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.878174773999139</v>
+        <v>1.823781009409752</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.227924025324892</v>
+        <v>1.193355481727575</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>1.327224258580473</v>
+        <v>1.278073089700996</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5078935498421289</v>
+        <v>0.5310760667903525</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1902628073150054</v>
+        <v>-0.1773208722741434</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.0426689576174113</v>
-      </c>
-      <c r="L5" s="3" t="n">
-        <v>0.006018657839302</v>
+        <v>-0.03718827475572406</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>-0.01389096340552665</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -841,7 +841,7 @@
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
-      <c r="D6" s="6" t="inlineStr">
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.511589937204509</v>
+        <v>1.45566593275839</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.073295742938953</v>
+        <v>1.048117633301714</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.243298381184007</v>
+        <v>1.206125612440316</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.468837821445625</v>
+        <v>0.4602903569968053</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1856841660081686</v>
+        <v>-0.182167575679309</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.07578244591578909</v>
-      </c>
-      <c r="L6" s="3" t="n">
-        <v>0.001618996222342073</v>
+        <v>-0.07162238552854727</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>-0.0174497447351627</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -887,7 +887,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D7" s="6" t="inlineStr">
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.493349991977438</v>
+        <v>1.440288831818975</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.028542775811386</v>
+        <v>1.001009037773101</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.180001238669052</v>
+        <v>1.154143996591405</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4346761161162371</v>
+        <v>0.4276759167715161</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1854266510664576</v>
+        <v>-0.1804701277998986</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.06947631963279777</v>
-      </c>
-      <c r="L7" s="3" t="n">
-        <v>0.003374578177727683</v>
+        <v>-0.07108854331958103</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>-0.01635487845860861</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -933,7 +933,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D8" s="6" t="inlineStr">
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -944,25 +944,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.474515780256429</v>
+        <v>1.423848652543255</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9262837732525739</v>
+        <v>0.9059575530649846</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>1.015852309634522</v>
+        <v>0.9951564926246654</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3784264595339513</v>
+        <v>0.3765777159478942</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1375920990750901</v>
+        <v>-0.1327426577215431</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.04443209254659475</v>
-      </c>
-      <c r="L8" s="3" t="n">
-        <v>0.009005539048457356</v>
+        <v>-0.04470774091627172</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>-0.01135372765586395</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -979,7 +979,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="D9" s="6" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -990,25 +990,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.276512095714432</v>
+        <v>1.225086868311845</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9706241032526481</v>
+        <v>0.933738046656581</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.841615521563986</v>
+        <v>0.8112097931937217</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5270874057525829</v>
+        <v>0.5423295454545454</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.02310570626753972</v>
+        <v>0.02676122931442082</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.07005185402602487</v>
+        <v>0.06764995083579151</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-0.003371605613267659</v>
+        <v>-0.007767522617198264</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1017,7 +1017,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>BDRY</t>
+          <t>COPX</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1025,36 +1025,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D10" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight</t>
+          <t>Copper Miners</t>
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.682926829268292</v>
+        <v>1.470326923797775</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.057356608478803</v>
+        <v>0.8159858265543973</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7344139650872819</v>
+        <v>0.7451494999866728</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.385390428211587</v>
+        <v>0.1002023514754371</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.307448494453249</v>
+        <v>0.003620659594345099</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.1861969805895038</v>
+        <v>0.04059040590405893</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.04430379746835444</v>
+        <v>0.003781979977752981</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>COPX</t>
+          <t>BDRY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,36 +1071,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D11" s="9" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Copper Miners</t>
+          <t>Dry Bulk Freight</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.458790040429374</v>
+        <v>1.686666666666667</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.8406845270576686</v>
+        <v>0.9803439803439804</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7198697678003514</v>
+        <v>0.7162162162162162</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.02308836185590812</v>
-      </c>
-      <c r="J11" s="5" t="n">
-        <v>-0.0006041910445887533</v>
+        <v>0.3993055555555558</v>
+      </c>
+      <c r="J11" s="3" t="n">
+        <v>0.2733017377567142</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.07024645791165618</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>0.007283729269385919</v>
+        <v>0.1539012168933429</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>-0.0277442702050662</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1109,44 +1109,40 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>EPU</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XBI</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Peru Equity</t>
+          <t>Biotech</t>
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>1.346457316613031</v>
+        <v>0.9063198657827731</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7170194623650876</v>
+        <v>0.7529947364623264</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6447102092677597</v>
+        <v>0.6413274056180427</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.05892498972400273</v>
+        <v>0.3202616574992243</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.1183287057425373</v>
+        <v>0.2260562302959048</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.04396473779385168</v>
-      </c>
-      <c r="L12" s="3" t="n">
-        <v>0.01639524647887325</v>
+        <v>0.06803476896934835</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>-0.01179173973513947</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1155,40 +1151,44 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>XBI</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>EPU</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Biotech</t>
+          <t>Peru Equity</t>
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>0.9438279414815054</v>
+        <v>1.372062403885896</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.7912143818860746</v>
+        <v>0.6842094408481632</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6427126400631422</v>
+        <v>0.6382863961507237</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.3112843693366956</v>
+        <v>0.1088964293236221</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.2768433092500748</v>
+        <v>0.1208029543117535</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.09040031603897836</v>
-      </c>
-      <c r="L13" s="3" t="n">
-        <v>0.01352509179926575</v>
+        <v>0.02803114571746379</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>-0.0008648648648648116</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OIH</t>
+          <t>PICK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1212,29 +1212,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Oil Services</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.7623034191857612</v>
+        <v>0.9153768621191096</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.7458378122517804</v>
+        <v>0.6111862732966729</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.566193805217065</v>
+        <v>0.5680494196955619</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1406466090859275</v>
-      </c>
-      <c r="J14" s="3" t="n">
-        <v>0.01370530123834701</v>
+        <v>0.1147439514421964</v>
+      </c>
+      <c r="J14" s="5" t="n">
+        <v>-0.01686471847348525</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.1147010072676273</v>
+        <v>0.02750988142292488</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.02401143178410803</v>
+        <v>0.001695437731195959</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>PICK</t>
+          <t>OIH</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1258,29 +1258,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Oil Services</t>
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.9050397034133006</v>
+        <v>0.7922107069610018</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.627556061257635</v>
+        <v>0.7789392683560596</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5517507049189849</v>
+        <v>0.568040184670217</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.06785133457254577</v>
+        <v>0.153764889205821</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.02469373357009885</v>
+        <v>-0.00482948720869314</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.04885150436751862</v>
+        <v>0.1344985197112138</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.01122894572676225</v>
+        <v>0.0006184433551699176</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1308,25 +1308,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8483221832366232</v>
+        <v>0.8602038216720049</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.5962682210125698</v>
+        <v>0.5924359297893469</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5422704685227915</v>
+        <v>0.55959113371793</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.04749732287096031</v>
+        <v>0.07750757759722982</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.1218600260700018</v>
+        <v>-0.1054409819488434</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.03501185660482631</v>
+        <v>0.02105987611837579</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.006826395395529206</v>
+        <v>-0.001077295987072402</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1335,44 +1335,40 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>QTEC</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D17" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Silver</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.6401903224429437</v>
+        <v>1.064827586206897</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.4506798491539374</v>
+        <v>0.6036422067487948</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.5180241978289608</v>
-      </c>
-      <c r="I17" s="3" t="n">
-        <v>0.3565040453774377</v>
+        <v>0.5016068559185858</v>
+      </c>
+      <c r="I17" s="5" t="n">
+        <v>-0.1937525245725057</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.08250021953317255</v>
-      </c>
-      <c r="K17" s="5" t="n">
-        <v>-0.04436315888201092</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>-0.007629374715927395</v>
+        <v>-0.106001791579576</v>
+      </c>
+      <c r="K17" s="3" t="n">
+        <v>0.06795077581594433</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0.01371254443880154</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1381,7 +1377,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BOAT</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1389,36 +1385,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.075281232127661</v>
+        <v>0.6488801942847164</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.6850829235369784</v>
+        <v>0.4569555441382527</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.5092959518884592</v>
+        <v>0.4964096195425953</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.2053651075120586</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.2431251427008061</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0.116469517743403</v>
+        <v>0.364016191691821</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>-0.06774295766310723</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>-0.02636582583343894</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.008838643371017474</v>
+        <v>0.004511868174982059</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1427,40 +1423,44 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>BOAT</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.051478260869565</v>
+        <v>1.097117833650111</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.5876177658142665</v>
+        <v>0.7125862668132095</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4492597577388966</v>
-      </c>
-      <c r="I19" s="5" t="n">
-        <v>-0.217148924873905</v>
-      </c>
-      <c r="J19" s="5" t="n">
-        <v>-0.1091980063434526</v>
+        <v>0.4717219289300643</v>
+      </c>
+      <c r="I19" s="3" t="n">
+        <v>0.2762004709309709</v>
+      </c>
+      <c r="J19" s="3" t="n">
+        <v>0.2684634985667869</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.09546805349182752</v>
+        <v>0.1636615811373094</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.01830110497237558</v>
+        <v>0.02358682391215949</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1473,7 +1473,7 @@
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" s="6" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -1484,25 +1484,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.6936519661417311</v>
+        <v>0.6964322188413878</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4207349212000051</v>
+        <v>0.4134087088715164</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.446349783606302</v>
+        <v>0.4301013011119168</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.3160573132055344</v>
+        <v>0.3139379137806972</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.06329862661013597</v>
+        <v>-0.04768293739939866</v>
       </c>
       <c r="K20" s="5" t="n">
-        <v>-0.01771000535045475</v>
-      </c>
-      <c r="L20" s="5" t="n">
-        <v>-0.0002722718362011545</v>
+        <v>-0.01167231456080897</v>
+      </c>
+      <c r="L20" s="3" t="n">
+        <v>0.0007625272331155397</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IYW</t>
+          <t>DXJ</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1521,34 +1521,34 @@
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>Growth &amp; Technology</t>
+          <t>International</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Japan Hedged Equity</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.6604008188942445</v>
+        <v>0.7020389651276646</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.3817094472205089</v>
+        <v>0.4483841982896968</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4106967477762746</v>
+        <v>0.4208949673876661</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.2980812611137345</v>
-      </c>
-      <c r="J21" s="5" t="n">
-        <v>-0.03551384280651371</v>
-      </c>
-      <c r="K21" s="5" t="n">
-        <v>-0.02054821534214157</v>
-      </c>
-      <c r="L21" s="3" t="n">
-        <v>0.001613293538759386</v>
+        <v>0.1400794867557256</v>
+      </c>
+      <c r="J21" s="3" t="n">
+        <v>0.04255921259492657</v>
+      </c>
+      <c r="K21" s="3" t="n">
+        <v>0.01934642006127318</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>-0.002664446294754486</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1557,44 +1557,40 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>QCLN</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>SIL</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6702603585472395</v>
+        <v>1.909319211433743</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.304563344319208</v>
+        <v>0.6634032263908556</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.4082497372925555</v>
-      </c>
-      <c r="I22" s="3" t="n">
-        <v>0.00554204542457204</v>
-      </c>
-      <c r="J22" s="5" t="n">
-        <v>-0.2896319108373662</v>
-      </c>
-      <c r="K22" s="5" t="n">
-        <v>-0.07362784471218209</v>
+        <v>0.391345863951692</v>
+      </c>
+      <c r="I22" s="5" t="n">
+        <v>-0.0205281830578774</v>
+      </c>
+      <c r="J22" s="3" t="n">
+        <v>0.1329430320622402</v>
+      </c>
+      <c r="K22" s="3" t="n">
+        <v>0.195535394532649</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.005187798298402102</v>
+        <v>0.01479379876380604</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1611,7 +1607,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -1622,25 +1618,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6609424487068054</v>
+        <v>0.6769792095670568</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3906265063595988</v>
+        <v>0.3937272578296995</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.4037451625496926</v>
+        <v>0.3910980430900381</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.3024509998814944</v>
+        <v>0.3114537800223924</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.03930696243430143</v>
-      </c>
-      <c r="K23" s="5" t="n">
-        <v>-0.009345468493915043</v>
+        <v>-0.02342513648093103</v>
+      </c>
+      <c r="K23" s="3" t="n">
+        <v>0.001890028350425288</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.00144529046813302</v>
+        <v>0.007106920451746657</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1653,7 +1649,7 @@
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
-      <c r="D24" s="6" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -1664,25 +1660,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.658726044119706</v>
+        <v>0.6667064380678893</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3875080151199981</v>
+        <v>0.3876825292115467</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3995054400324696</v>
+        <v>0.3883783419455655</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.3027692529572004</v>
+        <v>0.3083894620531504</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-0.03751273430046287</v>
+        <v>-0.02456897176362494</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.008572617561381612</v>
+        <v>-0.000501169395255574</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.002103137881719563</v>
+        <v>0.00444892134642827</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1691,7 +1687,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>DXJ</t>
+          <t>IYW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1701,34 +1697,34 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.6888785153447232</v>
+        <v>0.6752190956809732</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.4472997261317506</v>
+        <v>0.3805158132283537</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.39846199533543</v>
+        <v>0.3837097945266603</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.1171215233764056</v>
-      </c>
-      <c r="J25" s="3" t="n">
-        <v>0.05170181136219942</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0.03492245835726604</v>
+        <v>0.3085193282068714</v>
+      </c>
+      <c r="J25" s="5" t="n">
+        <v>-0.02205855424853942</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>-0.002308273968241403</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.0006108735491754391</v>
+        <v>0.009300265721877699</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1745,7 +1741,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D26" s="6" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -1756,25 +1752,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.5600197361720183</v>
+        <v>0.57889003612364</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3432738802680906</v>
+        <v>0.3502574742205327</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3787268565801516</v>
+        <v>0.3794992222721332</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.08850721231390812</v>
+        <v>0.1141679655950023</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-0.1882099968903905</v>
+        <v>-0.1830497839404744</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>-0.02571428571428569</v>
+        <v>-0.02119736465196209</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.0020570085218925</v>
+        <v>0.002052785923753575</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1783,7 +1779,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1791,36 +1787,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.599265345140771</v>
+        <v>1.149615412126278</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.5276297495868847</v>
+        <v>0.460679362253942</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3576947739375842</v>
+        <v>0.3775952997679377</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.2379972884221135</v>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v>0.2774930011533621</v>
+        <v>0.05275781696118398</v>
+      </c>
+      <c r="J27" s="5" t="n">
+        <v>-0.07694376733826824</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.1251643439389953</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>0.01484678872972212</v>
+        <v>0.0603109363831309</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>-0.006613092248451302</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1829,7 +1825,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ROBO</t>
+          <t>QCLN</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1837,36 +1833,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D28" s="6" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.4304228059809661</v>
+        <v>0.6642964922487335</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.2668871682835519</v>
+        <v>0.297952538868528</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3542365497216067</v>
+        <v>0.3771450929463389</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.04822638501394994</v>
+        <v>0.02734224205237545</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.1198125836680053</v>
+        <v>-0.2865574738084697</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.06450082997391504</v>
-      </c>
-      <c r="L28" s="3" t="n">
-        <v>0.0003803727653099997</v>
+        <v>-0.05750487329434695</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>-0.003092783505154628</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1875,40 +1871,44 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>IBB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>U.S. Industrials</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.5064890661684365</v>
+        <v>0.5882029437675038</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.1715193775875941</v>
+        <v>0.5189599426594367</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3519481311025898</v>
-      </c>
-      <c r="I29" s="5" t="n">
-        <v>-0.09839973032375726</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>-0.1791010194624651</v>
-      </c>
-      <c r="K29" s="5" t="n">
-        <v>-0.1334583401271807</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>0.00235760090531878</v>
+        <v>0.369963871917991</v>
+      </c>
+      <c r="I29" s="3" t="n">
+        <v>0.2619034416105581</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0.2406808110272713</v>
+      </c>
+      <c r="K29" s="3" t="n">
+        <v>0.1087591240875911</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>-0.00533208606173996</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1917,86 +1917,86 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>VDE</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>U.S. Industrials</t>
+        </is>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>0.5419015474990554</v>
+      </c>
+      <c r="G30" s="3" t="n">
+        <v>0.1827700949487048</v>
+      </c>
+      <c r="H30" s="3" t="n">
+        <v>0.3544321023495536</v>
+      </c>
+      <c r="I30" s="5" t="n">
+        <v>-0.06016083033763786</v>
+      </c>
+      <c r="J30" s="5" t="n">
+        <v>-0.1912746585735964</v>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>-0.1267409470752089</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0.003011197892161643</v>
+      </c>
+    </row>
+    <row r="31" ht="21" customHeight="1">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>ROBO</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F30" s="3" t="n">
-        <v>0.57763563626492</v>
-      </c>
-      <c r="G30" s="3" t="n">
-        <v>0.4885317967329457</v>
-      </c>
-      <c r="H30" s="3" t="n">
-        <v>0.3372832413293425</v>
-      </c>
-      <c r="I30" s="3" t="n">
-        <v>0.1724307188753615</v>
-      </c>
-      <c r="J30" s="3" t="n">
-        <v>0.1184119400694059</v>
-      </c>
-      <c r="K30" s="3" t="n">
-        <v>0.1131013615733736</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>0.006952427875403844</v>
-      </c>
-    </row>
-    <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="14" t="n">
-        <v>30</v>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C31" s="14" t="inlineStr"/>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="inlineStr">
-        <is>
-          <t>Energy</t>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5553784769376733</v>
+        <v>0.4401624296382005</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.4852250039825217</v>
+        <v>0.2684843243328814</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3332622677259882</v>
+        <v>0.3538522763309957</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.1761726057449642</v>
-      </c>
-      <c r="J31" s="3" t="n">
-        <v>0.1183807866762665</v>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v>0.1139781271360218</v>
+        <v>0.07770961145194288</v>
+      </c>
+      <c r="J31" s="5" t="n">
+        <v>-0.10758636261007</v>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>-0.06305558847931736</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.006484483557202436</v>
+        <v>0.002409332995181312</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2005,10 +2005,14 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
+          <t>VDE</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D32" s="11" t="inlineStr">
         <is>
           <t>Natural Resources</t>
@@ -2016,75 +2020,71 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>1.891754506523302</v>
+        <v>0.5877913456433581</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.6672956261175087</v>
+        <v>0.5183011998403988</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3304169281812877</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>-0.08229431609059457</v>
+        <v>0.3357578266170063</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.1653733921202758</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.1272811437533774</v>
+        <v>0.1146962530365627</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.2532128769563557</v>
+        <v>0.1366590332363682</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.04454342984409787</v>
+        <v>0.0002178530581122828</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
-      <c r="A33" t="n">
+      <c r="A33" s="14" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>XME</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+      <c r="B33" s="15" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C33" s="14" t="inlineStr"/>
       <c r="D33" s="11" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Metals &amp; Mining</t>
+      <c r="E33" s="14" t="inlineStr">
+        <is>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>1.138159516690923</v>
+        <v>0.5687129409666234</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.4701569616923915</v>
+        <v>0.5174940107120454</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3276216501016522</v>
+        <v>0.335497262805702</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.01653870356081288</v>
-      </c>
-      <c r="J33" s="5" t="n">
-        <v>-0.07008701124089634</v>
+        <v>0.168876982897215</v>
+      </c>
+      <c r="J33" s="3" t="n">
+        <v>0.1164192478729047</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.1073613944001484</v>
+        <v>0.1362763915547025</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.03170078604128879</v>
+        <v>0.0003072196620585999</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2093,40 +2093,40 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SPMO</t>
+          <t>DBC</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Broad Commodities</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5164137058906009</v>
+        <v>0.5049993902836152</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.2765652844358022</v>
+        <v>0.4753972294620112</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3191494568881006</v>
+        <v>0.3159822453829653</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.2217612086303504</v>
-      </c>
-      <c r="J34" s="5" t="n">
-        <v>-0.05529379113093158</v>
-      </c>
-      <c r="K34" s="5" t="n">
-        <v>-0.03228153734206518</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>0.005153222481791842</v>
+        <v>0.2039969834087481</v>
+      </c>
+      <c r="J34" s="3" t="n">
+        <v>0.06860776439089689</v>
+      </c>
+      <c r="K34" s="3" t="n">
+        <v>0.1211376404494382</v>
+      </c>
+      <c r="L34" s="17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CALF</t>
+          <t>XAR</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2143,36 +2143,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D35" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D35" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Small Cap Value</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.547346018746754</v>
+        <v>0.579921948845445</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.3501479602325526</v>
+        <v>0.1735655458803631</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.3079631197695643</v>
-      </c>
-      <c r="I35" s="3" t="n">
-        <v>0.2646287803086949</v>
-      </c>
-      <c r="J35" s="3" t="n">
-        <v>0.1547891535226833</v>
-      </c>
-      <c r="K35" s="3" t="n">
-        <v>0.0322523164647186</v>
+        <v>0.3159459738509016</v>
+      </c>
+      <c r="I35" s="5" t="n">
+        <v>-0.09701987347957486</v>
+      </c>
+      <c r="J35" s="5" t="n">
+        <v>-0.1027213641316745</v>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>-0.1081962563811684</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.01117123407226384</v>
+        <v>0.005395467807042031</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2181,44 +2181,40 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XOP</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D36" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>SPMO</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.6113377635258623</v>
+        <v>0.5337611968125415</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.474668642602462</v>
+        <v>0.2702144256557857</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.3074624785783919</v>
+        <v>0.310955506478674</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2171040605115115</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0.1388450941965242</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0.1278860133759814</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0.006330427563304264</v>
+        <v>0.2221980424408088</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-0.04584554001505492</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>-0.03107739402409004</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>-0.005056717233839048</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2227,40 +2223,44 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>SCHA</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" s="16" t="inlineStr">
+          <t>CALF</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Small Cap Value</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.4105823607387138</v>
+        <v>0.5636227890592904</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2680680110471252</v>
+        <v>0.3566198581073625</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3049261241104444</v>
+        <v>0.3020647274654891</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.1247110045989814</v>
+        <v>0.2670302134348874</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.002583376024379413</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>-0.02824536376604836</v>
+        <v>0.144380801896109</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.04189893903974107</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.00978357545211983</v>
+        <v>0.002595604775912808</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2269,44 +2269,40 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>MTUM</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D38" s="16" t="inlineStr">
+          <t>SCHA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4012338488343969</v>
+        <v>0.4293660830439341</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2327899148299879</v>
+        <v>0.2695640052217778</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.301400531657773</v>
+        <v>0.2934265885798377</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1863279737166403</v>
+        <v>0.1435591718154656</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.09815500418585166</v>
+        <v>-0.006170363829195447</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.05272059996808698</v>
+        <v>-0.01844912078408767</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.001045460677188803</v>
+        <v>0.000293772032902373</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2315,7 +2311,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>XAR</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2323,36 +2319,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D39" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D39" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5475373948854847</v>
+        <v>0.6075761834267475</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.153911667307016</v>
+        <v>0.5046649393937073</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.3001555449378339</v>
-      </c>
-      <c r="I39" s="5" t="n">
-        <v>-0.1276447491957901</v>
-      </c>
-      <c r="J39" s="5" t="n">
-        <v>-0.08427336350791681</v>
-      </c>
-      <c r="K39" s="5" t="n">
-        <v>-0.11248183203942</v>
+        <v>0.2918690298256055</v>
+      </c>
+      <c r="I39" s="3" t="n">
+        <v>0.1849595167568439</v>
+      </c>
+      <c r="J39" s="3" t="n">
+        <v>0.1305286851851388</v>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v>0.1647194140081119</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.006665608633550146</v>
+        <v>-0.003934562021122301</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2361,40 +2357,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DBC</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D40" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Broad Commodities</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5098186873181481</v>
+        <v>0.4344671122363226</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.462323241544637</v>
+        <v>0.1930320317487348</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2965352636432406</v>
+        <v>0.2883691523119736</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.2214996174445294</v>
-      </c>
-      <c r="J40" s="3" t="n">
-        <v>0.05414328161109272</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0.1278700105969623</v>
-      </c>
-      <c r="L40" s="18" t="n">
-        <v>0</v>
+        <v>0.02593323037064765</v>
+      </c>
+      <c r="J40" s="5" t="n">
+        <v>-0.05562855305987047</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>-0.07399829497016197</v>
+      </c>
+      <c r="L40" s="3" t="n">
+        <v>0.0005526897568164379</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2403,40 +2399,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>QQQM</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D41" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4371693358946382</v>
+        <v>0.514970115233254</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2598657263160833</v>
+        <v>0.1458926495616735</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2863674069477622</v>
-      </c>
-      <c r="I41" s="3" t="n">
-        <v>0.1641337974063803</v>
+        <v>0.287515243537251</v>
+      </c>
+      <c r="I41" s="5" t="n">
+        <v>-0.06335012291954489</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.04690722187242302</v>
+        <v>-0.02972052895445654</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.02060195282354116</v>
+        <v>-0.1099968289202473</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.001681537405628042</v>
+        <v>0.0051931772395577</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2445,7 +2441,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ARKQ</t>
+          <t>MTUM</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2453,78 +2449,78 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D42" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.7181767162799211</v>
+        <v>0.4260921063471326</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2380902176809228</v>
+        <v>0.2279328782982473</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2861013719989147</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>-0.02061939690301551</v>
+        <v>0.2864493497867067</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>0.2001473530267921</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.1344089894115106</v>
+        <v>-0.09102745287646519</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.03733076984699191</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>0.0001664585934249008</v>
+        <v>-0.04548680560036134</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>-0.003905197953137707</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
-      <c r="A43" s="14" t="n">
+      <c r="A43" t="n">
         <v>42</v>
       </c>
-      <c r="B43" s="15" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C43" s="14" t="inlineStr"/>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E43" s="14" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>FNDX</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Fundamental Equity</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4368529167152122</v>
+        <v>0.4029695938776281</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2593688767642219</v>
+        <v>0.2930648176661497</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2859095815347252</v>
+        <v>0.2768272502773865</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1634611471792522</v>
-      </c>
-      <c r="J43" s="5" t="n">
-        <v>-0.04638601977083168</v>
-      </c>
-      <c r="K43" s="5" t="n">
-        <v>-0.02063963528355328</v>
+        <v>0.1522086236253049</v>
+      </c>
+      <c r="J43" s="3" t="n">
+        <v>0.04845924817290737</v>
+      </c>
+      <c r="K43" s="3" t="n">
+        <v>0.01271712158808924</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.001794697868972905</v>
+        <v>0.002764127764127711</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2533,40 +2529,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>FNDX</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Fundamental Equity</t>
+          <t>Developed ex-US Hedged</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.375466911653618</v>
+        <v>0.3532948595184806</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.292595187188941</v>
+        <v>0.2749005115875094</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2838721521833716</v>
+        <v>0.276796073095817</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.1396699567010307</v>
+        <v>0.1126356623956433</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.05393383764138182</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0.006794317479925871</v>
+        <v>0.04226173629252483</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>-0.001484623541887609</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.007727975270479082</v>
+        <v>0.0006376195536663687</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2575,40 +2571,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4052164407417695</v>
+        <v>0.4847651985162242</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.1889117314793753</v>
+        <v>0.2900258577442842</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2809720292452051</v>
+        <v>0.2764410668462658</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.003414604883829497</v>
-      </c>
-      <c r="J45" s="5" t="n">
-        <v>-0.04930452578068634</v>
-      </c>
-      <c r="K45" s="5" t="n">
-        <v>-0.07186753158074433</v>
+        <v>0.1191665247897196</v>
+      </c>
+      <c r="J45" s="3" t="n">
+        <v>0.0231747927328485</v>
+      </c>
+      <c r="K45" s="3" t="n">
+        <v>0.01064270905321374</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.008345697329376733</v>
+        <v>0.007301281168204943</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2617,40 +2613,44 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>VEA</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
+          <t>ARKQ</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Developed Markets</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4697897234318233</v>
+        <v>0.7501943024155069</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2833595497650527</v>
+        <v>0.2735967274991811</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2769940298158184</v>
+        <v>0.2764123429615966</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.08468691526367422</v>
-      </c>
-      <c r="J46" s="3" t="n">
-        <v>0.01802751739161801</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0.004984768762115843</v>
+        <v>0.0102572586649019</v>
+      </c>
+      <c r="J46" s="5" t="n">
+        <v>-0.1247670918732979</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>-0.00220588235294128</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.006517819997226448</v>
+        <v>0.01571856287425155</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2667,7 +2667,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D47" s="16" t="inlineStr">
+      <c r="D47" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2678,25 +2678,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4134133316867059</v>
+        <v>0.423794961728853</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2332225735770852</v>
+        <v>0.2347741885421706</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2757304985180495</v>
+        <v>0.2719055559740935</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1225626349433049</v>
+        <v>0.1444185917257119</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-0.003006390685538762</v>
+        <v>-0.01831639366357762</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.0333204583494271</v>
+        <v>-0.02919349416905859</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.01076976925769357</v>
+        <v>0.000879741942363621</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2705,82 +2705,82 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>QQQM</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>International</t>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Developed ex-US Hedged</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.3425492603027773</v>
+        <v>0.4498719607765767</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2690943113501858</v>
+        <v>0.2568614864903487</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2717910693428549</v>
+        <v>0.2651286212082491</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.09157675413903954</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>0.04753066019908592</v>
+        <v>0.1732696764147281</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-0.0366644106201347</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.002120441051738586</v>
+        <v>-0.0065346199424412</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.003197612449371334</v>
+        <v>0.004794192178618095</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
-      <c r="A49" t="n">
+      <c r="A49" s="14" t="n">
         <v>48</v>
       </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr"/>
-      <c r="D49" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>Aerospace &amp; Defense</t>
+      <c r="B49" s="15" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C49" s="14" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E49" s="14" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4721562942640944</v>
+        <v>0.4487851420472242</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.1321275061693294</v>
+        <v>0.2561128108437916</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2691433401374945</v>
-      </c>
-      <c r="I49" s="5" t="n">
-        <v>-0.09344381592008533</v>
+        <v>0.2643266154274972</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0.1731170520537197</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.005082668079171238</v>
+        <v>-0.03670873398118657</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.1079593058049072</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>-0.008294154173689394</v>
+        <v>-0.006496584413773876</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.004793863854266611</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" s="16" t="inlineStr">
+      <c r="D50" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2804,25 +2804,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.3037009198740486</v>
+        <v>0.3242223421056316</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.3052144599135536</v>
+        <v>0.3146859561148418</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2605280875342024</v>
+        <v>0.263601016105808</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1296126708725589</v>
+        <v>0.1381050054109061</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.09141628085037423</v>
+        <v>0.08250224380297744</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.03545051698670587</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>0.006894570525710852</v>
+        <v>0.04042806183115344</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-0.0002856326763781558</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2831,40 +2831,40 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ONEQ</t>
+          <t>XLI</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D51" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.442331434630503</v>
+        <v>0.33741703024905</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2390268420788917</v>
+        <v>0.1692835723404544</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2573872398356056</v>
+        <v>0.2600242508855819</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.153367917315999</v>
+        <v>0.01036017063767081</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.02264657919987823</v>
+        <v>-0.01592041639782404</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.01460202328688687</v>
+        <v>-0.07201502548966987</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.00388915896937303</v>
+        <v>0.0008681560365784158</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2873,10 +2873,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D52" s="13" t="inlineStr">
         <is>
           <t>Industrials</t>
@@ -2884,29 +2888,29 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3122535980209629</v>
+        <v>0.4547552463540872</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.1641885658374895</v>
+        <v>0.1259665090135673</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2540002812603759</v>
+        <v>0.2571876546294987</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>-0.01140411860386537</v>
+        <v>-0.08360844090712327</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.003299279288328738</v>
+        <v>-0.05233926415779167</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.07162017167381973</v>
+        <v>-0.1043767373412547</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.001852602327331754</v>
+        <v>0.004585192883780564</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2915,44 +2919,40 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D53" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr"/>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4251766865363329</v>
+        <v>0.4572635163068262</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1115530147129156</v>
+        <v>0.2378374388933617</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2462702524154461</v>
-      </c>
-      <c r="I53" s="5" t="n">
-        <v>-0.1077931526632692</v>
+        <v>0.2345099188963364</v>
+      </c>
+      <c r="I53" s="3" t="n">
+        <v>0.1665223231173991</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.0360844115177541</v>
-      </c>
-      <c r="K53" s="5" t="n">
-        <v>-0.1080963277759617</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>-0.008599806201550431</v>
+        <v>-0.01300633706212295</v>
+      </c>
+      <c r="K53" s="3" t="n">
+        <v>0.002695417789757348</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0.008130081300812941</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>XMMO</t>
+          <t>VHT</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2969,36 +2969,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D54" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D54" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.2875927188099208</v>
+        <v>0.2268815844347871</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.1591801908302251</v>
+        <v>0.2887537356937762</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2278717830330863</v>
+        <v>0.232203525289612</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.01988774177956154</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>-0.113557361350035</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>-0.05594361980790818</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>0.003048174408587956</v>
+        <v>0.1421225070663346</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0.1426876450360028</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0.04589356323329219</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>-0.005455049773476883</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3007,40 +3007,44 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>VBK</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
-      <c r="D55" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ARGT</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3123152689757225</v>
+        <v>0.240677553598472</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1927413593967722</v>
+        <v>0.2884204467605762</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2265892386860922</v>
+        <v>0.2235574722918989</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.08790190103502149</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>-0.02228600855650553</v>
-      </c>
-      <c r="K55" s="5" t="n">
-        <v>-0.02759512167706402</v>
+        <v>0.1452737131477086</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.04703158860363921</v>
+      </c>
+      <c r="K55" s="3" t="n">
+        <v>0.05301179220227348</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.004091344340307002</v>
+        <v>0.012461695607763</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3049,40 +3053,40 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>IVV</t>
+          <t>VBK</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" s="16" t="inlineStr">
+      <c r="D56" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>US Large Blend</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3344498974423498</v>
+        <v>0.3290269918622535</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2093694746493144</v>
+        <v>0.2003693814959542</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.218570207380995</v>
+        <v>0.2209753940934249</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1231734840166645</v>
-      </c>
-      <c r="J56" s="3" t="n">
-        <v>0.01816479183419473</v>
+        <v>0.1102908821647923</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>-0.02511790903117472</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.007550433020560243</v>
+        <v>-0.01687668129689923</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.004690664401907574</v>
+        <v>0.00364235538981883</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3091,82 +3095,86 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D57" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>Mid Cap Momentum</t>
+        </is>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>0.3126075975841025</v>
+      </c>
+      <c r="G57" s="3" t="n">
+        <v>0.1596562908692358</v>
+      </c>
+      <c r="H57" s="3" t="n">
+        <v>0.2201907477072627</v>
+      </c>
+      <c r="I57" s="3" t="n">
+        <v>0.03132176522867036</v>
+      </c>
+      <c r="J57" s="5" t="n">
+        <v>-0.1173974145683463</v>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>-0.04961065059030401</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-0.001583322338039372</v>
+      </c>
+    </row>
+    <row r="58" ht="21" customHeight="1">
+      <c r="A58" t="n">
+        <v>57</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
           <t>VOO</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" s="16" t="inlineStr">
+      <c r="C58" t="inlineStr"/>
+      <c r="D58" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="E58" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
-      <c r="F57" s="3" t="n">
-        <v>0.334523973648378</v>
-      </c>
-      <c r="G57" s="3" t="n">
-        <v>0.2091848859935945</v>
-      </c>
-      <c r="H57" s="3" t="n">
-        <v>0.2185173768342532</v>
-      </c>
-      <c r="I57" s="3" t="n">
-        <v>0.1232125390588499</v>
-      </c>
-      <c r="J57" s="3" t="n">
-        <v>0.01765140948067367</v>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>-0.007658890236678095</v>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>0.004669560747129653</v>
-      </c>
-    </row>
-    <row r="58" ht="21" customHeight="1">
-      <c r="A58" s="14" t="n">
-        <v>57</v>
-      </c>
-      <c r="B58" s="15" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="C58" s="14" t="inlineStr"/>
-      <c r="D58" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E58" s="14" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
-        </is>
-      </c>
       <c r="F58" s="3" t="n">
-        <v>0.3335442837733791</v>
+        <v>0.3563694608388486</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2086472834252657</v>
+        <v>0.2079928206945116</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.218043206151729</v>
+        <v>0.2099592609858256</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1230677668596916</v>
+        <v>0.1339061954064642</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.01738412538509526</v>
+        <v>0.01788245370122099</v>
       </c>
       <c r="K58" s="5" t="n">
-        <v>-0.007713948634177403</v>
+        <v>-0.00162521198417187</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.004725773845467129</v>
+        <v>0.004321803784421707</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3175,90 +3183,82 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D59" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>IVV</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
+      <c r="D59" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>US Large Blend</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.2232181940545519</v>
+        <v>0.3576697045025226</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2909204695393164</v>
+        <v>0.2090645968507929</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2136427175635649</v>
+        <v>0.2098154909177741</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1257443464086216</v>
+        <v>0.1352291905626939</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.1825870212307843</v>
-      </c>
-      <c r="K59" s="3" t="n">
-        <v>0.06367421882684687</v>
+        <v>0.01856638620077966</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>-0.0006206682528189233</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.008768929382132695</v>
+        <v>0.005293895760981382</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
-      <c r="A60" t="n">
+      <c r="A60" s="14" t="n">
         <v>59</v>
       </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D60" s="16" t="inlineStr">
+      <c r="B60" s="15" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C60" s="14" t="inlineStr"/>
+      <c r="D60" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>S&amp;P 100</t>
+      <c r="E60" s="14" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3555717626923154</v>
+        <v>0.3554251402412061</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2076985088166667</v>
+        <v>0.2073939590513423</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2126543423440079</v>
+        <v>0.2090588317590476</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1374049523019703</v>
+        <v>0.1343078490366874</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.01707243475240117</v>
+        <v>0.01799050820465387</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.004086765168186068</v>
+        <v>-0.001376998921783779</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.006273326451203154</v>
+        <v>0.004665690835903735</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3267,44 +3267,40 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Cash Flow Factor</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.2529801963946936</v>
+        <v>0.3409832415168899</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.155434316292115</v>
+        <v>0.2782227019980155</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2053030980486876</v>
+        <v>0.2053889947304175</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1178798031198742</v>
+        <v>0.1332294197969721</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.1070897453242929</v>
-      </c>
-      <c r="K61" s="5" t="n">
-        <v>-0.04137447405329597</v>
-      </c>
-      <c r="L61" s="3" t="n">
-        <v>0.02091112770724401</v>
+        <v>0.1122590593677719</v>
+      </c>
+      <c r="K61" s="3" t="n">
+        <v>0.06042340488091735</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>-0.001799058953778188</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3313,7 +3309,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>ARGT</t>
+          <t>OEF</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -3321,36 +3317,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D62" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.2115690085119029</v>
+        <v>0.3805867905496703</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2532210842305114</v>
+        <v>0.2058119914760816</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.2019645981679137</v>
+        <v>0.1999814839375798</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1175418368262029</v>
+        <v>0.1492907654851512</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.03592291131957137</v>
+        <v>0.02033121451302589</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.04264392324093813</v>
+        <v>0.004858831254103801</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.02451288497800119</v>
+        <v>0.006709643467964765</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3359,40 +3355,44 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>COWZ</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
-      <c r="D63" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Cash Flow Factor</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3255753025803778</v>
+        <v>0.3166363736436004</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2736281509559286</v>
+        <v>0.1677776943654454</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.2005424647492489</v>
+        <v>0.1988463895307493</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.128603195163649</v>
+        <v>0.1474588248740929</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.1164284086579557</v>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>0.06087721871791096</v>
+        <v>0.08744780234264971</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>-0.02591549295774653</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.006541405706332659</v>
+        <v>0.01185076810534014</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3401,40 +3401,40 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D64" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.412955292450659</v>
+        <v>0.2820750768608502</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2116163036930034</v>
+        <v>0.192817502601238</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1974581803285855</v>
+        <v>0.1955379731175935</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.09449827102051089</v>
+        <v>0.1021304031107457</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.008324437204461077</v>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>0.01182348043297243</v>
+        <v>0.04386963929709498</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>-0.002275519956310035</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.001318391562294075</v>
+        <v>0.002881976212259829</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3443,40 +3443,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RSP</t>
+          <t>VWO</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D65" s="6" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Equal Weight</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2590602287909303</v>
+        <v>0.3977099287660812</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1887959522609914</v>
+        <v>0.2055448259817085</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1964014649108354</v>
+        <v>0.1934138074424667</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.0873772010453242</v>
+        <v>0.1065095393339808</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.04983263282233219</v>
-      </c>
-      <c r="K65" s="5" t="n">
-        <v>-0.0063569904191072</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0.005698791304747486</v>
+        <v>0.006334733328603237</v>
+      </c>
+      <c r="K65" s="3" t="n">
+        <v>0.01016497250458248</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>-0.002468323185782606</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3485,82 +3485,82 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>MGK</t>
+          <t>IAU</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D66" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.3584144714821011</v>
+        <v>0.5250726744186047</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1777698141690642</v>
+        <v>0.2491071428571427</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1925413952650257</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>0.1474657741460264</v>
+        <v>0.1882440476190474</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>-0.1212311557788944</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>-0.01488850355086291</v>
-      </c>
-      <c r="K66" s="5" t="n">
-        <v>-0.01238664012386648</v>
+        <v>-0.004034171808258269</v>
+      </c>
+      <c r="K66" s="3" t="n">
+        <v>0.05122103944896694</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.002920035938903665</v>
+        <v>0.01683827983040587</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
-      <c r="A67" t="n">
+      <c r="A67" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>VUG</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Large Growth</t>
+      <c r="B67" s="15" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="inlineStr"/>
+      <c r="D67" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E67" s="14" t="inlineStr">
+        <is>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3369884791744062</v>
+        <v>0.5212591986917416</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1604589859175878</v>
+        <v>0.2473639300298653</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1799279965236009</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>0.1354302701301024</v>
+        <v>0.1874200036569758</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>-0.1218973247806405</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-0.01363806087534891</v>
-      </c>
-      <c r="K67" s="5" t="n">
-        <v>-0.01650016836906498</v>
+        <v>-0.004765725678994248</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>0.05048249666358684</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.002861394071191459</v>
+        <v>0.01621232434579678</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3569,40 +3569,40 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SCHG</t>
+          <t>MGK</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" s="16" t="inlineStr">
+      <c r="D68" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3373024893975665</v>
+        <v>0.3810864795644295</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.172373183477877</v>
+        <v>0.1769580446494039</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1783445239709731</v>
+        <v>0.1752617636537892</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1440522789333059</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>0.02037569394792604</v>
-      </c>
-      <c r="K68" s="5" t="n">
-        <v>-0.005067567567567544</v>
+        <v>0.157249251447483</v>
+      </c>
+      <c r="J68" s="5" t="n">
+        <v>-0.00627430232577264</v>
+      </c>
+      <c r="K68" s="3" t="n">
+        <v>0.001443321860775004</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.001984689537850803</v>
+        <v>0.01030465949820791</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3611,44 +3611,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D69" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>SCHG</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.08609801074750778</v>
+        <v>0.3582087153267202</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1642790100182674</v>
+        <v>0.1727486014418051</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1598525611471451</v>
+        <v>0.1648623682015131</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.101174555180835</v>
+        <v>0.1550096107687677</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.2130412503202663</v>
+        <v>0.02692694588014244</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.0038163892717058</v>
+        <v>0.0067700987306063</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.007662019793551078</v>
+        <v>0.01047565118912797</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3657,44 +3653,40 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SPGP</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D70" s="16" t="inlineStr">
+          <t>VUG</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr"/>
+      <c r="D70" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2398474775145598</v>
+        <v>0.3554293195877352</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1278932358568845</v>
+        <v>0.1568230121687832</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1565501589155687</v>
+        <v>0.1625881285506414</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.09791655382358777</v>
-      </c>
-      <c r="J70" s="3" t="n">
-        <v>0.04170742938783767</v>
+        <v>0.1433732729334227</v>
+      </c>
+      <c r="J70" s="5" t="n">
+        <v>-0.008659546512509775</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.02477793361383829</v>
+        <v>-0.004958863969345195</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.006999758629012698</v>
+        <v>0.007876712328767299</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3703,82 +3695,90 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IAU</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr"/>
-      <c r="D71" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D71" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.5110866776617187</v>
+        <v>0.2710719492855216</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.2372093023255812</v>
+        <v>0.1356541676369951</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1506376594148535</v>
-      </c>
-      <c r="I71" s="5" t="n">
-        <v>-0.146818416968443</v>
-      </c>
-      <c r="J71" s="5" t="n">
-        <v>-0.01351836344060309</v>
-      </c>
-      <c r="K71" s="3" t="n">
-        <v>0.07523797105228835</v>
+        <v>0.1578989399927713</v>
+      </c>
+      <c r="I71" s="3" t="n">
+        <v>0.1113000730732334</v>
+      </c>
+      <c r="J71" s="3" t="n">
+        <v>0.03900729555650706</v>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>-0.01921132457027297</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.01364474492931778</v>
+        <v>0.008477287268074063</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
-      <c r="A72" s="14" t="n">
+      <c r="A72" t="n">
         <v>71</v>
       </c>
-      <c r="B72" s="15" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C72" s="14" t="inlineStr"/>
-      <c r="D72" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E72" s="14" t="inlineStr">
-        <is>
-          <t>Gold</t>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>IAK</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.5083227112544049</v>
+        <v>0.1412619514421911</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.2356951994840137</v>
+        <v>0.1394997498043227</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.149175343223072</v>
-      </c>
-      <c r="I72" s="5" t="n">
-        <v>-0.1472445951674439</v>
-      </c>
-      <c r="J72" s="5" t="n">
-        <v>-0.01358275921249419</v>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>0.07528864656831291</v>
+        <v>0.1445209337062467</v>
+      </c>
+      <c r="I72" s="3" t="n">
+        <v>0.1115627101770413</v>
+      </c>
+      <c r="J72" s="3" t="n">
+        <v>0.1426580979045964</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>-0.004387149028077797</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.01406427221172013</v>
+        <v>0.01878582775053528</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3787,40 +3787,44 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IGF</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D73" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2747195402131757</v>
+        <v>0.1015875986289971</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1166236745474623</v>
+        <v>0.1801112566673433</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1481871797130763</v>
-      </c>
-      <c r="I73" s="5" t="n">
-        <v>-0.03666734025248963</v>
-      </c>
-      <c r="J73" s="5" t="n">
-        <v>-0.00978710583473108</v>
-      </c>
-      <c r="K73" s="5" t="n">
-        <v>-0.02748986029743128</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>-0.0007717240314865093</v>
+        <v>0.1419592395524549</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0.1303986710963454</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.1714004672322635</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0.03340926347760065</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.007082452431289576</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3829,44 +3833,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IAK</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D74" s="19" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>IGF</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr"/>
+      <c r="D74" s="13" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.09410113148967203</v>
+        <v>0.2799470891518272</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1239553905337922</v>
+        <v>0.1219816880025888</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.144848487075399</v>
-      </c>
-      <c r="I74" s="3" t="n">
-        <v>0.08261244169750315</v>
-      </c>
-      <c r="J74" s="3" t="n">
-        <v>0.1341079537829872</v>
+        <v>0.1416837694000466</v>
+      </c>
+      <c r="I74" s="5" t="n">
+        <v>-0.02178829358849887</v>
+      </c>
+      <c r="J74" s="5" t="n">
+        <v>-0.01328464972191301</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01824966078697421</v>
+        <v>-0.01725703905540421</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.006188290919204587</v>
+        <v>0.002161160852114818</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3875,40 +3875,40 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
-      <c r="D75" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.2746817695793264</v>
+        <v>0.1459765046504415</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1082571922671844</v>
+        <v>0.076311766270869</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1305266135614458</v>
-      </c>
-      <c r="I75" s="3" t="n">
-        <v>0.07857038517978476</v>
+        <v>0.1299304498143374</v>
+      </c>
+      <c r="I75" s="5" t="n">
+        <v>-0.02821848275647121</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>-0.03645432313214547</v>
+        <v>-0.1130796092066086</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.01969827249276956</v>
+        <v>-0.04745308310991947</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.004807307106802217</v>
+        <v>0.009661835748792313</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3917,11 +3917,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>IWF</t>
+          <t>VONG</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" s="16" t="inlineStr">
+      <c r="D76" s="18" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3932,25 +3932,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2732411687757847</v>
+        <v>0.2913795589096753</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1072394225749558</v>
+        <v>0.104710345845773</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1298732470738608</v>
+        <v>0.1172350092451186</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.07728930828279479</v>
+        <v>0.08439051927742858</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>-0.03721651245173074</v>
+        <v>-0.03292598784009748</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.0200321802091713</v>
+        <v>-0.01121041078708063</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.00495008662651597</v>
+        <v>0.005580802040978883</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3959,40 +3959,40 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>IWF</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" s="6" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D77" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.1322298393073846</v>
+        <v>0.2903359067287579</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.06094534340918623</v>
+        <v>0.1037791659060732</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1191826731241958</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>-0.05258328481862073</v>
+        <v>0.1149384497684744</v>
+      </c>
+      <c r="I77" s="3" t="n">
+        <v>0.08481407453509004</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.1264568025348265</v>
+        <v>-0.03210587169787171</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.05203558910757633</v>
+        <v>-0.01000887884413593</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.0002844950213369835</v>
+        <v>0.006895985551268469</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4001,44 +4001,40 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>XRT</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D78" s="20" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+          <t>VFH</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr"/>
+      <c r="D78" s="19" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2182263684126184</v>
+        <v>0.2157261905295593</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.03420960812804097</v>
+        <v>0.1114929144091994</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1037704531448582</v>
+        <v>0.1057314633258233</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.0117649504028432</v>
+        <v>0.1512375242136201</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.04014276424747498</v>
-      </c>
-      <c r="K78" s="5" t="n">
-        <v>-0.06302111532214394</v>
+        <v>0.1233983731618407</v>
+      </c>
+      <c r="K78" s="3" t="n">
+        <v>0.005210533727643796</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0.007099627560521515</v>
+        <v>0.01348857021155747</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4047,7 +4043,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>VFH</t>
+          <t>XLF</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -4062,25 +4058,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1586133891078343</v>
+        <v>0.1964281794933134</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.09602385480860898</v>
+        <v>0.108528806401849</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1018533554901666</v>
+        <v>0.1009361433443021</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.1295468196036684</v>
+        <v>0.1498305405658145</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.139381369844608</v>
-      </c>
-      <c r="K79" s="5" t="n">
-        <v>-0.005290632054176125</v>
+        <v>0.1229081050034344</v>
+      </c>
+      <c r="K79" s="3" t="n">
+        <v>0.006896551724137945</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.01038979650329597</v>
+        <v>0.01283385362469658</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4089,40 +4085,40 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>XLP</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
-      <c r="D80" s="19" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D80" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.140704044424447</v>
+        <v>0.07713759982482316</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.09359173305748358</v>
+        <v>0.08410121328387699</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.09681319544909295</v>
+        <v>0.08818205539952029</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.1302883038932829</v>
+        <v>0.007863983404447605</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.1384343724996053</v>
+        <v>0.04339167695028112</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.002937111264685544</v>
-      </c>
-      <c r="L80" s="3" t="n">
-        <v>0.008916083916083783</v>
+        <v>-0.003750146490097195</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>-0.006079738103589305</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4131,40 +4127,44 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XLP</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr"/>
-      <c r="D81" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>XRT</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.06617299365111395</v>
+        <v>0.2331720999242666</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.09081311938251124</v>
+        <v>0.02480142167430799</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.08788219628136673</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>-0.005517396552006226</v>
+        <v>0.08711239231219814</v>
+      </c>
+      <c r="I81" s="3" t="n">
+        <v>0.02327038718120988</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.04909863512360557</v>
-      </c>
-      <c r="K81" s="3" t="n">
-        <v>0.002694154855335418</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>0.004105571847507372</v>
+        <v>0.03395122569161257</v>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>-0.05731787355064533</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>-0.002315350775642377</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4173,40 +4173,44 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLU</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr"/>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D82" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Mid Growth</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1201465919624274</v>
+        <v>0.1924746362705823</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.04280830060096674</v>
+        <v>0.04599446759114967</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.07901182593264466</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>-0.08605542255785603</v>
+        <v>0.07242424625952126</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0.08292525976067</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.01848056411465371</v>
+        <v>-0.01860319960316859</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.03355248243028786</v>
+        <v>-0.02464489101263345</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.00164473684210531</v>
+        <v>0.0056693551108562</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4215,44 +4219,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D83" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1761597130135908</v>
+        <v>0.146820224798323</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.03931369713782717</v>
+        <v>0.05265204855634087</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.07657098847622512</v>
-      </c>
-      <c r="I83" s="3" t="n">
-        <v>0.07404607190995627</v>
+        <v>0.07055179221919028</v>
+      </c>
+      <c r="I83" s="5" t="n">
+        <v>-0.07236271586553789</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-0.01671832884842872</v>
+        <v>-0.0167471987494392</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.03460737075140008</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>-0.0004382120946540002</v>
+        <v>-0.01672010994044881</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0.006093273962971546</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4280,25 +4280,25 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.1205030710734132</v>
+        <v>-0.1216730038022813</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05843013023583254</v>
+        <v>0.05702217529039078</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0.06335797254487852</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.03191489361702127</v>
+        <v>0.03054221002059032</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.01519243754220123</v>
+        <v>0.01384199864956104</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.004634227077126796</v>
+        <v>-0.005958291956305817</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>0.002667555851950665</v>
+        <v>0.001333777925975443</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4326,25 +4326,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.000758318752550835</v>
+        <v>0.00368354311509278</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05742561359442444</v>
+        <v>0.05295524084668135</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.05705024063965181</v>
+        <v>0.05633973983511709</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.02772710689529378</v>
+        <v>0.01892285298398844</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.01112706389088314</v>
-      </c>
-      <c r="K85" s="3" t="n">
-        <v>0.0003551136363637575</v>
+        <v>0.005747126436781658</v>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>-0.003203987184051238</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.001417936901807804</v>
+        <v>-0.006034788782392719</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4372,25 +4372,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.1161968945179135</v>
+        <v>0.1508328098294096</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.01559968812884494</v>
+        <v>0.02658834751169303</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.05622894192150274</v>
+        <v>0.05221960701231732</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.01064587184835109</v>
-      </c>
-      <c r="J86" s="5" t="n">
-        <v>-0.009453868988128944</v>
+        <v>0.02499793941101514</v>
+      </c>
+      <c r="J86" s="3" t="n">
+        <v>0.001948560455257153</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.03846633261037569</v>
+        <v>-0.02435923007878726</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.003147025930453351</v>
+        <v>0.01359892244728789</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4407,7 +4407,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="6" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -4418,25 +4418,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.1105116155415868</v>
+        <v>0.1247940279135042</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.09824958252660787</v>
+        <v>0.120783857491783</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.04419284585792171</v>
+        <v>0.04943048156188334</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.1134829527981551</v>
+        <v>0.1432426708516079</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.09792839545273435</v>
+        <v>0.09751714709029491</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0.05176892073443806</v>
+        <v>0.06799247514109119</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>0.005393835616438469</v>
+        <v>0.01317243137588164</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4460,25 +4460,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.0862655084118984</v>
+        <v>0.08777456032566833</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.04450386538354123</v>
+        <v>0.04296942544419302</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.04406074666604187</v>
+        <v>0.04081875942089486</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.01453898674401333</v>
+        <v>0.01987998576261063</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.008293782060548871</v>
+        <v>0.007670770309591068</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.0004244185205835027</v>
+        <v>0.002066321349256661</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.0006321112515803584</v>
+        <v>0.001769687776513651</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4506,25 +4506,25 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-0.003435885760119661</v>
+        <v>-0.002176729471000005</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.03887463329993346</v>
+        <v>0.0333653571287249</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.04163026893202892</v>
+        <v>0.03887454029696635</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01774006941766304</v>
-      </c>
-      <c r="J89" s="3" t="n">
-        <v>0.003803727653099997</v>
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="J89" s="17" t="n">
+        <v>0</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.002645502645502673</v>
+        <v>-0.005303030303030143</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.0007572889057174681</v>
+        <v>-0.003793626707131903</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4548,25 +4548,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04684532237506156</v>
+        <v>0.04774427032475792</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.02351380651347768</v>
+        <v>0.02377408116820789</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.02333901366698798</v>
+        <v>0.02297187664176414</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.00436070536305766</v>
+        <v>0.006074386492412209</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.004930708044105225</v>
+        <v>0.00517967661294727</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.0001708063937320148</v>
+        <v>0.0007841902057730277</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.0006128201985537984</v>
+        <v>0.0009799118079372171</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4583,7 +4583,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D91" s="17" t="inlineStr">
+      <c r="D91" s="16" t="inlineStr">
         <is>
           <t>Inflation &amp; Real Assets</t>
         </is>
@@ -4594,25 +4594,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.03364010750443769</v>
+        <v>0.04001502197630691</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.01057215947428825</v>
+        <v>0.0109346073439256</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.01255849561702127</v>
+        <v>0.009802118986184105</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.006798392038007917</v>
+        <v>-0.003926932907339697</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.009978520722056627</v>
-      </c>
-      <c r="K91" s="5" t="n">
-        <v>-0.001961700140121425</v>
+        <v>-0.007474358502731704</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0.001121495327102817</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.0002808725774741117</v>
+        <v>0.002433090024331008</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4621,40 +4621,40 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IWP</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" s="16" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
+          <t>Intermediate Treasury</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.1128325720789105</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>-0.02723710733610807</v>
+        <v>0.03012034097800287</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.001963098308293665</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.01223650869955861</v>
-      </c>
-      <c r="I92" s="3" t="n">
-        <v>0.01097405499207937</v>
+        <v>0.00809950784821778</v>
+      </c>
+      <c r="I92" s="5" t="n">
+        <v>-0.02286637089700239</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.03064075854024395</v>
+        <v>-0.007995838043526104</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.03899643580963041</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>-0.002972737819025517</v>
+        <v>-0.00608710696925352</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>0.002495118246908179</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4663,40 +4663,40 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>IWP</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" s="22" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+      <c r="D93" s="18" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Intermediate Treasury</t>
+          <t>Mid Growth</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.02399122521055363</v>
-      </c>
-      <c r="G93" s="3" t="n">
-        <v>0.002594680477317368</v>
+        <v>0.1344584088903931</v>
+      </c>
+      <c r="G93" s="5" t="n">
+        <v>-0.01502768154574441</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.01093069592805329</v>
-      </c>
-      <c r="I93" s="5" t="n">
-        <v>-0.02863508788495162</v>
+        <v>0.005802548753892411</v>
+      </c>
+      <c r="I93" s="3" t="n">
+        <v>0.02689994717503286</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.009524121922589779</v>
+        <v>-0.02780008779326903</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.008245882219535705</v>
+        <v>-0.02071005917159763</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>0.0005428881650382245</v>
+        <v>0.01105454545454543</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4720,25 +4720,25 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.05385439653051349</v>
-      </c>
-      <c r="G94" s="3" t="n">
-        <v>0.0002607581255067437</v>
-      </c>
-      <c r="H94" s="3" t="n">
-        <v>0.007635735022504697</v>
+        <v>-0.03772960375647705</v>
+      </c>
+      <c r="G94" s="5" t="n">
+        <v>-0.006130486181245676</v>
+      </c>
+      <c r="H94" s="5" t="n">
+        <v>-0.001139194187037562</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.05982671900073333</v>
+        <v>-0.05175013850611898</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.02883747037798634</v>
+        <v>-0.02661789206900678</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.007319090263142813</v>
+        <v>-0.004996984529937354</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>0.0003664345914253797</v>
+        <v>0.003904820012202492</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4755,7 +4755,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="D95" s="6" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -4766,25 +4766,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.04581589958159005</v>
+        <v>0.04033437826541264</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.04508118433619868</v>
+        <v>-0.05397187381223867</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>-0.03476599808978031</v>
+        <v>-0.04389965792474337</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.005569922418937723</v>
+        <v>-0.01171332142148096</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.05553209459459474</v>
+        <v>0.03665139525197825</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.01068672075994459</v>
-      </c>
-      <c r="L95" s="3" t="n">
-        <v>0.008269463493344231</v>
+        <v>-0.01053468495328957</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>-0.003802281368821214</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4801,7 +4801,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D96" s="6" t="inlineStr">
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
@@ -4812,25 +4812,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.08902360493705708</v>
+        <v>-0.05459268084578683</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1232927744675246</v>
+        <v>-0.1158543057221274</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>-0.1214227377250664</v>
+        <v>-0.123677098939435</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.1203562893764936</v>
+        <v>0.1275211450878335</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1860625574977002</v>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>-0.002128482972136192</v>
+        <v>0.1722660653889516</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>0.008926838734717668</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0.02770027899561578</v>
+        <v>0.01049562682215743</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -199,14 +199,14 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.686654966662124</v>
+        <v>1.740482763044557</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.22597821074228</v>
+        <v>1.270576234443266</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.383619836185349</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.4372027525969295</v>
+        <v>0.4659974650133043</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.2104255355214136</v>
+        <v>-0.1946062159474062</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.06613538914634665</v>
-      </c>
-      <c r="L2" s="5" t="n">
-        <v>-0.0170047868702986</v>
+        <v>-0.04742518082203639</v>
+      </c>
+      <c r="L2" s="3" t="n">
+        <v>0.002689765215409201</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -718,25 +718,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.342435491790483</v>
+        <v>2.383094077009304</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.501669362791878</v>
+        <v>1.532100566991992</v>
       </c>
       <c r="H3" s="7" t="n">
         <v>1.371951096040239</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4187211706696357</v>
+        <v>0.4359790042945761</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.1254105995979802</v>
+        <v>-0.1147717801637496</v>
       </c>
       <c r="K3" s="3" t="n">
-        <v>0.05468842379094241</v>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v>-0.002627753550262901</v>
+        <v>0.06751803239919596</v>
+      </c>
+      <c r="L3" s="3" t="n">
+        <v>0.009504640500950456</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -764,25 +764,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.409287615528959</v>
+        <v>1.476694965000443</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.051954947178543</v>
+        <v>1.109364798676841</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>1.322415522367409</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3384103426207239</v>
+        <v>0.3758565541563594</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>-0.2187398611239915</v>
+        <v>-0.1968816674945051</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>-0.1164565826330533</v>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v>-0.02352759074375055</v>
+        <v>-0.09173669467787127</v>
+      </c>
+      <c r="L4" s="3" t="n">
+        <v>0.003792276139617634</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -810,25 +810,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.823781009409752</v>
+        <v>1.874251497005988</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.193355481727575</v>
+        <v>1.232558139534884</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>1.278073089700996</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5310760667903525</v>
+        <v>0.5584415584415585</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1773208722741434</v>
+        <v>-0.1626168224299065</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>-0.03718827475572406</v>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v>-0.01389096340552665</v>
+        <v>-0.01997958290797708</v>
+      </c>
+      <c r="L5" s="3" t="n">
+        <v>0.003734129947722264</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.45566593275839</v>
+        <v>1.503065683150183</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.048117633301714</v>
+        <v>1.087650673245424</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.206125612440316</v>
+        <v>1.206125472503677</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4602903569968053</v>
+        <v>0.4884771708047568</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.182167575679309</v>
+        <v>-0.1663816121824047</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.07162238552854727</v>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v>-0.0174497447351627</v>
+        <v>-0.05370265686828724</v>
+      </c>
+      <c r="L6" s="3" t="n">
+        <v>0.001515634971282598</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.440288831818975</v>
+        <v>1.484475817840979</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.001009037773101</v>
+        <v>1.037241862850647</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.154143996591405</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4276759167715161</v>
+        <v>0.4535272401705219</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.1804701277998986</v>
+        <v>-0.165630673332319</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.07108854331958103</v>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v>-0.01635487845860861</v>
+        <v>-0.05426848619485869</v>
+      </c>
+      <c r="L7" s="3" t="n">
+        <v>0.001456256301109127</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -944,25 +944,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.423848652543255</v>
+        <v>1.461126298431551</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9059575530649846</v>
+        <v>0.9352702787860103</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.9951564926246654</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3765777159478942</v>
+        <v>0.3977488301504994</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1327426577215431</v>
+        <v>-0.1194046499768935</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.04470774091627172</v>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v>-0.01135372765586395</v>
+        <v>-0.03001579778830965</v>
+      </c>
+      <c r="L8" s="3" t="n">
+        <v>0.003851184420869069</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -990,25 +990,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.225086868311845</v>
+        <v>1.256850403455365</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.933738046656581</v>
+        <v>0.9613425223640566</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.8112097931937217</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5423295454545454</v>
+        <v>0.5643465909090908</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.02676122931442082</v>
+        <v>0.04141843971631198</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.06764995083579151</v>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v>-0.007767522617198264</v>
+        <v>0.08289085545722696</v>
+      </c>
+      <c r="L9" s="3" t="n">
+        <v>0.006396783331810152</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1036,25 +1036,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.470326923797775</v>
+        <v>1.497975751291523</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8159858265543973</v>
+        <v>0.8363110225297958</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.7451494999866728</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.1002023514754371</v>
+        <v>0.1125162297443887</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.003620659594345099</v>
+        <v>0.01485355926400711</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.04059040590405893</v>
+        <v>0.05223708487084866</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.003781979977752981</v>
+        <v>0.01501668520578403</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1082,25 +1082,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.686666666666667</v>
+        <v>1.69</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.9803439803439804</v>
+        <v>0.9828009828009827</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.7162162162162162</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.3993055555555558</v>
+        <v>0.4010416666666667</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2733017377567142</v>
+        <v>0.2748815165876777</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.1539012168933429</v>
+        <v>0.1553328561202576</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.0277442702050662</v>
+        <v>-0.02653799758745468</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.9063198657827731</v>
+        <v>0.917518415967276</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7529947364623264</v>
+        <v>0.7632925882981105</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.6413274056180427</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.3202616574992243</v>
+        <v>0.3280174474343562</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.2260562302959048</v>
+        <v>0.2332586166689563</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.06803476896934835</v>
+        <v>0.07430886870139219</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.01179173973513947</v>
+        <v>-0.005986575557840101</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.372062403885896</v>
+        <v>1.373602370821983</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6842094408481632</v>
+        <v>0.6853028466742928</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6382863961507237</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1088964293236221</v>
+        <v>0.1096163361160849</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.1208029543117535</v>
+        <v>0.121530590940824</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.02803114571746379</v>
+        <v>0.02869855394883203</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.0008648648648648116</v>
+        <v>-0.0002162162162161474</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1216,25 +1216,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9153768621191096</v>
+        <v>0.9209763026933415</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6111862732966729</v>
+        <v>0.6158966193795532</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.5680494196955619</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1147439514421964</v>
+        <v>0.1180029351439047</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.01686471847348525</v>
+        <v>-0.01399049623175508</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.02750988142292488</v>
+        <v>0.03051383399209495</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.001695437731195959</v>
+        <v>0.004623921085080251</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.7922107069610018</v>
+        <v>0.7633285657752276</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.7789392683560596</v>
+        <v>0.7502710013325351</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.568040184670217</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.153764889205821</v>
+        <v>0.1351715394976627</v>
       </c>
       <c r="J15" s="5" t="n">
-        <v>-0.00482948720869314</v>
+        <v>-0.02086702963756071</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.1344985197112138</v>
-      </c>
-      <c r="L15" s="3" t="n">
-        <v>0.0006184433551699176</v>
+        <v>0.1162156547031632</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>-0.01550689449814457</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1308,25 +1308,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8602038216720049</v>
+        <v>0.8672253513305133</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.5924359297893469</v>
+        <v>0.5984468730404104</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.55959113371793</v>
+        <v>0.559591261434137</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.07750757759722982</v>
+        <v>0.08157474019802802</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.1054409819488434</v>
+        <v>-0.1020643774051078</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.02105987611837579</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>-0.001077295987072402</v>
+        <v>0.02491397109428761</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.002693239967680894</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1350,25 +1350,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.064827586206897</v>
+        <v>1.087931034482759</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.6036422067487948</v>
+        <v>0.6215854311730047</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.5016068559185858</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.1937525245725057</v>
+        <v>-0.1847313854853911</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.106001791579576</v>
+        <v>-0.09599880561361607</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.06795077581594433</v>
+        <v>0.07990012484394504</v>
       </c>
       <c r="L17" s="3" t="n">
-        <v>0.01371254443880154</v>
+        <v>0.02505501946842714</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.6488801942847164</v>
+        <v>0.6640680960872998</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4569555441382527</v>
+        <v>0.4703756202673739</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.4964096195425953</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.364016191691821</v>
+        <v>0.3765801997066884</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.06774295766310723</v>
+        <v>-0.05915590054224606</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.02636582583343894</v>
+        <v>-0.01739764228672835</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.004511868174982059</v>
+        <v>0.01376446740338699</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1442,25 +1442,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.097117833650111</v>
+        <v>1.097534424399743</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.7125862668132095</v>
+        <v>0.7129265818194397</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4717219289300643</v>
+        <v>0.4717220244192444</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.2762004709309709</v>
+        <v>0.276453987115105</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.2684634985667869</v>
+        <v>0.2687154778076624</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.1636615811373094</v>
+        <v>0.1638927415626446</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.02358682391215949</v>
+        <v>0.02379015860105738</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1484,25 +1484,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.6964322188413878</v>
+        <v>0.717021333068101</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4134087088715164</v>
+        <v>0.4305628474411445</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.4301013011119168</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.3139379137806972</v>
+        <v>0.329884803667118</v>
       </c>
       <c r="J20" s="5" t="n">
-        <v>-0.04768293739939866</v>
-      </c>
-      <c r="K20" s="5" t="n">
-        <v>-0.01167231456080897</v>
+        <v>-0.03612493669405781</v>
+      </c>
+      <c r="K20" s="3" t="n">
+        <v>0.0003227368081328841</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.0007625272331155397</v>
+        <v>0.0129084967320261</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1530,25 +1530,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.7020389651276646</v>
+        <v>0.7055440267244657</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4483841982896968</v>
+        <v>0.4513669007629377</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.4208949673876661</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1400794867557256</v>
+        <v>0.1424272877803798</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.04255921259492657</v>
+        <v>0.04470618709629082</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.01934642006127318</v>
+        <v>0.0214455917394758</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.002664446294754486</v>
+        <v>-0.0006106022758812779</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1572,25 +1572,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.909319211433743</v>
+        <v>1.944469248835988</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.6634032263908556</v>
+        <v>0.6835002598799513</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0.391345863951692</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.0205281830578774</v>
+        <v>-0.008694324860174407</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.1329430320622402</v>
+        <v>0.1466311106323381</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.195535394532649</v>
+        <v>0.2099797063387847</v>
       </c>
       <c r="L22" s="3" t="n">
-        <v>0.01479379876380604</v>
+        <v>0.02705441280778187</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1618,25 +1618,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6769792095670568</v>
+        <v>0.6899844990408226</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3937272578296995</v>
+        <v>0.4045362517594182</v>
       </c>
       <c r="H23" s="3" t="n">
         <v>0.3910980430900381</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.3114537800223924</v>
+        <v>0.3216247054080685</v>
       </c>
       <c r="J23" s="5" t="n">
-        <v>-0.02342513648093103</v>
+        <v>-0.01585135063983989</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.001890028350425288</v>
+        <v>0.009660144902173595</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.007106920451746657</v>
+        <v>0.01491749639376572</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1660,25 +1660,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6667064380678893</v>
+        <v>0.6836996126106114</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3876825292115467</v>
+        <v>0.4018307214699295</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.3883783419455655</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.3083894620531504</v>
+        <v>0.3217292175579545</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-0.02456897176362494</v>
-      </c>
-      <c r="K24" s="5" t="n">
-        <v>-0.000501169395255574</v>
+        <v>-0.01462391197381729</v>
+      </c>
+      <c r="K24" s="3" t="n">
+        <v>0.009689274974941542</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.00444892134642827</v>
+        <v>0.01468983463443307</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1706,25 +1706,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.6752190956809732</v>
+        <v>0.6875814244111482</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.3805158132283537</v>
+        <v>0.3907036290552424</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.3837097945266603</v>
+        <v>0.383709910797144</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.3085193282068714</v>
+        <v>0.3181757195953701</v>
       </c>
       <c r="J25" s="5" t="n">
-        <v>-0.02205855424853942</v>
-      </c>
-      <c r="K25" s="5" t="n">
-        <v>-0.002308273968241403</v>
+        <v>-0.01484170605100388</v>
+      </c>
+      <c r="K25" s="3" t="n">
+        <v>0.005054324033907598</v>
       </c>
       <c r="L25" s="3" t="n">
-        <v>0.009300265721877699</v>
+        <v>0.01674853047749414</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1752,25 +1752,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.57889003612364</v>
+        <v>0.5936762465877772</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3502574742205327</v>
+        <v>0.3629025544590627</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.3794992222721332</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.1141679655950023</v>
+        <v>0.124602081749243</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-0.1830497839404744</v>
+        <v>-0.1753990941793082</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>-0.02119736465196209</v>
+        <v>-0.01203093669435673</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.002052785923753575</v>
+        <v>0.0114369501466276</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1798,25 +1798,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.149615412126278</v>
+        <v>1.144362434242556</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.460679362253942</v>
+        <v>0.4571098247545431</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3775952997679377</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.05275781696118398</v>
+        <v>0.05018513838261507</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>-0.07694376733826824</v>
+        <v>-0.07919948746527516</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.0603109363831309</v>
+        <v>0.05771979985704068</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>-0.006613092248451302</v>
+        <v>-0.009040683073832212</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1844,25 +1844,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6642964922487335</v>
+        <v>0.6911455359706367</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.297952538868528</v>
+        <v>0.318891587065373</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.3771450929463389</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.02734224205237545</v>
+        <v>0.04391570531609523</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-0.2865574738084697</v>
+        <v>-0.2750479563228566</v>
       </c>
       <c r="K28" s="5" t="n">
-        <v>-0.05750487329434695</v>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v>-0.003092783505154628</v>
+        <v>-0.04230019493177373</v>
+      </c>
+      <c r="L28" s="3" t="n">
+        <v>0.01298969072164957</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1890,25 +1890,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.5882029437675038</v>
+        <v>0.5967914577585347</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.5189599426594367</v>
+        <v>0.5271740117559209</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.369963871917991</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.2619034416105581</v>
+        <v>0.2687274280577141</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.2406808110272713</v>
+        <v>0.2473900320029196</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.1087591240875911</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>-0.00533208606173996</v>
+        <v>0.1147549530761209</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>4.677268475217211e-05</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1932,25 +1932,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5419015474990554</v>
+        <v>0.5570905579585168</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.1827700949487048</v>
+        <v>0.1944213624193507</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3544321023495536</v>
       </c>
       <c r="I30" s="5" t="n">
-        <v>-0.06016083033763786</v>
+        <v>-0.05090263418278773</v>
       </c>
       <c r="J30" s="5" t="n">
-        <v>-0.1912746585735964</v>
+        <v>-0.1833080424886192</v>
       </c>
       <c r="K30" s="5" t="n">
-        <v>-0.1267409470752089</v>
+        <v>-0.1181386203506473</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.003011197892161643</v>
+        <v>0.01289169097581633</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1978,25 +1978,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.4401624296382005</v>
+        <v>0.4532796585988519</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.2684843243328814</v>
+        <v>0.28003788174616</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3538522763309957</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.07770961145194288</v>
+        <v>0.08752556237218823</v>
       </c>
       <c r="J31" s="5" t="n">
-        <v>-0.10758636261007</v>
+        <v>-0.09945811695642359</v>
       </c>
       <c r="K31" s="5" t="n">
-        <v>-0.06305558847931736</v>
+        <v>-0.05452174943700372</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.002409332995181312</v>
+        <v>0.01153943697692106</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2024,25 +2024,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5877913456433581</v>
+        <v>0.5749092872347774</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.5183011998403988</v>
+        <v>0.5059828290929869</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3357578266170063</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1653733921202758</v>
+        <v>0.1559184160557006</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.1146962530365627</v>
+        <v>0.1056524337225171</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.1366590332363682</v>
-      </c>
-      <c r="L32" s="3" t="n">
-        <v>0.0002178530581122828</v>
+        <v>0.1274370242000371</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>-0.00789717335657103</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2066,25 +2066,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.5687129409666234</v>
+        <v>0.5566682979375626</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.5174940107120454</v>
+        <v>0.5058424903595264</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.335497262805702</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.168876982897215</v>
+        <v>0.1599021903381148</v>
       </c>
       <c r="J33" s="3" t="n">
-        <v>0.1164192478729047</v>
+        <v>0.1078472327633153</v>
       </c>
       <c r="K33" s="3" t="n">
-        <v>0.1362763915547025</v>
-      </c>
-      <c r="L33" s="3" t="n">
-        <v>0.0003072196620585999</v>
+        <v>0.1275519106613157</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>-0.007373271889400734</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2108,25 +2108,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5049993902836152</v>
+        <v>0.5064134204028921</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.4753972294620112</v>
+        <v>0.4767834467148726</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3159822453829653</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0.2039969834087481</v>
+        <v>0.2051282051282053</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0.06860776439089689</v>
+        <v>0.06961178045515393</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0.1211376404494382</v>
-      </c>
-      <c r="L34" s="17" t="n">
-        <v>0</v>
+        <v>0.122191011235955</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.0009395552771689353</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2154,25 +2154,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.579921948845445</v>
+        <v>0.5948067278992044</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1735655458803631</v>
+        <v>0.1846218709339815</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.3159459738509016</v>
+        <v>0.3159458801758652</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.09701987347957486</v>
+        <v>-0.08851270660148058</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1027213641316745</v>
+        <v>-0.09426791220367348</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1081962563811684</v>
+        <v>-0.0997943845717526</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.005395467807042031</v>
+        <v>0.01486751129051589</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2185,7 +2185,7 @@
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
-      <c r="D36" s="18" t="inlineStr">
+      <c r="D36" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2196,25 +2196,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5337611968125415</v>
+        <v>0.5528278710311592</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2702144256557857</v>
+        <v>0.286004865974721</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.310955506478674</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2221980424408088</v>
+        <v>0.2373915757980742</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.04584554001505492</v>
+        <v>-0.03398414185178045</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.03107739402409004</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>-0.005056717233839048</v>
+        <v>-0.01903240833166975</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.007311739784064519</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2231,7 +2231,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D37" s="18" t="inlineStr">
+      <c r="D37" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2242,25 +2242,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.5636227890592904</v>
+        <v>0.5611941259787481</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.3566198581073625</v>
+        <v>0.3545125783829983</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.3020647274654891</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.2670302134348874</v>
+        <v>0.2650620960857479</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.144380801896109</v>
+        <v>0.1426031996839818</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0.04189893903974107</v>
+        <v>0.04028052508541635</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.002595604775912808</v>
+        <v>0.001038241910365167</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2273,7 +2273,7 @@
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" s="18" t="inlineStr">
+      <c r="D38" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2284,25 +2284,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4293660830439341</v>
+        <v>0.4360826343886341</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2695640052217778</v>
+        <v>0.275529651061293</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.2934265885798377</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1435591718154656</v>
+        <v>0.1489327980563964</v>
       </c>
       <c r="J38" s="5" t="n">
-        <v>-0.006170363829195447</v>
+        <v>-0.00150038609682146</v>
       </c>
       <c r="K38" s="5" t="n">
-        <v>-0.01844912078408767</v>
+        <v>-0.01383684058806567</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.000293772032902373</v>
+        <v>0.004994124559341895</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2330,25 +2330,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.6075761834267475</v>
+        <v>0.6069912039968199</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.5046649393937073</v>
+        <v>0.5041175938689426</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2918690298256055</v>
+        <v>0.2918691069058941</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1849595167568439</v>
+        <v>0.1845283984295416</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.1305286851851388</v>
+        <v>0.1301173701749363</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.1647194140081119</v>
+        <v>0.1642956595435561</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.003934562021122301</v>
+        <v>-0.004296955891488818</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2372,25 +2372,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4344671122363226</v>
+        <v>0.4445040374261513</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.1930320317487348</v>
+        <v>0.2013795215676357</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.2883691523119736</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.02593323037064765</v>
+        <v>0.03311155162899504</v>
       </c>
       <c r="J40" s="5" t="n">
-        <v>-0.05562855305987047</v>
+        <v>-0.04902090898258737</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.07399829497016197</v>
+        <v>-0.06751918158567771</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.0005526897568164379</v>
+        <v>0.007553426676492281</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2414,25 +2414,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.514970115233254</v>
+        <v>0.5247535358004729</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1458926495616735</v>
+        <v>0.1532926592557828</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.287515243537251</v>
+        <v>0.2875151432739573</v>
       </c>
       <c r="I41" s="5" t="n">
-        <v>-0.06335012291954489</v>
+        <v>-0.05730129950277807</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.02972052895445654</v>
+        <v>-0.02345452782758695</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.1099968289202473</v>
+        <v>-0.1042492468685587</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.0051931772395577</v>
+        <v>0.01168464878900477</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2449,7 +2449,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D42" s="18" t="inlineStr">
+      <c r="D42" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2460,25 +2460,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4260921063471326</v>
+        <v>0.4431543141897338</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2279328782982473</v>
+        <v>0.2426242477357754</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2864493497867067</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.2001473530267921</v>
+        <v>0.2145062878304791</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.09102745287646519</v>
+        <v>-0.08015222367267538</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.04548680560036134</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>-0.003905197953137707</v>
+        <v>-0.03406671398154715</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0.008012388903851253</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2491,7 +2491,7 @@
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" s="18" t="inlineStr">
+      <c r="D43" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2502,25 +2502,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4029695938776281</v>
+        <v>0.4089855054709055</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2930648176661497</v>
+        <v>0.2986093528720688</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.2768272502773865</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1522086236253049</v>
+        <v>0.1571491812763781</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.04845924817290737</v>
+        <v>0.05295493867043288</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.01271712158808924</v>
+        <v>0.01705955334987586</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.002764127764127711</v>
+        <v>0.007063882063881977</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2544,25 +2544,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.3532948595184806</v>
+        <v>0.3564567633958602</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2749005115875094</v>
+        <v>0.2778792511005641</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.276796073095817</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.1126356623956433</v>
+        <v>0.1152352784292778</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.04226173629252483</v>
-      </c>
-      <c r="K44" s="5" t="n">
-        <v>-0.001484623541887609</v>
+        <v>0.04469692726517094</v>
+      </c>
+      <c r="K44" s="3" t="n">
+        <v>0.0008483563096499669</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.0006376195536663687</v>
+        <v>0.002975557917109573</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2586,25 +2586,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4847651985162242</v>
+        <v>0.4912630768467108</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2900258577442842</v>
+        <v>0.2956715723306258</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2764410668462658</v>
+        <v>0.2764411527521891</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1191665247897196</v>
+        <v>0.1240644089244667</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.0231747927328485</v>
+        <v>0.02765258176012564</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.01064270905321374</v>
+        <v>0.01506565307532837</v>
       </c>
       <c r="L45" s="3" t="n">
-        <v>0.007301281168204943</v>
+        <v>0.01170960187353631</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2632,25 +2632,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.7501943024155069</v>
+        <v>0.7599390999725573</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2735967274991811</v>
+        <v>0.2806879071823012</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.2764123429615966</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.0102572586649019</v>
+        <v>0.01588220696500953</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-0.1247670918732979</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>-0.00220588235294128</v>
+        <v>-0.1198939372223018</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.003349673202614367</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.01571856287425155</v>
+        <v>0.02137391882900874</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2667,7 +2667,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D47" s="18" t="inlineStr">
+      <c r="D47" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2678,25 +2678,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.423794961728853</v>
+        <v>0.4300904064736903</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2347741885421706</v>
+        <v>0.2402338409176885</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2719055559740935</v>
+        <v>0.2719056836332476</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1444185917257119</v>
+        <v>0.1494786142653046</v>
       </c>
       <c r="J47" s="5" t="n">
-        <v>-0.01831639366357762</v>
+        <v>-0.01397590041161056</v>
       </c>
       <c r="K47" s="5" t="n">
-        <v>-0.02919349416905859</v>
+        <v>-0.02490109378636252</v>
       </c>
       <c r="L47" s="3" t="n">
-        <v>0.000879741942363621</v>
+        <v>0.005305110500919863</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2720,25 +2720,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4498719607765767</v>
+        <v>0.4601991371572396</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2568614864903487</v>
+        <v>0.2658141449962368</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2651286212082491</v>
+        <v>0.2651287865880634</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1732696764147281</v>
+        <v>0.1816267537227056</v>
       </c>
       <c r="J48" s="5" t="n">
-        <v>-0.0366644106201347</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>-0.0065346199424412</v>
+        <v>-0.02980267187770436</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.0005417301506684957</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.004794192178618095</v>
+        <v>0.01195123621669758</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2762,25 +2762,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4487851420472242</v>
+        <v>0.4590110475036924</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2561128108437916</v>
+        <v>0.2649786483723819</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2643266154274972</v>
+        <v>0.2643264794090734</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1731170520537197</v>
+        <v>0.181397338539907</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.03670873398118657</v>
-      </c>
-      <c r="K49" s="5" t="n">
-        <v>-0.006496584413773876</v>
+        <v>-0.02990957161579222</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.0005158232259863116</v>
       </c>
       <c r="L49" s="3" t="n">
-        <v>0.004793863854266611</v>
+        <v>0.01188596243866669</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" s="18" t="inlineStr">
+      <c r="D50" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2804,25 +2804,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.3242223421056316</v>
+        <v>0.3272490402503263</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.3146859561148418</v>
+        <v>0.3176910469915384</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.263601016105808</v>
+        <v>0.2636011066361277</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1381050054109061</v>
+        <v>0.1407063175317573</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.08250224380297744</v>
+        <v>0.08497653464595567</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.04042806183115344</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>-0.0002856326763781558</v>
+        <v>0.04280618311533879</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.001999428734647202</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2846,25 +2846,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.33741703024905</v>
+        <v>0.3500233872127012</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1692835723404544</v>
+        <v>0.1803048593588521</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2600242508855819</v>
+        <v>0.2600241208840632</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.01036017063767081</v>
+        <v>0.01988360253577648</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.01592041639782404</v>
+        <v>-0.006644699510808816</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.07201502548966987</v>
+        <v>-0.06326804400321973</v>
       </c>
       <c r="L51" s="3" t="n">
-        <v>0.0008681560365784158</v>
+        <v>0.01030211830072925</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2892,25 +2892,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4547552463540872</v>
+        <v>0.4658218257537681</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.1259665090135673</v>
+        <v>0.1345318579441113</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0.2571876546294987</v>
       </c>
       <c r="I52" s="5" t="n">
-        <v>-0.08360844090712327</v>
+        <v>-0.0766372726971023</v>
       </c>
       <c r="J52" s="5" t="n">
-        <v>-0.05233926415779167</v>
+        <v>-0.04513030651536987</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.1043767373412547</v>
+        <v>-0.09756363438164284</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.004585192883780564</v>
+        <v>0.01222718102341513</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2923,7 +2923,7 @@
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
-      <c r="D53" s="18" t="inlineStr">
+      <c r="D53" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4572635163068262</v>
+        <v>0.4656577349564508</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2378374388933617</v>
+        <v>0.2449678388869871</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2345099188963364</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1665223231173991</v>
+        <v>0.173241921752868</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.01300633706212295</v>
+        <v>-0.007320889694969135</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.002695417789757348</v>
+        <v>0.008471313053523444</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.008130081300812941</v>
+        <v>0.01393728222996526</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.2268815844347871</v>
+        <v>0.2348657727288193</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2887537356937762</v>
+        <v>0.2971403403944994</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.232203525289612</v>
+        <v>0.2322034502011048</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1421225070663346</v>
+        <v>0.1495549745743585</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.1426876450360028</v>
+        <v>0.1501237902314649</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.04589356323329219</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>-0.005455049773476883</v>
+        <v>0.05269981201789076</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0.001017043178105803</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.240677553598472</v>
+        <v>0.2116382888249806</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2884204467605762</v>
+        <v>0.2582637131398686</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.2235574722918989</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1452737131477086</v>
+        <v>0.1184674680457849</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.04703158860363921</v>
+        <v>0.02252479597288404</v>
       </c>
       <c r="K55" s="3" t="n">
-        <v>0.05301179220227348</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>0.012461695607763</v>
+        <v>0.02836502709019451</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>-0.01123595505617991</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
-      <c r="D56" s="18" t="inlineStr">
+      <c r="D56" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3068,25 +3068,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3290269918622535</v>
+        <v>0.3374867679272771</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2003693814959542</v>
+        <v>0.2080104565202092</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2209753940934249</v>
+        <v>0.2209756517461703</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1102908821647923</v>
+        <v>0.1173583174295871</v>
       </c>
       <c r="J56" s="5" t="n">
-        <v>-0.02511790903117472</v>
+        <v>-0.01891240362767499</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.01687668129689923</v>
+        <v>-0.01061871725895513</v>
       </c>
       <c r="L56" s="3" t="n">
-        <v>0.00364235538981883</v>
+        <v>0.01003093111323095</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3103,7 +3103,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D57" s="18" t="inlineStr">
+      <c r="D57" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3114,25 +3114,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.3126075975841025</v>
+        <v>0.3249234179352378</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1596562908692358</v>
+        <v>0.1705373047825107</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2201907477072627</v>
+        <v>0.2201908903742278</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.03132176522867036</v>
+        <v>0.04099849911676801</v>
       </c>
       <c r="J57" s="5" t="n">
-        <v>-0.1173974145683463</v>
+        <v>-0.1091160899263948</v>
       </c>
       <c r="K57" s="5" t="n">
-        <v>-0.04961065059030401</v>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v>-0.001583322338039372</v>
+        <v>-0.04069329314242665</v>
+      </c>
+      <c r="L57" s="3" t="n">
+        <v>0.007784668162026609</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3145,7 +3145,7 @@
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="18" t="inlineStr">
+      <c r="D58" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3156,25 +3156,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3563694608388486</v>
+        <v>0.364567772959709</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2079928206945116</v>
+        <v>0.215294298993564</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.2099592609858256</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1339061954064642</v>
+        <v>0.1407598714690101</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.01788245370122099</v>
-      </c>
-      <c r="K58" s="5" t="n">
-        <v>-0.00162521198417187</v>
+        <v>0.02403484676131606</v>
+      </c>
+      <c r="K58" s="3" t="n">
+        <v>0.004409270774448748</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>0.004321803784421707</v>
+        <v>0.01039223212635587</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3187,7 +3187,7 @@
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
-      <c r="D59" s="18" t="inlineStr">
+      <c r="D59" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3198,25 +3198,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3576697045025226</v>
+        <v>0.3651352659470111</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2090645968507929</v>
+        <v>0.2157130219912173</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2098154909177741</v>
+        <v>0.2098153754032503</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1352291905626939</v>
+        <v>0.1414716149605197</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.01856638620077966</v>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>-0.0006206682528189233</v>
+        <v>0.02416739430210635</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0.004874831902348165</v>
       </c>
       <c r="L59" s="3" t="n">
-        <v>0.005293895760981382</v>
+        <v>0.01082191959001588</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3229,7 +3229,7 @@
         </is>
       </c>
       <c r="C60" s="14" t="inlineStr"/>
-      <c r="D60" s="18" t="inlineStr">
+      <c r="D60" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3240,25 +3240,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3554251402412061</v>
+        <v>0.3632537505760061</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2073939590513423</v>
+        <v>0.214367460394107</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2090588317590476</v>
+        <v>0.2090587158539257</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1343078490366874</v>
+        <v>0.140859338961268</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.01799050820465387</v>
-      </c>
-      <c r="K60" s="5" t="n">
-        <v>-0.001376998921783779</v>
+        <v>0.02387017708245054</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>0.004390807882669323</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.004665690835903735</v>
+        <v>0.01046839876627104</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3271,7 +3271,7 @@
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
-      <c r="D61" s="18" t="inlineStr">
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3282,25 +3282,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3409832415168899</v>
+        <v>0.3428422662627091</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.2782227019980155</v>
+        <v>0.2799948116638939</v>
       </c>
       <c r="H61" s="3" t="n">
         <v>0.2053889947304175</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1332294197969721</v>
+        <v>0.1348005128508984</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.1122590593677719</v>
+        <v>0.1138010794140325</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.06042340488091735</v>
+        <v>0.06189356071743624</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.001799058953778188</v>
+        <v>-0.0004151674508718894</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3317,7 +3317,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D62" s="18" t="inlineStr">
+      <c r="D62" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3328,25 +3328,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3805867905496703</v>
+        <v>0.3867934494842129</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2058119914760816</v>
+        <v>0.2112326711777044</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1999814839375798</v>
+        <v>0.1999813685233944</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1492907654851512</v>
+        <v>0.1544574673059416</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.02033121451302589</v>
+        <v>0.02491817135819696</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.004858831254103801</v>
+        <v>0.009376231122783851</v>
       </c>
       <c r="L62" s="3" t="n">
-        <v>0.006709643467964765</v>
+        <v>0.01123536376792522</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3363,7 +3363,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D63" s="19" t="inlineStr">
+      <c r="D63" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -3374,25 +3374,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3166363736436004</v>
+        <v>0.3156844965660675</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1677776943654454</v>
+        <v>0.1669333611804016</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1988463895307493</v>
+        <v>0.1988463123109321</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1474588248740929</v>
+        <v>0.1466292566085681</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.08744780234264971</v>
+        <v>0.08666161972094444</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.02591549295774653</v>
+        <v>-0.02661971830985921</v>
       </c>
       <c r="L63" s="3" t="n">
-        <v>0.01185076810534014</v>
+        <v>0.01111923920994884</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3405,7 +3405,7 @@
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
-      <c r="D64" s="18" t="inlineStr">
+      <c r="D64" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3416,25 +3416,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.2820750768608502</v>
+        <v>0.2868706191587262</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.192817502601238</v>
+        <v>0.1972790742480612</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.1955379731175935</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1021304031107457</v>
+        <v>0.1062527719952544</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.04386963929709498</v>
-      </c>
-      <c r="K64" s="5" t="n">
-        <v>-0.002275519956310035</v>
+        <v>0.04777409171794811</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0.001456332772038493</v>
       </c>
       <c r="L64" s="3" t="n">
-        <v>0.002881976212259829</v>
+        <v>0.006633119853614033</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3458,25 +3458,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.3977099287660812</v>
+        <v>0.4062411094242195</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.2055448259817085</v>
+        <v>0.2129029847678061</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1934138074424667</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1065095393339808</v>
+        <v>0.1132632267235152</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.006334733328603237</v>
+        <v>0.01247699415558423</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.01016497250458248</v>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v>-0.002468323185782606</v>
+        <v>0.01633061156473925</v>
+      </c>
+      <c r="L65" s="3" t="n">
+        <v>0.003620207339147585</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3500,25 +3500,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.5250726744186047</v>
+        <v>0.5279796511627906</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.2491071428571427</v>
+        <v>0.2514880952380951</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.1882440476190474</v>
       </c>
       <c r="I66" s="5" t="n">
-        <v>-0.1212311557788944</v>
+        <v>-0.1195561139028476</v>
       </c>
       <c r="J66" s="5" t="n">
-        <v>-0.004034171808258269</v>
+        <v>-0.002135738016136757</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.05122103944896694</v>
+        <v>0.05322479649342515</v>
       </c>
       <c r="L66" s="3" t="n">
-        <v>0.01683827983040587</v>
+        <v>0.01877649909145962</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3542,25 +3542,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.5212591986917416</v>
+        <v>0.5246413439381552</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.2473639300298653</v>
+        <v>0.2501371365880418</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.1874200036569758</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>-0.1218973247806405</v>
+        <v>-0.1199450796987964</v>
       </c>
       <c r="J67" s="5" t="n">
-        <v>-0.004765725678994248</v>
+        <v>-0.002553067328032621</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.05048249666358684</v>
+        <v>0.05281798583307684</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.01621232434579678</v>
+        <v>0.01847162222553278</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3573,7 +3573,7 @@
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
-      <c r="D68" s="18" t="inlineStr">
+      <c r="D68" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3584,25 +3584,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3810864795644295</v>
+        <v>0.3882828281830024</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1769580446494039</v>
+        <v>0.1830907528643175</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1752617636537892</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.157249251447483</v>
+        <v>0.1632792641767546</v>
       </c>
       <c r="J68" s="5" t="n">
-        <v>-0.00627430232577264</v>
+        <v>-0.001096352459842631</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.001443321860775004</v>
+        <v>0.006661485511269216</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.01030465949820791</v>
+        <v>0.01556899641577059</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
-      <c r="D69" s="18" t="inlineStr">
+      <c r="D69" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3626,25 +3626,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3582087153267202</v>
+        <v>0.3639170736147284</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1727486014418051</v>
+        <v>0.1776775710269309</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1648623682015131</v>
+        <v>0.1648624412082786</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1550096107687677</v>
+        <v>0.1598639520860925</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.02692694588014244</v>
+        <v>0.03124297395192799</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.0067700987306063</v>
+        <v>0.01100141043723557</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0.01047565118912797</v>
+        <v>0.01472253680634217</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3657,7 +3657,7 @@
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" s="18" t="inlineStr">
+      <c r="D70" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3668,25 +3668,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.3554293195877352</v>
+        <v>0.3644866882278774</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1568230121687832</v>
+        <v>0.1645535091353658</v>
       </c>
       <c r="H70" s="3" t="n">
         <v>0.1625881285506414</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1433732729334227</v>
+        <v>0.151014005431523</v>
       </c>
       <c r="J70" s="5" t="n">
-        <v>-0.008659546512509775</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>-0.004958863969345195</v>
+        <v>-0.002034890633501929</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0.001690521807731216</v>
       </c>
       <c r="L70" s="3" t="n">
-        <v>0.007876712328767299</v>
+        <v>0.01461187214611881</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3703,7 +3703,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
+      <c r="D71" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3714,25 +3714,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.2710719492855216</v>
+        <v>0.2716768394445621</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1356541676369951</v>
+        <v>0.1361945264796456</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1578989399927713</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1113000730732334</v>
+        <v>0.1118288439248147</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.03900729555650706</v>
+        <v>0.0395016685758045</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.01921132457027297</v>
+        <v>-0.01874465271836356</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0.008477287268074063</v>
+        <v>0.008957133717210519</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3749,7 +3749,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D72" s="19" t="inlineStr">
+      <c r="D72" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -3760,25 +3760,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.1412619514421911</v>
+        <v>0.1440470804488283</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1394997498043227</v>
+        <v>0.1422805785525787</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1445209337062467</v>
+        <v>0.1445207987986072</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1115627101770413</v>
+        <v>0.11427549287424</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.1426580979045964</v>
+        <v>0.1454467692844736</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.004387149028077797</v>
+        <v>-0.001957343412526957</v>
       </c>
       <c r="L72" s="3" t="n">
-        <v>0.01878582775053528</v>
+        <v>0.02127218730575331</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3806,25 +3806,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.1015875986289971</v>
+        <v>0.09014043034262476</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1801112566673433</v>
+        <v>0.1678481083089864</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1419592395524549</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1303986710963454</v>
+        <v>0.1186521120075936</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.1714004672322635</v>
+        <v>0.1592278372064428</v>
       </c>
       <c r="K73" s="3" t="n">
-        <v>0.03340926347760065</v>
-      </c>
-      <c r="L73" s="3" t="n">
-        <v>0.007082452431289576</v>
+        <v>0.02267057164551467</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>-0.003382663847780076</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3848,25 +3848,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.2799470891518272</v>
+        <v>0.2817216038802786</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1219816880025888</v>
+        <v>0.1235371154813356</v>
       </c>
       <c r="H74" s="3" t="n">
         <v>0.1416837694000466</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>-0.02178829358849887</v>
+        <v>-0.02043217754449034</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-0.01328464972191301</v>
+        <v>-0.01191674489250716</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01725703905540421</v>
+        <v>-0.01589464123524065</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.002161160852114818</v>
+        <v>0.003550478542760249</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3890,25 +3890,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1459765046504415</v>
+        <v>0.1550075606960968</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.076311766270869</v>
+        <v>0.08479369254741864</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1299304498143374</v>
+        <v>0.1299303192409582</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>-0.02821848275647121</v>
+        <v>-0.02056019891666849</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>-0.1130796092066086</v>
+        <v>-0.1060900874103196</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.04745308310991947</v>
+        <v>-0.03994638069705081</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.009661835748792313</v>
+        <v>0.01761864165956251</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
-      <c r="D76" s="18" t="inlineStr">
+      <c r="D76" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3932,25 +3932,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2913795589096753</v>
+        <v>0.3010037306798734</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.104710345845773</v>
+        <v>0.1129433413670211</v>
       </c>
       <c r="H76" s="3" t="n">
         <v>0.1172350092451186</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.08439051927742858</v>
+        <v>0.09247207868534724</v>
       </c>
       <c r="J76" s="5" t="n">
-        <v>-0.03292598784009748</v>
+        <v>-0.0257187447462236</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.01121041078708063</v>
+        <v>-0.003841329570398289</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.005580802040978883</v>
+        <v>0.01307502192457943</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3963,7 +3963,7 @@
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
-      <c r="D77" s="18" t="inlineStr">
+      <c r="D77" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -3974,25 +3974,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2903359067287579</v>
+        <v>0.2985417707573699</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1037791659060732</v>
+        <v>0.1107987917000288</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1149384497684744</v>
+        <v>0.1149385263203155</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.08481407453509004</v>
+        <v>0.09171294075770597</v>
       </c>
       <c r="J77" s="5" t="n">
-        <v>-0.03210587169787171</v>
+        <v>-0.02595049118359805</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.01000887884413593</v>
+        <v>-0.003712971184114844</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.006895985551268469</v>
+        <v>0.01329940070601765</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" s="19" t="inlineStr">
+      <c r="D78" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4016,25 +4016,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2157261905295593</v>
+        <v>0.2185364289918372</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1114929144091994</v>
+        <v>0.1140623425143577</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1057314633258233</v>
+        <v>0.1057315946878823</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1512375242136201</v>
+        <v>0.1538986924889809</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.1233983731618407</v>
+        <v>0.125995189238777</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.005210533727643796</v>
+        <v>0.007534150119701488</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0.01348857021155747</v>
+        <v>0.01583132187988068</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="19" t="inlineStr">
+      <c r="D79" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1964281794933134</v>
+        <v>0.1997060649165827</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.108528806401849</v>
+        <v>0.1115657911371921</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1009361433443021</v>
+        <v>0.1009360636263172</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.1498305405658145</v>
+        <v>0.152980847821963</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.1229081050034344</v>
+        <v>0.1259845655650877</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.006896551724137945</v>
+        <v>0.009655172413793212</v>
       </c>
       <c r="L79" s="3" t="n">
-        <v>0.01283385362469658</v>
+        <v>0.01560874089490127</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4100,25 +4100,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.07713759982482316</v>
+        <v>0.08030548778692337</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.08410121328387699</v>
+        <v>0.08728937118672331</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>0.08818205539952029</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.007863983404447605</v>
+        <v>0.01082794053715097</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.04339167695028112</v>
+        <v>0.0464601150074222</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.003750146490097195</v>
+        <v>-0.0008203445447086954</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.006079738103589305</v>
+        <v>-0.003156787092248314</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4135,7 +4135,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D81" s="20" t="inlineStr">
+      <c r="D81" s="19" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -4146,25 +4146,25 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.2331720999242666</v>
+        <v>0.2410424643626312</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.02480142167430799</v>
+        <v>0.03134178887766037</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.08711239231219814</v>
+        <v>0.08711249093964857</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.02327038718120988</v>
+        <v>0.02980098305656065</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.03395122569161257</v>
+        <v>0.04054989329581771</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.05731787355064533</v>
-      </c>
-      <c r="L81" s="5" t="n">
-        <v>-0.002315350775642377</v>
+        <v>-0.05130168453292494</v>
+      </c>
+      <c r="L81" s="3" t="n">
+        <v>0.004051863857374549</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4181,7 +4181,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D82" s="18" t="inlineStr">
+      <c r="D82" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -4192,25 +4192,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1924746362705823</v>
+        <v>0.1998373930996897</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.04599446759114967</v>
+        <v>0.05245262746766155</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.07242424625952126</v>
+        <v>0.07242413138725778</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.08292525976067</v>
+        <v>0.08961155377080265</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.01860319960316859</v>
+        <v>-0.0125437716889033</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.02464489101263345</v>
+        <v>-0.01862276624991821</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.0056693551108562</v>
+        <v>0.01187864880369882</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4234,25 +4234,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.146820224798323</v>
+        <v>0.1494914801842251</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.05265204855634087</v>
+        <v>0.05510406823618341</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.07055179221919028</v>
       </c>
       <c r="I83" s="5" t="n">
-        <v>-0.07236271586553789</v>
+        <v>-0.07020190225236655</v>
       </c>
       <c r="J83" s="5" t="n">
-        <v>-0.0167471987494392</v>
+        <v>-0.01445683583015067</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.01672010994044881</v>
+        <v>-0.01442968392120925</v>
       </c>
       <c r="L83" s="3" t="n">
-        <v>0.006093273962971546</v>
+        <v>0.008436840871806961</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4269,7 +4269,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D84" s="21" t="inlineStr">
+      <c r="D84" s="20" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -4280,25 +4280,25 @@
         </is>
       </c>
       <c r="F84" s="5" t="n">
-        <v>-0.1216730038022813</v>
+        <v>-0.1069502696225285</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05702217529039078</v>
+        <v>0.05484784147204524</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.06335797254487852</v>
+        <v>0.06652512384996467</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.03054221002059032</v>
+        <v>0.01810109289617468</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.01384199864956104</v>
+        <v>0.008457374830852515</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.005958291956305817</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>0.001333777925975443</v>
+        <v>-0.01094890510948909</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>-0.007326007326007411</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4315,7 +4315,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D85" s="21" t="inlineStr">
+      <c r="D85" s="20" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -4326,25 +4326,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.00368354311509278</v>
+        <v>0.004042001523348215</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.05295524084668135</v>
+        <v>0.0533312962898409</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0.05633973983511709</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.01892285298398844</v>
+        <v>0.01928675400291135</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.005747126436781658</v>
+        <v>0.006106321839080442</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.003203987184051238</v>
+        <v>-0.002847988608045471</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.006034788782392719</v>
+        <v>-0.005679801206957769</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4361,7 +4361,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D86" s="20" t="inlineStr">
+      <c r="D86" s="19" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -4372,25 +4372,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.1508328098294096</v>
+        <v>0.1500386434428183</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.02658834751169303</v>
+        <v>0.02588001178342614</v>
       </c>
       <c r="H86" s="3" t="n">
         <v>0.05221960701231732</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.02499793941101514</v>
+        <v>0.02429070104848674</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.001948560455257153</v>
+        <v>0.001257225934486295</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.02435923007878726</v>
+        <v>-0.02503241248628696</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.01359892244728789</v>
+        <v>0.01289954929285608</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4418,25 +4418,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.1247940279135042</v>
+        <v>0.1303604469410917</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.120783857491783</v>
+        <v>0.1263304308512878</v>
       </c>
       <c r="H87" s="3" t="n">
         <v>0.04943048156188334</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.1432426708516079</v>
+        <v>0.1489003891522491</v>
       </c>
       <c r="J87" s="3" t="n">
-        <v>0.09751714709029491</v>
+        <v>0.1029485773602437</v>
       </c>
       <c r="K87" s="3" t="n">
-        <v>0.06799247514109119</v>
+        <v>0.07327779270805346</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>0.01317243137588164</v>
+        <v>0.01818645364153992</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="C88" s="14" t="inlineStr"/>
-      <c r="D88" s="19" t="inlineStr">
+      <c r="D88" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4460,25 +4460,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.08777456032566833</v>
+        <v>0.08722552584727028</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.04296942544419302</v>
+        <v>0.0424430055449152</v>
       </c>
       <c r="H88" s="3" t="n">
         <v>0.04081875942089486</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.01987998576261063</v>
+        <v>0.01936531992436374</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.007670770309591068</v>
+        <v>0.007162069063010978</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.002066321349256661</v>
+        <v>0.001560546549837394</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.001769687776513651</v>
+        <v>0.001264062697509782</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4495,7 +4495,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="21" t="inlineStr">
+      <c r="D89" s="20" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -4506,25 +4506,25 @@
         </is>
       </c>
       <c r="F89" s="5" t="n">
-        <v>-0.002176729471000005</v>
+        <v>-0.005216556647021364</v>
       </c>
       <c r="G89" s="3" t="n">
-        <v>0.0333653571287249</v>
+        <v>0.03021725246115814</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.03887454029696635</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="J89" s="17" t="n">
-        <v>0</v>
+        <v>0.00692307692307681</v>
+      </c>
+      <c r="J89" s="5" t="n">
+        <v>-0.003046458492003135</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.005303030303030143</v>
+        <v>-0.008333333333333304</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.003793626707131903</v>
+        <v>-0.006828528072837625</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4537,7 +4537,7 @@
         </is>
       </c>
       <c r="C90" s="14" t="inlineStr"/>
-      <c r="D90" s="22" t="inlineStr">
+      <c r="D90" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4548,25 +4548,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04774427032475792</v>
+        <v>0.04761595636265392</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.02377408116820789</v>
+        <v>0.0236487050509413</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.02297187664176414</v>
+        <v>0.0229717788663848</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.006074386492412209</v>
+        <v>0.005951274110315596</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.00517967661294727</v>
+        <v>0.005056579397369365</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.0007841902057730277</v>
+        <v>0.0006617251800502544</v>
       </c>
       <c r="L90" s="3" t="n">
-        <v>0.0009799118079372171</v>
+        <v>0.0008574228319451205</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4594,25 +4594,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.04001502197630691</v>
+        <v>0.03884995660441404</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.0109346073439256</v>
+        <v>0.009802118986184105</v>
       </c>
       <c r="H91" s="3" t="n">
         <v>0.009802118986184105</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.003926932907339697</v>
+        <v>-0.005042772788324767</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.007474358502731704</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>0.001121495327102817</v>
+        <v>-0.008586224419270927</v>
+      </c>
+      <c r="K91" s="22" t="n">
+        <v>0</v>
       </c>
       <c r="L91" s="3" t="n">
-        <v>0.002433090024331008</v>
+        <v>0.001310125397716577</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" s="22" t="inlineStr">
+      <c r="D92" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4636,25 +4636,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.03012034097800287</v>
+        <v>0.02867101933122229</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.001963098308293665</v>
+        <v>0.0005534797455508667</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.00809950784821778</v>
+        <v>0.008099424455868309</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.02286637089700239</v>
+        <v>-0.02424105595279302</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.007995838043526104</v>
+        <v>-0.009391444994799047</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.00608710696925352</v>
+        <v>-0.007485317943109138</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0.002495118246908179</v>
+        <v>0.001084834020394831</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4667,7 +4667,7 @@
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
-      <c r="D93" s="18" t="inlineStr">
+      <c r="D93" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
@@ -4678,25 +4678,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.1344584088903931</v>
+        <v>0.1409051936538903</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.01502768154574441</v>
+        <v>-0.009430335701041015</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.005802548753892411</v>
+        <v>0.005802657491454255</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.02689994717503286</v>
+        <v>0.03273544536427386</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.02780008779326903</v>
+        <v>-0.02227542996962273</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.02071005917159763</v>
+        <v>-0.01514511129895746</v>
       </c>
       <c r="L93" s="3" t="n">
-        <v>0.01105454545454543</v>
+        <v>0.01679999999999993</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4709,7 +4709,7 @@
         </is>
       </c>
       <c r="C94" s="14" t="inlineStr"/>
-      <c r="D94" s="22" t="inlineStr">
+      <c r="D94" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4720,25 +4720,25 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.03772960375647705</v>
+        <v>-0.04006898781653645</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.006130486181245676</v>
+        <v>-0.008546694040490355</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>-0.001139194187037562</v>
+        <v>-0.001139286249561944</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.05175013850611898</v>
+        <v>-0.05405518633991735</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.02661789206900678</v>
+        <v>-0.02898420325882323</v>
       </c>
       <c r="K94" s="5" t="n">
-        <v>-0.004996984529937354</v>
+        <v>-0.007415856574352286</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>0.003904820012202492</v>
+        <v>0.001464307504575935</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4766,25 +4766,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.04033437826541264</v>
+        <v>0.04326018808777432</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05397187381223867</v>
+        <v>-0.05131128848346633</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>-0.04389965792474337</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.01171332142148096</v>
+        <v>-0.008933889219773561</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.03665139525197825</v>
+        <v>0.03956684714702208</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.01053468495328957</v>
+        <v>-0.007751937984496138</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.003802281368821214</v>
+        <v>-0.001000600360216097</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4812,25 +4812,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.05459268084578683</v>
+        <v>-0.05513821305533928</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1158543057221274</v>
+        <v>-0.1163644878884735</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>-0.123677098939435</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.1275211450878335</v>
+        <v>0.1268705270006507</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1722660653889516</v>
+        <v>0.1715896279594138</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.008926838734717668</v>
+        <v>0.00834465359984482</v>
       </c>
       <c r="L96" s="3" t="n">
-        <v>0.01049562682215743</v>
+        <v>0.009912536443148712</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -76,12 +76,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00ECFCCB"/>
+        <fgColor rgb="0070AD47"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="0070AD47"/>
+        <fgColor rgb="00ECFCCB"/>
       </patternFill>
     </fill>
     <fill>
@@ -111,17 +111,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E0F2FE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFEDD5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E0F2FE"/>
       </patternFill>
     </fill>
     <fill>
@@ -136,12 +136,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FAE8FF"/>
+        <fgColor rgb="00F3F4F6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F3F4F6"/>
+        <fgColor rgb="00FAE8FF"/>
       </patternFill>
     </fill>
     <fill>
@@ -182,10 +182,10 @@
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
@@ -196,17 +196,17 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.740482763044557</v>
+        <v>1.770571927606757</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.270576234443266</v>
+        <v>1.302617193355203</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.383619836185349</v>
+        <v>1.338421257721972</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.4659974650133043</v>
+        <v>0.5948104212509173</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.1946062159474062</v>
+        <v>-0.07091375235506958</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.04742518082203639</v>
+        <v>-0.01531121231836907</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.002689765215409201</v>
+        <v>0.03219059743566444</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -703,40 +703,44 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>EWY</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>PSI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>South Korea Equity</t>
+          <t>Semiconductors</t>
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>2.383094077009304</v>
+        <v>1.533497710044304</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.532100566991992</v>
-      </c>
-      <c r="H3" s="7" t="n">
-        <v>1.371951096040239</v>
+        <v>1.147294632170278</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>1.296873242205359</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4359790042945761</v>
+        <v>0.5162155413214795</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.1147717801637496</v>
-      </c>
-      <c r="K3" s="3" t="n">
-        <v>0.06751803239919596</v>
+        <v>-0.06748853800295351</v>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>-0.06512270998963021</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.009504640500950456</v>
+        <v>0.04263685427910557</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -745,44 +749,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>PSI</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>EWY</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Semiconductors</t>
+          <t>South Korea Equity</t>
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>1.476694965000443</v>
+        <v>2.37694680438722</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.109364798676841</v>
+        <v>1.590363463506903</v>
       </c>
       <c r="H4" s="8" t="n">
-        <v>1.322415522367409</v>
+        <v>1.29651281131565</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.3758565541563594</v>
-      </c>
-      <c r="J4" s="5" t="n">
-        <v>-0.1968816674945051</v>
-      </c>
-      <c r="K4" s="5" t="n">
-        <v>-0.09173669467787127</v>
+        <v>0.4607433125542493</v>
+      </c>
+      <c r="J4" s="3" t="n">
+        <v>0.05668131742679372</v>
+      </c>
+      <c r="K4" s="3" t="n">
+        <v>0.1279551547648063</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.003792276139617634</v>
+        <v>0.0252547629596811</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -810,25 +810,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.874251497005988</v>
+        <v>1.90187891440501</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.232558139534884</v>
+        <v>1.288442541982219</v>
       </c>
       <c r="H5" s="10" t="n">
-        <v>1.278073089700996</v>
+        <v>1.253210405004939</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.5584415584415585</v>
+        <v>0.6591071854857962</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.1626168224299065</v>
-      </c>
-      <c r="K5" s="5" t="n">
-        <v>-0.01997958290797708</v>
+        <v>-0.0187773542284343</v>
+      </c>
+      <c r="K5" s="3" t="n">
+        <v>0.0156364167762677</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.003734129947722264</v>
+        <v>0.03422619047619047</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.503065683150183</v>
+        <v>1.533534744574753</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.087650673245424</v>
+        <v>1.136597741756676</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.206125472503677</v>
+        <v>1.191116431606419</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.4884771708047568</v>
+        <v>0.6068641757156692</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.1663816121824047</v>
+        <v>-0.03752236574486423</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.05370265686828724</v>
+        <v>-0.02488169458424094</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.001515634971282598</v>
+        <v>0.03399044205495816</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.484475817840979</v>
+        <v>1.515024894112569</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.037241862850647</v>
+        <v>1.079175504954714</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.154143996591405</v>
+        <v>1.132718436157833</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.4535272401705219</v>
+        <v>0.5637892938862188</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.165630673332319</v>
+        <v>-0.03953532722905162</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.05426848619485869</v>
+        <v>-0.02510548523206746</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.001456256301109127</v>
+        <v>0.03378076062639823</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -944,25 +944,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.461126298431551</v>
+        <v>1.486964726675999</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9352702787860103</v>
+        <v>0.9682250354492876</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.9951564926246654</v>
+        <v>0.9777072884948463</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.3977488301504994</v>
+        <v>0.4944818162707589</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.1194046499768935</v>
+        <v>-0.00166757359265568</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.03001579778830965</v>
+        <v>-0.004794568488835971</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.003851184420869069</v>
+        <v>0.02920738327904449</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -979,7 +979,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D9" s="6" t="inlineStr">
+      <c r="D9" s="7" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -990,25 +990,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.256850403455365</v>
+        <v>1.248766281111661</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9613425223640566</v>
+        <v>0.9745913541681384</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.8112097931937217</v>
+        <v>0.7987389575530752</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5643465909090908</v>
+        <v>0.6103279631760645</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.04141843971631198</v>
+        <v>0.1414151712887439</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.08289085545722696</v>
+        <v>0.09776426750343203</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.006396783331810152</v>
+        <v>0.01652592390810859</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1036,25 +1036,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.497975751291523</v>
+        <v>1.297946931275868</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8363110225297958</v>
+        <v>0.8500633107589615</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7451494999866728</v>
+        <v>0.7632231863526957</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.1125162297443887</v>
+        <v>0.1336705544336463</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.01485355926400711</v>
+        <v>0.1239703237047451</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.05223708487084866</v>
-      </c>
-      <c r="L10" s="3" t="n">
-        <v>0.01501668520578403</v>
+        <v>0.04925078406318972</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>-0.01008219178082193</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1082,25 +1082,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.69</v>
+        <v>1.593004769475357</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>0.9828009828009827</v>
+        <v>1.023573200992555</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7162162162162162</v>
+        <v>0.7295285359801487</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.4010416666666667</v>
+        <v>0.5592734225621412</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2748815165876777</v>
+        <v>0.2842519685039371</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.1553328561202576</v>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v>-0.02653799758745468</v>
+        <v>0.1700143472022955</v>
+      </c>
+      <c r="L11" s="3" t="n">
+        <v>0.01053283767038393</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.917518415967276</v>
+        <v>0.8664313340721865</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7632925882981105</v>
+        <v>0.7533611714484496</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6413274056180427</v>
+        <v>0.660502028863464</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.3280174474343562</v>
+        <v>0.31693666110139</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.2332586166689563</v>
+        <v>0.2691392937377841</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.07430886870139219</v>
+        <v>0.05592233009708725</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.005986575557840101</v>
+        <v>-0.007543496775763492</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1159,7 +1159,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.373602370821983</v>
+        <v>1.355409763798361</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6853028466742928</v>
+        <v>0.6774698650070796</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6382863961507237</v>
+        <v>0.6380926381289791</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1096163361160849</v>
+        <v>0.119148960604234</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.121530590940824</v>
+        <v>0.1851070251240816</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.02869855394883203</v>
+        <v>0.02403846153846168</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.0002162162162161474</v>
+        <v>-0.009623702422145386</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>PICK</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1212,29 +1212,29 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.9209763026933415</v>
+        <v>0.8248710270235242</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6158966193795532</v>
+        <v>0.5786446689906584</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.5680494196955619</v>
+        <v>0.5508026113365021</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1180029351439047</v>
+        <v>0.07331965511321381</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.01399049623175508</v>
+        <v>-0.05457402463137584</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.03051383399209495</v>
-      </c>
-      <c r="L14" s="3" t="n">
-        <v>0.004623921085080251</v>
+        <v>0.01795332136445249</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>-0.01007252215954879</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.7633285657752276</v>
+        <v>0.7376907387544698</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.7502710013325351</v>
+        <v>0.6705661380340722</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.568040184670217</v>
+        <v>0.5470265509350694</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.1351715394976627</v>
-      </c>
-      <c r="J15" s="5" t="n">
-        <v>-0.02086702963756071</v>
+        <v>0.1340904829507406</v>
+      </c>
+      <c r="J15" s="3" t="n">
+        <v>0.02095490716180382</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.1162156547031632</v>
+        <v>0.07985615180575389</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>-0.01550689449814457</v>
+        <v>-0.0149368325539192</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1289,7 +1289,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>PICK</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1304,29 +1304,29 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8672253513305133</v>
+        <v>0.8239276169783167</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.5984468730404104</v>
+        <v>0.6084571679745967</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.559591261434137</v>
+        <v>0.545877083625423</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.08157474019802802</v>
-      </c>
-      <c r="J16" s="5" t="n">
-        <v>-0.1020643774051078</v>
+        <v>0.1384686341945827</v>
+      </c>
+      <c r="J16" s="3" t="n">
+        <v>0.05720210864966413</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.02491397109428761</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0.002693239967680894</v>
+        <v>0.04048192771084325</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>-0.006290273089905041</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1350,25 +1350,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.087931034482759</v>
+        <v>0.9922741014444072</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.6215854311730047</v>
+        <v>0.6060113728675873</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.5016068559185858</v>
+        <v>0.512320606552938</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.1847313854853911</v>
+        <v>-0.2189886752699499</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.09599880561361607</v>
+        <v>-0.0367061880786097</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.07990012484394504</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0.02505501946842714</v>
+        <v>0.06195165622202325</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>-0.02047894302229558</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>QTEC</t>
+          <t>BOAT</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1385,36 +1385,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Shipping</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.6640680960872998</v>
+        <v>1.105782947414392</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4703756202673739</v>
+        <v>0.7207680894967674</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4964096195425953</v>
+        <v>0.4826594375549524</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3765801997066884</v>
-      </c>
-      <c r="J18" s="5" t="n">
-        <v>-0.05915590054224606</v>
-      </c>
-      <c r="K18" s="5" t="n">
-        <v>-0.01739764228672835</v>
+        <v>0.2985972090874711</v>
+      </c>
+      <c r="J18" s="3" t="n">
+        <v>0.2674999736543959</v>
+      </c>
+      <c r="K18" s="3" t="n">
+        <v>0.1605956471935852</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.01376446740338699</v>
+        <v>0.006156901688182614</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BOAT</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1431,36 +1431,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>1.097534424399743</v>
+        <v>0.6504992509123821</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.7129265818194397</v>
+        <v>0.4708323425316732</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.4717220244192444</v>
+        <v>0.464012917780535</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.276453987115105</v>
+        <v>0.4150680735609238</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.2687154778076624</v>
+        <v>0.02544993091629255</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.1638927415626446</v>
+        <v>0.004658035915063197</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.02379015860105738</v>
+        <v>0.008610958815751246</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1484,25 +1484,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.717021333068101</v>
+        <v>0.7108171050296106</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4305628474411445</v>
+        <v>0.4384415244121684</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4301013011119168</v>
+        <v>0.4186917551982716</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.329884803667118</v>
-      </c>
-      <c r="J20" s="5" t="n">
-        <v>-0.03612493669405781</v>
+        <v>0.3720445059387629</v>
+      </c>
+      <c r="J20" s="3" t="n">
+        <v>0.04345017910771953</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.0003227368081328841</v>
+        <v>0.0139211136890951</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.0129084967320261</v>
+        <v>0.01043179007366768</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1519,7 +1519,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
+      <c r="D21" s="7" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1530,25 +1530,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.7055440267244657</v>
+        <v>0.663910987571136</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4513669007629377</v>
+        <v>0.4288149497125653</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.4208949673876661</v>
+        <v>0.414560247003918</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1424272877803798</v>
+        <v>0.1524400165032129</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.04470618709629082</v>
+        <v>0.06719009838123569</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.0214455917394758</v>
+        <v>0.01007712661149585</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.0006106022758812779</v>
+        <v>-0.003443679182403958</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1572,25 +1572,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.944469248835988</v>
+        <v>1.753180531358071</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.6835002598799513</v>
+        <v>0.6614063039094067</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.391345863951692</v>
+        <v>0.3982481437733469</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.008694324860174407</v>
+        <v>-0.02137271780777017</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.1466311106323381</v>
+        <v>0.249576615875847</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.2099797063387847</v>
-      </c>
-      <c r="L22" s="3" t="n">
-        <v>0.02705441280778187</v>
+        <v>0.1882056209464329</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>-0.02397395422257298</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1618,25 +1618,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6899844990408226</v>
+        <v>0.6780365821612708</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.4045362517594182</v>
+        <v>0.407052033276984</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3910980430900381</v>
+        <v>0.3812607569259066</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.3216247054080685</v>
-      </c>
-      <c r="J23" s="5" t="n">
-        <v>-0.01585135063983989</v>
+        <v>0.3597486281749049</v>
+      </c>
+      <c r="J23" s="3" t="n">
+        <v>0.0572471561769119</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.009660144902173595</v>
+        <v>0.01867227185146247</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.01491749639376572</v>
+        <v>0.008007765105556786</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1645,10 +1645,14 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>VGT</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
+          <t>QCLN</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -1656,29 +1660,29 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6836996126106114</v>
+        <v>0.6505295235814175</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.4018307214699295</v>
+        <v>0.3171718366740381</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3883783419455655</v>
+        <v>0.3786844300618613</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.3217292175579545</v>
+        <v>0.09387366888928628</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-0.01462391197381729</v>
-      </c>
-      <c r="K24" s="3" t="n">
-        <v>0.009689274974941542</v>
+        <v>-0.1977520768854862</v>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>-0.0446168768186227</v>
       </c>
       <c r="L24" s="3" t="n">
-        <v>0.01468983463443307</v>
+        <v>0.002442499491145833</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1687,7 +1691,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IYW</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1695,36 +1699,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D25" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.6875814244111482</v>
+        <v>0.5530938276857971</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.3907036290552424</v>
+        <v>0.5123536914418514</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.383709910797144</v>
+        <v>0.3784190999316743</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.3181757195953701</v>
-      </c>
-      <c r="J25" s="5" t="n">
-        <v>-0.01484170605100388</v>
+        <v>0.2646481303395474</v>
+      </c>
+      <c r="J25" s="3" t="n">
+        <v>0.2571228373950676</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.005054324033907598</v>
-      </c>
-      <c r="L25" s="3" t="n">
-        <v>0.01674853047749414</v>
+        <v>0.09716536249157892</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>-0.009775033908610453</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1733,14 +1737,10 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>DRIV</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VGT</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -1748,29 +1748,29 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Autonomous/EV</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.5936762465877772</v>
+        <v>0.6704869207071735</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3629025544590627</v>
+        <v>0.4024125877631208</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3794992222721332</v>
+        <v>0.377760354004183</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.124602081749243</v>
-      </c>
-      <c r="J26" s="5" t="n">
-        <v>-0.1753990941793082</v>
-      </c>
-      <c r="K26" s="5" t="n">
-        <v>-0.01203093669435673</v>
+        <v>0.3574945757036034</v>
+      </c>
+      <c r="J26" s="3" t="n">
+        <v>0.05729454357380392</v>
+      </c>
+      <c r="K26" s="3" t="n">
+        <v>0.01789297658862887</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.0114369501466276</v>
+        <v>0.007114493712772951</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1779,7 +1779,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>DRIV</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1787,36 +1787,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D27" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Autonomous/EV</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>1.144362434242556</v>
+        <v>0.5411492372871098</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4571098247545431</v>
+        <v>0.3632000760060674</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3775952997679377</v>
+        <v>0.3722461238272272</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.05018513838261507</v>
+        <v>0.1515040441534812</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>-0.07919948746527516</v>
-      </c>
-      <c r="K27" s="3" t="n">
-        <v>0.05771979985704068</v>
-      </c>
-      <c r="L27" s="5" t="n">
-        <v>-0.009040683073832212</v>
+        <v>-0.1007415156058398</v>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>-0.006592146746918992</v>
+      </c>
+      <c r="L27" s="3" t="n">
+        <v>0.004928964917367162</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1825,7 +1825,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>QCLN</t>
+          <t>IYW</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1840,29 +1840,29 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6911455359706367</v>
+        <v>0.6741831887155976</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.318891587065373</v>
+        <v>0.3924097561059978</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3771450929463389</v>
+        <v>0.3720418417781526</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.04391570531609523</v>
-      </c>
-      <c r="J28" s="5" t="n">
-        <v>-0.2750479563228566</v>
-      </c>
-      <c r="K28" s="5" t="n">
-        <v>-0.04230019493177373</v>
+        <v>0.3511661237426</v>
+      </c>
+      <c r="J28" s="3" t="n">
+        <v>0.05444483487505614</v>
+      </c>
+      <c r="K28" s="3" t="n">
+        <v>0.01484496588052187</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.01298969072164957</v>
+        <v>0.007008790686623856</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1871,7 +1871,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1879,36 +1879,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.5967914577585347</v>
+        <v>1.071495631171302</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.5271740117559209</v>
+        <v>0.4514061081742373</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.369963871917991</v>
+        <v>0.3577709735251533</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.2687274280577141</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>0.2473900320029196</v>
+        <v>0.07239739870515072</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>-0.004715827805634842</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.1147549530761209</v>
-      </c>
-      <c r="L29" s="3" t="n">
-        <v>4.677268475217211e-05</v>
+        <v>0.06896239238785684</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>-0.003547896604156109</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1917,86 +1917,86 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>VDE</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>U.S. Industrials</t>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5570905579585168</v>
+        <v>0.5747997055369787</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.1944213624193507</v>
+        <v>0.4741490071790762</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3544321023495536</v>
-      </c>
-      <c r="I30" s="5" t="n">
-        <v>-0.05090263418278773</v>
-      </c>
-      <c r="J30" s="5" t="n">
-        <v>-0.1833080424886192</v>
-      </c>
-      <c r="K30" s="5" t="n">
-        <v>-0.1181386203506473</v>
-      </c>
-      <c r="L30" s="3" t="n">
-        <v>0.01289169097581633</v>
+        <v>0.3473148914530824</v>
+      </c>
+      <c r="I30" s="3" t="n">
+        <v>0.1390549800743051</v>
+      </c>
+      <c r="J30" s="3" t="n">
+        <v>0.1134276030523451</v>
+      </c>
+      <c r="K30" s="3" t="n">
+        <v>0.09413843529125021</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>-0.01421826965305228</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
-      <c r="A31" t="n">
+      <c r="A31" s="13" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>ROBO</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Robotics</t>
+      <c r="B31" s="14" t="inlineStr">
+        <is>
+          <t>XLE</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr"/>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>Energy</t>
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.4532796585988519</v>
+        <v>0.5571805031268127</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.28003788174616</v>
+        <v>0.4745071150904128</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3538522763309957</v>
+        <v>0.3464803550582258</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.08752556237218823</v>
-      </c>
-      <c r="J31" s="5" t="n">
-        <v>-0.09945811695642359</v>
-      </c>
-      <c r="K31" s="5" t="n">
-        <v>-0.05452174943700372</v>
-      </c>
-      <c r="L31" s="3" t="n">
-        <v>0.01153943697692106</v>
+        <v>0.1413903680571551</v>
+      </c>
+      <c r="J31" s="3" t="n">
+        <v>0.1123516319287314</v>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v>0.0950825309491059</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>-0.01439182915506043</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2005,86 +2005,86 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>VDE</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
+          <t>DBC</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Broad Commodities</t>
+        </is>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>0.4916408149972069</v>
+      </c>
+      <c r="G32" s="3" t="n">
+        <v>0.4688061407316384</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.3431478207070686</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.1472191930207196</v>
+      </c>
+      <c r="J32" s="3" t="n">
+        <v>0.07971262401642143</v>
+      </c>
+      <c r="K32" s="3" t="n">
+        <v>0.0935550935550935</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>-0.01251564455569465</v>
+      </c>
+    </row>
+    <row r="33" ht="21" customHeight="1">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>ROBO</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D32" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="F32" s="3" t="n">
-        <v>0.5749092872347774</v>
-      </c>
-      <c r="G32" s="3" t="n">
-        <v>0.5059828290929869</v>
-      </c>
-      <c r="H32" s="3" t="n">
-        <v>0.3357578266170063</v>
-      </c>
-      <c r="I32" s="3" t="n">
-        <v>0.1559184160557006</v>
-      </c>
-      <c r="J32" s="3" t="n">
-        <v>0.1056524337225171</v>
-      </c>
-      <c r="K32" s="3" t="n">
-        <v>0.1274370242000371</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>-0.00789717335657103</v>
-      </c>
-    </row>
-    <row r="33" ht="21" customHeight="1">
-      <c r="A33" s="14" t="n">
-        <v>32</v>
-      </c>
-      <c r="B33" s="15" t="inlineStr">
-        <is>
-          <t>XLE</t>
-        </is>
-      </c>
-      <c r="C33" s="14" t="inlineStr"/>
-      <c r="D33" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E33" s="14" t="inlineStr">
-        <is>
-          <t>Energy</t>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.5566682979375626</v>
+        <v>0.4249456033069008</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.5058424903595264</v>
+        <v>0.2778951863276378</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.335497262805702</v>
+        <v>0.3203327503512046</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1599021903381148</v>
-      </c>
-      <c r="J33" s="3" t="n">
-        <v>0.1078472327633153</v>
-      </c>
-      <c r="K33" s="3" t="n">
-        <v>0.1275519106613157</v>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v>-0.007373271889400734</v>
+        <v>0.1169769380383441</v>
+      </c>
+      <c r="J33" s="5" t="n">
+        <v>-0.03573998560805935</v>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>-0.0321415673528348</v>
+      </c>
+      <c r="L33" s="3" t="n">
+        <v>0.007897705904475583</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2093,40 +2093,44 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>DBC</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
+          <t>XAR</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
-          <t>Inflation &amp; Real Assets</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Broad Commodities</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5064134204028921</v>
+        <v>0.548681083789702</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.4767834467148726</v>
+        <v>0.1818901988012578</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3159822453829653</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>0.2051282051282053</v>
-      </c>
-      <c r="J34" s="3" t="n">
-        <v>0.06961178045515393</v>
-      </c>
-      <c r="K34" s="3" t="n">
-        <v>0.122191011235955</v>
-      </c>
-      <c r="L34" s="3" t="n">
-        <v>0.0009395552771689353</v>
+        <v>0.3185919873131313</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>-0.09146377408603978</v>
+      </c>
+      <c r="J34" s="5" t="n">
+        <v>-0.06946722479987866</v>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>-0.1036725460393765</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>-0.001378332611349564</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2135,44 +2139,40 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>XAR</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D35" s="13" t="inlineStr">
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" s="16" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>U.S. Industrials</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5948067278992044</v>
+        <v>0.5463634967954014</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1846218709339815</v>
+        <v>0.1855043462607686</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.3159458801758652</v>
+        <v>0.317783047403464</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.08851270660148058</v>
+        <v>-0.01236883733147942</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.09426791220367348</v>
+        <v>-0.1483941548800499</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.0997943845717526</v>
+        <v>-0.1003797259369325</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.01486751129051589</v>
+        <v>0.01244890375325158</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2181,40 +2181,44 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SPMO</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XOP</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.5528278710311592</v>
+        <v>0.6055287833310221</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.286004865974721</v>
+        <v>0.4633222338064473</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.310955506478674</v>
+        <v>0.292486539191916</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.2373915757980742</v>
-      </c>
-      <c r="J36" s="5" t="n">
-        <v>-0.03398414185178045</v>
-      </c>
-      <c r="K36" s="5" t="n">
-        <v>-0.01903240833166975</v>
-      </c>
-      <c r="L36" s="3" t="n">
-        <v>0.007311739784064519</v>
+        <v>0.1626199709281648</v>
+      </c>
+      <c r="J36" s="3" t="n">
+        <v>0.1449905734563819</v>
+      </c>
+      <c r="K36" s="3" t="n">
+        <v>0.1321759952110146</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>-0.01663806998388195</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2223,7 +2227,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CALF</t>
+          <t>ARKQ</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2231,36 +2235,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D37" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Small Cap Value</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.5611941259787481</v>
+        <v>0.7085639326088764</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.3545125783829983</v>
+        <v>0.2767153658559489</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3020647274654891</v>
+        <v>0.2842205508936391</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.2650620960857479</v>
-      </c>
-      <c r="J37" s="3" t="n">
-        <v>0.1426031996839818</v>
-      </c>
-      <c r="K37" s="3" t="n">
-        <v>0.04028052508541635</v>
-      </c>
-      <c r="L37" s="3" t="n">
-        <v>0.001038241910365167</v>
+        <v>0.03184498736310015</v>
+      </c>
+      <c r="J37" s="5" t="n">
+        <v>-0.05493827160493825</v>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>-0.005844155844155874</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>-0.002687077599544008</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2269,7 +2273,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SCHA</t>
+          <t>SPMO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -2280,29 +2284,29 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.4360826343886341</v>
+        <v>0.5584716016696392</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.275529651061293</v>
+        <v>0.2863573558254935</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.2934265885798377</v>
+        <v>0.2814584202150137</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.1489327980563964</v>
-      </c>
-      <c r="J38" s="5" t="n">
-        <v>-0.00150038609682146</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>-0.01383684058806567</v>
+        <v>0.2713444831342522</v>
+      </c>
+      <c r="J38" s="3" t="n">
+        <v>0.03894981943858422</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.003822937625754586</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.004994124559341895</v>
+        <v>0.01533138864391836</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2311,7 +2315,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>CALF</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2319,36 +2323,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D39" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D39" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Small Cap Value</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.6069912039968199</v>
+        <v>0.5359080255765449</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.5041175938689426</v>
+        <v>0.3253391710678433</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2918691069058941</v>
+        <v>0.2753384805045207</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.1845283984295416</v>
+        <v>0.2629264418501225</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.1301173701749363</v>
+        <v>0.1528133128090909</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.1642956595435561</v>
+        <v>0.03920581973151349</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.004296955891488818</v>
+        <v>-0.01348314606741574</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2357,40 +2361,40 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>SCHA</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
-      <c r="D40" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D40" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4445040374261513</v>
+        <v>0.424663539535614</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2013795215676357</v>
+        <v>0.2641669297133249</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2883691523119736</v>
+        <v>0.2678493268287148</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.03311155162899504</v>
-      </c>
-      <c r="J40" s="5" t="n">
-        <v>-0.04902090898258737</v>
+        <v>0.1810069019535643</v>
+      </c>
+      <c r="J40" s="3" t="n">
+        <v>0.03732426678324252</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.06751918158567771</v>
+        <v>-0.002904443799012557</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.007553426676492281</v>
+        <v>0.00350774627301953</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2399,40 +2403,44 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ITA</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" s="13" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D41" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.5247535358004729</v>
+        <v>0.447805734289956</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.1532926592557828</v>
+        <v>0.2508440467738888</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2875151432739573</v>
-      </c>
-      <c r="I41" s="5" t="n">
-        <v>-0.05730129950277807</v>
+        <v>0.2670850367967565</v>
+      </c>
+      <c r="I41" s="3" t="n">
+        <v>0.262336816610546</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.02345452782758695</v>
+        <v>-0.00624493713928409</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.1042492468685587</v>
+        <v>-0.01281760067495208</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.01168464878900477</v>
+        <v>0.01603099325362378</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2441,44 +2449,40 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>MTUM</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D42" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>ITA</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4431543141897338</v>
+        <v>0.4903538977621034</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2426242477357754</v>
+        <v>0.1420379321930683</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2864493497867067</v>
-      </c>
-      <c r="I42" s="3" t="n">
-        <v>0.2145062878304791</v>
+        <v>0.2656739046368983</v>
+      </c>
+      <c r="I42" s="5" t="n">
+        <v>-0.06740362797471722</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.08015222367267538</v>
+        <v>-0.01621992103901537</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.03406671398154715</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>0.008012388903851253</v>
+        <v>-0.09768390735629429</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>-0.001814319851314306</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2487,40 +2491,40 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>FNDX</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
-      <c r="D43" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Fundamental Equity</t>
+          <t>Developed ex-US Hedged</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4089855054709055</v>
+        <v>0.3423372590829841</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2986093528720688</v>
+        <v>0.2671748426212666</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2768272502773865</v>
+        <v>0.2655667527194627</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1571491812763781</v>
+        <v>0.1276012279827634</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.05295493867043288</v>
+        <v>0.06646013955001573</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.01705955334987586</v>
+        <v>0.001270648030495591</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.007063882063881977</v>
+        <v>0.001907183725365691</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2529,40 +2533,40 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="6" t="inlineStr">
+      <c r="D44" s="7" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Developed ex-US Hedged</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.3564567633958602</v>
+        <v>0.4592865290637298</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2778792511005641</v>
+        <v>0.2898266906041567</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.276796073095817</v>
+        <v>0.2645772284716119</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.1152352784292778</v>
+        <v>0.1346972161273836</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.04469692726517094</v>
+        <v>0.0690645744654057</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.0008483563096499669</v>
+        <v>0.01996672212978368</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.002975557917109573</v>
+        <v>0.001633986928104569</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2571,40 +2575,40 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>FNDX</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D45" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Developed Markets</t>
+          <t>Fundamental Equity</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.4912630768467108</v>
+        <v>0.3916162350672219</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2956715723306258</v>
+        <v>0.2812916872839297</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2764411527521891</v>
+        <v>0.2636214065828029</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1240644089244667</v>
+        <v>0.1649635933558284</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.02765258176012564</v>
+        <v>0.06554198069974171</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.01506565307532837</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>0.01170960187353631</v>
+        <v>0.01398384089496596</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>-0.004879536444037713</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2613,44 +2617,40 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ARKQ</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>PAVE</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.7599390999725573</v>
+        <v>0.4228965687609654</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2806879071823012</v>
+        <v>0.1903991000561915</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2764123429615966</v>
+        <v>0.2619874180283208</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.01588220696500953</v>
+        <v>0.0689515273765926</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-0.1198939372223018</v>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v>0.003349673202614367</v>
+        <v>-0.0272315039162303</v>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>-0.0567266495287061</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.02137391882900874</v>
+        <v>0.006399707441945512</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2659,14 +2659,10 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>IWO</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>SCHD</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
       <c r="D47" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -2674,29 +2670,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.4300904064736903</v>
+        <v>0.3120597038431827</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2402338409176885</v>
+        <v>0.3044224615860005</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2719056836332476</v>
+        <v>0.2617404407419122</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1494786142653046</v>
-      </c>
-      <c r="J47" s="5" t="n">
-        <v>-0.01397590041161056</v>
-      </c>
-      <c r="K47" s="5" t="n">
-        <v>-0.02490109378636252</v>
-      </c>
-      <c r="L47" s="3" t="n">
-        <v>0.005305110500919863</v>
+        <v>0.137633189213179</v>
+      </c>
+      <c r="J47" s="3" t="n">
+        <v>0.08722825019203939</v>
+      </c>
+      <c r="K47" s="3" t="n">
+        <v>0.03382789317507418</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>-0.006841505131128689</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2705,124 +2701,128 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
+          <t>IWO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D48" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Small Growth</t>
+        </is>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>0.4090462993417128</v>
+      </c>
+      <c r="G48" s="3" t="n">
+        <v>0.2228796540814408</v>
+      </c>
+      <c r="H48" s="3" t="n">
+        <v>0.2492435064781673</v>
+      </c>
+      <c r="I48" s="3" t="n">
+        <v>0.1759889566770871</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.02827845489776415</v>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>-0.02110385386036595</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>-0.002439671174754743</v>
+      </c>
+    </row>
+    <row r="49" ht="21" customHeight="1">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
           <t>QQQM</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="C49" t="inlineStr"/>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="E49" t="inlineStr">
         <is>
           <t>Nasdaq-100</t>
         </is>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>0.4601991371572396</v>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>0.2658141449962368</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>0.2651287865880634</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>0.1816267537227056</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>-0.02980267187770436</v>
-      </c>
-      <c r="K48" s="3" t="n">
-        <v>0.0005417301506684957</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>0.01195123621669758</v>
-      </c>
-    </row>
-    <row r="49" ht="21" customHeight="1">
-      <c r="A49" s="14" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" s="15" t="inlineStr">
+      <c r="F49" s="3" t="n">
+        <v>0.4496373468080597</v>
+      </c>
+      <c r="G49" s="3" t="n">
+        <v>0.2611857609385513</v>
+      </c>
+      <c r="H49" s="3" t="n">
+        <v>0.2489618429487046</v>
+      </c>
+      <c r="I49" s="3" t="n">
+        <v>0.2061853002306882</v>
+      </c>
+      <c r="J49" s="3" t="n">
+        <v>0.0245699286352461</v>
+      </c>
+      <c r="K49" s="3" t="n">
+        <v>0.009787262964725096</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.005515887787215235</v>
+      </c>
+    </row>
+    <row r="50" ht="21" customHeight="1">
+      <c r="A50" s="13" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="14" t="inlineStr">
         <is>
           <t>QQQ</t>
         </is>
       </c>
-      <c r="C49" s="14" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="C50" s="13" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
-      <c r="E49" s="14" t="inlineStr">
+      <c r="E50" s="13" t="inlineStr">
         <is>
           <t>Nasdaq-100</t>
         </is>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>0.4590110475036924</v>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>0.2649786483723819</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>0.2643264794090734</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>0.181397338539907</v>
-      </c>
-      <c r="J49" s="5" t="n">
-        <v>-0.02990957161579222</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>0.0005158232259863116</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>0.01188596243866669</v>
-      </c>
-    </row>
-    <row r="50" ht="21" customHeight="1">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>SCHD</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr"/>
-      <c r="D50" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>Dividend</t>
-        </is>
-      </c>
       <c r="F50" s="3" t="n">
-        <v>0.3272490402503263</v>
+        <v>0.4482633633158033</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.3176910469915384</v>
+        <v>0.2606187156565578</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2636011066361277</v>
+        <v>0.2483561255753448</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1407063175317573</v>
+        <v>0.2061259945266605</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.08497653464595567</v>
+        <v>0.02468313510951514</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.04280618311533879</v>
+        <v>0.009822990274959809</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.001999428734647202</v>
+        <v>0.005573592319589871</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2831,40 +2831,44 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>XLI</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr"/>
-      <c r="D51" s="13" t="inlineStr">
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D51" s="16" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.3500233872127012</v>
+        <v>0.4304355597134075</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1803048593588521</v>
+        <v>0.128984283089794</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2600241208840632</v>
-      </c>
-      <c r="I51" s="3" t="n">
-        <v>0.01988360253577648</v>
+        <v>0.2407439762699701</v>
+      </c>
+      <c r="I51" s="5" t="n">
+        <v>-0.0830737517828245</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.006644699510808816</v>
+        <v>-0.02816106444834943</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.06326804400321973</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0.01030211830072925</v>
+        <v>-0.09007474170147289</v>
+      </c>
+      <c r="L51" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2873,44 +2877,40 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D52" s="13" t="inlineStr">
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr"/>
+      <c r="D52" s="16" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4658218257537681</v>
+        <v>0.3341455326267242</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.1345318579441113</v>
+        <v>0.1716173788981883</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2571876546294987</v>
-      </c>
-      <c r="I52" s="5" t="n">
-        <v>-0.0766372726971023</v>
-      </c>
-      <c r="J52" s="5" t="n">
-        <v>-0.04513030651536987</v>
+        <v>0.2353365686539364</v>
+      </c>
+      <c r="I52" s="3" t="n">
+        <v>0.0365700458807876</v>
+      </c>
+      <c r="J52" s="3" t="n">
+        <v>0.008503418192328027</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.09756363438164284</v>
+        <v>-0.05158042866421308</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.01222718102341513</v>
+        <v>0.003838221814848719</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2919,40 +2919,44 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>ONEQ</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
-      <c r="D53" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D53" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4656577349564508</v>
+        <v>0.2110256786435136</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2449678388869871</v>
+        <v>0.2803829853546311</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2345099188963364</v>
+        <v>0.2293427066468481</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.173241921752868</v>
-      </c>
-      <c r="J53" s="5" t="n">
-        <v>-0.007320889694969135</v>
+        <v>0.1488843741631856</v>
+      </c>
+      <c r="J53" s="3" t="n">
+        <v>0.1366693666429213</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.008471313053523444</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>0.01393728222996526</v>
+        <v>0.04151834832696921</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>-0.009082512315270908</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2961,44 +2965,40 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D54" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.2348657727288193</v>
+        <v>0.4469459839971441</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2971403403944994</v>
+        <v>0.2342367069816733</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2322034502011048</v>
+        <v>0.221764915662316</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1495549745743585</v>
+        <v>0.1929309488855759</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.1501237902314649</v>
+        <v>0.03698442396619872</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.05269981201789076</v>
+        <v>0.01020801232665636</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.001017043178105803</v>
+        <v>0.001336387934326</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>ARGT</t>
+          <t>XMMO</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -3015,36 +3015,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D55" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.2116382888249806</v>
+        <v>0.3169838945063816</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.2582637131398686</v>
+        <v>0.1620415886689424</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2235574722918989</v>
+        <v>0.2045764963095777</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.1184674680457849</v>
-      </c>
-      <c r="J55" s="3" t="n">
-        <v>0.02252479597288404</v>
-      </c>
-      <c r="K55" s="3" t="n">
-        <v>0.02836502709019451</v>
-      </c>
-      <c r="L55" s="5" t="n">
-        <v>-0.01123595505617991</v>
+        <v>0.07114540094117339</v>
+      </c>
+      <c r="J55" s="5" t="n">
+        <v>-0.06436180695245242</v>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>-0.03531108881083789</v>
+      </c>
+      <c r="L55" s="3" t="n">
+        <v>0.006873527101335597</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3068,25 +3068,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3374867679272771</v>
+        <v>0.3159078763852463</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2080104565202092</v>
+        <v>0.1915237809218715</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2209756517461703</v>
+        <v>0.2035901041379315</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1173583174295871</v>
-      </c>
-      <c r="J56" s="5" t="n">
-        <v>-0.01891240362767499</v>
+        <v>0.1418446635216428</v>
+      </c>
+      <c r="J56" s="3" t="n">
+        <v>0.01992542602704361</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.01061871725895513</v>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>0.01003093111323095</v>
+        <v>-0.01002527619209914</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>-0.00234688036634223</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3095,14 +3095,10 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr"/>
       <c r="D57" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3110,29 +3106,29 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Cash Flow Factor</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.3249234179352378</v>
+        <v>0.3277935407927195</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.1705373047825107</v>
+        <v>0.2646985977155558</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2201908903742278</v>
+        <v>0.2029492542563476</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.04099849911676801</v>
-      </c>
-      <c r="J57" s="5" t="n">
-        <v>-0.1091160899263948</v>
-      </c>
-      <c r="K57" s="5" t="n">
-        <v>-0.04069329314242665</v>
-      </c>
-      <c r="L57" s="3" t="n">
-        <v>0.007784668162026609</v>
+        <v>0.1299380801786043</v>
+      </c>
+      <c r="J57" s="3" t="n">
+        <v>0.1207514461767996</v>
+      </c>
+      <c r="K57" s="3" t="n">
+        <v>0.05133162786437007</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>-0.01426000276893258</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3156,25 +3152,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.364567772959709</v>
+        <v>0.3478174207498086</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.215294298993564</v>
+        <v>0.2039322659501936</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2099592609858256</v>
+        <v>0.1980471814095774</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1407598714690101</v>
+        <v>0.1548348065112952</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.02403484676131606</v>
+        <v>0.05005491374804683</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.004409270774448748</v>
-      </c>
-      <c r="L58" s="3" t="n">
-        <v>0.01039223212635587</v>
+        <v>0.004912231030577585</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>-0.001195970283656034</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3198,109 +3194,109 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3651352659470111</v>
+        <v>0.3482926029508551</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2157130219912173</v>
+        <v>0.2039471327292275</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2098153754032503</v>
+        <v>0.1980201038652212</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1414716149605197</v>
+        <v>0.1550272294652035</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.02416739430210635</v>
+        <v>0.05010611933034248</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.004874831902348165</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>0.01082191959001588</v>
+        <v>0.00494735342494157</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>-0.00151840747365295</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
-      <c r="A60" s="14" t="n">
+      <c r="A60" t="n">
         <v>59</v>
       </c>
-      <c r="B60" s="15" t="inlineStr">
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>VWO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr"/>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>Emerging Markets</t>
+        </is>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>0.3729800757566066</v>
+      </c>
+      <c r="G60" s="3" t="n">
+        <v>0.2246871528078966</v>
+      </c>
+      <c r="H60" s="3" t="n">
+        <v>0.1975251415910222</v>
+      </c>
+      <c r="I60" s="3" t="n">
+        <v>0.1270952264061589</v>
+      </c>
+      <c r="J60" s="3" t="n">
+        <v>0.05795067695476508</v>
+      </c>
+      <c r="K60" s="3" t="n">
+        <v>0.02268178785857233</v>
+      </c>
+      <c r="L60" s="3" t="n">
+        <v>0.005410723069355639</v>
+      </c>
+    </row>
+    <row r="61" ht="21" customHeight="1">
+      <c r="A61" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" s="14" t="inlineStr">
         <is>
           <t>SPY</t>
         </is>
       </c>
-      <c r="C60" s="14" t="inlineStr"/>
-      <c r="D60" s="17" t="inlineStr">
+      <c r="C61" s="13" t="inlineStr"/>
+      <c r="D61" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E60" s="14" t="inlineStr">
+      <c r="E61" s="13" t="inlineStr">
         <is>
           <t>S&amp;P 500</t>
         </is>
       </c>
-      <c r="F60" s="3" t="n">
-        <v>0.3632537505760061</v>
-      </c>
-      <c r="G60" s="3" t="n">
-        <v>0.214367460394107</v>
-      </c>
-      <c r="H60" s="3" t="n">
-        <v>0.2090587158539257</v>
-      </c>
-      <c r="I60" s="3" t="n">
-        <v>0.140859338961268</v>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>0.02387017708245054</v>
-      </c>
-      <c r="K60" s="3" t="n">
-        <v>0.004390807882669323</v>
-      </c>
-      <c r="L60" s="3" t="n">
-        <v>0.01046839876627104</v>
-      </c>
-    </row>
-    <row r="61" ht="21" customHeight="1">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>COWZ</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr"/>
-      <c r="D61" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>Cash Flow Factor</t>
-        </is>
-      </c>
       <c r="F61" s="3" t="n">
-        <v>0.3428422662627091</v>
+        <v>0.347344543969605</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.2799948116638939</v>
+        <v>0.2030410556060367</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2053889947304175</v>
+        <v>0.1971221110577652</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1348005128508984</v>
+        <v>0.1548002641618316</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.1138010794140325</v>
+        <v>0.04989460111075061</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.06189356071743624</v>
+        <v>0.0049443114395753</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.0004151674508718894</v>
+        <v>-0.001047635060853258</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3309,90 +3305,82 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D62" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr"/>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3867934494842129</v>
+        <v>0.5042595613558092</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2112326711777044</v>
+        <v>0.240322821700792</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1999813685233944</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>0.1544574673059416</v>
+        <v>0.1936930204752654</v>
+      </c>
+      <c r="I62" s="5" t="n">
+        <v>-0.1442565477418025</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.02491817135819696</v>
+        <v>0.02179266190593454</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.009376231122783851</v>
-      </c>
-      <c r="L62" s="3" t="n">
-        <v>0.01123536376792522</v>
+        <v>0.03906347815199696</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>-0.0131985731272295</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
-      <c r="A63" t="n">
+      <c r="A63" s="13" t="n">
         <v>62</v>
       </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D63" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>Banks</t>
+      <c r="B63" s="14" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C63" s="13" t="inlineStr"/>
+      <c r="D63" s="11" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E63" s="13" t="inlineStr">
+        <is>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3156844965660675</v>
+        <v>0.5016690156516579</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1669333611804016</v>
+        <v>0.23934004713949</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1988463123109321</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0.1466292566085681</v>
+        <v>0.1927821482139032</v>
+      </c>
+      <c r="I63" s="5" t="n">
+        <v>-0.1449388608477118</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.08666161972094444</v>
-      </c>
-      <c r="K63" s="5" t="n">
-        <v>-0.02661971830985921</v>
-      </c>
-      <c r="L63" s="3" t="n">
-        <v>0.01111923920994884</v>
+        <v>0.0218049666868565</v>
+      </c>
+      <c r="K63" s="3" t="n">
+        <v>0.03903302794672414</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>-0.01301740529471995</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3401,10 +3389,14 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RSP</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D64" s="17" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3412,29 +3404,29 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Equal Weight</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.2868706191587262</v>
+        <v>0.3679737868752242</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1972790742480612</v>
+        <v>0.2007100652504827</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1955379731175935</v>
+        <v>0.1925134514647706</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1062527719952544</v>
+        <v>0.1656140517742317</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.04777409171794811</v>
+        <v>0.05396696443259796</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.001456332772038493</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>0.006633119853614033</v>
+        <v>0.006873393147594387</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>-0.001353039134054934</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3443,40 +3435,40 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
-      <c r="D65" s="6" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D65" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.4062411094242195</v>
+        <v>0.2674877064130126</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.2129029847678061</v>
+        <v>0.1814794926013972</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1934138074424667</v>
+        <v>0.1805613142528613</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1132632267235152</v>
+        <v>0.1129816596683757</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.01247699415558423</v>
+        <v>0.05661920230742989</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.01633061156473925</v>
-      </c>
-      <c r="L65" s="3" t="n">
-        <v>0.003620207339147585</v>
+        <v>0.0007777472778844885</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>-0.005907748239036614</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3485,82 +3477,90 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IAU</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr"/>
-      <c r="D66" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>ARGT</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.5279796511627906</v>
+        <v>0.1637903547167829</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.2514880952380951</v>
+        <v>0.2138527319451498</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1882440476190474</v>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>-0.1195561139028476</v>
-      </c>
-      <c r="J66" s="5" t="n">
-        <v>-0.002135738016136757</v>
+        <v>0.1732895662995309</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0.1105422262193525</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0.04931021223757615</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.05322479649342515</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>0.01877649909145962</v>
+        <v>0.03457216940363006</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>-0.01074380165289246</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
-      <c r="A67" s="14" t="n">
+      <c r="A67" t="n">
         <v>66</v>
       </c>
-      <c r="B67" s="15" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C67" s="14" t="inlineStr"/>
-      <c r="D67" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E67" s="14" t="inlineStr">
-        <is>
-          <t>Gold</t>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.5246413439381552</v>
+        <v>0.3149230903969888</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.2501371365880418</v>
+        <v>0.1477130340512638</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1874200036569758</v>
-      </c>
-      <c r="I67" s="5" t="n">
-        <v>-0.1199450796987964</v>
-      </c>
-      <c r="J67" s="5" t="n">
-        <v>-0.002553067328032621</v>
-      </c>
-      <c r="K67" s="3" t="n">
-        <v>0.05281798583307684</v>
-      </c>
-      <c r="L67" s="3" t="n">
-        <v>0.01847162222553278</v>
+        <v>0.1656590319776483</v>
+      </c>
+      <c r="I67" s="3" t="n">
+        <v>0.1729069032654613</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0.08298391947976902</v>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>-0.01539558089807569</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>-0.0005787874403125892</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3584,25 +3584,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3882828281830024</v>
+        <v>0.368890240733913</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1830907528643175</v>
+        <v>0.1732407531592217</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1752617636537892</v>
+        <v>0.1641869715782336</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1632792641767546</v>
-      </c>
-      <c r="J68" s="5" t="n">
-        <v>-0.001096352459842631</v>
+        <v>0.1785832381157937</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0.03807510277921522</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.006661485511269216</v>
+        <v>0.00777691367625799</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0.01556899641577059</v>
+        <v>0.0004411602514613477</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3626,25 +3626,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3639170736147284</v>
+        <v>0.3389650571672791</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1776775710269309</v>
+        <v>0.1624781395874466</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1648624412082786</v>
+        <v>0.1536838247180545</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1598639520860925</v>
+        <v>0.171655678596222</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.03124297395192799</v>
+        <v>0.05857147738522883</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.01100141043723557</v>
-      </c>
-      <c r="L69" s="3" t="n">
-        <v>0.01472253680634217</v>
+        <v>0.007622811970637855</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>-0.004185267857143016</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3668,25 +3668,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.3644866882278774</v>
+        <v>0.3448009166932995</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1645535091353658</v>
+        <v>0.1541638466302326</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1625881285506414</v>
+        <v>0.151566718262478</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.151014005431523</v>
-      </c>
-      <c r="J70" s="5" t="n">
-        <v>-0.002034890633501929</v>
+        <v>0.1666923968156502</v>
+      </c>
+      <c r="J70" s="3" t="n">
+        <v>0.03547735498680149</v>
       </c>
       <c r="K70" s="3" t="n">
-        <v>0.001690521807731216</v>
-      </c>
-      <c r="L70" s="3" t="n">
-        <v>0.01461187214611881</v>
+        <v>0.00225529995489393</v>
+      </c>
+      <c r="L70" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3695,7 +3695,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SPGP</t>
+          <t>IAK</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3703,36 +3703,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D71" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D71" s="19" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.2716768394445621</v>
+        <v>0.1240082424315219</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1361945264796456</v>
+        <v>0.1177130934369355</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1578989399927713</v>
+        <v>0.1420842811885679</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1118288439248147</v>
+        <v>0.1104150692036279</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.0395016685758045</v>
+        <v>0.09825167522900524</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.01874465271836356</v>
-      </c>
-      <c r="L71" s="3" t="n">
-        <v>0.008957133717210519</v>
+        <v>-0.02133922001471666</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>-0.01061743423277195</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>XHE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3749,36 +3749,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D72" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D72" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.1440470804488283</v>
+        <v>0.09014043034262476</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1422805785525787</v>
+        <v>0.1678481083089864</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1445207987986072</v>
+        <v>0.1419592395524549</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.11427549287424</v>
+        <v>0.1186521120075936</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.1454467692844736</v>
-      </c>
-      <c r="K72" s="5" t="n">
-        <v>-0.001957343412526957</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>0.02127218730575331</v>
+        <v>0.1592278372064428</v>
+      </c>
+      <c r="K72" s="3" t="n">
+        <v>0.02267057164551467</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>-0.003382663847780076</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3787,7 +3787,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>XHE</t>
+          <t>SPGP</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -3795,36 +3795,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D73" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D73" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.09014043034262476</v>
+        <v>0.2513497712995145</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1678481083089864</v>
+        <v>0.1132947376090179</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1419592395524549</v>
+        <v>0.1404287391249801</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1186521120075936</v>
+        <v>0.1255258229554177</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.1592278372064428</v>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>0.02267057164551467</v>
+        <v>0.05140472468514123</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>-0.02379280755129098</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.003382663847780076</v>
+        <v>-0.008084971464806578</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="13" t="inlineStr">
+      <c r="D74" s="16" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -3848,25 +3848,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.2817216038802786</v>
+        <v>0.2790947295142823</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1235371154813356</v>
+        <v>0.11874782277976</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1416837694000466</v>
+        <v>0.1375228054869186</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>-0.02043217754449034</v>
+        <v>-0.01841913211362056</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-0.01191674489250716</v>
+        <v>-0.004773760453598896</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01589464123524065</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>0.003550478542760249</v>
+        <v>-0.01650514839491224</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>-0.0009229349330872605</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3890,25 +3890,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1550075606960968</v>
+        <v>0.1339461417668435</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.08479369254741864</v>
+        <v>0.0849036512296133</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1299303192409582</v>
+        <v>0.1163326149421147</v>
       </c>
       <c r="I75" s="5" t="n">
-        <v>-0.02056019891666849</v>
+        <v>-0.004767145874321477</v>
       </c>
       <c r="J75" s="5" t="n">
-        <v>-0.1060900874103196</v>
+        <v>-0.05429291846172923</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.03994638069705081</v>
+        <v>-0.02815376285868976</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.01761864165956251</v>
+        <v>0.002513264451270425</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3932,25 +3932,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.3010037306798734</v>
+        <v>0.2880208922052006</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1129433413670211</v>
+        <v>0.1079975904340629</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1172350092451186</v>
+        <v>0.1039173673869422</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.09247207868534724</v>
-      </c>
-      <c r="J76" s="5" t="n">
-        <v>-0.0257187447462236</v>
-      </c>
-      <c r="K76" s="5" t="n">
-        <v>-0.003841329570398289</v>
+        <v>0.1122618397722235</v>
+      </c>
+      <c r="J76" s="3" t="n">
+        <v>0.01149356770212351</v>
+      </c>
+      <c r="K76" s="3" t="n">
+        <v>0.003696130858760638</v>
       </c>
       <c r="L76" s="3" t="n">
-        <v>0.01307502192457943</v>
+        <v>0.004407019752892039</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3974,25 +3974,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2985417707573699</v>
+        <v>0.2852665263897856</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1107987917000288</v>
+        <v>0.105842365351738</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1149385263203155</v>
+        <v>0.1016498517459035</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.09171294075770597</v>
-      </c>
-      <c r="J77" s="5" t="n">
-        <v>-0.02595049118359805</v>
-      </c>
-      <c r="K77" s="5" t="n">
-        <v>-0.003712971184114844</v>
+        <v>0.1111063980929847</v>
+      </c>
+      <c r="J77" s="3" t="n">
+        <v>0.01132266916418612</v>
+      </c>
+      <c r="K77" s="3" t="n">
+        <v>0.003805668016194419</v>
       </c>
       <c r="L77" s="3" t="n">
-        <v>0.01329940070601765</v>
+        <v>0.004374949364011949</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4005,7 +4005,7 @@
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" s="18" t="inlineStr">
+      <c r="D78" s="19" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4016,25 +4016,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2185364289918372</v>
+        <v>0.2016337660027787</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1140623425143577</v>
+        <v>0.09347242307623538</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1057315946878823</v>
+        <v>0.08908189559558255</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1538986924889809</v>
+        <v>0.1612025748558932</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.125995189238777</v>
+        <v>0.1155330829606689</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.007534150119701488</v>
-      </c>
-      <c r="L78" s="3" t="n">
-        <v>0.01583132187988068</v>
+        <v>0.004031402503713366</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>-0.007897127681878557</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4047,7 +4047,7 @@
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="18" t="inlineStr">
+      <c r="D79" s="19" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1997060649165827</v>
+        <v>0.1832037512026288</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.1115657911371921</v>
+        <v>0.09122240327740871</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1009360636263172</v>
+        <v>0.08596259482642443</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.152980847821963</v>
+        <v>0.1586540746227985</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.1259845655650877</v>
+        <v>0.1145982701748662</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.009655172413793212</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>0.01560874089490127</v>
+        <v>0.004843452689845984</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>-0.008025956284153035</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4100,25 +4100,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.08030548778692337</v>
+        <v>0.07244309503299284</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.08728937118672331</v>
+        <v>0.08317414701827608</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.08818205539952029</v>
+        <v>0.08470351397488507</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.01082794053715097</v>
+        <v>0.003280632711087694</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.0464601150074222</v>
+        <v>0.02564370424868589</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.0008203445447086954</v>
+        <v>-0.001409940077546801</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.003156787092248314</v>
+        <v>-0.003166783954961394</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>XRT</t>
+          <t>EUO</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -4135,36 +4135,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D81" s="19" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+      <c r="D81" s="20" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Retail</t>
-        </is>
-      </c>
-      <c r="F81" s="3" t="n">
-        <v>0.2410424643626312</v>
+          <t>Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>-0.07489941194676575</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.03134178887766037</v>
+        <v>0.05432098765432092</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.08711249093964857</v>
+        <v>0.06631393298059951</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.02980098305656065</v>
-      </c>
-      <c r="J81" s="3" t="n">
-        <v>0.04054989329581771</v>
+        <v>0.02048480710139988</v>
+      </c>
+      <c r="J81" s="5" t="n">
+        <v>-0.004662004662004726</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.05130168453292494</v>
+        <v>-0.01124710552431363</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>0.004051863857374549</v>
+        <v>0.002683663200268471</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4173,44 +4173,40 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D82" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr"/>
+      <c r="D82" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1998373930996897</v>
+        <v>0.1566941127918744</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.05245262746766155</v>
+        <v>0.05562761881817591</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.07242413138725778</v>
-      </c>
-      <c r="I82" s="3" t="n">
-        <v>0.08961155377080265</v>
+        <v>0.06495642103098764</v>
+      </c>
+      <c r="I82" s="5" t="n">
+        <v>-0.06766952750770716</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.0125437716889033</v>
+        <v>-0.02424858487928927</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.01862276624991821</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>0.01187864880369882</v>
+        <v>-0.00875979714153996</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>-0.0006971880083662674</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4219,52 +4215,56 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>XLU</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr"/>
-      <c r="D83" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>EDEN</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D83" s="7" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1494914801842251</v>
+        <v>0.1287975816274116</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.05510406823618341</v>
+        <v>0.1298466270297642</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.07055179221919028</v>
-      </c>
-      <c r="I83" s="5" t="n">
-        <v>-0.07020190225236655</v>
-      </c>
-      <c r="J83" s="5" t="n">
-        <v>-0.01445683583015067</v>
-      </c>
-      <c r="K83" s="5" t="n">
-        <v>-0.01442968392120925</v>
-      </c>
-      <c r="L83" s="3" t="n">
-        <v>0.008436840871806961</v>
+        <v>0.06155451612850937</v>
+      </c>
+      <c r="I83" s="3" t="n">
+        <v>0.1530563136803349</v>
+      </c>
+      <c r="J83" s="3" t="n">
+        <v>0.1151748315107952</v>
+      </c>
+      <c r="K83" s="3" t="n">
+        <v>0.06433217499777233</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>-0.003004757532760194</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
-      <c r="A84" t="n">
+      <c r="A84" s="13" t="n">
         <v>83</v>
       </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
+      <c r="B84" s="14" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C84" s="13" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
@@ -4274,77 +4274,77 @@
           <t>Currency</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F84" s="5" t="n">
-        <v>-0.1069502696225285</v>
+      <c r="E84" s="13" t="inlineStr">
+        <is>
+          <t>US Dollar Basket</t>
+        </is>
+      </c>
+      <c r="F84" s="3" t="n">
+        <v>0.01818664829552352</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05484784147204524</v>
+        <v>0.05367898038083507</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.06652512384996467</v>
+        <v>0.05856060074610636</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.01810109289617468</v>
+        <v>0.02147797597378953</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.008457374830852515</v>
+        <v>0.001427551748750755</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.01094890510948909</v>
-      </c>
-      <c r="L84" s="5" t="n">
-        <v>-0.007326007326007411</v>
+        <v>-0.004611564384533584</v>
+      </c>
+      <c r="L84" s="3" t="n">
+        <v>0.00178507675830053</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
-      <c r="A85" s="14" t="n">
+      <c r="A85" t="n">
         <v>84</v>
       </c>
-      <c r="B85" s="15" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C85" s="14" t="inlineStr">
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D85" s="20" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E85" s="14" t="inlineStr">
-        <is>
-          <t>US Dollar Basket</t>
+      <c r="D85" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Mid Growth</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.004042001523348215</v>
+        <v>0.1825645249363164</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.0533312962898409</v>
+        <v>0.04292575582459923</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.05633973983511709</v>
+        <v>0.05156022711301511</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.01928675400291135</v>
+        <v>0.1059865714403436</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.006106321839080442</v>
+        <v>0.02185652333343513</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.002847988608045471</v>
+        <v>-0.008211104857133278</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.005679801206957769</v>
+        <v>-0.001000500250125103</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4353,7 +4353,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>VCR</t>
+          <t>XRT</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -4361,36 +4361,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D86" s="19" t="inlineStr">
+      <c r="D86" s="21" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.1500386434428183</v>
+        <v>0.2343672396646488</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.02588001178342614</v>
+        <v>0.008034594944869911</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.05221960701231732</v>
+        <v>0.04141552668502424</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.02429070104848674</v>
+        <v>0.05204308111663636</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.001257225934486295</v>
+        <v>0.05479426660633746</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.02503241248628696</v>
+        <v>-0.0320534223706177</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.01289954929285608</v>
+        <v>0.002767208578346558</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EDEN</t>
+          <t>USDU</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4407,78 +4407,78 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="6" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D87" s="20" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>US Dollar Basket</t>
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.1303604469410917</v>
+        <v>0.007011871331840336</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.1263304308512878</v>
+        <v>0.03179632752234385</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.04943048156188334</v>
+        <v>0.04005384386303334</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.1489003891522491</v>
-      </c>
-      <c r="J87" s="3" t="n">
-        <v>0.1029485773602437</v>
-      </c>
-      <c r="K87" s="3" t="n">
-        <v>0.07327779270805346</v>
+        <v>0.009230769230769154</v>
+      </c>
+      <c r="J87" s="5" t="n">
+        <v>-0.009063444108761365</v>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>-0.007939508506616288</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>0.01818645364153992</v>
+        <v>0.002291825821237437</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
-      <c r="A88" s="14" t="n">
+      <c r="A88" s="13" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="15" t="inlineStr">
+      <c r="B88" s="14" t="inlineStr">
         <is>
           <t>HYG</t>
         </is>
       </c>
-      <c r="C88" s="14" t="inlineStr"/>
-      <c r="D88" s="18" t="inlineStr">
+      <c r="C88" s="13" t="inlineStr"/>
+      <c r="D88" s="19" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
       </c>
-      <c r="E88" s="14" t="inlineStr">
+      <c r="E88" s="13" t="inlineStr">
         <is>
           <t>High Yield Credit</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.08722552584727028</v>
+        <v>0.08681672955867792</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.0424430055449152</v>
+        <v>0.0397368170939203</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.04081875942089486</v>
+        <v>0.0372025706220056</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.01936531992436374</v>
+        <v>0.02448336974500886</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.007162069063010978</v>
+        <v>0.01236182049937984</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.001560546549837394</v>
+        <v>0.002443347658109829</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0.001264062697509782</v>
+        <v>0.000126246686024567</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>USDU</t>
+          <t>VCR</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4495,124 +4495,124 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="20" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D89" s="21" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>US Dollar Basket</t>
-        </is>
-      </c>
-      <c r="F89" s="5" t="n">
-        <v>-0.005216556647021364</v>
-      </c>
-      <c r="G89" s="3" t="n">
-        <v>0.03021725246115814</v>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.1217343212439641</v>
+      </c>
+      <c r="G89" s="5" t="n">
+        <v>-0.002850800825397681</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.03887454029696635</v>
+        <v>0.02209850590178353</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.00692307692307681</v>
-      </c>
-      <c r="J89" s="5" t="n">
-        <v>-0.003046458492003135</v>
+        <v>0.03556688664814045</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.01266022911882714</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.008333333333333304</v>
+        <v>-0.02440988474508021</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.006828528072837625</v>
+        <v>-0.008592471358428888</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="14" t="n">
+      <c r="A90" s="13" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="15" t="inlineStr">
+      <c r="B90" s="14" t="inlineStr">
         <is>
           <t>SHY</t>
         </is>
       </c>
-      <c r="C90" s="14" t="inlineStr"/>
-      <c r="D90" s="21" t="inlineStr">
+      <c r="C90" s="13" t="inlineStr"/>
+      <c r="D90" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E90" s="14" t="inlineStr">
+      <c r="E90" s="13" t="inlineStr">
         <is>
           <t>Short Treasury</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04761595636265392</v>
+        <v>0.04850438450073868</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.0236487050509413</v>
+        <v>0.02265642412273938</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.0229717788663848</v>
+        <v>0.02098221377412379</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.005951274110315596</v>
+        <v>0.005218904814164871</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.005056579397369365</v>
+        <v>0.006897335925965864</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.0006617251800502544</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>0.0008574228319451205</v>
+        <v>0.001639803638132653</v>
+      </c>
+      <c r="L90" s="5" t="n">
+        <v>-0.0002447680822420528</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
-      <c r="A91" s="14" t="n">
+      <c r="A91" s="13" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="15" t="inlineStr">
+      <c r="B91" s="14" t="inlineStr">
         <is>
           <t>TIP</t>
         </is>
       </c>
-      <c r="C91" s="14" t="inlineStr">
+      <c r="C91" s="13" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D91" s="16" t="inlineStr">
+      <c r="D91" s="15" t="inlineStr">
         <is>
           <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
-      <c r="E91" s="14" t="inlineStr">
+      <c r="E91" s="13" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.03884995660441404</v>
+        <v>0.04317788517377652</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.009802118986184105</v>
+        <v>0.007312713607678489</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.009802118986184105</v>
+        <v>0.007030025287676267</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.005042772788324767</v>
+        <v>-0.007845986077447686</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.008586224419270927</v>
-      </c>
-      <c r="K91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>0.001310125397716577</v>
+        <v>-0.004707686268754618</v>
+      </c>
+      <c r="K91" s="3" t="n">
+        <v>0.0002807148872461251</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>-0.0009345794392522366</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4625,7 +4625,7 @@
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" s="21" t="inlineStr">
+      <c r="D92" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4636,25 +4636,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.02867101933122229</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>0.0005534797455508667</v>
-      </c>
-      <c r="H92" s="3" t="n">
-        <v>0.008099424455868309</v>
+        <v>0.03432451239952883</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.004021779944449633</v>
+      </c>
+      <c r="H92" s="5" t="n">
+        <v>-0.0002735691732980161</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.02424105595279302</v>
+        <v>-0.02373986519040594</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.009391444994799047</v>
+        <v>-0.00420878205430486</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.007485317943109138</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>0.001084834020394831</v>
+        <v>-0.003749236446666804</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>-0.0001083658430862666</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4678,67 +4678,67 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.1409051936538903</v>
+        <v>0.124514141877363</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.009430335701041015</v>
-      </c>
-      <c r="H93" s="3" t="n">
-        <v>0.005802657491454255</v>
+        <v>-0.01762051575255419</v>
+      </c>
+      <c r="H93" s="5" t="n">
+        <v>-0.01136511229701853</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.03273544536427386</v>
-      </c>
-      <c r="J93" s="5" t="n">
-        <v>-0.02227542996962273</v>
+        <v>0.04750482278981072</v>
+      </c>
+      <c r="J93" s="3" t="n">
+        <v>0.005034786171375982</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.01514511129895746</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>0.01679999999999993</v>
+        <v>-0.006327314090715075</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>-0.0002861025677705076</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
-      <c r="A94" s="14" t="n">
+      <c r="A94" s="13" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="15" t="inlineStr">
+      <c r="B94" s="14" t="inlineStr">
         <is>
           <t>TLT</t>
         </is>
       </c>
-      <c r="C94" s="14" t="inlineStr"/>
-      <c r="D94" s="21" t="inlineStr">
+      <c r="C94" s="13" t="inlineStr"/>
+      <c r="D94" s="22" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
       </c>
-      <c r="E94" s="14" t="inlineStr">
+      <c r="E94" s="13" t="inlineStr">
         <is>
           <t>Long Treasury</t>
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.04006898781653645</v>
+        <v>-0.02927729332589524</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.008546694040490355</v>
+        <v>-0.01293075823261569</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>-0.001139286249561944</v>
+        <v>-0.01442943523621854</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.05405518633991735</v>
+        <v>-0.04751838089531935</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.02898420325882323</v>
-      </c>
-      <c r="K94" s="5" t="n">
-        <v>-0.007415856574352286</v>
+        <v>-0.02086917799302457</v>
+      </c>
+      <c r="K94" s="3" t="n">
+        <v>0.001520618672253171</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>0.001464307504575935</v>
+        <v>0.003168027293773745</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4755,7 +4755,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D95" s="6" t="inlineStr">
+      <c r="D95" s="7" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -4766,25 +4766,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.04326018808777432</v>
+        <v>0.01961986511342739</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05131128848346633</v>
+        <v>-0.05134055904164292</v>
       </c>
       <c r="H95" s="5" t="n">
-        <v>-0.04389965792474337</v>
+        <v>-0.04696710401216975</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.008933889219773561</v>
+        <v>-0.002000400080016007</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.03956684714702208</v>
+        <v>0.05386565272496835</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.007751937984496138</v>
+        <v>-0.004588986432561781</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.001000600360216097</v>
+        <v>-0.0006009615384615641</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -676,25 +676,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.770571927606757</v>
+        <v>1.76190676837322</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.302617193355203</v>
+        <v>1.295415809304097</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.338421257721972</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.5948104212509173</v>
+        <v>0.589822687134592</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.07091375235506958</v>
+        <v>-0.07381944892730075</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.01531121231836907</v>
+        <v>-0.01839080459770115</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.03219059743566444</v>
+        <v>0.02896244430299166</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -722,25 +722,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.533497710044304</v>
+        <v>1.519821536299943</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.147294632170278</v>
+        <v>1.135702954468412</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1.296873242205359</v>
+        <v>1.296873103076994</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.5162155413214795</v>
+        <v>0.5080306907323744</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.06748853800295351</v>
+        <v>-0.07252243112768786</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.06512270998963021</v>
+        <v>-0.07016937435188386</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.04263685427910557</v>
+        <v>0.03700848111025445</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -764,25 +764,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.37694680438722</v>
+        <v>2.393364544901203</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.590363463506903</v>
+        <v>1.602957062886529</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>1.29651281131565</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.4607433125542493</v>
+        <v>0.4678450248559931</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.05668131742679372</v>
+        <v>0.06181859695188097</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.1279551547648063</v>
+        <v>0.1334389471118693</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.0252547629596811</v>
+        <v>0.0302392556490918</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -810,25 +810,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.90187891440501</v>
+        <v>1.902296450939458</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.288442541982219</v>
+        <v>1.288771814290418</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>1.253210405004939</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.6591071854857962</v>
+        <v>0.6593459059441396</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.0187773542284343</v>
+        <v>-0.01863617111393467</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.0156364167762677</v>
+        <v>0.01578255151249452</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.03422619047619047</v>
+        <v>0.03437500000000004</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -852,25 +852,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.533534744574753</v>
+        <v>1.522117810605325</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.136597741756676</v>
+        <v>1.126969535398306</v>
       </c>
       <c r="H6" s="3" t="n">
         <v>1.191116431606419</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.6068641757156692</v>
+        <v>0.5996231215989771</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.03752236574486423</v>
+        <v>-0.04185960391413457</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.02488169458424094</v>
+        <v>-0.02927589574100509</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.03399044205495816</v>
+        <v>0.0293309438470728</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -898,25 +898,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.515024894112569</v>
+        <v>1.503050916966636</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.079175504954714</v>
+        <v>1.069276989375131</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.132718436157833</v>
+        <v>1.13271861918637</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5637892938862188</v>
+        <v>0.5563442896738195</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.03953532722905162</v>
+        <v>-0.04410797877654371</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.02510548523206746</v>
+        <v>-0.02974683544303791</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.03378076062639823</v>
+        <v>0.0288590604026846</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -944,25 +944,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.486964726675999</v>
+        <v>1.468642853403902</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9682250354492876</v>
+        <v>0.9537248017774296</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.9777072884948463</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4944818162707589</v>
+        <v>0.4834717258776537</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.00166757359265568</v>
+        <v>-0.009022450806579152</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.004794568488835971</v>
+        <v>-0.01212640862322401</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.02920738327904449</v>
+        <v>0.02162504524068032</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -990,25 +990,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.248766281111661</v>
+        <v>1.245552323050225</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9745913541681384</v>
+        <v>0.9717692495083181</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7987389575530752</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.6103279631760645</v>
+        <v>0.6080264672036826</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.1414151712887439</v>
+        <v>0.1397838499184341</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.09776426750343203</v>
+        <v>0.09619533241812128</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.01652592390810859</v>
+        <v>0.01507309543267055</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1036,25 +1036,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.297946931275868</v>
+        <v>1.309903480126744</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8500633107589615</v>
+        <v>0.8596896019212414</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7632231863526957</v>
+        <v>0.7632233241123314</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.1336705544336463</v>
+        <v>0.1395692056080491</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.1239703237047451</v>
+        <v>0.129818503181566</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.04925078406318972</v>
+        <v>0.05471018701359043</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-0.01008219178082193</v>
+        <v>-0.004931506849315093</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1082,25 +1082,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.593004769475357</v>
+        <v>1.621621621621621</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.023573200992555</v>
+        <v>1.04590570719603</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.7295285359801487</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.5592734225621412</v>
+        <v>0.5764818355640533</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2842519685039371</v>
+        <v>0.2984251968503937</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.1700143472022955</v>
+        <v>0.1829268292682926</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.01053283767038393</v>
+        <v>0.0216852540272614</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1124,25 +1124,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8664313340721865</v>
+        <v>0.8686052249752656</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7533611714484496</v>
+        <v>0.7554033567172578</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.660502028863464</v>
+        <v>0.6605021650206104</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.31693666110139</v>
+        <v>0.3184704233032369</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.2691392937377841</v>
+        <v>0.2706173890290078</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.05592233009708725</v>
+        <v>0.05715210355987055</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.007543496775763492</v>
+        <v>-0.00638763839883183</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1170,25 +1170,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.355409763798361</v>
+        <v>1.370582727666044</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6774698650070796</v>
+        <v>0.6882757086620002</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6380926381289791</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.119148960604234</v>
+        <v>0.1263582398569527</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.1851070251240816</v>
+        <v>0.1927411898235381</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.02403846153846168</v>
+        <v>0.03063506261180682</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.009623702422145386</v>
+        <v>-0.003243944636678209</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1216,25 +1216,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8248710270235242</v>
+        <v>0.8340311072392603</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5786446689906584</v>
+        <v>0.5865689469383799</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.5508026113365021</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.07331965511321381</v>
+        <v>0.07870736739637607</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.05457402463137584</v>
+        <v>-0.04982829663128907</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.01795332136445249</v>
+        <v>0.02306311282971962</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-0.01007252215954879</v>
+        <v>-0.005103411227504684</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1262,25 +1262,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.7376907387544698</v>
+        <v>0.7438060442665135</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.6705661380340722</v>
+        <v>0.6764452177139673</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.5470265509350694</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.1340904829507406</v>
+        <v>0.1380815900141965</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02095490716180382</v>
+        <v>0.02454786592717628</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.07985615180575389</v>
+        <v>0.08365639665374425</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>-0.0149368325539192</v>
+        <v>-0.01147018450012793</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1308,25 +1308,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8239276169783167</v>
+        <v>0.8343468422103995</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6084571679745967</v>
+        <v>0.6176453604501124</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.545877083625423</v>
+        <v>0.5458769371817545</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.1384686341945827</v>
+        <v>0.1449721604359289</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.05720210864966413</v>
+        <v>0.06324139813863106</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.04048192771084325</v>
+        <v>0.04642570281124492</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.006290273089905041</v>
+        <v>-0.0006136851795029985</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1350,25 +1350,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>0.9922741014444072</v>
+        <v>1.007725898555593</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.6060113728675873</v>
+        <v>0.6184673707013268</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.512320606552938</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.2189886752699499</v>
+        <v>-0.2129312615222544</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.0367061880786097</v>
+        <v>-0.02923501705375986</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.06195165622202325</v>
+        <v>0.07018800358102073</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.02047894302229558</v>
+        <v>-0.01288191577208908</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1396,25 +1396,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.105782947414392</v>
+        <v>1.112849333143971</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7207680894967674</v>
+        <v>0.7265424790588371</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.4826594375549524</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.2985972090874711</v>
+        <v>0.3029549178427982</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.2674999736543959</v>
+        <v>0.2717533292706857</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.1605956471935852</v>
+        <v>0.1644902634593357</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.006156901688182614</v>
+        <v>0.009533267130089396</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1442,25 +1442,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.6504992509123821</v>
+        <v>0.6416329762384267</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4708323425316732</v>
+        <v>0.462931215923458</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.464012917780535</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.4150680735609238</v>
+        <v>0.4074665056016531</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.02544993091629255</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0.004658035915063197</v>
+        <v>0.01994134268344938</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>-0.0007388608692859844</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.008610958815751246</v>
+        <v>0.003192827426065081</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1484,25 +1484,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.7108171050296106</v>
+        <v>0.6988902761882037</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4384415244121684</v>
+        <v>0.4284137076652863</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4186917551982716</v>
+        <v>0.4186919209089364</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.3720445059387629</v>
+        <v>0.3624794040134809</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.04345017910771953</v>
+        <v>0.03617584706242583</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.0139211136890951</v>
+        <v>0.006852641234554424</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.01043179007366768</v>
+        <v>0.003387643168252907</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1530,25 +1530,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.663910987571136</v>
+        <v>0.6673421875438417</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4288149497125653</v>
+        <v>0.4317614525070901</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.414560247003918</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1524400165032129</v>
+        <v>0.1548165787934046</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.06719009838123569</v>
+        <v>0.06939085825416558</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.01007712661149585</v>
+        <v>0.01216010808984969</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.003443679182403958</v>
+        <v>-0.001388580315485499</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1572,25 +1572,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.753180531358071</v>
+        <v>1.786297437949475</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.6614063039094067</v>
+        <v>0.6813908738240149</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0.3982481437733469</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.02137271780777017</v>
+        <v>-0.009601096804952469</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.249576615875847</v>
+        <v>0.2646074070705531</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.1882056209464329</v>
+        <v>0.2024981984146048</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.02397395422257298</v>
+        <v>-0.01223362273086026</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1618,25 +1618,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6780365821612708</v>
+        <v>0.6664952525521191</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.407052033276984</v>
+        <v>0.3973743592104992</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3812607569259066</v>
+        <v>0.3812608589121027</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.3597486281749049</v>
+        <v>0.3503962062189596</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.0572471561769119</v>
+        <v>0.04997535511647522</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.01867227185146247</v>
+        <v>0.01166579085654229</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.008007765105556786</v>
+        <v>0.001074635144035607</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1664,25 +1664,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6505295235814175</v>
+        <v>0.6424863340248785</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3171718366740381</v>
+        <v>0.310753131277048</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.3786844300618613</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.09387366888928628</v>
+        <v>0.08854311700028261</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-0.1977520768854862</v>
+        <v>-0.2016615083889884</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.0446168768186227</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>0.002442499491145833</v>
+        <v>-0.04927255092143545</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>-0.002442499491146055</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1710,25 +1710,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5530938276857971</v>
+        <v>0.5535341377454481</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.5123536914418514</v>
+        <v>0.5127822821346839</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.3784190999316743</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2646481303395474</v>
+        <v>0.2650065229704768</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.2571228373950676</v>
+        <v>0.2574790974094436</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.09716536249157892</v>
+        <v>0.09747629165155214</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.009775033908610453</v>
+        <v>-0.009494410925588115</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1752,25 +1752,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.6704869207071735</v>
+        <v>0.6592349047465613</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.4024125877631208</v>
+        <v>0.3929662823116364</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.377760354004183</v>
+        <v>0.3777602329182244</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3574945757036034</v>
+        <v>0.3483510601195896</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.05729454357380392</v>
+        <v>0.05017296048089692</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.01789297658862887</v>
+        <v>0.01103678929765883</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.007114493712772951</v>
+        <v>0.0003309066843151243</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1798,25 +1798,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5411492372871098</v>
+        <v>0.5367027593953413</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3632000760060674</v>
+        <v>0.3592671137044743</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3722461238272272</v>
+        <v>0.3722462267693607</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.1515040441534812</v>
+        <v>0.1481817589712728</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>-0.1007415156058398</v>
+        <v>-0.1033360294096312</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>-0.006592146746918992</v>
+        <v>-0.009458297506448776</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.004928964917367162</v>
+        <v>0.002029573789504191</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1844,25 +1844,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6741831887155976</v>
+        <v>0.6629918516151567</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3924097561059978</v>
+        <v>0.3831017227159095</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3720418417781526</v>
+        <v>0.3720417271500722</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.3511661237426</v>
+        <v>0.3421339094751219</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.05444483487505614</v>
+        <v>0.04739612967554541</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.01484496588052187</v>
+        <v>0.008060976096412542</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.007008790686623856</v>
+        <v>0.0002771838124653314</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1890,25 +1890,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.071495631171302</v>
+        <v>1.089056771720362</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4514061081742373</v>
+        <v>0.4637103308613706</v>
       </c>
       <c r="H29" s="3" t="n">
         <v>0.3577709735251533</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.07239739870515072</v>
-      </c>
-      <c r="J29" s="5" t="n">
-        <v>-0.004715827805634842</v>
+        <v>0.08148859401462127</v>
+      </c>
+      <c r="J29" s="3" t="n">
+        <v>0.003721643983059408</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.06896239238785684</v>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v>-0.003547896604156109</v>
+        <v>0.07802446760308102</v>
+      </c>
+      <c r="L29" s="3" t="n">
+        <v>0.00489947626288223</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1936,25 +1936,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5747997055369787</v>
+        <v>0.5847095157911364</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4741490071790762</v>
+        <v>0.4834255476820128</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3473148914530824</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1390549800743051</v>
+        <v>0.1462228373304388</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.1134276030523451</v>
+        <v>0.1204341920786254</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.09413843529125021</v>
+        <v>0.1010236412381182</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.01421826965305228</v>
+        <v>-0.008014931927975422</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1978,25 +1978,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5571805031268127</v>
+        <v>0.5676937330898295</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.4745071150904128</v>
+        <v>0.4844621796137114</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3464803550582258</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.1413903680571551</v>
+        <v>0.1490964107367685</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1123516319287314</v>
+        <v>0.119861620965148</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.0950825309491059</v>
+        <v>0.1024759284731775</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.01439182915506043</v>
+        <v>-0.007737542556484067</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2020,25 +2020,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.4916408149972069</v>
+        <v>0.5067651832101063</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.4688061407316384</v>
+        <v>0.4836989786604764</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3431478207070686</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1472191930207196</v>
+        <v>0.158851326790258</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.07971262401642143</v>
+        <v>0.09066028053369823</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.0935550935550935</v>
+        <v>0.1046431046431047</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>-0.01251564455569465</v>
+        <v>-0.002503128911139019</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2066,25 +2066,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.4249456033069008</v>
+        <v>0.426363459628599</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2778951863276378</v>
+        <v>0.2791667238264712</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.3203327503512046</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1169769380383441</v>
+        <v>0.1180883578771881</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.03573998560805935</v>
+        <v>-0.03478052290717193</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.0321415673528348</v>
+        <v>-0.03117852413627054</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.007897705904475583</v>
+        <v>0.008900589193932662</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2112,25 +2112,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.548681083789702</v>
+        <v>0.5413525055230759</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1818901988012578</v>
+        <v>0.1762972173415152</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3185919873131313</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.09146377408603978</v>
+        <v>-0.0957631804709943</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.06946722479987866</v>
+        <v>-0.07387072401212003</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.1036725460393765</v>
+        <v>-0.1079141776536708</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-0.001378332611349564</v>
+        <v>-0.006104044421691102</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2154,25 +2154,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5463634967954014</v>
+        <v>0.5367146880431453</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1855043462607686</v>
+        <v>0.1781071820521309</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.317783047403464</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.01236883733147942</v>
+        <v>-0.01853133678655916</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1483941548800499</v>
+        <v>-0.1537079002891303</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1003797259369325</v>
+        <v>-0.1059930658741952</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.01244890375325158</v>
+        <v>0.006131549609810438</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2200,25 +2200,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.6055287833310221</v>
+        <v>0.6217428158809204</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.4633222338064473</v>
+        <v>0.4781003148637655</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.292486539191916</v>
+        <v>0.2924866917817843</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.1626199709281648</v>
+        <v>0.1743611232809001</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.1449905734563819</v>
+        <v>0.1565536887490468</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.1321759952110146</v>
+        <v>0.1436096976953007</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.01663806998388195</v>
+        <v>-0.006707221962252485</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2246,25 +2246,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.7085639326088764</v>
+        <v>0.7036815242449548</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2767153658559489</v>
+        <v>0.2730670120181828</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.2842205508936391</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.03184498736310015</v>
+        <v>0.02889637742207229</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.05493827160493825</v>
+        <v>-0.05763888888888891</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.005844155844155874</v>
+        <v>-0.008685064935065046</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.002687077599544008</v>
+        <v>-0.005537008386939268</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2288,25 +2288,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.5584716016696392</v>
+        <v>0.5519117122026806</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2863573558254935</v>
+        <v>0.2809427427823317</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.2814584202150137</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.2713444831342522</v>
+        <v>0.2659930631811915</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.03894981943858422</v>
-      </c>
-      <c r="K38" s="3" t="n">
-        <v>0.003822937625754586</v>
+        <v>0.03457660913427252</v>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>-0.0004024144869215762</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.01533138864391836</v>
+        <v>0.0110575944644189</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2334,25 +2334,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5359080255765449</v>
+        <v>0.5458657261103335</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.3253391710678433</v>
+        <v>0.3339318158434581</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2753384805045207</v>
+        <v>0.275338593485343</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2629264418501225</v>
+        <v>0.2711143301186443</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.1528133128090909</v>
+        <v>0.1602873083538494</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.03920581973151349</v>
+        <v>0.04594326766038437</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.01348314606741574</v>
+        <v>-0.007087294727744275</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2376,25 +2376,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.424663539535614</v>
+        <v>0.4288135609894888</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2641669297133249</v>
+        <v>0.2678492377798629</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2678493268287148</v>
+        <v>0.2678492377798629</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1810069019535643</v>
+        <v>0.1844470618776937</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.03732426678324252</v>
-      </c>
-      <c r="K40" s="5" t="n">
-        <v>-0.002904443799012557</v>
+        <v>0.04034589296088087</v>
+      </c>
+      <c r="K40" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.00350774627301953</v>
+        <v>0.006430868167202508</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2422,25 +2422,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.447805734289956</v>
+        <v>0.4428562965026259</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2508440467738888</v>
+        <v>0.2465679380083741</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.2670850367967565</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.262336816610546</v>
+        <v>0.2580214189073216</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.00624493713928409</v>
+        <v>-0.009642166990625811</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.01281760067495208</v>
+        <v>-0.01619236135899016</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.01603099325362378</v>
+        <v>0.01255761138200517</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2464,25 +2464,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4903538977621034</v>
+        <v>0.484539837070888</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.1420379321930683</v>
+        <v>0.137582581834732</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2656739046368983</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-0.06740362797471722</v>
+        <v>-0.07104184044994366</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.01621992103901537</v>
+        <v>-0.02005787142907456</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.09768390735629429</v>
+        <v>-0.1012040481619265</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.001814319851314306</v>
+        <v>-0.0057084697760863</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2506,25 +2506,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3423372590829841</v>
+        <v>0.3431889959225038</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2671748426212666</v>
+        <v>0.2679788875721685</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.2655667527194627</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1276012279827634</v>
+        <v>0.1283167109954428</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.06646013955001573</v>
+        <v>0.0671368274558215</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.001270648030495591</v>
+        <v>0.001905972045743498</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.001907183725365691</v>
+        <v>0.002542911633820921</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2548,25 +2548,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4592865290637298</v>
+        <v>0.461468824520616</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2898266906041567</v>
+        <v>0.2917554689615038</v>
       </c>
       <c r="H44" s="3" t="n">
         <v>0.2645772284716119</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.1346972161273836</v>
+        <v>0.1363940172934253</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.0690645744654057</v>
+        <v>0.07066323002809183</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.01996672212978368</v>
+        <v>0.02149195784803104</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.001633986928104569</v>
+        <v>0.003131808278867165</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2590,16 +2590,16 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3916162350672219</v>
+        <v>0.3916163482686827</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2812916872839297</v>
+        <v>0.2812917832480903</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2636214065828029</v>
+        <v>0.2636215012235226</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1649635933558284</v>
+        <v>0.164963514025785</v>
       </c>
       <c r="J45" s="3" t="n">
         <v>0.06554198069974171</v>
@@ -2632,25 +2632,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4228965687609654</v>
+        <v>0.4236721301174848</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.1903991000561915</v>
+        <v>0.191047936774972</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.2619874180283208</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.0689515273765926</v>
+        <v>0.06953416810735757</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-0.0272315039162303</v>
+        <v>-0.02670128852955678</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.0567266495287061</v>
+        <v>-0.05621251071122535</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.006399707441945512</v>
+        <v>0.006948253794112347</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2674,25 +2674,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3120597038431827</v>
+        <v>0.3139426827522573</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.3044224615860005</v>
+        <v>0.3062944800440746</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.2617404407419122</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.137633189213179</v>
+        <v>0.1392658430438523</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.08722825019203939</v>
+        <v>0.08878856628014486</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.03382789317507418</v>
+        <v>0.03531157270029661</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.006841505131128689</v>
+        <v>-0.005416191562143569</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2720,25 +2720,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4090462993417128</v>
+        <v>0.4101323825735688</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2228796540814408</v>
+        <v>0.2238222598219421</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2492435064781673</v>
+        <v>0.2492433825456852</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1759889566770871</v>
+        <v>0.1768955354357569</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.02827845489776415</v>
+        <v>0.02907116251624564</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.02110385386036595</v>
+        <v>-0.020349215436259</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.002439671174754743</v>
+        <v>-0.001670644391408072</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2762,25 +2762,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4496373468080597</v>
+        <v>0.440709553590787</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2611857609385513</v>
+        <v>0.2534184797158363</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2489618429487046</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.2061853002306882</v>
+        <v>0.1987567510638908</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.0245699286352461</v>
+        <v>0.01825989643021653</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.009787262964725096</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>0.005515887787215235</v>
+        <v>0.003568272955889462</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>-0.0006767960475110302</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2804,25 +2804,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4482633633158033</v>
+        <v>0.4394535020984527</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2606187156565578</v>
+        <v>0.25295022983654</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2483561255753448</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.2061259945266605</v>
+        <v>0.1987889940749692</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.02468313510951514</v>
+        <v>0.01844987203479853</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.009822990274959809</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>0.005573592319589871</v>
+        <v>0.00368012313720012</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-0.0005434252511600235</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4304355597134075</v>
+        <v>0.4249063046658954</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.128984283089794</v>
+        <v>0.124620385237421</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2407439762699701</v>
+        <v>0.240744105364707</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>-0.0830737517828245</v>
+        <v>-0.08661799300745876</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.02816106444834943</v>
+        <v>-0.03191764425600208</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.09007474170147289</v>
-      </c>
-      <c r="L51" s="18" t="n">
-        <v>0</v>
+        <v>-0.09359199824137177</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>-0.003865434559400804</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2892,25 +2892,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3341455326267242</v>
+        <v>0.3311002143863992</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.1716173788981883</v>
+        <v>0.1689429113323648</v>
       </c>
       <c r="H52" s="3" t="n">
         <v>0.2353365686539364</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.0365700458807876</v>
+        <v>0.03420385277257387</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.008503418192328027</v>
+        <v>0.006201293172200639</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.05158042866421308</v>
+        <v>-0.05374539943710743</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.003838221814848719</v>
+        <v>0.001546746104491348</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2938,25 +2938,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.2110256786435136</v>
+        <v>0.2117405920470938</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2803829853546311</v>
+        <v>0.2811388429504595</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2293427066468481</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1488843741631856</v>
+        <v>0.1495624780192868</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.1366693666429213</v>
+        <v>0.1373403847558998</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.04151834832696921</v>
+        <v>0.04213319526244264</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.009082512315270908</v>
+        <v>-0.008497536945812789</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2980,25 +2980,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4469459839971441</v>
+        <v>0.4392215821759962</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2342367069816733</v>
+        <v>0.2276478360959751</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.221764915662316</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1929309488855759</v>
+        <v>0.1865625853834223</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.03698442396619872</v>
+        <v>0.03144856812805696</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.01020801232665636</v>
-      </c>
-      <c r="L54" s="3" t="n">
-        <v>0.001336387934326</v>
+        <v>0.004815100154083263</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>-0.004009163802978222</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3026,25 +3026,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3169838945063816</v>
+        <v>0.3185252139867498</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1620415886689424</v>
+        <v>0.1634014969061208</v>
       </c>
       <c r="H55" s="3" t="n">
         <v>0.2045764963095777</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.07114540094117339</v>
+        <v>0.07239882168412493</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-0.06436180695245242</v>
+        <v>-0.06326685295239665</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.03531108881083789</v>
+        <v>-0.03418213748118404</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.006873527101335597</v>
+        <v>0.008051846032993026</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3068,25 +3068,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3159078763852463</v>
+        <v>0.3166628869288146</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1915237809218715</v>
+        <v>0.192207425296719</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.2035901041379315</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1418446635216428</v>
+        <v>0.142499918397532</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.01992542602704361</v>
+        <v>0.02051061475045102</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.01002527619209914</v>
+        <v>-0.009457271875266349</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.00234688036634223</v>
+        <v>-0.001774470520892968</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3110,25 +3110,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.3277935407927195</v>
+        <v>0.3315232979297777</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2646985977155558</v>
+        <v>0.2682510359309964</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2029492542563476</v>
+        <v>0.2029491727456918</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1299380801786043</v>
+        <v>0.1331120635498926</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.1207514461767996</v>
+        <v>0.1238996243963972</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.05133162786437007</v>
+        <v>0.05428480659432622</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.01426000276893258</v>
+        <v>-0.01149107019244078</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3152,25 +3152,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3478174207498086</v>
+        <v>0.3422732691888335</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2039322659501936</v>
+        <v>0.1989799757892141</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.1980471814095774</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1548348065112952</v>
+        <v>0.1500844752745718</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.05005491374804683</v>
+        <v>0.04573558718382476</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.004912231030577585</v>
+        <v>0.0007785956964894147</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.001195970283656034</v>
+        <v>-0.005304479963980202</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3194,25 +3194,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3482926029508551</v>
+        <v>0.3430624196466703</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2039471327292275</v>
+        <v>0.1992768822369084</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>0.1980201038652212</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1550272294652035</v>
+        <v>0.1505467449485591</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.05010611933034248</v>
+        <v>0.04603263596261997</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.00494735342494157</v>
+        <v>0.001049046145079169</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.00151840747365295</v>
+        <v>-0.005391633317462952</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3236,25 +3236,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3729800757566066</v>
+        <v>0.3745475220139527</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2246871528078966</v>
+        <v>0.2260851975028828</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.1975251415910222</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1270952264061589</v>
+        <v>0.1283818647924673</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.05795067695476508</v>
+        <v>0.0591583832069964</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.02268178785857233</v>
+        <v>0.02384923282188134</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.005410723069355639</v>
+        <v>0.006558452205279508</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3278,25 +3278,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.347344543969605</v>
+        <v>0.3419368872659836</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.2030410556060367</v>
+        <v>0.1982123290349127</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1971221110577652</v>
+        <v>0.1971219972480989</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1548002641618316</v>
+        <v>0.1501651692754191</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.04989460111075061</v>
+        <v>0.04568066814756855</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.0049443114395753</v>
+        <v>0.0009107942125534674</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.001047635060853258</v>
+        <v>-0.005057102577699535</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3320,25 +3320,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.5042595613558092</v>
+        <v>0.5133224578575311</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.240322821700792</v>
+        <v>0.247795546256165</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.1936930204752654</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>-0.1442565477418025</v>
+        <v>-0.139100845535162</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.02179266190593454</v>
+        <v>0.02794878108840182</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.03906347815199696</v>
+        <v>0.04532365093276569</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.0131985731272295</v>
+        <v>-0.007253269916765781</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3362,25 +3362,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.5016690156516579</v>
+        <v>0.5099028261998368</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.23934004713949</v>
+        <v>0.2461354801187672</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1927821482139032</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>-0.1449388608477118</v>
+        <v>-0.1402504698950391</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.0218049666868565</v>
+        <v>0.02740763173834049</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.03903302794672414</v>
+        <v>0.04473015628608823</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.01301740529471995</v>
+        <v>-0.007605675003656609</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3408,25 +3408,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3679737868752242</v>
+        <v>0.3607382819576714</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2007100652504827</v>
+        <v>0.1943592538058279</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.1925134514647706</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1656140517742317</v>
+        <v>0.1594488706249306</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.05396696443259796</v>
+        <v>0.04839230852379606</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.006873393147594387</v>
+        <v>0.001547825174458284</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>-0.001353039134054934</v>
+        <v>-0.006635095753538711</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3450,25 +3450,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2674877064130126</v>
+        <v>0.2698055104862489</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1814794926013972</v>
+        <v>0.1836399122450112</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1805613142528613</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1129816596683757</v>
+        <v>0.1150167395669519</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.05661920230742989</v>
+        <v>0.05855130599164915</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.0007777472778844885</v>
+        <v>0.002607740872906827</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.005907748239036614</v>
+        <v>-0.004089979550102263</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3496,25 +3496,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.1637903547167829</v>
+        <v>0.1772804058209561</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.2138527319451498</v>
+        <v>0.2279230800284739</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.1732895662995309</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1105422262193525</v>
+        <v>0.1234150527764064</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.04931021223757615</v>
+        <v>0.06147326920900165</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.03457216940363006</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-0.01074380165289246</v>
+        <v>0.04656439066551421</v>
+      </c>
+      <c r="L66" s="3" t="n">
+        <v>0.0007231404958678578</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3542,25 +3542,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3149230903969888</v>
+        <v>0.3202535065382257</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1477130340512638</v>
+        <v>0.1523656271346989</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1656590319776483</v>
+        <v>0.1656589580893892</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1729069032654613</v>
+        <v>0.1776617017729802</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.08298391947976902</v>
+        <v>0.08737418294370913</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.01539558089807569</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>-0.0005787874403125892</v>
+        <v>-0.01140413399857465</v>
+      </c>
+      <c r="L67" s="3" t="n">
+        <v>0.003472724641875091</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3584,25 +3584,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.368890240733913</v>
+        <v>0.3592321021155722</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1732407531592217</v>
+        <v>0.1649628950398367</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1641869715782336</v>
+        <v>0.1641868566951896</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1785832381157937</v>
+        <v>0.17026780131286</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.03807510277921522</v>
+        <v>0.03075101430188432</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.00777691367625799</v>
-      </c>
-      <c r="L68" s="3" t="n">
-        <v>0.0004411602514613477</v>
+        <v>0.0006665926008220247</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>-0.006617403771920216</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3626,25 +3626,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3389650571672791</v>
+        <v>0.3314616553231298</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1624781395874466</v>
+        <v>0.155963832276786</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1536838247180545</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.171655678596222</v>
+        <v>0.1650899420952627</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.05857147738522883</v>
+        <v>0.0526394433287134</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.007622811970637855</v>
+        <v>0.001976284584980226</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.004185267857143016</v>
+        <v>-0.009765625</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3668,25 +3668,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.3448009166932995</v>
+        <v>0.3352686869732637</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1541638466302326</v>
+        <v>0.1459827787289874</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.151566718262478</v>
+        <v>0.1515666041664203</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1666923968156502</v>
+        <v>0.1584226374772855</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.03547735498680149</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>0.00225529995489393</v>
-      </c>
-      <c r="L70" s="18" t="n">
-        <v>0</v>
+        <v>0.0281376752653606</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>-0.004848894903022205</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>-0.007088208820882014</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3714,25 +3714,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1240082424315219</v>
+        <v>0.1253912963291841</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1177130934369355</v>
+        <v>0.1190881397173811</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1420842811885679</v>
+        <v>0.1420841480499133</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1104150692036279</v>
+        <v>0.1117811380682443</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.09825167522900524</v>
+        <v>0.09960290763871948</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.02133922001471666</v>
+        <v>-0.02013512609539114</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.01061743423277195</v>
+        <v>-0.009400148779333262</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>XHE</t>
+          <t>SPGP</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3749,36 +3749,36 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D72" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D72" s="17" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.09014043034262476</v>
+        <v>0.2487499709265686</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1678481083089864</v>
+        <v>0.1109816751847064</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1419592395524549</v>
+        <v>0.1404287391249801</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1186521120075936</v>
+        <v>0.123187348335245</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.1592278372064428</v>
-      </c>
-      <c r="K72" s="3" t="n">
-        <v>0.02267057164551467</v>
+        <v>0.04922024947003689</v>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>-0.02582104688353226</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.003382663847780076</v>
+        <v>-0.01014584654407102</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3787,44 +3787,40 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SPGP</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D73" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>IGF</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr"/>
+      <c r="D73" s="16" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2513497712995145</v>
+        <v>0.2820486625989802</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1132947376090179</v>
+        <v>0.1213315359963414</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1404287391249801</v>
-      </c>
-      <c r="I73" s="3" t="n">
-        <v>0.1255258229554177</v>
-      </c>
-      <c r="J73" s="3" t="n">
-        <v>0.05140472468514123</v>
+        <v>0.1375228054869186</v>
+      </c>
+      <c r="I73" s="5" t="n">
+        <v>-0.01615220170279763</v>
+      </c>
+      <c r="J73" s="5" t="n">
+        <v>-0.002475316482360213</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.02379280755129098</v>
-      </c>
-      <c r="L73" s="5" t="n">
-        <v>-0.008084971464806578</v>
+        <v>-0.01423379769836486</v>
+      </c>
+      <c r="L73" s="3" t="n">
+        <v>0.001384402399630558</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3833,40 +3829,40 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>IGF</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.2790947295142823</v>
+        <v>0.1326826920267135</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.11874782277976</v>
+        <v>0.08369472000383649</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1375228054869186</v>
+        <v>0.1163324862504662</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>-0.01841913211362056</v>
+        <v>-0.005876040419308226</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-0.004773760453598896</v>
+        <v>-0.05534663108739857</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.01650514839491224</v>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v>-0.0009229349330872605</v>
+        <v>-0.02923659989171623</v>
+      </c>
+      <c r="L74" s="3" t="n">
+        <v>0.001396258028483643</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3875,40 +3871,44 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BOTZ</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
-      <c r="D75" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D75" s="12" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.1339461417668435</v>
+        <v>0.07610527173939152</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.0849036512296133</v>
+        <v>0.1426796190573569</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1163326149421147</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>-0.004767145874321477</v>
-      </c>
-      <c r="J75" s="5" t="n">
-        <v>-0.05429291846172923</v>
-      </c>
-      <c r="K75" s="5" t="n">
-        <v>-0.02815376285868976</v>
-      </c>
-      <c r="L75" s="3" t="n">
-        <v>0.002513264451270425</v>
+        <v>0.114585945900415</v>
+      </c>
+      <c r="I75" s="3" t="n">
+        <v>0.1351777696881447</v>
+      </c>
+      <c r="J75" s="3" t="n">
+        <v>0.1575105171987132</v>
+      </c>
+      <c r="K75" s="3" t="n">
+        <v>0.02520547945205487</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>-0.007742893508697501</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3932,25 +3932,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2880208922052006</v>
+        <v>0.2797456860955252</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1079975904340629</v>
+        <v>0.1008787575861081</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1039173673869422</v>
+        <v>0.1039172211548733</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1122618397722235</v>
+        <v>0.1051156822348338</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.01149356770212351</v>
-      </c>
-      <c r="K76" s="3" t="n">
-        <v>0.003696130858760638</v>
-      </c>
-      <c r="L76" s="3" t="n">
-        <v>0.004407019752892039</v>
+        <v>0.00499490182798934</v>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>-0.002752437873545066</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>-0.002046116313842661</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3974,25 +3974,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2852665263897856</v>
+        <v>0.2770760522540523</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.105842365351738</v>
+        <v>0.09879529961592937</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1016498517459035</v>
+        <v>0.1016497767703139</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1111063980929847</v>
+        <v>0.1040259375366359</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.01132266916418612</v>
-      </c>
-      <c r="K77" s="3" t="n">
-        <v>0.003805668016194419</v>
-      </c>
-      <c r="L77" s="3" t="n">
-        <v>0.004374949364011949</v>
+        <v>0.004878005869520363</v>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>-0.002591093117408905</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>-0.002025439520375927</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4016,25 +4016,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2016337660027787</v>
+        <v>0.2000255706377414</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.09347242307623538</v>
+        <v>0.09200891391601784</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0.08908189559558255</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1612025748558932</v>
+        <v>0.1596484153093829</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.1155330829606689</v>
+        <v>0.1140400476988872</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.004031402503713366</v>
+        <v>0.00268760166914217</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.007897127681878557</v>
+        <v>-0.009224963309804934</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4058,25 +4058,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1832037512026288</v>
+        <v>0.1805558516044821</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.09122240327740871</v>
+        <v>0.08878034935373735</v>
       </c>
       <c r="H79" s="3" t="n">
         <v>0.08596259482642443</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.1586540746227985</v>
+        <v>0.1560612028719079</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.1145982701748662</v>
+        <v>0.1121039032421285</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.004843452689845984</v>
+        <v>0.002594706798131785</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-0.008025956284153035</v>
+        <v>-0.01024590163934425</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4109,7 +4109,7 @@
         <v>0.08470351397488507</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.003280632711087694</v>
+        <v>0.003280723069199576</v>
       </c>
       <c r="J80" s="3" t="n">
         <v>0.02564370424868589</v>
@@ -4146,25 +4146,25 @@
         </is>
       </c>
       <c r="F81" s="5" t="n">
-        <v>-0.07489941194676575</v>
+        <v>-0.07397090683998764</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05432098765432092</v>
+        <v>0.05537918871252212</v>
       </c>
       <c r="H81" s="3" t="n">
         <v>0.06631393298059951</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.02048480710139988</v>
+        <v>0.02150904745646987</v>
       </c>
       <c r="J81" s="5" t="n">
-        <v>-0.004662004662004726</v>
+        <v>-0.00366300366300365</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.01124710552431363</v>
+        <v>-0.01025471386040355</v>
       </c>
       <c r="L81" s="3" t="n">
-        <v>0.002683663200268471</v>
+        <v>0.003690036900369176</v>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4188,25 +4188,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1566941127918744</v>
+        <v>0.1599218582813513</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.05562761881817591</v>
+        <v>0.05857355635906369</v>
       </c>
       <c r="H82" s="3" t="n">
         <v>0.06495642103098764</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>-0.06766952750770716</v>
+        <v>-0.06506767502633337</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.02424858487928927</v>
+        <v>-0.02152555767430131</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.00875979714153996</v>
-      </c>
-      <c r="L82" s="5" t="n">
-        <v>-0.0006971880083662674</v>
+        <v>-0.005993545412632639</v>
+      </c>
+      <c r="L82" s="3" t="n">
+        <v>0.002091564025098691</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4234,25 +4234,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1287975816274116</v>
+        <v>0.1239780215907751</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1298466270297642</v>
+        <v>0.1250226690575149</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.06155451612850937</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1530563136803349</v>
+        <v>0.1481332603527756</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.1151748315107952</v>
+        <v>0.1104135157797737</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0.06433217499777233</v>
+        <v>0.05978793548961958</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.003004757532760194</v>
+        <v>-0.007261497370837144</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4280,25 +4280,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.01818664829552352</v>
+        <v>0.01746092723472836</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05367898038083507</v>
+        <v>0.05292796186310111</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0.05856060074610636</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.02147797597378953</v>
+        <v>0.02074990899162721</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.001427551748750755</v>
+        <v>0.0007137758743753775</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.004611564384533584</v>
+        <v>-0.005321035828308007</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>0.00178507675830053</v>
+        <v>0.001071046054980318</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4326,25 +4326,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1825645249363164</v>
+        <v>0.1824855688672167</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.04292575582459923</v>
+        <v>0.042856122991628</v>
       </c>
       <c r="H85" s="3" t="n">
         <v>0.05156022711301511</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1059865714403436</v>
+        <v>0.105912603627867</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.02185652333343513</v>
+        <v>0.02178829722605169</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.008211104857133278</v>
+        <v>-0.008277323444690898</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.001000500250125103</v>
+        <v>-0.001067200266800183</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4372,25 +4372,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2343672396646488</v>
+        <v>0.2383414202919318</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.008034594944869911</v>
+        <v>0.01127996330849612</v>
       </c>
       <c r="H86" s="3" t="n">
         <v>0.04141552668502424</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.05204308111663636</v>
+        <v>0.0554301348445041</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.05479426660633746</v>
+        <v>0.05819017777857827</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.0320534223706177</v>
+        <v>-0.02893711741791871</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.002767208578346558</v>
+        <v>0.005995618586417617</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4418,25 +4418,25 @@
         </is>
       </c>
       <c r="F87" s="3" t="n">
-        <v>0.007011871331840336</v>
+        <v>0.006628101563802336</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.03179632752234385</v>
+        <v>0.03140311245850147</v>
       </c>
       <c r="H87" s="3" t="n">
         <v>0.04005384386303334</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.009230769230769154</v>
+        <v>0.008846153846153948</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>-0.009063444108761365</v>
+        <v>-0.009441087613293098</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.007939508506616288</v>
+        <v>-0.008317580340264641</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>0.002291825821237437</v>
+        <v>0.001909854851031456</v>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
@@ -4460,25 +4460,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.08681672955867792</v>
+        <v>0.08613066742278419</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.0397368170939203</v>
+        <v>0.0390806873503895</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.0372025706220056</v>
+        <v>0.03720267448056069</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.02448336974500886</v>
+        <v>0.02383666220920144</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.01236182049937984</v>
+        <v>0.01172286454097327</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.002443347658109829</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>0.000126246686024567</v>
+        <v>0.00181065178102191</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>-0.000504986744097824</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4506,25 +4506,25 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.1217343212439641</v>
+        <v>0.1175965830639425</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.002850800825397681</v>
+        <v>-0.006528894497549231</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.02209850590178353</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.03556688664814045</v>
+        <v>0.03174708514198388</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.01266022911882714</v>
+        <v>0.008924921319508394</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.02440988474508021</v>
+        <v>-0.02800845538275709</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.008592471358428888</v>
+        <v>-0.01224938625204586</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4548,25 +4548,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04850438450073868</v>
+        <v>0.04863283880769376</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.02265642412273938</v>
+        <v>0.02278170927684453</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.02098221377412379</v>
+        <v>0.02098231128860872</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.005218904814164871</v>
+        <v>0.005341768918599055</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.006897335925965864</v>
+        <v>0.007020594260636726</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.001639803638132653</v>
+        <v>0.00176241837722424</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.0002447680822420528</v>
+        <v>-0.0001223840411209709</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4594,25 +4594,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.04317788517377652</v>
+        <v>0.04356791223784717</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.007312713607678489</v>
+        <v>0.007689848700252133</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.007030025287676267</v>
+        <v>0.007030242477987114</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.007845986077447686</v>
+        <v>-0.007474740422097947</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.004707686268754618</v>
+        <v>-0.004335266319744013</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.0002807148872461251</v>
+        <v>0.00065500140357444</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>-0.0009345794392522366</v>
+        <v>-0.0005607476635514086</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4636,25 +4636,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.03432451239952883</v>
+        <v>0.03466071669762094</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-0.004021779944449633</v>
+        <v>-0.003697954794328662</v>
       </c>
       <c r="H92" s="5" t="n">
         <v>-0.0002735691732980161</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.02373986519040594</v>
+        <v>-0.02342245103581309</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.00420878205430486</v>
+        <v>-0.003884935687042956</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.003749236446666804</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>-0.0001083658430862666</v>
+        <v>-0.003425322683725418</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>0.0002167316861725332</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4678,25 +4678,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.124514141877363</v>
+        <v>0.1243533706791935</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.01762051575255419</v>
+        <v>-0.01776119195894699</v>
       </c>
       <c r="H93" s="5" t="n">
-        <v>-0.01136511229701853</v>
+        <v>-0.01136521832519133</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.04750482278981072</v>
+        <v>0.04735493299617977</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0.005034786171375982</v>
+        <v>0.00489097350969292</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.006327314090715075</v>
+        <v>-0.006469500924214389</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.0002861025677705076</v>
+        <v>-0.0004291538516558724</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4720,25 +4720,25 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.02927729332589524</v>
+        <v>-0.03010263754388598</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.01293075823261569</v>
+        <v>-0.01377009108777316</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>-0.01442943523621854</v>
+        <v>-0.01442952538653286</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.04751838089531935</v>
+        <v>-0.04832829986775411</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.02086917799302457</v>
+        <v>-0.02170167110052468</v>
       </c>
       <c r="K94" s="3" t="n">
-        <v>0.001520618672253171</v>
+        <v>0.0006690889345262185</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>0.003168027293773745</v>
+        <v>0.002315096868527045</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4766,25 +4766,25 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.01961986511342739</v>
+        <v>0.02002861230329045</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.05134055904164292</v>
+        <v>-0.05096025860429754</v>
       </c>
       <c r="H95" s="5" t="n">
         <v>-0.04696710401216975</v>
       </c>
       <c r="I95" s="5" t="n">
-        <v>-0.002000400080016007</v>
+        <v>-0.001600320064012895</v>
       </c>
       <c r="J95" s="3" t="n">
-        <v>0.05386565272496835</v>
+        <v>0.05428812843261488</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.004588986432561781</v>
+        <v>-0.00418994413407825</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.0006009615384615641</v>
+        <v>-0.0002003205128205954</v>
       </c>
     </row>
     <row r="96" ht="21" customHeight="1">
@@ -4812,25 +4812,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.05513821305533928</v>
+        <v>-0.08123147691078825</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1163644878884735</v>
+        <v>-0.1321285229291973</v>
       </c>
       <c r="H96" s="5" t="n">
-        <v>-0.123677098939435</v>
+        <v>-0.1319593472026728</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.1268705270006507</v>
+        <v>0.1240140227870288</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1715896279594138</v>
-      </c>
-      <c r="K96" s="3" t="n">
-        <v>0.00834465359984482</v>
-      </c>
-      <c r="L96" s="3" t="n">
-        <v>0.009912536443148712</v>
+        <v>0.1883252258512855</v>
+      </c>
+      <c r="K96" s="5" t="n">
+        <v>-0.0001948937828883945</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>-0.01270207852194005</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -200,9 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="16" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -676,25 +673,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.76190676837322</v>
+        <v>1.780701061260387</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.295415809304097</v>
+        <v>1.311035712738891</v>
       </c>
       <c r="H2" s="4" t="n">
         <v>1.338421257721972</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.589822687134592</v>
+        <v>0.6006411526826776</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.07381944892730075</v>
+        <v>-0.06751695213682762</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.01839080459770115</v>
+        <v>-0.01171112556929088</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.02896244430299166</v>
+        <v>0.03596435391470409</v>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -722,25 +719,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.519821536299943</v>
+        <v>1.547923635217787</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.135702954468412</v>
+        <v>1.159521464648385</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>1.296873103076994</v>
+        <v>1.296873381333742</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.5080306907323744</v>
+        <v>0.5248488768743713</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.07252243112768786</v>
+        <v>-0.06217881511795953</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.07016937435188386</v>
+        <v>-0.05979951607328038</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.03700848111025445</v>
+        <v>0.04857363145720894</v>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -764,25 +761,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.393364544901203</v>
+        <v>2.445354056528815</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.602957062886529</v>
+        <v>1.642836794255342</v>
       </c>
       <c r="H4" s="8" t="n">
         <v>1.29651281131565</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.4678450248559931</v>
+        <v>0.490333780478182</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.06181859695188097</v>
+        <v>0.07808664878132321</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.1334389471118693</v>
+        <v>0.1508042895442359</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.0302392556490918</v>
+        <v>0.04602348249889232</v>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -810,25 +807,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.902296450939458</v>
+        <v>1.936534446764092</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.288771814290418</v>
+        <v>1.315772143562726</v>
       </c>
       <c r="H5" s="10" t="n">
         <v>1.253210405004939</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.6593459059441396</v>
+        <v>0.6789209835282883</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.01863617111393467</v>
+        <v>-0.007059155724975286</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.01578255151249452</v>
+        <v>0.02776559988309213</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.03437500000000004</v>
+        <v>0.04657738095238084</v>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -852,25 +849,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.522117810605325</v>
+        <v>1.536413373225165</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.126969535398306</v>
+        <v>1.139025500733548</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.191116431606419</v>
+        <v>1.191116569173679</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5996231215989771</v>
+        <v>0.6086899115826985</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.04185960391413457</v>
+        <v>-0.03642878859962073</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.02927589574100509</v>
+        <v>-0.02377375497633882</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.0293309438470728</v>
+        <v>0.0351652727996814</v>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -898,25 +895,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.503050916966636</v>
+        <v>1.514480634235029</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.069276989375131</v>
+        <v>1.078725921146207</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.13271861918637</v>
+        <v>1.132718802214939</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5563442896738195</v>
+        <v>0.5634509855190464</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.04410797877654371</v>
+        <v>-0.0397431750266648</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.02974683544303791</v>
+        <v>-0.02531645569620244</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.0288590604026846</v>
+        <v>0.03355704697986583</v>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -944,25 +941,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.468642853403902</v>
+        <v>1.479399848212818</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9537248017774296</v>
+        <v>0.9622380654606684</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.9777072884948463</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4834717258776537</v>
+        <v>0.4899358839604793</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.009022450806579152</v>
+        <v>-0.004704312871912864</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.01212640862322401</v>
+        <v>-0.007821796038356643</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.02162504524068032</v>
+        <v>0.02607672819399198</v>
       </c>
     </row>
     <row r="9" ht="21" customHeight="1">
@@ -990,25 +987,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.245552323050225</v>
+        <v>1.253386345824977</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9717692495083181</v>
+        <v>0.9786481296166305</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.7987389575530752</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.6080264672036826</v>
+        <v>0.6136363636363638</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.1397838499184341</v>
+        <v>0.1437601957585646</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.09619533241812128</v>
+        <v>0.1000196116885663</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.01507309543267055</v>
+        <v>0.0186143648415511</v>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1036,25 +1033,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.309903480126744</v>
+        <v>1.306341954937121</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8596896019212414</v>
+        <v>0.8568220940264304</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7632233241123314</v>
+        <v>0.7632231863526957</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.1395692056080491</v>
+        <v>0.1378121605773759</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.129818503181566</v>
+        <v>0.1280764922735766</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.05471018701359043</v>
+        <v>0.05308398187942842</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>-0.004931506849315093</v>
+        <v>-0.006465753424657605</v>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1082,25 +1079,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.621621621621621</v>
+        <v>1.63275039745628</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.04590570719603</v>
+        <v>1.054590570719603</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.7295285359801487</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.5764818355640533</v>
+        <v>0.5831739961759079</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.2984251968503937</v>
+        <v>0.3039370078740158</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.1829268292682926</v>
+        <v>0.187948350071736</v>
       </c>
       <c r="L11" s="3" t="n">
-        <v>0.0216852540272614</v>
+        <v>0.02602230483271373</v>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1124,25 +1121,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8686052249752656</v>
+        <v>0.8740965847392723</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7554033567172578</v>
+        <v>0.7605620540331652</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6605021650206104</v>
+        <v>0.660502028863464</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.3184704233032369</v>
+        <v>0.32234519097106</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.2706173890290078</v>
+        <v>0.274351524501572</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.05715210355987055</v>
+        <v>0.06025889967637532</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.00638763839883183</v>
+        <v>-0.003467575130794431</v>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1170,25 +1167,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.370582727666044</v>
+        <v>1.37032555878693</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6882757086620002</v>
+        <v>0.6880925587695439</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.6380926381289791</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1263582398569527</v>
+        <v>0.1262360486831777</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.1927411898235381</v>
+        <v>0.1926117972015131</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.03063506261180682</v>
+        <v>0.03052325581395343</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>-0.003243944636678209</v>
+        <v>-0.003352076124567449</v>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1216,25 +1213,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8340311072392603</v>
+        <v>0.8365068511745186</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5865689469383799</v>
+        <v>0.5887106436810075</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.5508026113365021</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.07870736739637607</v>
+        <v>0.08016350585128484</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>-0.04982829663128907</v>
+        <v>-0.04854566744207633</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.02306311282971962</v>
+        <v>0.02444413755006236</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>-0.005103411227504684</v>
+        <v>-0.00376040827289803</v>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1262,25 +1259,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.7438060442665135</v>
+        <v>0.754682258767799</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.6764452177139673</v>
+        <v>0.6869012990238477</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.5470265509350694</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.1380815900141965</v>
+        <v>0.1451798676773899</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.02454786592717628</v>
+        <v>0.0309380274897515</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.08365639665374425</v>
+        <v>0.09041522138339109</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>-0.01147018450012793</v>
+        <v>-0.0053046695051302</v>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1308,25 +1305,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8343468422103995</v>
+        <v>0.832094036754814</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6176453604501124</v>
+        <v>0.6156586912938948</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.5458769371817545</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.1449721604359289</v>
+        <v>0.1435659925999622</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.06324139813863106</v>
+        <v>0.06193560581669222</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.04642570281124492</v>
+        <v>0.04514056224899599</v>
       </c>
       <c r="L16" s="5" t="n">
-        <v>-0.0006136851795029985</v>
+        <v>-0.001841055538508773</v>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1350,25 +1347,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.007725898555593</v>
+        <v>1.009405441719852</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.6184673707013268</v>
+        <v>0.619821283509342</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.512320606552938</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>-0.2129312615222544</v>
+        <v>-0.2122728469844614</v>
       </c>
       <c r="J17" s="5" t="n">
-        <v>-0.02923501705375986</v>
+        <v>-0.02842293324671108</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.07018800358102073</v>
+        <v>0.07108325872873777</v>
       </c>
       <c r="L17" s="5" t="n">
-        <v>-0.01288191577208908</v>
+        <v>-0.01205615194054499</v>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1396,25 +1393,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.112849333143971</v>
+        <v>1.11368050503854</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7265424790588371</v>
+        <v>0.7272218190073159</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.4826594375549524</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3029549178427982</v>
+        <v>0.3034674620023494</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>0.2717533292706857</v>
+        <v>0.272253724049073</v>
       </c>
       <c r="K18" s="3" t="n">
-        <v>0.1644902634593357</v>
+        <v>0.1649484536082475</v>
       </c>
       <c r="L18" s="3" t="n">
-        <v>0.009533267130089396</v>
+        <v>0.009930486593842991</v>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1442,25 +1439,25 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.6416329762384267</v>
+        <v>0.6479132541324786</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.462931215923458</v>
+        <v>0.4685278472709435</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.464012917780535</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.4074665056016531</v>
+        <v>0.4128509495728032</v>
       </c>
       <c r="J19" s="3" t="n">
-        <v>0.01994134268344938</v>
-      </c>
-      <c r="K19" s="5" t="n">
-        <v>-0.0007388608692859844</v>
+        <v>0.02384325934837994</v>
+      </c>
+      <c r="K19" s="3" t="n">
+        <v>0.003083941019627945</v>
       </c>
       <c r="L19" s="3" t="n">
-        <v>0.003192827426065081</v>
+        <v>0.007030670493759494</v>
       </c>
     </row>
     <row r="20" ht="21" customHeight="1">
@@ -1484,25 +1481,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.6988902761882037</v>
+        <v>0.7050811834036075</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.4284137076652863</v>
+        <v>0.43361890634831</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4186919209089364</v>
+        <v>0.4186917551982716</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.3624794040134809</v>
+        <v>0.3674444950892</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.03617584706242583</v>
+        <v>0.03995183621570808</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.006852641234554424</v>
+        <v>0.01052177197431603</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.003387643168252907</v>
+        <v>0.007044146905414772</v>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1530,25 +1527,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.6673421875438417</v>
+        <v>0.6690114772360265</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4317614525070901</v>
+        <v>0.4331948862990211</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.414560247003918</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1548165787934046</v>
+        <v>0.1559727442318763</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.06939085825416558</v>
+        <v>0.07046149819234748</v>
       </c>
       <c r="K21" s="3" t="n">
-        <v>0.01216010808984969</v>
+        <v>0.01317345043067042</v>
       </c>
       <c r="L21" s="5" t="n">
-        <v>-0.001388580315485499</v>
+        <v>-0.0003888024883358376</v>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1572,25 +1569,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.786297437949475</v>
+        <v>1.763199180820205</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.6813908738240149</v>
+        <v>0.6674520561524815</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0.3982481437733469</v>
       </c>
       <c r="I22" s="5" t="n">
-        <v>-0.009601096804952469</v>
+        <v>-0.0178115551514556</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.2646074070705531</v>
+        <v>0.25412374598517</v>
       </c>
       <c r="K22" s="3" t="n">
-        <v>0.2024981984146048</v>
+        <v>0.1925294258947874</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.01223362273086026</v>
+        <v>-0.02042225730071023</v>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1618,25 +1615,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6664952525521191</v>
+        <v>0.669553783211627</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3973743592104992</v>
+        <v>0.3999387636385074</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3812608589121027</v>
+        <v>0.3812606549397253</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.3503962062189596</v>
+        <v>0.3528745980372852</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.04997535511647522</v>
+        <v>0.05190238239749112</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>0.01166579085654229</v>
+        <v>0.01352250832019619</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>0.001074635144035607</v>
+        <v>0.002911914583838771</v>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1664,25 +1661,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6424863340248785</v>
+        <v>0.6565618098588615</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.310753131277048</v>
+        <v>0.3219858657217809</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.3786844300618613</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.08854311700028261</v>
+        <v>0.09787158280603903</v>
       </c>
       <c r="J24" s="5" t="n">
-        <v>-0.2016615083889884</v>
+        <v>-0.1948200032578596</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.04927255092143545</v>
-      </c>
-      <c r="L24" s="5" t="n">
-        <v>-0.002442499491146055</v>
+        <v>-0.04112512124151302</v>
+      </c>
+      <c r="L24" s="3" t="n">
+        <v>0.006106248727864694</v>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1710,25 +1707,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5535341377454481</v>
+        <v>0.5545609482485079</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.5127822821346839</v>
+        <v>0.5137823270846265</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.3784190999316743</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2650065229704768</v>
+        <v>0.2658427724426453</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.2574790974094436</v>
+        <v>0.258310370776321</v>
       </c>
       <c r="K25" s="3" t="n">
-        <v>0.09747629165155214</v>
+        <v>0.09820179302482246</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.009494410925588115</v>
+        <v>-0.00883962396520277</v>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1752,25 +1749,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.6592349047465613</v>
+        <v>0.6640373456185977</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3929662823116364</v>
+        <v>0.3969983121244756</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3777602329182244</v>
+        <v>0.377760354004183</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3483510601195896</v>
+        <v>0.3522537144371283</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>0.05017296048089692</v>
+        <v>0.05321266058152796</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>0.01103678929765883</v>
+        <v>0.01396321070234108</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.0003309066843151243</v>
+        <v>0.003226340172071573</v>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1798,25 +1795,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5367027593953413</v>
+        <v>0.5455957151788788</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3592671137044743</v>
+        <v>0.3671332428347083</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3722462267693607</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.1481817589712728</v>
+        <v>0.1548263293356897</v>
       </c>
       <c r="J27" s="5" t="n">
-        <v>-0.1033360294096312</v>
+        <v>-0.09814700180204816</v>
       </c>
       <c r="K27" s="5" t="n">
-        <v>-0.009458297506448776</v>
+        <v>-0.003725995987388986</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>0.002029573789504191</v>
+        <v>0.007828356045230356</v>
       </c>
     </row>
     <row r="28" ht="21" customHeight="1">
@@ -1844,25 +1841,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6629918516151567</v>
+        <v>0.6675996159510886</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3831017227159095</v>
+        <v>0.3869345103189425</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3720417271500722</v>
+        <v>0.3720418417781526</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.3421339094751219</v>
+        <v>0.3458530565264364</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.04739612967554541</v>
+        <v>0.05029853769887338</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.008060976096412542</v>
+        <v>0.01085438365457514</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.0002771838124653314</v>
+        <v>0.003049021937118868</v>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1890,25 +1887,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.089056771720362</v>
+        <v>1.083085891569514</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4637103308613706</v>
+        <v>0.4595270321590497</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3577709735251533</v>
+        <v>0.3577711009842448</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.08148859401462127</v>
+        <v>0.07839751281140894</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.003721643983059408</v>
+        <v>0.0008529035749034186</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>0.07802446760308102</v>
+        <v>0.07494336202990493</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.00489947626288223</v>
+        <v>0.002027369488089237</v>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1936,25 +1933,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5847095157911364</v>
+        <v>0.5836572413313341</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4834255476820128</v>
+        <v>0.4824404283365684</v>
       </c>
       <c r="H30" s="3" t="n">
         <v>0.3473148914530824</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1462228373304388</v>
+        <v>0.1454616489492566</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.1204341920786254</v>
+        <v>0.119690129527162</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.1010236412381182</v>
+        <v>0.1002924689251767</v>
       </c>
       <c r="L30" s="5" t="n">
-        <v>-0.008014931927975422</v>
+        <v>-0.00867369345630209</v>
       </c>
     </row>
     <row r="31" ht="21" customHeight="1">
@@ -1978,25 +1975,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5676937330898295</v>
+        <v>0.5662267707694086</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.4844621796137114</v>
+        <v>0.4830731008430185</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.3464803550582258</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.1490964107367685</v>
+        <v>0.1480211489675201</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.119861620965148</v>
+        <v>0.1188137155182061</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1024759284731775</v>
+        <v>0.1014442916093536</v>
       </c>
       <c r="L31" s="5" t="n">
-        <v>-0.007737542556484067</v>
+        <v>-0.008666047663262177</v>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2020,25 +2017,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5067651832101063</v>
+        <v>0.5077104562234127</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.4836989786604764</v>
+        <v>0.4846297810310287</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3431478207070686</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.158851326790258</v>
+        <v>0.1595783351508542</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.09066028053369823</v>
+        <v>0.09134450906602809</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.1046431046431047</v>
+        <v>0.1053361053361053</v>
       </c>
       <c r="L32" s="5" t="n">
-        <v>-0.002503128911139019</v>
+        <v>-0.001877346683354264</v>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2066,25 +2063,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.426363459628599</v>
+        <v>0.4279585479905097</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2791667238264712</v>
+        <v>0.2805972035126587</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.3203327503512046</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1180883578771881</v>
+        <v>0.1193387051958876</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.03478052290717193</v>
+        <v>-0.03370112736867359</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.03117852413627054</v>
+        <v>-0.03009510051763575</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.008900589193932662</v>
+        <v>0.0100288328945719</v>
       </c>
     </row>
     <row r="34" ht="21" customHeight="1">
@@ -2112,25 +2109,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5413525055230759</v>
+        <v>0.5446504306874409</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1762972173415152</v>
+        <v>0.1788140589983993</v>
       </c>
       <c r="H34" s="3" t="n">
         <v>0.3185919873131313</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.0957631804709943</v>
+        <v>-0.09382844759776487</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.07387072401212003</v>
+        <v>-0.0718891493666115</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.1079141776536708</v>
+        <v>-0.1060054434272385</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>-0.006104044421691102</v>
+        <v>-0.003977474107037415</v>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2154,25 +2151,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5367146880431453</v>
+        <v>0.5426744133949961</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1781071820521309</v>
+        <v>0.1826760187692307</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.317783047403464</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>-0.01853133678655916</v>
+        <v>-0.01472508712312759</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1537079002891303</v>
+        <v>-0.1504258810658748</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1059930658741952</v>
+        <v>-0.1025260029717682</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0.006131549609810438</v>
+        <v>0.01003344481605351</v>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2200,25 +2197,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.6217428158809204</v>
+        <v>0.6189414385293674</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.4781003148637655</v>
+        <v>0.4755470636917334</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.2924866917817843</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.1743611232809001</v>
+        <v>0.1723325472199564</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.1565536887490468</v>
+        <v>0.1545558730178536</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.1436096976953007</v>
+        <v>0.1416342412451361</v>
       </c>
       <c r="L36" s="5" t="n">
-        <v>-0.006707221962252485</v>
+        <v>-0.008423022929340274</v>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2246,25 +2243,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.7036815242449548</v>
+        <v>0.7053554928268708</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2730670120181828</v>
+        <v>0.2743178761911313</v>
       </c>
       <c r="H37" s="3" t="n">
         <v>0.2842205508936391</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.02889637742207229</v>
+        <v>0.02990732940185348</v>
       </c>
       <c r="J37" s="5" t="n">
-        <v>-0.05763888888888891</v>
+        <v>-0.05671296296296291</v>
       </c>
       <c r="K37" s="5" t="n">
-        <v>-0.008685064935065046</v>
+        <v>-0.007711038961038974</v>
       </c>
       <c r="L37" s="5" t="n">
-        <v>-0.005537008386939268</v>
+        <v>-0.004559889259832306</v>
       </c>
     </row>
     <row r="38" ht="21" customHeight="1">
@@ -2288,25 +2285,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.5519117122026806</v>
+        <v>0.5589922376025815</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2809427427823317</v>
+        <v>0.2867870870193954</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.2814584202150137</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.2659930631811915</v>
+        <v>0.2717691990035427</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.03457660913427252</v>
-      </c>
-      <c r="K38" s="5" t="n">
-        <v>-0.0004024144869215762</v>
+        <v>0.03929689962146599</v>
+      </c>
+      <c r="K38" s="3" t="n">
+        <v>0.004158283031522547</v>
       </c>
       <c r="L38" s="3" t="n">
-        <v>0.0110575944644189</v>
+        <v>0.01567057865816435</v>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2334,25 +2331,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5458657261103335</v>
+        <v>0.5455962817152487</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.3339318158434581</v>
+        <v>0.333699585374126</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.275338593485343</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2711143301186443</v>
+        <v>0.2708930358411168</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.1602873083538494</v>
+        <v>0.1600853084742613</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.04594326766038437</v>
+        <v>0.04576117447311745</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>-0.007087294727744275</v>
+        <v>-0.007260155574762339</v>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2376,25 +2373,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4288135609894888</v>
+        <v>0.4337934514140818</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2678492377798629</v>
+        <v>0.2722682033671824</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2678492377798629</v>
+        <v>0.2678493268287148</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1844470618776937</v>
+        <v>0.1885752537866485</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.04034589296088087</v>
-      </c>
-      <c r="K40" s="18" t="n">
-        <v>0</v>
+        <v>0.04397184437404666</v>
+      </c>
+      <c r="K40" s="3" t="n">
+        <v>0.003485332558814891</v>
       </c>
       <c r="L40" s="3" t="n">
-        <v>0.006430868167202508</v>
+        <v>0.009938614440222038</v>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2422,25 +2419,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4428562965026259</v>
+        <v>0.4508514368114691</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2465679380083741</v>
+        <v>0.2534754983218976</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.2670850367967565</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.2580214189073216</v>
+        <v>0.2649924459663764</v>
       </c>
       <c r="J41" s="5" t="n">
-        <v>-0.009642166990625811</v>
+        <v>-0.004154334153843142</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.01619236135899016</v>
+        <v>-0.01074082486939032</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.01255761138200517</v>
+        <v>0.01816845902077358</v>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2464,25 +2461,25 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.484539837070888</v>
+        <v>0.4906183303287333</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.137582581834732</v>
+        <v>0.1422403598761612</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2656739046368983</v>
+        <v>0.2656738068589226</v>
       </c>
       <c r="I42" s="5" t="n">
-        <v>-0.07104184044994366</v>
+        <v>-0.06723819317242319</v>
       </c>
       <c r="J42" s="5" t="n">
-        <v>-0.02005787142907456</v>
+        <v>-0.01604546874855806</v>
       </c>
       <c r="K42" s="5" t="n">
-        <v>-0.1012040481619265</v>
+        <v>-0.09752390095603825</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>-0.0057084697760863</v>
+        <v>-0.001637313036551791</v>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2506,25 +2503,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3431889959225038</v>
+        <v>0.3443246450418633</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2679788875721685</v>
+        <v>0.2690509475067042</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.2655667527194627</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.1283167109954428</v>
+        <v>0.129270688345682</v>
       </c>
       <c r="J43" s="3" t="n">
-        <v>0.0671368274558215</v>
+        <v>0.06803907799689601</v>
       </c>
       <c r="K43" s="3" t="n">
-        <v>0.001905972045743498</v>
+        <v>0.002753070732740337</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.002542911633820921</v>
+        <v>0.003390548845094488</v>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2548,25 +2545,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.461468824520616</v>
+        <v>0.4632542486309303</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2917554689615038</v>
+        <v>0.2933336468535885</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2645772284716119</v>
+        <v>0.2645773130569522</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.1363940172934253</v>
+        <v>0.1377823091565502</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.07066323002809183</v>
+        <v>0.071971220943017</v>
       </c>
       <c r="K44" s="3" t="n">
-        <v>0.02149195784803104</v>
+        <v>0.02273987798114252</v>
       </c>
       <c r="L44" s="3" t="n">
-        <v>0.003131808278867165</v>
+        <v>0.004357298474945592</v>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2590,25 +2587,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3916163482686827</v>
+        <v>0.3920427187433075</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2812917832480903</v>
+        <v>0.2816843601883992</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2636215012235226</v>
+        <v>0.2636214065828029</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.164963514025785</v>
+        <v>0.1653206156032558</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.06554198069974171</v>
+        <v>0.06586853355928812</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.01398384089496596</v>
+        <v>0.01429459291485391</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-0.004879536444037713</v>
+        <v>-0.004574565416285425</v>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2632,25 +2629,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4236721301174848</v>
+        <v>0.425998814187043</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.191047936774972</v>
+        <v>0.1929944469313138</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.2619874180283208</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.06953416810735757</v>
+        <v>0.07128209029965205</v>
       </c>
       <c r="J46" s="5" t="n">
-        <v>-0.02670128852955678</v>
+        <v>-0.02511064236953608</v>
       </c>
       <c r="K46" s="5" t="n">
-        <v>-0.05621251071122535</v>
+        <v>-0.05467009425878333</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.006948253794112347</v>
+        <v>0.008593892850612628</v>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2674,25 +2671,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3139426827522573</v>
+        <v>0.3105532265789543</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.3062944800440746</v>
+        <v>0.3029248468195411</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.2617404407419122</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1392658430438523</v>
+        <v>0.1363270661486402</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.08878856628014486</v>
+        <v>0.0859799973215547</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.03531157270029661</v>
+        <v>0.03264094955489605</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.005416191562143569</v>
+        <v>-0.007981755986317007</v>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2720,25 +2717,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4101323825735688</v>
+        <v>0.4141402494669566</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2238222598219421</v>
+        <v>0.2273005975859326</v>
       </c>
       <c r="H48" s="3" t="n">
         <v>0.2492433825456852</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1768955354357569</v>
+        <v>0.1802404984418828</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.02907116251624564</v>
+        <v>0.03199598028098749</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.020349215436259</v>
-      </c>
-      <c r="L48" s="5" t="n">
-        <v>-0.001670644391408072</v>
+        <v>-0.01756485987145129</v>
+      </c>
+      <c r="L48" s="3" t="n">
+        <v>0.001166799257491302</v>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2762,25 +2759,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.440709553590787</v>
+        <v>0.4444172082838467</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.2534184797158363</v>
+        <v>0.256644154465927</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2489618429487046</v>
+        <v>0.2489617620601334</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1987567510638908</v>
+        <v>0.2018418315921782</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.01825989643021653</v>
+        <v>0.02088045625307022</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.003568272955889462</v>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v>-0.0006767960475110302</v>
+        <v>0.006151022904913983</v>
+      </c>
+      <c r="L49" s="3" t="n">
+        <v>0.001895028933031062</v>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
@@ -2804,25 +2801,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4394535020984527</v>
+        <v>0.4428249635689041</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.25295022983654</v>
+        <v>0.2558848667790528</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2483561255753448</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1987889940749692</v>
+        <v>0.2015967755690107</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.01844987203479853</v>
+        <v>0.02083526655997492</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.00368012313720012</v>
-      </c>
-      <c r="L50" s="5" t="n">
-        <v>-0.0005434252511600235</v>
+        <v>0.006030924228643375</v>
+      </c>
+      <c r="L50" s="3" t="n">
+        <v>0.001797483523067855</v>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2850,25 +2847,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4249063046658954</v>
+        <v>0.4270661699188298</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.124620385237421</v>
+        <v>0.1263249615315105</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.240744105364707</v>
+        <v>0.2407439762699701</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>-0.08661799300745876</v>
+        <v>-0.08523349351222964</v>
       </c>
       <c r="J51" s="5" t="n">
-        <v>-0.03191764425600208</v>
+        <v>-0.0304502302686378</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.09359199824137177</v>
+        <v>-0.09221806990547377</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>-0.003865434559400804</v>
+        <v>-0.002355499184634846</v>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2892,25 +2889,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3311002143863992</v>
+        <v>0.3344500799148888</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.1689429113323648</v>
+        <v>0.1718847060957682</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2353365686539364</v>
+        <v>0.2353364426214075</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.03420385277257387</v>
+        <v>0.03680666519160902</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.006201293172200639</v>
+        <v>0.008733630694340855</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.05374539943710743</v>
+        <v>-0.05136393158692343</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.001546746104491348</v>
+        <v>0.004067369385884589</v>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
@@ -2938,25 +2935,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.2117405920470938</v>
+        <v>0.2103109042181897</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2811388429504595</v>
+        <v>0.2796271277588027</v>
       </c>
       <c r="H53" s="3" t="n">
         <v>0.2293427066468481</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1495624780192868</v>
+        <v>0.1482060199965338</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.1373403847558998</v>
+        <v>0.1359983485299427</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.04213319526244264</v>
+        <v>0.04090350139149579</v>
       </c>
       <c r="L53" s="5" t="n">
-        <v>-0.008497536945812789</v>
+        <v>-0.009667487684729026</v>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2980,25 +2977,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4392215821759962</v>
+        <v>0.4408768111376706</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2276478360959751</v>
+        <v>0.2290597370000531</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.221764915662316</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.1865625853834223</v>
+        <v>0.1879271316382964</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.03144856812805696</v>
+        <v>0.03263482295051578</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.004815100154083263</v>
+        <v>0.005970724191063148</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.004009163802978222</v>
+        <v>-0.002863688430698841</v>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3026,25 +3023,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3185252139867498</v>
+        <v>0.3210083123181748</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1634014969061208</v>
+        <v>0.1655925945476298</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2045764963095777</v>
+        <v>0.2045766351741902</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.07239882168412493</v>
+        <v>0.07441840515245657</v>
       </c>
       <c r="J55" s="5" t="n">
-        <v>-0.06326685295239665</v>
+        <v>-0.06150276039675151</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.03418213748118404</v>
+        <v>-0.03236327145007523</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.008051846032993026</v>
+        <v>0.009950248756219082</v>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3068,25 +3065,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3166628869288146</v>
+        <v>0.3191541177750707</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.192207425296719</v>
+        <v>0.1944635763351985</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2035901041379315</v>
+        <v>0.2035902296914684</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.142499918397532</v>
+        <v>0.1446617683774252</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.02051061475045102</v>
+        <v>0.02244173753769618</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.009457271875266349</v>
-      </c>
-      <c r="L56" s="5" t="n">
-        <v>-0.001774470520892968</v>
+        <v>-0.007582857629717998</v>
+      </c>
+      <c r="L56" s="3" t="n">
+        <v>0.000114481969089919</v>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3110,25 +3107,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.3315232979297777</v>
+        <v>0.3296585139524517</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2682510359309964</v>
+        <v>0.2664747739759108</v>
       </c>
       <c r="H57" s="3" t="n">
         <v>0.2029491727456918</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1331120635498926</v>
+        <v>0.1315250033629372</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.1238996243963972</v>
+        <v>0.1223255352865984</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.05428480659432622</v>
+        <v>0.05280821722934803</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.01149107019244078</v>
+        <v>-0.01287553648068684</v>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3152,25 +3149,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3422732691888335</v>
+        <v>0.3442858721527491</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.1989799757892141</v>
+        <v>0.2007777249572409</v>
       </c>
       <c r="H58" s="3" t="n">
         <v>0.1980471814095774</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1500844752745718</v>
+        <v>0.151808910586533</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.04573558718382476</v>
+        <v>0.04730356189549445</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.0007785956964894147</v>
+        <v>0.002279161947904784</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.005304479963980202</v>
+        <v>-0.003813034669068016</v>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3194,25 +3191,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3430624196466703</v>
+        <v>0.3447651274156656</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1992768822369084</v>
+        <v>0.2007974289088261</v>
       </c>
       <c r="H59" s="3" t="n">
         <v>0.1980201038652212</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1505467449485591</v>
+        <v>0.1520055073493269</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.04603263596261997</v>
+        <v>0.04735888636141317</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.001049046145079169</v>
+        <v>0.002318262468755217</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.005391633317462952</v>
+        <v>-0.004130583042734171</v>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3236,25 +3233,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3745475220139527</v>
+        <v>0.3756669252199267</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2260851975028828</v>
+        <v>0.2270838008564444</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.1975251415910222</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1283818647924673</v>
+        <v>0.1293008922112591</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.0591583832069964</v>
+        <v>0.06002103053001884</v>
       </c>
       <c r="K60" s="3" t="n">
-        <v>0.02384923282188134</v>
+        <v>0.02468312208138745</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.006558452205279508</v>
+        <v>0.007378258730939447</v>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
@@ -3278,25 +3275,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3419368872659836</v>
+        <v>0.3435590842611607</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1982123290349127</v>
+        <v>0.1996610267455765</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1971219972480989</v>
+        <v>0.1971221110577652</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1501651692754191</v>
+        <v>0.1515557712139433</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.04568066814756855</v>
+        <v>0.0469448480365231</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.0009107942125534674</v>
+        <v>0.00212084938066015</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.005057102577699535</v>
+        <v>-0.00385426232264563</v>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3320,25 +3317,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.5133224578575311</v>
+        <v>0.5115098785571868</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.247795546256165</v>
+        <v>0.2463010013450906</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.1936930204752654</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>-0.139100845535162</v>
+        <v>-0.14013198597649</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.02794878108840182</v>
+        <v>0.0267175572519085</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.04532365093276569</v>
+        <v>0.04407161637661194</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.007253269916765781</v>
+        <v>-0.008442330558858457</v>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
@@ -3362,25 +3359,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.5099028261998368</v>
+        <v>0.5086788813886209</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2461354801187672</v>
+        <v>0.2451253481894149</v>
       </c>
       <c r="H63" s="3" t="n">
         <v>0.1927821482139032</v>
       </c>
       <c r="I63" s="5" t="n">
-        <v>-0.1402504698950391</v>
+        <v>-0.1409473928744905</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.02740763173834049</v>
+        <v>0.02657480314960625</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.04473015628608823</v>
+        <v>0.04388328585726375</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.007605675003656609</v>
+        <v>-0.00841012139827424</v>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3408,25 +3405,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3607382819576714</v>
+        <v>0.3622354311501259</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1943592538058279</v>
+        <v>0.1956732147943772</v>
       </c>
       <c r="H64" s="3" t="n">
         <v>0.1925134514647706</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1594488706249306</v>
+        <v>0.1607244253454756</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.04839230852379606</v>
+        <v>0.0495456856083758</v>
       </c>
       <c r="K64" s="3" t="n">
-        <v>0.001547825174458284</v>
+        <v>0.002649666824072527</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>-0.006635095753538711</v>
+        <v>-0.005542256452955807</v>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
@@ -3450,25 +3447,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2698055104862489</v>
+        <v>0.2689364881725527</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1836399122450112</v>
+        <v>0.1828297548786559</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.1805613142528613</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1150167395669519</v>
+        <v>0.1142535522024297</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.05855130599164915</v>
+        <v>0.05782676711006696</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.002607740872906827</v>
+        <v>0.001921493274773534</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.004089979550102263</v>
+        <v>-0.004771642808452659</v>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3496,25 +3493,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.1772804058209561</v>
+        <v>0.1716900428331198</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.2279230800284739</v>
+        <v>0.2220921249669161</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.1732895662995309</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1234150527764064</v>
+        <v>0.1180803678969065</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.06147326920900165</v>
+        <v>0.05643272307669922</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.04656439066551421</v>
-      </c>
-      <c r="L66" s="3" t="n">
-        <v>0.0007231404958678578</v>
+        <v>0.04159464131374246</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>-0.0040289256198347</v>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3531,7 +3528,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D67" s="19" t="inlineStr">
+      <c r="D67" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -3542,25 +3539,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3202535065382257</v>
+        <v>0.3200632269889565</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1523656271346989</v>
+        <v>0.1521993874626801</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1656589580893892</v>
+        <v>0.1656588842011395</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1776617017729802</v>
+        <v>0.1774918875405691</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.08737418294370913</v>
+        <v>0.08721738781999711</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.01140413399857465</v>
+        <v>-0.01154668567355666</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0.003472724641875091</v>
+        <v>0.003328027781797083</v>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
@@ -3584,25 +3581,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3592321021155722</v>
+        <v>0.3616466367701576</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1649628950398367</v>
+        <v>0.1670323306255632</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.1641868566951896</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.17026780131286</v>
+        <v>0.1723466605135937</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.03075101430188432</v>
+        <v>0.03258203642121704</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.0006665926008220247</v>
+        <v>0.002444172869681127</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.006617403771920216</v>
+        <v>-0.004852762766074714</v>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3626,25 +3623,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3314616553231298</v>
+        <v>0.3329623165294675</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.155963832276786</v>
+        <v>0.157266693738918</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1536838247180545</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1650899420952627</v>
+        <v>0.1664030893954545</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.0526394433287134</v>
+        <v>0.0538258501400164</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.001976284584980226</v>
+        <v>0.003105590062111752</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.009765625</v>
+        <v>-0.008649553571428603</v>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3668,25 +3665,25 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.3352686869732637</v>
+        <v>0.3382947916462911</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1459827787289874</v>
+        <v>0.14858002063956</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1515666041664203</v>
+        <v>0.151566718262478</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1584226374772855</v>
+        <v>0.1610479579021633</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.0281376752653606</v>
+        <v>0.03046773231978617</v>
       </c>
       <c r="K70" s="5" t="n">
-        <v>-0.004848894903022205</v>
+        <v>-0.002593594948128164</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.007088208820882014</v>
+        <v>-0.004837983798379741</v>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3703,7 +3700,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D71" s="19" t="inlineStr">
+      <c r="D71" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -3714,25 +3711,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1253912963291841</v>
+        <v>0.1183230276739218</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1190881397173811</v>
+        <v>0.1120594594296969</v>
       </c>
       <c r="H71" s="3" t="n">
         <v>0.1420841480499133</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1117811380682443</v>
+        <v>0.1047984789697887</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.09960290763871948</v>
+        <v>0.09269660865573459</v>
       </c>
       <c r="K71" s="5" t="n">
-        <v>-0.02013512609539114</v>
+        <v>-0.02628938390527802</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.009400148779333262</v>
+        <v>-0.01562182998579831</v>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3760,25 +3757,25 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2487499709265686</v>
+        <v>0.2480499037549337</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1109816751847064</v>
+        <v>0.1103589276089303</v>
       </c>
       <c r="H72" s="3" t="n">
         <v>0.1404287391249801</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.123187348335245</v>
+        <v>0.1225577590144293</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.04922024947003689</v>
+        <v>0.04863212152750895</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.02582104688353226</v>
+        <v>-0.02636711131913561</v>
       </c>
       <c r="L72" s="5" t="n">
-        <v>-0.01014584654407102</v>
+        <v>-0.01070069752694991</v>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3802,25 +3799,25 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2820486625989802</v>
+        <v>0.2816548883262431</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1213315359963414</v>
+        <v>0.1209870409007974</v>
       </c>
       <c r="H73" s="3" t="n">
         <v>0.1375228054869186</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>-0.01615220170279763</v>
+        <v>-0.01645445909090726</v>
       </c>
       <c r="J73" s="5" t="n">
-        <v>-0.002475316482360213</v>
+        <v>-0.002781775678525333</v>
       </c>
       <c r="K73" s="5" t="n">
-        <v>-0.01423379769836486</v>
+        <v>-0.01453664445790437</v>
       </c>
       <c r="L73" s="3" t="n">
-        <v>0.001384402399630558</v>
+        <v>0.001076757421935026</v>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3844,25 +3841,25 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.1326826920267135</v>
+        <v>0.1355254539420063</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.08369472000383649</v>
+        <v>0.08641465910040669</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1163324862504662</v>
+        <v>0.1163326149421147</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>-0.005876040419308226</v>
+        <v>-0.00338102769308779</v>
       </c>
       <c r="J74" s="5" t="n">
-        <v>-0.05534663108739857</v>
+        <v>-0.05297577767964234</v>
       </c>
       <c r="K74" s="5" t="n">
-        <v>-0.02923659989171623</v>
+        <v>-0.0268002165674065</v>
       </c>
       <c r="L74" s="3" t="n">
-        <v>0.001396258028483643</v>
+        <v>0.00390952247975429</v>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3890,25 +3887,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.07610527173939152</v>
+        <v>0.08358221911117791</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1426796190573569</v>
+        <v>0.1506191353843189</v>
       </c>
       <c r="H75" s="3" t="n">
         <v>0.114585945900415</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1351777696881447</v>
+        <v>0.1430651619949037</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.1575105171987132</v>
+        <v>0.1655530809205643</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.02520547945205487</v>
+        <v>0.03232876712328769</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.007742893508697501</v>
+        <v>-0.0008485362749257597</v>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3932,25 +3929,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.2797456860955252</v>
+        <v>0.282167726665377</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1008787575861081</v>
+        <v>0.1029624215674034</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1039172211548733</v>
+        <v>0.1039173673869422</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1051156822348338</v>
+        <v>0.107207292510076</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.00499490182798934</v>
+        <v>0.006896950376516386</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.002752437873545066</v>
+        <v>-0.0008650519031141446</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.002046116313842661</v>
+        <v>-0.0001573935626032474</v>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3974,25 +3971,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2770760522540523</v>
+        <v>0.2794605910754389</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.09879529961592937</v>
+        <v>0.1008470299915947</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1016497767703139</v>
+        <v>0.1016498517459035</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1040259375366359</v>
+        <v>0.1060872839288154</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.004878005869520363</v>
+        <v>0.006754300246448297</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.002591093117408905</v>
+        <v>-0.0007287449392713308</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.002025439520375927</v>
+        <v>-0.0001620351616301585</v>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -4005,7 +4002,7 @@
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
-      <c r="D78" s="19" t="inlineStr">
+      <c r="D78" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4016,25 +4013,25 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2000255706377414</v>
+        <v>0.2023958124150707</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.09200891391601784</v>
+        <v>0.09416566425739115</v>
       </c>
       <c r="H78" s="3" t="n">
         <v>0.08908189559558255</v>
       </c>
       <c r="I78" s="3" t="n">
-        <v>0.1596484153093829</v>
+        <v>0.161938755693714</v>
       </c>
       <c r="J78" s="3" t="n">
-        <v>0.1140400476988872</v>
+        <v>0.1162403101899339</v>
       </c>
       <c r="K78" s="3" t="n">
-        <v>0.00268760166914217</v>
+        <v>0.004667939741141769</v>
       </c>
       <c r="L78" s="5" t="n">
-        <v>-0.009224963309804934</v>
+        <v>-0.007268152910755443</v>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4047,7 +4044,7 @@
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="19" t="inlineStr">
+      <c r="D79" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4058,25 +4055,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1805558516044821</v>
+        <v>0.1834073438369377</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.08878034935373735</v>
+        <v>0.09141033178882241</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.08596259482642443</v>
+        <v>0.08596267264564239</v>
       </c>
       <c r="I79" s="3" t="n">
-        <v>0.1560612028719079</v>
+        <v>0.1588535330622238</v>
       </c>
       <c r="J79" s="3" t="n">
-        <v>0.1121039032421285</v>
+        <v>0.1147901445543076</v>
       </c>
       <c r="K79" s="3" t="n">
-        <v>0.002594706798131785</v>
+        <v>0.005016433143054888</v>
       </c>
       <c r="L79" s="5" t="n">
-        <v>-0.01024590163934425</v>
+        <v>-0.007855191256830651</v>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4100,25 +4097,25 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.07244309503299284</v>
+        <v>0.06726952556642596</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.08317414701827608</v>
+        <v>0.07794880991652886</v>
       </c>
       <c r="H80" s="3" t="n">
         <v>0.08470351397488507</v>
       </c>
-      <c r="I80" s="3" t="n">
-        <v>0.003280723069199576</v>
+      <c r="I80" s="5" t="n">
+        <v>-0.001559200409543493</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.02564370424868589</v>
+        <v>0.02069589958058415</v>
       </c>
       <c r="K80" s="5" t="n">
-        <v>-0.001409940077546801</v>
+        <v>-0.006227235342497917</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.003166783954961394</v>
+        <v>-0.007975604034717421</v>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4135,7 +4132,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D81" s="20" t="inlineStr">
+      <c r="D81" s="19" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -4188,25 +4185,25 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1599218582813513</v>
+        <v>0.1588461018389289</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.05857355635906369</v>
+        <v>0.05759147812473575</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.06495642103098764</v>
+        <v>0.06495632128716444</v>
       </c>
       <c r="I82" s="5" t="n">
-        <v>-0.06506767502633337</v>
+        <v>-0.06593495918679138</v>
       </c>
       <c r="J82" s="5" t="n">
-        <v>-0.02152555767430131</v>
+        <v>-0.02243323340929726</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.005993545412632639</v>
+        <v>-0.006915629322268413</v>
       </c>
       <c r="L82" s="3" t="n">
-        <v>0.002091564025098691</v>
+        <v>0.001161980013943742</v>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4234,25 +4231,25 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1239780215907751</v>
+        <v>0.1234111050972515</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1250226690575149</v>
+        <v>0.1244551445901914</v>
       </c>
       <c r="H83" s="3" t="n">
         <v>0.06155451612850937</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1481332603527756</v>
+        <v>0.1475540776083568</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.1104135157797737</v>
+        <v>0.1098533609878889</v>
       </c>
       <c r="K83" s="3" t="n">
-        <v>0.05978793548961958</v>
+        <v>0.05925331907689557</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.007261497370837144</v>
+        <v>-0.007762290292963936</v>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
@@ -4269,7 +4266,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D84" s="20" t="inlineStr">
+      <c r="D84" s="19" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -4280,25 +4277,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.01746092723472836</v>
+        <v>0.01891236935631846</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05292796186310111</v>
+        <v>0.05442999889856925</v>
       </c>
       <c r="H84" s="3" t="n">
         <v>0.05856060074610636</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.02074990899162721</v>
+        <v>0.02220604295595185</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.0007137758743753775</v>
+        <v>0.002141327623126354</v>
       </c>
       <c r="K84" s="5" t="n">
-        <v>-0.005321035828308007</v>
+        <v>-0.003902092940759272</v>
       </c>
       <c r="L84" s="3" t="n">
-        <v>0.001071046054980318</v>
+        <v>0.002499107461620742</v>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4326,25 +4323,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1824855688672167</v>
+        <v>0.1850516411129475</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.042856122991628</v>
+        <v>0.04511907901795675</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.05156022711301511</v>
+        <v>0.05156011538341487</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.105912603627867</v>
+        <v>0.1083125074517182</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.02178829722605169</v>
+        <v>0.02400564571600916</v>
       </c>
       <c r="K85" s="5" t="n">
-        <v>-0.008277323444690898</v>
-      </c>
-      <c r="L85" s="5" t="n">
-        <v>-0.001067200266800183</v>
+        <v>-0.006125219349071176</v>
+      </c>
+      <c r="L85" s="3" t="n">
+        <v>0.001100550275137557</v>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4361,7 +4358,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D86" s="21" t="inlineStr">
+      <c r="D86" s="20" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -4372,25 +4369,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.2383414202919318</v>
+        <v>0.243166914133915</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.01127996330849612</v>
+        <v>0.01522076775004222</v>
       </c>
       <c r="H86" s="3" t="n">
         <v>0.04141552668502424</v>
       </c>
       <c r="I86" s="3" t="n">
-        <v>0.0554301348445041</v>
+        <v>0.05954298579977202</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.05819017777857827</v>
+        <v>0.06231378420201339</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.02893711741791871</v>
+        <v>-0.02515303283249848</v>
       </c>
       <c r="L86" s="3" t="n">
-        <v>0.005995618586417617</v>
+        <v>0.009915830739075204</v>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4407,7 +4404,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="20" t="inlineStr">
+      <c r="D87" s="19" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
@@ -4449,7 +4446,7 @@
         </is>
       </c>
       <c r="C88" s="13" t="inlineStr"/>
-      <c r="D88" s="19" t="inlineStr">
+      <c r="D88" s="18" t="inlineStr">
         <is>
           <t>Financials &amp; Credit</t>
         </is>
@@ -4460,25 +4457,25 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.08613066742278419</v>
+        <v>0.08599359141460416</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.0390806873503895</v>
+        <v>0.03894933654575516</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.03720267448056069</v>
+        <v>0.0372025706220056</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0.02383666220920144</v>
+        <v>0.02370734091802928</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0.01172286454097327</v>
+        <v>0.011595073349292</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0.00181065178102191</v>
+        <v>0.001684112605604193</v>
       </c>
       <c r="L88" s="5" t="n">
-        <v>-0.000504986744097824</v>
+        <v>-0.000631233430122391</v>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4495,7 +4492,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="21" t="inlineStr">
+      <c r="D89" s="20" t="inlineStr">
         <is>
           <t>Consumer</t>
         </is>
@@ -4506,25 +4503,25 @@
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.1175965830639425</v>
+        <v>0.1207504478549839</v>
       </c>
       <c r="G89" s="5" t="n">
-        <v>-0.006528894497549231</v>
+        <v>-0.003725312607587683</v>
       </c>
       <c r="H89" s="3" t="n">
         <v>0.02209850590178353</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.03174708514198388</v>
+        <v>0.03465868209422918</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.008924921319508394</v>
+        <v>0.01177211397773026</v>
       </c>
       <c r="K89" s="5" t="n">
-        <v>-0.02800845538275709</v>
+        <v>-0.0252654889526398</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.01224938625204586</v>
+        <v>-0.009461947626841383</v>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
@@ -4537,7 +4534,7 @@
         </is>
       </c>
       <c r="C90" s="13" t="inlineStr"/>
-      <c r="D90" s="22" t="inlineStr">
+      <c r="D90" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4548,25 +4545,25 @@
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04863283880769376</v>
+        <v>0.04850417915220362</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.02278170927684453</v>
+        <v>0.02265642412273938</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.02098231128860872</v>
+        <v>0.02098221377412379</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.005341768918599055</v>
+        <v>0.005218810442326527</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.007020594260636726</v>
+        <v>0.006897335925965864</v>
       </c>
       <c r="K90" s="3" t="n">
-        <v>0.00176241837722424</v>
+        <v>0.001639803638132653</v>
       </c>
       <c r="L90" s="5" t="n">
-        <v>-0.0001223840411209709</v>
+        <v>-0.0002447680822420528</v>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
@@ -4594,25 +4591,25 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.04356791223784717</v>
+        <v>0.04386089868234411</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.007689848700252133</v>
+        <v>0.007972464616699426</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.007030242477987114</v>
+        <v>0.007030170081206544</v>
       </c>
       <c r="I91" s="5" t="n">
-        <v>-0.007474740422097947</v>
+        <v>-0.007196235880658097</v>
       </c>
       <c r="J91" s="5" t="n">
-        <v>-0.004335266319744013</v>
+        <v>-0.004055951357985865</v>
       </c>
       <c r="K91" s="3" t="n">
-        <v>0.00065500140357444</v>
+        <v>0.0009357162908205652</v>
       </c>
       <c r="L91" s="5" t="n">
-        <v>-0.0005607476635514086</v>
+        <v>-0.0002803738317757043</v>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4625,7 +4622,7 @@
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
-      <c r="D92" s="22" t="inlineStr">
+      <c r="D92" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4636,25 +4633,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.03466071669762094</v>
+        <v>0.03410040564887895</v>
       </c>
       <c r="G92" s="5" t="n">
-        <v>-0.003697954794328662</v>
+        <v>-0.004237417365766438</v>
       </c>
       <c r="H92" s="5" t="n">
-        <v>-0.0002735691732980161</v>
+        <v>-0.0002733221818355114</v>
       </c>
       <c r="I92" s="5" t="n">
-        <v>-0.02342245103581309</v>
+        <v>-0.02395147462680114</v>
       </c>
       <c r="J92" s="5" t="n">
-        <v>-0.003884935687042956</v>
+        <v>-0.00442454298082029</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.003425322683725418</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>0.0002167316861725332</v>
+        <v>-0.003965178955294357</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>-0.0003250975292587999</v>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4678,25 +4675,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.1243533706791935</v>
+        <v>0.1238706429350735</v>
       </c>
       <c r="G93" s="5" t="n">
-        <v>-0.01776119195894699</v>
+        <v>-0.01818290450622762</v>
       </c>
       <c r="H93" s="5" t="n">
         <v>-0.01136521832519133</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.04735493299617977</v>
+        <v>0.04690526361528691</v>
       </c>
       <c r="J93" s="3" t="n">
-        <v>0.00489097350969292</v>
+        <v>0.004459535524643954</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.006469500924214389</v>
+        <v>-0.006896061424712108</v>
       </c>
       <c r="L93" s="5" t="n">
-        <v>-0.0004291538516558724</v>
+        <v>-0.0008583077033116338</v>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
@@ -4709,7 +4706,7 @@
         </is>
       </c>
       <c r="C94" s="13" t="inlineStr"/>
-      <c r="D94" s="22" t="inlineStr">
+      <c r="D94" s="21" t="inlineStr">
         <is>
           <t>Rates &amp; Duration</t>
         </is>
@@ -4720,25 +4717,25 @@
         </is>
       </c>
       <c r="F94" s="5" t="n">
-        <v>-0.03010263754388598</v>
+        <v>-0.03069234351705008</v>
       </c>
       <c r="G94" s="5" t="n">
-        <v>-0.01377009108777316</v>
+        <v>-0.01436964022052767</v>
       </c>
       <c r="H94" s="5" t="n">
-        <v>-0.01442952538653286</v>
+        <v>-0.01442961553683053</v>
       </c>
       <c r="I94" s="5" t="n">
-        <v>-0.04832829986775411</v>
+        <v>-0.04890675336892869</v>
       </c>
       <c r="J94" s="5" t="n">
-        <v>-0.02170167110052468</v>
+        <v>-0.02229630903445345</v>
       </c>
       <c r="K94" s="3" t="n">
-        <v>0.0006690889345262185</v>
+        <v>6.08534075783318e-05</v>
       </c>
       <c r="L94" s="3" t="n">
-        <v>0.002315096868527045</v>
+        <v>0.001705860850493401</v>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4812,25 +4809,25 @@
         </is>
       </c>
       <c r="F96" s="5" t="n">
-        <v>-0.08123147691078825</v>
+        <v>-0.07926140795289716</v>
       </c>
       <c r="G96" s="5" t="n">
-        <v>-0.1321285229291973</v>
+        <v>-0.1302675899374276</v>
       </c>
       <c r="H96" s="5" t="n">
         <v>-0.1319593472026728</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.1240140227870288</v>
+        <v>0.1264241893076248</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.1883252258512855</v>
-      </c>
-      <c r="K96" s="5" t="n">
-        <v>-0.0001948937828883945</v>
+        <v>0.1908732916377112</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>0.001948937828883057</v>
       </c>
       <c r="L96" s="5" t="n">
-        <v>-0.01270207852194005</v>
+        <v>-0.01058506543495008</v>
       </c>
     </row>
   </sheetData>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -10,7 +10,7 @@
     <sheet name="NEFTy Ranking" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NEFTy Ranking'!$A$1:$L$96</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'NEFTy Ranking'!$A$1:$N$104</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -181,6 +181,12 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="1" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -569,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L96"/>
+  <dimension ref="A1:N104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
@@ -584,6 +590,8 @@
     <col width="12" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
     <col width="12" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="58" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -647,6 +655,16 @@
           <t>1d</t>
         </is>
       </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Transition State</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>HIL Summary</t>
+        </is>
+      </c>
     </row>
     <row r="2" ht="21" customHeight="1">
       <c r="A2" t="n">
@@ -673,7 +691,7 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.780701061260387</v>
+        <v>1.780701320170908</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1.311035712738891</v>
@@ -692,6 +710,16 @@
       </c>
       <c r="L2" s="3" t="n">
         <v>0.03596435391470409</v>
+      </c>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N2" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="3" ht="21" customHeight="1">
@@ -722,10 +750,10 @@
         <v>1.547923635217787</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.159521464648385</v>
-      </c>
-      <c r="H3" s="6" t="n">
-        <v>1.296873381333742</v>
+        <v>1.159521333839812</v>
+      </c>
+      <c r="H3" s="8" t="n">
+        <v>1.296873242205359</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0.5248488768743713</v>
@@ -738,6 +766,16 @@
       </c>
       <c r="L3" s="3" t="n">
         <v>0.04857363145720894</v>
+      </c>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N3" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="4" ht="21" customHeight="1">
@@ -750,7 +788,7 @@
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="D4" s="9" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -766,7 +804,7 @@
       <c r="G4" s="3" t="n">
         <v>1.642836794255342</v>
       </c>
-      <c r="H4" s="8" t="n">
+      <c r="H4" s="10" t="n">
         <v>1.29651281131565</v>
       </c>
       <c r="I4" s="3" t="n">
@@ -780,6 +818,16 @@
       </c>
       <c r="L4" s="3" t="n">
         <v>0.04602348249889232</v>
+      </c>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>REACCELERATING</t>
+        </is>
+      </c>
+      <c r="N4" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="21" customHeight="1">
@@ -796,7 +844,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D5" s="9" t="inlineStr">
+      <c r="D5" s="11" t="inlineStr">
         <is>
           <t>Transportation &amp; Trade</t>
         </is>
@@ -812,7 +860,7 @@
       <c r="G5" s="3" t="n">
         <v>1.315772143562726</v>
       </c>
-      <c r="H5" s="10" t="n">
+      <c r="H5" s="12" t="n">
         <v>1.253210405004939</v>
       </c>
       <c r="I5" s="3" t="n">
@@ -826,6 +874,16 @@
       </c>
       <c r="L5" s="3" t="n">
         <v>0.04657738095238084</v>
+      </c>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>MIXED_TRANSITION</t>
+        </is>
+      </c>
+      <c r="N5" s="7" t="inlineStr">
+        <is>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="6" ht="21" customHeight="1">
@@ -849,13 +907,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.536413373225165</v>
+        <v>1.536413562056367</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.139025500733548</v>
+        <v>1.139025366436778</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.191116569173679</v>
+        <v>1.191116431606419</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.6086899115826985</v>
@@ -868,6 +926,16 @@
       </c>
       <c r="L6" s="3" t="n">
         <v>0.0351652727996814</v>
+      </c>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N6" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="7" ht="21" customHeight="1">
@@ -898,13 +966,13 @@
         <v>1.514480634235029</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.078725921146207</v>
+        <v>1.078725564356369</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.132718802214939</v>
+        <v>1.132718436157833</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5634509855190464</v>
+        <v>0.5634508846038371</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>-0.0397431750266648</v>
@@ -914,6 +982,16 @@
       </c>
       <c r="L7" s="3" t="n">
         <v>0.03355704697986583</v>
+      </c>
+      <c r="M7" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N7" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="8" ht="21" customHeight="1">
@@ -961,6 +1039,16 @@
       <c r="L8" s="3" t="n">
         <v>0.02607672819399198</v>
       </c>
+      <c r="M8" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N8" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="21" customHeight="1">
       <c r="A9" t="n">
@@ -976,7 +1064,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D9" s="7" t="inlineStr">
+      <c r="D9" s="9" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1006,6 +1094,16 @@
       </c>
       <c r="L9" s="3" t="n">
         <v>0.0186143648415511</v>
+      </c>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>REACCELERATING</t>
+        </is>
+      </c>
+      <c r="N9" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="10" ht="21" customHeight="1">
@@ -1022,7 +1120,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D10" s="11" t="inlineStr">
+      <c r="D10" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1052,6 +1150,16 @@
       </c>
       <c r="L10" s="5" t="n">
         <v>-0.006465753424657605</v>
+      </c>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N10" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="11" ht="21" customHeight="1">
@@ -1068,7 +1176,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D11" s="9" t="inlineStr">
+      <c r="D11" s="11" t="inlineStr">
         <is>
           <t>Transportation &amp; Trade</t>
         </is>
@@ -1098,6 +1206,16 @@
       </c>
       <c r="L11" s="3" t="n">
         <v>0.02602230483271373</v>
+      </c>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>ACCELERATING</t>
+        </is>
+      </c>
+      <c r="N11" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="12" ht="21" customHeight="1">
@@ -1110,7 +1228,7 @@
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
-      <c r="D12" s="12" t="inlineStr">
+      <c r="D12" s="14" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
@@ -1140,6 +1258,16 @@
       </c>
       <c r="L12" s="5" t="n">
         <v>-0.003467575130794431</v>
+      </c>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N12" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="13" ht="21" customHeight="1">
@@ -1156,7 +1284,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D13" s="7" t="inlineStr">
+      <c r="D13" s="9" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1186,6 +1314,16 @@
       </c>
       <c r="L13" s="5" t="n">
         <v>-0.003352076124567449</v>
+      </c>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N13" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="21" customHeight="1">
@@ -1202,7 +1340,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D14" s="11" t="inlineStr">
+      <c r="D14" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1213,7 +1351,7 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8365068511745186</v>
+        <v>0.8365070246181665</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0.5887106436810075</v>
@@ -1232,6 +1370,16 @@
       </c>
       <c r="L14" s="5" t="n">
         <v>-0.00376040827289803</v>
+      </c>
+      <c r="M14" s="6" t="inlineStr">
+        <is>
+          <t>MIXED_TRANSITION</t>
+        </is>
+      </c>
+      <c r="N14" s="7" t="inlineStr">
+        <is>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="15" ht="21" customHeight="1">
@@ -1248,7 +1396,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D15" s="11" t="inlineStr">
+      <c r="D15" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1278,6 +1426,16 @@
       </c>
       <c r="L15" s="5" t="n">
         <v>-0.0053046695051302</v>
+      </c>
+      <c r="M15" s="6" t="inlineStr">
+        <is>
+          <t>REACCELERATING</t>
+        </is>
+      </c>
+      <c r="N15" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="16" ht="21" customHeight="1">
@@ -1294,7 +1452,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D16" s="11" t="inlineStr">
+      <c r="D16" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1305,13 +1463,13 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.832094036754814</v>
+        <v>0.8320938409509537</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6156586912938948</v>
+        <v>0.6156588443481128</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5458769371817545</v>
+        <v>0.545877083625423</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.1435659925999622</v>
@@ -1324,6 +1482,16 @@
       </c>
       <c r="L16" s="5" t="n">
         <v>-0.001841055538508773</v>
+      </c>
+      <c r="M16" s="6" t="inlineStr">
+        <is>
+          <t>REACCELERATING</t>
+        </is>
+      </c>
+      <c r="N16" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="17" ht="21" customHeight="1">
@@ -1336,7 +1504,7 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" s="11" t="inlineStr">
+      <c r="D17" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1366,6 +1534,16 @@
       </c>
       <c r="L17" s="5" t="n">
         <v>-0.01205615194054499</v>
+      </c>
+      <c r="M17" s="6" t="inlineStr">
+        <is>
+          <t>MIXED_TRANSITION</t>
+        </is>
+      </c>
+      <c r="N17" s="7" t="inlineStr">
+        <is>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="18" ht="21" customHeight="1">
@@ -1382,7 +1560,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
+      <c r="D18" s="11" t="inlineStr">
         <is>
           <t>Transportation &amp; Trade</t>
         </is>
@@ -1393,7 +1571,7 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.11368050503854</v>
+        <v>1.113680672641568</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0.7272218190073159</v>
@@ -1412,6 +1590,16 @@
       </c>
       <c r="L18" s="3" t="n">
         <v>0.009930486593842991</v>
+      </c>
+      <c r="M18" s="6" t="inlineStr">
+        <is>
+          <t>ACCELERATING</t>
+        </is>
+      </c>
+      <c r="N18" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="19" ht="21" customHeight="1">
@@ -1459,6 +1647,16 @@
       <c r="L19" s="3" t="n">
         <v>0.007030670493759494</v>
       </c>
+      <c r="M19" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N19" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="21" customHeight="1">
       <c r="A20" t="n">
@@ -1490,7 +1688,7 @@
         <v>0.4186917551982716</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.3674444950892</v>
+        <v>0.367444342737236</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.03995183621570808</v>
@@ -1500,6 +1698,16 @@
       </c>
       <c r="L20" s="3" t="n">
         <v>0.007044146905414772</v>
+      </c>
+      <c r="M20" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N20" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="21" customHeight="1">
@@ -1516,7 +1724,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D21" s="7" t="inlineStr">
+      <c r="D21" s="9" t="inlineStr">
         <is>
           <t>International</t>
         </is>
@@ -1546,6 +1754,16 @@
       </c>
       <c r="L21" s="5" t="n">
         <v>-0.0003888024883358376</v>
+      </c>
+      <c r="M21" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N21" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="22" ht="21" customHeight="1">
@@ -1558,7 +1776,7 @@
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" s="11" t="inlineStr">
+      <c r="D22" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1569,7 +1787,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.763199180820205</v>
+        <v>1.763198887475063</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0.6674520561524815</v>
@@ -1588,6 +1806,16 @@
       </c>
       <c r="L22" s="5" t="n">
         <v>-0.02042225730071023</v>
+      </c>
+      <c r="M22" s="6" t="inlineStr">
+        <is>
+          <t>MIXED_TRANSITION</t>
+        </is>
+      </c>
+      <c r="N22" s="7" t="inlineStr">
+        <is>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="23" ht="21" customHeight="1">
@@ -1615,13 +1843,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.669553783211627</v>
+        <v>0.6695536361980647</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3999387636385074</v>
+        <v>0.3999388670037975</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3812606549397253</v>
+        <v>0.3812607569259066</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0.3528745980372852</v>
@@ -1634,6 +1862,16 @@
       </c>
       <c r="L23" s="3" t="n">
         <v>0.002911914583838771</v>
+      </c>
+      <c r="M23" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N23" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="24" ht="21" customHeight="1">
@@ -1661,7 +1899,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6565618098588615</v>
+        <v>0.6565619157488216</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0.3219858657217809</v>
@@ -1680,6 +1918,16 @@
       </c>
       <c r="L24" s="3" t="n">
         <v>0.006106248727864694</v>
+      </c>
+      <c r="M24" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N24" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="25" ht="21" customHeight="1">
@@ -1696,7 +1944,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D25" s="14" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
@@ -1726,6 +1974,16 @@
       </c>
       <c r="L25" s="5" t="n">
         <v>-0.00883962396520277</v>
+      </c>
+      <c r="M25" s="6" t="inlineStr">
+        <is>
+          <t>ACCELERATING</t>
+        </is>
+      </c>
+      <c r="N25" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="26" ht="21" customHeight="1">
@@ -1749,13 +2007,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.6640373456185977</v>
+        <v>0.6640376940542052</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3969983121244756</v>
+        <v>0.3969984349012043</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.377760354004183</v>
+        <v>0.3777604750901629</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.3522537144371283</v>
@@ -1768,6 +2026,16 @@
       </c>
       <c r="L26" s="3" t="n">
         <v>0.003226340172071573</v>
+      </c>
+      <c r="M26" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N26" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="27" ht="21" customHeight="1">
@@ -1815,6 +2083,16 @@
       <c r="L27" s="3" t="n">
         <v>0.007828356045230356</v>
       </c>
+      <c r="M27" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N27" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="21" customHeight="1">
       <c r="A28" t="n">
@@ -1841,13 +2119,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6675996159510886</v>
+        <v>0.6675999509793089</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3869345103189425</v>
+        <v>0.386934394446645</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3720418417781526</v>
+        <v>0.3720417271500722</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.3458530565264364</v>
@@ -1860,6 +2138,16 @@
       </c>
       <c r="L28" s="3" t="n">
         <v>0.003049021937118868</v>
+      </c>
+      <c r="M28" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N28" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="29" ht="21" customHeight="1">
@@ -1876,7 +2164,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D29" s="11" t="inlineStr">
+      <c r="D29" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1887,13 +2175,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.083085891569514</v>
+        <v>1.083086170660991</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4595270321590497</v>
+        <v>0.4595268951477454</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3577711009842448</v>
+        <v>0.3577709735251533</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.07839751281140894</v>
@@ -1906,6 +2194,16 @@
       </c>
       <c r="L29" s="3" t="n">
         <v>0.002027369488089237</v>
+      </c>
+      <c r="M29" s="6" t="inlineStr">
+        <is>
+          <t>REACCELERATING</t>
+        </is>
+      </c>
+      <c r="N29" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="30" ht="21" customHeight="1">
@@ -1922,7 +2220,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D30" s="11" t="inlineStr">
+      <c r="D30" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1953,23 +2251,33 @@
       <c r="L30" s="5" t="n">
         <v>-0.00867369345630209</v>
       </c>
+      <c r="M30" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N30" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="21" customHeight="1">
-      <c r="A31" s="13" t="n">
+      <c r="A31" s="15" t="n">
         <v>30</v>
       </c>
-      <c r="B31" s="14" t="inlineStr">
+      <c r="B31" s="16" t="inlineStr">
         <is>
           <t>XLE</t>
         </is>
       </c>
-      <c r="C31" s="13" t="inlineStr"/>
-      <c r="D31" s="11" t="inlineStr">
+      <c r="C31" s="15" t="inlineStr"/>
+      <c r="D31" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E31" s="13" t="inlineStr">
+      <c r="E31" s="15" t="inlineStr">
         <is>
           <t>Energy</t>
         </is>
@@ -1978,13 +2286,13 @@
         <v>0.5662267707694086</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.4830731008430185</v>
+        <v>0.4830732318209987</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3464803550582258</v>
+        <v>0.3464804739729828</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.1480211489675201</v>
+        <v>0.1480210704850085</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0.1188137155182061</v>
@@ -1994,6 +2302,16 @@
       </c>
       <c r="L31" s="5" t="n">
         <v>-0.008666047663262177</v>
+      </c>
+      <c r="M31" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N31" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="32" ht="21" customHeight="1">
@@ -2006,7 +2324,7 @@
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
-      <c r="D32" s="15" t="inlineStr">
+      <c r="D32" s="17" t="inlineStr">
         <is>
           <t>Inflation &amp; Real Assets</t>
         </is>
@@ -2036,6 +2354,16 @@
       </c>
       <c r="L32" s="5" t="n">
         <v>-0.001877346683354264</v>
+      </c>
+      <c r="M32" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N32" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="33" ht="21" customHeight="1">
@@ -2083,6 +2411,16 @@
       <c r="L33" s="3" t="n">
         <v>0.0100288328945719</v>
       </c>
+      <c r="M33" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N33" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="21" customHeight="1">
       <c r="A34" t="n">
@@ -2098,7 +2436,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D34" s="16" t="inlineStr">
+      <c r="D34" s="18" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -2112,10 +2450,10 @@
         <v>0.5446504306874409</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1788140589983993</v>
+        <v>0.1788139751629894</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3185919873131313</v>
+        <v>0.3185918935369341</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>-0.09382844759776487</v>
@@ -2128,6 +2466,16 @@
       </c>
       <c r="L34" s="5" t="n">
         <v>-0.003977474107037415</v>
+      </c>
+      <c r="M34" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N34" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="35" ht="21" customHeight="1">
@@ -2140,7 +2488,7 @@
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
-      <c r="D35" s="16" t="inlineStr">
+      <c r="D35" s="18" t="inlineStr">
         <is>
           <t>Industrials</t>
         </is>
@@ -2170,6 +2518,16 @@
       </c>
       <c r="L35" s="3" t="n">
         <v>0.01003344481605351</v>
+      </c>
+      <c r="M35" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N35" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="36" ht="21" customHeight="1">
@@ -2186,7 +2544,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D36" s="11" t="inlineStr">
+      <c r="D36" s="13" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -2200,10 +2558,10 @@
         <v>0.6189414385293674</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.4755470636917334</v>
+        <v>0.4755468894899149</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.2924866917817843</v>
+        <v>0.292486539191916</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.1723325472199564</v>
@@ -2216,6 +2574,16 @@
       </c>
       <c r="L36" s="5" t="n">
         <v>-0.008423022929340274</v>
+      </c>
+      <c r="M36" s="6" t="inlineStr">
+        <is>
+          <t>ACCELERATING</t>
+        </is>
+      </c>
+      <c r="N36" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="37" ht="21" customHeight="1">
@@ -2263,6 +2631,16 @@
       <c r="L37" s="5" t="n">
         <v>-0.004559889259832306</v>
       </c>
+      <c r="M37" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N37" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="21" customHeight="1">
       <c r="A38" t="n">
@@ -2270,40 +2648,50 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SPMO</t>
+          <t>EWZ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
-      <c r="D38" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D38" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Brazil Equity</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.5589922376025815</v>
+        <v>0.6394296452852541</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.2867870870193954</v>
+        <v>0.3561770077768018</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.2814584202150137</v>
+        <v>0.282744285485665</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.2717691990035427</v>
+        <v>0.05348465783876932</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.03929689962146599</v>
+        <v>0.1237996411221542</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.004158283031522547</v>
-      </c>
-      <c r="L38" s="3" t="n">
-        <v>0.01567057865816435</v>
+        <v>0.05724657916783005</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>-0.007081038552321117</v>
+      </c>
+      <c r="M38" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N38" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="39" ht="21" customHeight="1">
@@ -2312,44 +2700,50 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CALF</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D39" s="17" t="inlineStr">
+          <t>SPMO</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Small Cap Value</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5455962817152487</v>
+        <v>0.5589921137519795</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.333699585374126</v>
+        <v>0.2867870870193954</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.275338593485343</v>
+        <v>0.2814584202150137</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2708930358411168</v>
+        <v>0.2717691990035427</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.1600853084742613</v>
+        <v>0.03929689962146599</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.04576117447311745</v>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v>-0.007260155574762339</v>
+        <v>0.004158283031522547</v>
+      </c>
+      <c r="L39" s="3" t="n">
+        <v>0.01567057865816435</v>
+      </c>
+      <c r="M39" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N39" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="40" ht="21" customHeight="1">
@@ -2358,40 +2752,54 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SCHA</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" s="17" t="inlineStr">
+          <t>CALF</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Small Cap Value</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4337934514140818</v>
+        <v>0.5455962817152487</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2722682033671824</v>
+        <v>0.333699585374126</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.2678493268287148</v>
+        <v>0.275338593485343</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1885752537866485</v>
+        <v>0.2708930358411168</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.04397184437404666</v>
+        <v>0.1600853084742613</v>
       </c>
       <c r="K40" s="3" t="n">
-        <v>0.003485332558814891</v>
-      </c>
-      <c r="L40" s="3" t="n">
-        <v>0.009938614440222038</v>
+        <v>0.04576117447311745</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>-0.007260155574762339</v>
+      </c>
+      <c r="M40" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N40" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="41" ht="21" customHeight="1">
@@ -2400,44 +2808,50 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MTUM</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D41" s="17" t="inlineStr">
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Momentum Factor</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4508514368114691</v>
+        <v>0.4418595202594637</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2534754983218976</v>
+        <v>0.2641467152831039</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2670850367967565</v>
+        <v>0.2737129077841483</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.2649924459663764</v>
-      </c>
-      <c r="J41" s="5" t="n">
-        <v>-0.004154334153843142</v>
+        <v>0.1847492268813271</v>
+      </c>
+      <c r="J41" s="3" t="n">
+        <v>0.0534846513024354</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.01074082486939032</v>
+        <v>-0.007510477787091352</v>
       </c>
       <c r="L41" s="3" t="n">
-        <v>0.01816845902077358</v>
+        <v>0.002777871879128702</v>
+      </c>
+      <c r="M41" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N41" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="42" ht="21" customHeight="1">
@@ -2446,40 +2860,50 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SCHA</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4906183303287333</v>
+        <v>0.433793337924715</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.1422403598761612</v>
+        <v>0.2722682033671824</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2656738068589226</v>
-      </c>
-      <c r="I42" s="5" t="n">
-        <v>-0.06723819317242319</v>
-      </c>
-      <c r="J42" s="5" t="n">
-        <v>-0.01604546874855806</v>
-      </c>
-      <c r="K42" s="5" t="n">
-        <v>-0.09752390095603825</v>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v>-0.001637313036551791</v>
+        <v>0.2678493268287148</v>
+      </c>
+      <c r="I42" s="3" t="n">
+        <v>0.1885752537866485</v>
+      </c>
+      <c r="J42" s="3" t="n">
+        <v>0.04397184437404666</v>
+      </c>
+      <c r="K42" s="3" t="n">
+        <v>0.003485332558814891</v>
+      </c>
+      <c r="L42" s="3" t="n">
+        <v>0.009938614440222038</v>
+      </c>
+      <c r="M42" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N42" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="43" ht="21" customHeight="1">
@@ -2488,40 +2912,54 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HEFA</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" s="7" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>MTUM</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D43" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Developed ex-US Hedged</t>
+          <t>Momentum Factor</t>
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.3443246450418633</v>
+        <v>0.4508514368114691</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2690509475067042</v>
+        <v>0.2534754983218976</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2655667527194627</v>
+        <v>0.2670850367967565</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.129270688345682</v>
-      </c>
-      <c r="J43" s="3" t="n">
-        <v>0.06803907799689601</v>
-      </c>
-      <c r="K43" s="3" t="n">
-        <v>0.002753070732740337</v>
+        <v>0.2649924459663764</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>-0.004154334153843142</v>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>-0.01074082486939032</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.003390548845094488</v>
+        <v>0.01816845902077358</v>
+      </c>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N43" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="44" ht="21" customHeight="1">
@@ -2530,40 +2968,50 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>VEA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="7" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D44" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Developed Markets</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4632542486309303</v>
+        <v>0.4906183303287333</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2933336468535885</v>
+        <v>0.1422404481184474</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2645773130569522</v>
-      </c>
-      <c r="I44" s="3" t="n">
-        <v>0.1377823091565502</v>
-      </c>
-      <c r="J44" s="3" t="n">
-        <v>0.071971220943017</v>
-      </c>
-      <c r="K44" s="3" t="n">
-        <v>0.02273987798114252</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>0.004357298474945592</v>
+        <v>0.2656739046368983</v>
+      </c>
+      <c r="I44" s="5" t="n">
+        <v>-0.06723819317242319</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>-0.01604546874855806</v>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>-0.09752390095603825</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>-0.001637313036551791</v>
+      </c>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N44" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="45" ht="21" customHeight="1">
@@ -2572,40 +3020,50 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>FNDX</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D45" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Fundamental Equity</t>
+          <t>Developed ex-US Hedged</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3920427187433075</v>
+        <v>0.3443246450418633</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2816843601883992</v>
+        <v>0.2690509475067042</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2636214065828029</v>
+        <v>0.2655667527194627</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>0.1653206156032558</v>
+        <v>0.129270688345682</v>
       </c>
       <c r="J45" s="3" t="n">
-        <v>0.06586853355928812</v>
+        <v>0.06803907799689601</v>
       </c>
       <c r="K45" s="3" t="n">
-        <v>0.01429459291485391</v>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v>-0.004574565416285425</v>
+        <v>0.002753070732740337</v>
+      </c>
+      <c r="L45" s="3" t="n">
+        <v>0.003390548845094488</v>
+      </c>
+      <c r="M45" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N45" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="46" ht="21" customHeight="1">
@@ -2614,40 +3072,50 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>VEA</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
-      <c r="D46" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D46" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Developed Markets</t>
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.425998814187043</v>
+        <v>0.4632541378975084</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.1929944469313138</v>
+        <v>0.2933335603447877</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2619874180283208</v>
+        <v>0.2645772284716119</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.07128209029965205</v>
-      </c>
-      <c r="J46" s="5" t="n">
-        <v>-0.02511064236953608</v>
-      </c>
-      <c r="K46" s="5" t="n">
-        <v>-0.05467009425878333</v>
+        <v>0.1377823091565502</v>
+      </c>
+      <c r="J46" s="3" t="n">
+        <v>0.071971220943017</v>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v>0.02273987798114252</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.008593892850612628</v>
+        <v>0.004357298474945592</v>
+      </c>
+      <c r="M46" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N46" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="47" ht="21" customHeight="1">
@@ -2656,40 +3124,50 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>FNDX</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
-      <c r="D47" s="17" t="inlineStr">
+      <c r="D47" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>Fundamental Equity</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3105532265789543</v>
+        <v>0.3920427187433075</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.3029248468195411</v>
+        <v>0.2816843601883992</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2617404407419122</v>
+        <v>0.2636214065828029</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1363270661486402</v>
+        <v>0.1653206156032558</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.0859799973215547</v>
+        <v>0.06586853355928812</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.03264094955489605</v>
+        <v>0.01429459291485391</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.007981755986317007</v>
+        <v>-0.004574565416285425</v>
+      </c>
+      <c r="M47" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N47" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="48" ht="21" customHeight="1">
@@ -2698,44 +3176,50 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>IWO</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D48" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>PAVE</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr"/>
+      <c r="D48" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.4141402494669566</v>
+        <v>0.425998814187043</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2273005975859326</v>
+        <v>0.1929944469313138</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2492433825456852</v>
+        <v>0.2619874180283208</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.1802404984418828</v>
-      </c>
-      <c r="J48" s="3" t="n">
-        <v>0.03199598028098749</v>
+        <v>0.07128209029965205</v>
+      </c>
+      <c r="J48" s="5" t="n">
+        <v>-0.02511064236953608</v>
       </c>
       <c r="K48" s="5" t="n">
-        <v>-0.01756485987145129</v>
+        <v>-0.05467009425878333</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.001166799257491302</v>
+        <v>0.008593892850612628</v>
+      </c>
+      <c r="M48" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N48" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="49" ht="21" customHeight="1">
@@ -2744,82 +3228,102 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>QQQM</t>
+          <t>SCHD</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D49" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Nasdaq-100</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4444172082838467</v>
+        <v>0.3105532265789543</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.256644154465927</v>
+        <v>0.3029248468195411</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2489617620601334</v>
+        <v>0.2617404407419122</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.2018418315921782</v>
+        <v>0.1363270661486402</v>
       </c>
       <c r="J49" s="3" t="n">
-        <v>0.02088045625307022</v>
+        <v>0.0859799973215547</v>
       </c>
       <c r="K49" s="3" t="n">
-        <v>0.006151022904913983</v>
-      </c>
-      <c r="L49" s="3" t="n">
-        <v>0.001895028933031062</v>
+        <v>0.03264094955489605</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>-0.007981755986317007</v>
+      </c>
+      <c r="M49" s="6" t="inlineStr">
+        <is>
+          <t>ACCELERATING</t>
+        </is>
+      </c>
+      <c r="N49" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="50" ht="21" customHeight="1">
-      <c r="A50" s="13" t="n">
+      <c r="A50" t="n">
         <v>49</v>
       </c>
-      <c r="B50" s="14" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C50" s="13" t="inlineStr"/>
-      <c r="D50" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E50" s="13" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>EWJ</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr"/>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Japan Equity</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4428249635689041</v>
+        <v>0.4731443902293495</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2558848667790528</v>
+        <v>0.3020608478069629</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2483561255753448</v>
+        <v>0.260593097973469</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.2015967755690107</v>
+        <v>0.1656716357696715</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.02083526655997492</v>
+        <v>0.08921936815569764</v>
       </c>
       <c r="K50" s="3" t="n">
-        <v>0.006030924228643375</v>
+        <v>0.03289542827115066</v>
       </c>
       <c r="L50" s="3" t="n">
-        <v>0.001797483523067855</v>
+        <v>0.003881511746680166</v>
+      </c>
+      <c r="M50" s="6" t="inlineStr">
+        <is>
+          <t>ACCELERATING</t>
+        </is>
+      </c>
+      <c r="N50" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="51" ht="21" customHeight="1">
@@ -2828,7 +3332,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>PPA</t>
+          <t>IWO</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2836,36 +3340,46 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D51" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D51" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4270661699188298</v>
+        <v>0.4141402494669566</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.1263249615315105</v>
+        <v>0.2273007193415577</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2407439762699701</v>
-      </c>
-      <c r="I51" s="5" t="n">
-        <v>-0.08523349351222964</v>
-      </c>
-      <c r="J51" s="5" t="n">
-        <v>-0.0304502302686378</v>
+        <v>0.2492435064781673</v>
+      </c>
+      <c r="I51" s="3" t="n">
+        <v>0.1802404984418828</v>
+      </c>
+      <c r="J51" s="3" t="n">
+        <v>0.03199598028098749</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.09221806990547377</v>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v>-0.002355499184634846</v>
+        <v>-0.01756485987145129</v>
+      </c>
+      <c r="L51" s="3" t="n">
+        <v>0.001166799257491302</v>
+      </c>
+      <c r="M51" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N51" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
@@ -2874,86 +3388,102 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>XLI</t>
+          <t>QQQM</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
-      <c r="D52" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Industrials</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.3344500799148888</v>
+        <v>0.4444172082838467</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.1718847060957682</v>
+        <v>0.2566442358520458</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2353364426214075</v>
+        <v>0.2489618429487046</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.03680666519160902</v>
+        <v>0.2018418315921782</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.008733630694340855</v>
-      </c>
-      <c r="K52" s="5" t="n">
-        <v>-0.05136393158692343</v>
+        <v>0.02088045625307022</v>
+      </c>
+      <c r="K52" s="3" t="n">
+        <v>0.006151022904913983</v>
       </c>
       <c r="L52" s="3" t="n">
-        <v>0.004067369385884589</v>
+        <v>0.001895028933031062</v>
+      </c>
+      <c r="M52" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N52" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
-      <c r="A53" t="n">
+      <c r="A53" s="15" t="n">
         <v>52</v>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D53" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>Health Care</t>
+      <c r="B53" s="16" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C53" s="15" t="inlineStr"/>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
+        </is>
+      </c>
+      <c r="E53" s="15" t="inlineStr">
+        <is>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.2103109042181897</v>
+        <v>0.4428249635689041</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2796271277588027</v>
+        <v>0.2558848667790528</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2293427066468481</v>
+        <v>0.2483561255753448</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.1482060199965338</v>
+        <v>0.2015967755690107</v>
       </c>
       <c r="J53" s="3" t="n">
-        <v>0.1359983485299427</v>
+        <v>0.02083526655997492</v>
       </c>
       <c r="K53" s="3" t="n">
-        <v>0.04090350139149579</v>
-      </c>
-      <c r="L53" s="5" t="n">
-        <v>-0.009667487684729026</v>
+        <v>0.006030924228643375</v>
+      </c>
+      <c r="L53" s="3" t="n">
+        <v>0.001797483523067855</v>
+      </c>
+      <c r="M53" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N53" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="54" ht="21" customHeight="1">
@@ -2962,40 +3492,54 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ONEQ</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr"/>
-      <c r="D54" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D54" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4408768111376706</v>
+        <v>0.4270662639822698</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.2290597370000531</v>
+        <v>0.1263249615315105</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.221764915662316</v>
-      </c>
-      <c r="I54" s="3" t="n">
-        <v>0.1879271316382964</v>
-      </c>
-      <c r="J54" s="3" t="n">
-        <v>0.03263482295051578</v>
-      </c>
-      <c r="K54" s="3" t="n">
-        <v>0.005970724191063148</v>
+        <v>0.2407439762699701</v>
+      </c>
+      <c r="I54" s="5" t="n">
+        <v>-0.08523357081287031</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>-0.0304502302686378</v>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>-0.09221806990547377</v>
       </c>
       <c r="L54" s="5" t="n">
-        <v>-0.002863688430698841</v>
+        <v>-0.002355499184634846</v>
+      </c>
+      <c r="M54" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N54" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="55" ht="21" customHeight="1">
@@ -3004,44 +3548,50 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D55" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XLI</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr"/>
+      <c r="D55" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3210083123181748</v>
+        <v>0.3344499248844144</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1655925945476298</v>
+        <v>0.1718847060957682</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2045766351741902</v>
+        <v>0.2353364426214075</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.07441840515245657</v>
-      </c>
-      <c r="J55" s="5" t="n">
-        <v>-0.06150276039675151</v>
+        <v>0.03680666519160902</v>
+      </c>
+      <c r="J55" s="3" t="n">
+        <v>0.008733630694340855</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.03236327145007523</v>
+        <v>-0.05136393158692343</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.009950248756219082</v>
+        <v>0.004067369385884589</v>
+      </c>
+      <c r="M55" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N55" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="56" ht="21" customHeight="1">
@@ -3050,40 +3600,54 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VBK</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr"/>
-      <c r="D56" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D56" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.3191541177750707</v>
+        <v>0.2103107652399336</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.1944635763351985</v>
+        <v>0.2796271277588027</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2035902296914684</v>
+        <v>0.2293427066468481</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1446617683774252</v>
+        <v>0.1482060199965338</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.02244173753769618</v>
-      </c>
-      <c r="K56" s="5" t="n">
-        <v>-0.007582857629717998</v>
-      </c>
-      <c r="L56" s="3" t="n">
-        <v>0.000114481969089919</v>
+        <v>0.1359983485299427</v>
+      </c>
+      <c r="K56" s="3" t="n">
+        <v>0.04090350139149579</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>-0.009667487684729026</v>
+      </c>
+      <c r="M56" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N56" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="57" ht="21" customHeight="1">
@@ -3092,40 +3656,50 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>COWZ</t>
+          <t>ONEQ</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
-      <c r="D57" s="17" t="inlineStr">
+      <c r="D57" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Cash Flow Factor</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.3296585139524517</v>
+        <v>0.4408768111376706</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2664747739759108</v>
+        <v>0.2290597370000531</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2029491727456918</v>
+        <v>0.221764915662316</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1315250033629372</v>
+        <v>0.1879272347053123</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.1223255352865984</v>
+        <v>0.03263482295051578</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.05280821722934803</v>
+        <v>0.005970724191063148</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.01287553648068684</v>
+        <v>-0.002863688430698841</v>
+      </c>
+      <c r="M57" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N57" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="58" ht="21" customHeight="1">
@@ -3134,40 +3708,50 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>VOO</t>
+          <t>XLV</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
-      <c r="D58" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D58" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>S&amp;P 500</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.3442858721527491</v>
+        <v>0.1755440900895964</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2007777249572409</v>
+        <v>0.2693337995003819</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.1980471814095774</v>
+        <v>0.2175091474356246</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.151808910586533</v>
+        <v>0.1323776016142966</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.04730356189549445</v>
+        <v>0.1254567146663546</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.002279161947904784</v>
+        <v>0.04256612952265137</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.003813034669068016</v>
+        <v>-0.01044672746161834</v>
+      </c>
+      <c r="M58" s="6" t="inlineStr">
+        <is>
+          <t>ACCELERATING</t>
+        </is>
+      </c>
+      <c r="N58" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="59" ht="21" customHeight="1">
@@ -3176,40 +3760,54 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>IVV</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
-      <c r="D59" s="17" t="inlineStr">
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D59" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>US Large Blend</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3447651274156656</v>
+        <v>0.3210082260220046</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2007974289088261</v>
+        <v>0.1655925945476298</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.1980201038652212</v>
+        <v>0.2045766351741902</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1520055073493269</v>
-      </c>
-      <c r="J59" s="3" t="n">
-        <v>0.04735888636141317</v>
-      </c>
-      <c r="K59" s="3" t="n">
-        <v>0.002318262468755217</v>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v>-0.004130583042734171</v>
+        <v>0.07441851932386845</v>
+      </c>
+      <c r="J59" s="5" t="n">
+        <v>-0.06150276039675151</v>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>-0.03236327145007523</v>
+      </c>
+      <c r="L59" s="3" t="n">
+        <v>0.009950248756219082</v>
+      </c>
+      <c r="M59" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N59" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="60" ht="21" customHeight="1">
@@ -3218,82 +3816,102 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VWO</t>
+          <t>VBK</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
-      <c r="D60" s="7" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D60" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Emerging Markets</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3756669252199267</v>
+        <v>0.319154269748813</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.2270838008564444</v>
+        <v>0.1944635763351985</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.1975251415910222</v>
+        <v>0.2035902296914684</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1293008922112591</v>
+        <v>0.1446617683774252</v>
       </c>
       <c r="J60" s="3" t="n">
-        <v>0.06002103053001884</v>
-      </c>
-      <c r="K60" s="3" t="n">
-        <v>0.02468312208138745</v>
+        <v>0.02244173753769618</v>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>-0.007582857629717998</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.007378258730939447</v>
+        <v>0.000114481969089919</v>
+      </c>
+      <c r="M60" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N60" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="61" ht="21" customHeight="1">
-      <c r="A61" s="13" t="n">
+      <c r="A61" t="n">
         <v>60</v>
       </c>
-      <c r="B61" s="14" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="C61" s="13" t="inlineStr"/>
-      <c r="D61" s="17" t="inlineStr">
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr"/>
+      <c r="D61" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E61" s="13" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>Cash Flow Factor</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3435590842611607</v>
+        <v>0.3296584193612484</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.1996610267455765</v>
+        <v>0.2664747739759108</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.1971221110577652</v>
+        <v>0.2029491727456918</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1515557712139433</v>
+        <v>0.1315250033629372</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.0469448480365231</v>
+        <v>0.1223255352865984</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.00212084938066015</v>
+        <v>0.05280821722934803</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.00385426232264563</v>
+        <v>-0.01287553648068684</v>
+      </c>
+      <c r="M61" s="6" t="inlineStr">
+        <is>
+          <t>ACCELERATING</t>
+        </is>
+      </c>
+      <c r="N61" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="62" ht="21" customHeight="1">
@@ -3302,82 +3920,102 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>IAU</t>
+          <t>VOO</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.5115098785571868</v>
+        <v>0.3442858721527491</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2463010013450906</v>
+        <v>0.2007777249572409</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1936930204752654</v>
-      </c>
-      <c r="I62" s="5" t="n">
-        <v>-0.14013198597649</v>
+        <v>0.1980471814095774</v>
+      </c>
+      <c r="I62" s="3" t="n">
+        <v>0.151808910586533</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.0267175572519085</v>
+        <v>0.04730356189549445</v>
       </c>
       <c r="K62" s="3" t="n">
-        <v>0.04407161637661194</v>
+        <v>0.002279161947904784</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.008442330558858457</v>
+        <v>-0.003813034669068016</v>
+      </c>
+      <c r="M62" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N62" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="63" ht="21" customHeight="1">
-      <c r="A63" s="13" t="n">
+      <c r="A63" t="n">
         <v>62</v>
       </c>
-      <c r="B63" s="14" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C63" s="13" t="inlineStr"/>
-      <c r="D63" s="11" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E63" s="13" t="inlineStr">
-        <is>
-          <t>Gold</t>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>IVV</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr"/>
+      <c r="D63" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>US Large Blend</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.5086788813886209</v>
+        <v>0.3447654126339179</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2451253481894149</v>
+        <v>0.2007974289088261</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1927821482139032</v>
-      </c>
-      <c r="I63" s="5" t="n">
-        <v>-0.1409473928744905</v>
+        <v>0.1980201038652212</v>
+      </c>
+      <c r="I63" s="3" t="n">
+        <v>0.1520055073493269</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.02657480314960625</v>
+        <v>0.04735888636141317</v>
       </c>
       <c r="K63" s="3" t="n">
-        <v>0.04388328585726375</v>
+        <v>0.002318262468755217</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.00841012139827424</v>
+        <v>-0.004130583042734171</v>
+      </c>
+      <c r="M63" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N63" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
@@ -3386,86 +4024,102 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D64" s="17" t="inlineStr">
+          <t>VWO</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr"/>
+      <c r="D64" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>Emerging Markets</t>
+        </is>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>0.3756669252199267</v>
+      </c>
+      <c r="G64" s="3" t="n">
+        <v>0.2270838943447613</v>
+      </c>
+      <c r="H64" s="3" t="n">
+        <v>0.1975252328273418</v>
+      </c>
+      <c r="I64" s="3" t="n">
+        <v>0.1293008922112591</v>
+      </c>
+      <c r="J64" s="3" t="n">
+        <v>0.06002103053001884</v>
+      </c>
+      <c r="K64" s="3" t="n">
+        <v>0.02468312208138745</v>
+      </c>
+      <c r="L64" s="3" t="n">
+        <v>0.007378258730939447</v>
+      </c>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>REACCELERATING</t>
+        </is>
+      </c>
+      <c r="N64" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="21" customHeight="1">
+      <c r="A65" s="15" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" s="16" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C65" s="15" t="inlineStr"/>
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>S&amp;P 100</t>
-        </is>
-      </c>
-      <c r="F64" s="3" t="n">
-        <v>0.3622354311501259</v>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0.1956732147943772</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>0.1925134514647706</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>0.1607244253454756</v>
-      </c>
-      <c r="J64" s="3" t="n">
-        <v>0.0495456856083758</v>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>0.002649666824072527</v>
-      </c>
-      <c r="L64" s="5" t="n">
-        <v>-0.005542256452955807</v>
-      </c>
-    </row>
-    <row r="65" ht="21" customHeight="1">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>RSP</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr"/>
-      <c r="D65" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>Equal Weight</t>
+      <c r="E65" s="15" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.2689364881725527</v>
+        <v>0.3435590842611607</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1828297548786559</v>
+        <v>0.199660912694537</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1805613142528613</v>
+        <v>0.1971219972480989</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1142535522024297</v>
+        <v>0.151555666126193</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.05782676711006696</v>
+        <v>0.0469448480365231</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.001921493274773534</v>
+        <v>0.00212084938066015</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.004771642808452659</v>
+        <v>-0.00385426232264563</v>
+      </c>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N65" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="66" ht="21" customHeight="1">
@@ -3474,44 +4128,50 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>ARGT</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D66" s="7" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr"/>
+      <c r="D66" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Argentina Equity</t>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.1716900428331198</v>
+        <v>0.5115098785571868</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.2220921249669161</v>
+        <v>0.2463010013450906</v>
       </c>
       <c r="H66" s="3" t="n">
-        <v>0.1732895662995309</v>
-      </c>
-      <c r="I66" s="3" t="n">
-        <v>0.1180803678969065</v>
+        <v>0.1936930204752654</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>-0.14013198597649</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.05643272307669922</v>
+        <v>0.0267175572519085</v>
       </c>
       <c r="K66" s="3" t="n">
-        <v>0.04159464131374246</v>
+        <v>0.04407161637661194</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>-0.0040289256198347</v>
+        <v>-0.008442330558858457</v>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>MIXED_TRANSITION</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="67" ht="21" customHeight="1">
@@ -3520,86 +4180,102 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D67" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>QUAL</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr"/>
+      <c r="D67" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Quality Factor</t>
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.3200632269889565</v>
+        <v>0.2597787759939749</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1521993874626801</v>
+        <v>0.1805259008585947</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1656588842011395</v>
+        <v>0.1932020483249079</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0.1774918875405691</v>
+        <v>0.1248023884404867</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.08721738781999711</v>
+        <v>0.04615179003503123</v>
       </c>
       <c r="K67" s="5" t="n">
-        <v>-0.01154668567355666</v>
-      </c>
-      <c r="L67" s="3" t="n">
-        <v>0.003328027781797083</v>
+        <v>-0.01062363870738314</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>-0.003938064978072142</v>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N67" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="68" ht="21" customHeight="1">
-      <c r="A68" t="n">
+      <c r="A68" s="15" t="n">
         <v>67</v>
       </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>MGK</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr"/>
-      <c r="D68" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>Mega Cap Growth</t>
+      <c r="B68" s="16" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C68" s="15" t="inlineStr"/>
+      <c r="D68" s="13" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E68" s="15" t="inlineStr">
+        <is>
+          <t>Gold</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3616466367701576</v>
+        <v>0.5086788813886209</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1670323306255632</v>
+        <v>0.2451253481894149</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0.1641868566951896</v>
-      </c>
-      <c r="I68" s="3" t="n">
-        <v>0.1723466605135937</v>
+        <v>0.1927821482139032</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>-0.1409473928744905</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.03258203642121704</v>
+        <v>0.02657480314960625</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0.002444172869681127</v>
+        <v>0.04388328585726375</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.004852762766074714</v>
+        <v>-0.00841012139827424</v>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>MIXED_TRANSITION</t>
+        </is>
+      </c>
+      <c r="N68" s="7" t="inlineStr">
+        <is>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="69" ht="21" customHeight="1">
@@ -3608,40 +4284,54 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SCHG</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr"/>
-      <c r="D69" s="17" t="inlineStr">
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D69" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>S&amp;P 100</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3329623165294675</v>
+        <v>0.3622352829750961</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.157266693738918</v>
+        <v>0.1956732147943772</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1536838247180545</v>
+        <v>0.1925134514647706</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1664030893954545</v>
+        <v>0.1607244253454756</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.0538258501400164</v>
+        <v>0.0495456856083758</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.003105590062111752</v>
+        <v>0.002649666824072527</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.008649553571428603</v>
+        <v>-0.005542256452955807</v>
+      </c>
+      <c r="M69" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N69" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="70" ht="21" customHeight="1">
@@ -3650,40 +4340,50 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>VUG</t>
+          <t>RSP</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
-      <c r="D70" s="17" t="inlineStr">
+      <c r="D70" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Equal Weight</t>
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.3382947916462911</v>
+        <v>0.2689363759821515</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.14858002063956</v>
+        <v>0.1828297548786559</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.151566718262478</v>
+        <v>0.1805613142528613</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1610479579021633</v>
+        <v>0.1142536387079967</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.03046773231978617</v>
-      </c>
-      <c r="K70" s="5" t="n">
-        <v>-0.002593594948128164</v>
+        <v>0.05782676711006696</v>
+      </c>
+      <c r="K70" s="3" t="n">
+        <v>0.001921493274773534</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.004837983798379741</v>
+        <v>-0.004771642808452659</v>
+      </c>
+      <c r="M70" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N70" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="71" ht="21" customHeight="1">
@@ -3692,7 +4392,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>IAK</t>
+          <t>ARGT</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -3700,36 +4400,46 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D71" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D71" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Argentina Equity</t>
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1183230276739218</v>
+        <v>0.1716899341921996</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.1120594594296969</v>
+        <v>0.2220921249669161</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1420841480499133</v>
+        <v>0.1732895662995309</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1047984789697887</v>
+        <v>0.1180803678969065</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.09269660865573459</v>
-      </c>
-      <c r="K71" s="5" t="n">
-        <v>-0.02628938390527802</v>
+        <v>0.05643272307669922</v>
+      </c>
+      <c r="K71" s="3" t="n">
+        <v>0.04159464131374246</v>
       </c>
       <c r="L71" s="5" t="n">
-        <v>-0.01562182998579831</v>
+        <v>-0.0040289256198347</v>
+      </c>
+      <c r="M71" s="6" t="inlineStr">
+        <is>
+          <t>REACCELERATING</t>
+        </is>
+      </c>
+      <c r="N71" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="72" ht="21" customHeight="1">
@@ -3738,7 +4448,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SPGP</t>
+          <t>KBE</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3746,36 +4456,46 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D72" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D72" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>GARP Factor</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.2480499037549337</v>
+        <v>0.3200632269889565</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1103589276089303</v>
+        <v>0.1521994604977654</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1404287391249801</v>
+        <v>0.1656589580893892</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1225577590144293</v>
+        <v>0.1774918875405691</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.04863212152750895</v>
+        <v>0.08721738781999711</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.02636711131913561</v>
-      </c>
-      <c r="L72" s="5" t="n">
-        <v>-0.01070069752694991</v>
+        <v>-0.01154668567355666</v>
+      </c>
+      <c r="L72" s="3" t="n">
+        <v>0.003328027781797083</v>
+      </c>
+      <c r="M72" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N72" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="73" ht="21" customHeight="1">
@@ -3784,40 +4504,50 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>IGF</t>
+          <t>MGK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" s="16" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D73" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.2816548883262431</v>
+        <v>0.3616467935325718</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1209870409007974</v>
+        <v>0.1670324457894012</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1375228054869186</v>
-      </c>
-      <c r="I73" s="5" t="n">
-        <v>-0.01645445909090726</v>
-      </c>
-      <c r="J73" s="5" t="n">
-        <v>-0.002781775678525333</v>
-      </c>
-      <c r="K73" s="5" t="n">
-        <v>-0.01453664445790437</v>
-      </c>
-      <c r="L73" s="3" t="n">
-        <v>0.001076757421935026</v>
+        <v>0.1641869715782336</v>
+      </c>
+      <c r="I73" s="3" t="n">
+        <v>0.1723466605135937</v>
+      </c>
+      <c r="J73" s="3" t="n">
+        <v>0.03258203642121704</v>
+      </c>
+      <c r="K73" s="3" t="n">
+        <v>0.002444172869681127</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>-0.004852762766074714</v>
+      </c>
+      <c r="M73" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N73" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="74" ht="21" customHeight="1">
@@ -3826,40 +4556,50 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>BOTZ</t>
+          <t>SCHG</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
-      <c r="D74" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D74" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Robotics &amp; AI</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.1355254539420063</v>
+        <v>0.3329624119123964</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.08641465910040669</v>
+        <v>0.157266693738918</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1163326149421147</v>
-      </c>
-      <c r="I74" s="5" t="n">
-        <v>-0.00338102769308779</v>
-      </c>
-      <c r="J74" s="5" t="n">
-        <v>-0.05297577767964234</v>
-      </c>
-      <c r="K74" s="5" t="n">
-        <v>-0.0268002165674065</v>
-      </c>
-      <c r="L74" s="3" t="n">
-        <v>0.00390952247975429</v>
+        <v>0.1536838247180545</v>
+      </c>
+      <c r="I74" s="3" t="n">
+        <v>0.1664030893954545</v>
+      </c>
+      <c r="J74" s="3" t="n">
+        <v>0.0538258501400164</v>
+      </c>
+      <c r="K74" s="3" t="n">
+        <v>0.003105590062111752</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>-0.008649553571428603</v>
+      </c>
+      <c r="M74" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N74" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="75" ht="21" customHeight="1">
@@ -3868,44 +4608,50 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>XHE</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D75" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>VUG</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr"/>
+      <c r="D75" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Health Equipment</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.08358221911117791</v>
+        <v>0.3382947916462911</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1506191353843189</v>
+        <v>0.14858002063956</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.114585945900415</v>
+        <v>0.151566718262478</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1430651619949037</v>
+        <v>0.1610479579021633</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.1655530809205643</v>
-      </c>
-      <c r="K75" s="3" t="n">
-        <v>0.03232876712328769</v>
+        <v>0.03046773231978617</v>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>-0.002593594948128164</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.0008485362749257597</v>
+        <v>-0.004837983798379741</v>
+      </c>
+      <c r="M75" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N75" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="76" ht="21" customHeight="1">
@@ -3914,40 +4660,54 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>VONG</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr"/>
-      <c r="D76" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>IAK</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D76" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.282167726665377</v>
+        <v>0.1183230276739218</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1029624215674034</v>
+        <v>0.1120594594296969</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1039173673869422</v>
+        <v>0.1420841480499133</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.107207292510076</v>
+        <v>0.1047984789697887</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.006896950376516386</v>
+        <v>0.09269660865573459</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.0008650519031141446</v>
+        <v>-0.02628938390527802</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.0001573935626032474</v>
+        <v>-0.01562182998579831</v>
+      </c>
+      <c r="M76" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N76" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="77" ht="21" customHeight="1">
@@ -3956,40 +4716,54 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>IWF</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr"/>
-      <c r="D77" s="17" t="inlineStr">
+          <t>SPGP</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D77" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>GARP Factor</t>
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2794605910754389</v>
+        <v>0.2480499989697713</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1008470299915947</v>
+        <v>0.1103589276089303</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1016498517459035</v>
+        <v>0.1404287391249801</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1060872839288154</v>
+        <v>0.1225577590144293</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.006754300246448297</v>
+        <v>0.04863212152750895</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.0007287449392713308</v>
+        <v>-0.02636711131913561</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.0001620351616301585</v>
+        <v>-0.01070069752694991</v>
+      </c>
+      <c r="M77" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N77" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="78" ht="21" customHeight="1">
@@ -3998,40 +4772,50 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>VFH</t>
+          <t>IGF</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
       <c r="D78" s="18" t="inlineStr">
         <is>
-          <t>Financials &amp; Credit</t>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2023958124150707</v>
+        <v>0.2816548883262431</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.09416566425739115</v>
+        <v>0.1209870409007974</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.08908189559558255</v>
-      </c>
-      <c r="I78" s="3" t="n">
-        <v>0.161938755693714</v>
-      </c>
-      <c r="J78" s="3" t="n">
-        <v>0.1162403101899339</v>
-      </c>
-      <c r="K78" s="3" t="n">
-        <v>0.004667939741141769</v>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v>-0.007268152910755443</v>
+        <v>0.1375228054869186</v>
+      </c>
+      <c r="I78" s="5" t="n">
+        <v>-0.01645445909090726</v>
+      </c>
+      <c r="J78" s="5" t="n">
+        <v>-0.002781775678525333</v>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>-0.01453664445790437</v>
+      </c>
+      <c r="L78" s="3" t="n">
+        <v>0.001076757421935026</v>
+      </c>
+      <c r="M78" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N78" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="79" ht="21" customHeight="1">
@@ -4040,40 +4824,50 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>XLF</t>
+          <t>BOTZ</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
-      <c r="D79" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Financials</t>
+          <t>Robotics &amp; AI</t>
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1834073438369377</v>
+        <v>0.1355254539420063</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.09141033178882241</v>
+        <v>0.08641465910040669</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.08596267264564239</v>
-      </c>
-      <c r="I79" s="3" t="n">
-        <v>0.1588535330622238</v>
-      </c>
-      <c r="J79" s="3" t="n">
-        <v>0.1147901445543076</v>
-      </c>
-      <c r="K79" s="3" t="n">
-        <v>0.005016433143054888</v>
-      </c>
-      <c r="L79" s="5" t="n">
-        <v>-0.007855191256830651</v>
+        <v>0.1163326149421147</v>
+      </c>
+      <c r="I79" s="5" t="n">
+        <v>-0.00338102769308779</v>
+      </c>
+      <c r="J79" s="5" t="n">
+        <v>-0.05297577767964234</v>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>-0.0268002165674065</v>
+      </c>
+      <c r="L79" s="3" t="n">
+        <v>0.00390952247975429</v>
+      </c>
+      <c r="M79" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N79" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="80" ht="21" customHeight="1">
@@ -4082,40 +4876,54 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>XLP</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr"/>
-      <c r="D80" s="12" t="inlineStr">
+          <t>XHE</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D80" s="14" t="inlineStr">
         <is>
           <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Consumer Staples</t>
+          <t>Health Equipment</t>
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.06726952556642596</v>
+        <v>0.08358221911117791</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.07794880991652886</v>
+        <v>0.1506191353843189</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.08470351397488507</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>-0.001559200409543493</v>
+        <v>0.114585945900415</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.1430651619949037</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.02069589958058415</v>
-      </c>
-      <c r="K80" s="5" t="n">
-        <v>-0.006227235342497917</v>
+        <v>0.1655530809205643</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.03232876712328769</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.007975604034717421</v>
+        <v>-0.0008485362749257597</v>
+      </c>
+      <c r="M80" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N80" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="81" ht="21" customHeight="1">
@@ -4124,44 +4932,50 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D81" s="19" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>VNQ</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr"/>
+      <c r="D81" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F81" s="5" t="n">
-        <v>-0.07397090683998764</v>
+          <t>US Real Estate</t>
+        </is>
+      </c>
+      <c r="F81" s="3" t="n">
+        <v>0.07915144326221046</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.05537918871252212</v>
+        <v>0.09075576470765623</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.06631393298059951</v>
+        <v>0.1137023033944868</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.02150904745646987</v>
-      </c>
-      <c r="J81" s="5" t="n">
-        <v>-0.00366300366300365</v>
+        <v>0.04651865830450697</v>
+      </c>
+      <c r="J81" s="3" t="n">
+        <v>0.0007884748920772289</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.01025471386040355</v>
-      </c>
-      <c r="L81" s="3" t="n">
-        <v>0.003690036900369176</v>
+        <v>-0.02060383516931874</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>-0.006621146285950785</v>
+      </c>
+      <c r="M81" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N81" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="82" ht="21" customHeight="1">
@@ -4170,40 +4984,50 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>XLU</t>
+          <t>VONG</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
-      <c r="D82" s="12" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D82" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Utilities</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.1588461018389289</v>
+        <v>0.2821676279453948</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.05759147812473575</v>
+        <v>0.1029622754618329</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.06495632128716444</v>
-      </c>
-      <c r="I82" s="5" t="n">
-        <v>-0.06593495918679138</v>
-      </c>
-      <c r="J82" s="5" t="n">
-        <v>-0.02243323340929726</v>
+        <v>0.1039172211548733</v>
+      </c>
+      <c r="I82" s="3" t="n">
+        <v>0.1072072188939013</v>
+      </c>
+      <c r="J82" s="3" t="n">
+        <v>0.006896950376516386</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.006915629322268413</v>
-      </c>
-      <c r="L82" s="3" t="n">
-        <v>0.001161980013943742</v>
+        <v>-0.0008650519031141446</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>-0.0001573935626032474</v>
+      </c>
+      <c r="M82" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N82" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="83" ht="21" customHeight="1">
@@ -4212,90 +5036,102 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>EDEN</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D83" s="7" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>IWF</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr"/>
+      <c r="D83" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Denmark Equity</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.1234111050972515</v>
+        <v>0.2794604898724116</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1244551445901914</v>
+        <v>0.1008469550706432</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.06155451612850937</v>
+        <v>0.1016497767703139</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1475540776083568</v>
+        <v>0.1060873595664575</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.1098533609878889</v>
-      </c>
-      <c r="K83" s="3" t="n">
-        <v>0.05925331907689557</v>
+        <v>0.006754300246448297</v>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>-0.0007287449392713308</v>
       </c>
       <c r="L83" s="5" t="n">
-        <v>-0.007762290292963936</v>
+        <v>-0.0001620351616301585</v>
+      </c>
+      <c r="M83" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N83" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="84" ht="21" customHeight="1">
-      <c r="A84" s="13" t="n">
+      <c r="A84" t="n">
         <v>83</v>
       </c>
-      <c r="B84" s="14" t="inlineStr">
-        <is>
-          <t>UUP</t>
-        </is>
-      </c>
-      <c r="C84" s="13" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D84" s="19" t="inlineStr">
-        <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="E84" s="13" t="inlineStr">
-        <is>
-          <t>US Dollar Basket</t>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>VFH</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr"/>
+      <c r="D84" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.01891236935631846</v>
+        <v>0.2023956571142778</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.05442999889856925</v>
+        <v>0.09416553565621744</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.05856060074610636</v>
+        <v>0.08908176759192221</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.02220604295595185</v>
+        <v>0.161938755693714</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.002141327623126354</v>
-      </c>
-      <c r="K84" s="5" t="n">
-        <v>-0.003902092940759272</v>
-      </c>
-      <c r="L84" s="3" t="n">
-        <v>0.002499107461620742</v>
+        <v>0.1162403101899339</v>
+      </c>
+      <c r="K84" s="3" t="n">
+        <v>0.004667939741141769</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>-0.007268152910755443</v>
+      </c>
+      <c r="M84" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N84" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="85" ht="21" customHeight="1">
@@ -4304,44 +5140,50 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D85" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>XLF</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr"/>
+      <c r="D85" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
+          <t>Financials</t>
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1850516411129475</v>
+        <v>0.1834074357871016</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.04511907901795675</v>
+        <v>0.09141033178882241</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.05156011538341487</v>
+        <v>0.08596267264564239</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1083125074517182</v>
+        <v>0.1588536212363327</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.02400564571600916</v>
-      </c>
-      <c r="K85" s="5" t="n">
-        <v>-0.006125219349071176</v>
-      </c>
-      <c r="L85" s="3" t="n">
-        <v>0.001100550275137557</v>
+        <v>0.1147901445543076</v>
+      </c>
+      <c r="K85" s="3" t="n">
+        <v>0.005016433143054888</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>-0.007855191256830651</v>
+      </c>
+      <c r="M85" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N85" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="86" ht="21" customHeight="1">
@@ -4350,44 +5192,50 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>XRT</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D86" s="20" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+          <t>XLP</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr"/>
+      <c r="D86" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Retail</t>
+          <t>Consumer Staples</t>
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.243166914133915</v>
+        <v>0.06726942281909332</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.01522076775004222</v>
+        <v>0.07794880991652886</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.04141552668502424</v>
-      </c>
-      <c r="I86" s="3" t="n">
-        <v>0.05954298579977202</v>
+        <v>0.08470351397488507</v>
+      </c>
+      <c r="I86" s="5" t="n">
+        <v>-0.001559290331758945</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.06231378420201339</v>
+        <v>0.02069589958058415</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.02515303283249848</v>
-      </c>
-      <c r="L86" s="3" t="n">
-        <v>0.009915830739075204</v>
+        <v>-0.006227235342497917</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>-0.007975604034717421</v>
+      </c>
+      <c r="M86" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N86" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="87" ht="21" customHeight="1">
@@ -4396,7 +5244,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>USDU</t>
+          <t>EUO</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -4404,78 +5252,98 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D87" s="19" t="inlineStr">
+      <c r="D87" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>US Dollar Basket</t>
-        </is>
-      </c>
-      <c r="F87" s="3" t="n">
-        <v>0.006628101563802336</v>
+          <t>Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F87" s="5" t="n">
+        <v>-0.07397090683998764</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.03140311245850147</v>
+        <v>0.05537918871252212</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.04005384386303334</v>
+        <v>0.06631393298059951</v>
       </c>
       <c r="I87" s="3" t="n">
-        <v>0.008846153846153948</v>
+        <v>0.02150904745646987</v>
       </c>
       <c r="J87" s="5" t="n">
-        <v>-0.009441087613293098</v>
+        <v>-0.00366300366300365</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.008317580340264641</v>
+        <v>-0.01025471386040355</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>0.001909854851031456</v>
+        <v>0.003690036900369176</v>
+      </c>
+      <c r="M87" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N87" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="88" ht="21" customHeight="1">
-      <c r="A88" s="13" t="n">
+      <c r="A88" t="n">
         <v>87</v>
       </c>
-      <c r="B88" s="14" t="inlineStr">
-        <is>
-          <t>HYG</t>
-        </is>
-      </c>
-      <c r="C88" s="13" t="inlineStr"/>
-      <c r="D88" s="18" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E88" s="13" t="inlineStr">
-        <is>
-          <t>High Yield Credit</t>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr"/>
+      <c r="D88" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Utilities</t>
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.08599359141460416</v>
+        <v>0.1588459829087914</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.03894933654575516</v>
+        <v>0.05759147812473575</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.0372025706220056</v>
-      </c>
-      <c r="I88" s="3" t="n">
-        <v>0.02370734091802928</v>
-      </c>
-      <c r="J88" s="3" t="n">
-        <v>0.011595073349292</v>
-      </c>
-      <c r="K88" s="3" t="n">
-        <v>0.001684112605604193</v>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v>-0.000631233430122391</v>
+        <v>0.06495632128716444</v>
+      </c>
+      <c r="I88" s="5" t="n">
+        <v>-0.06593495918679138</v>
+      </c>
+      <c r="J88" s="5" t="n">
+        <v>-0.02243323340929726</v>
+      </c>
+      <c r="K88" s="5" t="n">
+        <v>-0.006915629322268413</v>
+      </c>
+      <c r="L88" s="3" t="n">
+        <v>0.001161980013943742</v>
+      </c>
+      <c r="M88" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N88" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="89" ht="21" customHeight="1">
@@ -4484,7 +5352,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>VCR</t>
+          <t>EDEN</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -4492,124 +5360,158 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="20" t="inlineStr">
-        <is>
-          <t>Consumer</t>
+      <c r="D89" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Consumer Discretionary</t>
+          <t>Denmark Equity</t>
         </is>
       </c>
       <c r="F89" s="3" t="n">
-        <v>0.1207504478549839</v>
-      </c>
-      <c r="G89" s="5" t="n">
-        <v>-0.003725312607587683</v>
+        <v>0.1234111050972515</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.1244551445901914</v>
       </c>
       <c r="H89" s="3" t="n">
-        <v>0.02209850590178353</v>
+        <v>0.06155451612850937</v>
       </c>
       <c r="I89" s="3" t="n">
-        <v>0.03465868209422918</v>
+        <v>0.1475540776083568</v>
       </c>
       <c r="J89" s="3" t="n">
-        <v>0.01177211397773026</v>
-      </c>
-      <c r="K89" s="5" t="n">
-        <v>-0.0252654889526398</v>
+        <v>0.1098533609878889</v>
+      </c>
+      <c r="K89" s="3" t="n">
+        <v>0.05925331907689557</v>
       </c>
       <c r="L89" s="5" t="n">
-        <v>-0.009461947626841383</v>
+        <v>-0.007762290292963936</v>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>ACCELERATING</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="13" t="n">
+      <c r="A90" s="15" t="n">
         <v>89</v>
       </c>
-      <c r="B90" s="14" t="inlineStr">
-        <is>
-          <t>SHY</t>
-        </is>
-      </c>
-      <c r="C90" s="13" t="inlineStr"/>
+      <c r="B90" s="16" t="inlineStr">
+        <is>
+          <t>UUP</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D90" s="21" t="inlineStr">
         <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E90" s="13" t="inlineStr">
-        <is>
-          <t>Short Treasury</t>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E90" s="15" t="inlineStr">
+        <is>
+          <t>US Dollar Basket</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
-        <v>0.04850417915220362</v>
+        <v>0.01891236935631846</v>
       </c>
       <c r="G90" s="3" t="n">
-        <v>0.02265642412273938</v>
+        <v>0.05442999889856925</v>
       </c>
       <c r="H90" s="3" t="n">
-        <v>0.02098221377412379</v>
+        <v>0.05856060074610636</v>
       </c>
       <c r="I90" s="3" t="n">
-        <v>0.005218810442326527</v>
+        <v>0.02220604295595185</v>
       </c>
       <c r="J90" s="3" t="n">
-        <v>0.006897335925965864</v>
-      </c>
-      <c r="K90" s="3" t="n">
-        <v>0.001639803638132653</v>
-      </c>
-      <c r="L90" s="5" t="n">
-        <v>-0.0002447680822420528</v>
+        <v>0.002141327623126354</v>
+      </c>
+      <c r="K90" s="5" t="n">
+        <v>-0.003902092940759272</v>
+      </c>
+      <c r="L90" s="3" t="n">
+        <v>0.002499107461620742</v>
+      </c>
+      <c r="M90" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N90" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="91" ht="21" customHeight="1">
-      <c r="A91" s="13" t="n">
+      <c r="A91" t="n">
         <v>90</v>
       </c>
-      <c r="B91" s="14" t="inlineStr">
-        <is>
-          <t>TIP</t>
-        </is>
-      </c>
-      <c r="C91" s="13" t="inlineStr">
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D91" s="15" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
-        </is>
-      </c>
-      <c r="E91" s="13" t="inlineStr">
-        <is>
-          <t>TIPS</t>
+      <c r="D91" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Mid Growth</t>
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.04386089868234411</v>
+        <v>0.1850515697269821</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.007972464616699426</v>
+        <v>0.04511930110844431</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.007030170081206544</v>
-      </c>
-      <c r="I91" s="5" t="n">
-        <v>-0.007196235880658097</v>
-      </c>
-      <c r="J91" s="5" t="n">
-        <v>-0.004055951357985865</v>
-      </c>
-      <c r="K91" s="3" t="n">
-        <v>0.0009357162908205652</v>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v>-0.0002803738317757043</v>
+        <v>0.05156033884263911</v>
+      </c>
+      <c r="I91" s="3" t="n">
+        <v>0.1083125074517182</v>
+      </c>
+      <c r="J91" s="3" t="n">
+        <v>0.02400564571600916</v>
+      </c>
+      <c r="K91" s="5" t="n">
+        <v>-0.006125219349071176</v>
+      </c>
+      <c r="L91" s="3" t="n">
+        <v>0.001100550275137557</v>
+      </c>
+      <c r="M91" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N91" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="92" ht="21" customHeight="1">
@@ -4618,40 +5520,54 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IEF</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr"/>
-      <c r="D92" s="21" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+          <t>XRT</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D92" s="22" t="inlineStr">
+        <is>
+          <t>Consumer</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Intermediate Treasury</t>
+          <t>Retail</t>
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.03410040564887895</v>
-      </c>
-      <c r="G92" s="5" t="n">
-        <v>-0.004237417365766438</v>
-      </c>
-      <c r="H92" s="5" t="n">
-        <v>-0.0002733221818355114</v>
-      </c>
-      <c r="I92" s="5" t="n">
-        <v>-0.02395147462680114</v>
-      </c>
-      <c r="J92" s="5" t="n">
-        <v>-0.00442454298082029</v>
+        <v>0.2431670487492301</v>
+      </c>
+      <c r="G92" s="3" t="n">
+        <v>0.01522076775004222</v>
+      </c>
+      <c r="H92" s="3" t="n">
+        <v>0.04141552668502424</v>
+      </c>
+      <c r="I92" s="3" t="n">
+        <v>0.05954308358488691</v>
+      </c>
+      <c r="J92" s="3" t="n">
+        <v>0.06231378420201339</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.003965178955294357</v>
-      </c>
-      <c r="L92" s="5" t="n">
-        <v>-0.0003250975292587999</v>
+        <v>-0.02515303283249848</v>
+      </c>
+      <c r="L92" s="3" t="n">
+        <v>0.009915830739075204</v>
+      </c>
+      <c r="M92" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N92" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="93" ht="21" customHeight="1">
@@ -4660,82 +5576,106 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>IWP</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr"/>
-      <c r="D93" s="17" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>USDU</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D93" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
+          <t>US Dollar Basket</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.1238706429350735</v>
-      </c>
-      <c r="G93" s="5" t="n">
-        <v>-0.01818290450622762</v>
-      </c>
-      <c r="H93" s="5" t="n">
-        <v>-0.01136521832519133</v>
+        <v>0.006628101563802336</v>
+      </c>
+      <c r="G93" s="3" t="n">
+        <v>0.03140311245850147</v>
+      </c>
+      <c r="H93" s="3" t="n">
+        <v>0.04005384386303334</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.04690526361528691</v>
-      </c>
-      <c r="J93" s="3" t="n">
-        <v>0.004459535524643954</v>
+        <v>0.008846153846153948</v>
+      </c>
+      <c r="J93" s="5" t="n">
+        <v>-0.009441087613293098</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.006896061424712108</v>
-      </c>
-      <c r="L93" s="5" t="n">
-        <v>-0.0008583077033116338</v>
+        <v>-0.008317580340264641</v>
+      </c>
+      <c r="L93" s="3" t="n">
+        <v>0.001909854851031456</v>
+      </c>
+      <c r="M93" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N93" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+        </is>
       </c>
     </row>
     <row r="94" ht="21" customHeight="1">
-      <c r="A94" s="13" t="n">
+      <c r="A94" s="15" t="n">
         <v>93</v>
       </c>
-      <c r="B94" s="14" t="inlineStr">
-        <is>
-          <t>TLT</t>
-        </is>
-      </c>
-      <c r="C94" s="13" t="inlineStr"/>
-      <c r="D94" s="21" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
-        </is>
-      </c>
-      <c r="E94" s="13" t="inlineStr">
-        <is>
-          <t>Long Treasury</t>
-        </is>
-      </c>
-      <c r="F94" s="5" t="n">
-        <v>-0.03069234351705008</v>
-      </c>
-      <c r="G94" s="5" t="n">
-        <v>-0.01436964022052767</v>
-      </c>
-      <c r="H94" s="5" t="n">
-        <v>-0.01442961553683053</v>
-      </c>
-      <c r="I94" s="5" t="n">
-        <v>-0.04890675336892869</v>
-      </c>
-      <c r="J94" s="5" t="n">
-        <v>-0.02229630903445345</v>
+      <c r="B94" s="16" t="inlineStr">
+        <is>
+          <t>HYG</t>
+        </is>
+      </c>
+      <c r="C94" s="15" t="inlineStr"/>
+      <c r="D94" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E94" s="15" t="inlineStr">
+        <is>
+          <t>High Yield Credit</t>
+        </is>
+      </c>
+      <c r="F94" s="3" t="n">
+        <v>0.08599347774646438</v>
+      </c>
+      <c r="G94" s="3" t="n">
+        <v>0.0389494405792199</v>
+      </c>
+      <c r="H94" s="3" t="n">
+        <v>0.03720267448056069</v>
+      </c>
+      <c r="I94" s="3" t="n">
+        <v>0.02370744192142005</v>
+      </c>
+      <c r="J94" s="3" t="n">
+        <v>0.011595073349292</v>
       </c>
       <c r="K94" s="3" t="n">
-        <v>6.08534075783318e-05</v>
-      </c>
-      <c r="L94" s="3" t="n">
-        <v>0.001705860850493401</v>
+        <v>0.001684112605604193</v>
+      </c>
+      <c r="L94" s="5" t="n">
+        <v>-0.000631233430122391</v>
+      </c>
+      <c r="M94" s="6" t="inlineStr">
+        <is>
+          <t>COOLING</t>
+        </is>
+      </c>
+      <c r="N94" s="7" t="inlineStr">
+        <is>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
+        </is>
       </c>
     </row>
     <row r="95" ht="21" customHeight="1">
@@ -4744,94 +5684,538 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
+          <t>VCR</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D95" s="22" t="inlineStr">
+        <is>
+          <t>Consumer</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Consumer Discretionary</t>
+        </is>
+      </c>
+      <c r="F95" s="3" t="n">
+        <v>0.1207504478549839</v>
+      </c>
+      <c r="G95" s="5" t="n">
+        <v>-0.003725234405933087</v>
+      </c>
+      <c r="H95" s="3" t="n">
+        <v>0.02209858613045479</v>
+      </c>
+      <c r="I95" s="3" t="n">
+        <v>0.03465868209422918</v>
+      </c>
+      <c r="J95" s="3" t="n">
+        <v>0.01177211397773026</v>
+      </c>
+      <c r="K95" s="5" t="n">
+        <v>-0.0252654889526398</v>
+      </c>
+      <c r="L95" s="5" t="n">
+        <v>-0.009461947626841383</v>
+      </c>
+      <c r="M95" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N95" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="21" customHeight="1">
+      <c r="A96" s="15" t="n">
+        <v>95</v>
+      </c>
+      <c r="B96" s="16" t="inlineStr">
+        <is>
+          <t>SHY</t>
+        </is>
+      </c>
+      <c r="C96" s="15" t="inlineStr"/>
+      <c r="D96" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E96" s="15" t="inlineStr">
+        <is>
+          <t>Short Treasury</t>
+        </is>
+      </c>
+      <c r="F96" s="3" t="n">
+        <v>0.04850417915220362</v>
+      </c>
+      <c r="G96" s="3" t="n">
+        <v>0.02265632644836857</v>
+      </c>
+      <c r="H96" s="3" t="n">
+        <v>0.02098211625965751</v>
+      </c>
+      <c r="I96" s="3" t="n">
+        <v>0.005218716070506169</v>
+      </c>
+      <c r="J96" s="3" t="n">
+        <v>0.006897335925965864</v>
+      </c>
+      <c r="K96" s="3" t="n">
+        <v>0.001639803638132653</v>
+      </c>
+      <c r="L96" s="5" t="n">
+        <v>-0.0002447680822420528</v>
+      </c>
+      <c r="M96" s="6" t="inlineStr">
+        <is>
+          <t>STEADY_POSITIVE</t>
+        </is>
+      </c>
+      <c r="N96" s="7" t="inlineStr">
+        <is>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="21" customHeight="1">
+      <c r="A97" s="15" t="n">
+        <v>96</v>
+      </c>
+      <c r="B97" s="16" t="inlineStr">
+        <is>
+          <t>TIP</t>
+        </is>
+      </c>
+      <c r="C97" s="15" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D97" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
+        </is>
+      </c>
+      <c r="E97" s="15" t="inlineStr">
+        <is>
+          <t>TIPS</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0.0438608209658331</v>
+      </c>
+      <c r="G97" s="3" t="n">
+        <v>0.007972464616699426</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0.007030170081206544</v>
+      </c>
+      <c r="I97" s="5" t="n">
+        <v>-0.007196306180585532</v>
+      </c>
+      <c r="J97" s="5" t="n">
+        <v>-0.004055951357985865</v>
+      </c>
+      <c r="K97" s="3" t="n">
+        <v>0.0009357162908205652</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>-0.0002803738317757043</v>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>MIXED_TRANSITION</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="21" customHeight="1">
+      <c r="A98" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>LQD</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Investment Grade Credit</t>
+        </is>
+      </c>
+      <c r="F98" s="3" t="n">
+        <v>0.03808619015196246</v>
+      </c>
+      <c r="G98" s="5" t="n">
+        <v>-0.0001862028403939453</v>
+      </c>
+      <c r="H98" s="3" t="n">
+        <v>0.003940580247929093</v>
+      </c>
+      <c r="I98" s="5" t="n">
+        <v>-0.01940789168962065</v>
+      </c>
+      <c r="J98" s="5" t="n">
+        <v>-0.01307892706561686</v>
+      </c>
+      <c r="K98" s="5" t="n">
+        <v>-0.004110584998271327</v>
+      </c>
+      <c r="L98" s="5" t="n">
+        <v>-0.0001895734597155974</v>
+      </c>
+      <c r="M98" s="6" t="inlineStr">
+        <is>
+          <t>FAST_REVERSAL</t>
+        </is>
+      </c>
+      <c r="N98" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="21" customHeight="1">
+      <c r="A99" t="n">
+        <v>98</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>IEF</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Intermediate Treasury</t>
+        </is>
+      </c>
+      <c r="F99" s="3" t="n">
+        <v>0.03410022876874885</v>
+      </c>
+      <c r="G99" s="5" t="n">
+        <v>-0.004237581373844668</v>
+      </c>
+      <c r="H99" s="5" t="n">
+        <v>-0.0002734868428240222</v>
+      </c>
+      <c r="I99" s="5" t="n">
+        <v>-0.02395147462680114</v>
+      </c>
+      <c r="J99" s="5" t="n">
+        <v>-0.00442454298082029</v>
+      </c>
+      <c r="K99" s="5" t="n">
+        <v>-0.003965178955294357</v>
+      </c>
+      <c r="L99" s="5" t="n">
+        <v>-0.0003250975292587999</v>
+      </c>
+      <c r="M99" s="6" t="inlineStr">
+        <is>
+          <t>BROAD_WEAKNESS</t>
+        </is>
+      </c>
+      <c r="N99" s="7" t="inlineStr">
+        <is>
+          <t>Long and 1m momentum negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="21" customHeight="1">
+      <c r="A100" t="n">
+        <v>99</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>FXE</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr"/>
+      <c r="D100" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Euro</t>
+        </is>
+      </c>
+      <c r="F100" s="3" t="n">
+        <v>0.08907073158488443</v>
+      </c>
+      <c r="G100" s="3" t="n">
+        <v>0.004564932100218577</v>
+      </c>
+      <c r="H100" s="5" t="n">
+        <v>-0.004175371193174904</v>
+      </c>
+      <c r="I100" s="3" t="n">
+        <v>0.00478065136126693</v>
+      </c>
+      <c r="J100" s="3" t="n">
+        <v>0.01032956152742326</v>
+      </c>
+      <c r="K100" s="3" t="n">
+        <v>0.008776950318919008</v>
+      </c>
+      <c r="L100" s="5" t="n">
+        <v>-0.001211782252050653</v>
+      </c>
+      <c r="M100" s="6" t="inlineStr">
+        <is>
+          <t>RECOVERY</t>
+        </is>
+      </c>
+      <c r="N100" s="7" t="inlineStr">
+        <is>
+          <t>Weak long trend; 3m and 1m now positive; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="101" ht="21" customHeight="1">
+      <c r="A101" t="n">
+        <v>100</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>Mid Growth</t>
+        </is>
+      </c>
+      <c r="F101" s="3" t="n">
+        <v>0.1238706429350735</v>
+      </c>
+      <c r="G101" s="5" t="n">
+        <v>-0.0181827992092316</v>
+      </c>
+      <c r="H101" s="5" t="n">
+        <v>-0.01136511229701853</v>
+      </c>
+      <c r="I101" s="3" t="n">
+        <v>0.04690526361528691</v>
+      </c>
+      <c r="J101" s="3" t="n">
+        <v>0.004459535524643954</v>
+      </c>
+      <c r="K101" s="5" t="n">
+        <v>-0.006896061424712108</v>
+      </c>
+      <c r="L101" s="5" t="n">
+        <v>-0.0008583077033116338</v>
+      </c>
+      <c r="M101" s="6" t="inlineStr">
+        <is>
+          <t>BROAD_WEAKNESS</t>
+        </is>
+      </c>
+      <c r="N101" s="7" t="inlineStr">
+        <is>
+          <t>Long and 1m momentum negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="102" ht="21" customHeight="1">
+      <c r="A102" s="15" t="n">
+        <v>101</v>
+      </c>
+      <c r="B102" s="16" t="inlineStr">
+        <is>
+          <t>TLT</t>
+        </is>
+      </c>
+      <c r="C102" s="15" t="inlineStr"/>
+      <c r="D102" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
+        </is>
+      </c>
+      <c r="E102" s="15" t="inlineStr">
+        <is>
+          <t>Long Treasury</t>
+        </is>
+      </c>
+      <c r="F102" s="5" t="n">
+        <v>-0.03069225632261574</v>
+      </c>
+      <c r="G102" s="5" t="n">
+        <v>-0.01436964022052767</v>
+      </c>
+      <c r="H102" s="5" t="n">
+        <v>-0.01442961553683053</v>
+      </c>
+      <c r="I102" s="5" t="n">
+        <v>-0.04890683731716705</v>
+      </c>
+      <c r="J102" s="5" t="n">
+        <v>-0.02229630903445345</v>
+      </c>
+      <c r="K102" s="3" t="n">
+        <v>6.08534075783318e-05</v>
+      </c>
+      <c r="L102" s="3" t="n">
+        <v>0.001705860850493401</v>
+      </c>
+      <c r="M102" s="6" t="inlineStr">
+        <is>
+          <t>REBOUND</t>
+        </is>
+      </c>
+      <c r="N102" s="7" t="inlineStr">
+        <is>
+          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d up.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="21" customHeight="1">
+      <c r="A103" t="n">
+        <v>102</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
           <t>INDA</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr">
+      <c r="C103" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D95" s="7" t="inlineStr">
+      <c r="D103" s="9" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="E95" t="inlineStr">
+      <c r="E103" t="inlineStr">
         <is>
           <t>India Equity</t>
         </is>
       </c>
-      <c r="F95" s="3" t="n">
+      <c r="F103" s="3" t="n">
         <v>0.02002861230329045</v>
       </c>
-      <c r="G95" s="5" t="n">
+      <c r="G103" s="5" t="n">
         <v>-0.05096025860429754</v>
       </c>
-      <c r="H95" s="5" t="n">
+      <c r="H103" s="5" t="n">
         <v>-0.04696710401216975</v>
       </c>
-      <c r="I95" s="5" t="n">
+      <c r="I103" s="5" t="n">
         <v>-0.001600320064012895</v>
       </c>
-      <c r="J95" s="3" t="n">
+      <c r="J103" s="3" t="n">
         <v>0.05428812843261488</v>
       </c>
-      <c r="K95" s="5" t="n">
+      <c r="K103" s="5" t="n">
         <v>-0.00418994413407825</v>
       </c>
-      <c r="L95" s="5" t="n">
+      <c r="L103" s="5" t="n">
         <v>-0.0002003205128205954</v>
       </c>
-    </row>
-    <row r="96" ht="21" customHeight="1">
-      <c r="A96" t="n">
-        <v>95</v>
-      </c>
-      <c r="B96" t="inlineStr">
+      <c r="M103" s="6" t="inlineStr">
+        <is>
+          <t>BROAD_WEAKNESS</t>
+        </is>
+      </c>
+      <c r="N103" s="7" t="inlineStr">
+        <is>
+          <t>Long and 1m momentum negative; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="21" customHeight="1">
+      <c r="A104" t="n">
+        <v>103</v>
+      </c>
+      <c r="B104" t="inlineStr">
         <is>
           <t>IPAY</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr">
+      <c r="C104" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
-      <c r="E96" t="inlineStr">
+      <c r="E104" t="inlineStr">
         <is>
           <t>Digital Payments</t>
         </is>
       </c>
-      <c r="F96" s="5" t="n">
+      <c r="F104" s="5" t="n">
         <v>-0.07926140795289716</v>
       </c>
-      <c r="G96" s="5" t="n">
+      <c r="G104" s="5" t="n">
         <v>-0.1302675899374276</v>
       </c>
-      <c r="H96" s="5" t="n">
+      <c r="H104" s="5" t="n">
         <v>-0.1319593472026728</v>
       </c>
-      <c r="I96" s="3" t="n">
+      <c r="I104" s="3" t="n">
         <v>0.1264241893076248</v>
       </c>
-      <c r="J96" s="3" t="n">
+      <c r="J104" s="3" t="n">
         <v>0.1908732916377112</v>
       </c>
-      <c r="K96" s="3" t="n">
+      <c r="K104" s="3" t="n">
         <v>0.001948937828883057</v>
       </c>
-      <c r="L96" s="5" t="n">
+      <c r="L104" s="5" t="n">
         <v>-0.01058506543495008</v>
       </c>
+      <c r="M104" s="6" t="inlineStr">
+        <is>
+          <t>RECOVERY</t>
+        </is>
+      </c>
+      <c r="N104" s="7" t="inlineStr">
+        <is>
+          <t>Weak long trend; 3m and 1m now positive; 1d down.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L96"/>
+  <autoFilter ref="A1:N104"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -91,17 +91,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE7F3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00C6E0B4"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCFCE7"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE7F3"/>
       </patternFill>
     </fill>
     <fill>
@@ -195,10 +195,10 @@
     <xf numFmtId="164" fontId="2" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="2" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="14" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.780701320170908</v>
+        <v>1.780701579081476</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.311035712738891</v>
+        <v>1.311035533903143</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.338421257721972</v>
+        <v>1.338421076767038</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0.6006411526826776</v>
@@ -844,14 +844,14 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D5" s="11" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Marine Shipping</t>
+          <t>AI Infrastructure</t>
         </is>
       </c>
       <c r="F5" s="3" t="n">
@@ -860,7 +860,7 @@
       <c r="G5" s="3" t="n">
         <v>1.315772143562726</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="11" t="n">
         <v>1.253210405004939</v>
       </c>
       <c r="I5" s="3" t="n">
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.536413562056367</v>
+        <v>1.536413184393991</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.139025366436778</v>
+        <v>1.139025500733548</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.191116431606419</v>
+        <v>1.191116569173679</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.6086899115826985</v>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.514480634235029</v>
+        <v>1.51448089526162</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>1.078725564356369</v>
@@ -1120,7 +1120,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D10" s="13" t="inlineStr">
+      <c r="D10" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1176,14 +1176,14 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D11" s="13" t="inlineStr">
         <is>
           <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Dry Bulk Freight</t>
+          <t>Dry Bulk Freight Futures</t>
         </is>
       </c>
       <c r="F11" s="3" t="n">
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8740965847392723</v>
+        <v>0.8740969119018904</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7605620540331652</v>
+        <v>0.7605621983949915</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.660502028863464</v>
+        <v>0.6605021650206104</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0.32234519097106</v>
@@ -1340,7 +1340,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D14" s="13" t="inlineStr">
+      <c r="D14" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1396,7 +1396,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D15" s="13" t="inlineStr">
+      <c r="D15" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1452,24 +1452,24 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D16" s="13" t="inlineStr">
+      <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Global Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
         <v>0.8320938409509537</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6156588443481128</v>
+        <v>0.6156586912938948</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.545877083625423</v>
+        <v>0.5458769371817545</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.1435659925999622</v>
@@ -1504,14 +1504,14 @@
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" s="13" t="inlineStr">
+      <c r="D17" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Silver</t>
+          <t>Silver Bullion</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
@@ -1560,14 +1560,14 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="11" t="inlineStr">
+      <c r="D18" s="13" t="inlineStr">
         <is>
           <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Shipping</t>
+          <t>Global Shipping</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.7050811834036075</v>
+        <v>0.7050813018463387</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.43361890634831</v>
@@ -1688,7 +1688,7 @@
         <v>0.4186917551982716</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.367444342737236</v>
+        <v>0.3674444950892</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.03995183621570808</v>
@@ -1776,7 +1776,7 @@
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" s="13" t="inlineStr">
+      <c r="D22" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.763198887475063</v>
+        <v>1.763199180820205</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0.6674520561524815</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6695536361980647</v>
+        <v>0.669553783211627</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0.3999388670037975</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6565619157488216</v>
+        <v>0.6565620216387955</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0.3219858657217809</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5545609482485079</v>
+        <v>0.5545611222542985</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.5137823270846265</v>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.6640376940542052</v>
+        <v>0.6640378682720638</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3969984349012043</v>
+        <v>0.3969983121244756</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3777604750901629</v>
+        <v>0.377760354004183</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.3522537144371283</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Autonomous/EV</t>
+          <t>Autonomous &amp; Electric Vehicles</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
@@ -2119,7 +2119,7 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6675999509793089</v>
+        <v>0.6675997834651819</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>0.386934394446645</v>
@@ -2164,7 +2164,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D29" s="13" t="inlineStr">
+      <c r="D29" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.083086170660991</v>
+        <v>1.083085891569514</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.4595268951477454</v>
@@ -2220,7 +2220,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D30" s="13" t="inlineStr">
+      <c r="D30" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5836572413313341</v>
+        <v>0.5836573472915509</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4824404283365684</v>
+        <v>0.4824403354880675</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3473148914530824</v>
+        <v>0.3473148070677907</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.1454616489492566</v>
@@ -2272,7 +2272,7 @@
         </is>
       </c>
       <c r="C31" s="15" t="inlineStr"/>
-      <c r="D31" s="13" t="inlineStr">
+      <c r="D31" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -2292,7 +2292,7 @@
         <v>0.3464804739729828</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.1480210704850085</v>
+        <v>0.1480211489675201</v>
       </c>
       <c r="J31" s="3" t="n">
         <v>0.1188137155182061</v>
@@ -2331,7 +2331,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Broad Commodities</t>
+          <t>Broad Commodity Futures</t>
         </is>
       </c>
       <c r="F32" s="3" t="n">
@@ -2447,13 +2447,13 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5446504306874409</v>
+        <v>0.5446502867422172</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1788139751629894</v>
+        <v>0.1788140589983993</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3185918935369341</v>
+        <v>0.3185919873131313</v>
       </c>
       <c r="I34" s="5" t="n">
         <v>-0.09382844759776487</v>
@@ -2495,11 +2495,11 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>U.S. Industrials</t>
+          <t>U.S. Industrial Renaissance</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5426744133949961</v>
+        <v>0.5426742463901268</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0.1826760187692307</v>
@@ -2544,7 +2544,7 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D36" s="13" t="inlineStr">
+      <c r="D36" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
@@ -2558,10 +2558,10 @@
         <v>0.6189414385293674</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.4755468894899149</v>
+        <v>0.4755470636917334</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.292486539191916</v>
+        <v>0.2924866917817843</v>
       </c>
       <c r="I36" s="3" t="n">
         <v>0.1723325472199564</v>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.6394296452852541</v>
+        <v>0.639429509880159</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0.3561770077768018</v>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5589921137519795</v>
+        <v>0.5589923614532029</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2867870870193954</v>
+        <v>0.2867870026424868</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2814584202150137</v>
+        <v>0.2814583361875154</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>0.2717691990035427</v>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Small Cap Value</t>
+          <t>Small Cap Cash Flow</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
         <v>0.5455962817152487</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.333699585374126</v>
+        <v>0.3336997035251041</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.275338593485343</v>
+        <v>0.275338706466185</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.2708930358411168</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4418595202594637</v>
+        <v>0.441859627426104</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.2641467152831039</v>
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.433793337924715</v>
+        <v>0.4337934514140818</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2722682033671824</v>
+        <v>0.2722680246487612</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2678493268287148</v>
+        <v>0.2678491487310233</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.1885752537866485</v>
@@ -2983,7 +2983,7 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4906183303287333</v>
+        <v>0.4906181800510183</v>
       </c>
       <c r="G44" s="3" t="n">
         <v>0.1422404481184474</v>
@@ -2992,7 +2992,7 @@
         <v>0.2656739046368983</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.06723819317242319</v>
+        <v>-0.06723825201656219</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>-0.01604546874855806</v>
@@ -3031,7 +3031,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Developed ex-US Hedged</t>
+          <t>Developed ex-US Currency-Hedged</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4632541378975084</v>
+        <v>0.4632542486309303</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2933335603447877</v>
+        <v>0.2933336468535885</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2645772284716119</v>
+        <v>0.2645773130569522</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0.1377823091565502</v>
@@ -3135,7 +3135,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fundamental Equity</t>
+          <t>Fundamental Large Cap</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
@@ -3187,7 +3187,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>U.S. Infrastructure Development</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
@@ -3246,10 +3246,10 @@
         <v>0.3105532265789543</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.3029248468195411</v>
+        <v>0.3029247537752928</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2617404407419122</v>
+        <v>0.2617403506387177</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>0.1363270661486402</v>
@@ -3295,13 +3295,13 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4731443902293495</v>
+        <v>0.4731442217620947</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.3020608478069629</v>
+        <v>0.3020609794165454</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.260593097973469</v>
+        <v>0.2605932253915781</v>
       </c>
       <c r="I50" s="3" t="n">
         <v>0.1656716357696715</v>
@@ -3347,17 +3347,17 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Russell 2000 Growth</t>
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4141402494669566</v>
+        <v>0.4141400878183397</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2273007193415577</v>
+        <v>0.2273005975859326</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2492435064781673</v>
+        <v>0.2492433825456852</v>
       </c>
       <c r="I51" s="3" t="n">
         <v>0.1802404984418828</v>
@@ -3511,13 +3511,13 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4270662639822698</v>
+        <v>0.4270660758554026</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.1263249615315105</v>
+        <v>0.1263250787213801</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.2407439762699701</v>
+        <v>0.240744105364707</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>-0.08523357081287031</v>
@@ -3563,13 +3563,13 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3344499248844144</v>
+        <v>0.3344500799148888</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1718847060957682</v>
+        <v>0.1718848256547709</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2353364426214075</v>
+        <v>0.2353365686539364</v>
       </c>
       <c r="I55" s="3" t="n">
         <v>0.03680666519160902</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2103107652399336</v>
+        <v>0.2103109042181897</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0.2796271277588027</v>
@@ -3628,7 +3628,7 @@
         <v>0.2293427066468481</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1482060199965338</v>
+        <v>0.1482061450779253</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>0.1359983485299427</v>
@@ -3671,7 +3671,7 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4408768111376706</v>
+        <v>0.4408766595046709</v>
       </c>
       <c r="G57" s="3" t="n">
         <v>0.2290597370000531</v>
@@ -3723,7 +3723,7 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1755440900895964</v>
+        <v>0.1755442130769598</v>
       </c>
       <c r="G58" s="3" t="n">
         <v>0.2693337995003819</v>
@@ -3782,13 +3782,13 @@
         <v>0.3210082260220046</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1655925945476298</v>
+        <v>0.1655927289181596</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2045766351741902</v>
+        <v>0.2045767740388342</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.07441851932386845</v>
+        <v>0.07441840515245657</v>
       </c>
       <c r="J59" s="5" t="n">
         <v>-0.06150276039675151</v>
@@ -3840,7 +3840,7 @@
         <v>0.2035902296914684</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1446617683774252</v>
+        <v>0.1446618828053032</v>
       </c>
       <c r="J60" s="3" t="n">
         <v>0.02244173753769618</v>
@@ -3879,11 +3879,11 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cash Flow Factor</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3296584193612484</v>
+        <v>0.3296585139524517</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0.2664747739759108</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3442858721527491</v>
+        <v>0.3442857163683846</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>0.2007777249572409</v>
@@ -3983,17 +3983,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>US Large Blend</t>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3447654126339179</v>
+        <v>0.3447652700247767</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2007974289088261</v>
+        <v>0.2007975426253341</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1980201038652212</v>
+        <v>0.1980202173187142</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>0.1520055073493269</v>
@@ -4042,10 +4042,10 @@
         <v>0.3756669252199267</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2270838943447613</v>
+        <v>0.2270838008564444</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1975252328273418</v>
+        <v>0.1975251415910222</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0.1293008922112591</v>
@@ -4091,7 +4091,7 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.3435590842611607</v>
+        <v>0.3435592273137664</v>
       </c>
       <c r="G65" s="3" t="n">
         <v>0.199660912694537</v>
@@ -4100,7 +4100,7 @@
         <v>0.1971219972480989</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.151555666126193</v>
+        <v>0.1515557712139433</v>
       </c>
       <c r="J65" s="3" t="n">
         <v>0.0469448480365231</v>
@@ -4132,14 +4132,14 @@
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="13" t="inlineStr">
+      <c r="D66" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F66" s="3" t="n">
@@ -4236,14 +4236,14 @@
         </is>
       </c>
       <c r="C68" s="15" t="inlineStr"/>
-      <c r="D68" s="13" t="inlineStr">
+      <c r="D68" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
       <c r="E68" s="15" t="inlineStr">
         <is>
-          <t>Gold</t>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F68" s="3" t="n">
@@ -4303,7 +4303,7 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3622352829750961</v>
+        <v>0.3622351348000985</v>
       </c>
       <c r="G69" s="3" t="n">
         <v>0.1956732147943772</v>
@@ -4364,7 +4364,7 @@
         <v>0.1805613142528613</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1142536387079967</v>
+        <v>0.1142535522024297</v>
       </c>
       <c r="J70" s="3" t="n">
         <v>0.05782676711006696</v>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.3200632269889565</v>
+        <v>0.3200631311227193</v>
       </c>
       <c r="G72" s="3" t="n">
         <v>0.1521994604977654</v>
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.3616467935325718</v>
+        <v>0.3616466367701576</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1670324457894012</v>
+        <v>0.1670322154617478</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1641869715782336</v>
+        <v>0.1641867418121681</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>0.1723466605135937</v>
@@ -4571,13 +4571,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3329624119123964</v>
+        <v>0.3329623165294675</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.157266693738918</v>
+        <v>0.1572665499479109</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1536838247180545</v>
+        <v>0.1536836813722207</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>0.1664030893954545</v>
@@ -4623,7 +4623,7 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3382947916462911</v>
+        <v>0.3382946371579334</v>
       </c>
       <c r="G75" s="3" t="n">
         <v>0.14858002063956</v>
@@ -4688,7 +4688,7 @@
         <v>0.1420841480499133</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1047984789697887</v>
+        <v>0.1047983510186623</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0.09269660865573459</v>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2480499989697713</v>
+        <v>0.2480500941846229</v>
       </c>
       <c r="G77" s="3" t="n">
         <v>0.1103589276089303</v>
@@ -4842,10 +4842,10 @@
         <v>0.1355254539420063</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.08641465910040669</v>
+        <v>0.08641453385772246</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1163326149421147</v>
+        <v>0.1163324862504662</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>-0.00338102769308779</v>
@@ -4943,17 +4943,17 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>US Real Estate</t>
+          <t>U.S. Equity REITs</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.07915144326221046</v>
+        <v>0.07915153579447609</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.09075576470765623</v>
+        <v>0.09075567017467434</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.1137023033944868</v>
+        <v>0.1137022068727878</v>
       </c>
       <c r="I81" s="3" t="n">
         <v>0.04651865830450697</v>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.2821676279453948</v>
+        <v>0.282167726665377</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.1029622754618329</v>
+        <v>0.1029623485146134</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.1039172211548733</v>
+        <v>0.103917294270903</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0.1072072188939013</v>
@@ -5047,20 +5047,20 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Russell 1000 Growth</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2794604898724116</v>
+        <v>0.2794606922784824</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1008469550706432</v>
+        <v>0.1008470299915947</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.1016497767703139</v>
+        <v>0.1016498517459035</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1060873595664575</v>
+        <v>0.1060872839288154</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0.006754300246448297</v>
@@ -5106,10 +5106,10 @@
         <v>0.2023956571142778</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.09416553565621744</v>
+        <v>0.09416579285859505</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.08908176759192221</v>
+        <v>0.08908202359927309</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>0.161938755693714</v>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1834074357871016</v>
+        <v>0.1834073438369377</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.09141033178882241</v>
+        <v>0.09141025357922961</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.08596267264564239</v>
+        <v>0.08596259482642443</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1588536212363327</v>
+        <v>0.1588535330622238</v>
       </c>
       <c r="J85" s="3" t="n">
         <v>0.1147901445543076</v>
@@ -5216,7 +5216,7 @@
         <v>0.08470351397488507</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.001559290331758945</v>
+        <v>-0.001559200409543493</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>0.02069589958058415</v>
@@ -5259,7 +5259,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Inverse Euro</t>
+          <t>2x Inverse Euro</t>
         </is>
       </c>
       <c r="F87" s="5" t="n">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="E90" s="15" t="inlineStr">
         <is>
-          <t>US Dollar Basket</t>
+          <t>US Dollar Index Bullish</t>
         </is>
       </c>
       <c r="F90" s="3" t="n">
@@ -5483,16 +5483,16 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1850515697269821</v>
+        <v>0.1850516411129475</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.04511930110844431</v>
+        <v>0.04511907901795675</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05156033884263911</v>
+        <v>0.05156011538341487</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.1083125074517182</v>
+        <v>0.1083126323317054</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>0.02400564571600916</v>
@@ -5548,7 +5548,7 @@
         <v>0.04141552668502424</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.05954308358488691</v>
+        <v>0.05954298579977202</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0.06231378420201339</v>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>US Dollar Basket</t>
+          <t>Bloomberg Dollar Bullish</t>
         </is>
       </c>
       <c r="F93" s="3" t="n">
@@ -5643,17 +5643,17 @@
       </c>
       <c r="E94" s="15" t="inlineStr">
         <is>
-          <t>High Yield Credit</t>
+          <t>High Yield Corporate Bonds</t>
         </is>
       </c>
       <c r="F94" s="3" t="n">
         <v>0.08599347774646438</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0389494405792199</v>
+        <v>0.03894954461270528</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.03720267448056069</v>
+        <v>0.03720277833913666</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>0.02370744192142005</v>
@@ -5703,13 +5703,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1207504478549839</v>
+        <v>0.1207505468186056</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.003725234405933087</v>
+        <v>-0.003725312607587683</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02209858613045479</v>
+        <v>0.02209850590178353</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>0.03465868209422918</v>
@@ -5751,20 +5751,20 @@
       </c>
       <c r="E96" s="15" t="inlineStr">
         <is>
-          <t>Short Treasury</t>
+          <t>1-3 Year Treasury</t>
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04850417915220362</v>
+        <v>0.04850438450073868</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.02265632644836857</v>
+        <v>0.02265652179712885</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.02098211625965751</v>
+        <v>0.02098231128860872</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.005218716070506169</v>
+        <v>0.005218810442326527</v>
       </c>
       <c r="J96" s="3" t="n">
         <v>0.006897335925965864</v>
@@ -5820,7 +5820,7 @@
         <v>0.007030170081206544</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.007196306180585532</v>
+        <v>-0.007196235880658097</v>
       </c>
       <c r="J97" s="5" t="n">
         <v>-0.004055951357985865</v>
@@ -5859,11 +5859,11 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Investment Grade Credit</t>
+          <t>Investment Grade Corporate Bonds</t>
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03808619015196246</v>
+        <v>0.03808611220723557</v>
       </c>
       <c r="G98" s="5" t="n">
         <v>-0.0001862028403939453</v>
@@ -5872,7 +5872,7 @@
         <v>0.003940580247929093</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01940789168962065</v>
+        <v>-0.01940796123955024</v>
       </c>
       <c r="J98" s="5" t="n">
         <v>-0.01307892706561686</v>
@@ -5911,17 +5911,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Intermediate Treasury</t>
+          <t>7-10 Year Treasury</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03410022876874885</v>
+        <v>0.03410040564887895</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.004237581373844668</v>
+        <v>-0.004237499369812214</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.0002734868428240222</v>
+        <v>-0.0002734045123364837</v>
       </c>
       <c r="I99" s="5" t="n">
         <v>-0.02395147462680114</v>
@@ -5963,17 +5963,17 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Euro</t>
+          <t>Euro Currency</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.08907073158488443</v>
+        <v>0.08907039377687376</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.004564932100218577</v>
+        <v>0.004565003954714042</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.004175371193174904</v>
+        <v>-0.004175299963855794</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0.00478065136126693</v>
@@ -6015,17 +6015,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Mid Growth</t>
+          <t>Russell Midcap Growth</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.1238706429350735</v>
+        <v>0.1238705739496417</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.0181827992092316</v>
+        <v>-0.01818290450622762</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01136511229701853</v>
+        <v>-0.01136521832519133</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0.04690526361528691</v>
@@ -6067,17 +6067,17 @@
       </c>
       <c r="E102" s="15" t="inlineStr">
         <is>
-          <t>Long Treasury</t>
+          <t>20+ Year Treasury</t>
         </is>
       </c>
       <c r="F102" s="5" t="n">
         <v>-0.03069225632261574</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.01436964022052767</v>
+        <v>-0.01436955006474394</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.01442961553683053</v>
+        <v>-0.01442952538653286</v>
       </c>
       <c r="I102" s="5" t="n">
         <v>-0.04890683731716705</v>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -907,13 +907,13 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.536413184393991</v>
+        <v>1.536413562056367</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.139025500733548</v>
+        <v>1.139025366436778</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.191116569173679</v>
+        <v>1.191116431606419</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.6086899115826985</v>
@@ -963,16 +963,16 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.51448089526162</v>
+        <v>1.514480373208492</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.078725564356369</v>
+        <v>1.078725742751273</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.132718436157833</v>
+        <v>1.13271861918637</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5634508846038371</v>
+        <v>0.5634509855190464</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>-0.0397431750266648</v>
@@ -1134,10 +1134,10 @@
         <v>1.306341954937121</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8568220940264304</v>
+        <v>0.856822239098896</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7632231863526957</v>
+        <v>0.7632233241123314</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.1378121605773759</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8740969119018904</v>
+        <v>0.8740965847392723</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.7605621983949915</v>
@@ -1351,7 +1351,7 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8365070246181665</v>
+        <v>0.8365068511745186</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>0.5887106436810075</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.7050813018463387</v>
+        <v>0.7050811834036075</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.43361890634831</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.763199180820205</v>
+        <v>1.763198887475063</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0.6674520561524815</v>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.669553783211627</v>
+        <v>0.6695536361980647</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3999388670037975</v>
+        <v>0.3999390737344237</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3812607569259066</v>
+        <v>0.381260960898314</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0.3528745980372852</v>
@@ -2007,16 +2007,16 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.6640378682720638</v>
+        <v>0.6640375198363835</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3969983121244756</v>
+        <v>0.3969981893477683</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.377760354004183</v>
+        <v>0.3777602329182244</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3522537144371283</v>
+        <v>0.352253829479843</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>0.05321266058152796</v>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6675997834651819</v>
+        <v>0.6675999509793089</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.386934394446645</v>
+        <v>0.3869342785743668</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3720417271500722</v>
+        <v>0.3720416125220107</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.3458530565264364</v>
@@ -2231,7 +2231,7 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5836573472915509</v>
+        <v>0.5836572413313341</v>
       </c>
       <c r="G30" s="3" t="n">
         <v>0.4824403354880675</v>
@@ -2240,7 +2240,7 @@
         <v>0.3473148070677907</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1454616489492566</v>
+        <v>0.1454615380799074</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>0.119690129527162</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5446502867422172</v>
+        <v>0.5446505746326915</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.1788140589983993</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5426742463901268</v>
+        <v>0.5426744133949961</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0.1826760187692307</v>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.639429509880159</v>
+        <v>0.6394293744750865</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0.3561770077768018</v>
@@ -2718,10 +2718,10 @@
         <v>0.5589923614532029</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2867870026424868</v>
+        <v>0.2867870870193954</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2814583361875154</v>
+        <v>0.2814584202150137</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>0.2717691990035427</v>
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5455962817152487</v>
+        <v>0.5455964403920479</v>
       </c>
       <c r="G40" s="3" t="n">
         <v>0.3336997035251041</v>
@@ -2823,7 +2823,7 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.441859627426104</v>
+        <v>0.4418595202594637</v>
       </c>
       <c r="G41" s="3" t="n">
         <v>0.2641467152831039</v>
@@ -2878,10 +2878,10 @@
         <v>0.4337934514140818</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2722680246487612</v>
+        <v>0.2722682033671824</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2678491487310233</v>
+        <v>0.2678493268287148</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.1885752537866485</v>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4508514368114691</v>
+        <v>0.4508515421590822</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0.2534754983218976</v>
@@ -2992,7 +2992,7 @@
         <v>0.2656739046368983</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.06723825201656219</v>
+        <v>-0.06723819317242319</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>-0.01604546874855806</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3443246450418633</v>
+        <v>0.3443244994462167</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0.2690509475067042</v>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4632542486309303</v>
+        <v>0.4632541378975084</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2933336468535885</v>
+        <v>0.2933335603447877</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2645773130569522</v>
+        <v>0.2645772284716119</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0.1377823091565502</v>
@@ -3139,16 +3139,16 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3920427187433075</v>
+        <v>0.3920428319794607</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2816843601883992</v>
+        <v>0.2816844561819696</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2636214065828029</v>
+        <v>0.2636215012235226</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1653206156032558</v>
+        <v>0.1653205362489003</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>0.06586853355928812</v>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4141400878183397</v>
+        <v>0.4141402494669566</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0.2273005975859326</v>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4428249635689041</v>
+        <v>0.4428250519323516</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2558848667790528</v>
+        <v>0.2558850006773479</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2483561255753448</v>
+        <v>0.2483562586709505</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>0.2015967755690107</v>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4270660758554026</v>
+        <v>0.4270661699188298</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.1263250787213801</v>
@@ -3520,7 +3520,7 @@
         <v>0.240744105364707</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.08523357081287031</v>
+        <v>-0.08523349351222964</v>
       </c>
       <c r="J54" s="5" t="n">
         <v>-0.0304502302686378</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3344500799148888</v>
+        <v>0.3344502349453995</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0.1718848256547709</v>
@@ -3628,7 +3628,7 @@
         <v>0.2293427066468481</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1482061450779253</v>
+        <v>0.1482060199965338</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>0.1359983485299427</v>
@@ -3680,7 +3680,7 @@
         <v>0.221764915662316</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1879272347053123</v>
+        <v>0.1879271316382964</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>0.03263482295051578</v>
@@ -3779,13 +3779,13 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3210082260220046</v>
+        <v>0.3210081397258455</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1655927289181596</v>
+        <v>0.1655924601771304</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2045767740388342</v>
+        <v>0.2045764963095777</v>
       </c>
       <c r="I59" s="3" t="n">
         <v>0.07441840515245657</v>
@@ -3840,7 +3840,7 @@
         <v>0.2035902296914684</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1446618828053032</v>
+        <v>0.1446617683774252</v>
       </c>
       <c r="J60" s="3" t="n">
         <v>0.02244173753769618</v>
@@ -3883,16 +3883,16 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3296585139524517</v>
+        <v>0.3296584193612484</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.2664747739759108</v>
+        <v>0.2664748597909989</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2029491727456918</v>
+        <v>0.2029492542563476</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1315250033629372</v>
+        <v>0.1315250718642484</v>
       </c>
       <c r="J61" s="3" t="n">
         <v>0.1223255352865984</v>
@@ -3935,7 +3935,7 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3442857163683846</v>
+        <v>0.3442858721527491</v>
       </c>
       <c r="G62" s="3" t="n">
         <v>0.2007777249572409</v>
@@ -3987,13 +3987,13 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3447652700247767</v>
+        <v>0.3447651274156656</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2007975426253341</v>
+        <v>0.2007974289088261</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1980202173187142</v>
+        <v>0.1980201038652212</v>
       </c>
       <c r="I63" s="3" t="n">
         <v>0.1520055073493269</v>
@@ -4042,10 +4042,10 @@
         <v>0.3756669252199267</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2270838008564444</v>
+        <v>0.2270838943447613</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1975251415910222</v>
+        <v>0.1975252328273418</v>
       </c>
       <c r="I64" s="3" t="n">
         <v>0.1293008922112591</v>
@@ -4091,13 +4091,13 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.3435592273137664</v>
+        <v>0.3435590842611607</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.199660912694537</v>
+        <v>0.1996610267455765</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1971219972480989</v>
+        <v>0.1971221110577652</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>0.1515557712139433</v>
@@ -4519,13 +4519,13 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.3616466367701576</v>
+        <v>0.3616464800077797</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1670322154617478</v>
+        <v>0.1670323306255632</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1641867418121681</v>
+        <v>0.1641868566951896</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>0.1723466605135937</v>
@@ -4571,13 +4571,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3329623165294675</v>
+        <v>0.3329624119123964</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.1572665499479109</v>
+        <v>0.15726662184341</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1536836813722207</v>
+        <v>0.1536837530451332</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>0.1664030893954545</v>
@@ -4623,13 +4623,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3382946371579334</v>
+        <v>0.3382944826696117</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.14858002063956</v>
+        <v>0.1485799068394213</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.151566718262478</v>
+        <v>0.1515666041664203</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0.1610479579021633</v>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1183230276739218</v>
+        <v>0.1183231587769082</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0.1120594594296969</v>
@@ -4735,13 +4735,13 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2480500941846229</v>
+        <v>0.2480499989697713</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1103589276089303</v>
+        <v>0.1103588522443257</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1404287391249801</v>
+        <v>0.1404286617194144</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>0.1225577590144293</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.07915153579447609</v>
+        <v>0.07915144326221046</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0.09075567017467434</v>
@@ -5002,10 +5002,10 @@
         <v>0.282167726665377</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.1029623485146134</v>
+        <v>0.1029624215674034</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.103917294270903</v>
+        <v>0.1039173673869422</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0.1072072188939013</v>
@@ -5106,10 +5106,10 @@
         <v>0.2023956571142778</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.09416579285859505</v>
+        <v>0.09416566425739115</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.08908202359927309</v>
+        <v>0.08908189559558255</v>
       </c>
       <c r="I84" s="3" t="n">
         <v>0.161938755693714</v>
@@ -5158,10 +5158,10 @@
         <v>0.1834073438369377</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.09141025357922961</v>
+        <v>0.09141017536964791</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.08596259482642443</v>
+        <v>0.0859625170072178</v>
       </c>
       <c r="I85" s="3" t="n">
         <v>0.1588535330622238</v>
@@ -5210,13 +5210,13 @@
         <v>0.06726942281909332</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.07794880991652886</v>
+        <v>0.07794870510268992</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.08470351397488507</v>
+        <v>0.08470340850425551</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.001559200409543493</v>
+        <v>-0.001559290331758945</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>0.02069589958058415</v>
@@ -5486,13 +5486,13 @@
         <v>0.1850516411129475</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.04511907901795675</v>
+        <v>0.04511930110844431</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05156011538341487</v>
+        <v>0.05156033884263911</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.1083126323317054</v>
+        <v>0.1083125074517182</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>0.02400564571600916</v>
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.08599347774646438</v>
+        <v>0.08599359141460416</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.03894954461270528</v>
+        <v>0.0389494405792199</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.03720277833913666</v>
+        <v>0.03720267448056069</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>0.02370744192142005</v>
@@ -5703,7 +5703,7 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1207505468186056</v>
+        <v>0.1207504478549839</v>
       </c>
       <c r="G95" s="5" t="n">
         <v>-0.003725312607587683</v>
@@ -5755,13 +5755,13 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04850438450073868</v>
+        <v>0.04850448717503664</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.02265652179712885</v>
+        <v>0.02265622877401685</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.02098231128860872</v>
+        <v>0.02098201874521033</v>
       </c>
       <c r="I96" s="3" t="n">
         <v>0.005218810442326527</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03808611220723557</v>
+        <v>0.03808603426252022</v>
       </c>
       <c r="G98" s="5" t="n">
         <v>-0.0001862028403939453</v>
@@ -5915,19 +5915,19 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03410040564887895</v>
+        <v>0.03410031720880613</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.004237499369812214</v>
+        <v>-0.004237581373844668</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.0002734045123364837</v>
+        <v>-0.0002734868428240222</v>
       </c>
       <c r="I99" s="5" t="n">
         <v>-0.02395147462680114</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.00442454298082029</v>
+        <v>-0.004424624954043832</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>-0.003965178955294357</v>
@@ -5967,19 +5967,19 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.08907039377687376</v>
+        <v>0.08907047822885672</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.004565003954714042</v>
+        <v>0.004564932100218577</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.004175299963855794</v>
+        <v>-0.004175371193174904</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0.00478065136126693</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.01032956152742326</v>
+        <v>0.01032948884590601</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0.008776950318919008</v>
@@ -6019,13 +6019,13 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.1238705739496417</v>
+        <v>0.1238706429350735</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.01818290450622762</v>
+        <v>-0.0181830098032012</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01136521832519133</v>
+        <v>-0.01136532435334159</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0.04690526361528691</v>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03069225632261574</v>
+        <v>-0.03069234351705008</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>-0.01436955006474394</v>
@@ -6080,7 +6080,7 @@
         <v>-0.01442952538653286</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04890683731716705</v>
+        <v>-0.04890666942067545</v>
       </c>
       <c r="J102" s="5" t="n">
         <v>-0.02229630903445345</v>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.780701579081476</v>
+        <v>1.780701061260387</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.311035533903143</v>
+        <v>1.311035712738891</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.338421076767038</v>
+        <v>1.338421257721972</v>
       </c>
       <c r="I2" s="3" t="n">
         <v>0.6006411526826776</v>
@@ -750,10 +750,10 @@
         <v>1.547923635217787</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.159521333839812</v>
+        <v>1.159521203031256</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>1.296873242205359</v>
+        <v>1.296873103076994</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0.5248488768743713</v>
@@ -910,10 +910,10 @@
         <v>1.536413562056367</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.139025366436778</v>
+        <v>1.139025500733548</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.191116431606419</v>
+        <v>1.191116569173679</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.6086899115826985</v>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.514480373208492</v>
+        <v>1.51448089526162</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>1.078725742751273</v>
@@ -972,7 +972,7 @@
         <v>1.13271861918637</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5634509855190464</v>
+        <v>0.5634508846038371</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>-0.0397431750266648</v>
@@ -1239,13 +1239,13 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8740965847392723</v>
+        <v>0.8740967483205673</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7605621983949915</v>
+        <v>0.7605620540331652</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.6605021650206104</v>
+        <v>0.660502028863464</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0.32234519097106</v>
@@ -1466,10 +1466,10 @@
         <v>0.8320938409509537</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6156586912938948</v>
+        <v>0.6156588443481128</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.5458769371817545</v>
+        <v>0.545877083625423</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>0.1435659925999622</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.113680672641568</v>
+        <v>1.113680840244623</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0.7272218190073159</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.7050811834036075</v>
+        <v>0.7050813018463387</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.43361890634831</v>
@@ -1688,7 +1688,7 @@
         <v>0.4186917551982716</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.3674444950892</v>
+        <v>0.367444342737236</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.03995183621570808</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6695536361980647</v>
+        <v>0.6695534891845289</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0.3999390737344237</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6565620216387955</v>
+        <v>0.6565618098588615</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0.3219858657217809</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5545611222542985</v>
+        <v>0.5545607742427558</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.5137823270846265</v>
@@ -2010,13 +2010,13 @@
         <v>0.6640375198363835</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3969981893477683</v>
+        <v>0.3969983121244756</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3777602329182244</v>
+        <v>0.377760354004183</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.352253829479843</v>
+        <v>0.3522537144371283</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>0.05321266058152796</v>
@@ -2122,10 +2122,10 @@
         <v>0.6675999509793089</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3869342785743668</v>
+        <v>0.3869345103189425</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3720416125220107</v>
+        <v>0.3720418417781526</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.3458530565264364</v>
@@ -2175,16 +2175,16 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.083085891569514</v>
+        <v>1.083086170660991</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4595268951477454</v>
+        <v>0.4595267581364666</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3577709735251533</v>
+        <v>0.3577708460660856</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.07839751281140894</v>
+        <v>0.07839758760940141</v>
       </c>
       <c r="J29" s="3" t="n">
         <v>0.0008529035749034186</v>
@@ -2234,10 +2234,10 @@
         <v>0.5836572413313341</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4824403354880675</v>
+        <v>0.4824404283365684</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3473148070677907</v>
+        <v>0.3473148914530824</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.1454615380799074</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5662267707694086</v>
+        <v>0.5662266246922192</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.4830732318209987</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5446505746326915</v>
+        <v>0.544650718577969</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.1788140589983993</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5426744133949961</v>
+        <v>0.5426745803999016</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0.1826760187692307</v>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.6394293744750865</v>
+        <v>0.639429509880159</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0.3561770077768018</v>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5589923614532029</v>
+        <v>0.5589924853038439</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2867870870193954</v>
+        <v>0.2867870026424868</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2814584202150137</v>
+        <v>0.2814583361875154</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>0.2717691990035427</v>
@@ -2774,10 +2774,10 @@
         <v>0.5455964403920479</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.3336997035251041</v>
+        <v>0.333699585374126</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.275338706466185</v>
+        <v>0.275338593485343</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.2708930358411168</v>
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4508515421590822</v>
+        <v>0.4508514368114691</v>
       </c>
       <c r="G43" s="3" t="n">
         <v>0.2534754983218976</v>
@@ -2986,13 +2986,13 @@
         <v>0.4906181800510183</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1422404481184474</v>
+        <v>0.1422405363607471</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2656739046368983</v>
+        <v>0.2656740024148891</v>
       </c>
       <c r="I44" s="5" t="n">
-        <v>-0.06723819317242319</v>
+        <v>-0.06723825201656219</v>
       </c>
       <c r="J44" s="5" t="n">
         <v>-0.01604546874855806</v>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3443244994462167</v>
+        <v>0.3443246450418633</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2690509475067042</v>
+        <v>0.2690510772539778</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2655667527194627</v>
+        <v>0.2655668821105137</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>0.129270688345682</v>
@@ -3087,13 +3087,13 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4632541378975084</v>
+        <v>0.4632542486309303</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2933335603447877</v>
+        <v>0.2933336468535885</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2645772284716119</v>
+        <v>0.2645773130569522</v>
       </c>
       <c r="I46" s="3" t="n">
         <v>0.1377823091565502</v>
@@ -3139,16 +3139,16 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3920428319794607</v>
+        <v>0.3920427187433075</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2816844561819696</v>
+        <v>0.2816843601883992</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2636215012235226</v>
+        <v>0.2636214065828029</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1653205362489003</v>
+        <v>0.1653206156032558</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>0.06586853355928812</v>
@@ -3246,10 +3246,10 @@
         <v>0.3105532265789543</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.3029247537752928</v>
+        <v>0.3029248468195411</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2617403506387177</v>
+        <v>0.2617404407419122</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>0.1363270661486402</v>
@@ -3351,7 +3351,7 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4141402494669566</v>
+        <v>0.4141404111156104</v>
       </c>
       <c r="G51" s="3" t="n">
         <v>0.2273005975859326</v>
@@ -3406,10 +3406,10 @@
         <v>0.4444172082838467</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2566442358520458</v>
+        <v>0.256644154465927</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2489618429487046</v>
+        <v>0.2489617620601334</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>0.2018418315921782</v>
@@ -3455,13 +3455,13 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4428250519323516</v>
+        <v>0.442824875205468</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2558850006773479</v>
+        <v>0.2558848667790528</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2483562586709505</v>
+        <v>0.2483561255753448</v>
       </c>
       <c r="I53" s="3" t="n">
         <v>0.2015967755690107</v>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4270661699188298</v>
+        <v>0.4270660758554026</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.1263250787213801</v>
@@ -3520,7 +3520,7 @@
         <v>0.240744105364707</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.08523349351222964</v>
+        <v>-0.08523357081287031</v>
       </c>
       <c r="J54" s="5" t="n">
         <v>-0.0304502302686378</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3344502349453995</v>
+        <v>0.3344499248844144</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0.1718848256547709</v>
@@ -3619,7 +3619,7 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2103109042181897</v>
+        <v>0.2103107652399336</v>
       </c>
       <c r="G56" s="3" t="n">
         <v>0.2796271277588027</v>
@@ -3628,7 +3628,7 @@
         <v>0.2293427066468481</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1482060199965338</v>
+        <v>0.1482061450779253</v>
       </c>
       <c r="J56" s="3" t="n">
         <v>0.1359983485299427</v>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4408766595046709</v>
+        <v>0.4408768111376706</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2290597370000531</v>
+        <v>0.2290598473281396</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.221764915662316</v>
+        <v>0.2217650253355736</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0.1879271316382964</v>
@@ -3726,10 +3726,10 @@
         <v>0.1755442130769598</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2693337995003819</v>
+        <v>0.269333942895492</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2175091474356246</v>
+        <v>0.217509284976166</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0.1323776016142966</v>
@@ -3779,16 +3779,16 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3210081397258455</v>
+        <v>0.3210082260220046</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1655924601771304</v>
+        <v>0.1655925945476298</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2045764963095777</v>
+        <v>0.2045766351741902</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.07441840515245657</v>
+        <v>0.07441851932386845</v>
       </c>
       <c r="J59" s="5" t="n">
         <v>-0.06150276039675151</v>
@@ -3834,10 +3834,10 @@
         <v>0.319154269748813</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1944635763351985</v>
+        <v>0.194463451733716</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2035902296914684</v>
+        <v>0.2035901041379315</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>0.1446617683774252</v>
@@ -3886,10 +3886,10 @@
         <v>0.3296584193612484</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.2664748597909989</v>
+        <v>0.2664747739759108</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2029492542563476</v>
+        <v>0.2029491727456918</v>
       </c>
       <c r="I61" s="3" t="n">
         <v>0.1315250718642484</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3447651274156656</v>
+        <v>0.3447652700247767</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0.2007974289088261</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3756669252199267</v>
+        <v>0.3756670427192907</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0.2270838943447613</v>
@@ -4094,10 +4094,10 @@
         <v>0.3435590842611607</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1996610267455765</v>
+        <v>0.199660912694537</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1971221110577652</v>
+        <v>0.1971219972480989</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>0.1515557712139433</v>
@@ -4198,10 +4198,10 @@
         <v>0.2597787759939749</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1805259008585947</v>
+        <v>0.1805259963985431</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1932020483249079</v>
+        <v>0.1932021448907368</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0.1248023884404867</v>
@@ -4303,13 +4303,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3622351348000985</v>
+        <v>0.3622352829750961</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1956732147943772</v>
+        <v>0.1956731006391765</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1925134514647706</v>
+        <v>0.192513337611244</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>0.1607244253454756</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2689363759821515</v>
+        <v>0.2689364881725527</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>0.1828297548786559</v>
@@ -4364,7 +4364,7 @@
         <v>0.1805613142528613</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1142535522024297</v>
+        <v>0.1142536387079967</v>
       </c>
       <c r="J70" s="3" t="n">
         <v>0.05782676711006696</v>
@@ -4470,10 +4470,10 @@
         <v>0.3200631311227193</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1521994604977654</v>
+        <v>0.1521995335328601</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1656589580893892</v>
+        <v>0.1656590319776483</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0.1774918875405691</v>
@@ -4519,7 +4519,7 @@
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.3616464800077797</v>
+        <v>0.3616466367701576</v>
       </c>
       <c r="G73" s="3" t="n">
         <v>0.1670323306255632</v>
@@ -4571,13 +4571,13 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3329624119123964</v>
+        <v>0.3329623165294675</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.15726662184341</v>
+        <v>0.157266693738918</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1536837530451332</v>
+        <v>0.1536838247180545</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>0.1664030893954545</v>
@@ -4623,13 +4623,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3382944826696117</v>
+        <v>0.3382946371579334</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1485799068394213</v>
+        <v>0.14858002063956</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1515666041664203</v>
+        <v>0.151566718262478</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0.1610479579021633</v>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1183231587769082</v>
+        <v>0.1183228965709657</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0.1120594594296969</v>
@@ -4688,7 +4688,7 @@
         <v>0.1420841480499133</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1047983510186623</v>
+        <v>0.1047984789697887</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0.09269660865573459</v>
@@ -4738,10 +4738,10 @@
         <v>0.2480499989697713</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1103588522443257</v>
+        <v>0.1103589276089303</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1404286617194144</v>
+        <v>0.1404287391249801</v>
       </c>
       <c r="I77" s="3" t="n">
         <v>0.1225577590144293</v>
@@ -4999,13 +4999,13 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.282167726665377</v>
+        <v>0.2821676279453948</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.1029624215674034</v>
+        <v>0.1029623485146134</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.1039173673869422</v>
+        <v>0.103917294270903</v>
       </c>
       <c r="I82" s="3" t="n">
         <v>0.1072072188939013</v>
@@ -5051,16 +5051,16 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2794606922784824</v>
+        <v>0.2794605910754389</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1008470299915947</v>
+        <v>0.1008469550706432</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.1016498517459035</v>
+        <v>0.1016497767703139</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1060872839288154</v>
+        <v>0.1060873595664575</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0.006754300246448297</v>
@@ -5103,7 +5103,7 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.2023956571142778</v>
+        <v>0.2023957347646692</v>
       </c>
       <c r="G84" s="3" t="n">
         <v>0.09416566425739115</v>
@@ -5155,16 +5155,16 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1834073438369377</v>
+        <v>0.1834072518867882</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.09141017536964791</v>
+        <v>0.09141033178882241</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.0859625170072178</v>
+        <v>0.08596267264564239</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1588535330622238</v>
+        <v>0.1588536212363327</v>
       </c>
       <c r="J85" s="3" t="n">
         <v>0.1147901445543076</v>
@@ -5207,13 +5207,13 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.06726942281909332</v>
+        <v>0.06726952556642596</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.07794870510268992</v>
+        <v>0.07794880991652886</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.08470340850425551</v>
+        <v>0.08470351397488507</v>
       </c>
       <c r="I86" s="5" t="n">
         <v>-0.001559290331758945</v>
@@ -5315,7 +5315,7 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1588459829087914</v>
+        <v>0.1588458639786785</v>
       </c>
       <c r="G88" s="3" t="n">
         <v>0.05759147812473575</v>
@@ -5486,10 +5486,10 @@
         <v>0.1850516411129475</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.04511930110844431</v>
+        <v>0.04511907901795675</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05156033884263911</v>
+        <v>0.05156011538341487</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>0.1083125074517182</v>
@@ -5647,16 +5647,16 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.08599359141460416</v>
+        <v>0.08599336407834857</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.0389494405792199</v>
+        <v>0.03894933654575516</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.03720267448056069</v>
+        <v>0.0372025706220056</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.02370744192142005</v>
+        <v>0.02370734091802928</v>
       </c>
       <c r="J94" s="3" t="n">
         <v>0.011595073349292</v>
@@ -5703,13 +5703,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1207504478549839</v>
+        <v>0.1207505468186056</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.003725312607587683</v>
+        <v>-0.003725390809229623</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02209850590178353</v>
+        <v>0.02209842567312537</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>0.03465868209422918</v>
@@ -5758,13 +5758,13 @@
         <v>0.04850448717503664</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.02265622877401685</v>
+        <v>0.02265642412273938</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.02098201874521033</v>
+        <v>0.02098221377412379</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.005218810442326527</v>
+        <v>0.005218904814164871</v>
       </c>
       <c r="J96" s="3" t="n">
         <v>0.006897335925965864</v>
@@ -5811,16 +5811,16 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.0438608209658331</v>
+        <v>0.04386089868234411</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0.007972464616699426</v>
+        <v>0.007972537081222919</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.007030170081206544</v>
+        <v>0.007030242477987114</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.007196235880658097</v>
+        <v>-0.007196306180585532</v>
       </c>
       <c r="J97" s="5" t="n">
         <v>-0.004055951357985865</v>
@@ -5863,7 +5863,7 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03808603426252022</v>
+        <v>0.03808611220723557</v>
       </c>
       <c r="G98" s="5" t="n">
         <v>-0.0001862028403939453</v>
@@ -5875,7 +5875,7 @@
         <v>-0.01940796123955024</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01307892706561686</v>
+        <v>-0.01307885661499408</v>
       </c>
       <c r="K98" s="5" t="n">
         <v>-0.004110584998271327</v>
@@ -5915,7 +5915,7 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03410031720880613</v>
+        <v>0.03410022876874885</v>
       </c>
       <c r="G99" s="5" t="n">
         <v>-0.004237581373844668</v>
@@ -5924,10 +5924,10 @@
         <v>-0.0002734868428240222</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.02395147462680114</v>
+        <v>-0.02395139583762362</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.004424624954043832</v>
+        <v>-0.00442454298082029</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>-0.003965178955294357</v>
@@ -5967,19 +5967,19 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.08907047822885672</v>
+        <v>0.08907039377687376</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.004564932100218577</v>
+        <v>0.004564860245733771</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.004175371193174904</v>
+        <v>-0.004175442422483688</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0.00478065136126693</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.01032948884590601</v>
+        <v>0.01032956152742326</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0.008776950318919008</v>
@@ -6019,13 +6019,13 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.1238706429350735</v>
+        <v>0.1238707119205138</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.0181830098032012</v>
+        <v>-0.01818290450622762</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01136532435334159</v>
+        <v>-0.01136521832519133</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0.04690526361528691</v>
@@ -6074,13 +6074,13 @@
         <v>-0.03069234351705008</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.01436955006474394</v>
+        <v>-0.01436945990894378</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.01442952538653286</v>
+        <v>-0.01442943523621854</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04890666942067545</v>
+        <v>-0.04890658547240734</v>
       </c>
       <c r="J102" s="5" t="n">
         <v>-0.02229630903445345</v>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.780701061260387</v>
+        <v>1.780701320170908</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>1.311035712738891</v>
@@ -750,10 +750,10 @@
         <v>1.547923635217787</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.159521203031256</v>
+        <v>1.159521333839812</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>1.296873103076994</v>
+        <v>1.296873242205359</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0.5248488768743713</v>
@@ -907,7 +907,7 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.536413562056367</v>
+        <v>1.536413373225165</v>
       </c>
       <c r="G6" s="3" t="n">
         <v>1.139025500733548</v>
@@ -972,7 +972,7 @@
         <v>1.13271861918637</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5634508846038371</v>
+        <v>0.5634509855190464</v>
       </c>
       <c r="J7" s="5" t="n">
         <v>-0.0397431750266648</v>
@@ -1134,10 +1134,10 @@
         <v>1.306341954937121</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.856822239098896</v>
+        <v>0.8568220940264304</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7632233241123314</v>
+        <v>0.7632231863526957</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.1378121605773759</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8740967483205673</v>
+        <v>0.8740969119018904</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.7605620540331652</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8320938409509537</v>
+        <v>0.832094036754814</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.6156588443481128</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.113680840244623</v>
+        <v>1.11368050503854</v>
       </c>
       <c r="G18" s="3" t="n">
         <v>0.7272218190073159</v>
@@ -1679,7 +1679,7 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.7050813018463387</v>
+        <v>0.7050811834036075</v>
       </c>
       <c r="G20" s="3" t="n">
         <v>0.43361890634831</v>
@@ -1688,7 +1688,7 @@
         <v>0.4186917551982716</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.367444342737236</v>
+        <v>0.3674444950892</v>
       </c>
       <c r="J20" s="3" t="n">
         <v>0.03995183621570808</v>
@@ -1787,7 +1787,7 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.763198887475063</v>
+        <v>1.763199180820205</v>
       </c>
       <c r="G22" s="3" t="n">
         <v>0.6674520561524815</v>
@@ -1843,13 +1843,13 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6695534891845289</v>
+        <v>0.6695536361980647</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3999390737344237</v>
+        <v>0.3999387636385074</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.381260960898314</v>
+        <v>0.3812606549397253</v>
       </c>
       <c r="I23" s="3" t="n">
         <v>0.3528745980372852</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6565618098588615</v>
+        <v>0.6565620216387955</v>
       </c>
       <c r="G24" s="3" t="n">
         <v>0.3219858657217809</v>
@@ -1955,7 +1955,7 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5545607742427558</v>
+        <v>0.5545609482485079</v>
       </c>
       <c r="G25" s="3" t="n">
         <v>0.5137823270846265</v>
@@ -2010,13 +2010,13 @@
         <v>0.6640375198363835</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3969983121244756</v>
+        <v>0.3969981893477683</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.377760354004183</v>
+        <v>0.3777602329182244</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.3522537144371283</v>
+        <v>0.352253829479843</v>
       </c>
       <c r="J26" s="3" t="n">
         <v>0.05321266058152796</v>
@@ -2066,10 +2066,10 @@
         <v>0.5455957151788788</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3671332428347083</v>
+        <v>0.3671331402761369</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3722462267693607</v>
+        <v>0.3722461238272272</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>0.1548263293356897</v>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6675999509793089</v>
+        <v>0.6675997834651819</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3869345103189425</v>
+        <v>0.386934394446645</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3720418417781526</v>
+        <v>0.3720417271500722</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.3458530565264364</v>
@@ -2175,7 +2175,7 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.083086170660991</v>
+        <v>1.083085891569514</v>
       </c>
       <c r="G29" s="3" t="n">
         <v>0.4595267581364666</v>
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5836572413313341</v>
+        <v>0.5836571353711313</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4824404283365684</v>
+        <v>0.4824403354880675</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3473148914530824</v>
+        <v>0.3473148070677907</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1454615380799074</v>
+        <v>0.1454616489492566</v>
       </c>
       <c r="J30" s="3" t="n">
         <v>0.119690129527162</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5662266246922192</v>
+        <v>0.5662267707694086</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.4830732318209987</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.544650718577969</v>
+        <v>0.5446505746326915</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.1788140589983993</v>
@@ -2499,7 +2499,7 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5426745803999016</v>
+        <v>0.5426742463901268</v>
       </c>
       <c r="G35" s="3" t="n">
         <v>0.1826760187692307</v>
@@ -2715,13 +2715,13 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5589924853038439</v>
+        <v>0.5589922376025815</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2867870026424868</v>
+        <v>0.2867870870193954</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2814583361875154</v>
+        <v>0.2814584202150137</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>0.2717691990035427</v>
@@ -2771,13 +2771,13 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5455964403920479</v>
+        <v>0.5455962817152487</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.333699585374126</v>
+        <v>0.3336997035251041</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.275338593485343</v>
+        <v>0.275338706466185</v>
       </c>
       <c r="I40" s="3" t="n">
         <v>0.2708930358411168</v>
@@ -2826,10 +2826,10 @@
         <v>0.4418595202594637</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2641467152831039</v>
+        <v>0.264146797660618</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2737129077841483</v>
+        <v>0.2737129907850389</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.1847492268813271</v>
@@ -2878,10 +2878,10 @@
         <v>0.4337934514140818</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2722682033671824</v>
+        <v>0.2722681140079657</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2678493268287148</v>
+        <v>0.2678492377798629</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.1885752537866485</v>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4508514368114691</v>
+        <v>0.4508513314638714</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2534754983218976</v>
+        <v>0.2534755769633175</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2670850367967565</v>
+        <v>0.2670851162920209</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>0.2649924459663764</v>
@@ -3035,13 +3035,13 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3443246450418633</v>
+        <v>0.3443247906375415</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2690510772539778</v>
+        <v>0.2690509475067042</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2655668821105137</v>
+        <v>0.2655667527194627</v>
       </c>
       <c r="I45" s="3" t="n">
         <v>0.129270688345682</v>
@@ -3243,13 +3243,13 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.3105532265789543</v>
+        <v>0.3105533207159228</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.3029248468195411</v>
+        <v>0.3029247537752928</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2617404407419122</v>
+        <v>0.2617403506387177</v>
       </c>
       <c r="I49" s="3" t="n">
         <v>0.1363270661486402</v>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4270660758554026</v>
+        <v>0.4270662639822698</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.1263250787213801</v>
@@ -3520,7 +3520,7 @@
         <v>0.240744105364707</v>
       </c>
       <c r="I54" s="5" t="n">
-        <v>-0.08523357081287031</v>
+        <v>-0.08523349351222964</v>
       </c>
       <c r="J54" s="5" t="n">
         <v>-0.0304502302686378</v>
@@ -3622,10 +3622,10 @@
         <v>0.2103107652399336</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2796271277588027</v>
+        <v>0.2796270500822648</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2293427066468481</v>
+        <v>0.2293426320226992</v>
       </c>
       <c r="I56" s="3" t="n">
         <v>0.1482061450779253</v>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4408768111376706</v>
+        <v>0.4408766595046709</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2290598473281396</v>
+        <v>0.2290597370000531</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2217650253355736</v>
+        <v>0.221764915662316</v>
       </c>
       <c r="I57" s="3" t="n">
         <v>0.1879271316382964</v>
@@ -3726,10 +3726,10 @@
         <v>0.1755442130769598</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.269333942895492</v>
+        <v>0.2693337995003819</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.217509284976166</v>
+        <v>0.2175091474356246</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0.1323776016142966</v>
@@ -3834,10 +3834,10 @@
         <v>0.319154269748813</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.194463451733716</v>
+        <v>0.1944635763351985</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2035901041379315</v>
+        <v>0.2035902296914684</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>0.1446617683774252</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3296584193612484</v>
+        <v>0.3296585139524517</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0.2664747739759108</v>
@@ -3892,7 +3892,7 @@
         <v>0.2029491727456918</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1315250718642484</v>
+        <v>0.1315250033629372</v>
       </c>
       <c r="J61" s="3" t="n">
         <v>0.1223255352865984</v>
@@ -3935,13 +3935,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3442858721527491</v>
+        <v>0.3442857163683846</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2007777249572409</v>
+        <v>0.2007776006587514</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1980471814095774</v>
+        <v>0.1980470573937401</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>0.151808910586533</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3447652700247767</v>
+        <v>0.3447654126339179</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0.2007974289088261</v>
@@ -4039,7 +4039,7 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3756670427192907</v>
+        <v>0.3756669252199267</v>
       </c>
       <c r="G64" s="3" t="n">
         <v>0.2270838943447613</v>
@@ -4094,10 +4094,10 @@
         <v>0.3435590842611607</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.199660912694537</v>
+        <v>0.1996610267455765</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1971219972480989</v>
+        <v>0.1971221110577652</v>
       </c>
       <c r="I65" s="3" t="n">
         <v>0.1515557712139433</v>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.2597787759939749</v>
+        <v>0.2597786671955813</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1805259963985431</v>
+        <v>0.1805259008585947</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1932021448907368</v>
+        <v>0.1932020483249079</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0.1248023884404867</v>
@@ -4467,13 +4467,13 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.3200631311227193</v>
+        <v>0.3200630352564959</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1521995335328601</v>
+        <v>0.1521994604977654</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1656590319776483</v>
+        <v>0.1656589580893892</v>
       </c>
       <c r="I72" s="3" t="n">
         <v>0.1774918875405691</v>
@@ -4571,7 +4571,7 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3329623165294675</v>
+        <v>0.3329624119123964</v>
       </c>
       <c r="G74" s="3" t="n">
         <v>0.157266693738918</v>
@@ -4626,10 +4626,10 @@
         <v>0.3382946371579334</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.14858002063956</v>
+        <v>0.1485799068394213</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.151566718262478</v>
+        <v>0.1515666041664203</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0.1610479579021633</v>
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1183228965709657</v>
+        <v>0.1183230276739218</v>
       </c>
       <c r="G76" s="3" t="n">
         <v>0.1120594594296969</v>
@@ -4688,7 +4688,7 @@
         <v>0.1420841480499133</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1047984789697887</v>
+        <v>0.1047983510186623</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0.09269660865573459</v>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1355254539420063</v>
+        <v>0.1355253855311671</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.08641453385772246</v>
+        <v>0.08641465910040669</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1163324862504662</v>
+        <v>0.1163326149421147</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>-0.00338102769308779</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.07915144326221046</v>
+        <v>0.07915153579447609</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0.09075567017467434</v>
@@ -4999,16 +4999,16 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.2821676279453948</v>
+        <v>0.282167726665377</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.1029623485146134</v>
+        <v>0.1029624215674034</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.103917294270903</v>
+        <v>0.1039173673869422</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1072072188939013</v>
+        <v>0.107207292510076</v>
       </c>
       <c r="J82" s="3" t="n">
         <v>0.006896950376516386</v>
@@ -5051,16 +5051,16 @@
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2794605910754389</v>
+        <v>0.2794606922784824</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1008469550706432</v>
+        <v>0.1008470299915947</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.1016497767703139</v>
+        <v>0.1016498517459035</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1060873595664575</v>
+        <v>0.1060872839288154</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0.006754300246448297</v>
@@ -5158,13 +5158,13 @@
         <v>0.1834072518867882</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.09141033178882241</v>
+        <v>0.09141025357922961</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.08596267264564239</v>
+        <v>0.08596259482642443</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1588536212363327</v>
+        <v>0.1588535330622238</v>
       </c>
       <c r="J85" s="3" t="n">
         <v>0.1147901445543076</v>
@@ -5216,7 +5216,7 @@
         <v>0.08470351397488507</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.001559290331758945</v>
+        <v>-0.001559200409543493</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>0.02069589958058415</v>
@@ -5483,16 +5483,16 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1850516411129475</v>
+        <v>0.1850515697269821</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.04511907901795675</v>
+        <v>0.04511919006318865</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05156011538341487</v>
+        <v>0.05156022711301511</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.1083125074517182</v>
+        <v>0.1083126323317054</v>
       </c>
       <c r="J91" s="3" t="n">
         <v>0.02400564571600916</v>
@@ -5539,16 +5539,16 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.2431670487492301</v>
+        <v>0.2431667795186294</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.01522076775004222</v>
+        <v>0.01522085752528057</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.04141552668502424</v>
+        <v>0.04141561877664612</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.05954298579977202</v>
+        <v>0.05954308358488691</v>
       </c>
       <c r="J92" s="3" t="n">
         <v>0.06231378420201339</v>
@@ -5647,13 +5647,13 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.08599336407834857</v>
+        <v>0.08599370508276771</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.03894933654575516</v>
+        <v>0.03894954461270528</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.0372025706220056</v>
+        <v>0.03720277833913666</v>
       </c>
       <c r="I94" s="3" t="n">
         <v>0.02370734091802928</v>
@@ -5703,13 +5703,13 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1207505468186056</v>
+        <v>0.1207504478549839</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.003725390809229623</v>
+        <v>-0.003725312607587683</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02209842567312537</v>
+        <v>0.02209850590178353</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>0.03465868209422918</v>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04850448717503664</v>
+        <v>0.04850428182646116</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0.02265642412273938</v>
@@ -5764,7 +5764,7 @@
         <v>0.02098221377412379</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.005218904814164871</v>
+        <v>0.005218810442326527</v>
       </c>
       <c r="J96" s="3" t="n">
         <v>0.006897335925965864</v>
@@ -5814,13 +5814,13 @@
         <v>0.04386089868234411</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0.007972537081222919</v>
+        <v>0.007972392152186147</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.007030242477987114</v>
+        <v>0.007030097684436187</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.007196306180585532</v>
+        <v>-0.007196235880658097</v>
       </c>
       <c r="J97" s="5" t="n">
         <v>-0.004055951357985865</v>
@@ -5863,19 +5863,19 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03808611220723557</v>
+        <v>0.03808619015196246</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.0001862028403939453</v>
+        <v>-0.0001861305370725042</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.003940580247929093</v>
+        <v>0.003940652849686144</v>
       </c>
       <c r="I98" s="5" t="n">
         <v>-0.01940796123955024</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01307885661499408</v>
+        <v>-0.01307892706561686</v>
       </c>
       <c r="K98" s="5" t="n">
         <v>-0.004110584998271327</v>
@@ -5915,16 +5915,16 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03410022876874885</v>
+        <v>0.03410049408896643</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.004237581373844668</v>
+        <v>-0.004237663377863576</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.0002734868428240222</v>
+        <v>-0.0002735691732980161</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.02395139583762362</v>
+        <v>-0.02395131704843334</v>
       </c>
       <c r="J99" s="5" t="n">
         <v>-0.00442454298082029</v>
@@ -5967,19 +5967,19 @@
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.08907039377687376</v>
+        <v>0.089070562680853</v>
       </c>
       <c r="G100" s="3" t="n">
-        <v>0.004564860245733771</v>
+        <v>0.004564932100218577</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.004175442422483688</v>
+        <v>-0.004175371193174904</v>
       </c>
       <c r="I100" s="3" t="n">
         <v>0.00478065136126693</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.01032956152742326</v>
+        <v>0.01032948884590601</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0.008776950318919008</v>
@@ -6071,16 +6071,16 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03069234351705008</v>
+        <v>-0.0306921691281653</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.01436945990894378</v>
+        <v>-0.01436964022052767</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.01442943523621854</v>
+        <v>-0.01442961553683053</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04890658547240734</v>
+        <v>-0.04890666942067545</v>
       </c>
       <c r="J102" s="5" t="n">
         <v>-0.02229630903445345</v>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -747,13 +747,13 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.547923635217787</v>
+        <v>1.547923817311105</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.159521333839812</v>
+        <v>1.159521464648385</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>1.296873242205359</v>
+        <v>1.296873381333742</v>
       </c>
       <c r="I3" s="3" t="n">
         <v>0.5248488768743713</v>
@@ -910,10 +910,10 @@
         <v>1.536413373225165</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.139025500733548</v>
+        <v>1.139025366436778</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.191116569173679</v>
+        <v>1.191116431606419</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>0.6086899115826985</v>
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.51448089526162</v>
+        <v>1.514480373208492</v>
       </c>
       <c r="G7" s="3" t="n">
         <v>1.078725742751273</v>
@@ -1131,13 +1131,13 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.306341954937121</v>
+        <v>1.306341731120818</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.8568220940264304</v>
+        <v>0.856822239098896</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7632231863526957</v>
+        <v>0.7632233241123314</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>0.1378121605773759</v>
@@ -1239,7 +1239,7 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8740969119018904</v>
+        <v>0.8740967483205673</v>
       </c>
       <c r="G12" s="3" t="n">
         <v>0.7605620540331652</v>
@@ -1463,7 +1463,7 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.832094036754814</v>
+        <v>0.8320938409509537</v>
       </c>
       <c r="G16" s="3" t="n">
         <v>0.6156588443481128</v>
@@ -1580,7 +1580,7 @@
         <v>0.4826594375549524</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3034674620023494</v>
+        <v>0.3034675894610721</v>
       </c>
       <c r="J18" s="3" t="n">
         <v>0.272253724049073</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.6690114772360265</v>
+        <v>0.6690113591472602</v>
       </c>
       <c r="G21" s="3" t="n">
         <v>0.4331948862990211</v>
@@ -1843,7 +1843,7 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.6695536361980647</v>
+        <v>0.669553783211627</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>0.3999387636385074</v>
@@ -2007,13 +2007,13 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.6640375198363835</v>
+        <v>0.6640376940542052</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3969981893477683</v>
+        <v>0.3969983121244756</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.3777602329182244</v>
+        <v>0.377760354004183</v>
       </c>
       <c r="I26" s="3" t="n">
         <v>0.352253829479843</v>
@@ -2119,13 +2119,13 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6675997834651819</v>
+        <v>0.6676001184934695</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.386934394446645</v>
+        <v>0.3869345103189425</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3720417271500722</v>
+        <v>0.3720418417781526</v>
       </c>
       <c r="I28" s="3" t="n">
         <v>0.3458530565264364</v>
@@ -2175,13 +2175,13 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.083085891569514</v>
+        <v>1.083086031115243</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4595267581364666</v>
+        <v>0.4595268951477454</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3577708460660856</v>
+        <v>0.3577709735251533</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.07839758760940141</v>
@@ -2231,13 +2231,13 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5836571353711313</v>
+        <v>0.5836572413313341</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4824403354880675</v>
+        <v>0.4824405211850811</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3473148070677907</v>
+        <v>0.3473149758383847</v>
       </c>
       <c r="I30" s="3" t="n">
         <v>0.1454616489492566</v>
@@ -2283,7 +2283,7 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5662267707694086</v>
+        <v>0.5662266246922192</v>
       </c>
       <c r="G31" s="3" t="n">
         <v>0.4830732318209987</v>
@@ -2447,7 +2447,7 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5446505746326915</v>
+        <v>0.5446504306874409</v>
       </c>
       <c r="G34" s="3" t="n">
         <v>0.1788140589983993</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.6189414385293674</v>
+        <v>0.6189415433818992</v>
       </c>
       <c r="G36" s="3" t="n">
         <v>0.4755470636917334</v>
@@ -2663,7 +2663,7 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.639429509880159</v>
+        <v>0.6394296452852541</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>0.3561770077768018</v>
@@ -2718,10 +2718,10 @@
         <v>0.5589922376025815</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2867870870193954</v>
+        <v>0.2867870026424868</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2814584202150137</v>
+        <v>0.2814583361875154</v>
       </c>
       <c r="I39" s="3" t="n">
         <v>0.2717691990035427</v>
@@ -2823,13 +2823,13 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4418595202594637</v>
+        <v>0.4418594130928397</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.264146797660618</v>
+        <v>0.2641467152831039</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2737129907850389</v>
+        <v>0.2737129077841483</v>
       </c>
       <c r="I41" s="3" t="n">
         <v>0.1847492268813271</v>
@@ -2875,13 +2875,13 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4337934514140818</v>
+        <v>0.433793337924715</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2722681140079657</v>
+        <v>0.2722682033671824</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2678492377798629</v>
+        <v>0.2678493268287148</v>
       </c>
       <c r="I42" s="3" t="n">
         <v>0.1885752537866485</v>
@@ -2931,13 +2931,13 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4508513314638714</v>
+        <v>0.4508515421590822</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2534755769633175</v>
+        <v>0.2534754983218976</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2670851162920209</v>
+        <v>0.2670850367967565</v>
       </c>
       <c r="I43" s="3" t="n">
         <v>0.2649924459663764</v>
@@ -3035,7 +3035,7 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3443247906375415</v>
+        <v>0.3443246450418633</v>
       </c>
       <c r="G45" s="3" t="n">
         <v>0.2690509475067042</v>
@@ -3142,13 +3142,13 @@
         <v>0.3920427187433075</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2816843601883992</v>
+        <v>0.2816844561819696</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2636214065828029</v>
+        <v>0.2636215012235226</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1653206156032558</v>
+        <v>0.1653205362489003</v>
       </c>
       <c r="J47" s="3" t="n">
         <v>0.06586853355928812</v>
@@ -3243,7 +3243,7 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.3105533207159228</v>
+        <v>0.310553132441999</v>
       </c>
       <c r="G49" s="3" t="n">
         <v>0.3029247537752928</v>
@@ -3406,10 +3406,10 @@
         <v>0.4444172082838467</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.256644154465927</v>
+        <v>0.2566442358520458</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2489617620601334</v>
+        <v>0.2489618429487046</v>
       </c>
       <c r="I52" s="3" t="n">
         <v>0.2018418315921782</v>
@@ -3511,7 +3511,7 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4270662639822698</v>
+        <v>0.4270660758554026</v>
       </c>
       <c r="G54" s="3" t="n">
         <v>0.1263250787213801</v>
@@ -3563,7 +3563,7 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3344499248844144</v>
+        <v>0.3344500799148888</v>
       </c>
       <c r="G55" s="3" t="n">
         <v>0.1718848256547709</v>
@@ -3680,7 +3680,7 @@
         <v>0.221764915662316</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1879271316382964</v>
+        <v>0.1879272347053123</v>
       </c>
       <c r="J57" s="3" t="n">
         <v>0.03263482295051578</v>
@@ -3726,10 +3726,10 @@
         <v>0.1755442130769598</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2693337995003819</v>
+        <v>0.269333942895492</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2175091474356246</v>
+        <v>0.217509284976166</v>
       </c>
       <c r="I58" s="3" t="n">
         <v>0.1323776016142966</v>
@@ -3779,16 +3779,16 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3210082260220046</v>
+        <v>0.3210083123181748</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1655925945476298</v>
+        <v>0.1655927289181596</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2045766351741902</v>
+        <v>0.2045767740388342</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.07441851932386845</v>
+        <v>0.07441840515245657</v>
       </c>
       <c r="J59" s="5" t="n">
         <v>-0.06150276039675151</v>
@@ -3834,10 +3834,10 @@
         <v>0.319154269748813</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1944635763351985</v>
+        <v>0.194463451733716</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2035902296914684</v>
+        <v>0.2035901041379315</v>
       </c>
       <c r="I60" s="3" t="n">
         <v>0.1446617683774252</v>
@@ -3883,7 +3883,7 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3296585139524517</v>
+        <v>0.3296584193612484</v>
       </c>
       <c r="G61" s="3" t="n">
         <v>0.2664747739759108</v>
@@ -3935,13 +3935,13 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3442857163683846</v>
+        <v>0.3442858721527491</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2007776006587514</v>
+        <v>0.2007777249572409</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1980470573937401</v>
+        <v>0.1980471814095774</v>
       </c>
       <c r="I62" s="3" t="n">
         <v>0.151808910586533</v>
@@ -3987,7 +3987,7 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3447654126339179</v>
+        <v>0.3447651274156656</v>
       </c>
       <c r="G63" s="3" t="n">
         <v>0.2007974289088261</v>
@@ -4094,13 +4094,13 @@
         <v>0.3435590842611607</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.1996610267455765</v>
+        <v>0.199660912694537</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1971221110577652</v>
+        <v>0.1971219972480989</v>
       </c>
       <c r="I65" s="3" t="n">
-        <v>0.1515557712139433</v>
+        <v>0.151555666126193</v>
       </c>
       <c r="J65" s="3" t="n">
         <v>0.0469448480365231</v>
@@ -4195,13 +4195,13 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.2597786671955813</v>
+        <v>0.2597787759939749</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.1805259008585947</v>
+        <v>0.1805259963985431</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0.1932020483249079</v>
+        <v>0.1932021448907368</v>
       </c>
       <c r="I67" s="3" t="n">
         <v>0.1248023884404867</v>
@@ -4303,13 +4303,13 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3622352829750961</v>
+        <v>0.3622355793251881</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1956731006391765</v>
+        <v>0.1956732147943772</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.192513337611244</v>
+        <v>0.1925134514647706</v>
       </c>
       <c r="I69" s="3" t="n">
         <v>0.1607244253454756</v>
@@ -4355,7 +4355,7 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2689364881725527</v>
+        <v>0.2689363759821515</v>
       </c>
       <c r="G70" s="3" t="n">
         <v>0.1828297548786559</v>
@@ -4364,7 +4364,7 @@
         <v>0.1805613142528613</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1142536387079967</v>
+        <v>0.1142535522024297</v>
       </c>
       <c r="J70" s="3" t="n">
         <v>0.05782676711006696</v>
@@ -4467,7 +4467,7 @@
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.3200630352564959</v>
+        <v>0.3200632269889565</v>
       </c>
       <c r="G72" s="3" t="n">
         <v>0.1521994604977654</v>
@@ -4522,10 +4522,10 @@
         <v>0.3616466367701576</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1670323306255632</v>
+        <v>0.1670324457894012</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1641868566951896</v>
+        <v>0.1641869715782336</v>
       </c>
       <c r="I73" s="3" t="n">
         <v>0.1723466605135937</v>
@@ -4574,10 +4574,10 @@
         <v>0.3329624119123964</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.157266693738918</v>
+        <v>0.15726662184341</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1536838247180545</v>
+        <v>0.1536837530451332</v>
       </c>
       <c r="I74" s="3" t="n">
         <v>0.1664030893954545</v>
@@ -4623,13 +4623,13 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3382946371579334</v>
+        <v>0.3382947916462911</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.1485799068394213</v>
+        <v>0.14858002063956</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.1515666041664203</v>
+        <v>0.151566718262478</v>
       </c>
       <c r="I75" s="3" t="n">
         <v>0.1610479579021633</v>
@@ -4688,7 +4688,7 @@
         <v>0.1420841480499133</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1047983510186623</v>
+        <v>0.1047984789697887</v>
       </c>
       <c r="J76" s="3" t="n">
         <v>0.09269660865573459</v>
@@ -4839,13 +4839,13 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1355253855311671</v>
+        <v>0.1355254539420063</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.08641465910040669</v>
+        <v>0.08641453385772246</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1163326149421147</v>
+        <v>0.1163324862504662</v>
       </c>
       <c r="I79" s="5" t="n">
         <v>-0.00338102769308779</v>
@@ -4947,7 +4947,7 @@
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.07915153579447609</v>
+        <v>0.07915144326221046</v>
       </c>
       <c r="G81" s="3" t="n">
         <v>0.09075567017467434</v>
@@ -4999,7 +4999,7 @@
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.282167726665377</v>
+        <v>0.2821678253853748</v>
       </c>
       <c r="G82" s="3" t="n">
         <v>0.1029624215674034</v>
@@ -5008,7 +5008,7 @@
         <v>0.1039173673869422</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.107207292510076</v>
+        <v>0.1072072188939013</v>
       </c>
       <c r="J82" s="3" t="n">
         <v>0.006896950376516386</v>
@@ -5054,13 +5054,13 @@
         <v>0.2794606922784824</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1008470299915947</v>
+        <v>0.1008469550706432</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.1016498517459035</v>
+        <v>0.1016497767703139</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1060872839288154</v>
+        <v>0.1060873595664575</v>
       </c>
       <c r="J83" s="3" t="n">
         <v>0.006754300246448297</v>
@@ -5155,7 +5155,7 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1834072518867882</v>
+        <v>0.1834074357871016</v>
       </c>
       <c r="G85" s="3" t="n">
         <v>0.09141025357922961</v>
@@ -5164,7 +5164,7 @@
         <v>0.08596259482642443</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1588535330622238</v>
+        <v>0.1588536212363327</v>
       </c>
       <c r="J85" s="3" t="n">
         <v>0.1147901445543076</v>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.06726952556642596</v>
+        <v>0.06726962831377814</v>
       </c>
       <c r="G86" s="3" t="n">
         <v>0.07794880991652886</v>
@@ -5216,7 +5216,7 @@
         <v>0.08470351397488507</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.001559200409543493</v>
+        <v>-0.001559290331758945</v>
       </c>
       <c r="J86" s="3" t="n">
         <v>0.02069589958058415</v>
@@ -5315,13 +5315,13 @@
         </is>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0.1588458639786785</v>
+        <v>0.1588459829087914</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.05759147812473575</v>
+        <v>0.05759157717876762</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.06495632128716444</v>
+        <v>0.06495642103098764</v>
       </c>
       <c r="I88" s="5" t="n">
         <v>-0.06593495918679138</v>
@@ -5483,13 +5483,13 @@
         </is>
       </c>
       <c r="F91" s="3" t="n">
-        <v>0.1850515697269821</v>
+        <v>0.1850516411129475</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.04511919006318865</v>
+        <v>0.04511907901795675</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05156022711301511</v>
+        <v>0.05156011538341487</v>
       </c>
       <c r="I91" s="3" t="n">
         <v>0.1083126323317054</v>
@@ -5539,13 +5539,13 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.2431667795186294</v>
+        <v>0.243166914133915</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0.01522085752528057</v>
+        <v>0.01522076775004222</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.04141561877664612</v>
+        <v>0.04141552668502424</v>
       </c>
       <c r="I92" s="3" t="n">
         <v>0.05954308358488691</v>
@@ -5647,7 +5647,7 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.08599370508276771</v>
+        <v>0.08599359141460416</v>
       </c>
       <c r="G94" s="3" t="n">
         <v>0.03894954461270528</v>
@@ -5706,10 +5706,10 @@
         <v>0.1207504478549839</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.003725312607587683</v>
+        <v>-0.003725390809229623</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02209850590178353</v>
+        <v>0.02209842567312537</v>
       </c>
       <c r="I95" s="3" t="n">
         <v>0.03465868209422918</v>
@@ -5755,7 +5755,7 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04850428182646116</v>
+        <v>0.04850417915220362</v>
       </c>
       <c r="G96" s="3" t="n">
         <v>0.02265642412273938</v>
@@ -5811,16 +5811,16 @@
         </is>
       </c>
       <c r="F97" s="3" t="n">
-        <v>0.04386089868234411</v>
+        <v>0.04386074324933342</v>
       </c>
       <c r="G97" s="3" t="n">
-        <v>0.007972392152186147</v>
+        <v>0.007972464616699426</v>
       </c>
       <c r="H97" s="3" t="n">
-        <v>0.007030097684436187</v>
+        <v>0.007030170081206544</v>
       </c>
       <c r="I97" s="5" t="n">
-        <v>-0.007196235880658097</v>
+        <v>-0.007196306180585532</v>
       </c>
       <c r="J97" s="5" t="n">
         <v>-0.004055951357985865</v>
@@ -5863,19 +5863,19 @@
         </is>
       </c>
       <c r="F98" s="3" t="n">
-        <v>0.03808619015196246</v>
+        <v>0.03808626809670113</v>
       </c>
       <c r="G98" s="5" t="n">
-        <v>-0.0001861305370725042</v>
+        <v>-0.000186058233740849</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.003940652849686144</v>
+        <v>0.003940725451453408</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01940796123955024</v>
+        <v>-0.01940803078946995</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01307892706561686</v>
+        <v>-0.01307885661499408</v>
       </c>
       <c r="K98" s="5" t="n">
         <v>-0.004110584998271327</v>
@@ -5915,19 +5915,19 @@
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03410049408896643</v>
+        <v>0.03410040564887895</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.004237663377863576</v>
+        <v>-0.004237581373844668</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.0002735691732980161</v>
+        <v>-0.0002734868428240222</v>
       </c>
       <c r="I99" s="5" t="n">
         <v>-0.02395131704843334</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.00442454298082029</v>
+        <v>-0.004424624954043832</v>
       </c>
       <c r="K99" s="5" t="n">
         <v>-0.003965178955294357</v>
@@ -5979,7 +5979,7 @@
         <v>0.00478065136126693</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0.01032948884590601</v>
+        <v>0.01032956152742326</v>
       </c>
       <c r="K100" s="3" t="n">
         <v>0.008776950318919008</v>
@@ -6019,7 +6019,7 @@
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.1238707119205138</v>
+        <v>0.1238706429350735</v>
       </c>
       <c r="G101" s="5" t="n">
         <v>-0.01818290450622762</v>
@@ -6071,7 +6071,7 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.0306921691281653</v>
+        <v>-0.03069225632261574</v>
       </c>
       <c r="G102" s="5" t="n">
         <v>-0.01436964022052767</v>
@@ -6080,7 +6080,7 @@
         <v>-0.01442961553683053</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04890666942067545</v>
+        <v>-0.04890675336892869</v>
       </c>
       <c r="J102" s="5" t="n">
         <v>-0.02229630903445345</v>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -167,7 +167,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -210,6 +210,9 @@
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="20" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="21" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -691,25 +694,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.780701320170908</v>
+        <v>1.952042885808761</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.311035712738891</v>
+        <v>1.315979714215984</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.338421257721972</v>
+        <v>1.357144270162411</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.6006411526826776</v>
+        <v>0.565685053982852</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.06751695213682762</v>
+        <v>-0.09967921835131344</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.01171112556929088</v>
+        <v>-0.01746374053871202</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.03596435391470409</v>
+        <v>0.01979372394118939</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -747,25 +750,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.547923817311105</v>
+        <v>1.709651103911419</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.159521464648385</v>
+        <v>1.169449572957524</v>
       </c>
       <c r="H3" s="8" t="n">
-        <v>1.296873381333742</v>
+        <v>1.325003289900756</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.5248488768743713</v>
+        <v>0.4896410011462258</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.06217881511795953</v>
+        <v>-0.09184689519707478</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.05979951607328038</v>
+        <v>-0.06690472982077877</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.04857363145720894</v>
+        <v>0.01830882352941177</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -799,25 +802,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.445354056528815</v>
+        <v>2.555720469202406</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.642836794255342</v>
+        <v>1.653147978372339</v>
       </c>
       <c r="H4" s="10" t="n">
-        <v>1.29651281131565</v>
+        <v>1.306402950527906</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.490333780478182</v>
+        <v>0.4269923071177835</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.07808664878132321</v>
+        <v>0.02919629390217637</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.1508042895442359</v>
+        <v>0.150340177012463</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.04602348249889232</v>
+        <v>0.01159527717477626</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -855,25 +858,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>1.936534446764092</v>
+        <v>2.101687581133709</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.315772143562726</v>
+        <v>1.334093129273852</v>
       </c>
       <c r="H5" s="11" t="n">
-        <v>1.253210405004939</v>
+        <v>1.244545750569847</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.6789209835282883</v>
+        <v>0.6335460346399271</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.007059155724975286</v>
+        <v>-0.03174388761312974</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.02776559988309213</v>
+        <v>0.03989554620629621</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.04657738095238084</v>
+        <v>0.01919522252239458</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -907,25 +910,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.536413373225165</v>
+        <v>1.681861775351244</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.139025366436778</v>
+        <v>1.142393627444674</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.191116431606419</v>
+        <v>1.209290053494302</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.6086899115826985</v>
+        <v>0.5679009792056828</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.03642878859962073</v>
+        <v>-0.07766178103186316</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.02377375497633882</v>
+        <v>-0.03027960314392464</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.0351652727996814</v>
+        <v>0.01338821990535921</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -963,25 +966,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.514480373208492</v>
+        <v>1.664434776876004</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.078725742751273</v>
+        <v>1.069829698947712</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>1.13271861918637</v>
+        <v>1.1505873515523</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5634509855190464</v>
+        <v>0.5237208250758487</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.0397431750266648</v>
+        <v>-0.07869388083700368</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.02531645569620244</v>
+        <v>-0.0375514403292182</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.03355704697986583</v>
+        <v>0.01244588744588726</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1019,25 +1022,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.479399848212818</v>
+        <v>1.616177871358606</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9622380654606684</v>
+        <v>0.9605276489109318</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>0.9777072884948463</v>
+        <v>0.9930206926385206</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.4899358839604793</v>
+        <v>0.453457413089231</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.004704312871912864</v>
+        <v>-0.04172796576166904</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.007821796038356643</v>
+        <v>-0.01630341513643385</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.02607672819399198</v>
+        <v>0.01091691504559011</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1075,25 +1078,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.253386345824977</v>
+        <v>1.293083288319668</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9786481296166305</v>
+        <v>0.9343248615330488</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.7987389575530752</v>
+        <v>0.79083565312476</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.6136363636363638</v>
+        <v>0.5736291690220461</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.1437601957585646</v>
+        <v>0.1087324504630089</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.1000196116885663</v>
-      </c>
-      <c r="L9" s="3" t="n">
-        <v>0.0186143648415511</v>
+        <v>0.08012416335241035</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>-0.007398823319664904</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1102,7 +1105,7 @@
       </c>
       <c r="N9" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1131,25 +1134,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.306341731120818</v>
+        <v>1.447634702590118</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.856822239098896</v>
+        <v>0.9126637880051682</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.7632233241123314</v>
+        <v>0.7704710121776548</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.1378121605773759</v>
+        <v>0.160301245480573</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.1280764922735766</v>
+        <v>0.173861137092141</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.05308398187942842</v>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v>-0.006465753424657605</v>
+        <v>0.08031352947858683</v>
+      </c>
+      <c r="L10" s="3" t="n">
+        <v>0.04897418927862351</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1158,7 +1161,7 @@
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1187,25 +1190,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.63275039745628</v>
+        <v>1.533846153846154</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.054590570719603</v>
+        <v>1.048507462686567</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.7295285359801487</v>
+        <v>0.7114427860696519</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.5831739961759079</v>
+        <v>0.6052631578947367</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.3039370078740158</v>
+        <v>0.3314470493128536</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.187948350071736</v>
-      </c>
-      <c r="L11" s="3" t="n">
-        <v>0.02602230483271373</v>
+        <v>0.1969476744186045</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>-0.005434782608695676</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1214,7 +1217,7 @@
       </c>
       <c r="N11" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1239,25 +1242,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8740967483205673</v>
+        <v>0.8741845451039705</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7605620540331652</v>
+        <v>0.7088435173225585</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0.660502028863464</v>
+        <v>0.6559156670015456</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.32234519097106</v>
+        <v>0.2787871232427279</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.274351524501572</v>
+        <v>0.265743326130216</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.06025889967637532</v>
+        <v>0.03196289000444819</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.003467575130794431</v>
+        <v>-0.00860753311763629</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1295,25 +1298,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.37032555878693</v>
+        <v>1.35107655534142</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6880925587695439</v>
+        <v>0.6936300668403621</v>
       </c>
       <c r="H13" s="3" t="n">
-        <v>0.6380926381289791</v>
+        <v>0.639253250827674</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1262360486831777</v>
+        <v>0.1349013448262313</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.1926117972015131</v>
+        <v>0.2189519699363107</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.03052325581395343</v>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v>-0.003352076124567449</v>
+        <v>0.0331716993608111</v>
+      </c>
+      <c r="L13" s="3" t="n">
+        <v>0.01714223717044594</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1322,7 +1325,7 @@
       </c>
       <c r="N13" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1332,7 +1335,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LIT</t>
+          <t>PICK</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1347,38 +1350,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Lithium &amp; Battery</t>
+          <t>Global Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8365068511745186</v>
+        <v>0.8835227611629839</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.5887106436810075</v>
+        <v>0.6356700577665451</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>0.5508026113365021</v>
+        <v>0.5592277183382703</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.08016350585128484</v>
-      </c>
-      <c r="J14" s="5" t="n">
-        <v>-0.04854566744207633</v>
+        <v>0.1605009688538652</v>
+      </c>
+      <c r="J14" s="3" t="n">
+        <v>0.08529194560440168</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.02444413755006236</v>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v>-0.00376040827289803</v>
+        <v>0.04902576995600261</v>
+      </c>
+      <c r="L14" s="3" t="n">
+        <v>0.02612972640639422</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1407,25 +1410,25 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.754682258767799</v>
+        <v>0.7861061338609379</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.6869012990238477</v>
+        <v>0.7335303663290476</v>
       </c>
       <c r="H15" s="3" t="n">
-        <v>0.5470265509350694</v>
+        <v>0.5483062375226981</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.1451798676773899</v>
+        <v>0.146681789407048</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>0.0309380274897515</v>
+        <v>0.01144691840580725</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.09041522138339109</v>
-      </c>
-      <c r="L15" s="5" t="n">
-        <v>-0.0053046695051302</v>
+        <v>0.1196301637993202</v>
+      </c>
+      <c r="L15" s="3" t="n">
+        <v>0.01684092344396904</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
@@ -1434,7 +1437,7 @@
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1444,14 +1447,10 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>PICK</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>SLV</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
       <c r="D16" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
@@ -1459,38 +1458,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Global Metals &amp; Mining</t>
+          <t>Silver Bullion</t>
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.8320938409509537</v>
+        <v>1.015830245874032</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6156588443481128</v>
+        <v>0.6084385917764041</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>0.545877083625423</v>
-      </c>
-      <c r="I16" s="3" t="n">
-        <v>0.1435659925999622</v>
-      </c>
-      <c r="J16" s="3" t="n">
-        <v>0.06193560581669222</v>
+        <v>0.5452835259338886</v>
+      </c>
+      <c r="I16" s="5" t="n">
+        <v>-0.2352415026833632</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>-0.02809353686261773</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.04514056224899599</v>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v>-0.001841055538508773</v>
+        <v>0.04086956521739138</v>
+      </c>
+      <c r="L16" s="3" t="n">
+        <v>0.0005015045135405849</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1500,49 +1499,53 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SLV</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>BOAT</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D17" s="13" t="inlineStr">
+        <is>
+          <t>Transportation &amp; Trade</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Silver Bullion</t>
+          <t>Global Shipping</t>
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.009405441719852</v>
+        <v>1.110984938070323</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.619821283509342</v>
+        <v>0.7183924464337479</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>0.512320606552938</v>
-      </c>
-      <c r="I17" s="5" t="n">
-        <v>-0.2122728469844614</v>
-      </c>
-      <c r="J17" s="5" t="n">
-        <v>-0.02842293324671108</v>
+        <v>0.4997923849232022</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>0.2796862630837045</v>
+      </c>
+      <c r="J17" s="3" t="n">
+        <v>0.2725039214382665</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.07108325872873777</v>
-      </c>
-      <c r="L17" s="5" t="n">
-        <v>-0.01205615194054499</v>
+        <v>0.1457535480964181</v>
+      </c>
+      <c r="L17" s="3" t="n">
+        <v>0.0001966568338249708</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1552,7 +1555,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BOAT</t>
+          <t>QTEC</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1560,45 +1563,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D18" s="13" t="inlineStr">
-        <is>
-          <t>Transportation &amp; Trade</t>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Global Shipping</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>1.11368050503854</v>
+        <v>0.7107524175238917</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.7272218190073159</v>
+        <v>0.4505516375104908</v>
       </c>
       <c r="H18" s="3" t="n">
-        <v>0.4826594375549524</v>
+        <v>0.4759598345421556</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3034675894610721</v>
-      </c>
-      <c r="J18" s="3" t="n">
-        <v>0.272253724049073</v>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v>0.1649484536082475</v>
-      </c>
-      <c r="L18" s="3" t="n">
-        <v>0.009930486593842991</v>
+        <v>0.3785766942517619</v>
+      </c>
+      <c r="J18" s="5" t="n">
+        <v>-0.006220205082071995</v>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>-0.01721469408383081</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>-0.003554843875100078</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1611,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>QTEC</t>
+          <t>LIT</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1616,45 +1619,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Lithium &amp; Battery</t>
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.6479132541324786</v>
+        <v>0.8258365928135685</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4685278472709435</v>
+        <v>0.4742889263445975</v>
       </c>
       <c r="H19" s="3" t="n">
-        <v>0.464012917780535</v>
+        <v>0.4740897519422276</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.4128509495728032</v>
-      </c>
-      <c r="J19" s="3" t="n">
-        <v>0.02384325934837994</v>
+        <v>0.04071382070756369</v>
+      </c>
+      <c r="J19" s="5" t="n">
+        <v>-0.03569613085545897</v>
       </c>
       <c r="K19" s="3" t="n">
-        <v>0.003083941019627945</v>
-      </c>
-      <c r="L19" s="3" t="n">
-        <v>0.007030670493759494</v>
+        <v>0.0001351168760976851</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>-0.002156915610676879</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1664,49 +1667,49 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>XLK</t>
+          <t>SIL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D20" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Silver Miners</t>
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.7050811834036075</v>
+        <v>1.793787975716156</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.43361890634831</v>
+        <v>0.6393069185609002</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>0.4186917551982716</v>
-      </c>
-      <c r="I20" s="3" t="n">
-        <v>0.3674444950892</v>
+        <v>0.4567593362048366</v>
+      </c>
+      <c r="I20" s="5" t="n">
+        <v>-0.02657541935153074</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.03995183621570808</v>
+        <v>0.2531709328317007</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.01052177197431603</v>
+        <v>0.1253107344632769</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>0.007044146905414772</v>
+        <v>0.003021452311410933</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1716,53 +1719,49 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DXJ</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>XLK</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Japan Hedged Equity</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.6690113591472602</v>
+        <v>0.7553368735079555</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4331948862990211</v>
+        <v>0.4336428714579958</v>
       </c>
       <c r="H21" s="3" t="n">
-        <v>0.414560247003918</v>
+        <v>0.4376965991675175</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.1559727442318763</v>
+        <v>0.3444249634820267</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.07046149819234748</v>
-      </c>
-      <c r="K21" s="3" t="n">
-        <v>0.01317345043067042</v>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v>-0.0003888024883358376</v>
+        <v>0.0189135285662887</v>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>-0.002819598872160434</v>
+      </c>
+      <c r="L21" s="3" t="n">
+        <v>0.0008543357539512186</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N21" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1772,49 +1771,53 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SIL</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+          <t>DXJ</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Silver Miners</t>
+          <t>Japan Hedged Equity</t>
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>1.763199180820205</v>
+        <v>0.6503903872797008</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.6674520561524815</v>
+        <v>0.3987689576249738</v>
       </c>
       <c r="H22" s="3" t="n">
-        <v>0.3982481437733469</v>
-      </c>
-      <c r="I22" s="5" t="n">
-        <v>-0.0178115551514556</v>
+        <v>0.4249030360541073</v>
+      </c>
+      <c r="I22" s="3" t="n">
+        <v>0.124807274619029</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.25412374598517</v>
-      </c>
-      <c r="K22" s="3" t="n">
-        <v>0.1925294258947874</v>
+        <v>0.04331481038720186</v>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>-0.01834095216858067</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.02042225730071023</v>
+        <v>-0.02155914874701337</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1843,34 +1846,34 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.669553783211627</v>
+        <v>0.7217059397088346</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3999387636385074</v>
+        <v>0.3957325745253024</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3812606549397253</v>
+        <v>0.3994019973724008</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.3528745980372852</v>
+        <v>0.3276364954581834</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.05190238239749112</v>
-      </c>
-      <c r="K23" s="3" t="n">
-        <v>0.01352250832019619</v>
-      </c>
-      <c r="L23" s="3" t="n">
-        <v>0.002911914583838771</v>
+        <v>0.03316624104019561</v>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>-0.00262213635109021</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>-0.000794994988075115</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N23" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1880,14 +1883,10 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>QCLN</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>VGT</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -1895,38 +1894,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Clean Energy</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.6565620216387955</v>
+        <v>0.7146585364893061</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3219858657217809</v>
+        <v>0.3925996530460425</v>
       </c>
       <c r="H24" s="3" t="n">
-        <v>0.3786844300618613</v>
+        <v>0.3965091888567571</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.09787158280603903</v>
-      </c>
-      <c r="J24" s="5" t="n">
-        <v>-0.1948200032578596</v>
+        <v>0.3268498473677466</v>
+      </c>
+      <c r="J24" s="3" t="n">
+        <v>0.034150661371525</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.04112512124151302</v>
-      </c>
-      <c r="L24" s="3" t="n">
-        <v>0.006106248727864694</v>
+        <v>-0.002799505969534821</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>-0.001319370000824605</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1936,7 +1935,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>IBB</t>
+          <t>IYW</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1944,45 +1943,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D25" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Biotechnology</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.5545609482485079</v>
+        <v>0.7179145617386125</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.5137823270846265</v>
+        <v>0.3841501350712611</v>
       </c>
       <c r="H25" s="3" t="n">
-        <v>0.3784190999316743</v>
+        <v>0.3912143607170988</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.2658427724426453</v>
+        <v>0.3190487522854586</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.258310370776321</v>
-      </c>
-      <c r="K25" s="3" t="n">
-        <v>0.09820179302482246</v>
+        <v>0.0314296416016191</v>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>-0.005077740602243752</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.00883962396520277</v>
+        <v>-0.002171252615372543</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N25" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1992,10 +1991,14 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>VGT</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
+          <t>DRIV</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
@@ -2003,38 +2006,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Autonomous &amp; Electric Vehicles</t>
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.6640376940542052</v>
+        <v>0.5639587302757341</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3969983121244756</v>
+        <v>0.3538717787997472</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>0.377760354004183</v>
+        <v>0.3888053969453829</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.352253829479843</v>
-      </c>
-      <c r="J26" s="3" t="n">
-        <v>0.05321266058152796</v>
-      </c>
-      <c r="K26" s="3" t="n">
-        <v>0.01396321070234108</v>
+        <v>0.138059343146631</v>
+      </c>
+      <c r="J26" s="5" t="n">
+        <v>-0.1068284468198212</v>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>-0.0251537171604248</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>0.003226340172071573</v>
+        <v>0.003452243958573131</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2047,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>DRIV</t>
+          <t>IBB</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2052,45 +2055,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D27" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Autonomous &amp; Electric Vehicles</t>
+          <t>Biotechnology</t>
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5455957151788788</v>
+        <v>0.5404060209266297</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.3671331402761369</v>
+        <v>0.4647299724249707</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>0.3722461238272272</v>
+        <v>0.3849438682359683</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.1548263293356897</v>
-      </c>
-      <c r="J27" s="5" t="n">
-        <v>-0.09814700180204816</v>
-      </c>
-      <c r="K27" s="5" t="n">
-        <v>-0.003725995987388986</v>
-      </c>
-      <c r="L27" s="3" t="n">
-        <v>0.007828356045230356</v>
+        <v>0.2218002372416121</v>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v>0.2528720490270324</v>
+      </c>
+      <c r="K27" s="3" t="n">
+        <v>0.05760963026655186</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>-0.01330690826727066</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N27" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2100,7 +2103,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>IYW</t>
+          <t>XME</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2108,45 +2111,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Metals &amp; Mining</t>
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>0.6676001184934695</v>
+        <v>1.163097434055064</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.3869345103189425</v>
+        <v>0.4495784249599848</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0.3720418417781526</v>
+        <v>0.384047243894313</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.3458530565264364</v>
+        <v>0.08324944753562336</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.05029853769887338</v>
+        <v>0.02287656931465198</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.01085438365457514</v>
+        <v>0.04734750302401936</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.003049021937118868</v>
+        <v>0.02191873208565154</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>REACCELERATING</t>
         </is>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2159,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>XME</t>
+          <t>QCLN</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2164,45 +2167,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Metals &amp; Mining</t>
+          <t>Clean Energy</t>
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>1.083086031115243</v>
+        <v>0.7248821221996085</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.4595268951477454</v>
+        <v>0.3234095124788039</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3577709735251533</v>
+        <v>0.3831121972522837</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.07839758760940141</v>
-      </c>
-      <c r="J29" s="3" t="n">
-        <v>0.0008529035749034186</v>
-      </c>
-      <c r="K29" s="3" t="n">
-        <v>0.07494336202990493</v>
+        <v>0.08122603105180604</v>
+      </c>
+      <c r="J29" s="5" t="n">
+        <v>-0.1786120591581343</v>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>-0.04316546762589935</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.002027369488089237</v>
+        <v>0.02245599838154955</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N29" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2231,25 +2234,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.5836572413313341</v>
+        <v>0.6032533367665098</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.4824405211850811</v>
+        <v>0.5313848597421695</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3473149758383847</v>
+        <v>0.3583030682636079</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1454616489492566</v>
+        <v>0.1651344707891862</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.119690129527162</v>
+        <v>0.1207781127924663</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.1002924689251767</v>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v>-0.00867369345630209</v>
+        <v>0.1274250169366262</v>
+      </c>
+      <c r="L30" s="3" t="n">
+        <v>0.01373352530734295</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2258,7 +2261,7 @@
       </c>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2283,25 +2286,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5662266246922192</v>
+        <v>0.5851334475159131</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.4830732318209987</v>
+        <v>0.5351717784895758</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0.3464804739729828</v>
+        <v>0.357410076320938</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.1480211489675201</v>
+        <v>0.1705776548356706</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1188137155182061</v>
+        <v>0.1229038776220586</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1014442916093536</v>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v>-0.008666047663262177</v>
+        <v>0.1309565217391304</v>
+      </c>
+      <c r="L31" s="3" t="n">
+        <v>0.01514205432407123</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2310,7 +2313,7 @@
       </c>
       <c r="N31" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2335,34 +2338,34 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5077104562234127</v>
+        <v>0.5348081839829713</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.4846297810310287</v>
+        <v>0.5159975317676597</v>
       </c>
       <c r="H32" s="3" t="n">
-        <v>0.3431478207070686</v>
+        <v>0.3564682340886116</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1595783351508542</v>
+        <v>0.1904937361827561</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.09134450906602809</v>
+        <v>0.09636918900576874</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.1053361053361053</v>
-      </c>
-      <c r="L32" s="5" t="n">
-        <v>-0.001877346683354264</v>
+        <v>0.1176063645797303</v>
+      </c>
+      <c r="L32" s="3" t="n">
+        <v>0.01285266457680256</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2372,44 +2375,40 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ROBO</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+          <t>AIRR</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Robotics</t>
+          <t>U.S. Industrial Renaissance</t>
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.4279585479905097</v>
+        <v>0.582999820099811</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.2805972035126587</v>
+        <v>0.1916582797458248</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.3203327503512046</v>
-      </c>
-      <c r="I33" s="3" t="n">
-        <v>0.1193387051958876</v>
+        <v>0.3443289551620783</v>
+      </c>
+      <c r="I33" s="5" t="n">
+        <v>-0.03125567447245658</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.03370112736867359</v>
+        <v>-0.1453878570313718</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.03009510051763575</v>
+        <v>-0.1135664562085155</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.0100288328945719</v>
+        <v>0.007266372332597637</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2447,25 +2446,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5446504306874409</v>
+        <v>0.5864008316842255</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.1788140589983993</v>
+        <v>0.174478872315555</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3185919873131313</v>
+        <v>0.3285316675721524</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.09382844759776487</v>
+        <v>-0.1006766758070096</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.0718891493666115</v>
+        <v>-0.06449300945872405</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.1060054434272385</v>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v>-0.003977474107037415</v>
+        <v>-0.1159571871840462</v>
+      </c>
+      <c r="L34" s="3" t="n">
+        <v>0.002569982603194632</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2474,7 +2473,7 @@
       </c>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2484,40 +2483,44 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>AIRR</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>ROBO</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>U.S. Industrial Renaissance</t>
+          <t>Robotics</t>
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.5426742463901268</v>
+        <v>0.4435215510053252</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.1826760187692307</v>
+        <v>0.2580322709248917</v>
       </c>
       <c r="H35" s="3" t="n">
-        <v>0.317783047403464</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>-0.01472508712312759</v>
+        <v>0.3255333785487629</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>0.1058368980267697</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.1504258810658748</v>
+        <v>-0.04968575833036881</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.1025260029717682</v>
-      </c>
-      <c r="L35" s="3" t="n">
-        <v>0.01003344481605351</v>
+        <v>-0.05092373282804352</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>-0.005336974059823696</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2526,7 +2529,7 @@
       </c>
       <c r="N35" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2536,7 +2539,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>XOP</t>
+          <t>ARKQ</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2544,45 +2547,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D36" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Oil &amp; Gas E&amp;P</t>
+          <t>Autonomy &amp; Robotics</t>
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.6189415433818992</v>
+        <v>0.7871983426149323</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.4755470636917334</v>
+        <v>0.2741006993596988</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.2924866917817843</v>
+        <v>0.318977930470749</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.1723325472199564</v>
-      </c>
-      <c r="J36" s="3" t="n">
-        <v>0.1545558730178536</v>
-      </c>
-      <c r="K36" s="3" t="n">
-        <v>0.1416342412451361</v>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v>-0.008423022929340274</v>
+        <v>0.01504068381688173</v>
+      </c>
+      <c r="J36" s="5" t="n">
+        <v>-0.06212029161603894</v>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>-0.03402424716464603</v>
+      </c>
+      <c r="L36" s="3" t="n">
+        <v>0.01022494887525571</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2592,7 +2595,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ARKQ</t>
+          <t>XOP</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2600,45 +2603,45 @@
           <t>HB</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
+      <c r="D37" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Autonomy &amp; Robotics</t>
+          <t>Oil &amp; Gas E&amp;P</t>
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.7053554928268708</v>
+        <v>0.6755536939403202</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.2743178761911313</v>
+        <v>0.5397456331333756</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.2842205508936391</v>
+        <v>0.3133774520883419</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.02990732940185348</v>
-      </c>
-      <c r="J37" s="5" t="n">
-        <v>-0.05671296296296291</v>
-      </c>
-      <c r="K37" s="5" t="n">
-        <v>-0.007711038961038974</v>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v>-0.004559889259832306</v>
+        <v>0.2163145243634894</v>
+      </c>
+      <c r="J37" s="3" t="n">
+        <v>0.164179259218582</v>
+      </c>
+      <c r="K37" s="3" t="n">
+        <v>0.1723557692307693</v>
+      </c>
+      <c r="L37" s="3" t="n">
+        <v>0.02291437260762419</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>ACCELERATING</t>
         </is>
       </c>
       <c r="N37" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive trend strengthening through 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2648,40 +2651,44 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>EWZ</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+          <t>CALF</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D38" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Brazil Equity</t>
+          <t>Small Cap Cash Flow</t>
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.6394296452852541</v>
+        <v>0.5247578785694103</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.3561770077768018</v>
+        <v>0.3085998181067384</v>
       </c>
       <c r="H38" s="3" t="n">
-        <v>0.282744285485665</v>
+        <v>0.2984842418520643</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.05348465783876932</v>
+        <v>0.2495997064462407</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.1237996411221542</v>
+        <v>0.1341419925767213</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.05724657916783005</v>
+        <v>0.007790295737625685</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.007081038552321117</v>
+        <v>-0.01567125195890651</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2715,25 +2722,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.5589922376025815</v>
+        <v>0.6094133100748802</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2867870026424868</v>
+        <v>0.2969297100938024</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.2814583361875154</v>
+        <v>0.2896068041978299</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2717691990035427</v>
+        <v>0.2673727535476751</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.03929689962146599</v>
+        <v>0.01954968403269297</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.004158283031522547</v>
+        <v>0.005678402030863783</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.01567057865816435</v>
+        <v>0.005476890195030615</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2752,14 +2759,10 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CALF</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>IWM</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -2767,38 +2770,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Small Cap Cash Flow</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.5455962817152487</v>
+        <v>0.4599126470316062</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.3336997035251041</v>
+        <v>0.2541335419367787</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.275338706466185</v>
+        <v>0.2814573608459154</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.2708930358411168</v>
+        <v>0.1685122726963868</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.1600853084742613</v>
-      </c>
-      <c r="K40" s="3" t="n">
-        <v>0.04576117447311745</v>
+        <v>0.04125814471937428</v>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>-0.02132245655922538</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.007260155574762339</v>
+        <v>-0.002972872538089866</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2808,40 +2811,40 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>IWM</t>
+          <t>HEFA</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D41" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Developed ex-US Currency-Hedged</t>
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.4418594130928397</v>
+        <v>0.3521189891256404</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2641467152831039</v>
+        <v>0.2663067627150033</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.2737129077841483</v>
+        <v>0.2810969245220378</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1847492268813271</v>
+        <v>0.1167721758113234</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.0534846513024354</v>
+        <v>0.05630612403464297</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.007510477787091352</v>
-      </c>
-      <c r="L41" s="3" t="n">
-        <v>0.002777871879128702</v>
+        <v>-0.01154492023509646</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>-0.005491024287222812</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2850,7 +2853,7 @@
       </c>
       <c r="N41" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2860,49 +2863,49 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SCHA</t>
+          <t>EWJ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr"/>
-      <c r="D42" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D42" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Small Cap Blend</t>
+          <t>Japan Equity</t>
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.433793337924715</v>
+        <v>0.4853274854011134</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2722682033671824</v>
+        <v>0.2953196255677726</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.2678493268287148</v>
+        <v>0.2764819660074971</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1885752537866485</v>
+        <v>0.1544167937583565</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.04397184437404666</v>
+        <v>0.07519585958133801</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.003485332558814891</v>
+        <v>0.01475748194014437</v>
       </c>
       <c r="L42" s="3" t="n">
-        <v>0.009938614440222038</v>
+        <v>0.0005087505087504329</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -2931,25 +2934,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.4508515421590822</v>
+        <v>0.5201936636107622</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2534754983218976</v>
+        <v>0.2659110205765836</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.2670850367967565</v>
+        <v>0.2751452288809066</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2649924459663764</v>
+        <v>0.2445187483403846</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.004154334153843142</v>
+        <v>-0.02431362500973122</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.01074082486939032</v>
+        <v>-0.007241691452217758</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.01816845902077358</v>
+        <v>0.007282031096240704</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2968,49 +2971,49 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>SCHA</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
-      <c r="D44" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D44" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Small Cap Blend</t>
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4906181800510183</v>
+        <v>0.4579929420519961</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.1422405363607471</v>
+        <v>0.2648118145490679</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2656740024148891</v>
-      </c>
-      <c r="I44" s="5" t="n">
-        <v>-0.06723825201656219</v>
-      </c>
-      <c r="J44" s="5" t="n">
-        <v>-0.01604546874855806</v>
+        <v>0.2746931568502324</v>
+      </c>
+      <c r="I44" s="3" t="n">
+        <v>0.176824454930451</v>
+      </c>
+      <c r="J44" s="3" t="n">
+        <v>0.03461055372360944</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.09752390095603825</v>
-      </c>
-      <c r="L44" s="5" t="n">
-        <v>-0.001637313036551791</v>
+        <v>-0.007751937984496027</v>
+      </c>
+      <c r="L44" s="3" t="n">
+        <v>0.0002894356005789245</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3020,49 +3023,49 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HEFA</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
-      <c r="D45" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D45" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Developed ex-US Currency-Hedged</t>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.3443246450418633</v>
+        <v>0.51989100746336</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.2690509475067042</v>
+        <v>0.1433221116145802</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>0.2655667527194627</v>
-      </c>
-      <c r="I45" s="3" t="n">
-        <v>0.129270688345682</v>
-      </c>
-      <c r="J45" s="3" t="n">
-        <v>0.06803907799689601</v>
-      </c>
-      <c r="K45" s="3" t="n">
-        <v>0.002753070732740337</v>
-      </c>
-      <c r="L45" s="3" t="n">
-        <v>0.003390548845094488</v>
+        <v>0.272020673916745</v>
+      </c>
+      <c r="I45" s="5" t="n">
+        <v>-0.06738050042579624</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>-0.007576273900549491</v>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>-0.1011764705882353</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>-0.001019458357342407</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N45" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3087,25 +3090,25 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4632542486309303</v>
+        <v>0.4780360083262694</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2933336468535885</v>
+        <v>0.2880642025088083</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>0.2645773130569522</v>
+        <v>0.2720092090620112</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1377823091565502</v>
+        <v>0.1276706089343866</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.071971220943017</v>
+        <v>0.06210289172913863</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.02273987798114252</v>
+        <v>0.01262175881465222</v>
       </c>
       <c r="L46" s="3" t="n">
-        <v>0.004357298474945592</v>
+        <v>0.0006778741865509641</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
@@ -3124,7 +3127,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>FNDX</t>
+          <t>SCHD</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -3135,38 +3138,38 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Fundamental Large Cap</t>
+          <t>Dividend</t>
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.3920427187433075</v>
+        <v>0.302092867845597</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.2816844561819696</v>
+        <v>0.29778014653898</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.2636215012235226</v>
+        <v>0.271524478834434</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1653205362489003</v>
+        <v>0.1338028625069978</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.06586853355928812</v>
+        <v>0.08007321214799523</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.01429459291485391</v>
+        <v>0.0206489675516226</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.004574565416285425</v>
+        <v>-0.005747126436781436</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N47" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3176,49 +3179,49 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>PAVE</t>
+          <t>FNDX</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
-      <c r="D48" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+      <c r="D48" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>U.S. Infrastructure Development</t>
+          <t>Fundamental Large Cap</t>
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.425998814187043</v>
+        <v>0.3994155046211489</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.1929944469313138</v>
+        <v>0.2797348233797869</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2619874180283208</v>
+        <v>0.2706893713399177</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.07128209029965205</v>
-      </c>
-      <c r="J48" s="5" t="n">
-        <v>-0.02511064236953608</v>
-      </c>
-      <c r="K48" s="5" t="n">
-        <v>-0.05467009425878333</v>
-      </c>
-      <c r="L48" s="3" t="n">
-        <v>0.008593892850612628</v>
+        <v>0.158058340173383</v>
+      </c>
+      <c r="J48" s="3" t="n">
+        <v>0.0598448041540347</v>
+      </c>
+      <c r="K48" s="3" t="n">
+        <v>0.007118539151965253</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>-0.003063725490196068</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N48" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3228,49 +3231,49 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SCHD</t>
+          <t>PAVE</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
-      <c r="D49" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D49" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Dividend</t>
+          <t>U.S. Infrastructure Development</t>
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.310553132441999</v>
+        <v>0.4415124405147994</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.3029247537752928</v>
+        <v>0.1912250202822765</v>
       </c>
       <c r="H49" s="3" t="n">
-        <v>0.2617403506387177</v>
+        <v>0.2690687318999239</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.1363270661486402</v>
-      </c>
-      <c r="J49" s="3" t="n">
-        <v>0.0859799973215547</v>
-      </c>
-      <c r="K49" s="3" t="n">
-        <v>0.03264094955489605</v>
+        <v>0.05721466237300921</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>-0.02341875623653566</v>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>-0.06133924007497005</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.007981755986317007</v>
+        <v>-0.001269035532994844</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N49" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3280,49 +3283,49 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EWJ</t>
+          <t>QQQM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
-      <c r="D50" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Growth &amp; Technology</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Japan Equity</t>
+          <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4731442217620947</v>
+        <v>0.4814455248901417</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.3020609794165454</v>
+        <v>0.2521514367630013</v>
       </c>
       <c r="H50" s="3" t="n">
-        <v>0.2605932253915781</v>
+        <v>0.2616444957840165</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1656716357696715</v>
+        <v>0.1838349351989175</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.08921936815569764</v>
-      </c>
-      <c r="K50" s="3" t="n">
-        <v>0.03289542827115066</v>
-      </c>
-      <c r="L50" s="3" t="n">
-        <v>0.003881511746680166</v>
+        <v>0.003364663480652119</v>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>-0.007524353375881754</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>-0.002060323572128264</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3351,25 +3354,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4141404111156104</v>
+        <v>0.4436910464969233</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.2273005975859326</v>
+        <v>0.219417184885873</v>
       </c>
       <c r="H51" s="3" t="n">
-        <v>0.2492433825456852</v>
+        <v>0.2613478852967264</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.1802404984418828</v>
+        <v>0.1607046573974369</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.03199598028098749</v>
+        <v>0.02152869221345655</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.01756485987145129</v>
-      </c>
-      <c r="L51" s="3" t="n">
-        <v>0.001166799257491302</v>
+        <v>-0.03324277219602223</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>-0.0009270540869842359</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3378,111 +3381,115 @@
       </c>
       <c r="N51" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="52" ht="21" customHeight="1">
-      <c r="A52" t="n">
+      <c r="A52" s="15" t="n">
         <v>51</v>
       </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>QQQM</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr"/>
+      <c r="B52" s="16" t="inlineStr">
+        <is>
+          <t>QQQ</t>
+        </is>
+      </c>
+      <c r="C52" s="15" t="inlineStr"/>
       <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Growth &amp; Technology</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E52" s="15" t="inlineStr">
         <is>
           <t>Nasdaq-100</t>
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4444172082838467</v>
+        <v>0.4805229879132382</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2566442358520458</v>
+        <v>0.2514415899049023</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.2489618429487046</v>
+        <v>0.261174733777882</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.2018418315921782</v>
+        <v>0.1832698588160768</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.02088045625307022</v>
-      </c>
-      <c r="K52" s="3" t="n">
-        <v>0.006151022904913983</v>
-      </c>
-      <c r="L52" s="3" t="n">
-        <v>0.001895028933031062</v>
+        <v>0.003028268473278084</v>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>-0.007717522094518814</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>-0.002100255925225336</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N52" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="53" ht="21" customHeight="1">
-      <c r="A53" s="15" t="n">
+      <c r="A53" t="n">
         <v>52</v>
       </c>
-      <c r="B53" s="16" t="inlineStr">
-        <is>
-          <t>QQQ</t>
-        </is>
-      </c>
-      <c r="C53" s="15" t="inlineStr"/>
-      <c r="D53" s="2" t="inlineStr">
-        <is>
-          <t>Growth &amp; Technology</t>
-        </is>
-      </c>
-      <c r="E53" s="15" t="inlineStr">
-        <is>
-          <t>Nasdaq-100</t>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>PPA</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D53" s="18" t="inlineStr">
+        <is>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Aerospace &amp; Defense</t>
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.442824875205468</v>
+        <v>0.4526987060192829</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.2558848667790528</v>
+        <v>0.1249334073197237</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2483561255753448</v>
-      </c>
-      <c r="I53" s="3" t="n">
-        <v>0.2015967755690107</v>
-      </c>
-      <c r="J53" s="3" t="n">
-        <v>0.02083526655997492</v>
-      </c>
-      <c r="K53" s="3" t="n">
-        <v>0.006030924228643375</v>
+        <v>0.2514543680219057</v>
+      </c>
+      <c r="I53" s="5" t="n">
+        <v>-0.08658814704368756</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>-0.02610591128439199</v>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>-0.1010991402764175</v>
       </c>
       <c r="L53" s="3" t="n">
-        <v>0.001797483523067855</v>
+        <v>0.00012108003390221</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3492,53 +3499,49 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PPA</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D54" s="18" t="inlineStr">
-        <is>
-          <t>Industrials</t>
+          <t>EWZ</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr"/>
+      <c r="D54" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aerospace &amp; Defense</t>
+          <t>Brazil Equity</t>
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.4270660758554026</v>
+        <v>0.6920808213364746</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.1263250787213801</v>
+        <v>0.3774403004818963</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.240744105364707</v>
-      </c>
-      <c r="I54" s="5" t="n">
-        <v>-0.08523349351222964</v>
-      </c>
-      <c r="J54" s="5" t="n">
-        <v>-0.0304502302686378</v>
-      </c>
-      <c r="K54" s="5" t="n">
-        <v>-0.09221806990547377</v>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v>-0.002355499184634846</v>
+        <v>0.2462555099598109</v>
+      </c>
+      <c r="I54" s="3" t="n">
+        <v>0.06285312742431404</v>
+      </c>
+      <c r="J54" s="3" t="n">
+        <v>0.1704318796017108</v>
+      </c>
+      <c r="K54" s="3" t="n">
+        <v>0.1052631578947367</v>
+      </c>
+      <c r="L54" s="3" t="n">
+        <v>0.0316957210776545</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N54" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3563,25 +3566,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3344500799148888</v>
+        <v>0.3464755659205758</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1718848256547709</v>
+        <v>0.1766354392723104</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2353365686539364</v>
+        <v>0.2427385538381706</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.03680666519160902</v>
+        <v>0.03109419023878557</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.008733630694340855</v>
+        <v>0.01227531588670483</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.05136393158692343</v>
+        <v>-0.05319148936170215</v>
       </c>
       <c r="L55" s="3" t="n">
-        <v>0.004067369385884589</v>
+        <v>0.0003423289781481209</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3600,53 +3603,49 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>VHT</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D56" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>ONEQ</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr"/>
+      <c r="D56" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Health Care</t>
+          <t>Nasdaq Composite</t>
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.2103107652399336</v>
+        <v>0.4778351026344523</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2796270500822648</v>
+        <v>0.2264826474790356</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.2293426320226992</v>
+        <v>0.2382553739858415</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1482061450779253</v>
+        <v>0.1689658949284116</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.1359983485299427</v>
-      </c>
-      <c r="K56" s="3" t="n">
-        <v>0.04090350139149579</v>
+        <v>0.02139729601737406</v>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>-0.009507510933637553</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.009667487684729026</v>
+        <v>-0.002680451847597021</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N56" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3656,49 +3655,53 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ONEQ</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
-      <c r="D57" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>VHT</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D57" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Nasdaq Composite</t>
+          <t>Health Care</t>
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.4408766595046709</v>
+        <v>0.1970270392823368</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2290597370000531</v>
+        <v>0.2548869137101146</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.221764915662316</v>
+        <v>0.2354908318314333</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1879272347053123</v>
+        <v>0.1190700858764808</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.03263482295051578</v>
+        <v>0.1228123475764273</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.005970724191063148</v>
+        <v>0.01569909009355364</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.002863688430698841</v>
+        <v>-0.01442516943356353</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N57" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3723,34 +3726,34 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1755442130769598</v>
+        <v>0.1583533897709555</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.269333942895492</v>
+        <v>0.2430939489162565</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.217509284976166</v>
+        <v>0.2224347427376865</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1323776016142966</v>
+        <v>0.1015085204950394</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.1254567146663546</v>
+        <v>0.1085689069443569</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.04256612952265137</v>
+        <v>0.01690004828585212</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.01044672746161834</v>
+        <v>-0.0173228346456693</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N58" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3760,14 +3763,10 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>XMMO</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
+          <t>COWZ</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3775,38 +3774,38 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Mid Cap Momentum</t>
+          <t>Large Cap Cash Flow</t>
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3210083123181748</v>
+        <v>0.3119478613897209</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.1655927289181596</v>
+        <v>0.2491846837553984</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2045767740388342</v>
+        <v>0.2212734482656766</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.07441840515245657</v>
-      </c>
-      <c r="J59" s="5" t="n">
-        <v>-0.06150276039675151</v>
-      </c>
-      <c r="K59" s="5" t="n">
-        <v>-0.03236327145007523</v>
-      </c>
-      <c r="L59" s="3" t="n">
-        <v>0.009950248756219082</v>
+        <v>0.1168902845103761</v>
+      </c>
+      <c r="J59" s="3" t="n">
+        <v>0.1114630410072381</v>
+      </c>
+      <c r="K59" s="3" t="n">
+        <v>0.02285420642638081</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>-0.01262272089761562</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N59" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3816,10 +3815,14 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>VBK</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr"/>
+          <t>XMMO</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
       <c r="D60" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
@@ -3827,38 +3830,38 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Small Growth</t>
+          <t>Mid Cap Momentum</t>
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.319154269748813</v>
+        <v>0.3700480430690825</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.194463451733716</v>
+        <v>0.1751849954205564</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.2035901041379315</v>
+        <v>0.2199209533338997</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.1446617683774252</v>
-      </c>
-      <c r="J60" s="3" t="n">
-        <v>0.02244173753769618</v>
+        <v>0.06697413279917575</v>
+      </c>
+      <c r="J60" s="5" t="n">
+        <v>-0.05510123589555349</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.007582857629717998</v>
+        <v>-0.03667119397456475</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.000114481969089919</v>
+        <v>0.01140782991962652</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N60" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -3868,7 +3871,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>COWZ</t>
+          <t>VBK</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -3879,38 +3882,38 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Large Cap Cash Flow</t>
+          <t>Small Growth</t>
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3296584193612484</v>
+        <v>0.3529393194235411</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.2664747739759108</v>
+        <v>0.179815398400089</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2029491727456918</v>
+        <v>0.2194131006507771</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1315250033629372</v>
+        <v>0.1220610307949428</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.1223255352865984</v>
-      </c>
-      <c r="K61" s="3" t="n">
-        <v>0.05280821722934803</v>
+        <v>0.01501704101434376</v>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>-0.03247275449932074</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.01287553648068684</v>
+        <v>-0.00154532967032972</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
-          <t>ACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N61" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3935,34 +3938,34 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3442858721527491</v>
+        <v>0.3641706161501508</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.2007777249572409</v>
+        <v>0.1997138093082413</v>
       </c>
       <c r="H62" s="3" t="n">
-        <v>0.1980471814095774</v>
+        <v>0.2086591557352897</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.151808910586533</v>
+        <v>0.1377647633414834</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.04730356189549445</v>
-      </c>
-      <c r="K62" s="3" t="n">
-        <v>0.002279161947904784</v>
+        <v>0.04093744819898126</v>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>-0.007401049654570779</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.003813034669068016</v>
+        <v>-0.003615768138867992</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N62" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3987,138 +3990,138 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3447651274156656</v>
+        <v>0.3646408107623884</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.2007974289088261</v>
+        <v>0.1998712868884449</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.1980201038652212</v>
+        <v>0.2083811226627361</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1520055073493269</v>
+        <v>0.1380204828733071</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.04735888636141317</v>
-      </c>
-      <c r="K63" s="3" t="n">
-        <v>0.002318262468755217</v>
+        <v>0.04129957247782046</v>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>-0.007042344186525606</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.004130583042734171</v>
+        <v>-0.003437047756874034</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N63" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="64" ht="21" customHeight="1">
-      <c r="A64" t="n">
+      <c r="A64" s="15" t="n">
         <v>63</v>
       </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>VWO</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr"/>
-      <c r="D64" s="9" t="inlineStr">
-        <is>
-          <t>International</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>Emerging Markets</t>
+      <c r="B64" s="16" t="inlineStr">
+        <is>
+          <t>SPY</t>
+        </is>
+      </c>
+      <c r="C64" s="15" t="inlineStr"/>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E64" s="15" t="inlineStr">
+        <is>
+          <t>S&amp;P 500</t>
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3756669252199267</v>
+        <v>0.3628138660580156</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.2270838943447613</v>
+        <v>0.1987248153376957</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.1975252328273418</v>
+        <v>0.2079414495256811</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.1293008922112591</v>
+        <v>0.137361154919005</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.06002103053001884</v>
-      </c>
-      <c r="K64" s="3" t="n">
-        <v>0.02468312208138745</v>
-      </c>
-      <c r="L64" s="3" t="n">
-        <v>0.007378258730939447</v>
+        <v>0.04074149258465898</v>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>-0.007630033882523368</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>-0.003674418000753077</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N64" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
     <row r="65" ht="21" customHeight="1">
-      <c r="A65" s="15" t="n">
+      <c r="A65" t="n">
         <v>64</v>
       </c>
-      <c r="B65" s="16" t="inlineStr">
-        <is>
-          <t>SPY</t>
-        </is>
-      </c>
-      <c r="C65" s="15" t="inlineStr"/>
-      <c r="D65" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E65" s="15" t="inlineStr">
-        <is>
-          <t>S&amp;P 500</t>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>IAU</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr"/>
+      <c r="D65" s="12" t="inlineStr">
+        <is>
+          <t>Natural Resources</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Gold Bullion</t>
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.3435590842611607</v>
+        <v>0.5064698377984327</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.199660912694537</v>
+        <v>0.2198937426210152</v>
       </c>
       <c r="H65" s="3" t="n">
-        <v>0.1971219972480989</v>
-      </c>
-      <c r="I65" s="3" t="n">
-        <v>0.151555666126193</v>
+        <v>0.2054309327036601</v>
+      </c>
+      <c r="I65" s="5" t="n">
+        <v>-0.1458979127918992</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.0469448480365231</v>
+        <v>0.01572868026542151</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.00212084938066015</v>
+        <v>0.01199804113614089</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.00385426232264563</v>
+        <v>-0.008754047247871544</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N65" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4128,153 +4131,157 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>IAU</t>
+          <t>QUAL</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
-      <c r="D66" s="12" t="inlineStr">
+      <c r="D66" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Quality Factor</t>
+        </is>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>0.2726696157562489</v>
+      </c>
+      <c r="G66" s="3" t="n">
+        <v>0.1799822630071801</v>
+      </c>
+      <c r="H66" s="3" t="n">
+        <v>0.2040428471746563</v>
+      </c>
+      <c r="I66" s="3" t="n">
+        <v>0.1063113418612354</v>
+      </c>
+      <c r="J66" s="3" t="n">
+        <v>0.03621711241274772</v>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>-0.01998316274535861</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>-0.006289873303980564</v>
+      </c>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N66" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="21" customHeight="1">
+      <c r="A67" s="15" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="16" t="inlineStr">
+        <is>
+          <t>GLD</t>
+        </is>
+      </c>
+      <c r="C67" s="15" t="inlineStr"/>
+      <c r="D67" s="12" t="inlineStr">
         <is>
           <t>Natural Resources</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
+      <c r="E67" s="15" t="inlineStr">
         <is>
           <t>Gold Bullion</t>
         </is>
       </c>
-      <c r="F66" s="3" t="n">
-        <v>0.5115098785571868</v>
-      </c>
-      <c r="G66" s="3" t="n">
-        <v>0.2463010013450906</v>
-      </c>
-      <c r="H66" s="3" t="n">
-        <v>0.1936930204752654</v>
-      </c>
-      <c r="I66" s="5" t="n">
-        <v>-0.14013198597649</v>
-      </c>
-      <c r="J66" s="3" t="n">
-        <v>0.0267175572519085</v>
-      </c>
-      <c r="K66" s="3" t="n">
-        <v>0.04407161637661194</v>
-      </c>
-      <c r="L66" s="5" t="n">
-        <v>-0.008442330558858457</v>
-      </c>
-      <c r="M66" s="6" t="inlineStr">
+      <c r="F67" s="3" t="n">
+        <v>0.5030009319664492</v>
+      </c>
+      <c r="G67" s="3" t="n">
+        <v>0.2178824950913758</v>
+      </c>
+      <c r="H67" s="3" t="n">
+        <v>0.2036550370034738</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>-0.1467631684760755</v>
+      </c>
+      <c r="J67" s="3" t="n">
+        <v>0.01487653233317388</v>
+      </c>
+      <c r="K67" s="3" t="n">
+        <v>0.01182021231209363</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>-0.008825626275290599</v>
+      </c>
+      <c r="M67" s="6" t="inlineStr">
         <is>
           <t>MIXED_TRANSITION</t>
         </is>
       </c>
-      <c r="N66" s="7" t="inlineStr">
+      <c r="N67" s="7" t="inlineStr">
         <is>
           <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="21" customHeight="1">
-      <c r="A67" t="n">
-        <v>66</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>QUAL</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
-      <c r="D67" s="19" t="inlineStr">
+    <row r="68" ht="21" customHeight="1">
+      <c r="A68" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>OEF</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D68" s="19" t="inlineStr">
         <is>
           <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>Quality Factor</t>
-        </is>
-      </c>
-      <c r="F67" s="3" t="n">
-        <v>0.2597787759939749</v>
-      </c>
-      <c r="G67" s="3" t="n">
-        <v>0.1805259963985431</v>
-      </c>
-      <c r="H67" s="3" t="n">
-        <v>0.1932021448907368</v>
-      </c>
-      <c r="I67" s="3" t="n">
-        <v>0.1248023884404867</v>
-      </c>
-      <c r="J67" s="3" t="n">
-        <v>0.04615179003503123</v>
-      </c>
-      <c r="K67" s="5" t="n">
-        <v>-0.01062363870738314</v>
-      </c>
-      <c r="L67" s="5" t="n">
-        <v>-0.003938064978072142</v>
-      </c>
-      <c r="M67" s="6" t="inlineStr">
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>S&amp;P 100</t>
+        </is>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>0.3825287040841341</v>
+      </c>
+      <c r="G68" s="3" t="n">
+        <v>0.1947313627138785</v>
+      </c>
+      <c r="H68" s="3" t="n">
+        <v>0.2022009837590333</v>
+      </c>
+      <c r="I68" s="3" t="n">
+        <v>0.1460628386989751</v>
+      </c>
+      <c r="J68" s="3" t="n">
+        <v>0.04055206801918354</v>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>-0.006213288082495771</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>-0.003977079463094224</v>
+      </c>
+      <c r="M68" s="6" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="N67" s="7" t="inlineStr">
+      <c r="N68" s="7" t="inlineStr">
         <is>
           <t>Established trend; positive 3m but negative 1m; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="21" customHeight="1">
-      <c r="A68" s="15" t="n">
-        <v>67</v>
-      </c>
-      <c r="B68" s="16" t="inlineStr">
-        <is>
-          <t>GLD</t>
-        </is>
-      </c>
-      <c r="C68" s="15" t="inlineStr"/>
-      <c r="D68" s="12" t="inlineStr">
-        <is>
-          <t>Natural Resources</t>
-        </is>
-      </c>
-      <c r="E68" s="15" t="inlineStr">
-        <is>
-          <t>Gold Bullion</t>
-        </is>
-      </c>
-      <c r="F68" s="3" t="n">
-        <v>0.5086788813886209</v>
-      </c>
-      <c r="G68" s="3" t="n">
-        <v>0.2451253481894149</v>
-      </c>
-      <c r="H68" s="3" t="n">
-        <v>0.1927821482139032</v>
-      </c>
-      <c r="I68" s="5" t="n">
-        <v>-0.1409473928744905</v>
-      </c>
-      <c r="J68" s="3" t="n">
-        <v>0.02657480314960625</v>
-      </c>
-      <c r="K68" s="3" t="n">
-        <v>0.04388328585726375</v>
-      </c>
-      <c r="L68" s="5" t="n">
-        <v>-0.00841012139827424</v>
-      </c>
-      <c r="M68" s="6" t="inlineStr">
-        <is>
-          <t>MIXED_TRANSITION</t>
-        </is>
-      </c>
-      <c r="N68" s="7" t="inlineStr">
-        <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4284,44 +4291,40 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>OEF</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D69" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>VWO</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr"/>
+      <c r="D69" s="9" t="inlineStr">
+        <is>
+          <t>International</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>S&amp;P 100</t>
+          <t>Emerging Markets</t>
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3622355793251881</v>
+        <v>0.3783788556252263</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.1956732147943772</v>
+        <v>0.2092040530621921</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0.1925134514647706</v>
+        <v>0.1940001484106915</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1607244253454756</v>
+        <v>0.1121491845136178</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.0495456856083758</v>
+        <v>0.05113638419241129</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.002649666824072527</v>
+        <v>0.01273358690259641</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.005542256452955807</v>
+        <v>-0.003255208333333259</v>
       </c>
       <c r="M69" s="6" t="inlineStr">
         <is>
@@ -4355,34 +4358,34 @@
         </is>
       </c>
       <c r="F70" s="3" t="n">
-        <v>0.2689363759821515</v>
+        <v>0.276640648848975</v>
       </c>
       <c r="G70" s="3" t="n">
-        <v>0.1828297548786559</v>
+        <v>0.175460637043759</v>
       </c>
       <c r="H70" s="3" t="n">
-        <v>0.1805613142528613</v>
+        <v>0.1873290724997061</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0.1142535522024297</v>
+        <v>0.1054816803180532</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0.05782676711006696</v>
-      </c>
-      <c r="K70" s="3" t="n">
-        <v>0.001921493274773534</v>
+        <v>0.0535805032199308</v>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>-0.009995910763778482</v>
       </c>
       <c r="L70" s="5" t="n">
-        <v>-0.004771642808452659</v>
+        <v>-0.005068493150685027</v>
       </c>
       <c r="M70" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N70" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4411,25 +4414,25 @@
         </is>
       </c>
       <c r="F71" s="3" t="n">
-        <v>0.1716899341921996</v>
+        <v>0.1939903572728365</v>
       </c>
       <c r="G71" s="3" t="n">
-        <v>0.2220921249669161</v>
+        <v>0.2220128981494067</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0.1732895662995309</v>
+        <v>0.1779170366234846</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.1180803678969065</v>
+        <v>0.1148212554466594</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.05643272307669922</v>
+        <v>0.05342601016586013</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0.04159464131374246</v>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v>-0.0040289256198347</v>
+        <v>0.03743545611015486</v>
+      </c>
+      <c r="L71" s="3" t="n">
+        <v>0.0003111710403485013</v>
       </c>
       <c r="M71" s="6" t="inlineStr">
         <is>
@@ -4438,7 +4441,7 @@
       </c>
       <c r="N71" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d down.</t>
+          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4448,44 +4451,40 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KBE</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D72" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
+          <t>MGK</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr"/>
+      <c r="D72" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Banks</t>
+          <t>Mega Cap Growth</t>
         </is>
       </c>
       <c r="F72" s="3" t="n">
-        <v>0.3200632269889565</v>
+        <v>0.3986097367981389</v>
       </c>
       <c r="G72" s="3" t="n">
-        <v>0.1521994604977654</v>
+        <v>0.1664381849334453</v>
       </c>
       <c r="H72" s="3" t="n">
-        <v>0.1656589580893892</v>
+        <v>0.177461894708778</v>
       </c>
       <c r="I72" s="3" t="n">
-        <v>0.1774918875405691</v>
+        <v>0.1539135571354793</v>
       </c>
       <c r="J72" s="3" t="n">
-        <v>0.08721738781999711</v>
+        <v>0.02469445150973915</v>
       </c>
       <c r="K72" s="5" t="n">
-        <v>-0.01154668567355666</v>
-      </c>
-      <c r="L72" s="3" t="n">
-        <v>0.003328027781797083</v>
+        <v>-0.00936226456658229</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>-0.003214008644574995</v>
       </c>
       <c r="M72" s="6" t="inlineStr">
         <is>
@@ -4494,7 +4493,7 @@
       </c>
       <c r="N72" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4504,49 +4503,53 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>MGK</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr"/>
-      <c r="D73" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+          <t>KBE</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D73" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Mega Cap Growth</t>
+          <t>Banks</t>
         </is>
       </c>
       <c r="F73" s="3" t="n">
-        <v>0.3616466367701576</v>
+        <v>0.33258750268646</v>
       </c>
       <c r="G73" s="3" t="n">
-        <v>0.1670324457894012</v>
+        <v>0.15402125716353</v>
       </c>
       <c r="H73" s="3" t="n">
-        <v>0.1641869715782336</v>
+        <v>0.1716028346449825</v>
       </c>
       <c r="I73" s="3" t="n">
-        <v>0.1723466605135937</v>
+        <v>0.1729202144706561</v>
       </c>
       <c r="J73" s="3" t="n">
-        <v>0.03258203642121704</v>
-      </c>
-      <c r="K73" s="3" t="n">
-        <v>0.002444172869681127</v>
+        <v>0.07911732259366078</v>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>-0.01500643132771184</v>
       </c>
       <c r="L73" s="5" t="n">
-        <v>-0.004852762766074714</v>
+        <v>-0.006057109893279566</v>
       </c>
       <c r="M73" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N73" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4571,34 +4574,34 @@
         </is>
       </c>
       <c r="F74" s="3" t="n">
-        <v>0.3329624119123964</v>
+        <v>0.3613885364513962</v>
       </c>
       <c r="G74" s="3" t="n">
-        <v>0.15726662184341</v>
+        <v>0.1508951141285448</v>
       </c>
       <c r="H74" s="3" t="n">
-        <v>0.1536837530451332</v>
+        <v>0.1665446794198113</v>
       </c>
       <c r="I74" s="3" t="n">
-        <v>0.1664030893954545</v>
+        <v>0.1449763106830873</v>
       </c>
       <c r="J74" s="3" t="n">
-        <v>0.0538258501400164</v>
-      </c>
-      <c r="K74" s="3" t="n">
-        <v>0.003105590062111752</v>
+        <v>0.04545512987906264</v>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>-0.01341531581889333</v>
       </c>
       <c r="L74" s="5" t="n">
-        <v>-0.008649553571428603</v>
+        <v>-0.006473402758232605</v>
       </c>
       <c r="M74" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N74" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4623,25 +4626,25 @@
         </is>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.3382947916462911</v>
+        <v>0.3728037776351192</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.14858002063956</v>
+        <v>0.1481171927658866</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.151566718262478</v>
+        <v>0.1645300321451133</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.1610479579021633</v>
+        <v>0.1420210270936946</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.03046773231978617</v>
+        <v>0.02352097573477363</v>
       </c>
       <c r="K75" s="5" t="n">
-        <v>-0.002593594948128164</v>
+        <v>-0.0140939597315437</v>
       </c>
       <c r="L75" s="5" t="n">
-        <v>-0.004837983798379741</v>
+        <v>-0.003504804974561959</v>
       </c>
       <c r="M75" s="6" t="inlineStr">
         <is>
@@ -4679,25 +4682,25 @@
         </is>
       </c>
       <c r="F76" s="3" t="n">
-        <v>0.1183230276739218</v>
+        <v>0.1151178706991003</v>
       </c>
       <c r="G76" s="3" t="n">
-        <v>0.1120594594296969</v>
+        <v>0.1221415025436818</v>
       </c>
       <c r="H76" s="3" t="n">
-        <v>0.1420841480499133</v>
+        <v>0.1507390145198644</v>
       </c>
       <c r="I76" s="3" t="n">
-        <v>0.1047984789697887</v>
+        <v>0.1119057141769471</v>
       </c>
       <c r="J76" s="3" t="n">
-        <v>0.09269660865573459</v>
+        <v>0.1004626491537068</v>
       </c>
       <c r="K76" s="5" t="n">
-        <v>-0.02628938390527802</v>
+        <v>-0.02485143165856296</v>
       </c>
       <c r="L76" s="5" t="n">
-        <v>-0.01562182998579831</v>
+        <v>-0.007969222313822466</v>
       </c>
       <c r="M76" s="6" t="inlineStr">
         <is>
@@ -4735,25 +4738,25 @@
         </is>
       </c>
       <c r="F77" s="3" t="n">
-        <v>0.2480499989697713</v>
+        <v>0.2476034079985261</v>
       </c>
       <c r="G77" s="3" t="n">
-        <v>0.1103589276089303</v>
+        <v>0.1056387017513472</v>
       </c>
       <c r="H77" s="3" t="n">
-        <v>0.1404287391249801</v>
+        <v>0.1477710503375029</v>
       </c>
       <c r="I77" s="3" t="n">
-        <v>0.1225577590144293</v>
+        <v>0.1046601734653514</v>
       </c>
       <c r="J77" s="3" t="n">
-        <v>0.04863212152750895</v>
+        <v>0.03482341256581711</v>
       </c>
       <c r="K77" s="5" t="n">
-        <v>-0.02636711131913561</v>
+        <v>-0.03670797287818572</v>
       </c>
       <c r="L77" s="5" t="n">
-        <v>-0.01070069752694991</v>
+        <v>-0.009694735998718063</v>
       </c>
       <c r="M77" s="6" t="inlineStr">
         <is>
@@ -4787,34 +4790,34 @@
         </is>
       </c>
       <c r="F78" s="3" t="n">
-        <v>0.2816548883262431</v>
+        <v>0.3064583455670453</v>
       </c>
       <c r="G78" s="3" t="n">
-        <v>0.1209870409007974</v>
+        <v>0.1219594261817281</v>
       </c>
       <c r="H78" s="3" t="n">
-        <v>0.1375228054869186</v>
+        <v>0.1352136262148658</v>
       </c>
       <c r="I78" s="5" t="n">
-        <v>-0.01645445909090726</v>
-      </c>
-      <c r="J78" s="5" t="n">
-        <v>-0.002781775678525333</v>
+        <v>-0.01553012610498161</v>
+      </c>
+      <c r="J78" s="3" t="n">
+        <v>0.006047344912958552</v>
       </c>
       <c r="K78" s="5" t="n">
-        <v>-0.01453664445790437</v>
+        <v>-0.01167551175132675</v>
       </c>
       <c r="L78" s="3" t="n">
-        <v>0.001076757421935026</v>
+        <v>0.001536570374923274</v>
       </c>
       <c r="M78" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N78" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -4839,25 +4842,25 @@
         </is>
       </c>
       <c r="F79" s="3" t="n">
-        <v>0.1355254539420063</v>
+        <v>0.1615015050065065</v>
       </c>
       <c r="G79" s="3" t="n">
-        <v>0.08641453385772246</v>
+        <v>0.06825724565422098</v>
       </c>
       <c r="H79" s="3" t="n">
-        <v>0.1163324862504662</v>
+        <v>0.1254105044553291</v>
       </c>
       <c r="I79" s="5" t="n">
-        <v>-0.00338102769308779</v>
+        <v>-0.01031161859925545</v>
       </c>
       <c r="J79" s="5" t="n">
-        <v>-0.05297577767964234</v>
+        <v>-0.06790571616572927</v>
       </c>
       <c r="K79" s="5" t="n">
-        <v>-0.0268002165674065</v>
-      </c>
-      <c r="L79" s="3" t="n">
-        <v>0.00390952247975429</v>
+        <v>-0.05078436586014345</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>-0.006954102920723182</v>
       </c>
       <c r="M79" s="6" t="inlineStr">
         <is>
@@ -4866,7 +4869,7 @@
       </c>
       <c r="N79" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4895,34 +4898,34 @@
         </is>
       </c>
       <c r="F80" s="3" t="n">
-        <v>0.08358221911117791</v>
+        <v>0.08742321395752528</v>
       </c>
       <c r="G80" s="3" t="n">
-        <v>0.1506191353843189</v>
+        <v>0.1195955259313846</v>
       </c>
       <c r="H80" s="3" t="n">
-        <v>0.114585945900415</v>
+        <v>0.1231018186151871</v>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.1430651619949037</v>
+        <v>0.1184925715666141</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.1655530809205643</v>
-      </c>
-      <c r="K80" s="3" t="n">
-        <v>0.03232876712328769</v>
+        <v>0.1422227704452943</v>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>-0.00312197222521271</v>
       </c>
       <c r="L80" s="5" t="n">
-        <v>-0.0008485362749257597</v>
+        <v>-0.01698513800424639</v>
       </c>
       <c r="M80" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N80" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -4932,40 +4935,40 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>VNQ</t>
+          <t>VONG</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
-      <c r="D81" s="17" t="inlineStr">
-        <is>
-          <t>Inflation &amp; Real Assets</t>
+      <c r="D81" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>U.S. Equity REITs</t>
+          <t>Large Growth</t>
         </is>
       </c>
       <c r="F81" s="3" t="n">
-        <v>0.07915144326221046</v>
+        <v>0.3167517378136087</v>
       </c>
       <c r="G81" s="3" t="n">
-        <v>0.09075567017467434</v>
+        <v>0.1027335290149729</v>
       </c>
       <c r="H81" s="3" t="n">
-        <v>0.1137022068727878</v>
+        <v>0.1149890210612494</v>
       </c>
       <c r="I81" s="3" t="n">
-        <v>0.04651865830450697</v>
+        <v>0.0923451119171208</v>
       </c>
       <c r="J81" s="3" t="n">
-        <v>0.0007884748920772289</v>
+        <v>0.003405453061565922</v>
       </c>
       <c r="K81" s="5" t="n">
-        <v>-0.02060383516931874</v>
+        <v>-0.01099158091674457</v>
       </c>
       <c r="L81" s="5" t="n">
-        <v>-0.006621146285950785</v>
+        <v>-0.001416765053128599</v>
       </c>
       <c r="M81" s="6" t="inlineStr">
         <is>
@@ -4984,7 +4987,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>VONG</t>
+          <t>IWF</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -4995,29 +4998,29 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Large Growth</t>
+          <t>Russell 1000 Growth</t>
         </is>
       </c>
       <c r="F82" s="3" t="n">
-        <v>0.2821678253853748</v>
+        <v>0.3141706371157758</v>
       </c>
       <c r="G82" s="3" t="n">
-        <v>0.1029624215674034</v>
+        <v>0.101198677214172</v>
       </c>
       <c r="H82" s="3" t="n">
-        <v>0.1039173673869422</v>
+        <v>0.1134411683915102</v>
       </c>
       <c r="I82" s="3" t="n">
-        <v>0.1072072188939013</v>
+        <v>0.09138943387342202</v>
       </c>
       <c r="J82" s="3" t="n">
-        <v>0.006896950376516386</v>
+        <v>0.002915296448248395</v>
       </c>
       <c r="K82" s="5" t="n">
-        <v>-0.0008650519031141446</v>
+        <v>-0.01099518459069015</v>
       </c>
       <c r="L82" s="5" t="n">
-        <v>-0.0001573935626032474</v>
+        <v>-0.001458552791507972</v>
       </c>
       <c r="M82" s="6" t="inlineStr">
         <is>
@@ -5036,40 +5039,40 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IWF</t>
+          <t>VNQ</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
-      <c r="D83" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D83" s="17" t="inlineStr">
+        <is>
+          <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Russell 1000 Growth</t>
+          <t>U.S. Equity REITs</t>
         </is>
       </c>
       <c r="F83" s="3" t="n">
-        <v>0.2794606922784824</v>
+        <v>0.1098850576361321</v>
       </c>
       <c r="G83" s="3" t="n">
-        <v>0.1008469550706432</v>
+        <v>0.08085259535261735</v>
       </c>
       <c r="H83" s="3" t="n">
-        <v>0.1016497767703139</v>
+        <v>0.1056778316416351</v>
       </c>
       <c r="I83" s="3" t="n">
-        <v>0.1060873595664575</v>
+        <v>0.04634961114927316</v>
       </c>
       <c r="J83" s="3" t="n">
-        <v>0.006754300246448297</v>
+        <v>0.01673912391138455</v>
       </c>
       <c r="K83" s="5" t="n">
-        <v>-0.0007287449392713308</v>
-      </c>
-      <c r="L83" s="5" t="n">
-        <v>-0.0001620351616301585</v>
+        <v>-0.02245250431778933</v>
+      </c>
+      <c r="L83" s="3" t="n">
+        <v>0.002082899395959181</v>
       </c>
       <c r="M83" s="6" t="inlineStr">
         <is>
@@ -5078,7 +5081,7 @@
       </c>
       <c r="N83" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5103,25 +5106,25 @@
         </is>
       </c>
       <c r="F84" s="3" t="n">
-        <v>0.2023957347646692</v>
+        <v>0.2157750842307866</v>
       </c>
       <c r="G84" s="3" t="n">
-        <v>0.09416566425739115</v>
+        <v>0.10578130044318</v>
       </c>
       <c r="H84" s="3" t="n">
-        <v>0.08908189559558255</v>
+        <v>0.1035100590158233</v>
       </c>
       <c r="I84" s="3" t="n">
-        <v>0.161938755693714</v>
+        <v>0.160545628875987</v>
       </c>
       <c r="J84" s="3" t="n">
-        <v>0.1162403101899339</v>
+        <v>0.1154042675294027</v>
       </c>
       <c r="K84" s="3" t="n">
-        <v>0.004667939741141769</v>
+        <v>0.00205819730305179</v>
       </c>
       <c r="L84" s="5" t="n">
-        <v>-0.007268152910755443</v>
+        <v>-0.006054206265399653</v>
       </c>
       <c r="M84" s="6" t="inlineStr">
         <is>
@@ -5155,25 +5158,25 @@
         </is>
       </c>
       <c r="F85" s="3" t="n">
-        <v>0.1834074357871016</v>
+        <v>0.1962568275577192</v>
       </c>
       <c r="G85" s="3" t="n">
-        <v>0.09141025357922961</v>
+        <v>0.1052640211900091</v>
       </c>
       <c r="H85" s="3" t="n">
-        <v>0.08596259482642443</v>
+        <v>0.1022023480011172</v>
       </c>
       <c r="I85" s="3" t="n">
-        <v>0.1588536212363327</v>
+        <v>0.1575656543332895</v>
       </c>
       <c r="J85" s="3" t="n">
-        <v>0.1147901445543076</v>
+        <v>0.1153037028803214</v>
       </c>
       <c r="K85" s="3" t="n">
-        <v>0.005016433143054888</v>
+        <v>0.002777777777777768</v>
       </c>
       <c r="L85" s="5" t="n">
-        <v>-0.007855191256830651</v>
+        <v>-0.005851979345955272</v>
       </c>
       <c r="M85" s="6" t="inlineStr">
         <is>
@@ -5207,25 +5210,25 @@
         </is>
       </c>
       <c r="F86" s="3" t="n">
-        <v>0.06726962831377814</v>
+        <v>0.06067079989233504</v>
       </c>
       <c r="G86" s="3" t="n">
-        <v>0.07794880991652886</v>
+        <v>0.07018095704986926</v>
       </c>
       <c r="H86" s="3" t="n">
-        <v>0.08470351397488507</v>
+        <v>0.08174567229646001</v>
       </c>
       <c r="I86" s="5" t="n">
-        <v>-0.001559290331758945</v>
+        <v>-0.008124003426279613</v>
       </c>
       <c r="J86" s="3" t="n">
-        <v>0.02069589958058415</v>
+        <v>0.02075719285270927</v>
       </c>
       <c r="K86" s="5" t="n">
-        <v>-0.006227235342497917</v>
+        <v>-0.01069078947368429</v>
       </c>
       <c r="L86" s="5" t="n">
-        <v>-0.007975604034717421</v>
+        <v>-0.004374556632773752</v>
       </c>
       <c r="M86" s="6" t="inlineStr">
         <is>
@@ -5244,53 +5247,49 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>EUO</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D87" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
+          <t>XLU</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr"/>
+      <c r="D87" s="14" t="inlineStr">
+        <is>
+          <t>Defensive Equity</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2x Inverse Euro</t>
-        </is>
-      </c>
-      <c r="F87" s="5" t="n">
-        <v>-0.07397090683998764</v>
+          <t>Utilities</t>
+        </is>
+      </c>
+      <c r="F87" s="3" t="n">
+        <v>0.1918289686219015</v>
       </c>
       <c r="G87" s="3" t="n">
-        <v>0.05537918871252212</v>
+        <v>0.06827320408510729</v>
       </c>
       <c r="H87" s="3" t="n">
-        <v>0.06631393298059951</v>
-      </c>
-      <c r="I87" s="3" t="n">
-        <v>0.02150904745646987</v>
-      </c>
-      <c r="J87" s="5" t="n">
-        <v>-0.00366300366300365</v>
+        <v>0.07393716989745336</v>
+      </c>
+      <c r="I87" s="5" t="n">
+        <v>-0.06163877778379045</v>
+      </c>
+      <c r="J87" s="3" t="n">
+        <v>0.003148064735903455</v>
       </c>
       <c r="K87" s="5" t="n">
-        <v>-0.01025471386040355</v>
+        <v>-0.005274019720247547</v>
       </c>
       <c r="L87" s="3" t="n">
-        <v>0.003690036900369176</v>
+        <v>0.006963788300835771</v>
       </c>
       <c r="M87" s="6" t="inlineStr">
         <is>
-          <t>FAST_REVERSAL</t>
+          <t>CORRECTION</t>
         </is>
       </c>
       <c r="N87" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5300,40 +5299,44 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>XLU</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr"/>
-      <c r="D88" s="14" t="inlineStr">
-        <is>
-          <t>Defensive Equity</t>
+          <t>EUO</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D88" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="F88" s="3" t="n">
-        <v>0.1588459829087914</v>
+          <t>2x Inverse Euro</t>
+        </is>
+      </c>
+      <c r="F88" s="5" t="n">
+        <v>-0.07465923172242872</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0.05759157717876762</v>
+        <v>0.06450463292943698</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0.06495642103098764</v>
-      </c>
-      <c r="I88" s="5" t="n">
-        <v>-0.06593495918679138</v>
+        <v>0.07234497505345683</v>
+      </c>
+      <c r="I88" s="3" t="n">
+        <v>0.01945392491467568</v>
       </c>
       <c r="J88" s="5" t="n">
-        <v>-0.02243323340929726</v>
+        <v>-0.003336670003336595</v>
       </c>
       <c r="K88" s="5" t="n">
-        <v>-0.006915629322268413</v>
-      </c>
-      <c r="L88" s="3" t="n">
-        <v>0.001161980013943742</v>
+        <v>-0.007311399135925489</v>
+      </c>
+      <c r="L88" s="5" t="n">
+        <v>-0.001671122994652441</v>
       </c>
       <c r="M88" s="6" t="inlineStr">
         <is>
@@ -5342,7 +5345,7 @@
       </c>
       <c r="N88" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5352,165 +5355,165 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
+          <t>VOT</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HB</t>
+        </is>
+      </c>
+      <c r="D89" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Mid Growth</t>
+        </is>
+      </c>
+      <c r="F89" s="3" t="n">
+        <v>0.2177748192480871</v>
+      </c>
+      <c r="G89" s="3" t="n">
+        <v>0.04889184006475955</v>
+      </c>
+      <c r="H89" s="3" t="n">
+        <v>0.07195633079193353</v>
+      </c>
+      <c r="I89" s="3" t="n">
+        <v>0.09466009167582334</v>
+      </c>
+      <c r="J89" s="3" t="n">
+        <v>0.02111653149647763</v>
+      </c>
+      <c r="K89" s="5" t="n">
+        <v>-0.02151625963170944</v>
+      </c>
+      <c r="L89" s="5" t="n">
+        <v>-0.001632353920980822</v>
+      </c>
+      <c r="M89" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N89" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="21" customHeight="1">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
           <t>EDEN</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D89" s="9" t="inlineStr">
+      <c r="D90" s="9" t="inlineStr">
         <is>
           <t>International</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Denmark Equity</t>
         </is>
       </c>
-      <c r="F89" s="3" t="n">
+      <c r="F90" s="3" t="n">
         <v>0.1234111050972515</v>
       </c>
-      <c r="G89" s="3" t="n">
+      <c r="G90" s="3" t="n">
         <v>0.1244551445901914</v>
       </c>
-      <c r="H89" s="3" t="n">
+      <c r="H90" s="3" t="n">
         <v>0.06155451612850937</v>
       </c>
-      <c r="I89" s="3" t="n">
+      <c r="I90" s="3" t="n">
         <v>0.1475540776083568</v>
       </c>
-      <c r="J89" s="3" t="n">
+      <c r="J90" s="3" t="n">
         <v>0.1098533609878889</v>
       </c>
-      <c r="K89" s="3" t="n">
+      <c r="K90" s="3" t="n">
         <v>0.05925331907689557</v>
       </c>
-      <c r="L89" s="5" t="n">
+      <c r="L90" s="5" t="n">
         <v>-0.007762290292963936</v>
       </c>
-      <c r="M89" s="6" t="inlineStr">
+      <c r="M90" s="6" t="inlineStr">
         <is>
           <t>ACCELERATING</t>
         </is>
       </c>
-      <c r="N89" s="7" t="inlineStr">
+      <c r="N90" s="7" t="inlineStr">
         <is>
           <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
-    <row r="90" ht="21" customHeight="1">
-      <c r="A90" s="15" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="16" t="inlineStr">
+    <row r="91" ht="21" customHeight="1">
+      <c r="A91" s="15" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="16" t="inlineStr">
         <is>
           <t>UUP</t>
         </is>
       </c>
-      <c r="C90" s="15" t="inlineStr">
+      <c r="C91" s="15" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D90" s="21" t="inlineStr">
+      <c r="D91" s="21" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="E90" s="15" t="inlineStr">
+      <c r="E91" s="15" t="inlineStr">
         <is>
           <t>US Dollar Index Bullish</t>
         </is>
       </c>
-      <c r="F90" s="3" t="n">
-        <v>0.01891236935631846</v>
-      </c>
-      <c r="G90" s="3" t="n">
-        <v>0.05442999889856925</v>
-      </c>
-      <c r="H90" s="3" t="n">
-        <v>0.05856060074610636</v>
-      </c>
-      <c r="I90" s="3" t="n">
-        <v>0.02220604295595185</v>
-      </c>
-      <c r="J90" s="3" t="n">
-        <v>0.002141327623126354</v>
-      </c>
-      <c r="K90" s="5" t="n">
-        <v>-0.003902092940759272</v>
-      </c>
-      <c r="L90" s="3" t="n">
-        <v>0.002499107461620742</v>
-      </c>
-      <c r="M90" s="6" t="inlineStr">
-        <is>
-          <t>CORRECTION</t>
-        </is>
-      </c>
-      <c r="N90" s="7" t="inlineStr">
-        <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="21" customHeight="1">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>VOT</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>HB</t>
-        </is>
-      </c>
-      <c r="D91" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>Mid Growth</t>
-        </is>
-      </c>
       <c r="F91" s="3" t="n">
-        <v>0.1850516411129475</v>
+        <v>0.01599669471000831</v>
       </c>
       <c r="G91" s="3" t="n">
-        <v>0.04511907901795675</v>
+        <v>0.05604332132128742</v>
       </c>
       <c r="H91" s="3" t="n">
-        <v>0.05156011538341487</v>
+        <v>0.05944017260502288</v>
       </c>
       <c r="I91" s="3" t="n">
-        <v>0.1083126323317054</v>
-      </c>
-      <c r="J91" s="3" t="n">
-        <v>0.02400564571600916</v>
+        <v>0.01893663510560817</v>
+      </c>
+      <c r="J91" s="5" t="n">
+        <v>-0.001783803068141299</v>
       </c>
       <c r="K91" s="5" t="n">
-        <v>-0.006125219349071176</v>
-      </c>
-      <c r="L91" s="3" t="n">
-        <v>0.001100550275137557</v>
+        <v>-0.00320627003918772</v>
+      </c>
+      <c r="L91" s="5" t="n">
+        <v>-0.003561253561253475</v>
       </c>
       <c r="M91" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N91" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5539,25 +5542,25 @@
         </is>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0.243166914133915</v>
-      </c>
-      <c r="G92" s="3" t="n">
-        <v>0.01522076775004222</v>
+        <v>0.2317697044105949</v>
+      </c>
+      <c r="G92" s="5" t="n">
+        <v>-0.004775002300912989</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0.04141552668502424</v>
+        <v>0.04807901543403381</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0.05954308358488691</v>
+        <v>0.04585648979572077</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0.06231378420201339</v>
+        <v>0.03195322470282713</v>
       </c>
       <c r="K92" s="5" t="n">
-        <v>-0.02515303283249848</v>
-      </c>
-      <c r="L92" s="3" t="n">
-        <v>0.009915830739075204</v>
+        <v>-0.05042942083241575</v>
+      </c>
+      <c r="L92" s="5" t="n">
+        <v>-0.01541271834684332</v>
       </c>
       <c r="M92" s="6" t="inlineStr">
         <is>
@@ -5566,7 +5569,7 @@
       </c>
       <c r="N92" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5595,25 +5598,25 @@
         </is>
       </c>
       <c r="F93" s="3" t="n">
-        <v>0.006628101563802336</v>
+        <v>0.005440147056304134</v>
       </c>
       <c r="G93" s="3" t="n">
-        <v>0.03140311245850147</v>
+        <v>0.03334781074747806</v>
       </c>
       <c r="H93" s="3" t="n">
-        <v>0.04005384386303334</v>
+        <v>0.04045528518135444</v>
       </c>
       <c r="I93" s="3" t="n">
-        <v>0.008846153846153948</v>
+        <v>0.006925740669488478</v>
       </c>
       <c r="J93" s="5" t="n">
-        <v>-0.009441087613293098</v>
+        <v>-0.01095993953136809</v>
       </c>
       <c r="K93" s="5" t="n">
-        <v>-0.008317580340264641</v>
-      </c>
-      <c r="L93" s="3" t="n">
-        <v>0.001909854851031456</v>
+        <v>-0.006831119544592035</v>
+      </c>
+      <c r="L93" s="5" t="n">
+        <v>-0.002287457110179081</v>
       </c>
       <c r="M93" s="6" t="inlineStr">
         <is>
@@ -5622,7 +5625,7 @@
       </c>
       <c r="N93" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5647,34 +5650,34 @@
         </is>
       </c>
       <c r="F94" s="3" t="n">
-        <v>0.08599359141460416</v>
+        <v>0.09037615383853947</v>
       </c>
       <c r="G94" s="3" t="n">
-        <v>0.03894954461270528</v>
+        <v>0.03869783294320484</v>
       </c>
       <c r="H94" s="3" t="n">
-        <v>0.03720277833913666</v>
+        <v>0.03864658607606719</v>
       </c>
       <c r="I94" s="3" t="n">
-        <v>0.02370734091802928</v>
+        <v>0.0178353433481877</v>
       </c>
       <c r="J94" s="3" t="n">
-        <v>0.011595073349292</v>
+        <v>0.01045134342740295</v>
       </c>
       <c r="K94" s="3" t="n">
-        <v>0.001684112605604193</v>
-      </c>
-      <c r="L94" s="5" t="n">
-        <v>-0.000631233430122391</v>
+        <v>4.934004292200811e-05</v>
+      </c>
+      <c r="L94" s="3" t="n">
+        <v>0.000252652854977331</v>
       </c>
       <c r="M94" s="6" t="inlineStr">
         <is>
-          <t>COOLING</t>
+          <t>STEADY_POSITIVE</t>
         </is>
       </c>
       <c r="N94" s="7" t="inlineStr">
         <is>
-          <t>Positive trend losing velocity into 1m; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5703,34 +5706,34 @@
         </is>
       </c>
       <c r="F95" s="3" t="n">
-        <v>0.1207504478549839</v>
+        <v>0.1457415121590284</v>
       </c>
       <c r="G95" s="5" t="n">
-        <v>-0.003725390809229623</v>
+        <v>-0.01154543208271985</v>
       </c>
       <c r="H95" s="3" t="n">
-        <v>0.02209842567312537</v>
+        <v>0.03530854743602019</v>
       </c>
       <c r="I95" s="3" t="n">
-        <v>0.03465868209422918</v>
-      </c>
-      <c r="J95" s="3" t="n">
-        <v>0.01177211397773026</v>
+        <v>0.02705392061426393</v>
+      </c>
+      <c r="J95" s="5" t="n">
+        <v>-0.00124254664314194</v>
       </c>
       <c r="K95" s="5" t="n">
-        <v>-0.0252654889526398</v>
+        <v>-0.04525605398967847</v>
       </c>
       <c r="L95" s="5" t="n">
-        <v>-0.009461947626841383</v>
+        <v>-0.006557546341715237</v>
       </c>
       <c r="M95" s="6" t="inlineStr">
         <is>
-          <t>CORRECTION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N95" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -5755,25 +5758,25 @@
         </is>
       </c>
       <c r="F96" s="3" t="n">
-        <v>0.04850417915220362</v>
+        <v>0.04786792136342632</v>
       </c>
       <c r="G96" s="3" t="n">
-        <v>0.02265642412273938</v>
+        <v>0.02117659255543813</v>
       </c>
       <c r="H96" s="3" t="n">
-        <v>0.02098221377412379</v>
+        <v>0.02100039797751041</v>
       </c>
       <c r="I96" s="3" t="n">
-        <v>0.005218810442326527</v>
+        <v>0.004733137434684842</v>
       </c>
       <c r="J96" s="3" t="n">
-        <v>0.006897335925965864</v>
+        <v>0.006405592443359254</v>
       </c>
       <c r="K96" s="3" t="n">
-        <v>0.001639803638132653</v>
-      </c>
-      <c r="L96" s="5" t="n">
-        <v>-0.0002447680822420528</v>
+        <v>0.0001725705281572232</v>
+      </c>
+      <c r="L96" s="24" t="n">
+        <v>0</v>
       </c>
       <c r="M96" s="6" t="inlineStr">
         <is>
@@ -5782,106 +5785,106 @@
       </c>
       <c r="N96" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d down.</t>
+          <t>Positive across long, 6m, 3m, and 1m horizons; 1d flat.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="21" customHeight="1">
-      <c r="A97" s="15" t="n">
+      <c r="A97" t="n">
         <v>96</v>
       </c>
-      <c r="B97" s="16" t="inlineStr">
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>IWP</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" s="19" t="inlineStr">
+        <is>
+          <t>Broad Equity &amp; Factors</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Russell Midcap Growth</t>
+        </is>
+      </c>
+      <c r="F97" s="3" t="n">
+        <v>0.1663523496795087</v>
+      </c>
+      <c r="G97" s="5" t="n">
+        <v>-0.01825308464131625</v>
+      </c>
+      <c r="H97" s="3" t="n">
+        <v>0.01295364720427772</v>
+      </c>
+      <c r="I97" s="3" t="n">
+        <v>0.03452199154126578</v>
+      </c>
+      <c r="J97" s="3" t="n">
+        <v>0.004965074427294436</v>
+      </c>
+      <c r="K97" s="5" t="n">
+        <v>-0.03080766028309745</v>
+      </c>
+      <c r="L97" s="5" t="n">
+        <v>-7.158708568966166e-05</v>
+      </c>
+      <c r="M97" s="6" t="inlineStr">
+        <is>
+          <t>CORRECTION</t>
+        </is>
+      </c>
+      <c r="N97" s="7" t="inlineStr">
+        <is>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="21" customHeight="1">
+      <c r="A98" s="15" t="n">
+        <v>97</v>
+      </c>
+      <c r="B98" s="16" t="inlineStr">
         <is>
           <t>TIP</t>
         </is>
       </c>
-      <c r="C97" s="15" t="inlineStr">
+      <c r="C98" s="15" t="inlineStr">
         <is>
           <t>HB</t>
         </is>
       </c>
-      <c r="D97" s="17" t="inlineStr">
+      <c r="D98" s="17" t="inlineStr">
         <is>
           <t>Inflation &amp; Real Assets</t>
         </is>
       </c>
-      <c r="E97" s="15" t="inlineStr">
+      <c r="E98" s="15" t="inlineStr">
         <is>
           <t>TIPS</t>
         </is>
       </c>
-      <c r="F97" s="3" t="n">
-        <v>0.04386074324933342</v>
-      </c>
-      <c r="G97" s="3" t="n">
-        <v>0.007972464616699426</v>
-      </c>
-      <c r="H97" s="3" t="n">
-        <v>0.007030170081206544</v>
-      </c>
-      <c r="I97" s="5" t="n">
-        <v>-0.007196306180585532</v>
-      </c>
-      <c r="J97" s="5" t="n">
-        <v>-0.004055951357985865</v>
-      </c>
-      <c r="K97" s="3" t="n">
-        <v>0.0009357162908205652</v>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v>-0.0002803738317757043</v>
-      </c>
-      <c r="M97" s="6" t="inlineStr">
-        <is>
-          <t>MIXED_TRANSITION</t>
-        </is>
-      </c>
-      <c r="N97" s="7" t="inlineStr">
-        <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="21" customHeight="1">
-      <c r="A98" t="n">
-        <v>97</v>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>LQD</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" s="20" t="inlineStr">
-        <is>
-          <t>Financials &amp; Credit</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>Investment Grade Corporate Bonds</t>
-        </is>
-      </c>
       <c r="F98" s="3" t="n">
-        <v>0.03808626809670113</v>
-      </c>
-      <c r="G98" s="5" t="n">
-        <v>-0.000186058233740849</v>
+        <v>0.04521552763612569</v>
+      </c>
+      <c r="G98" s="3" t="n">
+        <v>0.004385577740041224</v>
       </c>
       <c r="H98" s="3" t="n">
-        <v>0.003940725451453408</v>
+        <v>0.004573208148735297</v>
       </c>
       <c r="I98" s="5" t="n">
-        <v>-0.01940803078946995</v>
+        <v>-0.007963443410951565</v>
       </c>
       <c r="J98" s="5" t="n">
-        <v>-0.01307885661499408</v>
+        <v>-0.002121971796825051</v>
       </c>
       <c r="K98" s="5" t="n">
-        <v>-0.004110584998271327</v>
-      </c>
-      <c r="L98" s="5" t="n">
-        <v>-0.0001895734597155974</v>
+        <v>-0.0001867762420619812</v>
+      </c>
+      <c r="L98" s="3" t="n">
+        <v>0.0008413573899224147</v>
       </c>
       <c r="M98" s="6" t="inlineStr">
         <is>
@@ -5890,7 +5893,7 @@
       </c>
       <c r="N98" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5900,40 +5903,40 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>IEF</t>
+          <t>LQD</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
-      <c r="D99" s="23" t="inlineStr">
-        <is>
-          <t>Rates &amp; Duration</t>
+      <c r="D99" s="20" t="inlineStr">
+        <is>
+          <t>Financials &amp; Credit</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>7-10 Year Treasury</t>
+          <t>Investment Grade Corporate Bonds</t>
         </is>
       </c>
       <c r="F99" s="3" t="n">
-        <v>0.03410040564887895</v>
+        <v>0.04163561191608722</v>
       </c>
       <c r="G99" s="5" t="n">
-        <v>-0.004237581373844668</v>
+        <v>-0.006379026396524878</v>
       </c>
       <c r="H99" s="5" t="n">
-        <v>-0.0002734868428240222</v>
+        <v>-0.0007796722571444814</v>
       </c>
       <c r="I99" s="5" t="n">
-        <v>-0.02395131704843334</v>
+        <v>-0.02497072622797991</v>
       </c>
       <c r="J99" s="5" t="n">
-        <v>-0.004424624954043832</v>
+        <v>-0.01179322085694856</v>
       </c>
       <c r="K99" s="5" t="n">
-        <v>-0.003965178955294357</v>
-      </c>
-      <c r="L99" s="5" t="n">
-        <v>-0.0003250975292587999</v>
+        <v>-0.005603723206901612</v>
+      </c>
+      <c r="L99" s="3" t="n">
+        <v>0.000284414106939801</v>
       </c>
       <c r="M99" s="6" t="inlineStr">
         <is>
@@ -5942,7 +5945,7 @@
       </c>
       <c r="N99" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -5952,49 +5955,49 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>FXE</t>
+          <t>IEF</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
-      <c r="D100" s="21" t="inlineStr">
-        <is>
-          <t>Currency</t>
+      <c r="D100" s="23" t="inlineStr">
+        <is>
+          <t>Rates &amp; Duration</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Euro Currency</t>
+          <t>7-10 Year Treasury</t>
         </is>
       </c>
       <c r="F100" s="3" t="n">
-        <v>0.089070562680853</v>
-      </c>
-      <c r="G100" s="3" t="n">
-        <v>0.004564932100218577</v>
+        <v>0.0344230792083402</v>
+      </c>
+      <c r="G100" s="5" t="n">
+        <v>-0.00928819930574154</v>
       </c>
       <c r="H100" s="5" t="n">
-        <v>-0.004175371193174904</v>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>0.00478065136126693</v>
-      </c>
-      <c r="J100" s="3" t="n">
-        <v>0.01032956152742326</v>
-      </c>
-      <c r="K100" s="3" t="n">
-        <v>0.008776950318919008</v>
+        <v>-0.002773776456259647</v>
+      </c>
+      <c r="I100" s="5" t="n">
+        <v>-0.02718888787046725</v>
+      </c>
+      <c r="J100" s="5" t="n">
+        <v>-0.003576105840603083</v>
+      </c>
+      <c r="K100" s="5" t="n">
+        <v>-0.006532542662518681</v>
       </c>
       <c r="L100" s="5" t="n">
-        <v>-0.001211782252050653</v>
+        <v>-0.0002168021680216681</v>
       </c>
       <c r="M100" s="6" t="inlineStr">
         <is>
-          <t>RECOVERY</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N100" s="7" t="inlineStr">
         <is>
-          <t>Weak long trend; 3m and 1m now positive; 1d down.</t>
+          <t>Long and 1m momentum negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -6004,49 +6007,49 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>IWP</t>
+          <t>FXE</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
-      <c r="D101" s="19" t="inlineStr">
-        <is>
-          <t>Broad Equity &amp; Factors</t>
+      <c r="D101" s="21" t="inlineStr">
+        <is>
+          <t>Currency</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Russell Midcap Growth</t>
+          <t>Euro Currency</t>
         </is>
       </c>
       <c r="F101" s="3" t="n">
-        <v>0.1238706429350735</v>
+        <v>0.090415137008097</v>
       </c>
       <c r="G101" s="5" t="n">
-        <v>-0.01818290450622762</v>
+        <v>-0.0006342122917789572</v>
       </c>
       <c r="H101" s="5" t="n">
-        <v>-0.01136521832519133</v>
+        <v>-0.006714807330343131</v>
       </c>
       <c r="I101" s="3" t="n">
-        <v>0.04690526361528691</v>
+        <v>0.005342725473955978</v>
       </c>
       <c r="J101" s="3" t="n">
-        <v>0.004459535524643954</v>
-      </c>
-      <c r="K101" s="5" t="n">
-        <v>-0.006896061424712108</v>
-      </c>
-      <c r="L101" s="5" t="n">
-        <v>-0.0008583077033116338</v>
+        <v>0.01003700074043223</v>
+      </c>
+      <c r="K101" s="3" t="n">
+        <v>0.006121701081862829</v>
+      </c>
+      <c r="L101" s="3" t="n">
+        <v>0.0009332711152589823</v>
       </c>
       <c r="M101" s="6" t="inlineStr">
         <is>
-          <t>BROAD_WEAKNESS</t>
+          <t>RECOVERY</t>
         </is>
       </c>
       <c r="N101" s="7" t="inlineStr">
         <is>
-          <t>Long and 1m momentum negative; 1d down.</t>
+          <t>Weak long trend; 3m and 1m now positive; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6071,34 +6074,34 @@
         </is>
       </c>
       <c r="F102" s="5" t="n">
-        <v>-0.03069225632261574</v>
+        <v>-0.02581908527558152</v>
       </c>
       <c r="G102" s="5" t="n">
-        <v>-0.01436964022052767</v>
+        <v>-0.02751862407202665</v>
       </c>
       <c r="H102" s="5" t="n">
-        <v>-0.01442961553683053</v>
+        <v>-0.02640759758592726</v>
       </c>
       <c r="I102" s="5" t="n">
-        <v>-0.04890675336892869</v>
+        <v>-0.05550838198087849</v>
       </c>
       <c r="J102" s="5" t="n">
-        <v>-0.02229630903445345</v>
-      </c>
-      <c r="K102" s="3" t="n">
-        <v>6.08534075783318e-05</v>
+        <v>-0.01553886527065873</v>
+      </c>
+      <c r="K102" s="5" t="n">
+        <v>-0.001141161828445481</v>
       </c>
       <c r="L102" s="3" t="n">
-        <v>0.001705860850493401</v>
+        <v>0.001702955844787857</v>
       </c>
       <c r="M102" s="6" t="inlineStr">
         <is>
-          <t>REBOUND</t>
+          <t>BROAD_WEAKNESS</t>
         </is>
       </c>
       <c r="N102" s="7" t="inlineStr">
         <is>
-          <t>Weak long trend; 1m rebound not yet confirmed by 3m; 1d up.</t>
+          <t>Long and 1m momentum negative; 1d up.</t>
         </is>
       </c>
     </row>
@@ -6127,25 +6130,25 @@
         </is>
       </c>
       <c r="F103" s="3" t="n">
-        <v>0.02002861230329045</v>
+        <v>0.007355946056395668</v>
       </c>
       <c r="G103" s="5" t="n">
-        <v>-0.05096025860429754</v>
+        <v>-0.06059451219512191</v>
       </c>
       <c r="H103" s="5" t="n">
-        <v>-0.04696710401216975</v>
+        <v>-0.04020579268292679</v>
       </c>
       <c r="I103" s="5" t="n">
-        <v>-0.001600320064012895</v>
+        <v>-0.01360544217687076</v>
       </c>
       <c r="J103" s="3" t="n">
-        <v>0.05428812843261488</v>
+        <v>0.04427028171997449</v>
       </c>
       <c r="K103" s="5" t="n">
-        <v>-0.00418994413407825</v>
+        <v>-0.02124280325590633</v>
       </c>
       <c r="L103" s="5" t="n">
-        <v>-0.0002003205128205954</v>
+        <v>-0.01222199959927872</v>
       </c>
       <c r="M103" s="6" t="inlineStr">
         <is>
@@ -6183,25 +6186,25 @@
         </is>
       </c>
       <c r="F104" s="5" t="n">
-        <v>-0.07926140795289716</v>
+        <v>-0.06969924899702173</v>
       </c>
       <c r="G104" s="5" t="n">
-        <v>-0.1302675899374276</v>
+        <v>-0.1419358489718351</v>
       </c>
       <c r="H104" s="5" t="n">
-        <v>-0.1319593472026728</v>
+        <v>-0.1427845771133071</v>
       </c>
       <c r="I104" s="3" t="n">
-        <v>0.1264241893076248</v>
+        <v>0.107581069237511</v>
       </c>
       <c r="J104" s="3" t="n">
-        <v>0.1908732916377112</v>
+        <v>0.172581767571329</v>
       </c>
       <c r="K104" s="3" t="n">
-        <v>0.001948937828883057</v>
+        <v>0.000990099009900991</v>
       </c>
       <c r="L104" s="5" t="n">
-        <v>-0.01058506543495008</v>
+        <v>-0.01672826298385532</v>
       </c>
       <c r="M104" s="6" t="inlineStr">
         <is>

--- a/NEFTy_LATEST.xlsx
+++ b/NEFTy_LATEST.xlsx
@@ -694,25 +694,25 @@
         </is>
       </c>
       <c r="F2" s="3" t="n">
-        <v>1.952042885808761</v>
+        <v>1.956997969832948</v>
       </c>
       <c r="G2" s="3" t="n">
-        <v>1.315979714215984</v>
+        <v>1.319867100510907</v>
       </c>
       <c r="H2" s="4" t="n">
-        <v>1.357144270162411</v>
+        <v>1.357144449408483</v>
       </c>
       <c r="I2" s="3" t="n">
-        <v>0.565685053982852</v>
+        <v>0.5683127855345096</v>
       </c>
       <c r="J2" s="5" t="n">
-        <v>-0.09967921835131344</v>
+        <v>-0.09816809292162265</v>
       </c>
       <c r="K2" s="5" t="n">
-        <v>-0.01746374053871202</v>
+        <v>-0.0158146221827562</v>
       </c>
       <c r="L2" s="3" t="n">
-        <v>0.01979372394118939</v>
+        <v>0.021505376344086</v>
       </c>
       <c r="M2" s="6" t="inlineStr">
         <is>
@@ -750,25 +750,25 @@
         </is>
       </c>
       <c r="F3" s="3" t="n">
-        <v>1.709651103911419</v>
+        <v>1.738607902370191</v>
       </c>
       <c r="G3" s="3" t="n">
-        <v>1.169449572957524</v>
+        <v>1.192633812743625</v>
       </c>
       <c r="H3" s="8" t="n">
         <v>1.325003289900756</v>
       </c>
       <c r="I3" s="3" t="n">
-        <v>0.4896410011462258</v>
+        <v>0.5055603359840943</v>
       </c>
       <c r="J3" s="5" t="n">
-        <v>-0.09184689519707478</v>
+        <v>-0.08214174251378847</v>
       </c>
       <c r="K3" s="5" t="n">
-        <v>-0.06690472982077877</v>
+        <v>-0.05693302789381482</v>
       </c>
       <c r="L3" s="3" t="n">
-        <v>0.01830882352941177</v>
+        <v>0.02919117647058833</v>
       </c>
       <c r="M3" s="6" t="inlineStr">
         <is>
@@ -802,25 +802,25 @@
         </is>
       </c>
       <c r="F4" s="3" t="n">
-        <v>2.555720469202406</v>
+        <v>2.534318404198832</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>1.653147978372339</v>
+        <v>1.637178543769972</v>
       </c>
       <c r="H4" s="10" t="n">
         <v>1.306402950527906</v>
       </c>
       <c r="I4" s="3" t="n">
-        <v>0.4269923071177835</v>
+        <v>0.4184031667786992</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>0.02919629390217637</v>
+        <v>0.02300150829562608</v>
       </c>
       <c r="K4" s="3" t="n">
-        <v>0.150340177012463</v>
+        <v>0.1434162201216207</v>
       </c>
       <c r="L4" s="3" t="n">
-        <v>0.01159527717477626</v>
+        <v>0.005506432996240651</v>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
@@ -858,25 +858,25 @@
         </is>
       </c>
       <c r="F5" s="3" t="n">
-        <v>2.101687581133709</v>
+        <v>2.117265253137171</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>1.334093129273852</v>
+        <v>1.345815695213286</v>
       </c>
       <c r="H5" s="11" t="n">
         <v>1.244545750569847</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>0.6335460346399271</v>
+        <v>0.6417502278942571</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>-0.03174388761312974</v>
+        <v>-0.02688099419154388</v>
       </c>
       <c r="K5" s="3" t="n">
-        <v>0.03989554620629621</v>
+        <v>0.04511823589148412</v>
       </c>
       <c r="L5" s="3" t="n">
-        <v>0.01919522252239458</v>
+        <v>0.02431394852836632</v>
       </c>
       <c r="M5" s="6" t="inlineStr">
         <is>
@@ -910,25 +910,25 @@
         </is>
       </c>
       <c r="F6" s="3" t="n">
-        <v>1.681861775351244</v>
+        <v>1.689904810028867</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>1.142393627444674</v>
+        <v>1.148818804328168</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>1.209290053494302</v>
+        <v>1.209289916403035</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>0.5679009792056828</v>
+        <v>0.5726033131093784</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>-0.07766178103186316</v>
+        <v>-0.07489557172703498</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>-0.03027960314392464</v>
+        <v>-0.02737128867782135</v>
       </c>
       <c r="L6" s="3" t="n">
-        <v>0.01338821990535921</v>
+        <v>0.01642749971146062</v>
       </c>
       <c r="M6" s="6" t="inlineStr">
         <is>
@@ -966,25 +966,25 @@
         </is>
       </c>
       <c r="F7" s="3" t="n">
-        <v>1.664434776876004</v>
+        <v>1.665858557132834</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>1.069829698947712</v>
+        <v>1.070935968161473</v>
       </c>
       <c r="H7" s="3" t="n">
         <v>1.1505873515523</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.5237208250758487</v>
+        <v>0.5245352135446224</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.07869388083700368</v>
+        <v>-0.07820146709079145</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>-0.0375514403292182</v>
+        <v>-0.03703703703703709</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.01244588744588726</v>
+        <v>0.01298701298701288</v>
       </c>
       <c r="M7" s="6" t="inlineStr">
         <is>
@@ -1022,25 +1022,25 @@
         </is>
       </c>
       <c r="F8" s="3" t="n">
-        <v>1.616177871358606</v>
+        <v>1.618596877415515</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>0.9605276489109318</v>
+        <v>0.9623404187188918</v>
       </c>
       <c r="H8" s="3" t="n">
         <v>0.9930206926385206</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>0.453457413089231</v>
+        <v>0.4548013287014732</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>-0.04172796576166904</v>
+        <v>-0.04084191520663361</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>-0.01630341513643385</v>
+        <v>-0.01539385618671707</v>
       </c>
       <c r="L8" s="3" t="n">
-        <v>0.01091691504559011</v>
+        <v>0.01185164282816897</v>
       </c>
       <c r="M8" s="6" t="inlineStr">
         <is>
@@ -1078,25 +1078,25 @@
         </is>
       </c>
       <c r="F9" s="3" t="n">
-        <v>1.293083288319668</v>
+        <v>1.296996048308719</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.9343248615330488</v>
+        <v>0.9376254607579371</v>
       </c>
       <c r="H9" s="3" t="n">
         <v>0.79083565312476</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.5736291690220461</v>
+        <v>0.5763143018654606</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.1087324504630089</v>
+        <v>0.1106243154435926</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.08012416335241035</v>
+        <v>0.08196721311475419</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>-0.007398823319664904</v>
+        <v>-0.005705116776609009</v>
       </c>
       <c r="M9" s="6" t="inlineStr">
         <is>
@@ -1134,25 +1134,25 @@
         </is>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.447634702590118</v>
+        <v>1.429103714305524</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.9126637880051682</v>
+        <v>0.898183052701659</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>0.7704710121776548</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>0.160301245480573</v>
+        <v>0.1515166303728337</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.173861137092141</v>
+        <v>0.1649738603444404</v>
       </c>
       <c r="K10" s="3" t="n">
-        <v>0.08031352947858683</v>
+        <v>0.07213449960240825</v>
       </c>
       <c r="L10" s="3" t="n">
-        <v>0.04897418927862351</v>
+        <v>0.04103242885506275</v>
       </c>
       <c r="M10" s="6" t="inlineStr">
         <is>
@@ -1190,25 +1190,25 @@
         </is>
       </c>
       <c r="F11" s="3" t="n">
-        <v>1.533846153846154</v>
+        <v>1.507692307692308</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>1.048507462686567</v>
+        <v>1.027363184079602</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>0.7114427860696519</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.6052631578947367</v>
+        <v>0.5886939571150098</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>0.3314470493128536</v>
+        <v>0.3177041228779307</v>
       </c>
       <c r="K11" s="3" t="n">
-        <v>0.1969476744186045</v>
+        <v>0.1845930232558139</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>-0.005434782608695676</v>
+        <v>-0.01570048309178729</v>
       </c>
       <c r="M11" s="6" t="inlineStr">
         <is>
@@ -1242,25 +1242,25 @@
         </is>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0.8741845451039705</v>
+        <v>0.8687606533860586</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0.7088435173225585</v>
+        <v>0.7038979726603565</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>0.6559156670015456</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0.2787871232427279</v>
+        <v>0.2750861999180723</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0.265743326130216</v>
+        <v>0.2620801527109968</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0.03196289000444819</v>
+        <v>0.02897629789667655</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>-0.00860753311763629</v>
+        <v>-0.01147671082351498</v>
       </c>
       <c r="M12" s="6" t="inlineStr">
         <is>
@@ -1298,25 +1298,25 @@
         </is>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1.35107655534142</v>
+        <v>1.339791611713226</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>0.6936300668403621</v>
+        <v>0.6855006425195282</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>0.639253250827674</v>
       </c>
       <c r="I13" s="3" t="n">
-        <v>0.1349013448262313</v>
+        <v>0.1294538183710654</v>
       </c>
       <c r="J13" s="3" t="n">
-        <v>0.2189519699363107</v>
+        <v>0.2131010004806164</v>
       </c>
       <c r="K13" s="3" t="n">
-        <v>0.0331716993608111</v>
+        <v>0.02821247520387926</v>
       </c>
       <c r="L13" s="3" t="n">
-        <v>0.01714223717044594</v>
+        <v>0.01225995443202765</v>
       </c>
       <c r="M13" s="6" t="inlineStr">
         <is>
@@ -1354,25 +1354,25 @@
         </is>
       </c>
       <c r="F14" s="3" t="n">
-        <v>0.8835227611629839</v>
+        <v>0.8657483552382881</v>
       </c>
       <c r="G14" s="3" t="n">
-        <v>0.6356700577665451</v>
+        <v>0.6202345853819895</v>
       </c>
       <c r="H14" s="3" t="n">
         <v>0.5592277183382703</v>
       </c>
       <c r="I14" s="3" t="n">
-        <v>0.1605009688538652</v>
+        <v>0.1495495666612656</v>
       </c>
       <c r="J14" s="3" t="n">
-        <v>0.08529194560440168</v>
+        <v>0.07505027505720596</v>
       </c>
       <c r="K14" s="3" t="n">
-        <v>0.04902576995600261</v>
+        <v>0.03912633563796342</v>
       </c>
       <c r="L14" s="3" t="n">
-        <v>0.02612972640639422</v>
+        <v>0.01644635720873033</v>
       </c>
       <c r="M14" s="6" t="inlineStr">
         <is>
@@ -1410,34 +1410,34 @@
         </is>
       </c>
       <c r="F15" s="3" t="n">
-        <v>0.7861061338609379</v>
+        <v>0.7607975198140964</v>
       </c>
       <c r="G15" s="3" t="n">
-        <v>0.7335303663290476</v>
+        <v>0.7089667358996157</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>0.5483062375226981</v>
       </c>
       <c r="I15" s="3" t="n">
-        <v>0.146681789407048</v>
-      </c>
-      <c r="J15" s="3" t="n">
-        <v>0.01144691840580725</v>
+        <v>0.1304336357881408</v>
+      </c>
+      <c r="J15" s="5" t="n">
+        <v>-0.002884995695772608</v>
       </c>
       <c r="K15" s="3" t="n">
-        <v>0.1196301637993202</v>
+        <v>0.1037653239929948</v>
       </c>
       <c r="L15" s="3" t="n">
-        <v>0.01684092344396904</v>
+        <v>0.002432577830795646</v>
       </c>
       <c r="M15" s="6" t="inlineStr">
         <is>
-          <t>REACCELERATING</t>
+          <t>MIXED_TRANSITION</t>
         </is>
       </c>
       <c r="N15" s="7" t="inlineStr">
         <is>
-          <t>Positive trend cooled, then strengthened into 1m; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
         </is>
       </c>
     </row>
@@ -1462,25 +1462,25 @@
         </is>
       </c>
       <c r="F16" s="3" t="n">
-        <v>1.015830245874032</v>
+        <v>0.9996631862579992</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.6084385917764041</v>
+        <v>0.595538833646869</v>
       </c>
       <c r="H16" s="3" t="n">
         <v>0.5452835259338886</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>-0.2352415026833632</v>
+        <v>-0.2413749041656019</v>
       </c>
       <c r="J16" s="5" t="n">
-        <v>-0.02809353686261773</v>
+        <v>-0.03588827541409545</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>0.04086956521739138</v>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v>0.0005015045135405849</v>
+        <v>0.03252173913043466</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>-0.007522567703109329</v>
       </c>
       <c r="M16" s="6" t="inlineStr">
         <is>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1518,25 +1518,25 @@
         </is>
       </c>
       <c r="F17" s="3" t="n">
-        <v>1.110984938070323</v>
+        <v>1.099363646790685</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>0.7183924464337479</v>
+        <v>0.708932165564667</v>
       </c>
       <c r="H17" s="3" t="n">
         <v>0.4997923849232022</v>
       </c>
       <c r="I17" s="3" t="n">
-        <v>0.2796862630837045</v>
+        <v>0.2726411951784069</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.2725039214382665</v>
+        <v>0.2654983945408478</v>
       </c>
       <c r="K17" s="3" t="n">
-        <v>0.1457535480964181</v>
-      </c>
-      <c r="L17" s="3" t="n">
-        <v>0.0001966568338249708</v>
+        <v>0.1394458211308853</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>-0.005309734513274433</v>
       </c>
       <c r="M17" s="6" t="inlineStr">
         <is>
@@ -1545,7 +1545,7 @@
       </c>
       <c r="N17" s="7" t="inlineStr">
         <is>
-          <t>Positive trend strengthening through 1m; 1d up.</t>
+          <t>Positive trend strengthening through 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1574,25 +1574,25 @@
         </is>
       </c>
       <c r="F18" s="3" t="n">
-        <v>0.7107524175238917</v>
+        <v>0.7131167022173908</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>0.4505516375104908</v>
+        <v>0.4525563209460166</v>
       </c>
       <c r="H18" s="3" t="n">
         <v>0.4759598345421556</v>
       </c>
       <c r="I18" s="3" t="n">
-        <v>0.3785766942517619</v>
+        <v>0.380481907270108</v>
       </c>
       <c r="J18" s="5" t="n">
-        <v>-0.006220205082071995</v>
+        <v>-0.004846786968635275</v>
       </c>
       <c r="K18" s="5" t="n">
-        <v>-0.01721469408383081</v>
+        <v>-0.01585647051391381</v>
       </c>
       <c r="L18" s="5" t="n">
-        <v>-0.003554843875100078</v>
+        <v>-0.002177742193754995</v>
       </c>
       <c r="M18" s="6" t="inlineStr">
         <is>
@@ -1630,34 +1630,34 @@
         </is>
       </c>
       <c r="F19" s="3" t="n">
-        <v>0.8258365928135685</v>
+        <v>0.8201632286370337</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>0.4742889263445975</v>
+        <v>0.469707915090082</v>
       </c>
       <c r="H19" s="3" t="n">
         <v>0.4740897519422276</v>
       </c>
       <c r="I19" s="3" t="n">
-        <v>0.04071382070756369</v>
+        <v>0.0374800436370053</v>
       </c>
       <c r="J19" s="5" t="n">
-        <v>-0.03569613085545897</v>
-      </c>
-      <c r="K19" s="3" t="n">
-        <v>0.0001351168760976851</v>
+        <v>-0.03869248170527295</v>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>-0.00297257127415218</v>
       </c>
       <c r="L19" s="5" t="n">
-        <v>-0.002156915610676879</v>
+        <v>-0.005257481801024588</v>
       </c>
       <c r="M19" s="6" t="inlineStr">
         <is>
-          <t>MIXED_TRANSITION</t>
+          <t>FAST_REVERSAL</t>
         </is>
       </c>
       <c r="N19" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1682,25 +1682,25 @@
         </is>
       </c>
       <c r="F20" s="3" t="n">
-        <v>1.793787975716156</v>
+        <v>1.763210318385796</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.6393069185609002</v>
+        <v>0.6213649109172474</v>
       </c>
       <c r="H20" s="3" t="n">
         <v>0.4567593362048366</v>
       </c>
       <c r="I20" s="5" t="n">
-        <v>-0.02657541935153074</v>
+        <v>-0.03722942871900581</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.2531709328317007</v>
+        <v>0.2394551348922835</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>0.1253107344632769</v>
-      </c>
-      <c r="L20" s="3" t="n">
-        <v>0.003021452311410933</v>
+        <v>0.1129943502824859</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>-0.0079564910867157</v>
       </c>
       <c r="M20" s="6" t="inlineStr">
         <is>
@@ -1709,7 +1709,7 @@
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>Positive long and 1m momentum with mixed middle horizons; 1d up.</t>
+          <t>Positive long and 1m momentum with mixed middle horizons; 1d down.</t>
         </is>
       </c>
     </row>
@@ -1734,25 +1734,25 @@
         </is>
       </c>
       <c r="F21" s="3" t="n">
-        <v>0.7553368735079555</v>
+        <v>0.7593637346667712</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>0.4336428714579958</v>
+        <v>0.4369317448827021</v>
       </c>
       <c r="H21" s="3" t="n">
         <v>0.4376965991675175</v>
       </c>
       <c r="I21" s="3" t="n">
-        <v>0.3444249634820267</v>
+        <v>0.3475091650094342</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>0.0189135285662887</v>
+        <v>0.02125098491116462</v>
       </c>
       <c r="K21" s="5" t="n">
-        <v>-0.002819598872160434</v>
+        <v>-0.0005319997872000881</v>
       </c>
       <c r="L21" s="3" t="n">
-        <v>0.0008543357539512186</v>
+        <v>0.003150363092695452</v>
       </c>
       <c r="M21" s="6" t="inlineStr">
         <is>
@@ -1790,25 +1790,25 @@
         </is>
       </c>
       <c r="F22" s="3" t="n">
-        <v>0.6503903872797008</v>
+        <v>0.6456105680006889</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>0.3987689576249738</v>
+        <v>0.3947177782940139</v>
       </c>
       <c r="H22" s="3" t="n">
         <v>0.4249030360541073</v>
       </c>
       <c r="I22" s="3" t="n">
-        <v>0.124807274619029</v>
+        <v>0.1215495557817543</v>
       </c>
       <c r="J22" s="3" t="n">
-        <v>0.04331481038720186</v>
+        <v>0.04029311379286127</v>
       </c>
       <c r="K22" s="5" t="n">
-        <v>-0.01834095216858067</v>
+        <v>-0.02118407849258552</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>-0.02155914874701337</v>
+        <v>-0.02439295438128575</v>
       </c>
       <c r="M22" s="6" t="inlineStr">
         <is>
@@ -1846,25 +1846,25 @@
         </is>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.7217059397088346</v>
+        <v>0.7211103585756851</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.3957325745253024</v>
+        <v>0.3952498585209028</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>0.3994019973724008</v>
+        <v>0.3994021004695771</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.3276364954581834</v>
+        <v>0.3271772327988995</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.03316624104019561</v>
+        <v>0.03280884300468978</v>
       </c>
       <c r="K23" s="5" t="n">
-        <v>-0.00262213635109021</v>
+        <v>-0.002967154292022989</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>-0.000794994988075115</v>
+        <v>-0.001140644982890238</v>
       </c>
       <c r="M23" s="6" t="inlineStr">
         <is>
@@ -1898,25 +1898,25 @@
         </is>
       </c>
       <c r="F24" s="3" t="n">
-        <v>0.7146585364893061</v>
+        <v>0.7138090648338742</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>0.3925996530460425</v>
+        <v>0.3919097349617986</v>
       </c>
       <c r="H24" s="3" t="n">
         <v>0.3965091888567571</v>
       </c>
       <c r="I24" s="3" t="n">
-        <v>0.3268498473677466</v>
+        <v>0.3261923920344274</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>0.034150661371525</v>
+        <v>0.03363832515088028</v>
       </c>
       <c r="K24" s="5" t="n">
-        <v>-0.002799505969534821</v>
+        <v>-0.003293536434746835</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>-0.001319370000824605</v>
+        <v>-0.001814133751133817</v>
       </c>
       <c r="M24" s="6" t="inlineStr">
         <is>
@@ -1954,25 +1954,25 @@
         </is>
       </c>
       <c r="F25" s="3" t="n">
-        <v>0.7179145617386125</v>
+        <v>0.7200893028786142</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>0.3841501350712611</v>
+        <v>0.3859025011229418</v>
       </c>
       <c r="H25" s="3" t="n">
         <v>0.3912143607170988</v>
       </c>
       <c r="I25" s="3" t="n">
-        <v>0.3190487522854586</v>
+        <v>0.3207186984823702</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>0.0314296416016191</v>
+        <v>0.03273545535898781</v>
       </c>
       <c r="K25" s="5" t="n">
-        <v>-0.005077740602243752</v>
+        <v>-0.00381814603424524</v>
       </c>
       <c r="L25" s="5" t="n">
-        <v>-0.002171252615372543</v>
+        <v>-0.0009079783664284191</v>
       </c>
       <c r="M25" s="6" t="inlineStr">
         <is>
@@ -2010,25 +2010,25 @@
         </is>
       </c>
       <c r="F26" s="3" t="n">
-        <v>0.5639587302757341</v>
+        <v>0.5563362249962938</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>0.3538717787997472</v>
+        <v>0.3472732064833493</v>
       </c>
       <c r="H26" s="3" t="n">
         <v>0.3888053969453829</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>0.138059343146631</v>
+        <v>0.1325126089627169</v>
       </c>
       <c r="J26" s="5" t="n">
-        <v>-0.1068284468198212</v>
+        <v>-0.1111816338622705</v>
       </c>
       <c r="K26" s="5" t="n">
-        <v>-0.0251537171604248</v>
-      </c>
-      <c r="L26" s="3" t="n">
-        <v>0.003452243958573131</v>
+        <v>-0.02990497484628285</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>-0.001438434982738657</v>
       </c>
       <c r="M26" s="6" t="inlineStr">
         <is>
@@ -2037,7 +2037,7 @@
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2066,25 +2066,25 @@
         </is>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.5404060209266297</v>
+        <v>0.5273668877047515</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.4647299724249707</v>
+        <v>0.4523312538635542</v>
       </c>
       <c r="H27" s="3" t="n">
         <v>0.3849438682359683</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.2218002372416121</v>
+        <v>0.2114578822922213</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.2528720490270324</v>
+        <v>0.2422666758717105</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>0.05760963026655186</v>
+        <v>0.0486571240706084</v>
       </c>
       <c r="L27" s="5" t="n">
-        <v>-0.01330690826727066</v>
+        <v>-0.02165911664779152</v>
       </c>
       <c r="M27" s="6" t="inlineStr">
         <is>
@@ -2122,25 +2122,25 @@
         </is>
       </c>
       <c r="F28" s="3" t="n">
-        <v>1.163097434055064</v>
+        <v>1.140435053744473</v>
       </c>
       <c r="G28" s="3" t="n">
-        <v>0.4495784249599848</v>
+        <v>0.4343914541655682</v>
       </c>
       <c r="H28" s="3" t="n">
         <v>0.384047243894313</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0.08324944753562336</v>
+        <v>0.07190043913461497</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0.02287656931465198</v>
+        <v>0.01216007663168206</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0.04734750302401936</v>
+        <v>0.03637463279764996</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0.02191873208565154</v>
+        <v>0.01121227448996787</v>
       </c>
       <c r="M28" s="6" t="inlineStr">
         <is>
@@ -2178,25 +2178,25 @@
         </is>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.7248821221996085</v>
+        <v>0.7259061060107204</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.3234095124788039</v>
+        <v>0.3241952063935356</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>0.3831121972522837</v>
+        <v>0.3831123354104518</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.08122603105180604</v>
+        <v>0.08186783518578999</v>
       </c>
       <c r="J29" s="5" t="n">
-        <v>-0.1786120591581343</v>
+        <v>-0.1781244921176662</v>
       </c>
       <c r="K29" s="5" t="n">
-        <v>-0.04316546762589935</v>
+        <v>-0.04259750094661108</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>0.02245599838154955</v>
+        <v>0.02306291725672671</v>
       </c>
       <c r="M29" s="6" t="inlineStr">
         <is>
@@ -2234,25 +2234,25 @@
         </is>
       </c>
       <c r="F30" s="3" t="n">
-        <v>0.6032533367665098</v>
+        <v>0.5960716080488211</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>0.5313848597421695</v>
+        <v>0.5245250684341964</v>
       </c>
       <c r="H30" s="3" t="n">
-        <v>0.3583030682636079</v>
+        <v>0.3583029815718857</v>
       </c>
       <c r="I30" s="3" t="n">
-        <v>0.1651344707891862</v>
+        <v>0.1599153608468333</v>
       </c>
       <c r="J30" s="3" t="n">
-        <v>0.1207781127924663</v>
+        <v>0.1157576929711519</v>
       </c>
       <c r="K30" s="3" t="n">
-        <v>0.1274250169366262</v>
+        <v>0.1223748229352712</v>
       </c>
       <c r="L30" s="3" t="n">
-        <v>0.01373352530734295</v>
+        <v>0.009192601617011853</v>
       </c>
       <c r="M30" s="6" t="inlineStr">
         <is>
@@ -2286,25 +2286,25 @@
         </is>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0.5851334475159131</v>
+        <v>0.5787959855801326</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0.5351717784895758</v>
+        <v>0.5290339242314288</v>
       </c>
       <c r="H31" s="3" t="n">
         <v>0.357410076320938</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0.1705776548356706</v>
+        <v>0.1658975042858122</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0.1229038776220586</v>
+        <v>0.1184143342085304</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0.1309565217391304</v>
+        <v>0.1264347826086956</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0.01514205432407123</v>
+        <v>0.01108335935060878</v>
       </c>
       <c r="M31" s="6" t="inlineStr">
         <is>
@@ -2338,25 +2338,25 @@
         </is>
       </c>
       <c r="F32" s="3" t="n">
-        <v>0.5348081839829713</v>
+        <v>0.53908341569323</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>0.5159975317676597</v>
+        <v>0.5202203661179874</v>
       </c>
       <c r="H32" s="3" t="n">
         <v>0.3564682340886116</v>
       </c>
       <c r="I32" s="3" t="n">
-        <v>0.1904937361827561</v>
+        <v>0.193809874723655</v>
       </c>
       <c r="J32" s="3" t="n">
-        <v>0.09636918900576874</v>
+        <v>0.09942314217848658</v>
       </c>
       <c r="K32" s="3" t="n">
-        <v>0.1176063645797303</v>
+        <v>0.1207194742303701</v>
       </c>
       <c r="L32" s="3" t="n">
-        <v>0.01285266457680256</v>
+        <v>0.01567398119122254</v>
       </c>
       <c r="M32" s="6" t="inlineStr">
         <is>
@@ -2390,25 +2390,25 @@
         </is>
       </c>
       <c r="F33" s="3" t="n">
-        <v>0.582999820099811</v>
+        <v>0.5811206311982222</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.1916582797458248</v>
+        <v>0.1902436548132436</v>
       </c>
       <c r="H33" s="3" t="n">
         <v>0.3443289551620783</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>-0.03125567447245658</v>
+        <v>-0.03240567686784135</v>
       </c>
       <c r="J33" s="5" t="n">
-        <v>-0.1453878570313718</v>
+        <v>-0.1464023724051817</v>
       </c>
       <c r="K33" s="5" t="n">
-        <v>-0.1135664562085155</v>
+        <v>-0.114618746964546</v>
       </c>
       <c r="L33" s="3" t="n">
-        <v>0.007266372332597637</v>
+        <v>0.006070640176600417</v>
       </c>
       <c r="M33" s="6" t="inlineStr">
         <is>
@@ -2446,25 +2446,25 @@
         </is>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0.5864008316842255</v>
+        <v>0.5845239525206603</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0.174478872315555</v>
+        <v>0.1730892572791771</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0.3285316675721524</v>
+        <v>0.3285315736778391</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>-0.1006766758070096</v>
+        <v>-0.1017406699595429</v>
       </c>
       <c r="J34" s="5" t="n">
-        <v>-0.06449300945872405</v>
+        <v>-0.065599812697129</v>
       </c>
       <c r="K34" s="5" t="n">
-        <v>-0.1159571871840462</v>
+        <v>-0.1170031028832409</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0.002569982603194632</v>
+        <v>0.00138383678633569</v>
       </c>
       <c r="M34" s="6" t="inlineStr">
         <is>
@@ -2502,25 +2502,25 @@
         </is>
       </c>
       <c r="F35" s="3" t="n">
-        <v>0.4435215510053252</v>
+        <v>0.4346954272220385</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>0.2580322709248917</v>
+        <v>0.2503402842421716</v>
       </c>
       <c r="H35" s="3" t="n">
         <v>0.3255333785487629</v>
       </c>
       <c r="I35" s="3" t="n">
-        <v>0.1058368980267697</v>
+        <v>0.09907547950876228</v>
       </c>
       <c r="J35" s="5" t="n">
-        <v>-0.04968575833036881</v>
+        <v>-0.05549626467449298</v>
       </c>
       <c r="K35" s="5" t="n">
-        <v>-0.05092373282804352</v>
+        <v>-0.05672666982472752</v>
       </c>
       <c r="L35" s="5" t="n">
-        <v>-0.005336974059823696</v>
+        <v>-0.0114186421745065</v>
       </c>
       <c r="M35" s="6" t="inlineStr">
         <is>
@@ -2558,25 +2558,25 @@
         </is>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.7871983426149323</v>
+        <v>0.795157525517266</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.2741006993596988</v>
+        <v>0.2797748320289122</v>
       </c>
       <c r="H36" s="3" t="n">
         <v>0.318977930470749</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.01504068381688173</v>
+        <v>0.01956110791485166</v>
       </c>
       <c r="J36" s="5" t="n">
-        <v>-0.06212029161603894</v>
+        <v>-0.05794349939246668</v>
       </c>
       <c r="K36" s="5" t="n">
-        <v>-0.03402424716464603</v>
+        <v>-0.02972233085647236</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.01022494887525571</v>
+        <v>0.01472392638036801</v>
       </c>
       <c r="M36" s="6" t="inlineStr">
         <is>
@@ -2614,25 +2614,25 @@
         </is>
       </c>
       <c r="F37" s="3" t="n">
-        <v>0.6755536939403202</v>
+        <v>0.6655043853857825</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.5397456331333756</v>
+        <v>0.5305110400876896</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.3133774520883419</v>
+        <v>0.3133775311773068</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.2163145243634894</v>
+        <v>0.2090196299944855</v>
       </c>
       <c r="J37" s="3" t="n">
-        <v>0.164179259218582</v>
+        <v>0.1571970481601148</v>
       </c>
       <c r="K37" s="3" t="n">
-        <v>0.1723557692307693</v>
+        <v>0.1653245192307691</v>
       </c>
       <c r="L37" s="3" t="n">
-        <v>0.02291437260762419</v>
+        <v>0.01677940328247063</v>
       </c>
       <c r="M37" s="6" t="inlineStr">
         <is>
@@ -2670,25 +2670,25 @@
         </is>
       </c>
       <c r="F38" s="3" t="n">
-        <v>0.5247578785694103</v>
+        <v>0.5134290989003973</v>
       </c>
       <c r="G38" s="3" t="n">
-        <v>0.3085998181067384</v>
+        <v>0.2988773358211407</v>
       </c>
       <c r="H38" s="3" t="n">
         <v>0.2984842418520643</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.2495997064462407</v>
+        <v>0.2403156808967029</v>
       </c>
       <c r="J38" s="3" t="n">
-        <v>0.1341419925767213</v>
+        <v>0.1257156766934342</v>
       </c>
       <c r="K38" s="3" t="n">
-        <v>0.007790295737625685</v>
+        <v>0.0003027329530898015</v>
       </c>
       <c r="L38" s="5" t="n">
-        <v>-0.01567125195890651</v>
+        <v>-0.02298450287306286</v>
       </c>
       <c r="M38" s="6" t="inlineStr">
         <is>
@@ -2722,25 +2722,25 @@
         </is>
       </c>
       <c r="F39" s="3" t="n">
-        <v>0.6094133100748802</v>
+        <v>0.6086649446457237</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.2969297100938024</v>
+        <v>0.2963266472553105</v>
       </c>
       <c r="H39" s="3" t="n">
         <v>0.2896068041978299</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.2673727535476751</v>
+        <v>0.2667834344780036</v>
       </c>
       <c r="J39" s="3" t="n">
-        <v>0.01954968403269297</v>
+        <v>0.01907560087949589</v>
       </c>
       <c r="K39" s="3" t="n">
-        <v>0.005678402030863783</v>
+        <v>0.005210768922439657</v>
       </c>
       <c r="L39" s="3" t="n">
-        <v>0.005476890195030615</v>
+        <v>0.005009350788137912</v>
       </c>
       <c r="M39" s="6" t="inlineStr">
         <is>
@@ -2774,25 +2774,25 @@
         </is>
       </c>
       <c r="F40" s="3" t="n">
-        <v>0.4599126470316062</v>
+        <v>0.4577359993239898</v>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.2541335419367787</v>
+        <v>0.2522637938310215</v>
       </c>
       <c r="H40" s="3" t="n">
         <v>0.2814573608459154</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.1685122726963868</v>
+        <v>0.1667701746379502</v>
       </c>
       <c r="J40" s="3" t="n">
-        <v>0.04125814471937428</v>
+        <v>0.03970576582303531</v>
       </c>
       <c r="K40" s="5" t="n">
-        <v>-0.02132245655922538</v>
+        <v>-0.02278153601273381</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>-0.002972872538089866</v>
+        <v>-0.004459308807134854</v>
       </c>
       <c r="M40" s="6" t="inlineStr">
         <is>
@@ -2826,25 +2826,25 @@
         </is>
       </c>
       <c r="F41" s="3" t="n">
-        <v>0.3521189891256404</v>
+        <v>0.3463762879613776</v>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.2663067627150033</v>
+        <v>0.2609285220578998</v>
       </c>
       <c r="H41" s="3" t="n">
         <v>0.2810969245220378</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.1167721758113234</v>
+        <v>0.1120290363939891</v>
       </c>
       <c r="J41" s="3" t="n">
-        <v>0.05630612403464297</v>
+        <v>0.0518197952003483</v>
       </c>
       <c r="K41" s="5" t="n">
-        <v>-0.01154492023509646</v>
+        <v>-0.01574307304785894</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>-0.005491024287222812</v>
+        <v>-0.009714889123548009</v>
       </c>
       <c r="M41" s="6" t="inlineStr">
         <is>
@@ -2878,34 +2878,34 @@
         </is>
       </c>
       <c r="F42" s="3" t="n">
-        <v>0.4853274854011134</v>
+        <v>0.4797384365899835</v>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.2953196255677726</v>
+        <v>0.2904455458214075</v>
       </c>
       <c r="H42" s="3" t="n">
         <v>0.2764819660074971</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.1544167937583565</v>
+        <v>0.1500729087416719</v>
       </c>
       <c r="J42" s="3" t="n">
-        <v>0.07519585958133801</v>
+        <v>0.07115007021852815</v>
       </c>
       <c r="K42" s="3" t="n">
-        <v>0.01475748194014437</v>
-      </c>
-      <c r="L42" s="3" t="n">
-        <v>0.0005087505087504329</v>
+        <v>0.01093911248709989</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>-0.003256003256003281</v>
       </c>
       <c r="M42" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -2934,25 +2934,25 @@
         </is>
       </c>
       <c r="F43" s="3" t="n">
-        <v>0.5201936636107622</v>
+        <v>0.5281639378012448</v>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.2659110205765836</v>
+        <v>0.2725481077953158</v>
       </c>
       <c r="H43" s="3" t="n">
         <v>0.2751452288809066</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.2445187483403846</v>
+        <v>0.2510436772997047</v>
       </c>
       <c r="J43" s="5" t="n">
-        <v>-0.02431362500973122</v>
+        <v>-0.0191981662897418</v>
       </c>
       <c r="K43" s="5" t="n">
-        <v>-0.007241691452217758</v>
+        <v>-0.002036725720936272</v>
       </c>
       <c r="L43" s="3" t="n">
-        <v>0.007282031096240704</v>
+        <v>0.01256314373810929</v>
       </c>
       <c r="M43" s="6" t="inlineStr">
         <is>
@@ -2986,25 +2986,25 @@
         </is>
       </c>
       <c r="F44" s="3" t="n">
-        <v>0.4579929420519961</v>
+        <v>0.4537742124742992</v>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.2648118145490679</v>
+        <v>0.2611521461750907</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.2746931568502324</v>
+        <v>0.2746932458293212</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.176824454930451</v>
+        <v>0.1734192915770643</v>
       </c>
       <c r="J44" s="3" t="n">
-        <v>0.03461055372360944</v>
+        <v>0.03161688892695524</v>
       </c>
       <c r="K44" s="5" t="n">
-        <v>-0.007751937984496027</v>
-      </c>
-      <c r="L44" s="3" t="n">
-        <v>0.0002894356005789245</v>
+        <v>-0.01062302612690202</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>-0.002604920405209765</v>
       </c>
       <c r="M44" s="6" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3038,25 +3038,25 @@
         </is>
       </c>
       <c r="F45" s="3" t="n">
-        <v>0.51989100746336</v>
+        <v>0.507415196105621</v>
       </c>
       <c r="G45" s="3" t="n">
-        <v>0.1433221116145802</v>
+        <v>0.1339373130233699</v>
       </c>
       <c r="H45" s="3" t="n">
         <v>0.272020673916745</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>-0.06738050042579624</v>
+        <v>-0.07503577628972513</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>-0.007576273900549491</v>
+        <v>-0.01572244433840542</v>
       </c>
       <c r="K45" s="5" t="n">
-        <v>-0.1011764705882353</v>
+        <v>-0.1085543369890329</v>
       </c>
       <c r="L45" s="5" t="n">
-        <v>-0.001019458357342407</v>
+        <v>-0.009219449492487097</v>
       </c>
       <c r="M45" s="6" t="inlineStr">
         <is>
@@ -3090,34 +3090,34 @@
         </is>
       </c>
       <c r="F46" s="3" t="n">
-        <v>0.4780360083262694</v>
+        <v>0.4708269410467378</v>
       </c>
       <c r="G46" s="3" t="n">
-        <v>0.2880642025088083</v>
+        <v>0.2817818137687573</v>
       </c>
       <c r="H46" s="3" t="n">
         <v>0.2720092090620112</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>0.1276706089343866</v>
+        <v>0.1221705219649194</v>
       </c>
       <c r="J46" s="3" t="n">
-        <v>0.06210289172913863</v>
+        <v>0.05692260394940019</v>
       </c>
       <c r="K46" s="3" t="n">
-        <v>0.01262175881465222</v>
-      </c>
-      <c r="L46" s="3" t="n">
-        <v>0.0006778741865509641</v>
+        <v>0.007682809713266625</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>-0.004202819956616088</v>
       </c>
       <c r="M46" s="6" t="inlineStr">
         <is>
-          <t>STEADY_POSITIVE</t>
+          <t>COOLING</t>
         </is>
       </c>
       <c r="N46" s="7" t="inlineStr">
         <is>
-          <t>Positive across long, 6m, 3m, and 1m horizons; 1d up.</t>
+          <t>Positive trend losing velocity into 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3142,25 +3142,25 @@
         </is>
       </c>
       <c r="F47" s="3" t="n">
-        <v>0.302092867845597</v>
+        <v>0.2949426468949996</v>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.29778014653898</v>
+        <v>0.2906536081620317</v>
       </c>
       <c r="H47" s="3" t="n">
         <v>0.271524478834434</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.1338028625069978</v>
+        <v>0.1275767069484548</v>
       </c>
       <c r="J47" s="3" t="n">
-        <v>0.08007321214799523</v>
+        <v>0.07414217427781833</v>
       </c>
       <c r="K47" s="3" t="n">
-        <v>0.0206489675516226</v>
+        <v>0.01504424778761049</v>
       </c>
       <c r="L47" s="5" t="n">
-        <v>-0.005747126436781436</v>
+        <v>-0.01120689655172413</v>
       </c>
       <c r="M47" s="6" t="inlineStr">
         <is>
@@ -3194,25 +3194,25 @@
         </is>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.3994155046211489</v>
+        <v>0.3959750239705746</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.2797348233797869</v>
+        <v>0.2765884834321608</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.2706893713399177</v>
+        <v>0.2706892760225852</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.158058340173383</v>
+        <v>0.1552112391526741</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.0598448041540347</v>
+        <v>0.05723916234910775</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.007118539151965253</v>
+        <v>0.00464252553389044</v>
       </c>
       <c r="L48" s="5" t="n">
-        <v>-0.003063725490196068</v>
+        <v>-0.005514705882352922</v>
       </c>
       <c r="M48" s="6" t="inlineStr">
         <is>
@@ -3246,25 +3246,25 @@
         </is>
       </c>
       <c r="F49" s="3" t="n">
-        <v>0.4415124405147994</v>
+        <v>0.4341858207408995</v>
       </c>
       <c r="G49" s="3" t="n">
-        <v>0.1912250202822765</v>
+        <v>0.1851705093786817</v>
       </c>
       <c r="H49" s="3" t="n">
         <v>0.2690687318999239</v>
       </c>
       <c r="I49" s="3" t="n">
-        <v>0.05721466237300921</v>
+        <v>0.05184127145878792</v>
       </c>
       <c r="J49" s="5" t="n">
-        <v>-0.02341875623653566</v>
+        <v>-0.0283823203725635</v>
       </c>
       <c r="K49" s="5" t="n">
-        <v>-0.06133924007497005</v>
+        <v>-0.06611006985857892</v>
       </c>
       <c r="L49" s="5" t="n">
-        <v>-0.001269035532994844</v>
+        <v>-0.006345177664974555</v>
       </c>
       <c r="M49" s="6" t="inlineStr">
         <is>
@@ -3298,25 +3298,25 @@
         </is>
       </c>
       <c r="F50" s="3" t="n">
-        <v>0.4814455248901417</v>
+        <v>0.4829497341146292</v>
       </c>
       <c r="G50" s="3" t="n">
-        <v>0.2521514367630013</v>
+        <v>0.253422828596173</v>
       </c>
       <c r="H50" s="3" t="n">
         <v>0.2616444957840165</v>
       </c>
       <c r="I50" s="3" t="n">
-        <v>0.1838349351989175</v>
+        <v>0.1850369607880316</v>
       </c>
       <c r="J50" s="3" t="n">
-        <v>0.003364663480652119</v>
+        <v>0.004383445715283596</v>
       </c>
       <c r="K50" s="5" t="n">
-        <v>-0.007524353375881754</v>
+        <v>-0.006516627477326176</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>-0.002060323572128264</v>
+        <v>-0.001047049684196333</v>
       </c>
       <c r="M50" s="6" t="inlineStr">
         <is>
@@ -3354,25 +3354,25 @@
         </is>
       </c>
       <c r="F51" s="3" t="n">
-        <v>0.4436910464969233</v>
+        <v>0.4433850158727517</v>
       </c>
       <c r="G51" s="3" t="n">
-        <v>0.219417184885873</v>
+        <v>0.2191585529635238</v>
       </c>
       <c r="H51" s="3" t="n">
         <v>0.2613478852967264</v>
       </c>
       <c r="I51" s="3" t="n">
-        <v>0.1607046573974369</v>
+        <v>0.1604584780910083</v>
       </c>
       <c r="J51" s="3" t="n">
-        <v>0.02152869221345655</v>
+        <v>0.02131203139165039</v>
       </c>
       <c r="K51" s="5" t="n">
-        <v>-0.03324277219602223</v>
+        <v>-0.03344781628050031</v>
       </c>
       <c r="L51" s="5" t="n">
-        <v>-0.0009270540869842359</v>
+        <v>-0.001138952164009166</v>
       </c>
       <c r="M51" s="6" t="inlineStr">
         <is>
@@ -3406,25 +3406,25 @@
         </is>
       </c>
       <c r="F52" s="3" t="n">
-        <v>0.4805229879132382</v>
+        <v>0.4824007618922013</v>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.2514415899049023</v>
+        <v>0.2530287613287705</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>0.261174733777882</v>
+        <v>0.2611745995093557</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>0.1832698588160768</v>
+        <v>0.1847706959078919</v>
       </c>
       <c r="J52" s="3" t="n">
-        <v>0.003028268473278084</v>
+        <v>0.004300490543541757</v>
       </c>
       <c r="K52" s="5" t="n">
-        <v>-0.007717522094518814</v>
+        <v>-0.006458929781613443</v>
       </c>
       <c r="L52" s="5" t="n">
-        <v>-0.002100255925225336</v>
+        <v>-0.0008345387782352498</v>
       </c>
       <c r="M52" s="6" t="inlineStr">
         <is>
@@ -3462,25 +3462,25 @@
         </is>
       </c>
       <c r="F53" s="3" t="n">
-        <v>0.4526987060192829</v>
+        <v>0.4417065429442151</v>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.1249334073197237</v>
+        <v>0.1164216179998903</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.2514543680219057</v>
+        <v>0.251454498054406</v>
       </c>
       <c r="I53" s="5" t="n">
-        <v>-0.08658814704368756</v>
+        <v>-0.09349955634269114</v>
       </c>
       <c r="J53" s="5" t="n">
-        <v>-0.02610591128439199</v>
+        <v>-0.0334749646191046</v>
       </c>
       <c r="K53" s="5" t="n">
-        <v>-0.1010991402764175</v>
-      </c>
-      <c r="L53" s="3" t="n">
-        <v>0.00012108003390221</v>
+        <v>-0.1079007508978127</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>-0.007446422084998239</v>
       </c>
       <c r="M53" s="6" t="inlineStr">
         <is>
@@ -3489,7 +3489,7 @@
       </c>
       <c r="N53" s="7" t="inlineStr">
         <is>
-          <t>Established trend; 3m and 1m now negative; 1d up.</t>
+          <t>Established trend; 3m and 1m now negative; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3514,25 +3514,25 @@
         </is>
       </c>
       <c r="F54" s="3" t="n">
-        <v>0.6920808213364746</v>
+        <v>0.6725869408573588</v>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.3774403004818963</v>
+        <v>0.3615711725961601</v>
       </c>
       <c r="H54" s="3" t="n">
         <v>0.2462555099598109</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.06285312742431404</v>
+        <v>0.05060827572587723</v>
       </c>
       <c r="J54" s="3" t="n">
-        <v>0.1704318796017108</v>
+        <v>0.1569476413574515</v>
       </c>
       <c r="K54" s="3" t="n">
-        <v>0.1052631578947367</v>
+        <v>0.09252971137521215</v>
       </c>
       <c r="L54" s="3" t="n">
-        <v>0.0316957210776545</v>
+        <v>0.01980982567353418</v>
       </c>
       <c r="M54" s="6" t="inlineStr">
         <is>
@@ -3566,25 +3566,25 @@
         </is>
       </c>
       <c r="F55" s="3" t="n">
-        <v>0.3464755659205758</v>
+        <v>0.3394869143176966</v>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.1766354392723104</v>
+        <v>0.1705285708868121</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.2427385538381706</v>
+        <v>0.2427386810963186</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.03109419023878557</v>
+        <v>0.02574259203472851</v>
       </c>
       <c r="J55" s="3" t="n">
-        <v>0.01227531588670483</v>
+        <v>0.00702139164409421</v>
       </c>
       <c r="K55" s="5" t="n">
-        <v>-0.05319148936170215</v>
-      </c>
-      <c r="L55" s="3" t="n">
-        <v>0.0003423289781481209</v>
+        <v>-0.05810562695755495</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>-0.004849660523763455</v>
       </c>
       <c r="M55" s="6" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="N55" s="7" t="inlineStr">
         <is>
-          <t>Established trend; positive 3m but negative 1m; 1d up.</t>
+          <t>Established trend; positive 3m but negative 1m; 1d down.</t>
         </is>
       </c>
     </row>
@@ -3618,25 +3618,25 @@
         </is>
       </c>
       <c r="F56" s="3" t="n">
-        <v>0.4778351026344523</v>
+        <v>0.4769842982554859</v>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.2264826474790356</v>
+        <v>0.2257762838886272</v>
       </c>
       <c r="H56" s="3" t="n">
         <v>0.2382553739858415</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.1689658949284116</v>
+        <v>0.1682927567610619</v>
       </c>
       <c r="J56" s="3" t="n">
-        <v>0.02139729601737406</v>
+        <v>0.02080904647080994</v>
       </c>
       <c r="K56" s="5" t="n">
-        <v>-0.009507510933637553</v>
+        <v>-0.0100779615896559</v>
       </c>
       <c r="L56" s="5" t="n">
-        <v>-0.002680451847597021</v>
+        <v>-0.003254834386367866</v>
       </c>
       <c r="M56" s="6" t="inlineStr">
         <is>
@@ -3674,25 +3674,25 @@
         </is>
       </c>
       <c r="F57" s="3" t="n">
-        <v>0.1970270392823368</v>
+        <v>0.1879271870185353</v>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.2548869137101146</v>
+        <v>0.2453471329138988</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.2354908318314333</v>
+        <v>0.2354907572076095</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.1190700858764808</v>
+        <v>0.1105628658053108</v>
       </c>
       <c r="J57" s="3" t="n">
-        <v>0.1228123475764273</v>
+        <v>0.1142766786670237</v>
       </c>
       <c r="K57" s="3" t="n">
-        <v>0.01569909009355364</v>
+        <v>0.007977700884275407</v>
       </c>
       <c r="L57" s="5" t="n">
-        <v>-0.01442516943356353</v>
+        <v>-0.02191755269539264</v>
       </c>
       <c r="M57" s="6" t="inlineStr">
         <is>
@@ -3726,25 +3726,25 @@
         </is>
       </c>
       <c r="F58" s="3" t="n">
-        <v>0.1583533897709555</v>
+        <v>0.1490718325162885</v>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.2430939489162565</v>
+        <v>0.2331335378845987</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.2224347427376865</v>
+        <v>0.2224350179903087</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.1015085204950394</v>
+        <v>0.09268233042697038</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>0.1085689069443569</v>
+        <v>0.09968614326691805</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>0.01690004828585212</v>
+        <v>0.008751810719459074</v>
       </c>
       <c r="L58" s="5" t="n">
-        <v>-0.0173228346456693</v>
+        <v>-0.02519685039370079</v>
       </c>
       <c r="M58" s="6" t="inlineStr">
         <is>
@@ -3778,25 +3778,25 @@
         </is>
       </c>
       <c r="F59" s="3" t="n">
-        <v>0.3119478613897209</v>
+        <v>0.3039345434863461</v>
       </c>
       <c r="G59" s="3" t="n">
-        <v>0.2491846837553984</v>
+        <v>0.2415548045269671</v>
       </c>
       <c r="H59" s="3" t="n">
-        <v>0.2212734482656766</v>
+        <v>0.2212735309316951</v>
       </c>
       <c r="I59" s="3" t="n">
-        <v>0.1168902845103761</v>
+        <v>0.1100683694203266</v>
       </c>
       <c r="J59" s="3" t="n">
-        <v>0.1114630410072381</v>
+        <v>0.104674275273813</v>
       </c>
       <c r="K59" s="3" t="n">
-        <v>0.02285420642638081</v>
+        <v>0.01660665942690143</v>
       </c>
       <c r="L59" s="5" t="n">
-        <v>-0.01262272089761562</v>
+        <v>-0.01865357643758758</v>
       </c>
       <c r="M59" s="6" t="inlineStr">
         <is>
@@ -3834,25 +3834,25 @@
         </is>
       </c>
       <c r="F60" s="3" t="n">
-        <v>0.3700480430690825</v>
+        <v>0.3662727796993555</v>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.1751849954205564</v>
+        <v>0.1719465338207691</v>
       </c>
       <c r="H60" s="3" t="n">
         <v>0.2199209533338997</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.06697413279917575</v>
+        <v>0.06403386827018553</v>
       </c>
       <c r="J60" s="5" t="n">
-        <v>-0.05510123589555349</v>
+        <v>-0.05770509688353664</v>
       </c>
       <c r="K60" s="5" t="n">
-        <v>-0.03667119397456475</v>
+        <v>-0.03932584269662909</v>
       </c>
       <c r="L60" s="3" t="n">
-        <v>0.01140782991962652</v>
+        <v>0.008620689655172598</v>
       </c>
       <c r="M60" s="6" t="inlineStr">
         <is>
@@ -3886,25 +3886,25 @@
         </is>
       </c>
       <c r="F61" s="3" t="n">
-        <v>0.3529393194235411</v>
+        <v>0.3490614317191751</v>
       </c>
       <c r="G61" s="3" t="n">
-        <v>0.179815398400089</v>
+        <v>0.1764337481965261</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.2194131006507771</v>
+        <v>0.2194129748121567</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.1220610307949428</v>
+        <v>0.1188450347192911</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.01501704101434376</v>
+        <v>0.01210784915130469</v>
       </c>
       <c r="K61" s="5" t="n">
-        <v>-0.03247275449932074</v>
+        <v>-0.03524583344887844</v>
       </c>
       <c r="L61" s="5" t="n">
-        <v>-0.00154532967032972</v>
+        <v>-0.004407051282051322</v>
       </c>
       <c r="M61" s="6" t="inlineStr">
         <is>
@@ -3938,25 +3938,25 @@
         </is>
       </c>
       <c r="F62" s="3" t="n">
-        <v>0.3641706161501508</v>
+        <v>0.3615018673909776</v>
       </c>
       <c r="G62" s="3" t="n">
-        <v>0.1997138093082413</v>
+        <v>0.1973669313482933</v>
       </c>
       <c r="H62" s="3" t="n">
         <v>0.2086591557352897</v>
       </c>
       <c r="I62" s="3" t="n">
-        <v>0.1377647633414834</v>
+        <v>0.1355390699919743</v>
       </c>
       <c r="J62" s="3" t="n">
-        <v>0.04093744819898126</v>
+        <v>0.03890116826629364</v>
       </c>
       <c r="K62" s="5" t="n">
-        <v>-0.007401049654570779</v>
+        <v>-0.009342769906150128</v>
       </c>
       <c r="L62" s="5" t="n">
-        <v>-0.003615768138867992</v>
+        <v>-0.005564893151226546</v>
       </c>
       <c r="M62" s="6" t="inlineStr">
         <is>
@@ -3990,25 +3990,25 @@
         </is>
       </c>
       <c r="F63" s="3" t="n">
-        <v>0.3646408107623884</v>
+        <v>0.3609959178985416</v>
       </c>
       <c r="G63" s="3" t="n">
-        <v>0.1998712868884449</v>
+        <v>0.1966663722188706</v>
       </c>
       <c r="H63" s="3" t="n">
-        <v>0.2083811226627361</v>
+        <v>0.2083810079219492</v>
       </c>
       <c r="I63" s="3" t="n">
-        <v>0.1380204828733071</v>
+        <v>0.1349808824859942</v>
       </c>
       <c r="J63" s="3" t="n">
-        <v>0.04129957247782046</v>
+        <v>0.03851830919526433</v>
       </c>
       <c r="K63" s="5" t="n">
-        <v>-0.007042344186525606</v>
+        <v>-0.009694488432273718</v>
       </c>
       <c r="L63" s="5" t="n">
-        <v>-0.003437047756874034</v>
+        <v>-0.006098821583626068</v>
       </c>
       <c r="M63" s="6" t="inlineStr">
         <is>
@@ -4042,25 +4042,25 @@
         </is>
       </c>
       <c r="F64" s="3" t="n">
-        <v>0.3628138660580156</v>
+        <v>0.3603273505191504</v>
       </c>
       <c r="G64" s="3" t="n">
-        <v>0.1987248153376957</v>
+        <v>0.1965377033102444</v>
       </c>
       <c r="H64" s="3" t="n">
-        <v>0.2079414495256811</v>
+        <v>0.2079413343538561</v>
       </c>
       <c r="I64" s="3" t="n">
-        <v>0.137361154919005</v>
+        <v>0.1352862138138691</v>
       </c>
       <c r="J64" s="3" t="n">
-        <v>0.04074149258465898</v>
+        <v>0.03884272526603616</v>
       </c>
       <c r="K64" s="5" t="n">
-        <v>-0.007630033882523368</v>
+        <v>-0.009440550397020298</v>
       </c>
       <c r="L64" s="5" t="n">
-        <v>-0.003674418000753077</v>
+        <v>-0.005492151287344704</v>
       </c>
       <c r="M64" s="6" t="inlineStr">
         <is>
@@ -4094,25 +4094,25 @@
         </is>
       </c>
       <c r="F65" s="3" t="n">
-        <v>0.5064698377984327</v>
+        <v>0.4935301622015675</v>
       </c>
       <c r="G65" s="3" t="n">
-        <v>0.2198937426210152</v>
+        <v>0.2094155844155843</v>
       </c>
       <c r="H65" s="3" t="n">
         <v>0.2054309327036601</v>
       </c>
       <c r="I65" s="5" t="n">
-        <v>-0.1458979127918992</v>
+        <v>-0.1532341392849762</v>
       </c>
       <c r="J65" s="3" t="n">
-        <v>0.01572868026542151</v>
+        <v>0.007004177930695521</v>
       </c>
       <c r="K65" s="3" t="n">
-        <v>0.01199804113614089</v>
+        <v>0.003305582761997883</v>
       </c>
       <c r="L65" s="5" t="n">
-        <v>-0.008754047247871544</v>
+        <v>-0.01726825758484229</v>
       </c>
       <c r="M65" s="6" t="inlineStr">
         <is>
@@ -4146,25 +4146,25 @@
         </is>
       </c>
       <c r="F66" s="3" t="n">
-        <v>0.2726696157562489</v>
+        <v>0.2704254443978933</v>
       </c>
       <c r="G66" s="3" t="n">
-        <v>0.1799822630071801</v>
+        <v>0.177901635994915</v>
       </c>
       <c r="H66" s="3" t="n">
         <v>0.2040428471746563</v>
       </c>
       <c r="I66" s="3" t="n">
-        <v>0.1063113418612354</v>
+        <v>0.1043606165545807</v>
       </c>
       <c r="J66" s="3" t="n">
-        <v>0.03621711241274772</v>
+        <v>0.03438998213948152</v>
       </c>
       <c r="K66" s="5" t="n">
-        <v>-0.01998316274535861</v>
+        <v>-0.02171119677433653</v>
       </c>
       <c r="L66" s="5" t="n">
-        <v>-0.006289873303980564</v>
+        <v>-0.008042052295803792</v>
       </c>
       <c r="M66" s="6" t="inlineStr">
         <is>
@@ -4198,25 +4198,25 @@
         </is>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0.5030009319664492</v>
+        <v>0.490102516309413</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0.2178824950913758</v>
+        <v>0.2074309016764839</v>
       </c>
       <c r="H67" s="3" t="n">
         <v>0.2036550370034738</v>
       </c>
       <c r="I67" s="5" t="n">
-        <v>-0.1467631684760755</v>
+        <v>-0.1540854548917528</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0.01487653233317388</v>
+        <v>0.00616709039192509</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0.01182021231209363</v>
+        <v>0.003136999021256415</v>
       </c>
       <c r="L67" s="5" t="n">
-        <v>-0.008825626275290599</v>
+        <v>-0.01733166162696353</v>
       </c>
       <c r="M67" s="6" t="inlineStr">
         <is>
@@ -4254,25 +4254,25 @@
         </is>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0.3825287040841341</v>
+        <v>0.3820204010679817</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0.1947313627138785</v>
+        <v>0.1942919732406341</v>
       </c>
       <c r="H68" s="3" t="n">
         <v>0.2022009837590333</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0.1460628386989751</v>
+        <v>0.1456413481759029</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0.04055206801918354</v>
+        <v>0.04016938146778015</v>
       </c>
       <c r="K68" s="5" t="n">
-        <v>-0.006213288082495771</v>
+        <v>-0.006578775616760346</v>
       </c>
       <c r="L68" s="5" t="n">
-        <v>-0.003977079463094224</v>
+        <v>-0.00434338941364254</v>
       </c>
       <c r="M68" s="6" t="inlineStr">
         <is>
@@ -4306,25 +4306,25 @@
         </is>
       </c>
       <c r="F69" s="3" t="n">
-        <v>0.3783788556252263</v>
+        <v>0.378153895760954</v>
       </c>
       <c r="G69" s="3" t="n">
-        <v>0.2092040530621921</v>
+        <v>0.2090065997550297</v>
       </c>
       <c r="H69" s="3" t="n">
         <v>0.1940001484106915</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0.1121491845136178</v>
+        <v>0.1119675794867541</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0.05113638419241129</v>
+        <v>0.05096474206566515</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0.01273358690259641</v>
+        <v>0.01256821564412092</v>
       </c>
       <c r="L69" s="5" t="n">
-        <v>-0.003255